--- a/Raw Sales Data/Amazon.xlsx
+++ b/Raw Sales Data/Amazon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2131" uniqueCount="745">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2247" uniqueCount="780">
   <si>
     <t>amazon-order-id</t>
   </si>
@@ -2254,6 +2254,111 @@
   </si>
   <si>
     <t>2026-03-01T03:54:07+00:00</t>
+  </si>
+  <si>
+    <t>202-9915845-2691544</t>
+  </si>
+  <si>
+    <t>2026-03-02T18:36:25+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-03T04:53:43+00:00</t>
+  </si>
+  <si>
+    <t>CHEDDLETON</t>
+  </si>
+  <si>
+    <t>ST13 7JJ</t>
+  </si>
+  <si>
+    <t>204-1019426-5898762</t>
+  </si>
+  <si>
+    <t>2026-03-02T17:18:40+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-02T20:05:34+00:00</t>
+  </si>
+  <si>
+    <t>LLANGOLLEN</t>
+  </si>
+  <si>
+    <t>LL20 8BU</t>
+  </si>
+  <si>
+    <t>205-9793985-5567544</t>
+  </si>
+  <si>
+    <t>2026-03-02T16:36:48+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-02T17:06:49+00:00</t>
+  </si>
+  <si>
+    <t>BALLYMONEY</t>
+  </si>
+  <si>
+    <t>Antrim</t>
+  </si>
+  <si>
+    <t>BT53 6RR</t>
+  </si>
+  <si>
+    <t>204-9006195-0597907</t>
+  </si>
+  <si>
+    <t>2026-03-02T10:38:04+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-02T20:04:34+00:00</t>
+  </si>
+  <si>
+    <t>Ipswich</t>
+  </si>
+  <si>
+    <t>IP2 9DZ</t>
+  </si>
+  <si>
+    <t>206-4636978-7341159</t>
+  </si>
+  <si>
+    <t>2026-03-02T08:43:32+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-02T10:36:59+00:00</t>
+  </si>
+  <si>
+    <t>NE5 2HX</t>
+  </si>
+  <si>
+    <t>203-8386789-4369953</t>
+  </si>
+  <si>
+    <t>2026-03-02T08:42:21+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-02T09:26:26+00:00</t>
+  </si>
+  <si>
+    <t>ALDERSHOT</t>
+  </si>
+  <si>
+    <t>GU12 6RT</t>
+  </si>
+  <si>
+    <t>026-5313264-3260342</t>
+  </si>
+  <si>
+    <t>2026-03-02T07:57:32+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-02T10:02:11+00:00</t>
+  </si>
+  <si>
+    <t>IPSWICH</t>
+  </si>
+  <si>
+    <t>IP2 9NY</t>
   </si>
 </sst>
 </file>
@@ -3060,7 +3165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG131"/>
+  <dimension ref="A1:AG138"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
@@ -3171,13 +3276,13 @@
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>714</v>
+        <v>745</v>
       </c>
       <c r="C2" t="s">
-        <v>715</v>
+        <v>746</v>
       </c>
       <c r="D2" t="s">
-        <v>716</v>
+        <v>747</v>
       </c>
       <c r="E2" t="s">
         <v>98</v>
@@ -3219,13 +3324,10 @@
         <v>2</v>
       </c>
       <c r="Y2" t="s">
-        <v>717</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>51</v>
+        <v>748</v>
       </c>
       <c r="AA2" t="s">
-        <v>718</v>
+        <v>749</v>
       </c>
       <c r="AB2" t="s">
         <v>39</v>
@@ -3239,13 +3341,13 @@
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>719</v>
+        <v>750</v>
       </c>
       <c r="C3" t="s">
-        <v>720</v>
+        <v>751</v>
       </c>
       <c r="D3" t="s">
-        <v>721</v>
+        <v>752</v>
       </c>
       <c r="E3" t="s">
         <v>33</v>
@@ -3263,13 +3365,13 @@
         <v>54</v>
       </c>
       <c r="K3" t="s">
-        <v>722</v>
+        <v>40</v>
       </c>
       <c r="L3" t="s">
-        <v>723</v>
+        <v>41</v>
       </c>
       <c r="M3" t="s">
-        <v>724</v>
+        <v>42</v>
       </c>
       <c r="N3" t="s">
         <v>33</v>
@@ -3281,19 +3383,16 @@
         <v>38</v>
       </c>
       <c r="Q3">
-        <v>12.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R3">
-        <v>2.17</v>
+        <v>11</v>
       </c>
       <c r="Y3" t="s">
-        <v>725</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>726</v>
+        <v>753</v>
       </c>
       <c r="AA3" t="s">
-        <v>727</v>
+        <v>754</v>
       </c>
       <c r="AB3" t="s">
         <v>39</v>
@@ -3307,16 +3406,16 @@
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>728</v>
+        <v>755</v>
       </c>
       <c r="C4" t="s">
-        <v>729</v>
+        <v>756</v>
       </c>
       <c r="D4" t="s">
-        <v>730</v>
+        <v>757</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F4" t="s">
         <v>34</v>
@@ -3331,16 +3430,16 @@
         <v>54</v>
       </c>
       <c r="K4" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L4" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M4" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N4" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O4">
         <v>1</v>
@@ -3349,16 +3448,25 @@
         <v>38</v>
       </c>
       <c r="Q4">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R4">
-        <v>2</v>
+        <v>11</v>
+      </c>
+      <c r="S4">
+        <v>6.99</v>
+      </c>
+      <c r="T4">
+        <v>1.17</v>
       </c>
       <c r="Y4" t="s">
-        <v>731</v>
+        <v>758</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>759</v>
       </c>
       <c r="AA4" t="s">
-        <v>732</v>
+        <v>760</v>
       </c>
       <c r="AB4" t="s">
         <v>39</v>
@@ -3372,13 +3480,13 @@
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>733</v>
+        <v>761</v>
       </c>
       <c r="C5" t="s">
-        <v>734</v>
+        <v>762</v>
       </c>
       <c r="D5" t="s">
-        <v>735</v>
+        <v>763</v>
       </c>
       <c r="E5" t="s">
         <v>33</v>
@@ -3396,13 +3504,13 @@
         <v>54</v>
       </c>
       <c r="K5" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="L5" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="M5" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="N5" t="s">
         <v>33</v>
@@ -3414,16 +3522,19 @@
         <v>38</v>
       </c>
       <c r="Q5">
-        <v>40.99</v>
+        <v>11.99</v>
       </c>
       <c r="R5">
-        <v>6.83</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="s">
-        <v>736</v>
+        <v>764</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>279</v>
       </c>
       <c r="AA5" t="s">
-        <v>737</v>
+        <v>765</v>
       </c>
       <c r="AB5" t="s">
         <v>39</v>
@@ -3437,13 +3548,13 @@
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>738</v>
+        <v>766</v>
       </c>
       <c r="C6" t="s">
-        <v>739</v>
+        <v>767</v>
       </c>
       <c r="D6" t="s">
-        <v>740</v>
+        <v>768</v>
       </c>
       <c r="E6" t="s">
         <v>33</v>
@@ -3461,13 +3572,13 @@
         <v>54</v>
       </c>
       <c r="K6" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L6" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M6" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="N6" t="s">
         <v>33</v>
@@ -3479,16 +3590,19 @@
         <v>38</v>
       </c>
       <c r="Q6">
-        <v>40.99</v>
+        <v>11.99</v>
       </c>
       <c r="R6">
-        <v>6.83</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="s">
-        <v>741</v>
+        <v>91</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>121</v>
       </c>
       <c r="AA6" t="s">
-        <v>742</v>
+        <v>769</v>
       </c>
       <c r="AB6" t="s">
         <v>39</v>
@@ -3502,13 +3616,13 @@
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>708</v>
+        <v>770</v>
       </c>
       <c r="C7" t="s">
-        <v>709</v>
+        <v>771</v>
       </c>
       <c r="D7" t="s">
-        <v>743</v>
+        <v>772</v>
       </c>
       <c r="E7" t="s">
         <v>33</v>
@@ -3550,13 +3664,13 @@
         <v>11</v>
       </c>
       <c r="Y7" t="s">
-        <v>711</v>
+        <v>773</v>
       </c>
       <c r="Z7" t="s">
-        <v>712</v>
+        <v>64</v>
       </c>
       <c r="AA7" t="s">
-        <v>713</v>
+        <v>774</v>
       </c>
       <c r="AB7" t="s">
         <v>39</v>
@@ -3570,13 +3684,13 @@
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>643</v>
+        <v>775</v>
       </c>
       <c r="C8" t="s">
-        <v>644</v>
+        <v>776</v>
       </c>
       <c r="D8" t="s">
-        <v>744</v>
+        <v>777</v>
       </c>
       <c r="E8" t="s">
         <v>33</v>
@@ -3594,13 +3708,13 @@
         <v>54</v>
       </c>
       <c r="K8" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L8" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M8" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="N8" t="s">
         <v>33</v>
@@ -3612,16 +3726,16 @@
         <v>38</v>
       </c>
       <c r="Q8">
-        <v>14.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R8">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="Y8" t="s">
-        <v>646</v>
+        <v>778</v>
       </c>
       <c r="AA8" t="s">
-        <v>647</v>
+        <v>779</v>
       </c>
       <c r="AB8" t="s">
         <v>39</v>
@@ -3635,13 +3749,13 @@
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="C9" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="D9" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="E9" t="s">
         <v>98</v>
@@ -3659,13 +3773,13 @@
         <v>54</v>
       </c>
       <c r="K9" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L9" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M9" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N9" t="s">
         <v>99</v>
@@ -3677,19 +3791,19 @@
         <v>38</v>
       </c>
       <c r="Q9">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R9">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="Z9" t="s">
-        <v>712</v>
+        <v>51</v>
       </c>
       <c r="AA9" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="AB9" t="s">
         <v>39</v>
@@ -3703,22 +3817,22 @@
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>138</v>
+        <v>719</v>
       </c>
       <c r="C10" t="s">
-        <v>139</v>
+        <v>720</v>
       </c>
       <c r="D10" t="s">
-        <v>187</v>
+        <v>721</v>
       </c>
       <c r="E10" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s">
         <v>34</v>
       </c>
       <c r="G10" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="H10" t="s">
         <v>36</v>
@@ -3727,25 +3841,40 @@
         <v>54</v>
       </c>
       <c r="K10" t="s">
-        <v>141</v>
+        <v>722</v>
       </c>
       <c r="L10" t="s">
-        <v>142</v>
+        <v>723</v>
       </c>
       <c r="M10" t="s">
-        <v>143</v>
+        <v>724</v>
+      </c>
+      <c r="N10" t="s">
+        <v>33</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P10" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q10">
+        <v>12.99</v>
+      </c>
+      <c r="R10">
+        <v>2.17</v>
       </c>
       <c r="Y10" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA10">
-        <v>80100</v>
+        <v>725</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>726</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>727</v>
       </c>
       <c r="AB10" t="s">
-        <v>145</v>
+        <v>39</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
@@ -3756,22 +3885,22 @@
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>146</v>
+        <v>728</v>
       </c>
       <c r="C11" t="s">
-        <v>147</v>
+        <v>729</v>
       </c>
       <c r="D11" t="s">
-        <v>148</v>
+        <v>730</v>
       </c>
       <c r="E11" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
         <v>34</v>
       </c>
       <c r="G11" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="H11" t="s">
         <v>36</v>
@@ -3780,25 +3909,37 @@
         <v>54</v>
       </c>
       <c r="K11" t="s">
-        <v>141</v>
+        <v>72</v>
       </c>
       <c r="L11" t="s">
-        <v>142</v>
+        <v>73</v>
       </c>
       <c r="M11" t="s">
-        <v>143</v>
+        <v>74</v>
+      </c>
+      <c r="N11" t="s">
+        <v>33</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P11" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q11">
+        <v>11.99</v>
+      </c>
+      <c r="R11">
+        <v>2</v>
       </c>
       <c r="Y11" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA11">
-        <v>80100</v>
+        <v>731</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>732</v>
       </c>
       <c r="AB11" t="s">
-        <v>145</v>
+        <v>39</v>
       </c>
       <c r="AD11" t="b">
         <v>0</v>
@@ -3809,22 +3950,22 @@
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>632</v>
+        <v>733</v>
       </c>
       <c r="C12" t="s">
-        <v>633</v>
+        <v>734</v>
       </c>
       <c r="D12" t="s">
-        <v>634</v>
+        <v>735</v>
       </c>
       <c r="E12" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F12" t="s">
         <v>34</v>
       </c>
       <c r="G12" t="s">
-        <v>635</v>
+        <v>35</v>
       </c>
       <c r="H12" t="s">
         <v>36</v>
@@ -3833,37 +3974,37 @@
         <v>54</v>
       </c>
       <c r="K12" t="s">
-        <v>636</v>
+        <v>43</v>
       </c>
       <c r="L12" t="s">
-        <v>637</v>
+        <v>44</v>
       </c>
       <c r="M12" t="s">
-        <v>638</v>
+        <v>45</v>
+      </c>
+      <c r="N12" t="s">
+        <v>33</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="Q12">
-        <v>22.9</v>
+        <v>40.99</v>
       </c>
       <c r="R12">
-        <v>4.8099999999999996</v>
+        <v>6.83</v>
       </c>
       <c r="Y12" t="s">
-        <v>639</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>640</v>
+        <v>736</v>
       </c>
       <c r="AA12" t="s">
-        <v>641</v>
+        <v>737</v>
       </c>
       <c r="AB12" t="s">
-        <v>642</v>
+        <v>39</v>
       </c>
       <c r="AD12" t="b">
         <v>0</v>
@@ -3874,16 +4015,16 @@
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>643</v>
+        <v>738</v>
       </c>
       <c r="C13" t="s">
-        <v>644</v>
+        <v>739</v>
       </c>
       <c r="D13" t="s">
-        <v>645</v>
+        <v>740</v>
       </c>
       <c r="E13" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F13" t="s">
         <v>34</v>
@@ -3898,16 +4039,16 @@
         <v>54</v>
       </c>
       <c r="K13" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="L13" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="M13" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="N13" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O13">
         <v>1</v>
@@ -3916,16 +4057,16 @@
         <v>38</v>
       </c>
       <c r="Q13">
-        <v>14.99</v>
+        <v>40.99</v>
       </c>
       <c r="R13">
-        <v>2.5</v>
+        <v>6.83</v>
       </c>
       <c r="Y13" t="s">
-        <v>646</v>
+        <v>741</v>
       </c>
       <c r="AA13" t="s">
-        <v>647</v>
+        <v>742</v>
       </c>
       <c r="AB13" t="s">
         <v>39</v>
@@ -3939,13 +4080,13 @@
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>609</v>
+        <v>708</v>
       </c>
       <c r="C14" t="s">
-        <v>610</v>
+        <v>709</v>
       </c>
       <c r="D14" t="s">
-        <v>611</v>
+        <v>743</v>
       </c>
       <c r="E14" t="s">
         <v>33</v>
@@ -3963,13 +4104,13 @@
         <v>54</v>
       </c>
       <c r="K14" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L14" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M14" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="N14" t="s">
         <v>33</v>
@@ -3981,19 +4122,19 @@
         <v>38</v>
       </c>
       <c r="Q14">
-        <v>14.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R14">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="Y14" t="s">
-        <v>612</v>
+        <v>711</v>
       </c>
       <c r="Z14" t="s">
-        <v>613</v>
+        <v>712</v>
       </c>
       <c r="AA14" t="s">
-        <v>614</v>
+        <v>713</v>
       </c>
       <c r="AB14" t="s">
         <v>39</v>
@@ -4007,16 +4148,16 @@
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>493</v>
+        <v>643</v>
       </c>
       <c r="C15" t="s">
-        <v>494</v>
+        <v>644</v>
       </c>
       <c r="D15" t="s">
-        <v>648</v>
+        <v>744</v>
       </c>
       <c r="E15" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F15" t="s">
         <v>34</v>
@@ -4031,22 +4172,34 @@
         <v>54</v>
       </c>
       <c r="K15" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L15" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M15" t="s">
-        <v>42</v>
+        <v>83</v>
+      </c>
+      <c r="N15" t="s">
+        <v>33</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P15" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q15">
+        <v>14.99</v>
+      </c>
+      <c r="R15">
+        <v>2.5</v>
       </c>
       <c r="Y15" t="s">
-        <v>495</v>
+        <v>646</v>
       </c>
       <c r="AA15" t="s">
-        <v>496</v>
+        <v>647</v>
       </c>
       <c r="AB15" t="s">
         <v>39</v>
@@ -4060,13 +4213,13 @@
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>615</v>
+        <v>708</v>
       </c>
       <c r="C16" t="s">
-        <v>616</v>
+        <v>709</v>
       </c>
       <c r="D16" t="s">
-        <v>617</v>
+        <v>710</v>
       </c>
       <c r="E16" t="s">
         <v>98</v>
@@ -4084,13 +4237,13 @@
         <v>54</v>
       </c>
       <c r="K16" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L16" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M16" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N16" t="s">
         <v>99</v>
@@ -4102,16 +4255,19 @@
         <v>38</v>
       </c>
       <c r="Q16">
-        <v>40.99</v>
+        <v>65.989999999999995</v>
+      </c>
+      <c r="R16">
+        <v>11</v>
       </c>
       <c r="Y16" t="s">
-        <v>618</v>
+        <v>711</v>
       </c>
       <c r="Z16" t="s">
-        <v>619</v>
+        <v>712</v>
       </c>
       <c r="AA16" t="s">
-        <v>620</v>
+        <v>713</v>
       </c>
       <c r="AB16" t="s">
         <v>39</v>
@@ -4125,22 +4281,22 @@
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>621</v>
+        <v>138</v>
       </c>
       <c r="C17" t="s">
-        <v>622</v>
+        <v>139</v>
       </c>
       <c r="D17" t="s">
-        <v>623</v>
+        <v>187</v>
       </c>
       <c r="E17" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F17" t="s">
         <v>34</v>
       </c>
       <c r="G17" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="H17" t="s">
         <v>36</v>
@@ -4149,46 +4305,25 @@
         <v>54</v>
       </c>
       <c r="K17" t="s">
-        <v>40</v>
+        <v>141</v>
       </c>
       <c r="L17" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="M17" t="s">
-        <v>42</v>
-      </c>
-      <c r="N17" t="s">
-        <v>33</v>
+        <v>143</v>
       </c>
       <c r="O17">
-        <v>1</v>
-      </c>
-      <c r="P17" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q17">
-        <v>64.989999999999995</v>
-      </c>
-      <c r="R17">
-        <v>10.83</v>
-      </c>
-      <c r="S17">
-        <v>6.99</v>
-      </c>
-      <c r="T17">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="s">
-        <v>624</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>625</v>
-      </c>
-      <c r="AA17" t="s">
-        <v>626</v>
+        <v>144</v>
+      </c>
+      <c r="AA17">
+        <v>80100</v>
       </c>
       <c r="AB17" t="s">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="AD17" t="b">
         <v>0</v>
@@ -4199,22 +4334,22 @@
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>627</v>
+        <v>146</v>
       </c>
       <c r="C18" t="s">
-        <v>628</v>
+        <v>147</v>
       </c>
       <c r="D18" t="s">
-        <v>629</v>
+        <v>148</v>
       </c>
       <c r="E18" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F18" t="s">
         <v>34</v>
       </c>
       <c r="G18" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="H18" t="s">
         <v>36</v>
@@ -4223,37 +4358,25 @@
         <v>54</v>
       </c>
       <c r="K18" t="s">
-        <v>72</v>
+        <v>141</v>
       </c>
       <c r="L18" t="s">
-        <v>73</v>
+        <v>142</v>
       </c>
       <c r="M18" t="s">
-        <v>74</v>
-      </c>
-      <c r="N18" t="s">
-        <v>33</v>
+        <v>143</v>
       </c>
       <c r="O18">
-        <v>1</v>
-      </c>
-      <c r="P18" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q18">
-        <v>11.99</v>
-      </c>
-      <c r="R18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="s">
-        <v>630</v>
-      </c>
-      <c r="AA18" t="s">
-        <v>631</v>
+        <v>144</v>
+      </c>
+      <c r="AA18">
+        <v>80100</v>
       </c>
       <c r="AB18" t="s">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="AD18" t="b">
         <v>0</v>
@@ -4264,22 +4387,22 @@
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>649</v>
+        <v>632</v>
       </c>
       <c r="C19" t="s">
-        <v>650</v>
+        <v>633</v>
       </c>
       <c r="D19" t="s">
-        <v>651</v>
+        <v>634</v>
       </c>
       <c r="E19" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F19" t="s">
         <v>34</v>
       </c>
       <c r="G19" t="s">
-        <v>35</v>
+        <v>635</v>
       </c>
       <c r="H19" t="s">
         <v>36</v>
@@ -4288,40 +4411,37 @@
         <v>54</v>
       </c>
       <c r="K19" t="s">
-        <v>48</v>
+        <v>636</v>
       </c>
       <c r="L19" t="s">
-        <v>49</v>
+        <v>637</v>
       </c>
       <c r="M19" t="s">
-        <v>50</v>
-      </c>
-      <c r="N19" t="s">
-        <v>33</v>
+        <v>638</v>
       </c>
       <c r="O19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P19" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="Q19">
-        <v>39.99</v>
+        <v>22.9</v>
       </c>
       <c r="R19">
-        <v>6.67</v>
+        <v>4.8099999999999996</v>
       </c>
       <c r="Y19" t="s">
-        <v>652</v>
+        <v>639</v>
       </c>
       <c r="Z19" t="s">
-        <v>653</v>
+        <v>640</v>
       </c>
       <c r="AA19" t="s">
-        <v>654</v>
+        <v>641</v>
       </c>
       <c r="AB19" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="AD19" t="b">
         <v>0</v>
@@ -4332,16 +4452,16 @@
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>655</v>
+        <v>643</v>
       </c>
       <c r="C20" t="s">
-        <v>656</v>
+        <v>644</v>
       </c>
       <c r="D20" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="E20" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F20" t="s">
         <v>34</v>
@@ -4365,7 +4485,7 @@
         <v>83</v>
       </c>
       <c r="N20" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O20">
         <v>1</v>
@@ -4380,10 +4500,10 @@
         <v>2.5</v>
       </c>
       <c r="Y20" t="s">
-        <v>658</v>
+        <v>646</v>
       </c>
       <c r="AA20" t="s">
-        <v>659</v>
+        <v>647</v>
       </c>
       <c r="AB20" t="s">
         <v>39</v>
@@ -4397,13 +4517,13 @@
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>571</v>
+        <v>609</v>
       </c>
       <c r="C21" t="s">
-        <v>572</v>
+        <v>610</v>
       </c>
       <c r="D21" t="s">
-        <v>660</v>
+        <v>611</v>
       </c>
       <c r="E21" t="s">
         <v>33</v>
@@ -4421,13 +4541,13 @@
         <v>54</v>
       </c>
       <c r="K21" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L21" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M21" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="N21" t="s">
         <v>33</v>
@@ -4439,16 +4559,19 @@
         <v>38</v>
       </c>
       <c r="Q21">
-        <v>64.989999999999995</v>
+        <v>14.99</v>
       </c>
       <c r="R21">
-        <v>10.83</v>
+        <v>2.5</v>
       </c>
       <c r="Y21" t="s">
-        <v>573</v>
+        <v>612</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>613</v>
       </c>
       <c r="AA21" t="s">
-        <v>574</v>
+        <v>614</v>
       </c>
       <c r="AB21" t="s">
         <v>39</v>
@@ -4462,16 +4585,16 @@
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>599</v>
+        <v>493</v>
       </c>
       <c r="C22" t="s">
-        <v>600</v>
+        <v>494</v>
       </c>
       <c r="D22" t="s">
-        <v>601</v>
+        <v>648</v>
       </c>
       <c r="E22" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F22" t="s">
         <v>34</v>
@@ -4486,34 +4609,22 @@
         <v>54</v>
       </c>
       <c r="K22" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L22" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M22" t="s">
-        <v>83</v>
-      </c>
-      <c r="N22" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O22">
-        <v>1</v>
-      </c>
-      <c r="P22" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q22">
-        <v>14.99</v>
-      </c>
-      <c r="R22">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="s">
-        <v>61</v>
+        <v>495</v>
       </c>
       <c r="AA22" t="s">
-        <v>602</v>
+        <v>496</v>
       </c>
       <c r="AB22" t="s">
         <v>39</v>
@@ -4527,16 +4638,16 @@
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>589</v>
+        <v>615</v>
       </c>
       <c r="C23" t="s">
-        <v>590</v>
+        <v>616</v>
       </c>
       <c r="D23" t="s">
-        <v>591</v>
+        <v>617</v>
       </c>
       <c r="E23" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F23" t="s">
         <v>34</v>
@@ -4551,16 +4662,16 @@
         <v>54</v>
       </c>
       <c r="K23" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L23" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M23" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N23" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O23">
         <v>1</v>
@@ -4569,16 +4680,16 @@
         <v>38</v>
       </c>
       <c r="Q23">
-        <v>64.989999999999995</v>
-      </c>
-      <c r="R23">
-        <v>10.83</v>
+        <v>40.99</v>
       </c>
       <c r="Y23" t="s">
-        <v>592</v>
+        <v>618</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>619</v>
       </c>
       <c r="AA23" t="s">
-        <v>593</v>
+        <v>620</v>
       </c>
       <c r="AB23" t="s">
         <v>39</v>
@@ -4592,13 +4703,13 @@
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>594</v>
+        <v>621</v>
       </c>
       <c r="C24" t="s">
-        <v>595</v>
+        <v>622</v>
       </c>
       <c r="D24" t="s">
-        <v>596</v>
+        <v>623</v>
       </c>
       <c r="E24" t="s">
         <v>33</v>
@@ -4639,11 +4750,20 @@
       <c r="R24">
         <v>10.83</v>
       </c>
+      <c r="S24">
+        <v>6.99</v>
+      </c>
+      <c r="T24">
+        <v>1.17</v>
+      </c>
       <c r="Y24" t="s">
-        <v>597</v>
+        <v>624</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>625</v>
       </c>
       <c r="AA24" t="s">
-        <v>598</v>
+        <v>626</v>
       </c>
       <c r="AB24" t="s">
         <v>39</v>
@@ -4657,13 +4777,13 @@
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>603</v>
+        <v>627</v>
       </c>
       <c r="C25" t="s">
-        <v>604</v>
+        <v>628</v>
       </c>
       <c r="D25" t="s">
-        <v>605</v>
+        <v>629</v>
       </c>
       <c r="E25" t="s">
         <v>33</v>
@@ -4681,13 +4801,13 @@
         <v>54</v>
       </c>
       <c r="K25" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L25" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M25" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N25" t="s">
         <v>33</v>
@@ -4699,19 +4819,16 @@
         <v>38</v>
       </c>
       <c r="Q25">
-        <v>64.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R25">
-        <v>10.83</v>
+        <v>2</v>
       </c>
       <c r="Y25" t="s">
-        <v>606</v>
-      </c>
-      <c r="Z25" t="s">
-        <v>607</v>
+        <v>630</v>
       </c>
       <c r="AA25" t="s">
-        <v>608</v>
+        <v>631</v>
       </c>
       <c r="AB25" t="s">
         <v>39</v>
@@ -4725,13 +4842,13 @@
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>578</v>
+        <v>649</v>
       </c>
       <c r="C26" t="s">
-        <v>579</v>
+        <v>650</v>
       </c>
       <c r="D26" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="E26" t="s">
         <v>33</v>
@@ -4749,13 +4866,13 @@
         <v>54</v>
       </c>
       <c r="K26" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L26" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M26" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N26" t="s">
         <v>33</v>
@@ -4767,19 +4884,19 @@
         <v>38</v>
       </c>
       <c r="Q26">
-        <v>64.989999999999995</v>
+        <v>39.99</v>
       </c>
       <c r="R26">
-        <v>10.83</v>
+        <v>6.67</v>
       </c>
       <c r="Y26" t="s">
-        <v>580</v>
+        <v>652</v>
       </c>
       <c r="Z26" t="s">
-        <v>581</v>
+        <v>653</v>
       </c>
       <c r="AA26" t="s">
-        <v>582</v>
+        <v>654</v>
       </c>
       <c r="AB26" t="s">
         <v>39</v>
@@ -4793,16 +4910,16 @@
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>575</v>
+        <v>655</v>
       </c>
       <c r="C27" t="s">
-        <v>576</v>
+        <v>656</v>
       </c>
       <c r="D27" t="s">
-        <v>577</v>
+        <v>657</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F27" t="s">
         <v>34</v>
@@ -4817,22 +4934,34 @@
         <v>54</v>
       </c>
       <c r="K27" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L27" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M27" t="s">
-        <v>42</v>
+        <v>83</v>
+      </c>
+      <c r="N27" t="s">
+        <v>33</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P27" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q27">
+        <v>14.99</v>
+      </c>
+      <c r="R27">
+        <v>2.5</v>
       </c>
       <c r="Y27" t="s">
-        <v>573</v>
+        <v>658</v>
       </c>
       <c r="AA27" t="s">
-        <v>574</v>
+        <v>659</v>
       </c>
       <c r="AB27" t="s">
         <v>39</v>
@@ -4846,13 +4975,13 @@
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>518</v>
+        <v>571</v>
       </c>
       <c r="C28" t="s">
-        <v>519</v>
+        <v>572</v>
       </c>
       <c r="D28" t="s">
-        <v>583</v>
+        <v>660</v>
       </c>
       <c r="E28" t="s">
         <v>33</v>
@@ -4870,13 +4999,13 @@
         <v>54</v>
       </c>
       <c r="K28" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L28" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M28" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N28" t="s">
         <v>33</v>
@@ -4888,22 +5017,16 @@
         <v>38</v>
       </c>
       <c r="Q28">
-        <v>37.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R28">
-        <v>6.33</v>
-      </c>
-      <c r="S28">
-        <v>6.99</v>
-      </c>
-      <c r="T28">
-        <v>1.17</v>
+        <v>10.83</v>
       </c>
       <c r="Y28" t="s">
-        <v>46</v>
+        <v>573</v>
       </c>
       <c r="AA28" t="s">
-        <v>520</v>
+        <v>574</v>
       </c>
       <c r="AB28" t="s">
         <v>39</v>
@@ -4917,13 +5040,13 @@
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>584</v>
+        <v>599</v>
       </c>
       <c r="C29" t="s">
-        <v>585</v>
+        <v>600</v>
       </c>
       <c r="D29" t="s">
-        <v>586</v>
+        <v>601</v>
       </c>
       <c r="E29" t="s">
         <v>33</v>
@@ -4941,13 +5064,13 @@
         <v>54</v>
       </c>
       <c r="K29" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L29" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M29" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="N29" t="s">
         <v>33</v>
@@ -4959,16 +5082,16 @@
         <v>38</v>
       </c>
       <c r="Q29">
-        <v>64.989999999999995</v>
+        <v>14.99</v>
       </c>
       <c r="R29">
-        <v>10.83</v>
+        <v>2.5</v>
       </c>
       <c r="Y29" t="s">
-        <v>587</v>
+        <v>61</v>
       </c>
       <c r="AA29" t="s">
-        <v>588</v>
+        <v>602</v>
       </c>
       <c r="AB29" t="s">
         <v>39</v>
@@ -4982,13 +5105,13 @@
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>457</v>
+        <v>589</v>
       </c>
       <c r="C30" t="s">
-        <v>458</v>
+        <v>590</v>
       </c>
       <c r="D30" t="s">
-        <v>459</v>
+        <v>591</v>
       </c>
       <c r="E30" t="s">
         <v>33</v>
@@ -5030,13 +5153,10 @@
         <v>10.83</v>
       </c>
       <c r="Y30" t="s">
-        <v>460</v>
-      </c>
-      <c r="Z30" t="s">
-        <v>279</v>
+        <v>592</v>
       </c>
       <c r="AA30" t="s">
-        <v>461</v>
+        <v>593</v>
       </c>
       <c r="AB30" t="s">
         <v>39</v>
@@ -5050,13 +5170,13 @@
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>462</v>
+        <v>594</v>
       </c>
       <c r="C31" t="s">
-        <v>463</v>
+        <v>595</v>
       </c>
       <c r="D31" t="s">
-        <v>459</v>
+        <v>596</v>
       </c>
       <c r="E31" t="s">
         <v>33</v>
@@ -5098,10 +5218,10 @@
         <v>10.83</v>
       </c>
       <c r="Y31" t="s">
-        <v>56</v>
+        <v>597</v>
       </c>
       <c r="AA31" t="s">
-        <v>464</v>
+        <v>598</v>
       </c>
       <c r="AB31" t="s">
         <v>39</v>
@@ -5115,13 +5235,13 @@
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>465</v>
+        <v>603</v>
       </c>
       <c r="C32" t="s">
-        <v>466</v>
+        <v>604</v>
       </c>
       <c r="D32" t="s">
-        <v>467</v>
+        <v>605</v>
       </c>
       <c r="E32" t="s">
         <v>33</v>
@@ -5139,34 +5259,37 @@
         <v>54</v>
       </c>
       <c r="K32" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L32" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M32" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N32" t="s">
         <v>33</v>
       </c>
       <c r="O32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P32" t="s">
         <v>38</v>
       </c>
       <c r="Q32">
-        <v>79.98</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R32">
-        <v>13.34</v>
+        <v>10.83</v>
       </c>
       <c r="Y32" t="s">
-        <v>468</v>
+        <v>606</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>607</v>
       </c>
       <c r="AA32" t="s">
-        <v>469</v>
+        <v>608</v>
       </c>
       <c r="AB32" t="s">
         <v>39</v>
@@ -5180,13 +5303,13 @@
     </row>
     <row r="33" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>470</v>
+        <v>578</v>
       </c>
       <c r="C33" t="s">
-        <v>471</v>
+        <v>579</v>
       </c>
       <c r="D33" t="s">
-        <v>472</v>
+        <v>661</v>
       </c>
       <c r="E33" t="s">
         <v>33</v>
@@ -5204,13 +5327,13 @@
         <v>54</v>
       </c>
       <c r="K33" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L33" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M33" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N33" t="s">
         <v>33</v>
@@ -5222,16 +5345,19 @@
         <v>38</v>
       </c>
       <c r="Q33">
-        <v>37.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R33">
-        <v>6.33</v>
+        <v>10.83</v>
       </c>
       <c r="Y33" t="s">
-        <v>473</v>
+        <v>580</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>581</v>
       </c>
       <c r="AA33" t="s">
-        <v>474</v>
+        <v>582</v>
       </c>
       <c r="AB33" t="s">
         <v>39</v>
@@ -5245,13 +5371,13 @@
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>475</v>
+        <v>575</v>
       </c>
       <c r="C34" t="s">
-        <v>476</v>
+        <v>576</v>
       </c>
       <c r="D34" t="s">
-        <v>477</v>
+        <v>577</v>
       </c>
       <c r="E34" t="s">
         <v>53</v>
@@ -5281,13 +5407,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="s">
-        <v>478</v>
-      </c>
-      <c r="Z34" t="s">
-        <v>279</v>
+        <v>573</v>
       </c>
       <c r="AA34" t="s">
-        <v>479</v>
+        <v>574</v>
       </c>
       <c r="AB34" t="s">
         <v>39</v>
@@ -5301,13 +5424,13 @@
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>480</v>
+        <v>518</v>
       </c>
       <c r="C35" t="s">
-        <v>481</v>
+        <v>519</v>
       </c>
       <c r="D35" t="s">
-        <v>482</v>
+        <v>583</v>
       </c>
       <c r="E35" t="s">
         <v>33</v>
@@ -5325,13 +5448,13 @@
         <v>54</v>
       </c>
       <c r="K35" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L35" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M35" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N35" t="s">
         <v>33</v>
@@ -5343,16 +5466,22 @@
         <v>38</v>
       </c>
       <c r="Q35">
-        <v>11.99</v>
+        <v>37.99</v>
       </c>
       <c r="R35">
-        <v>2</v>
+        <v>6.33</v>
+      </c>
+      <c r="S35">
+        <v>6.99</v>
+      </c>
+      <c r="T35">
+        <v>1.17</v>
       </c>
       <c r="Y35" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="AA35" t="s">
-        <v>483</v>
+        <v>520</v>
       </c>
       <c r="AB35" t="s">
         <v>39</v>
@@ -5366,13 +5495,13 @@
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>484</v>
+        <v>584</v>
       </c>
       <c r="C36" t="s">
-        <v>485</v>
+        <v>585</v>
       </c>
       <c r="D36" t="s">
-        <v>486</v>
+        <v>586</v>
       </c>
       <c r="E36" t="s">
         <v>33</v>
@@ -5414,10 +5543,10 @@
         <v>10.83</v>
       </c>
       <c r="Y36" t="s">
-        <v>67</v>
+        <v>587</v>
       </c>
       <c r="AA36" t="s">
-        <v>487</v>
+        <v>588</v>
       </c>
       <c r="AB36" t="s">
         <v>39</v>
@@ -5431,13 +5560,13 @@
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>488</v>
+        <v>457</v>
       </c>
       <c r="C37" t="s">
-        <v>489</v>
+        <v>458</v>
       </c>
       <c r="D37" t="s">
-        <v>490</v>
+        <v>459</v>
       </c>
       <c r="E37" t="s">
         <v>33</v>
@@ -5455,37 +5584,37 @@
         <v>54</v>
       </c>
       <c r="K37" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L37" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M37" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N37" t="s">
         <v>33</v>
       </c>
       <c r="O37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P37" t="s">
         <v>38</v>
       </c>
       <c r="Q37">
-        <v>79.98</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R37">
-        <v>13.34</v>
+        <v>10.83</v>
       </c>
       <c r="Y37" t="s">
-        <v>63</v>
+        <v>460</v>
       </c>
       <c r="Z37" t="s">
-        <v>491</v>
+        <v>279</v>
       </c>
       <c r="AA37" t="s">
-        <v>492</v>
+        <v>461</v>
       </c>
       <c r="AB37" t="s">
         <v>39</v>
@@ -5499,13 +5628,13 @@
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>497</v>
+        <v>462</v>
       </c>
       <c r="C38" t="s">
-        <v>498</v>
+        <v>463</v>
       </c>
       <c r="D38" t="s">
-        <v>499</v>
+        <v>459</v>
       </c>
       <c r="E38" t="s">
         <v>33</v>
@@ -5541,19 +5670,16 @@
         <v>38</v>
       </c>
       <c r="Q38">
-        <v>59.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R38">
-        <v>10</v>
+        <v>10.83</v>
       </c>
       <c r="Y38" t="s">
-        <v>500</v>
-      </c>
-      <c r="Z38" t="s">
-        <v>501</v>
+        <v>56</v>
       </c>
       <c r="AA38" t="s">
-        <v>502</v>
+        <v>464</v>
       </c>
       <c r="AB38" t="s">
         <v>39</v>
@@ -5567,13 +5693,13 @@
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>503</v>
+        <v>465</v>
       </c>
       <c r="C39" t="s">
-        <v>504</v>
+        <v>466</v>
       </c>
       <c r="D39" t="s">
-        <v>499</v>
+        <v>467</v>
       </c>
       <c r="E39" t="s">
         <v>33</v>
@@ -5591,37 +5717,34 @@
         <v>54</v>
       </c>
       <c r="K39" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L39" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M39" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N39" t="s">
         <v>33</v>
       </c>
       <c r="O39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P39" t="s">
         <v>38</v>
       </c>
       <c r="Q39">
-        <v>59.99</v>
+        <v>79.98</v>
       </c>
       <c r="R39">
-        <v>10</v>
+        <v>13.34</v>
       </c>
       <c r="Y39" t="s">
-        <v>505</v>
-      </c>
-      <c r="Z39" t="s">
-        <v>93</v>
+        <v>468</v>
       </c>
       <c r="AA39" t="s">
-        <v>506</v>
+        <v>469</v>
       </c>
       <c r="AB39" t="s">
         <v>39</v>
@@ -5635,13 +5758,13 @@
     </row>
     <row r="40" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>507</v>
+        <v>470</v>
       </c>
       <c r="C40" t="s">
-        <v>508</v>
+        <v>471</v>
       </c>
       <c r="D40" t="s">
-        <v>509</v>
+        <v>472</v>
       </c>
       <c r="E40" t="s">
         <v>33</v>
@@ -5659,13 +5782,13 @@
         <v>54</v>
       </c>
       <c r="K40" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L40" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M40" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N40" t="s">
         <v>33</v>
@@ -5677,16 +5800,16 @@
         <v>38</v>
       </c>
       <c r="Q40">
-        <v>59.99</v>
+        <v>37.99</v>
       </c>
       <c r="R40">
-        <v>10</v>
+        <v>6.33</v>
       </c>
       <c r="Y40" t="s">
-        <v>510</v>
+        <v>473</v>
       </c>
       <c r="AA40" t="s">
-        <v>511</v>
+        <v>474</v>
       </c>
       <c r="AB40" t="s">
         <v>39</v>
@@ -5700,16 +5823,16 @@
     </row>
     <row r="41" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>512</v>
+        <v>475</v>
       </c>
       <c r="C41" t="s">
-        <v>513</v>
+        <v>476</v>
       </c>
       <c r="D41" t="s">
-        <v>514</v>
+        <v>477</v>
       </c>
       <c r="E41" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F41" t="s">
         <v>34</v>
@@ -5732,29 +5855,17 @@
       <c r="M41" t="s">
         <v>42</v>
       </c>
-      <c r="N41" t="s">
-        <v>33</v>
-      </c>
       <c r="O41">
-        <v>1</v>
-      </c>
-      <c r="P41" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q41">
-        <v>59.99</v>
-      </c>
-      <c r="R41">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="s">
-        <v>515</v>
+        <v>478</v>
       </c>
       <c r="Z41" t="s">
-        <v>516</v>
+        <v>279</v>
       </c>
       <c r="AA41" t="s">
-        <v>517</v>
+        <v>479</v>
       </c>
       <c r="AB41" t="s">
         <v>39</v>
@@ -5768,13 +5879,13 @@
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>521</v>
+        <v>480</v>
       </c>
       <c r="C42" t="s">
-        <v>522</v>
+        <v>481</v>
       </c>
       <c r="D42" t="s">
-        <v>523</v>
+        <v>482</v>
       </c>
       <c r="E42" t="s">
         <v>33</v>
@@ -5792,13 +5903,13 @@
         <v>54</v>
       </c>
       <c r="K42" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L42" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M42" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="N42" t="s">
         <v>33</v>
@@ -5810,16 +5921,16 @@
         <v>38</v>
       </c>
       <c r="Q42">
-        <v>14.99</v>
+        <v>11.99</v>
       </c>
       <c r="R42">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Y42" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="AA42" t="s">
-        <v>524</v>
+        <v>483</v>
       </c>
       <c r="AB42" t="s">
         <v>39</v>
@@ -5833,13 +5944,13 @@
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>525</v>
+        <v>484</v>
       </c>
       <c r="C43" t="s">
-        <v>526</v>
+        <v>485</v>
       </c>
       <c r="D43" t="s">
-        <v>527</v>
+        <v>486</v>
       </c>
       <c r="E43" t="s">
         <v>33</v>
@@ -5875,16 +5986,16 @@
         <v>38</v>
       </c>
       <c r="Q43">
-        <v>59.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R43">
-        <v>10</v>
+        <v>10.83</v>
       </c>
       <c r="Y43" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="AA43" t="s">
-        <v>528</v>
+        <v>487</v>
       </c>
       <c r="AB43" t="s">
         <v>39</v>
@@ -5898,13 +6009,13 @@
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>529</v>
+        <v>488</v>
       </c>
       <c r="C44" t="s">
-        <v>530</v>
+        <v>489</v>
       </c>
       <c r="D44" t="s">
-        <v>527</v>
+        <v>490</v>
       </c>
       <c r="E44" t="s">
         <v>33</v>
@@ -5922,34 +6033,37 @@
         <v>54</v>
       </c>
       <c r="K44" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L44" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M44" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N44" t="s">
         <v>33</v>
       </c>
       <c r="O44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P44" t="s">
         <v>38</v>
       </c>
       <c r="Q44">
-        <v>59.99</v>
+        <v>79.98</v>
       </c>
       <c r="R44">
-        <v>10</v>
+        <v>13.34</v>
       </c>
       <c r="Y44" t="s">
-        <v>531</v>
+        <v>63</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>491</v>
       </c>
       <c r="AA44" t="s">
-        <v>532</v>
+        <v>492</v>
       </c>
       <c r="AB44" t="s">
         <v>39</v>
@@ -5963,13 +6077,13 @@
     </row>
     <row r="45" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>533</v>
+        <v>497</v>
       </c>
       <c r="C45" t="s">
-        <v>534</v>
+        <v>498</v>
       </c>
       <c r="D45" t="s">
-        <v>535</v>
+        <v>499</v>
       </c>
       <c r="E45" t="s">
         <v>33</v>
@@ -5987,13 +6101,13 @@
         <v>54</v>
       </c>
       <c r="K45" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L45" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M45" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N45" t="s">
         <v>33</v>
@@ -6005,19 +6119,19 @@
         <v>38</v>
       </c>
       <c r="Q45">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R45">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y45" t="s">
-        <v>536</v>
+        <v>500</v>
       </c>
       <c r="Z45" t="s">
-        <v>537</v>
+        <v>501</v>
       </c>
       <c r="AA45" t="s">
-        <v>538</v>
+        <v>502</v>
       </c>
       <c r="AB45" t="s">
         <v>39</v>
@@ -6031,13 +6145,13 @@
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>539</v>
+        <v>503</v>
       </c>
       <c r="C46" t="s">
-        <v>540</v>
+        <v>504</v>
       </c>
       <c r="D46" t="s">
-        <v>541</v>
+        <v>499</v>
       </c>
       <c r="E46" t="s">
         <v>33</v>
@@ -6079,13 +6193,13 @@
         <v>10</v>
       </c>
       <c r="Y46" t="s">
-        <v>71</v>
+        <v>505</v>
       </c>
       <c r="Z46" t="s">
-        <v>542</v>
+        <v>93</v>
       </c>
       <c r="AA46" t="s">
-        <v>543</v>
+        <v>506</v>
       </c>
       <c r="AB46" t="s">
         <v>39</v>
@@ -6099,13 +6213,13 @@
     </row>
     <row r="47" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>544</v>
+        <v>507</v>
       </c>
       <c r="C47" t="s">
-        <v>545</v>
+        <v>508</v>
       </c>
       <c r="D47" t="s">
-        <v>546</v>
+        <v>509</v>
       </c>
       <c r="E47" t="s">
         <v>33</v>
@@ -6123,37 +6237,34 @@
         <v>54</v>
       </c>
       <c r="K47" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L47" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M47" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N47" t="s">
         <v>33</v>
       </c>
       <c r="O47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P47" t="s">
         <v>38</v>
       </c>
       <c r="Q47">
-        <v>76.98</v>
+        <v>59.99</v>
       </c>
       <c r="R47">
-        <v>12.84</v>
+        <v>10</v>
       </c>
       <c r="Y47" t="s">
-        <v>547</v>
-      </c>
-      <c r="Z47" t="s">
-        <v>548</v>
+        <v>510</v>
       </c>
       <c r="AA47" t="s">
-        <v>549</v>
+        <v>511</v>
       </c>
       <c r="AB47" t="s">
         <v>39</v>
@@ -6167,13 +6278,13 @@
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>550</v>
+        <v>512</v>
       </c>
       <c r="C48" t="s">
-        <v>551</v>
+        <v>513</v>
       </c>
       <c r="D48" t="s">
-        <v>552</v>
+        <v>514</v>
       </c>
       <c r="E48" t="s">
         <v>33</v>
@@ -6215,10 +6326,13 @@
         <v>10</v>
       </c>
       <c r="Y48" t="s">
-        <v>553</v>
+        <v>515</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>516</v>
       </c>
       <c r="AA48" t="s">
-        <v>554</v>
+        <v>517</v>
       </c>
       <c r="AB48" t="s">
         <v>39</v>
@@ -6232,13 +6346,13 @@
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>555</v>
+        <v>521</v>
       </c>
       <c r="C49" t="s">
-        <v>556</v>
+        <v>522</v>
       </c>
       <c r="D49" t="s">
-        <v>557</v>
+        <v>523</v>
       </c>
       <c r="E49" t="s">
         <v>33</v>
@@ -6256,13 +6370,13 @@
         <v>54</v>
       </c>
       <c r="K49" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L49" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M49" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="N49" t="s">
         <v>33</v>
@@ -6274,16 +6388,16 @@
         <v>38</v>
       </c>
       <c r="Q49">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="R49">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="Y49" t="s">
-        <v>558</v>
+        <v>58</v>
       </c>
       <c r="AA49" t="s">
-        <v>559</v>
+        <v>524</v>
       </c>
       <c r="AB49" t="s">
         <v>39</v>
@@ -6297,13 +6411,13 @@
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>418</v>
+        <v>525</v>
       </c>
       <c r="C50" t="s">
-        <v>419</v>
+        <v>526</v>
       </c>
       <c r="D50" t="s">
-        <v>560</v>
+        <v>527</v>
       </c>
       <c r="E50" t="s">
         <v>33</v>
@@ -6345,10 +6459,10 @@
         <v>10</v>
       </c>
       <c r="Y50" t="s">
-        <v>420</v>
+        <v>90</v>
       </c>
       <c r="AA50" t="s">
-        <v>421</v>
+        <v>528</v>
       </c>
       <c r="AB50" t="s">
         <v>39</v>
@@ -6362,13 +6476,13 @@
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>561</v>
+        <v>529</v>
       </c>
       <c r="C51" t="s">
-        <v>562</v>
+        <v>530</v>
       </c>
       <c r="D51" t="s">
-        <v>563</v>
+        <v>527</v>
       </c>
       <c r="E51" t="s">
         <v>33</v>
@@ -6410,13 +6524,10 @@
         <v>10</v>
       </c>
       <c r="Y51" t="s">
-        <v>564</v>
-      </c>
-      <c r="Z51" t="s">
-        <v>565</v>
+        <v>531</v>
       </c>
       <c r="AA51" t="s">
-        <v>566</v>
+        <v>532</v>
       </c>
       <c r="AB51" t="s">
         <v>39</v>
@@ -6430,13 +6541,13 @@
     </row>
     <row r="52" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>567</v>
+        <v>533</v>
       </c>
       <c r="C52" t="s">
-        <v>568</v>
+        <v>534</v>
       </c>
       <c r="D52" t="s">
-        <v>569</v>
+        <v>535</v>
       </c>
       <c r="E52" t="s">
         <v>33</v>
@@ -6454,13 +6565,13 @@
         <v>54</v>
       </c>
       <c r="K52" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L52" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M52" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="N52" t="s">
         <v>33</v>
@@ -6472,16 +6583,19 @@
         <v>38</v>
       </c>
       <c r="Q52">
-        <v>14.99</v>
+        <v>11.99</v>
       </c>
       <c r="R52">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Y52" t="s">
-        <v>69</v>
+        <v>536</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>537</v>
       </c>
       <c r="AA52" t="s">
-        <v>570</v>
+        <v>538</v>
       </c>
       <c r="AB52" t="s">
         <v>39</v>
@@ -6495,13 +6609,13 @@
     </row>
     <row r="53" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>413</v>
+        <v>539</v>
       </c>
       <c r="C53" t="s">
-        <v>414</v>
+        <v>540</v>
       </c>
       <c r="D53" t="s">
-        <v>415</v>
+        <v>541</v>
       </c>
       <c r="E53" t="s">
         <v>33</v>
@@ -6543,10 +6657,13 @@
         <v>10</v>
       </c>
       <c r="Y53" t="s">
-        <v>416</v>
+        <v>71</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>542</v>
       </c>
       <c r="AA53" t="s">
-        <v>417</v>
+        <v>543</v>
       </c>
       <c r="AB53" t="s">
         <v>39</v>
@@ -6560,13 +6677,13 @@
     </row>
     <row r="54" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>422</v>
+        <v>544</v>
       </c>
       <c r="C54" t="s">
-        <v>423</v>
+        <v>545</v>
       </c>
       <c r="D54" t="s">
-        <v>424</v>
+        <v>546</v>
       </c>
       <c r="E54" t="s">
         <v>33</v>
@@ -6584,34 +6701,37 @@
         <v>54</v>
       </c>
       <c r="K54" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="L54" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="M54" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="N54" t="s">
         <v>33</v>
       </c>
       <c r="O54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P54" t="s">
         <v>38</v>
       </c>
       <c r="Q54">
-        <v>22.99</v>
+        <v>76.98</v>
       </c>
       <c r="R54">
-        <v>3.83</v>
+        <v>12.84</v>
       </c>
       <c r="Y54" t="s">
-        <v>425</v>
+        <v>547</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>548</v>
       </c>
       <c r="AA54" t="s">
-        <v>426</v>
+        <v>549</v>
       </c>
       <c r="AB54" t="s">
         <v>39</v>
@@ -6625,13 +6745,13 @@
     </row>
     <row r="55" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>427</v>
+        <v>550</v>
       </c>
       <c r="C55" t="s">
-        <v>428</v>
+        <v>551</v>
       </c>
       <c r="D55" t="s">
-        <v>424</v>
+        <v>552</v>
       </c>
       <c r="E55" t="s">
         <v>33</v>
@@ -6649,13 +6769,13 @@
         <v>54</v>
       </c>
       <c r="K55" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L55" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M55" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N55" t="s">
         <v>33</v>
@@ -6667,19 +6787,16 @@
         <v>38</v>
       </c>
       <c r="Q55">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R55">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y55" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z55" t="s">
-        <v>97</v>
+        <v>553</v>
       </c>
       <c r="AA55" t="s">
-        <v>429</v>
+        <v>554</v>
       </c>
       <c r="AB55" t="s">
         <v>39</v>
@@ -6693,13 +6810,13 @@
     </row>
     <row r="56" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>430</v>
+        <v>555</v>
       </c>
       <c r="C56" t="s">
-        <v>431</v>
+        <v>556</v>
       </c>
       <c r="D56" t="s">
-        <v>432</v>
+        <v>557</v>
       </c>
       <c r="E56" t="s">
         <v>33</v>
@@ -6717,13 +6834,13 @@
         <v>54</v>
       </c>
       <c r="K56" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L56" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M56" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N56" t="s">
         <v>33</v>
@@ -6735,19 +6852,16 @@
         <v>38</v>
       </c>
       <c r="Q56">
-        <v>38.49</v>
+        <v>59.99</v>
       </c>
       <c r="R56">
-        <v>6.42</v>
+        <v>10</v>
       </c>
       <c r="Y56" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z56" t="s">
-        <v>433</v>
+        <v>558</v>
       </c>
       <c r="AA56" t="s">
-        <v>434</v>
+        <v>559</v>
       </c>
       <c r="AB56" t="s">
         <v>39</v>
@@ -6761,13 +6875,13 @@
     </row>
     <row r="57" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>435</v>
+        <v>418</v>
       </c>
       <c r="C57" t="s">
-        <v>436</v>
+        <v>419</v>
       </c>
       <c r="D57" t="s">
-        <v>437</v>
+        <v>560</v>
       </c>
       <c r="E57" t="s">
         <v>33</v>
@@ -6785,13 +6899,13 @@
         <v>54</v>
       </c>
       <c r="K57" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="L57" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="M57" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="N57" t="s">
         <v>33</v>
@@ -6803,16 +6917,16 @@
         <v>38</v>
       </c>
       <c r="Q57">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R57">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y57" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="AA57" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="AB57" t="s">
         <v>39</v>
@@ -6826,13 +6940,13 @@
     </row>
     <row r="58" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>440</v>
+        <v>561</v>
       </c>
       <c r="C58" t="s">
-        <v>441</v>
+        <v>562</v>
       </c>
       <c r="D58" t="s">
-        <v>442</v>
+        <v>563</v>
       </c>
       <c r="E58" t="s">
         <v>33</v>
@@ -6850,13 +6964,13 @@
         <v>54</v>
       </c>
       <c r="K58" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L58" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M58" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N58" t="s">
         <v>33</v>
@@ -6868,16 +6982,19 @@
         <v>38</v>
       </c>
       <c r="Q58">
-        <v>37.99</v>
+        <v>59.99</v>
       </c>
       <c r="R58">
-        <v>6.33</v>
+        <v>10</v>
       </c>
       <c r="Y58" t="s">
-        <v>443</v>
+        <v>564</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>565</v>
       </c>
       <c r="AA58" t="s">
-        <v>444</v>
+        <v>566</v>
       </c>
       <c r="AB58" t="s">
         <v>39</v>
@@ -6891,13 +7008,13 @@
     </row>
     <row r="59" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>445</v>
+        <v>567</v>
       </c>
       <c r="C59" t="s">
-        <v>446</v>
+        <v>568</v>
       </c>
       <c r="D59" t="s">
-        <v>447</v>
+        <v>569</v>
       </c>
       <c r="E59" t="s">
         <v>33</v>
@@ -6915,13 +7032,13 @@
         <v>54</v>
       </c>
       <c r="K59" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L59" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M59" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="N59" t="s">
         <v>33</v>
@@ -6933,16 +7050,16 @@
         <v>38</v>
       </c>
       <c r="Q59">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="R59">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="Y59" t="s">
-        <v>448</v>
+        <v>69</v>
       </c>
       <c r="AA59" t="s">
-        <v>449</v>
+        <v>570</v>
       </c>
       <c r="AB59" t="s">
         <v>39</v>
@@ -6956,16 +7073,16 @@
     </row>
     <row r="60" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>450</v>
+        <v>413</v>
       </c>
       <c r="C60" t="s">
-        <v>451</v>
+        <v>414</v>
       </c>
       <c r="D60" t="s">
-        <v>452</v>
+        <v>415</v>
       </c>
       <c r="E60" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F60" t="s">
         <v>34</v>
@@ -6988,14 +7105,26 @@
       <c r="M60" t="s">
         <v>42</v>
       </c>
+      <c r="N60" t="s">
+        <v>33</v>
+      </c>
       <c r="O60">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P60" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q60">
+        <v>59.99</v>
+      </c>
+      <c r="R60">
+        <v>10</v>
       </c>
       <c r="Y60" t="s">
-        <v>453</v>
+        <v>416</v>
       </c>
       <c r="AA60" t="s">
-        <v>454</v>
+        <v>417</v>
       </c>
       <c r="AB60" t="s">
         <v>39</v>
@@ -7009,13 +7138,13 @@
     </row>
     <row r="61" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>403</v>
+        <v>422</v>
       </c>
       <c r="C61" t="s">
-        <v>404</v>
+        <v>423</v>
       </c>
       <c r="D61" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="E61" t="s">
         <v>33</v>
@@ -7033,13 +7162,13 @@
         <v>54</v>
       </c>
       <c r="K61" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="L61" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="M61" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="N61" t="s">
         <v>33</v>
@@ -7051,22 +7180,16 @@
         <v>38</v>
       </c>
       <c r="Q61">
-        <v>59.99</v>
+        <v>22.99</v>
       </c>
       <c r="R61">
-        <v>10</v>
-      </c>
-      <c r="S61">
-        <v>5.99</v>
-      </c>
-      <c r="T61">
-        <v>1</v>
+        <v>3.83</v>
       </c>
       <c r="Y61" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="AA61" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="AB61" t="s">
         <v>39</v>
@@ -7080,13 +7203,13 @@
     </row>
     <row r="62" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="C62" t="s">
-        <v>408</v>
+        <v>428</v>
       </c>
       <c r="D62" t="s">
-        <v>456</v>
+        <v>424</v>
       </c>
       <c r="E62" t="s">
         <v>33</v>
@@ -7104,13 +7227,13 @@
         <v>54</v>
       </c>
       <c r="K62" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="L62" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="M62" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="N62" t="s">
         <v>33</v>
@@ -7122,16 +7245,19 @@
         <v>38</v>
       </c>
       <c r="Q62">
-        <v>22.99</v>
+        <v>11.99</v>
       </c>
       <c r="R62">
-        <v>3.83</v>
+        <v>2</v>
       </c>
       <c r="Y62" t="s">
-        <v>409</v>
+        <v>96</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>97</v>
       </c>
       <c r="AA62" t="s">
-        <v>410</v>
+        <v>429</v>
       </c>
       <c r="AB62" t="s">
         <v>39</v>
@@ -7145,13 +7271,13 @@
     </row>
     <row r="63" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>399</v>
+        <v>430</v>
       </c>
       <c r="C63" t="s">
-        <v>400</v>
+        <v>431</v>
       </c>
       <c r="D63" t="s">
-        <v>411</v>
+        <v>432</v>
       </c>
       <c r="E63" t="s">
         <v>33</v>
@@ -7169,13 +7295,13 @@
         <v>54</v>
       </c>
       <c r="K63" t="s">
-        <v>340</v>
+        <v>43</v>
       </c>
       <c r="L63" t="s">
-        <v>142</v>
+        <v>44</v>
       </c>
       <c r="M63" t="s">
-        <v>143</v>
+        <v>45</v>
       </c>
       <c r="N63" t="s">
         <v>33</v>
@@ -7187,16 +7313,19 @@
         <v>38</v>
       </c>
       <c r="Q63">
-        <v>44.99</v>
+        <v>38.49</v>
       </c>
       <c r="R63">
-        <v>7.5</v>
+        <v>6.42</v>
       </c>
       <c r="Y63" t="s">
-        <v>401</v>
+        <v>59</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>433</v>
       </c>
       <c r="AA63" t="s">
-        <v>402</v>
+        <v>434</v>
       </c>
       <c r="AB63" t="s">
         <v>39</v>
@@ -7210,13 +7339,13 @@
     </row>
     <row r="64" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>394</v>
+        <v>435</v>
       </c>
       <c r="C64" t="s">
-        <v>395</v>
+        <v>436</v>
       </c>
       <c r="D64" t="s">
-        <v>412</v>
+        <v>437</v>
       </c>
       <c r="E64" t="s">
         <v>33</v>
@@ -7234,13 +7363,13 @@
         <v>54</v>
       </c>
       <c r="K64" t="s">
-        <v>340</v>
+        <v>95</v>
       </c>
       <c r="L64" t="s">
-        <v>142</v>
+        <v>85</v>
       </c>
       <c r="M64" t="s">
-        <v>143</v>
+        <v>86</v>
       </c>
       <c r="N64" t="s">
         <v>33</v>
@@ -7252,19 +7381,16 @@
         <v>38</v>
       </c>
       <c r="Q64">
-        <v>44.99</v>
+        <v>14.99</v>
       </c>
       <c r="R64">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="Y64" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z64" t="s">
-        <v>397</v>
+        <v>438</v>
       </c>
       <c r="AA64" t="s">
-        <v>398</v>
+        <v>439</v>
       </c>
       <c r="AB64" t="s">
         <v>39</v>
@@ -7278,13 +7404,13 @@
     </row>
     <row r="65" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>338</v>
+        <v>440</v>
       </c>
       <c r="C65" t="s">
-        <v>339</v>
+        <v>441</v>
       </c>
       <c r="D65" t="s">
-        <v>662</v>
+        <v>442</v>
       </c>
       <c r="E65" t="s">
         <v>33</v>
@@ -7302,13 +7428,13 @@
         <v>54</v>
       </c>
       <c r="K65" t="s">
-        <v>340</v>
+        <v>48</v>
       </c>
       <c r="L65" t="s">
-        <v>142</v>
+        <v>49</v>
       </c>
       <c r="M65" t="s">
-        <v>143</v>
+        <v>50</v>
       </c>
       <c r="N65" t="s">
         <v>33</v>
@@ -7320,16 +7446,16 @@
         <v>38</v>
       </c>
       <c r="Q65">
-        <v>44.99</v>
+        <v>37.99</v>
       </c>
       <c r="R65">
-        <v>7.5</v>
+        <v>6.33</v>
       </c>
       <c r="Y65" t="s">
-        <v>341</v>
+        <v>443</v>
       </c>
       <c r="AA65" t="s">
-        <v>342</v>
+        <v>444</v>
       </c>
       <c r="AB65" t="s">
         <v>39</v>
@@ -7343,13 +7469,13 @@
     </row>
     <row r="66" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>663</v>
+        <v>445</v>
       </c>
       <c r="C66" t="s">
-        <v>664</v>
+        <v>446</v>
       </c>
       <c r="D66" t="s">
-        <v>665</v>
+        <v>447</v>
       </c>
       <c r="E66" t="s">
         <v>33</v>
@@ -7391,19 +7517,16 @@
         <v>10</v>
       </c>
       <c r="Y66" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z66" t="s">
-        <v>666</v>
+        <v>448</v>
       </c>
       <c r="AA66" t="s">
-        <v>667</v>
+        <v>449</v>
       </c>
       <c r="AB66" t="s">
         <v>39</v>
       </c>
       <c r="AD66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="b">
         <v>0</v>
@@ -7411,16 +7534,16 @@
     </row>
     <row r="67" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>334</v>
+        <v>450</v>
       </c>
       <c r="C67" t="s">
-        <v>335</v>
+        <v>451</v>
       </c>
       <c r="D67" t="s">
-        <v>668</v>
+        <v>452</v>
       </c>
       <c r="E67" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F67" t="s">
         <v>34</v>
@@ -7435,34 +7558,22 @@
         <v>54</v>
       </c>
       <c r="K67" t="s">
-        <v>203</v>
+        <v>40</v>
       </c>
       <c r="L67" t="s">
-        <v>204</v>
+        <v>41</v>
       </c>
       <c r="M67" t="s">
-        <v>205</v>
-      </c>
-      <c r="N67" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O67">
-        <v>1</v>
-      </c>
-      <c r="P67" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q67">
-        <v>69.989999999999995</v>
-      </c>
-      <c r="R67">
-        <v>11.67</v>
+        <v>0</v>
       </c>
       <c r="Y67" t="s">
-        <v>336</v>
+        <v>453</v>
       </c>
       <c r="AA67" t="s">
-        <v>337</v>
+        <v>454</v>
       </c>
       <c r="AB67" t="s">
         <v>39</v>
@@ -7476,13 +7587,13 @@
     </row>
     <row r="68" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>326</v>
+        <v>403</v>
       </c>
       <c r="C68" t="s">
-        <v>327</v>
+        <v>404</v>
       </c>
       <c r="D68" t="s">
-        <v>669</v>
+        <v>455</v>
       </c>
       <c r="E68" t="s">
         <v>33</v>
@@ -7500,34 +7611,40 @@
         <v>54</v>
       </c>
       <c r="K68" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L68" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M68" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N68" t="s">
         <v>33</v>
       </c>
       <c r="O68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P68" t="s">
         <v>38</v>
       </c>
       <c r="Q68">
-        <v>75.98</v>
+        <v>59.99</v>
       </c>
       <c r="R68">
-        <v>12.66</v>
+        <v>10</v>
+      </c>
+      <c r="S68">
+        <v>5.99</v>
+      </c>
+      <c r="T68">
+        <v>1</v>
       </c>
       <c r="Y68" t="s">
-        <v>91</v>
+        <v>405</v>
       </c>
       <c r="AA68" t="s">
-        <v>328</v>
+        <v>406</v>
       </c>
       <c r="AB68" t="s">
         <v>39</v>
@@ -7541,13 +7658,13 @@
     </row>
     <row r="69" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>343</v>
+        <v>407</v>
       </c>
       <c r="C69" t="s">
-        <v>344</v>
+        <v>408</v>
       </c>
       <c r="D69" t="s">
-        <v>345</v>
+        <v>456</v>
       </c>
       <c r="E69" t="s">
         <v>33</v>
@@ -7565,13 +7682,13 @@
         <v>54</v>
       </c>
       <c r="K69" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="L69" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="M69" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="N69" t="s">
         <v>33</v>
@@ -7583,16 +7700,16 @@
         <v>38</v>
       </c>
       <c r="Q69">
-        <v>59.99</v>
+        <v>22.99</v>
       </c>
       <c r="R69">
-        <v>10</v>
+        <v>3.83</v>
       </c>
       <c r="Y69" t="s">
-        <v>346</v>
+        <v>409</v>
       </c>
       <c r="AA69" t="s">
-        <v>347</v>
+        <v>410</v>
       </c>
       <c r="AB69" t="s">
         <v>39</v>
@@ -7606,13 +7723,13 @@
     </row>
     <row r="70" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>288</v>
+        <v>399</v>
       </c>
       <c r="C70" t="s">
-        <v>289</v>
+        <v>400</v>
       </c>
       <c r="D70" t="s">
-        <v>348</v>
+        <v>411</v>
       </c>
       <c r="E70" t="s">
         <v>33</v>
@@ -7627,37 +7744,37 @@
         <v>36</v>
       </c>
       <c r="J70" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K70" t="s">
-        <v>48</v>
+        <v>340</v>
       </c>
       <c r="L70" t="s">
-        <v>49</v>
+        <v>142</v>
       </c>
       <c r="M70" t="s">
-        <v>50</v>
+        <v>143</v>
       </c>
       <c r="N70" t="s">
         <v>33</v>
       </c>
       <c r="O70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P70" t="s">
         <v>38</v>
       </c>
       <c r="Q70">
-        <v>75.98</v>
+        <v>44.99</v>
       </c>
       <c r="R70">
-        <v>12.66</v>
+        <v>7.5</v>
       </c>
       <c r="Y70" t="s">
-        <v>290</v>
+        <v>401</v>
       </c>
       <c r="AA70" t="s">
-        <v>291</v>
+        <v>402</v>
       </c>
       <c r="AB70" t="s">
         <v>39</v>
@@ -7671,13 +7788,13 @@
     </row>
     <row r="71" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>349</v>
+        <v>394</v>
       </c>
       <c r="C71" t="s">
-        <v>350</v>
+        <v>395</v>
       </c>
       <c r="D71" t="s">
-        <v>351</v>
+        <v>412</v>
       </c>
       <c r="E71" t="s">
         <v>33</v>
@@ -7695,13 +7812,13 @@
         <v>54</v>
       </c>
       <c r="K71" t="s">
-        <v>48</v>
+        <v>340</v>
       </c>
       <c r="L71" t="s">
-        <v>49</v>
+        <v>142</v>
       </c>
       <c r="M71" t="s">
-        <v>50</v>
+        <v>143</v>
       </c>
       <c r="N71" t="s">
         <v>33</v>
@@ -7713,19 +7830,19 @@
         <v>38</v>
       </c>
       <c r="Q71">
-        <v>37.99</v>
+        <v>44.99</v>
       </c>
       <c r="R71">
-        <v>6.33</v>
+        <v>7.5</v>
       </c>
       <c r="Y71" t="s">
-        <v>352</v>
+        <v>396</v>
       </c>
       <c r="Z71" t="s">
-        <v>353</v>
+        <v>397</v>
       </c>
       <c r="AA71" t="s">
-        <v>354</v>
+        <v>398</v>
       </c>
       <c r="AB71" t="s">
         <v>39</v>
@@ -7739,13 +7856,13 @@
     </row>
     <row r="72" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="C72" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="D72" t="s">
-        <v>357</v>
+        <v>662</v>
       </c>
       <c r="E72" t="s">
         <v>33</v>
@@ -7763,13 +7880,13 @@
         <v>54</v>
       </c>
       <c r="K72" t="s">
-        <v>72</v>
+        <v>340</v>
       </c>
       <c r="L72" t="s">
-        <v>73</v>
+        <v>142</v>
       </c>
       <c r="M72" t="s">
-        <v>74</v>
+        <v>143</v>
       </c>
       <c r="N72" t="s">
         <v>33</v>
@@ -7781,16 +7898,16 @@
         <v>38</v>
       </c>
       <c r="Q72">
-        <v>11.99</v>
+        <v>44.99</v>
       </c>
       <c r="R72">
-        <v>2</v>
+        <v>7.5</v>
       </c>
       <c r="Y72" t="s">
-        <v>58</v>
+        <v>341</v>
       </c>
       <c r="AA72" t="s">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="AB72" t="s">
         <v>39</v>
@@ -7804,13 +7921,13 @@
     </row>
     <row r="73" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>359</v>
+        <v>663</v>
       </c>
       <c r="C73" t="s">
-        <v>360</v>
+        <v>664</v>
       </c>
       <c r="D73" t="s">
-        <v>361</v>
+        <v>665</v>
       </c>
       <c r="E73" t="s">
         <v>33</v>
@@ -7828,43 +7945,43 @@
         <v>54</v>
       </c>
       <c r="K73" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L73" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M73" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N73" t="s">
         <v>33</v>
       </c>
       <c r="O73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P73" t="s">
         <v>38</v>
       </c>
       <c r="Q73">
-        <v>75.98</v>
+        <v>59.99</v>
       </c>
       <c r="R73">
-        <v>12.66</v>
+        <v>10</v>
       </c>
       <c r="Y73" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="Z73" t="s">
-        <v>59</v>
+        <v>666</v>
       </c>
       <c r="AA73" t="s">
-        <v>362</v>
+        <v>667</v>
       </c>
       <c r="AB73" t="s">
         <v>39</v>
       </c>
       <c r="AD73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG73" t="b">
         <v>0</v>
@@ -7872,13 +7989,13 @@
     </row>
     <row r="74" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="C74" t="s">
-        <v>364</v>
+        <v>335</v>
       </c>
       <c r="D74" t="s">
-        <v>365</v>
+        <v>668</v>
       </c>
       <c r="E74" t="s">
         <v>33</v>
@@ -7896,13 +8013,13 @@
         <v>54</v>
       </c>
       <c r="K74" t="s">
-        <v>260</v>
+        <v>203</v>
       </c>
       <c r="L74" t="s">
-        <v>261</v>
+        <v>204</v>
       </c>
       <c r="M74" t="s">
-        <v>262</v>
+        <v>205</v>
       </c>
       <c r="N74" t="s">
         <v>33</v>
@@ -7914,16 +8031,16 @@
         <v>38</v>
       </c>
       <c r="Q74">
-        <v>24.49</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="R74">
-        <v>4.08</v>
+        <v>11.67</v>
       </c>
       <c r="Y74" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
       <c r="AA74" t="s">
-        <v>367</v>
+        <v>337</v>
       </c>
       <c r="AB74" t="s">
         <v>39</v>
@@ -7937,13 +8054,13 @@
     </row>
     <row r="75" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>265</v>
+        <v>326</v>
       </c>
       <c r="C75" t="s">
-        <v>266</v>
+        <v>327</v>
       </c>
       <c r="D75" t="s">
-        <v>368</v>
+        <v>669</v>
       </c>
       <c r="E75" t="s">
         <v>33</v>
@@ -7973,22 +8090,22 @@
         <v>33</v>
       </c>
       <c r="O75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P75" t="s">
         <v>38</v>
       </c>
       <c r="Q75">
-        <v>37.99</v>
+        <v>75.98</v>
       </c>
       <c r="R75">
-        <v>6.33</v>
+        <v>12.66</v>
       </c>
       <c r="Y75" t="s">
-        <v>267</v>
+        <v>91</v>
       </c>
       <c r="AA75" t="s">
-        <v>268</v>
+        <v>328</v>
       </c>
       <c r="AB75" t="s">
         <v>39</v>
@@ -8002,13 +8119,13 @@
     </row>
     <row r="76" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>369</v>
+        <v>343</v>
       </c>
       <c r="C76" t="s">
-        <v>370</v>
+        <v>344</v>
       </c>
       <c r="D76" t="s">
-        <v>371</v>
+        <v>345</v>
       </c>
       <c r="E76" t="s">
         <v>33</v>
@@ -8026,13 +8143,13 @@
         <v>54</v>
       </c>
       <c r="K76" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L76" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M76" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N76" t="s">
         <v>33</v>
@@ -8044,22 +8161,16 @@
         <v>38</v>
       </c>
       <c r="Q76">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R76">
-        <v>2</v>
-      </c>
-      <c r="S76">
-        <v>5.99</v>
-      </c>
-      <c r="T76">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y76" t="s">
-        <v>84</v>
+        <v>346</v>
       </c>
       <c r="AA76" t="s">
-        <v>372</v>
+        <v>347</v>
       </c>
       <c r="AB76" t="s">
         <v>39</v>
@@ -8073,13 +8184,13 @@
     </row>
     <row r="77" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>373</v>
+        <v>288</v>
       </c>
       <c r="C77" t="s">
-        <v>374</v>
+        <v>289</v>
       </c>
       <c r="D77" t="s">
-        <v>375</v>
+        <v>348</v>
       </c>
       <c r="E77" t="s">
         <v>33</v>
@@ -8094,37 +8205,37 @@
         <v>36</v>
       </c>
       <c r="J77" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K77" t="s">
-        <v>260</v>
+        <v>48</v>
       </c>
       <c r="L77" t="s">
-        <v>261</v>
+        <v>49</v>
       </c>
       <c r="M77" t="s">
-        <v>262</v>
+        <v>50</v>
       </c>
       <c r="N77" t="s">
         <v>33</v>
       </c>
       <c r="O77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P77" t="s">
         <v>38</v>
       </c>
       <c r="Q77">
-        <v>24.49</v>
+        <v>75.98</v>
       </c>
       <c r="R77">
-        <v>4.08</v>
+        <v>12.66</v>
       </c>
       <c r="Y77" t="s">
-        <v>376</v>
+        <v>290</v>
       </c>
       <c r="AA77" t="s">
-        <v>377</v>
+        <v>291</v>
       </c>
       <c r="AB77" t="s">
         <v>39</v>
@@ -8138,13 +8249,13 @@
     </row>
     <row r="78" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>378</v>
+        <v>349</v>
       </c>
       <c r="C78" t="s">
-        <v>379</v>
+        <v>350</v>
       </c>
       <c r="D78" t="s">
-        <v>380</v>
+        <v>351</v>
       </c>
       <c r="E78" t="s">
         <v>33</v>
@@ -8162,13 +8273,13 @@
         <v>54</v>
       </c>
       <c r="K78" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L78" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M78" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N78" t="s">
         <v>33</v>
@@ -8180,16 +8291,19 @@
         <v>38</v>
       </c>
       <c r="Q78">
-        <v>59.99</v>
+        <v>37.99</v>
       </c>
       <c r="R78">
-        <v>10</v>
+        <v>6.33</v>
       </c>
       <c r="Y78" t="s">
-        <v>57</v>
+        <v>352</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>353</v>
       </c>
       <c r="AA78" t="s">
-        <v>381</v>
+        <v>354</v>
       </c>
       <c r="AB78" t="s">
         <v>39</v>
@@ -8203,13 +8317,13 @@
     </row>
     <row r="79" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>382</v>
+        <v>355</v>
       </c>
       <c r="C79" t="s">
-        <v>383</v>
+        <v>356</v>
       </c>
       <c r="D79" t="s">
-        <v>384</v>
+        <v>357</v>
       </c>
       <c r="E79" t="s">
         <v>33</v>
@@ -8251,10 +8365,10 @@
         <v>2</v>
       </c>
       <c r="Y79" t="s">
-        <v>385</v>
+        <v>58</v>
       </c>
       <c r="AA79" t="s">
-        <v>386</v>
+        <v>358</v>
       </c>
       <c r="AB79" t="s">
         <v>39</v>
@@ -8268,16 +8382,16 @@
     </row>
     <row r="80" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>387</v>
+        <v>359</v>
       </c>
       <c r="C80" t="s">
-        <v>388</v>
+        <v>360</v>
       </c>
       <c r="D80" t="s">
-        <v>389</v>
+        <v>361</v>
       </c>
       <c r="E80" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F80" t="s">
         <v>34</v>
@@ -8292,25 +8406,37 @@
         <v>54</v>
       </c>
       <c r="K80" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="L80" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M80" t="s">
-        <v>45</v>
+        <v>50</v>
+      </c>
+      <c r="N80" t="s">
+        <v>33</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="P80" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q80">
+        <v>75.98</v>
+      </c>
+      <c r="R80">
+        <v>12.66</v>
       </c>
       <c r="Y80" t="s">
-        <v>390</v>
+        <v>101</v>
       </c>
       <c r="Z80" t="s">
-        <v>391</v>
+        <v>59</v>
       </c>
       <c r="AA80" t="s">
-        <v>392</v>
+        <v>362</v>
       </c>
       <c r="AB80" t="s">
         <v>39</v>
@@ -8324,13 +8450,13 @@
     </row>
     <row r="81" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>323</v>
+        <v>363</v>
       </c>
       <c r="C81" t="s">
-        <v>324</v>
+        <v>364</v>
       </c>
       <c r="D81" t="s">
-        <v>393</v>
+        <v>365</v>
       </c>
       <c r="E81" t="s">
         <v>33</v>
@@ -8348,13 +8474,13 @@
         <v>54</v>
       </c>
       <c r="K81" t="s">
-        <v>95</v>
+        <v>260</v>
       </c>
       <c r="L81" t="s">
-        <v>85</v>
+        <v>261</v>
       </c>
       <c r="M81" t="s">
-        <v>86</v>
+        <v>262</v>
       </c>
       <c r="N81" t="s">
         <v>33</v>
@@ -8366,16 +8492,16 @@
         <v>38</v>
       </c>
       <c r="Q81">
-        <v>14.99</v>
+        <v>24.49</v>
       </c>
       <c r="R81">
-        <v>2.5</v>
+        <v>4.08</v>
       </c>
       <c r="Y81" t="s">
-        <v>58</v>
+        <v>366</v>
       </c>
       <c r="AA81" t="s">
-        <v>325</v>
+        <v>367</v>
       </c>
       <c r="AB81" t="s">
         <v>39</v>
@@ -8389,13 +8515,13 @@
     </row>
     <row r="82" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>318</v>
+        <v>265</v>
       </c>
       <c r="C82" t="s">
-        <v>319</v>
+        <v>266</v>
       </c>
       <c r="D82" t="s">
-        <v>320</v>
+        <v>368</v>
       </c>
       <c r="E82" t="s">
         <v>33</v>
@@ -8413,13 +8539,13 @@
         <v>54</v>
       </c>
       <c r="K82" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L82" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M82" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N82" t="s">
         <v>33</v>
@@ -8431,19 +8557,16 @@
         <v>38</v>
       </c>
       <c r="Q82">
-        <v>11.99</v>
+        <v>37.99</v>
       </c>
       <c r="R82">
-        <v>2</v>
+        <v>6.33</v>
       </c>
       <c r="Y82" t="s">
-        <v>321</v>
-      </c>
-      <c r="Z82" t="s">
-        <v>65</v>
+        <v>267</v>
       </c>
       <c r="AA82" t="s">
-        <v>322</v>
+        <v>268</v>
       </c>
       <c r="AB82" t="s">
         <v>39</v>
@@ -8457,13 +8580,13 @@
     </row>
     <row r="83" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>329</v>
+        <v>369</v>
       </c>
       <c r="C83" t="s">
-        <v>330</v>
+        <v>370</v>
       </c>
       <c r="D83" t="s">
-        <v>331</v>
+        <v>371</v>
       </c>
       <c r="E83" t="s">
         <v>33</v>
@@ -8481,13 +8604,13 @@
         <v>54</v>
       </c>
       <c r="K83" t="s">
-        <v>260</v>
+        <v>72</v>
       </c>
       <c r="L83" t="s">
-        <v>261</v>
+        <v>73</v>
       </c>
       <c r="M83" t="s">
-        <v>262</v>
+        <v>74</v>
       </c>
       <c r="N83" t="s">
         <v>33</v>
@@ -8499,16 +8622,22 @@
         <v>38</v>
       </c>
       <c r="Q83">
-        <v>24.49</v>
+        <v>11.99</v>
       </c>
       <c r="R83">
-        <v>4.08</v>
+        <v>2</v>
+      </c>
+      <c r="S83">
+        <v>5.99</v>
+      </c>
+      <c r="T83">
+        <v>1</v>
       </c>
       <c r="Y83" t="s">
-        <v>332</v>
+        <v>84</v>
       </c>
       <c r="AA83" t="s">
-        <v>333</v>
+        <v>372</v>
       </c>
       <c r="AB83" t="s">
         <v>39</v>
@@ -8522,13 +8651,13 @@
     </row>
     <row r="84" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>670</v>
+        <v>373</v>
       </c>
       <c r="C84" t="s">
-        <v>671</v>
+        <v>374</v>
       </c>
       <c r="D84" t="s">
-        <v>672</v>
+        <v>375</v>
       </c>
       <c r="E84" t="s">
         <v>33</v>
@@ -8546,13 +8675,13 @@
         <v>54</v>
       </c>
       <c r="K84" t="s">
-        <v>40</v>
+        <v>260</v>
       </c>
       <c r="L84" t="s">
-        <v>41</v>
+        <v>261</v>
       </c>
       <c r="M84" t="s">
-        <v>42</v>
+        <v>262</v>
       </c>
       <c r="N84" t="s">
         <v>33</v>
@@ -8564,16 +8693,16 @@
         <v>38</v>
       </c>
       <c r="Q84">
-        <v>59.99</v>
+        <v>24.49</v>
       </c>
       <c r="R84">
-        <v>10</v>
+        <v>4.08</v>
       </c>
       <c r="Y84" t="s">
-        <v>673</v>
+        <v>376</v>
       </c>
       <c r="AA84" t="s">
-        <v>674</v>
+        <v>377</v>
       </c>
       <c r="AB84" t="s">
         <v>39</v>
@@ -8587,13 +8716,13 @@
     </row>
     <row r="85" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>675</v>
+        <v>378</v>
       </c>
       <c r="C85" t="s">
-        <v>676</v>
+        <v>379</v>
       </c>
       <c r="D85" t="s">
-        <v>677</v>
+        <v>380</v>
       </c>
       <c r="E85" t="s">
         <v>33</v>
@@ -8611,13 +8740,13 @@
         <v>54</v>
       </c>
       <c r="K85" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L85" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M85" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N85" t="s">
         <v>33</v>
@@ -8629,16 +8758,16 @@
         <v>38</v>
       </c>
       <c r="Q85">
-        <v>37.99</v>
+        <v>59.99</v>
       </c>
       <c r="R85">
-        <v>6.33</v>
+        <v>10</v>
       </c>
       <c r="Y85" t="s">
-        <v>678</v>
+        <v>57</v>
       </c>
       <c r="AA85" t="s">
-        <v>679</v>
+        <v>381</v>
       </c>
       <c r="AB85" t="s">
         <v>39</v>
@@ -8652,13 +8781,13 @@
     </row>
     <row r="86" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>680</v>
+        <v>382</v>
       </c>
       <c r="C86" t="s">
-        <v>681</v>
+        <v>383</v>
       </c>
       <c r="D86" t="s">
-        <v>682</v>
+        <v>384</v>
       </c>
       <c r="E86" t="s">
         <v>33</v>
@@ -8676,13 +8805,13 @@
         <v>54</v>
       </c>
       <c r="K86" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L86" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M86" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N86" t="s">
         <v>33</v>
@@ -8694,19 +8823,16 @@
         <v>38</v>
       </c>
       <c r="Q86">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R86">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y86" t="s">
-        <v>683</v>
-      </c>
-      <c r="Z86" t="s">
-        <v>76</v>
+        <v>385</v>
       </c>
       <c r="AA86" t="s">
-        <v>684</v>
+        <v>386</v>
       </c>
       <c r="AB86" t="s">
         <v>39</v>
@@ -8720,16 +8846,16 @@
     </row>
     <row r="87" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>685</v>
+        <v>387</v>
       </c>
       <c r="C87" t="s">
-        <v>686</v>
+        <v>388</v>
       </c>
       <c r="D87" t="s">
-        <v>687</v>
+        <v>389</v>
       </c>
       <c r="E87" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F87" t="s">
         <v>34</v>
@@ -8744,34 +8870,25 @@
         <v>54</v>
       </c>
       <c r="K87" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="L87" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="M87" t="s">
-        <v>50</v>
-      </c>
-      <c r="N87" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O87">
-        <v>1</v>
-      </c>
-      <c r="P87" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q87">
-        <v>37.99</v>
-      </c>
-      <c r="R87">
-        <v>6.33</v>
+        <v>0</v>
       </c>
       <c r="Y87" t="s">
-        <v>52</v>
+        <v>390</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>391</v>
       </c>
       <c r="AA87" t="s">
-        <v>688</v>
+        <v>392</v>
       </c>
       <c r="AB87" t="s">
         <v>39</v>
@@ -8785,16 +8902,16 @@
     </row>
     <row r="88" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>689</v>
+        <v>323</v>
       </c>
       <c r="C88" t="s">
-        <v>690</v>
+        <v>324</v>
       </c>
       <c r="D88" t="s">
-        <v>691</v>
+        <v>393</v>
       </c>
       <c r="E88" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F88" t="s">
         <v>34</v>
@@ -8806,28 +8923,37 @@
         <v>36</v>
       </c>
       <c r="J88" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K88" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="L88" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="M88" t="s">
-        <v>50</v>
+        <v>86</v>
+      </c>
+      <c r="N88" t="s">
+        <v>33</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P88" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q88">
+        <v>14.99</v>
+      </c>
+      <c r="R88">
+        <v>2.5</v>
       </c>
       <c r="Y88" t="s">
-        <v>692</v>
-      </c>
-      <c r="Z88" t="s">
-        <v>693</v>
+        <v>58</v>
       </c>
       <c r="AA88" t="s">
-        <v>694</v>
+        <v>325</v>
       </c>
       <c r="AB88" t="s">
         <v>39</v>
@@ -8841,16 +8967,16 @@
     </row>
     <row r="89" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>695</v>
+        <v>318</v>
       </c>
       <c r="C89" t="s">
-        <v>696</v>
+        <v>319</v>
       </c>
       <c r="D89" t="s">
-        <v>697</v>
+        <v>320</v>
       </c>
       <c r="E89" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F89" t="s">
         <v>34</v>
@@ -8862,28 +8988,40 @@
         <v>36</v>
       </c>
       <c r="J89" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K89" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L89" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M89" t="s">
-        <v>50</v>
+        <v>74</v>
+      </c>
+      <c r="N89" t="s">
+        <v>33</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P89" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q89">
+        <v>11.99</v>
+      </c>
+      <c r="R89">
+        <v>2</v>
       </c>
       <c r="Y89" t="s">
-        <v>692</v>
+        <v>321</v>
       </c>
       <c r="Z89" t="s">
-        <v>693</v>
+        <v>65</v>
       </c>
       <c r="AA89" t="s">
-        <v>694</v>
+        <v>322</v>
       </c>
       <c r="AB89" t="s">
         <v>39</v>
@@ -8897,13 +9035,13 @@
     </row>
     <row r="90" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>300</v>
+        <v>329</v>
       </c>
       <c r="C90" t="s">
-        <v>301</v>
+        <v>330</v>
       </c>
       <c r="D90" t="s">
-        <v>698</v>
+        <v>331</v>
       </c>
       <c r="E90" t="s">
         <v>33</v>
@@ -8921,13 +9059,13 @@
         <v>54</v>
       </c>
       <c r="K90" t="s">
-        <v>95</v>
+        <v>260</v>
       </c>
       <c r="L90" t="s">
-        <v>85</v>
+        <v>261</v>
       </c>
       <c r="M90" t="s">
-        <v>86</v>
+        <v>262</v>
       </c>
       <c r="N90" t="s">
         <v>33</v>
@@ -8939,16 +9077,16 @@
         <v>38</v>
       </c>
       <c r="Q90">
-        <v>14.99</v>
+        <v>24.49</v>
       </c>
       <c r="R90">
-        <v>2.5</v>
+        <v>4.08</v>
       </c>
       <c r="Y90" t="s">
-        <v>58</v>
+        <v>332</v>
       </c>
       <c r="AA90" t="s">
-        <v>302</v>
+        <v>333</v>
       </c>
       <c r="AB90" t="s">
         <v>39</v>
@@ -8962,16 +9100,16 @@
     </row>
     <row r="91" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>699</v>
+        <v>670</v>
       </c>
       <c r="C91" t="s">
-        <v>700</v>
+        <v>671</v>
       </c>
       <c r="D91" t="s">
-        <v>701</v>
+        <v>672</v>
       </c>
       <c r="E91" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F91" t="s">
         <v>34</v>
@@ -8986,25 +9124,34 @@
         <v>54</v>
       </c>
       <c r="K91" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L91" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M91" t="s">
-        <v>50</v>
+        <v>42</v>
+      </c>
+      <c r="N91" t="s">
+        <v>33</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P91" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q91">
+        <v>59.99</v>
+      </c>
+      <c r="R91">
+        <v>10</v>
       </c>
       <c r="Y91" t="s">
-        <v>692</v>
-      </c>
-      <c r="Z91" t="s">
-        <v>693</v>
+        <v>673</v>
       </c>
       <c r="AA91" t="s">
-        <v>694</v>
+        <v>674</v>
       </c>
       <c r="AB91" t="s">
         <v>39</v>
@@ -9018,13 +9165,13 @@
     </row>
     <row r="92" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>303</v>
+        <v>675</v>
       </c>
       <c r="C92" t="s">
-        <v>304</v>
+        <v>676</v>
       </c>
       <c r="D92" t="s">
-        <v>702</v>
+        <v>677</v>
       </c>
       <c r="E92" t="s">
         <v>33</v>
@@ -9042,13 +9189,13 @@
         <v>54</v>
       </c>
       <c r="K92" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L92" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M92" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N92" t="s">
         <v>33</v>
@@ -9060,16 +9207,16 @@
         <v>38</v>
       </c>
       <c r="Q92">
-        <v>59.99</v>
+        <v>37.99</v>
       </c>
       <c r="R92">
-        <v>10</v>
+        <v>6.33</v>
       </c>
       <c r="Y92" t="s">
-        <v>305</v>
+        <v>678</v>
       </c>
       <c r="AA92" t="s">
-        <v>306</v>
+        <v>679</v>
       </c>
       <c r="AB92" t="s">
         <v>39</v>
@@ -9083,13 +9230,13 @@
     </row>
     <row r="93" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>292</v>
+        <v>680</v>
       </c>
       <c r="C93" t="s">
-        <v>293</v>
+        <v>681</v>
       </c>
       <c r="D93" t="s">
-        <v>294</v>
+        <v>682</v>
       </c>
       <c r="E93" t="s">
         <v>33</v>
@@ -9104,7 +9251,7 @@
         <v>36</v>
       </c>
       <c r="J93" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K93" t="s">
         <v>40</v>
@@ -9131,13 +9278,13 @@
         <v>10</v>
       </c>
       <c r="Y93" t="s">
-        <v>77</v>
+        <v>683</v>
       </c>
       <c r="Z93" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="AA93" t="s">
-        <v>295</v>
+        <v>684</v>
       </c>
       <c r="AB93" t="s">
         <v>39</v>
@@ -9151,13 +9298,13 @@
     </row>
     <row r="94" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>296</v>
+        <v>685</v>
       </c>
       <c r="C94" t="s">
-        <v>297</v>
+        <v>686</v>
       </c>
       <c r="D94" t="s">
-        <v>298</v>
+        <v>687</v>
       </c>
       <c r="E94" t="s">
         <v>33</v>
@@ -9172,16 +9319,16 @@
         <v>36</v>
       </c>
       <c r="J94" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K94" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L94" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M94" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N94" t="s">
         <v>33</v>
@@ -9193,19 +9340,16 @@
         <v>38</v>
       </c>
       <c r="Q94">
-        <v>59.99</v>
+        <v>37.99</v>
       </c>
       <c r="R94">
-        <v>10</v>
+        <v>6.33</v>
       </c>
       <c r="Y94" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z94" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AA94" t="s">
-        <v>299</v>
+        <v>688</v>
       </c>
       <c r="AB94" t="s">
         <v>39</v>
@@ -9219,16 +9363,16 @@
     </row>
     <row r="95" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>307</v>
+        <v>689</v>
       </c>
       <c r="C95" t="s">
-        <v>308</v>
+        <v>690</v>
       </c>
       <c r="D95" t="s">
-        <v>309</v>
+        <v>691</v>
       </c>
       <c r="E95" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F95" t="s">
         <v>34</v>
@@ -9243,34 +9387,25 @@
         <v>37</v>
       </c>
       <c r="K95" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="L95" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="M95" t="s">
-        <v>89</v>
-      </c>
-      <c r="N95" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="O95">
-        <v>1</v>
-      </c>
-      <c r="P95" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q95">
-        <v>20.49</v>
-      </c>
-      <c r="R95">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="Y95" t="s">
-        <v>310</v>
+        <v>692</v>
+      </c>
+      <c r="Z95" t="s">
+        <v>693</v>
       </c>
       <c r="AA95" t="s">
-        <v>311</v>
+        <v>694</v>
       </c>
       <c r="AB95" t="s">
         <v>39</v>
@@ -9284,16 +9419,16 @@
     </row>
     <row r="96" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>312</v>
+        <v>695</v>
       </c>
       <c r="C96" t="s">
-        <v>313</v>
+        <v>696</v>
       </c>
       <c r="D96" t="s">
-        <v>314</v>
+        <v>697</v>
       </c>
       <c r="E96" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F96" t="s">
         <v>34</v>
@@ -9308,37 +9443,25 @@
         <v>37</v>
       </c>
       <c r="K96" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L96" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M96" t="s">
-        <v>42</v>
-      </c>
-      <c r="N96" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="O96">
-        <v>1</v>
-      </c>
-      <c r="P96" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q96">
-        <v>59.99</v>
-      </c>
-      <c r="R96">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y96" t="s">
-        <v>100</v>
+        <v>692</v>
       </c>
       <c r="Z96" t="s">
-        <v>315</v>
+        <v>693</v>
       </c>
       <c r="AA96" t="s">
-        <v>316</v>
+        <v>694</v>
       </c>
       <c r="AB96" t="s">
         <v>39</v>
@@ -9352,13 +9475,13 @@
     </row>
     <row r="97" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>253</v>
+        <v>300</v>
       </c>
       <c r="C97" t="s">
-        <v>254</v>
+        <v>301</v>
       </c>
       <c r="D97" t="s">
-        <v>317</v>
+        <v>698</v>
       </c>
       <c r="E97" t="s">
         <v>33</v>
@@ -9376,13 +9499,13 @@
         <v>54</v>
       </c>
       <c r="K97" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="L97" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="M97" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="N97" t="s">
         <v>33</v>
@@ -9394,19 +9517,16 @@
         <v>38</v>
       </c>
       <c r="Q97">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="R97">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="Y97" t="s">
-        <v>255</v>
-      </c>
-      <c r="Z97" t="s">
-        <v>102</v>
+        <v>58</v>
       </c>
       <c r="AA97" t="s">
-        <v>256</v>
+        <v>302</v>
       </c>
       <c r="AB97" t="s">
         <v>39</v>
@@ -9420,16 +9540,16 @@
     </row>
     <row r="98" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>257</v>
+        <v>699</v>
       </c>
       <c r="C98" t="s">
-        <v>258</v>
+        <v>700</v>
       </c>
       <c r="D98" t="s">
-        <v>259</v>
+        <v>701</v>
       </c>
       <c r="E98" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F98" t="s">
         <v>34</v>
@@ -9444,37 +9564,25 @@
         <v>54</v>
       </c>
       <c r="K98" t="s">
-        <v>260</v>
+        <v>48</v>
       </c>
       <c r="L98" t="s">
-        <v>261</v>
+        <v>49</v>
       </c>
       <c r="M98" t="s">
-        <v>262</v>
-      </c>
-      <c r="N98" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="O98">
-        <v>1</v>
-      </c>
-      <c r="P98" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q98">
-        <v>24.49</v>
-      </c>
-      <c r="R98">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="Y98" t="s">
-        <v>263</v>
+        <v>692</v>
       </c>
       <c r="Z98" t="s">
-        <v>64</v>
+        <v>693</v>
       </c>
       <c r="AA98" t="s">
-        <v>264</v>
+        <v>694</v>
       </c>
       <c r="AB98" t="s">
         <v>39</v>
@@ -9488,13 +9596,13 @@
     </row>
     <row r="99" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>269</v>
+        <v>303</v>
       </c>
       <c r="C99" t="s">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="D99" t="s">
-        <v>271</v>
+        <v>702</v>
       </c>
       <c r="E99" t="s">
         <v>33</v>
@@ -9536,10 +9644,10 @@
         <v>10</v>
       </c>
       <c r="Y99" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="AA99" t="s">
-        <v>273</v>
+        <v>306</v>
       </c>
       <c r="AB99" t="s">
         <v>39</v>
@@ -9553,13 +9661,13 @@
     </row>
     <row r="100" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>149</v>
+        <v>292</v>
       </c>
       <c r="C100" t="s">
-        <v>150</v>
+        <v>293</v>
       </c>
       <c r="D100" t="s">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="E100" t="s">
         <v>33</v>
@@ -9574,7 +9682,7 @@
         <v>36</v>
       </c>
       <c r="J100" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K100" t="s">
         <v>40</v>
@@ -9601,10 +9709,13 @@
         <v>10</v>
       </c>
       <c r="Y100" t="s">
-        <v>63</v>
+        <v>77</v>
+      </c>
+      <c r="Z100" t="s">
+        <v>92</v>
       </c>
       <c r="AA100" t="s">
-        <v>151</v>
+        <v>295</v>
       </c>
       <c r="AB100" t="s">
         <v>39</v>
@@ -9618,13 +9729,13 @@
     </row>
     <row r="101" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="C101" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="D101" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="E101" t="s">
         <v>33</v>
@@ -9639,7 +9750,7 @@
         <v>36</v>
       </c>
       <c r="J101" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K101" t="s">
         <v>40</v>
@@ -9654,25 +9765,25 @@
         <v>33</v>
       </c>
       <c r="O101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P101" t="s">
         <v>38</v>
       </c>
       <c r="Q101">
-        <v>119.98</v>
+        <v>59.99</v>
       </c>
       <c r="R101">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Y101" t="s">
-        <v>278</v>
+        <v>62</v>
       </c>
       <c r="Z101" t="s">
-        <v>279</v>
+        <v>51</v>
       </c>
       <c r="AA101" t="s">
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="AB101" t="s">
         <v>39</v>
@@ -9686,13 +9797,13 @@
     </row>
     <row r="102" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>281</v>
+        <v>307</v>
       </c>
       <c r="C102" t="s">
-        <v>282</v>
+        <v>308</v>
       </c>
       <c r="D102" t="s">
-        <v>283</v>
+        <v>309</v>
       </c>
       <c r="E102" t="s">
         <v>33</v>
@@ -9710,13 +9821,13 @@
         <v>37</v>
       </c>
       <c r="K102" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="L102" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="M102" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="N102" t="s">
         <v>33</v>
@@ -9728,16 +9839,16 @@
         <v>38</v>
       </c>
       <c r="Q102">
-        <v>11.99</v>
+        <v>20.49</v>
       </c>
       <c r="R102">
-        <v>2</v>
+        <v>3.42</v>
       </c>
       <c r="Y102" t="s">
-        <v>75</v>
+        <v>310</v>
       </c>
       <c r="AA102" t="s">
-        <v>284</v>
+        <v>311</v>
       </c>
       <c r="AB102" t="s">
         <v>39</v>
@@ -9751,16 +9862,16 @@
     </row>
     <row r="103" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>238</v>
+        <v>312</v>
       </c>
       <c r="C103" t="s">
-        <v>239</v>
+        <v>313</v>
       </c>
       <c r="D103" t="s">
-        <v>285</v>
+        <v>314</v>
       </c>
       <c r="E103" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F103" t="s">
         <v>34</v>
@@ -9772,7 +9883,7 @@
         <v>36</v>
       </c>
       <c r="J103" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K103" t="s">
         <v>40</v>
@@ -9783,14 +9894,29 @@
       <c r="M103" t="s">
         <v>42</v>
       </c>
+      <c r="N103" t="s">
+        <v>33</v>
+      </c>
       <c r="O103">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P103" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q103">
+        <v>59.99</v>
+      </c>
+      <c r="R103">
+        <v>10</v>
       </c>
       <c r="Y103" t="s">
-        <v>240</v>
+        <v>100</v>
+      </c>
+      <c r="Z103" t="s">
+        <v>315</v>
       </c>
       <c r="AA103" t="s">
-        <v>241</v>
+        <v>316</v>
       </c>
       <c r="AB103" t="s">
         <v>39</v>
@@ -9804,13 +9930,13 @@
     </row>
     <row r="104" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>224</v>
+        <v>253</v>
       </c>
       <c r="C104" t="s">
-        <v>225</v>
+        <v>254</v>
       </c>
       <c r="D104" t="s">
-        <v>286</v>
+        <v>317</v>
       </c>
       <c r="E104" t="s">
         <v>33</v>
@@ -9852,10 +9978,13 @@
         <v>10</v>
       </c>
       <c r="Y104" t="s">
-        <v>226</v>
+        <v>255</v>
+      </c>
+      <c r="Z104" t="s">
+        <v>102</v>
       </c>
       <c r="AA104" t="s">
-        <v>227</v>
+        <v>256</v>
       </c>
       <c r="AB104" t="s">
         <v>39</v>
@@ -9869,13 +9998,13 @@
     </row>
     <row r="105" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>213</v>
+        <v>257</v>
       </c>
       <c r="C105" t="s">
-        <v>214</v>
+        <v>258</v>
       </c>
       <c r="D105" t="s">
-        <v>287</v>
+        <v>259</v>
       </c>
       <c r="E105" t="s">
         <v>33</v>
@@ -9893,13 +10022,13 @@
         <v>54</v>
       </c>
       <c r="K105" t="s">
-        <v>40</v>
+        <v>260</v>
       </c>
       <c r="L105" t="s">
-        <v>41</v>
+        <v>261</v>
       </c>
       <c r="M105" t="s">
-        <v>42</v>
+        <v>262</v>
       </c>
       <c r="N105" t="s">
         <v>33</v>
@@ -9911,19 +10040,19 @@
         <v>38</v>
       </c>
       <c r="Q105">
-        <v>59.99</v>
+        <v>24.49</v>
       </c>
       <c r="R105">
-        <v>10</v>
+        <v>4.08</v>
       </c>
       <c r="Y105" t="s">
-        <v>215</v>
+        <v>263</v>
       </c>
       <c r="Z105" t="s">
-        <v>216</v>
+        <v>64</v>
       </c>
       <c r="AA105" t="s">
-        <v>217</v>
+        <v>264</v>
       </c>
       <c r="AB105" t="s">
         <v>39</v>
@@ -9937,13 +10066,13 @@
     </row>
     <row r="106" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>218</v>
+        <v>269</v>
       </c>
       <c r="C106" t="s">
-        <v>219</v>
+        <v>270</v>
       </c>
       <c r="D106" t="s">
-        <v>220</v>
+        <v>271</v>
       </c>
       <c r="E106" t="s">
         <v>33</v>
@@ -9961,13 +10090,13 @@
         <v>54</v>
       </c>
       <c r="K106" t="s">
-        <v>203</v>
+        <v>40</v>
       </c>
       <c r="L106" t="s">
-        <v>204</v>
+        <v>41</v>
       </c>
       <c r="M106" t="s">
-        <v>205</v>
+        <v>42</v>
       </c>
       <c r="N106" t="s">
         <v>33</v>
@@ -9979,19 +10108,16 @@
         <v>38</v>
       </c>
       <c r="Q106">
-        <v>69.989999999999995</v>
+        <v>59.99</v>
       </c>
       <c r="R106">
-        <v>11.67</v>
+        <v>10</v>
       </c>
       <c r="Y106" t="s">
-        <v>221</v>
-      </c>
-      <c r="Z106" t="s">
-        <v>222</v>
+        <v>272</v>
       </c>
       <c r="AA106" t="s">
-        <v>223</v>
+        <v>273</v>
       </c>
       <c r="AB106" t="s">
         <v>39</v>
@@ -10005,13 +10131,13 @@
     </row>
     <row r="107" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>228</v>
+        <v>149</v>
       </c>
       <c r="C107" t="s">
-        <v>229</v>
+        <v>150</v>
       </c>
       <c r="D107" t="s">
-        <v>230</v>
+        <v>274</v>
       </c>
       <c r="E107" t="s">
         <v>33</v>
@@ -10053,10 +10179,10 @@
         <v>10</v>
       </c>
       <c r="Y107" t="s">
-        <v>231</v>
+        <v>63</v>
       </c>
       <c r="AA107" t="s">
-        <v>232</v>
+        <v>151</v>
       </c>
       <c r="AB107" t="s">
         <v>39</v>
@@ -10070,13 +10196,13 @@
     </row>
     <row r="108" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>233</v>
+        <v>275</v>
       </c>
       <c r="C108" t="s">
-        <v>234</v>
+        <v>276</v>
       </c>
       <c r="D108" t="s">
-        <v>235</v>
+        <v>277</v>
       </c>
       <c r="E108" t="s">
         <v>33</v>
@@ -10094,34 +10220,37 @@
         <v>54</v>
       </c>
       <c r="K108" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="L108" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="M108" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="N108" t="s">
         <v>33</v>
       </c>
       <c r="O108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P108" t="s">
         <v>38</v>
       </c>
       <c r="Q108">
-        <v>14.99</v>
+        <v>119.98</v>
       </c>
       <c r="R108">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="Y108" t="s">
-        <v>236</v>
+        <v>278</v>
+      </c>
+      <c r="Z108" t="s">
+        <v>279</v>
       </c>
       <c r="AA108" t="s">
-        <v>237</v>
+        <v>280</v>
       </c>
       <c r="AB108" t="s">
         <v>39</v>
@@ -10135,16 +10264,16 @@
     </row>
     <row r="109" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>242</v>
+        <v>281</v>
       </c>
       <c r="C109" t="s">
-        <v>243</v>
+        <v>282</v>
       </c>
       <c r="D109" t="s">
-        <v>244</v>
+        <v>283</v>
       </c>
       <c r="E109" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F109" t="s">
         <v>34</v>
@@ -10156,25 +10285,37 @@
         <v>36</v>
       </c>
       <c r="J109" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K109" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L109" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M109" t="s">
-        <v>42</v>
+        <v>74</v>
+      </c>
+      <c r="N109" t="s">
+        <v>33</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P109" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q109">
+        <v>11.99</v>
+      </c>
+      <c r="R109">
+        <v>2</v>
       </c>
       <c r="Y109" t="s">
-        <v>240</v>
+        <v>75</v>
       </c>
       <c r="AA109" t="s">
-        <v>241</v>
+        <v>284</v>
       </c>
       <c r="AB109" t="s">
         <v>39</v>
@@ -10188,16 +10329,16 @@
     </row>
     <row r="110" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="C110" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="D110" t="s">
-        <v>247</v>
+        <v>285</v>
       </c>
       <c r="E110" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F110" t="s">
         <v>34</v>
@@ -10209,7 +10350,7 @@
         <v>36</v>
       </c>
       <c r="J110" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K110" t="s">
         <v>40</v>
@@ -10220,26 +10361,14 @@
       <c r="M110" t="s">
         <v>42</v>
       </c>
-      <c r="N110" t="s">
-        <v>33</v>
-      </c>
       <c r="O110">
-        <v>1</v>
-      </c>
-      <c r="P110" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q110">
-        <v>59.99</v>
-      </c>
-      <c r="R110">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y110" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="AA110" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="AB110" t="s">
         <v>39</v>
@@ -10253,13 +10382,13 @@
     </row>
     <row r="111" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>188</v>
+        <v>224</v>
       </c>
       <c r="C111" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D111" t="s">
-        <v>250</v>
+        <v>286</v>
       </c>
       <c r="E111" t="s">
         <v>33</v>
@@ -10274,16 +10403,16 @@
         <v>36</v>
       </c>
       <c r="J111" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K111" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L111" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M111" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N111" t="s">
         <v>33</v>
@@ -10295,16 +10424,16 @@
         <v>38</v>
       </c>
       <c r="Q111">
-        <v>37.99</v>
+        <v>59.99</v>
       </c>
       <c r="R111">
-        <v>6.33</v>
+        <v>10</v>
       </c>
       <c r="Y111" t="s">
-        <v>52</v>
+        <v>226</v>
       </c>
       <c r="AA111" t="s">
-        <v>190</v>
+        <v>227</v>
       </c>
       <c r="AB111" t="s">
         <v>39</v>
@@ -10318,13 +10447,13 @@
     </row>
     <row r="112" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="C112" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="D112" t="s">
-        <v>251</v>
+        <v>287</v>
       </c>
       <c r="E112" t="s">
         <v>33</v>
@@ -10366,10 +10495,13 @@
         <v>10</v>
       </c>
       <c r="Y112" t="s">
-        <v>193</v>
+        <v>215</v>
+      </c>
+      <c r="Z112" t="s">
+        <v>216</v>
       </c>
       <c r="AA112" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="AB112" t="s">
         <v>39</v>
@@ -10383,13 +10515,13 @@
     </row>
     <row r="113" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="C113" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="D113" t="s">
-        <v>252</v>
+        <v>220</v>
       </c>
       <c r="E113" t="s">
         <v>33</v>
@@ -10431,13 +10563,13 @@
         <v>11.67</v>
       </c>
       <c r="Y113" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="Z113" t="s">
-        <v>60</v>
+        <v>222</v>
       </c>
       <c r="AA113" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="AB113" t="s">
         <v>39</v>
@@ -10451,13 +10583,13 @@
     </row>
     <row r="114" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>195</v>
+        <v>228</v>
       </c>
       <c r="C114" t="s">
-        <v>196</v>
+        <v>229</v>
       </c>
       <c r="D114" t="s">
-        <v>197</v>
+        <v>230</v>
       </c>
       <c r="E114" t="s">
         <v>33</v>
@@ -10472,7 +10604,7 @@
         <v>36</v>
       </c>
       <c r="J114" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K114" t="s">
         <v>40</v>
@@ -10499,13 +10631,10 @@
         <v>10</v>
       </c>
       <c r="Y114" t="s">
-        <v>198</v>
-      </c>
-      <c r="Z114" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="AA114" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="AB114" t="s">
         <v>39</v>
@@ -10519,13 +10648,13 @@
     </row>
     <row r="115" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="C115" t="s">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="D115" t="s">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="E115" t="s">
         <v>33</v>
@@ -10540,16 +10669,16 @@
         <v>36</v>
       </c>
       <c r="J115" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K115" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="L115" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="M115" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="N115" t="s">
         <v>33</v>
@@ -10561,16 +10690,16 @@
         <v>38</v>
       </c>
       <c r="Q115">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="R115">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="Y115" t="s">
-        <v>211</v>
+        <v>236</v>
       </c>
       <c r="AA115" t="s">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="AB115" t="s">
         <v>39</v>
@@ -10584,16 +10713,16 @@
     </row>
     <row r="116" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>152</v>
+        <v>242</v>
       </c>
       <c r="C116" t="s">
-        <v>153</v>
+        <v>243</v>
       </c>
       <c r="D116" t="s">
-        <v>154</v>
+        <v>244</v>
       </c>
       <c r="E116" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F116" t="s">
         <v>34</v>
@@ -10608,34 +10737,22 @@
         <v>54</v>
       </c>
       <c r="K116" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="L116" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="M116" t="s">
-        <v>86</v>
-      </c>
-      <c r="N116" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O116">
-        <v>1</v>
-      </c>
-      <c r="P116" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q116">
-        <v>14.99</v>
-      </c>
-      <c r="R116">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y116" t="s">
-        <v>155</v>
+        <v>240</v>
       </c>
       <c r="AA116" t="s">
-        <v>156</v>
+        <v>241</v>
       </c>
       <c r="AB116" t="s">
         <v>39</v>
@@ -10649,13 +10766,13 @@
     </row>
     <row r="117" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>157</v>
+        <v>245</v>
       </c>
       <c r="C117" t="s">
-        <v>158</v>
+        <v>246</v>
       </c>
       <c r="D117" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="E117" t="s">
         <v>33</v>
@@ -10670,16 +10787,16 @@
         <v>36</v>
       </c>
       <c r="J117" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K117" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L117" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M117" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N117" t="s">
         <v>33</v>
@@ -10691,16 +10808,16 @@
         <v>38</v>
       </c>
       <c r="Q117">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R117">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y117" t="s">
-        <v>68</v>
+        <v>248</v>
       </c>
       <c r="AA117" t="s">
-        <v>160</v>
+        <v>249</v>
       </c>
       <c r="AB117" t="s">
         <v>39</v>
@@ -10714,16 +10831,16 @@
     </row>
     <row r="118" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="C118" t="s">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="D118" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="E118" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F118" t="s">
         <v>34</v>
@@ -10735,25 +10852,37 @@
         <v>36</v>
       </c>
       <c r="J118" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K118" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L118" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M118" t="s">
-        <v>42</v>
+        <v>50</v>
+      </c>
+      <c r="N118" t="s">
+        <v>33</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P118" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q118">
+        <v>37.99</v>
+      </c>
+      <c r="R118">
+        <v>6.33</v>
       </c>
       <c r="Y118" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="AA118" t="s">
-        <v>151</v>
+        <v>190</v>
       </c>
       <c r="AB118" t="s">
         <v>39</v>
@@ -10767,13 +10896,13 @@
     </row>
     <row r="119" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="C119" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="D119" t="s">
-        <v>166</v>
+        <v>251</v>
       </c>
       <c r="E119" t="s">
         <v>33</v>
@@ -10791,13 +10920,13 @@
         <v>54</v>
       </c>
       <c r="K119" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L119" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M119" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N119" t="s">
         <v>33</v>
@@ -10809,16 +10938,16 @@
         <v>38</v>
       </c>
       <c r="Q119">
-        <v>37.99</v>
+        <v>59.99</v>
       </c>
       <c r="R119">
-        <v>6.33</v>
+        <v>10</v>
       </c>
       <c r="Y119" t="s">
-        <v>100</v>
+        <v>193</v>
       </c>
       <c r="AA119" t="s">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="AB119" t="s">
         <v>39</v>
@@ -10832,13 +10961,13 @@
     </row>
     <row r="120" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="C120" t="s">
-        <v>169</v>
+        <v>202</v>
       </c>
       <c r="D120" t="s">
-        <v>170</v>
+        <v>252</v>
       </c>
       <c r="E120" t="s">
         <v>33</v>
@@ -10856,13 +10985,13 @@
         <v>54</v>
       </c>
       <c r="K120" t="s">
-        <v>72</v>
+        <v>203</v>
       </c>
       <c r="L120" t="s">
-        <v>73</v>
+        <v>204</v>
       </c>
       <c r="M120" t="s">
-        <v>74</v>
+        <v>205</v>
       </c>
       <c r="N120" t="s">
         <v>33</v>
@@ -10874,16 +11003,19 @@
         <v>38</v>
       </c>
       <c r="Q120">
-        <v>11.99</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="R120">
-        <v>2</v>
+        <v>11.67</v>
       </c>
       <c r="Y120" t="s">
-        <v>66</v>
+        <v>206</v>
+      </c>
+      <c r="Z120" t="s">
+        <v>60</v>
       </c>
       <c r="AA120" t="s">
-        <v>171</v>
+        <v>207</v>
       </c>
       <c r="AB120" t="s">
         <v>39</v>
@@ -10897,13 +11029,13 @@
     </row>
     <row r="121" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="C121" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="D121" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="E121" t="s">
         <v>33</v>
@@ -10918,16 +11050,16 @@
         <v>36</v>
       </c>
       <c r="J121" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K121" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L121" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M121" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="N121" t="s">
         <v>33</v>
@@ -10939,16 +11071,19 @@
         <v>38</v>
       </c>
       <c r="Q121">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R121">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y121" t="s">
-        <v>175</v>
+        <v>198</v>
+      </c>
+      <c r="Z121" t="s">
+        <v>199</v>
       </c>
       <c r="AA121" t="s">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="AB121" t="s">
         <v>39</v>
@@ -10962,13 +11097,13 @@
     </row>
     <row r="122" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="C122" t="s">
-        <v>178</v>
+        <v>209</v>
       </c>
       <c r="D122" t="s">
-        <v>179</v>
+        <v>210</v>
       </c>
       <c r="E122" t="s">
         <v>33</v>
@@ -10983,16 +11118,16 @@
         <v>36</v>
       </c>
       <c r="J122" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K122" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L122" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M122" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N122" t="s">
         <v>33</v>
@@ -11004,19 +11139,16 @@
         <v>38</v>
       </c>
       <c r="Q122">
-        <v>37.99</v>
+        <v>59.99</v>
       </c>
       <c r="R122">
-        <v>6.33</v>
+        <v>10</v>
       </c>
       <c r="Y122" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z122" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="AA122" t="s">
-        <v>182</v>
+        <v>212</v>
       </c>
       <c r="AB122" t="s">
         <v>39</v>
@@ -11030,13 +11162,13 @@
     </row>
     <row r="123" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="C123" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="D123" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="E123" t="s">
         <v>33</v>
@@ -11054,37 +11186,34 @@
         <v>54</v>
       </c>
       <c r="K123" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="L123" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="M123" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="N123" t="s">
         <v>33</v>
       </c>
       <c r="O123">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P123" t="s">
         <v>38</v>
       </c>
       <c r="Q123">
-        <v>75.98</v>
+        <v>14.99</v>
       </c>
       <c r="R123">
-        <v>12.66</v>
+        <v>2.5</v>
       </c>
       <c r="Y123" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z123" t="s">
-        <v>47</v>
+        <v>155</v>
       </c>
       <c r="AA123" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="AB123" t="s">
         <v>39</v>
@@ -11098,13 +11227,13 @@
     </row>
     <row r="124" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="C124" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="D124" t="s">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="E124" t="s">
         <v>33</v>
@@ -11146,10 +11275,10 @@
         <v>2</v>
       </c>
       <c r="Y124" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AA124" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="AB124" t="s">
         <v>39</v>
@@ -11163,16 +11292,16 @@
     </row>
     <row r="125" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>117</v>
+        <v>161</v>
       </c>
       <c r="C125" t="s">
-        <v>118</v>
+        <v>162</v>
       </c>
       <c r="D125" t="s">
-        <v>119</v>
+        <v>163</v>
       </c>
       <c r="E125" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F125" t="s">
         <v>34</v>
@@ -11187,37 +11316,22 @@
         <v>54</v>
       </c>
       <c r="K125" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L125" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M125" t="s">
-        <v>83</v>
-      </c>
-      <c r="N125" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O125">
-        <v>1</v>
-      </c>
-      <c r="P125" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q125">
-        <v>14.99</v>
-      </c>
-      <c r="R125">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y125" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z125" t="s">
-        <v>121</v>
+        <v>63</v>
       </c>
       <c r="AA125" t="s">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="AB125" t="s">
         <v>39</v>
@@ -11231,13 +11345,13 @@
     </row>
     <row r="126" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="C126" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
       <c r="D126" t="s">
-        <v>125</v>
+        <v>166</v>
       </c>
       <c r="E126" t="s">
         <v>33</v>
@@ -11255,13 +11369,13 @@
         <v>54</v>
       </c>
       <c r="K126" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L126" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M126" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N126" t="s">
         <v>33</v>
@@ -11273,19 +11387,16 @@
         <v>38</v>
       </c>
       <c r="Q126">
-        <v>59.99</v>
+        <v>37.99</v>
       </c>
       <c r="R126">
-        <v>10</v>
+        <v>6.33</v>
       </c>
       <c r="Y126" t="s">
-        <v>126</v>
-      </c>
-      <c r="Z126" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="AA126" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="AB126" t="s">
         <v>39</v>
@@ -11299,13 +11410,13 @@
     </row>
     <row r="127" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>129</v>
+        <v>168</v>
       </c>
       <c r="C127" t="s">
-        <v>130</v>
+        <v>169</v>
       </c>
       <c r="D127" t="s">
-        <v>131</v>
+        <v>170</v>
       </c>
       <c r="E127" t="s">
         <v>33</v>
@@ -11323,13 +11434,13 @@
         <v>54</v>
       </c>
       <c r="K127" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="L127" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="M127" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="N127" t="s">
         <v>33</v>
@@ -11341,16 +11452,16 @@
         <v>38</v>
       </c>
       <c r="Q127">
-        <v>38.49</v>
+        <v>11.99</v>
       </c>
       <c r="R127">
-        <v>6.42</v>
+        <v>2</v>
       </c>
       <c r="Y127" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="AA127" t="s">
-        <v>132</v>
+        <v>171</v>
       </c>
       <c r="AB127" t="s">
         <v>39</v>
@@ -11364,16 +11475,16 @@
     </row>
     <row r="128" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="C128" t="s">
-        <v>106</v>
+        <v>173</v>
       </c>
       <c r="D128" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="E128" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F128" t="s">
         <v>34</v>
@@ -11396,14 +11507,26 @@
       <c r="M128" t="s">
         <v>83</v>
       </c>
+      <c r="N128" t="s">
+        <v>33</v>
+      </c>
       <c r="O128">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P128" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q128">
+        <v>14.99</v>
+      </c>
+      <c r="R128">
+        <v>2.5</v>
       </c>
       <c r="Y128" t="s">
-        <v>103</v>
+        <v>175</v>
       </c>
       <c r="AA128" t="s">
-        <v>104</v>
+        <v>176</v>
       </c>
       <c r="AB128" t="s">
         <v>39</v>
@@ -11417,13 +11540,13 @@
     </row>
     <row r="129" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>107</v>
+        <v>177</v>
       </c>
       <c r="C129" t="s">
-        <v>108</v>
+        <v>178</v>
       </c>
       <c r="D129" t="s">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="E129" t="s">
         <v>33</v>
@@ -11465,13 +11588,13 @@
         <v>6.33</v>
       </c>
       <c r="Y129" t="s">
-        <v>109</v>
+        <v>180</v>
       </c>
       <c r="Z129" t="s">
-        <v>110</v>
+        <v>181</v>
       </c>
       <c r="AA129" t="s">
-        <v>111</v>
+        <v>182</v>
       </c>
       <c r="AB129" t="s">
         <v>39</v>
@@ -11485,13 +11608,13 @@
     </row>
     <row r="130" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>112</v>
+        <v>183</v>
       </c>
       <c r="C130" t="s">
-        <v>113</v>
+        <v>184</v>
       </c>
       <c r="D130" t="s">
-        <v>114</v>
+        <v>179</v>
       </c>
       <c r="E130" t="s">
         <v>33</v>
@@ -11506,40 +11629,40 @@
         <v>36</v>
       </c>
       <c r="J130" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K130" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L130" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M130" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N130" t="s">
         <v>33</v>
       </c>
       <c r="O130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P130" t="s">
         <v>38</v>
       </c>
       <c r="Q130">
-        <v>59.99</v>
+        <v>75.98</v>
       </c>
       <c r="R130">
-        <v>10</v>
+        <v>12.66</v>
       </c>
       <c r="Y130" t="s">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="Z130" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="AA130" t="s">
-        <v>116</v>
+        <v>185</v>
       </c>
       <c r="AB130" t="s">
         <v>39</v>
@@ -11553,13 +11676,13 @@
     </row>
     <row r="131" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>703</v>
+        <v>133</v>
       </c>
       <c r="C131" t="s">
-        <v>704</v>
+        <v>134</v>
       </c>
       <c r="D131" t="s">
-        <v>705</v>
+        <v>186</v>
       </c>
       <c r="E131" t="s">
         <v>33</v>
@@ -11601,18 +11724,473 @@
         <v>2</v>
       </c>
       <c r="Y131" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA131" t="s">
+        <v>135</v>
+      </c>
+      <c r="AB131" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>117</v>
+      </c>
+      <c r="C132" t="s">
+        <v>118</v>
+      </c>
+      <c r="D132" t="s">
+        <v>119</v>
+      </c>
+      <c r="E132" t="s">
+        <v>33</v>
+      </c>
+      <c r="F132" t="s">
+        <v>34</v>
+      </c>
+      <c r="G132" t="s">
+        <v>35</v>
+      </c>
+      <c r="H132" t="s">
+        <v>36</v>
+      </c>
+      <c r="J132" t="s">
+        <v>54</v>
+      </c>
+      <c r="K132" t="s">
+        <v>94</v>
+      </c>
+      <c r="L132" t="s">
+        <v>82</v>
+      </c>
+      <c r="M132" t="s">
+        <v>83</v>
+      </c>
+      <c r="N132" t="s">
+        <v>33</v>
+      </c>
+      <c r="O132">
+        <v>1</v>
+      </c>
+      <c r="P132" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q132">
+        <v>14.99</v>
+      </c>
+      <c r="R132">
+        <v>2.5</v>
+      </c>
+      <c r="Y132" t="s">
+        <v>120</v>
+      </c>
+      <c r="Z132" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA132" t="s">
+        <v>122</v>
+      </c>
+      <c r="AB132" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>123</v>
+      </c>
+      <c r="C133" t="s">
+        <v>124</v>
+      </c>
+      <c r="D133" t="s">
+        <v>125</v>
+      </c>
+      <c r="E133" t="s">
+        <v>33</v>
+      </c>
+      <c r="F133" t="s">
+        <v>34</v>
+      </c>
+      <c r="G133" t="s">
+        <v>35</v>
+      </c>
+      <c r="H133" t="s">
+        <v>36</v>
+      </c>
+      <c r="J133" t="s">
+        <v>54</v>
+      </c>
+      <c r="K133" t="s">
+        <v>40</v>
+      </c>
+      <c r="L133" t="s">
+        <v>41</v>
+      </c>
+      <c r="M133" t="s">
+        <v>42</v>
+      </c>
+      <c r="N133" t="s">
+        <v>33</v>
+      </c>
+      <c r="O133">
+        <v>1</v>
+      </c>
+      <c r="P133" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q133">
+        <v>59.99</v>
+      </c>
+      <c r="R133">
+        <v>10</v>
+      </c>
+      <c r="Y133" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z133" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA133" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB133" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>129</v>
+      </c>
+      <c r="C134" t="s">
+        <v>130</v>
+      </c>
+      <c r="D134" t="s">
+        <v>131</v>
+      </c>
+      <c r="E134" t="s">
+        <v>33</v>
+      </c>
+      <c r="F134" t="s">
+        <v>34</v>
+      </c>
+      <c r="G134" t="s">
+        <v>35</v>
+      </c>
+      <c r="H134" t="s">
+        <v>36</v>
+      </c>
+      <c r="J134" t="s">
+        <v>54</v>
+      </c>
+      <c r="K134" t="s">
+        <v>43</v>
+      </c>
+      <c r="L134" t="s">
+        <v>44</v>
+      </c>
+      <c r="M134" t="s">
+        <v>45</v>
+      </c>
+      <c r="N134" t="s">
+        <v>33</v>
+      </c>
+      <c r="O134">
+        <v>1</v>
+      </c>
+      <c r="P134" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q134">
+        <v>38.49</v>
+      </c>
+      <c r="R134">
+        <v>6.42</v>
+      </c>
+      <c r="Y134" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA134" t="s">
+        <v>132</v>
+      </c>
+      <c r="AB134" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>105</v>
+      </c>
+      <c r="C135" t="s">
+        <v>106</v>
+      </c>
+      <c r="D135" t="s">
+        <v>136</v>
+      </c>
+      <c r="E135" t="s">
+        <v>53</v>
+      </c>
+      <c r="F135" t="s">
+        <v>34</v>
+      </c>
+      <c r="G135" t="s">
+        <v>35</v>
+      </c>
+      <c r="H135" t="s">
+        <v>36</v>
+      </c>
+      <c r="J135" t="s">
+        <v>54</v>
+      </c>
+      <c r="K135" t="s">
+        <v>94</v>
+      </c>
+      <c r="L135" t="s">
+        <v>82</v>
+      </c>
+      <c r="M135" t="s">
+        <v>83</v>
+      </c>
+      <c r="O135">
+        <v>0</v>
+      </c>
+      <c r="Y135" t="s">
+        <v>103</v>
+      </c>
+      <c r="AA135" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB135" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>107</v>
+      </c>
+      <c r="C136" t="s">
+        <v>108</v>
+      </c>
+      <c r="D136" t="s">
+        <v>137</v>
+      </c>
+      <c r="E136" t="s">
+        <v>33</v>
+      </c>
+      <c r="F136" t="s">
+        <v>34</v>
+      </c>
+      <c r="G136" t="s">
+        <v>35</v>
+      </c>
+      <c r="H136" t="s">
+        <v>36</v>
+      </c>
+      <c r="J136" t="s">
+        <v>54</v>
+      </c>
+      <c r="K136" t="s">
+        <v>48</v>
+      </c>
+      <c r="L136" t="s">
+        <v>49</v>
+      </c>
+      <c r="M136" t="s">
+        <v>50</v>
+      </c>
+      <c r="N136" t="s">
+        <v>33</v>
+      </c>
+      <c r="O136">
+        <v>1</v>
+      </c>
+      <c r="P136" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q136">
+        <v>37.99</v>
+      </c>
+      <c r="R136">
+        <v>6.33</v>
+      </c>
+      <c r="Y136" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z136" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA136" t="s">
+        <v>111</v>
+      </c>
+      <c r="AB136" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>112</v>
+      </c>
+      <c r="C137" t="s">
+        <v>113</v>
+      </c>
+      <c r="D137" t="s">
+        <v>114</v>
+      </c>
+      <c r="E137" t="s">
+        <v>33</v>
+      </c>
+      <c r="F137" t="s">
+        <v>34</v>
+      </c>
+      <c r="G137" t="s">
+        <v>35</v>
+      </c>
+      <c r="H137" t="s">
+        <v>36</v>
+      </c>
+      <c r="J137" t="s">
+        <v>37</v>
+      </c>
+      <c r="K137" t="s">
+        <v>40</v>
+      </c>
+      <c r="L137" t="s">
+        <v>41</v>
+      </c>
+      <c r="M137" t="s">
+        <v>42</v>
+      </c>
+      <c r="N137" t="s">
+        <v>33</v>
+      </c>
+      <c r="O137">
+        <v>1</v>
+      </c>
+      <c r="P137" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q137">
+        <v>59.99</v>
+      </c>
+      <c r="R137">
+        <v>10</v>
+      </c>
+      <c r="Y137" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z137" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA137" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB137" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>703</v>
+      </c>
+      <c r="C138" t="s">
+        <v>704</v>
+      </c>
+      <c r="D138" t="s">
+        <v>705</v>
+      </c>
+      <c r="E138" t="s">
+        <v>33</v>
+      </c>
+      <c r="F138" t="s">
+        <v>34</v>
+      </c>
+      <c r="G138" t="s">
+        <v>35</v>
+      </c>
+      <c r="H138" t="s">
+        <v>36</v>
+      </c>
+      <c r="J138" t="s">
+        <v>54</v>
+      </c>
+      <c r="K138" t="s">
+        <v>72</v>
+      </c>
+      <c r="L138" t="s">
+        <v>73</v>
+      </c>
+      <c r="M138" t="s">
+        <v>74</v>
+      </c>
+      <c r="N138" t="s">
+        <v>33</v>
+      </c>
+      <c r="O138">
+        <v>1</v>
+      </c>
+      <c r="P138" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q138">
+        <v>11.99</v>
+      </c>
+      <c r="R138">
+        <v>2</v>
+      </c>
+      <c r="Y138" t="s">
         <v>706</v>
       </c>
-      <c r="AA131" t="s">
+      <c r="AA138" t="s">
         <v>707</v>
       </c>
-      <c r="AB131" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD131" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG131" t="b">
+      <c r="AB138" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Raw Sales Data/Amazon.xlsx
+++ b/Raw Sales Data/Amazon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2247" uniqueCount="780">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2491" uniqueCount="819">
   <si>
     <t>amazon-order-id</t>
   </si>
@@ -2359,6 +2359,123 @@
   </si>
   <si>
     <t>IP2 9NY</t>
+  </si>
+  <si>
+    <t>203-1652841-0273131</t>
+  </si>
+  <si>
+    <t>2026-03-04T13:59:18+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-04T23:29:22+00:00</t>
+  </si>
+  <si>
+    <t>BRECON</t>
+  </si>
+  <si>
+    <t>LD3 0LE</t>
+  </si>
+  <si>
+    <t>205-6803171-8804356</t>
+  </si>
+  <si>
+    <t>2026-03-04T11:27:43+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-05T00:38:56+00:00</t>
+  </si>
+  <si>
+    <t>CAERPHILLY</t>
+  </si>
+  <si>
+    <t>CF83 1HU</t>
+  </si>
+  <si>
+    <t>203-3013042-8779563</t>
+  </si>
+  <si>
+    <t>2026-03-04T00:13:15+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-04T09:47:39+00:00</t>
+  </si>
+  <si>
+    <t>KING'S LYNN</t>
+  </si>
+  <si>
+    <t>PE30 4QY</t>
+  </si>
+  <si>
+    <t>204-1186340-7565932</t>
+  </si>
+  <si>
+    <t>2026-03-03T23:35:54+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-04T09:46:57+00:00</t>
+  </si>
+  <si>
+    <t>NOTTINGHAM</t>
+  </si>
+  <si>
+    <t>NG6 0LP</t>
+  </si>
+  <si>
+    <t>206-7111291-1973940</t>
+  </si>
+  <si>
+    <t>2026-03-03T20:31:16+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-04T00:57:07+00:00</t>
+  </si>
+  <si>
+    <t>BL2 1NF</t>
+  </si>
+  <si>
+    <t>026-2283171-3449942</t>
+  </si>
+  <si>
+    <t>2026-03-03T11:49:47+00:00</t>
+  </si>
+  <si>
+    <t>BISHOP AUCKLAND</t>
+  </si>
+  <si>
+    <t>DL14 0SH</t>
+  </si>
+  <si>
+    <t>026-5575666-5693941</t>
+  </si>
+  <si>
+    <t>2026-03-03T11:35:47+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-04T01:04:51+00:00</t>
+  </si>
+  <si>
+    <t>RG5 4DG</t>
+  </si>
+  <si>
+    <t>026-3357149-3321143</t>
+  </si>
+  <si>
+    <t>2026-03-03T09:03:35+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-03T23:00:14+00:00</t>
+  </si>
+  <si>
+    <t>DUNMOW</t>
+  </si>
+  <si>
+    <t>CM6 2HW</t>
+  </si>
+  <si>
+    <t>2026-03-03T09:25:29+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-03T11:24:47+00:00</t>
   </si>
 </sst>
 </file>
@@ -3165,7 +3282,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG138"/>
+  <dimension ref="A1:AG153"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
@@ -3276,16 +3393,16 @@
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>745</v>
+        <v>780</v>
       </c>
       <c r="C2" t="s">
-        <v>746</v>
+        <v>781</v>
       </c>
       <c r="D2" t="s">
-        <v>747</v>
+        <v>782</v>
       </c>
       <c r="E2" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F2" t="s">
         <v>34</v>
@@ -3300,16 +3417,16 @@
         <v>54</v>
       </c>
       <c r="K2" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L2" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M2" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N2" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O2">
         <v>1</v>
@@ -3318,16 +3435,16 @@
         <v>38</v>
       </c>
       <c r="Q2">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y2" t="s">
-        <v>748</v>
+        <v>783</v>
       </c>
       <c r="AA2" t="s">
-        <v>749</v>
+        <v>784</v>
       </c>
       <c r="AB2" t="s">
         <v>39</v>
@@ -3341,13 +3458,13 @@
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>750</v>
+        <v>785</v>
       </c>
       <c r="C3" t="s">
-        <v>751</v>
+        <v>786</v>
       </c>
       <c r="D3" t="s">
-        <v>752</v>
+        <v>787</v>
       </c>
       <c r="E3" t="s">
         <v>33</v>
@@ -3365,13 +3482,13 @@
         <v>54</v>
       </c>
       <c r="K3" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L3" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M3" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N3" t="s">
         <v>33</v>
@@ -3383,16 +3500,16 @@
         <v>38</v>
       </c>
       <c r="Q3">
-        <v>65.989999999999995</v>
+        <v>40.99</v>
       </c>
       <c r="R3">
-        <v>11</v>
+        <v>6.83</v>
       </c>
       <c r="Y3" t="s">
-        <v>753</v>
+        <v>788</v>
       </c>
       <c r="AA3" t="s">
-        <v>754</v>
+        <v>789</v>
       </c>
       <c r="AB3" t="s">
         <v>39</v>
@@ -3406,16 +3523,16 @@
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>755</v>
+        <v>790</v>
       </c>
       <c r="C4" t="s">
-        <v>756</v>
+        <v>791</v>
       </c>
       <c r="D4" t="s">
-        <v>757</v>
+        <v>792</v>
       </c>
       <c r="E4" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F4" t="s">
         <v>34</v>
@@ -3439,7 +3556,7 @@
         <v>42</v>
       </c>
       <c r="N4" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O4">
         <v>1</v>
@@ -3453,20 +3570,11 @@
       <c r="R4">
         <v>11</v>
       </c>
-      <c r="S4">
-        <v>6.99</v>
-      </c>
-      <c r="T4">
-        <v>1.17</v>
-      </c>
       <c r="Y4" t="s">
-        <v>758</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>759</v>
+        <v>793</v>
       </c>
       <c r="AA4" t="s">
-        <v>760</v>
+        <v>794</v>
       </c>
       <c r="AB4" t="s">
         <v>39</v>
@@ -3480,13 +3588,13 @@
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>761</v>
+        <v>795</v>
       </c>
       <c r="C5" t="s">
-        <v>762</v>
+        <v>796</v>
       </c>
       <c r="D5" t="s">
-        <v>763</v>
+        <v>797</v>
       </c>
       <c r="E5" t="s">
         <v>33</v>
@@ -3522,19 +3630,16 @@
         <v>38</v>
       </c>
       <c r="Q5">
-        <v>11.99</v>
+        <v>14.99</v>
       </c>
       <c r="R5">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Y5" t="s">
-        <v>764</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>279</v>
+        <v>798</v>
       </c>
       <c r="AA5" t="s">
-        <v>765</v>
+        <v>799</v>
       </c>
       <c r="AB5" t="s">
         <v>39</v>
@@ -3548,13 +3653,13 @@
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>766</v>
+        <v>800</v>
       </c>
       <c r="C6" t="s">
-        <v>767</v>
+        <v>801</v>
       </c>
       <c r="D6" t="s">
-        <v>768</v>
+        <v>802</v>
       </c>
       <c r="E6" t="s">
         <v>33</v>
@@ -3590,19 +3695,16 @@
         <v>38</v>
       </c>
       <c r="Q6">
-        <v>11.99</v>
+        <v>14.99</v>
       </c>
       <c r="R6">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Y6" t="s">
-        <v>91</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="AA6" t="s">
-        <v>769</v>
+        <v>803</v>
       </c>
       <c r="AB6" t="s">
         <v>39</v>
@@ -3616,13 +3718,13 @@
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>770</v>
+        <v>804</v>
       </c>
       <c r="C7" t="s">
-        <v>771</v>
+        <v>805</v>
       </c>
       <c r="D7" t="s">
-        <v>772</v>
+        <v>802</v>
       </c>
       <c r="E7" t="s">
         <v>33</v>
@@ -3640,13 +3742,13 @@
         <v>54</v>
       </c>
       <c r="K7" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L7" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M7" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N7" t="s">
         <v>33</v>
@@ -3658,19 +3760,16 @@
         <v>38</v>
       </c>
       <c r="Q7">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R7">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="s">
-        <v>773</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>64</v>
+        <v>806</v>
       </c>
       <c r="AA7" t="s">
-        <v>774</v>
+        <v>807</v>
       </c>
       <c r="AB7" t="s">
         <v>39</v>
@@ -3684,13 +3783,13 @@
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>775</v>
+        <v>808</v>
       </c>
       <c r="C8" t="s">
-        <v>776</v>
+        <v>809</v>
       </c>
       <c r="D8" t="s">
-        <v>777</v>
+        <v>810</v>
       </c>
       <c r="E8" t="s">
         <v>33</v>
@@ -3708,13 +3807,13 @@
         <v>54</v>
       </c>
       <c r="K8" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L8" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M8" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N8" t="s">
         <v>33</v>
@@ -3726,16 +3825,16 @@
         <v>38</v>
       </c>
       <c r="Q8">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R8">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="s">
-        <v>778</v>
+        <v>66</v>
       </c>
       <c r="AA8" t="s">
-        <v>779</v>
+        <v>811</v>
       </c>
       <c r="AB8" t="s">
         <v>39</v>
@@ -3749,16 +3848,16 @@
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>714</v>
+        <v>812</v>
       </c>
       <c r="C9" t="s">
-        <v>715</v>
+        <v>813</v>
       </c>
       <c r="D9" t="s">
-        <v>716</v>
+        <v>814</v>
       </c>
       <c r="E9" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s">
         <v>34</v>
@@ -3773,16 +3872,16 @@
         <v>54</v>
       </c>
       <c r="K9" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="L9" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="M9" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="N9" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O9">
         <v>1</v>
@@ -3791,19 +3890,16 @@
         <v>38</v>
       </c>
       <c r="Q9">
-        <v>11.99</v>
+        <v>40.99</v>
       </c>
       <c r="R9">
-        <v>2</v>
+        <v>6.83</v>
       </c>
       <c r="Y9" t="s">
-        <v>717</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>51</v>
+        <v>815</v>
       </c>
       <c r="AA9" t="s">
-        <v>718</v>
+        <v>816</v>
       </c>
       <c r="AB9" t="s">
         <v>39</v>
@@ -3817,13 +3913,13 @@
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>719</v>
+        <v>745</v>
       </c>
       <c r="C10" t="s">
-        <v>720</v>
+        <v>746</v>
       </c>
       <c r="D10" t="s">
-        <v>721</v>
+        <v>817</v>
       </c>
       <c r="E10" t="s">
         <v>33</v>
@@ -3841,13 +3937,13 @@
         <v>54</v>
       </c>
       <c r="K10" t="s">
-        <v>722</v>
+        <v>72</v>
       </c>
       <c r="L10" t="s">
-        <v>723</v>
+        <v>73</v>
       </c>
       <c r="M10" t="s">
-        <v>724</v>
+        <v>74</v>
       </c>
       <c r="N10" t="s">
         <v>33</v>
@@ -3859,19 +3955,16 @@
         <v>38</v>
       </c>
       <c r="Q10">
-        <v>12.99</v>
+        <v>11.99</v>
       </c>
       <c r="R10">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="s">
-        <v>725</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>726</v>
+        <v>748</v>
       </c>
       <c r="AA10" t="s">
-        <v>727</v>
+        <v>749</v>
       </c>
       <c r="AB10" t="s">
         <v>39</v>
@@ -3885,13 +3978,13 @@
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>728</v>
+        <v>750</v>
       </c>
       <c r="C11" t="s">
-        <v>729</v>
+        <v>751</v>
       </c>
       <c r="D11" t="s">
-        <v>730</v>
+        <v>752</v>
       </c>
       <c r="E11" t="s">
         <v>33</v>
@@ -3909,13 +4002,13 @@
         <v>54</v>
       </c>
       <c r="K11" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L11" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M11" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N11" t="s">
         <v>33</v>
@@ -3927,16 +4020,16 @@
         <v>38</v>
       </c>
       <c r="Q11">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R11">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y11" t="s">
-        <v>731</v>
+        <v>753</v>
       </c>
       <c r="AA11" t="s">
-        <v>732</v>
+        <v>754</v>
       </c>
       <c r="AB11" t="s">
         <v>39</v>
@@ -3950,13 +4043,13 @@
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>733</v>
+        <v>755</v>
       </c>
       <c r="C12" t="s">
-        <v>734</v>
+        <v>756</v>
       </c>
       <c r="D12" t="s">
-        <v>735</v>
+        <v>818</v>
       </c>
       <c r="E12" t="s">
         <v>33</v>
@@ -3974,13 +4067,13 @@
         <v>54</v>
       </c>
       <c r="K12" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L12" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N12" t="s">
         <v>33</v>
@@ -3992,16 +4085,25 @@
         <v>38</v>
       </c>
       <c r="Q12">
-        <v>40.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R12">
-        <v>6.83</v>
+        <v>11</v>
+      </c>
+      <c r="S12">
+        <v>6.99</v>
+      </c>
+      <c r="T12">
+        <v>1.17</v>
       </c>
       <c r="Y12" t="s">
-        <v>736</v>
+        <v>758</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>759</v>
       </c>
       <c r="AA12" t="s">
-        <v>737</v>
+        <v>760</v>
       </c>
       <c r="AB12" t="s">
         <v>39</v>
@@ -4015,13 +4117,13 @@
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>738</v>
+        <v>761</v>
       </c>
       <c r="C13" t="s">
-        <v>739</v>
+        <v>762</v>
       </c>
       <c r="D13" t="s">
-        <v>740</v>
+        <v>763</v>
       </c>
       <c r="E13" t="s">
         <v>33</v>
@@ -4039,13 +4141,13 @@
         <v>54</v>
       </c>
       <c r="K13" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L13" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M13" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="N13" t="s">
         <v>33</v>
@@ -4057,16 +4159,19 @@
         <v>38</v>
       </c>
       <c r="Q13">
-        <v>40.99</v>
+        <v>11.99</v>
       </c>
       <c r="R13">
-        <v>6.83</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="s">
-        <v>741</v>
+        <v>764</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>279</v>
       </c>
       <c r="AA13" t="s">
-        <v>742</v>
+        <v>765</v>
       </c>
       <c r="AB13" t="s">
         <v>39</v>
@@ -4080,13 +4185,13 @@
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>708</v>
+        <v>766</v>
       </c>
       <c r="C14" t="s">
-        <v>709</v>
+        <v>767</v>
       </c>
       <c r="D14" t="s">
-        <v>743</v>
+        <v>768</v>
       </c>
       <c r="E14" t="s">
         <v>33</v>
@@ -4104,13 +4209,13 @@
         <v>54</v>
       </c>
       <c r="K14" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L14" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M14" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N14" t="s">
         <v>33</v>
@@ -4122,19 +4227,19 @@
         <v>38</v>
       </c>
       <c r="Q14">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R14">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="s">
-        <v>711</v>
+        <v>91</v>
       </c>
       <c r="Z14" t="s">
-        <v>712</v>
+        <v>121</v>
       </c>
       <c r="AA14" t="s">
-        <v>713</v>
+        <v>769</v>
       </c>
       <c r="AB14" t="s">
         <v>39</v>
@@ -4148,13 +4253,13 @@
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>643</v>
+        <v>770</v>
       </c>
       <c r="C15" t="s">
-        <v>644</v>
+        <v>771</v>
       </c>
       <c r="D15" t="s">
-        <v>744</v>
+        <v>772</v>
       </c>
       <c r="E15" t="s">
         <v>33</v>
@@ -4172,13 +4277,13 @@
         <v>54</v>
       </c>
       <c r="K15" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L15" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M15" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="N15" t="s">
         <v>33</v>
@@ -4190,16 +4295,19 @@
         <v>38</v>
       </c>
       <c r="Q15">
-        <v>14.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R15">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="Y15" t="s">
-        <v>646</v>
+        <v>773</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>64</v>
       </c>
       <c r="AA15" t="s">
-        <v>647</v>
+        <v>774</v>
       </c>
       <c r="AB15" t="s">
         <v>39</v>
@@ -4213,16 +4321,16 @@
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>708</v>
+        <v>775</v>
       </c>
       <c r="C16" t="s">
-        <v>709</v>
+        <v>776</v>
       </c>
       <c r="D16" t="s">
-        <v>710</v>
+        <v>777</v>
       </c>
       <c r="E16" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F16" t="s">
         <v>34</v>
@@ -4246,7 +4354,7 @@
         <v>42</v>
       </c>
       <c r="N16" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O16">
         <v>1</v>
@@ -4261,13 +4369,10 @@
         <v>11</v>
       </c>
       <c r="Y16" t="s">
-        <v>711</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>712</v>
+        <v>778</v>
       </c>
       <c r="AA16" t="s">
-        <v>713</v>
+        <v>779</v>
       </c>
       <c r="AB16" t="s">
         <v>39</v>
@@ -4281,22 +4386,22 @@
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>138</v>
+        <v>745</v>
       </c>
       <c r="C17" t="s">
-        <v>139</v>
+        <v>746</v>
       </c>
       <c r="D17" t="s">
-        <v>187</v>
+        <v>747</v>
       </c>
       <c r="E17" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="F17" t="s">
         <v>34</v>
       </c>
       <c r="G17" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="H17" t="s">
         <v>36</v>
@@ -4305,25 +4410,37 @@
         <v>54</v>
       </c>
       <c r="K17" t="s">
-        <v>141</v>
+        <v>72</v>
       </c>
       <c r="L17" t="s">
-        <v>142</v>
+        <v>73</v>
       </c>
       <c r="M17" t="s">
-        <v>143</v>
+        <v>74</v>
+      </c>
+      <c r="N17" t="s">
+        <v>99</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P17" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q17">
+        <v>11.99</v>
+      </c>
+      <c r="R17">
+        <v>2</v>
       </c>
       <c r="Y17" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA17">
-        <v>80100</v>
+        <v>748</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>749</v>
       </c>
       <c r="AB17" t="s">
-        <v>145</v>
+        <v>39</v>
       </c>
       <c r="AD17" t="b">
         <v>0</v>
@@ -4334,22 +4451,22 @@
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>146</v>
+        <v>750</v>
       </c>
       <c r="C18" t="s">
-        <v>147</v>
+        <v>751</v>
       </c>
       <c r="D18" t="s">
-        <v>148</v>
+        <v>752</v>
       </c>
       <c r="E18" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F18" t="s">
         <v>34</v>
       </c>
       <c r="G18" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="H18" t="s">
         <v>36</v>
@@ -4358,25 +4475,37 @@
         <v>54</v>
       </c>
       <c r="K18" t="s">
-        <v>141</v>
+        <v>40</v>
       </c>
       <c r="L18" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="M18" t="s">
-        <v>143</v>
+        <v>42</v>
+      </c>
+      <c r="N18" t="s">
+        <v>33</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P18" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q18">
+        <v>65.989999999999995</v>
+      </c>
+      <c r="R18">
+        <v>11</v>
       </c>
       <c r="Y18" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA18">
-        <v>80100</v>
+        <v>753</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>754</v>
       </c>
       <c r="AB18" t="s">
-        <v>145</v>
+        <v>39</v>
       </c>
       <c r="AD18" t="b">
         <v>0</v>
@@ -4387,22 +4516,22 @@
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>632</v>
+        <v>755</v>
       </c>
       <c r="C19" t="s">
-        <v>633</v>
+        <v>756</v>
       </c>
       <c r="D19" t="s">
-        <v>634</v>
+        <v>757</v>
       </c>
       <c r="E19" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="F19" t="s">
         <v>34</v>
       </c>
       <c r="G19" t="s">
-        <v>635</v>
+        <v>35</v>
       </c>
       <c r="H19" t="s">
         <v>36</v>
@@ -4411,37 +4540,46 @@
         <v>54</v>
       </c>
       <c r="K19" t="s">
-        <v>636</v>
+        <v>40</v>
       </c>
       <c r="L19" t="s">
-        <v>637</v>
+        <v>41</v>
       </c>
       <c r="M19" t="s">
-        <v>638</v>
+        <v>42</v>
+      </c>
+      <c r="N19" t="s">
+        <v>99</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="Q19">
-        <v>22.9</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R19">
-        <v>4.8099999999999996</v>
+        <v>11</v>
+      </c>
+      <c r="S19">
+        <v>6.99</v>
+      </c>
+      <c r="T19">
+        <v>1.17</v>
       </c>
       <c r="Y19" t="s">
-        <v>639</v>
+        <v>758</v>
       </c>
       <c r="Z19" t="s">
-        <v>640</v>
+        <v>759</v>
       </c>
       <c r="AA19" t="s">
-        <v>641</v>
+        <v>760</v>
       </c>
       <c r="AB19" t="s">
-        <v>642</v>
+        <v>39</v>
       </c>
       <c r="AD19" t="b">
         <v>0</v>
@@ -4452,16 +4590,16 @@
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>643</v>
+        <v>761</v>
       </c>
       <c r="C20" t="s">
-        <v>644</v>
+        <v>762</v>
       </c>
       <c r="D20" t="s">
-        <v>645</v>
+        <v>763</v>
       </c>
       <c r="E20" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F20" t="s">
         <v>34</v>
@@ -4476,16 +4614,16 @@
         <v>54</v>
       </c>
       <c r="K20" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L20" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M20" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="N20" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O20">
         <v>1</v>
@@ -4494,16 +4632,19 @@
         <v>38</v>
       </c>
       <c r="Q20">
-        <v>14.99</v>
+        <v>11.99</v>
       </c>
       <c r="R20">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="s">
-        <v>646</v>
+        <v>764</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>279</v>
       </c>
       <c r="AA20" t="s">
-        <v>647</v>
+        <v>765</v>
       </c>
       <c r="AB20" t="s">
         <v>39</v>
@@ -4517,13 +4658,13 @@
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>609</v>
+        <v>766</v>
       </c>
       <c r="C21" t="s">
-        <v>610</v>
+        <v>767</v>
       </c>
       <c r="D21" t="s">
-        <v>611</v>
+        <v>768</v>
       </c>
       <c r="E21" t="s">
         <v>33</v>
@@ -4541,13 +4682,13 @@
         <v>54</v>
       </c>
       <c r="K21" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L21" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M21" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="N21" t="s">
         <v>33</v>
@@ -4559,19 +4700,19 @@
         <v>38</v>
       </c>
       <c r="Q21">
-        <v>14.99</v>
+        <v>11.99</v>
       </c>
       <c r="R21">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="s">
-        <v>612</v>
+        <v>91</v>
       </c>
       <c r="Z21" t="s">
-        <v>613</v>
+        <v>121</v>
       </c>
       <c r="AA21" t="s">
-        <v>614</v>
+        <v>769</v>
       </c>
       <c r="AB21" t="s">
         <v>39</v>
@@ -4585,16 +4726,16 @@
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>493</v>
+        <v>770</v>
       </c>
       <c r="C22" t="s">
-        <v>494</v>
+        <v>771</v>
       </c>
       <c r="D22" t="s">
-        <v>648</v>
+        <v>772</v>
       </c>
       <c r="E22" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F22" t="s">
         <v>34</v>
@@ -4617,14 +4758,29 @@
       <c r="M22" t="s">
         <v>42</v>
       </c>
+      <c r="N22" t="s">
+        <v>33</v>
+      </c>
       <c r="O22">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P22" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q22">
+        <v>65.989999999999995</v>
+      </c>
+      <c r="R22">
+        <v>11</v>
       </c>
       <c r="Y22" t="s">
-        <v>495</v>
+        <v>773</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>64</v>
       </c>
       <c r="AA22" t="s">
-        <v>496</v>
+        <v>774</v>
       </c>
       <c r="AB22" t="s">
         <v>39</v>
@@ -4638,16 +4794,16 @@
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>615</v>
+        <v>775</v>
       </c>
       <c r="C23" t="s">
-        <v>616</v>
+        <v>776</v>
       </c>
       <c r="D23" t="s">
-        <v>617</v>
+        <v>777</v>
       </c>
       <c r="E23" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F23" t="s">
         <v>34</v>
@@ -4662,16 +4818,16 @@
         <v>54</v>
       </c>
       <c r="K23" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L23" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N23" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O23">
         <v>1</v>
@@ -4680,16 +4836,16 @@
         <v>38</v>
       </c>
       <c r="Q23">
-        <v>40.99</v>
+        <v>65.989999999999995</v>
+      </c>
+      <c r="R23">
+        <v>11</v>
       </c>
       <c r="Y23" t="s">
-        <v>618</v>
-      </c>
-      <c r="Z23" t="s">
-        <v>619</v>
+        <v>778</v>
       </c>
       <c r="AA23" t="s">
-        <v>620</v>
+        <v>779</v>
       </c>
       <c r="AB23" t="s">
         <v>39</v>
@@ -4703,16 +4859,16 @@
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>621</v>
+        <v>714</v>
       </c>
       <c r="C24" t="s">
-        <v>622</v>
+        <v>715</v>
       </c>
       <c r="D24" t="s">
-        <v>623</v>
+        <v>716</v>
       </c>
       <c r="E24" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F24" t="s">
         <v>34</v>
@@ -4727,16 +4883,16 @@
         <v>54</v>
       </c>
       <c r="K24" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L24" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M24" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N24" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O24">
         <v>1</v>
@@ -4745,25 +4901,19 @@
         <v>38</v>
       </c>
       <c r="Q24">
-        <v>64.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R24">
-        <v>10.83</v>
-      </c>
-      <c r="S24">
-        <v>6.99</v>
-      </c>
-      <c r="T24">
-        <v>1.17</v>
+        <v>2</v>
       </c>
       <c r="Y24" t="s">
-        <v>624</v>
+        <v>717</v>
       </c>
       <c r="Z24" t="s">
-        <v>625</v>
+        <v>51</v>
       </c>
       <c r="AA24" t="s">
-        <v>626</v>
+        <v>718</v>
       </c>
       <c r="AB24" t="s">
         <v>39</v>
@@ -4777,13 +4927,13 @@
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>627</v>
+        <v>719</v>
       </c>
       <c r="C25" t="s">
-        <v>628</v>
+        <v>720</v>
       </c>
       <c r="D25" t="s">
-        <v>629</v>
+        <v>721</v>
       </c>
       <c r="E25" t="s">
         <v>33</v>
@@ -4801,13 +4951,13 @@
         <v>54</v>
       </c>
       <c r="K25" t="s">
-        <v>72</v>
+        <v>722</v>
       </c>
       <c r="L25" t="s">
-        <v>73</v>
+        <v>723</v>
       </c>
       <c r="M25" t="s">
-        <v>74</v>
+        <v>724</v>
       </c>
       <c r="N25" t="s">
         <v>33</v>
@@ -4819,16 +4969,19 @@
         <v>38</v>
       </c>
       <c r="Q25">
-        <v>11.99</v>
+        <v>12.99</v>
       </c>
       <c r="R25">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="Y25" t="s">
-        <v>630</v>
+        <v>725</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>726</v>
       </c>
       <c r="AA25" t="s">
-        <v>631</v>
+        <v>727</v>
       </c>
       <c r="AB25" t="s">
         <v>39</v>
@@ -4842,13 +4995,13 @@
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>649</v>
+        <v>728</v>
       </c>
       <c r="C26" t="s">
-        <v>650</v>
+        <v>729</v>
       </c>
       <c r="D26" t="s">
-        <v>651</v>
+        <v>730</v>
       </c>
       <c r="E26" t="s">
         <v>33</v>
@@ -4866,13 +5019,13 @@
         <v>54</v>
       </c>
       <c r="K26" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L26" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M26" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="N26" t="s">
         <v>33</v>
@@ -4884,19 +5037,16 @@
         <v>38</v>
       </c>
       <c r="Q26">
-        <v>39.99</v>
+        <v>11.99</v>
       </c>
       <c r="R26">
-        <v>6.67</v>
+        <v>2</v>
       </c>
       <c r="Y26" t="s">
-        <v>652</v>
-      </c>
-      <c r="Z26" t="s">
-        <v>653</v>
+        <v>731</v>
       </c>
       <c r="AA26" t="s">
-        <v>654</v>
+        <v>732</v>
       </c>
       <c r="AB26" t="s">
         <v>39</v>
@@ -4910,13 +5060,13 @@
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>655</v>
+        <v>733</v>
       </c>
       <c r="C27" t="s">
-        <v>656</v>
+        <v>734</v>
       </c>
       <c r="D27" t="s">
-        <v>657</v>
+        <v>735</v>
       </c>
       <c r="E27" t="s">
         <v>33</v>
@@ -4934,13 +5084,13 @@
         <v>54</v>
       </c>
       <c r="K27" t="s">
-        <v>94</v>
+        <v>43</v>
       </c>
       <c r="L27" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="M27" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="N27" t="s">
         <v>33</v>
@@ -4952,16 +5102,16 @@
         <v>38</v>
       </c>
       <c r="Q27">
-        <v>14.99</v>
+        <v>40.99</v>
       </c>
       <c r="R27">
-        <v>2.5</v>
+        <v>6.83</v>
       </c>
       <c r="Y27" t="s">
-        <v>658</v>
+        <v>736</v>
       </c>
       <c r="AA27" t="s">
-        <v>659</v>
+        <v>737</v>
       </c>
       <c r="AB27" t="s">
         <v>39</v>
@@ -4975,13 +5125,13 @@
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>571</v>
+        <v>738</v>
       </c>
       <c r="C28" t="s">
-        <v>572</v>
+        <v>739</v>
       </c>
       <c r="D28" t="s">
-        <v>660</v>
+        <v>740</v>
       </c>
       <c r="E28" t="s">
         <v>33</v>
@@ -4999,13 +5149,13 @@
         <v>54</v>
       </c>
       <c r="K28" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L28" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M28" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N28" t="s">
         <v>33</v>
@@ -5017,16 +5167,16 @@
         <v>38</v>
       </c>
       <c r="Q28">
-        <v>64.989999999999995</v>
+        <v>40.99</v>
       </c>
       <c r="R28">
-        <v>10.83</v>
+        <v>6.83</v>
       </c>
       <c r="Y28" t="s">
-        <v>573</v>
+        <v>741</v>
       </c>
       <c r="AA28" t="s">
-        <v>574</v>
+        <v>742</v>
       </c>
       <c r="AB28" t="s">
         <v>39</v>
@@ -5040,13 +5190,13 @@
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>599</v>
+        <v>708</v>
       </c>
       <c r="C29" t="s">
-        <v>600</v>
+        <v>709</v>
       </c>
       <c r="D29" t="s">
-        <v>601</v>
+        <v>743</v>
       </c>
       <c r="E29" t="s">
         <v>33</v>
@@ -5064,13 +5214,13 @@
         <v>54</v>
       </c>
       <c r="K29" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L29" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M29" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="N29" t="s">
         <v>33</v>
@@ -5082,16 +5232,19 @@
         <v>38</v>
       </c>
       <c r="Q29">
-        <v>14.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R29">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="Y29" t="s">
-        <v>61</v>
+        <v>711</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>712</v>
       </c>
       <c r="AA29" t="s">
-        <v>602</v>
+        <v>713</v>
       </c>
       <c r="AB29" t="s">
         <v>39</v>
@@ -5105,13 +5258,13 @@
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>589</v>
+        <v>643</v>
       </c>
       <c r="C30" t="s">
-        <v>590</v>
+        <v>644</v>
       </c>
       <c r="D30" t="s">
-        <v>591</v>
+        <v>744</v>
       </c>
       <c r="E30" t="s">
         <v>33</v>
@@ -5129,13 +5282,13 @@
         <v>54</v>
       </c>
       <c r="K30" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L30" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M30" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="N30" t="s">
         <v>33</v>
@@ -5147,16 +5300,16 @@
         <v>38</v>
       </c>
       <c r="Q30">
-        <v>64.989999999999995</v>
+        <v>14.99</v>
       </c>
       <c r="R30">
-        <v>10.83</v>
+        <v>2.5</v>
       </c>
       <c r="Y30" t="s">
-        <v>592</v>
+        <v>646</v>
       </c>
       <c r="AA30" t="s">
-        <v>593</v>
+        <v>647</v>
       </c>
       <c r="AB30" t="s">
         <v>39</v>
@@ -5170,16 +5323,16 @@
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>594</v>
+        <v>708</v>
       </c>
       <c r="C31" t="s">
-        <v>595</v>
+        <v>709</v>
       </c>
       <c r="D31" t="s">
-        <v>596</v>
+        <v>710</v>
       </c>
       <c r="E31" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F31" t="s">
         <v>34</v>
@@ -5203,7 +5356,7 @@
         <v>42</v>
       </c>
       <c r="N31" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O31">
         <v>1</v>
@@ -5212,16 +5365,19 @@
         <v>38</v>
       </c>
       <c r="Q31">
-        <v>64.989999999999995</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R31">
-        <v>10.83</v>
+        <v>11</v>
       </c>
       <c r="Y31" t="s">
-        <v>597</v>
+        <v>711</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>712</v>
       </c>
       <c r="AA31" t="s">
-        <v>598</v>
+        <v>713</v>
       </c>
       <c r="AB31" t="s">
         <v>39</v>
@@ -5235,22 +5391,22 @@
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>603</v>
+        <v>138</v>
       </c>
       <c r="C32" t="s">
-        <v>604</v>
+        <v>139</v>
       </c>
       <c r="D32" t="s">
-        <v>605</v>
+        <v>187</v>
       </c>
       <c r="E32" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F32" t="s">
         <v>34</v>
       </c>
       <c r="G32" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="H32" t="s">
         <v>36</v>
@@ -5259,40 +5415,25 @@
         <v>54</v>
       </c>
       <c r="K32" t="s">
-        <v>40</v>
+        <v>141</v>
       </c>
       <c r="L32" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="M32" t="s">
-        <v>42</v>
-      </c>
-      <c r="N32" t="s">
-        <v>33</v>
+        <v>143</v>
       </c>
       <c r="O32">
-        <v>1</v>
-      </c>
-      <c r="P32" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q32">
-        <v>64.989999999999995</v>
-      </c>
-      <c r="R32">
-        <v>10.83</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="s">
-        <v>606</v>
-      </c>
-      <c r="Z32" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA32" t="s">
-        <v>608</v>
+        <v>144</v>
+      </c>
+      <c r="AA32">
+        <v>80100</v>
       </c>
       <c r="AB32" t="s">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="AD32" t="b">
         <v>0</v>
@@ -5303,22 +5444,22 @@
     </row>
     <row r="33" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>578</v>
+        <v>146</v>
       </c>
       <c r="C33" t="s">
-        <v>579</v>
+        <v>147</v>
       </c>
       <c r="D33" t="s">
-        <v>661</v>
+        <v>148</v>
       </c>
       <c r="E33" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F33" t="s">
         <v>34</v>
       </c>
       <c r="G33" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="H33" t="s">
         <v>36</v>
@@ -5327,40 +5468,25 @@
         <v>54</v>
       </c>
       <c r="K33" t="s">
-        <v>40</v>
+        <v>141</v>
       </c>
       <c r="L33" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="M33" t="s">
-        <v>42</v>
-      </c>
-      <c r="N33" t="s">
-        <v>33</v>
+        <v>143</v>
       </c>
       <c r="O33">
-        <v>1</v>
-      </c>
-      <c r="P33" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q33">
-        <v>64.989999999999995</v>
-      </c>
-      <c r="R33">
-        <v>10.83</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="s">
-        <v>580</v>
-      </c>
-      <c r="Z33" t="s">
-        <v>581</v>
-      </c>
-      <c r="AA33" t="s">
-        <v>582</v>
+        <v>144</v>
+      </c>
+      <c r="AA33">
+        <v>80100</v>
       </c>
       <c r="AB33" t="s">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="AD33" t="b">
         <v>0</v>
@@ -5371,13 +5497,13 @@
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>575</v>
+        <v>632</v>
       </c>
       <c r="C34" t="s">
-        <v>576</v>
+        <v>633</v>
       </c>
       <c r="D34" t="s">
-        <v>577</v>
+        <v>634</v>
       </c>
       <c r="E34" t="s">
         <v>53</v>
@@ -5386,7 +5512,7 @@
         <v>34</v>
       </c>
       <c r="G34" t="s">
-        <v>35</v>
+        <v>635</v>
       </c>
       <c r="H34" t="s">
         <v>36</v>
@@ -5395,25 +5521,37 @@
         <v>54</v>
       </c>
       <c r="K34" t="s">
-        <v>40</v>
+        <v>636</v>
       </c>
       <c r="L34" t="s">
-        <v>41</v>
+        <v>637</v>
       </c>
       <c r="M34" t="s">
-        <v>42</v>
+        <v>638</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
+      <c r="P34" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q34">
+        <v>22.9</v>
+      </c>
+      <c r="R34">
+        <v>4.8099999999999996</v>
+      </c>
       <c r="Y34" t="s">
-        <v>573</v>
+        <v>639</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>640</v>
       </c>
       <c r="AA34" t="s">
-        <v>574</v>
+        <v>641</v>
       </c>
       <c r="AB34" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="AD34" t="b">
         <v>0</v>
@@ -5424,16 +5562,16 @@
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>518</v>
+        <v>643</v>
       </c>
       <c r="C35" t="s">
-        <v>519</v>
+        <v>644</v>
       </c>
       <c r="D35" t="s">
-        <v>583</v>
+        <v>645</v>
       </c>
       <c r="E35" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F35" t="s">
         <v>34</v>
@@ -5448,16 +5586,16 @@
         <v>54</v>
       </c>
       <c r="K35" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="L35" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="M35" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="N35" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O35">
         <v>1</v>
@@ -5466,22 +5604,16 @@
         <v>38</v>
       </c>
       <c r="Q35">
-        <v>37.99</v>
+        <v>14.99</v>
       </c>
       <c r="R35">
-        <v>6.33</v>
-      </c>
-      <c r="S35">
-        <v>6.99</v>
-      </c>
-      <c r="T35">
-        <v>1.17</v>
+        <v>2.5</v>
       </c>
       <c r="Y35" t="s">
-        <v>46</v>
+        <v>646</v>
       </c>
       <c r="AA35" t="s">
-        <v>520</v>
+        <v>647</v>
       </c>
       <c r="AB35" t="s">
         <v>39</v>
@@ -5495,13 +5627,13 @@
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>584</v>
+        <v>609</v>
       </c>
       <c r="C36" t="s">
-        <v>585</v>
+        <v>610</v>
       </c>
       <c r="D36" t="s">
-        <v>586</v>
+        <v>611</v>
       </c>
       <c r="E36" t="s">
         <v>33</v>
@@ -5519,13 +5651,13 @@
         <v>54</v>
       </c>
       <c r="K36" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L36" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M36" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="N36" t="s">
         <v>33</v>
@@ -5537,16 +5669,19 @@
         <v>38</v>
       </c>
       <c r="Q36">
-        <v>64.989999999999995</v>
+        <v>14.99</v>
       </c>
       <c r="R36">
-        <v>10.83</v>
+        <v>2.5</v>
       </c>
       <c r="Y36" t="s">
-        <v>587</v>
+        <v>612</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>613</v>
       </c>
       <c r="AA36" t="s">
-        <v>588</v>
+        <v>614</v>
       </c>
       <c r="AB36" t="s">
         <v>39</v>
@@ -5560,16 +5695,16 @@
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>457</v>
+        <v>493</v>
       </c>
       <c r="C37" t="s">
-        <v>458</v>
+        <v>494</v>
       </c>
       <c r="D37" t="s">
-        <v>459</v>
+        <v>648</v>
       </c>
       <c r="E37" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F37" t="s">
         <v>34</v>
@@ -5592,29 +5727,14 @@
       <c r="M37" t="s">
         <v>42</v>
       </c>
-      <c r="N37" t="s">
-        <v>33</v>
-      </c>
       <c r="O37">
-        <v>1</v>
-      </c>
-      <c r="P37" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q37">
-        <v>64.989999999999995</v>
-      </c>
-      <c r="R37">
-        <v>10.83</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="s">
-        <v>460</v>
-      </c>
-      <c r="Z37" t="s">
-        <v>279</v>
+        <v>495</v>
       </c>
       <c r="AA37" t="s">
-        <v>461</v>
+        <v>496</v>
       </c>
       <c r="AB37" t="s">
         <v>39</v>
@@ -5628,16 +5748,16 @@
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>462</v>
+        <v>615</v>
       </c>
       <c r="C38" t="s">
-        <v>463</v>
+        <v>616</v>
       </c>
       <c r="D38" t="s">
-        <v>459</v>
+        <v>617</v>
       </c>
       <c r="E38" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F38" t="s">
         <v>34</v>
@@ -5652,16 +5772,16 @@
         <v>54</v>
       </c>
       <c r="K38" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L38" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M38" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N38" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O38">
         <v>1</v>
@@ -5670,16 +5790,16 @@
         <v>38</v>
       </c>
       <c r="Q38">
-        <v>64.989999999999995</v>
-      </c>
-      <c r="R38">
-        <v>10.83</v>
+        <v>40.99</v>
       </c>
       <c r="Y38" t="s">
-        <v>56</v>
+        <v>618</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>619</v>
       </c>
       <c r="AA38" t="s">
-        <v>464</v>
+        <v>620</v>
       </c>
       <c r="AB38" t="s">
         <v>39</v>
@@ -5693,13 +5813,13 @@
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>465</v>
+        <v>621</v>
       </c>
       <c r="C39" t="s">
-        <v>466</v>
+        <v>622</v>
       </c>
       <c r="D39" t="s">
-        <v>467</v>
+        <v>623</v>
       </c>
       <c r="E39" t="s">
         <v>33</v>
@@ -5717,34 +5837,43 @@
         <v>54</v>
       </c>
       <c r="K39" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L39" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M39" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N39" t="s">
         <v>33</v>
       </c>
       <c r="O39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P39" t="s">
         <v>38</v>
       </c>
       <c r="Q39">
-        <v>79.98</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R39">
-        <v>13.34</v>
+        <v>10.83</v>
+      </c>
+      <c r="S39">
+        <v>6.99</v>
+      </c>
+      <c r="T39">
+        <v>1.17</v>
       </c>
       <c r="Y39" t="s">
-        <v>468</v>
+        <v>624</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>625</v>
       </c>
       <c r="AA39" t="s">
-        <v>469</v>
+        <v>626</v>
       </c>
       <c r="AB39" t="s">
         <v>39</v>
@@ -5758,13 +5887,13 @@
     </row>
     <row r="40" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>470</v>
+        <v>627</v>
       </c>
       <c r="C40" t="s">
-        <v>471</v>
+        <v>628</v>
       </c>
       <c r="D40" t="s">
-        <v>472</v>
+        <v>629</v>
       </c>
       <c r="E40" t="s">
         <v>33</v>
@@ -5782,13 +5911,13 @@
         <v>54</v>
       </c>
       <c r="K40" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L40" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M40" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="N40" t="s">
         <v>33</v>
@@ -5800,16 +5929,16 @@
         <v>38</v>
       </c>
       <c r="Q40">
-        <v>37.99</v>
+        <v>11.99</v>
       </c>
       <c r="R40">
-        <v>6.33</v>
+        <v>2</v>
       </c>
       <c r="Y40" t="s">
-        <v>473</v>
+        <v>630</v>
       </c>
       <c r="AA40" t="s">
-        <v>474</v>
+        <v>631</v>
       </c>
       <c r="AB40" t="s">
         <v>39</v>
@@ -5823,16 +5952,16 @@
     </row>
     <row r="41" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>475</v>
+        <v>649</v>
       </c>
       <c r="C41" t="s">
-        <v>476</v>
+        <v>650</v>
       </c>
       <c r="D41" t="s">
-        <v>477</v>
+        <v>651</v>
       </c>
       <c r="E41" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F41" t="s">
         <v>34</v>
@@ -5847,25 +5976,37 @@
         <v>54</v>
       </c>
       <c r="K41" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L41" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M41" t="s">
-        <v>42</v>
+        <v>50</v>
+      </c>
+      <c r="N41" t="s">
+        <v>33</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P41" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q41">
+        <v>39.99</v>
+      </c>
+      <c r="R41">
+        <v>6.67</v>
       </c>
       <c r="Y41" t="s">
-        <v>478</v>
+        <v>652</v>
       </c>
       <c r="Z41" t="s">
-        <v>279</v>
+        <v>653</v>
       </c>
       <c r="AA41" t="s">
-        <v>479</v>
+        <v>654</v>
       </c>
       <c r="AB41" t="s">
         <v>39</v>
@@ -5879,13 +6020,13 @@
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>480</v>
+        <v>655</v>
       </c>
       <c r="C42" t="s">
-        <v>481</v>
+        <v>656</v>
       </c>
       <c r="D42" t="s">
-        <v>482</v>
+        <v>657</v>
       </c>
       <c r="E42" t="s">
         <v>33</v>
@@ -5903,13 +6044,13 @@
         <v>54</v>
       </c>
       <c r="K42" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="L42" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="M42" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="N42" t="s">
         <v>33</v>
@@ -5921,16 +6062,16 @@
         <v>38</v>
       </c>
       <c r="Q42">
-        <v>11.99</v>
+        <v>14.99</v>
       </c>
       <c r="R42">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Y42" t="s">
-        <v>61</v>
+        <v>658</v>
       </c>
       <c r="AA42" t="s">
-        <v>483</v>
+        <v>659</v>
       </c>
       <c r="AB42" t="s">
         <v>39</v>
@@ -5944,13 +6085,13 @@
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>484</v>
+        <v>571</v>
       </c>
       <c r="C43" t="s">
-        <v>485</v>
+        <v>572</v>
       </c>
       <c r="D43" t="s">
-        <v>486</v>
+        <v>660</v>
       </c>
       <c r="E43" t="s">
         <v>33</v>
@@ -5992,10 +6133,10 @@
         <v>10.83</v>
       </c>
       <c r="Y43" t="s">
-        <v>67</v>
+        <v>573</v>
       </c>
       <c r="AA43" t="s">
-        <v>487</v>
+        <v>574</v>
       </c>
       <c r="AB43" t="s">
         <v>39</v>
@@ -6009,13 +6150,13 @@
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>488</v>
+        <v>599</v>
       </c>
       <c r="C44" t="s">
-        <v>489</v>
+        <v>600</v>
       </c>
       <c r="D44" t="s">
-        <v>490</v>
+        <v>601</v>
       </c>
       <c r="E44" t="s">
         <v>33</v>
@@ -6033,37 +6174,34 @@
         <v>54</v>
       </c>
       <c r="K44" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="L44" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="M44" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="N44" t="s">
         <v>33</v>
       </c>
       <c r="O44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P44" t="s">
         <v>38</v>
       </c>
       <c r="Q44">
-        <v>79.98</v>
+        <v>14.99</v>
       </c>
       <c r="R44">
-        <v>13.34</v>
+        <v>2.5</v>
       </c>
       <c r="Y44" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z44" t="s">
-        <v>491</v>
+        <v>61</v>
       </c>
       <c r="AA44" t="s">
-        <v>492</v>
+        <v>602</v>
       </c>
       <c r="AB44" t="s">
         <v>39</v>
@@ -6077,13 +6215,13 @@
     </row>
     <row r="45" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>497</v>
+        <v>589</v>
       </c>
       <c r="C45" t="s">
-        <v>498</v>
+        <v>590</v>
       </c>
       <c r="D45" t="s">
-        <v>499</v>
+        <v>591</v>
       </c>
       <c r="E45" t="s">
         <v>33</v>
@@ -6119,19 +6257,16 @@
         <v>38</v>
       </c>
       <c r="Q45">
-        <v>59.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R45">
-        <v>10</v>
+        <v>10.83</v>
       </c>
       <c r="Y45" t="s">
-        <v>500</v>
-      </c>
-      <c r="Z45" t="s">
-        <v>501</v>
+        <v>592</v>
       </c>
       <c r="AA45" t="s">
-        <v>502</v>
+        <v>593</v>
       </c>
       <c r="AB45" t="s">
         <v>39</v>
@@ -6145,13 +6280,13 @@
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>503</v>
+        <v>594</v>
       </c>
       <c r="C46" t="s">
-        <v>504</v>
+        <v>595</v>
       </c>
       <c r="D46" t="s">
-        <v>499</v>
+        <v>596</v>
       </c>
       <c r="E46" t="s">
         <v>33</v>
@@ -6187,19 +6322,16 @@
         <v>38</v>
       </c>
       <c r="Q46">
-        <v>59.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R46">
-        <v>10</v>
+        <v>10.83</v>
       </c>
       <c r="Y46" t="s">
-        <v>505</v>
-      </c>
-      <c r="Z46" t="s">
-        <v>93</v>
+        <v>597</v>
       </c>
       <c r="AA46" t="s">
-        <v>506</v>
+        <v>598</v>
       </c>
       <c r="AB46" t="s">
         <v>39</v>
@@ -6213,13 +6345,13 @@
     </row>
     <row r="47" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>507</v>
+        <v>603</v>
       </c>
       <c r="C47" t="s">
-        <v>508</v>
+        <v>604</v>
       </c>
       <c r="D47" t="s">
-        <v>509</v>
+        <v>605</v>
       </c>
       <c r="E47" t="s">
         <v>33</v>
@@ -6255,16 +6387,19 @@
         <v>38</v>
       </c>
       <c r="Q47">
-        <v>59.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R47">
-        <v>10</v>
+        <v>10.83</v>
       </c>
       <c r="Y47" t="s">
-        <v>510</v>
+        <v>606</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>607</v>
       </c>
       <c r="AA47" t="s">
-        <v>511</v>
+        <v>608</v>
       </c>
       <c r="AB47" t="s">
         <v>39</v>
@@ -6278,13 +6413,13 @@
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>512</v>
+        <v>578</v>
       </c>
       <c r="C48" t="s">
-        <v>513</v>
+        <v>579</v>
       </c>
       <c r="D48" t="s">
-        <v>514</v>
+        <v>661</v>
       </c>
       <c r="E48" t="s">
         <v>33</v>
@@ -6320,19 +6455,19 @@
         <v>38</v>
       </c>
       <c r="Q48">
-        <v>59.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R48">
-        <v>10</v>
+        <v>10.83</v>
       </c>
       <c r="Y48" t="s">
-        <v>515</v>
+        <v>580</v>
       </c>
       <c r="Z48" t="s">
-        <v>516</v>
+        <v>581</v>
       </c>
       <c r="AA48" t="s">
-        <v>517</v>
+        <v>582</v>
       </c>
       <c r="AB48" t="s">
         <v>39</v>
@@ -6346,16 +6481,16 @@
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>521</v>
+        <v>575</v>
       </c>
       <c r="C49" t="s">
-        <v>522</v>
+        <v>576</v>
       </c>
       <c r="D49" t="s">
-        <v>523</v>
+        <v>577</v>
       </c>
       <c r="E49" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F49" t="s">
         <v>34</v>
@@ -6370,34 +6505,22 @@
         <v>54</v>
       </c>
       <c r="K49" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L49" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M49" t="s">
-        <v>83</v>
-      </c>
-      <c r="N49" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O49">
-        <v>1</v>
-      </c>
-      <c r="P49" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q49">
-        <v>14.99</v>
-      </c>
-      <c r="R49">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="s">
-        <v>58</v>
+        <v>573</v>
       </c>
       <c r="AA49" t="s">
-        <v>524</v>
+        <v>574</v>
       </c>
       <c r="AB49" t="s">
         <v>39</v>
@@ -6411,13 +6534,13 @@
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="C50" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="D50" t="s">
-        <v>527</v>
+        <v>583</v>
       </c>
       <c r="E50" t="s">
         <v>33</v>
@@ -6435,13 +6558,13 @@
         <v>54</v>
       </c>
       <c r="K50" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L50" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M50" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N50" t="s">
         <v>33</v>
@@ -6453,16 +6576,22 @@
         <v>38</v>
       </c>
       <c r="Q50">
-        <v>59.99</v>
+        <v>37.99</v>
       </c>
       <c r="R50">
-        <v>10</v>
+        <v>6.33</v>
+      </c>
+      <c r="S50">
+        <v>6.99</v>
+      </c>
+      <c r="T50">
+        <v>1.17</v>
       </c>
       <c r="Y50" t="s">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="AA50" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="AB50" t="s">
         <v>39</v>
@@ -6476,13 +6605,13 @@
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>529</v>
+        <v>584</v>
       </c>
       <c r="C51" t="s">
-        <v>530</v>
+        <v>585</v>
       </c>
       <c r="D51" t="s">
-        <v>527</v>
+        <v>586</v>
       </c>
       <c r="E51" t="s">
         <v>33</v>
@@ -6518,16 +6647,16 @@
         <v>38</v>
       </c>
       <c r="Q51">
-        <v>59.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R51">
-        <v>10</v>
+        <v>10.83</v>
       </c>
       <c r="Y51" t="s">
-        <v>531</v>
+        <v>587</v>
       </c>
       <c r="AA51" t="s">
-        <v>532</v>
+        <v>588</v>
       </c>
       <c r="AB51" t="s">
         <v>39</v>
@@ -6541,13 +6670,13 @@
     </row>
     <row r="52" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>533</v>
+        <v>457</v>
       </c>
       <c r="C52" t="s">
-        <v>534</v>
+        <v>458</v>
       </c>
       <c r="D52" t="s">
-        <v>535</v>
+        <v>459</v>
       </c>
       <c r="E52" t="s">
         <v>33</v>
@@ -6565,13 +6694,13 @@
         <v>54</v>
       </c>
       <c r="K52" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L52" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M52" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N52" t="s">
         <v>33</v>
@@ -6583,19 +6712,19 @@
         <v>38</v>
       </c>
       <c r="Q52">
-        <v>11.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R52">
-        <v>2</v>
+        <v>10.83</v>
       </c>
       <c r="Y52" t="s">
-        <v>536</v>
+        <v>460</v>
       </c>
       <c r="Z52" t="s">
-        <v>537</v>
+        <v>279</v>
       </c>
       <c r="AA52" t="s">
-        <v>538</v>
+        <v>461</v>
       </c>
       <c r="AB52" t="s">
         <v>39</v>
@@ -6609,13 +6738,13 @@
     </row>
     <row r="53" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>539</v>
+        <v>462</v>
       </c>
       <c r="C53" t="s">
-        <v>540</v>
+        <v>463</v>
       </c>
       <c r="D53" t="s">
-        <v>541</v>
+        <v>459</v>
       </c>
       <c r="E53" t="s">
         <v>33</v>
@@ -6651,19 +6780,16 @@
         <v>38</v>
       </c>
       <c r="Q53">
-        <v>59.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R53">
-        <v>10</v>
+        <v>10.83</v>
       </c>
       <c r="Y53" t="s">
-        <v>71</v>
-      </c>
-      <c r="Z53" t="s">
-        <v>542</v>
+        <v>56</v>
       </c>
       <c r="AA53" t="s">
-        <v>543</v>
+        <v>464</v>
       </c>
       <c r="AB53" t="s">
         <v>39</v>
@@ -6677,13 +6803,13 @@
     </row>
     <row r="54" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>544</v>
+        <v>465</v>
       </c>
       <c r="C54" t="s">
-        <v>545</v>
+        <v>466</v>
       </c>
       <c r="D54" t="s">
-        <v>546</v>
+        <v>467</v>
       </c>
       <c r="E54" t="s">
         <v>33</v>
@@ -6701,13 +6827,13 @@
         <v>54</v>
       </c>
       <c r="K54" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="L54" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M54" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="N54" t="s">
         <v>33</v>
@@ -6719,19 +6845,16 @@
         <v>38</v>
       </c>
       <c r="Q54">
-        <v>76.98</v>
+        <v>79.98</v>
       </c>
       <c r="R54">
-        <v>12.84</v>
+        <v>13.34</v>
       </c>
       <c r="Y54" t="s">
-        <v>547</v>
-      </c>
-      <c r="Z54" t="s">
-        <v>548</v>
+        <v>468</v>
       </c>
       <c r="AA54" t="s">
-        <v>549</v>
+        <v>469</v>
       </c>
       <c r="AB54" t="s">
         <v>39</v>
@@ -6745,13 +6868,13 @@
     </row>
     <row r="55" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>550</v>
+        <v>470</v>
       </c>
       <c r="C55" t="s">
-        <v>551</v>
+        <v>471</v>
       </c>
       <c r="D55" t="s">
-        <v>552</v>
+        <v>472</v>
       </c>
       <c r="E55" t="s">
         <v>33</v>
@@ -6769,13 +6892,13 @@
         <v>54</v>
       </c>
       <c r="K55" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L55" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M55" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N55" t="s">
         <v>33</v>
@@ -6787,16 +6910,16 @@
         <v>38</v>
       </c>
       <c r="Q55">
-        <v>59.99</v>
+        <v>37.99</v>
       </c>
       <c r="R55">
-        <v>10</v>
+        <v>6.33</v>
       </c>
       <c r="Y55" t="s">
-        <v>553</v>
+        <v>473</v>
       </c>
       <c r="AA55" t="s">
-        <v>554</v>
+        <v>474</v>
       </c>
       <c r="AB55" t="s">
         <v>39</v>
@@ -6810,16 +6933,16 @@
     </row>
     <row r="56" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>555</v>
+        <v>475</v>
       </c>
       <c r="C56" t="s">
-        <v>556</v>
+        <v>476</v>
       </c>
       <c r="D56" t="s">
-        <v>557</v>
+        <v>477</v>
       </c>
       <c r="E56" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F56" t="s">
         <v>34</v>
@@ -6842,26 +6965,17 @@
       <c r="M56" t="s">
         <v>42</v>
       </c>
-      <c r="N56" t="s">
-        <v>33</v>
-      </c>
       <c r="O56">
-        <v>1</v>
-      </c>
-      <c r="P56" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q56">
-        <v>59.99</v>
-      </c>
-      <c r="R56">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="s">
-        <v>558</v>
+        <v>478</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>279</v>
       </c>
       <c r="AA56" t="s">
-        <v>559</v>
+        <v>479</v>
       </c>
       <c r="AB56" t="s">
         <v>39</v>
@@ -6875,13 +6989,13 @@
     </row>
     <row r="57" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>418</v>
+        <v>480</v>
       </c>
       <c r="C57" t="s">
-        <v>419</v>
+        <v>481</v>
       </c>
       <c r="D57" t="s">
-        <v>560</v>
+        <v>482</v>
       </c>
       <c r="E57" t="s">
         <v>33</v>
@@ -6899,13 +7013,13 @@
         <v>54</v>
       </c>
       <c r="K57" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L57" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M57" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N57" t="s">
         <v>33</v>
@@ -6917,16 +7031,16 @@
         <v>38</v>
       </c>
       <c r="Q57">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R57">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y57" t="s">
-        <v>420</v>
+        <v>61</v>
       </c>
       <c r="AA57" t="s">
-        <v>421</v>
+        <v>483</v>
       </c>
       <c r="AB57" t="s">
         <v>39</v>
@@ -6940,13 +7054,13 @@
     </row>
     <row r="58" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>561</v>
+        <v>484</v>
       </c>
       <c r="C58" t="s">
-        <v>562</v>
+        <v>485</v>
       </c>
       <c r="D58" t="s">
-        <v>563</v>
+        <v>486</v>
       </c>
       <c r="E58" t="s">
         <v>33</v>
@@ -6982,19 +7096,16 @@
         <v>38</v>
       </c>
       <c r="Q58">
-        <v>59.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R58">
-        <v>10</v>
+        <v>10.83</v>
       </c>
       <c r="Y58" t="s">
-        <v>564</v>
-      </c>
-      <c r="Z58" t="s">
-        <v>565</v>
+        <v>67</v>
       </c>
       <c r="AA58" t="s">
-        <v>566</v>
+        <v>487</v>
       </c>
       <c r="AB58" t="s">
         <v>39</v>
@@ -7008,13 +7119,13 @@
     </row>
     <row r="59" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>567</v>
+        <v>488</v>
       </c>
       <c r="C59" t="s">
-        <v>568</v>
+        <v>489</v>
       </c>
       <c r="D59" t="s">
-        <v>569</v>
+        <v>490</v>
       </c>
       <c r="E59" t="s">
         <v>33</v>
@@ -7032,34 +7143,37 @@
         <v>54</v>
       </c>
       <c r="K59" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="L59" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="M59" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="N59" t="s">
         <v>33</v>
       </c>
       <c r="O59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P59" t="s">
         <v>38</v>
       </c>
       <c r="Q59">
-        <v>14.99</v>
+        <v>79.98</v>
       </c>
       <c r="R59">
-        <v>2.5</v>
+        <v>13.34</v>
       </c>
       <c r="Y59" t="s">
-        <v>69</v>
+        <v>63</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>491</v>
       </c>
       <c r="AA59" t="s">
-        <v>570</v>
+        <v>492</v>
       </c>
       <c r="AB59" t="s">
         <v>39</v>
@@ -7073,13 +7187,13 @@
     </row>
     <row r="60" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>413</v>
+        <v>497</v>
       </c>
       <c r="C60" t="s">
-        <v>414</v>
+        <v>498</v>
       </c>
       <c r="D60" t="s">
-        <v>415</v>
+        <v>499</v>
       </c>
       <c r="E60" t="s">
         <v>33</v>
@@ -7121,10 +7235,13 @@
         <v>10</v>
       </c>
       <c r="Y60" t="s">
-        <v>416</v>
+        <v>500</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>501</v>
       </c>
       <c r="AA60" t="s">
-        <v>417</v>
+        <v>502</v>
       </c>
       <c r="AB60" t="s">
         <v>39</v>
@@ -7138,13 +7255,13 @@
     </row>
     <row r="61" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>422</v>
+        <v>503</v>
       </c>
       <c r="C61" t="s">
-        <v>423</v>
+        <v>504</v>
       </c>
       <c r="D61" t="s">
-        <v>424</v>
+        <v>499</v>
       </c>
       <c r="E61" t="s">
         <v>33</v>
@@ -7162,13 +7279,13 @@
         <v>54</v>
       </c>
       <c r="K61" t="s">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="L61" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="M61" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="N61" t="s">
         <v>33</v>
@@ -7180,16 +7297,19 @@
         <v>38</v>
       </c>
       <c r="Q61">
-        <v>22.99</v>
+        <v>59.99</v>
       </c>
       <c r="R61">
-        <v>3.83</v>
+        <v>10</v>
       </c>
       <c r="Y61" t="s">
-        <v>425</v>
+        <v>505</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>93</v>
       </c>
       <c r="AA61" t="s">
-        <v>426</v>
+        <v>506</v>
       </c>
       <c r="AB61" t="s">
         <v>39</v>
@@ -7203,13 +7323,13 @@
     </row>
     <row r="62" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>427</v>
+        <v>507</v>
       </c>
       <c r="C62" t="s">
-        <v>428</v>
+        <v>508</v>
       </c>
       <c r="D62" t="s">
-        <v>424</v>
+        <v>509</v>
       </c>
       <c r="E62" t="s">
         <v>33</v>
@@ -7227,13 +7347,13 @@
         <v>54</v>
       </c>
       <c r="K62" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L62" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M62" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N62" t="s">
         <v>33</v>
@@ -7245,19 +7365,16 @@
         <v>38</v>
       </c>
       <c r="Q62">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R62">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y62" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z62" t="s">
-        <v>97</v>
+        <v>510</v>
       </c>
       <c r="AA62" t="s">
-        <v>429</v>
+        <v>511</v>
       </c>
       <c r="AB62" t="s">
         <v>39</v>
@@ -7271,13 +7388,13 @@
     </row>
     <row r="63" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>430</v>
+        <v>512</v>
       </c>
       <c r="C63" t="s">
-        <v>431</v>
+        <v>513</v>
       </c>
       <c r="D63" t="s">
-        <v>432</v>
+        <v>514</v>
       </c>
       <c r="E63" t="s">
         <v>33</v>
@@ -7295,13 +7412,13 @@
         <v>54</v>
       </c>
       <c r="K63" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L63" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M63" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N63" t="s">
         <v>33</v>
@@ -7313,19 +7430,19 @@
         <v>38</v>
       </c>
       <c r="Q63">
-        <v>38.49</v>
+        <v>59.99</v>
       </c>
       <c r="R63">
-        <v>6.42</v>
+        <v>10</v>
       </c>
       <c r="Y63" t="s">
-        <v>59</v>
+        <v>515</v>
       </c>
       <c r="Z63" t="s">
-        <v>433</v>
+        <v>516</v>
       </c>
       <c r="AA63" t="s">
-        <v>434</v>
+        <v>517</v>
       </c>
       <c r="AB63" t="s">
         <v>39</v>
@@ -7339,13 +7456,13 @@
     </row>
     <row r="64" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>435</v>
+        <v>521</v>
       </c>
       <c r="C64" t="s">
-        <v>436</v>
+        <v>522</v>
       </c>
       <c r="D64" t="s">
-        <v>437</v>
+        <v>523</v>
       </c>
       <c r="E64" t="s">
         <v>33</v>
@@ -7363,13 +7480,13 @@
         <v>54</v>
       </c>
       <c r="K64" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L64" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="M64" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="N64" t="s">
         <v>33</v>
@@ -7387,10 +7504,10 @@
         <v>2.5</v>
       </c>
       <c r="Y64" t="s">
-        <v>438</v>
+        <v>58</v>
       </c>
       <c r="AA64" t="s">
-        <v>439</v>
+        <v>524</v>
       </c>
       <c r="AB64" t="s">
         <v>39</v>
@@ -7404,13 +7521,13 @@
     </row>
     <row r="65" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>440</v>
+        <v>525</v>
       </c>
       <c r="C65" t="s">
-        <v>441</v>
+        <v>526</v>
       </c>
       <c r="D65" t="s">
-        <v>442</v>
+        <v>527</v>
       </c>
       <c r="E65" t="s">
         <v>33</v>
@@ -7428,13 +7545,13 @@
         <v>54</v>
       </c>
       <c r="K65" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L65" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M65" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N65" t="s">
         <v>33</v>
@@ -7446,16 +7563,16 @@
         <v>38</v>
       </c>
       <c r="Q65">
-        <v>37.99</v>
+        <v>59.99</v>
       </c>
       <c r="R65">
-        <v>6.33</v>
+        <v>10</v>
       </c>
       <c r="Y65" t="s">
-        <v>443</v>
+        <v>90</v>
       </c>
       <c r="AA65" t="s">
-        <v>444</v>
+        <v>528</v>
       </c>
       <c r="AB65" t="s">
         <v>39</v>
@@ -7469,13 +7586,13 @@
     </row>
     <row r="66" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>445</v>
+        <v>529</v>
       </c>
       <c r="C66" t="s">
-        <v>446</v>
+        <v>530</v>
       </c>
       <c r="D66" t="s">
-        <v>447</v>
+        <v>527</v>
       </c>
       <c r="E66" t="s">
         <v>33</v>
@@ -7517,10 +7634,10 @@
         <v>10</v>
       </c>
       <c r="Y66" t="s">
-        <v>448</v>
+        <v>531</v>
       </c>
       <c r="AA66" t="s">
-        <v>449</v>
+        <v>532</v>
       </c>
       <c r="AB66" t="s">
         <v>39</v>
@@ -7534,16 +7651,16 @@
     </row>
     <row r="67" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>450</v>
+        <v>533</v>
       </c>
       <c r="C67" t="s">
-        <v>451</v>
+        <v>534</v>
       </c>
       <c r="D67" t="s">
-        <v>452</v>
+        <v>535</v>
       </c>
       <c r="E67" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F67" t="s">
         <v>34</v>
@@ -7558,22 +7675,37 @@
         <v>54</v>
       </c>
       <c r="K67" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L67" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M67" t="s">
-        <v>42</v>
+        <v>74</v>
+      </c>
+      <c r="N67" t="s">
+        <v>33</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P67" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q67">
+        <v>11.99</v>
+      </c>
+      <c r="R67">
+        <v>2</v>
       </c>
       <c r="Y67" t="s">
-        <v>453</v>
+        <v>536</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>537</v>
       </c>
       <c r="AA67" t="s">
-        <v>454</v>
+        <v>538</v>
       </c>
       <c r="AB67" t="s">
         <v>39</v>
@@ -7587,13 +7719,13 @@
     </row>
     <row r="68" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>403</v>
+        <v>539</v>
       </c>
       <c r="C68" t="s">
-        <v>404</v>
+        <v>540</v>
       </c>
       <c r="D68" t="s">
-        <v>455</v>
+        <v>541</v>
       </c>
       <c r="E68" t="s">
         <v>33</v>
@@ -7634,17 +7766,14 @@
       <c r="R68">
         <v>10</v>
       </c>
-      <c r="S68">
-        <v>5.99</v>
-      </c>
-      <c r="T68">
-        <v>1</v>
-      </c>
       <c r="Y68" t="s">
-        <v>405</v>
+        <v>71</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>542</v>
       </c>
       <c r="AA68" t="s">
-        <v>406</v>
+        <v>543</v>
       </c>
       <c r="AB68" t="s">
         <v>39</v>
@@ -7658,13 +7787,13 @@
     </row>
     <row r="69" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>407</v>
+        <v>544</v>
       </c>
       <c r="C69" t="s">
-        <v>408</v>
+        <v>545</v>
       </c>
       <c r="D69" t="s">
-        <v>456</v>
+        <v>546</v>
       </c>
       <c r="E69" t="s">
         <v>33</v>
@@ -7682,34 +7811,37 @@
         <v>54</v>
       </c>
       <c r="K69" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="L69" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="M69" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="N69" t="s">
         <v>33</v>
       </c>
       <c r="O69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P69" t="s">
         <v>38</v>
       </c>
       <c r="Q69">
-        <v>22.99</v>
+        <v>76.98</v>
       </c>
       <c r="R69">
-        <v>3.83</v>
+        <v>12.84</v>
       </c>
       <c r="Y69" t="s">
-        <v>409</v>
+        <v>547</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>548</v>
       </c>
       <c r="AA69" t="s">
-        <v>410</v>
+        <v>549</v>
       </c>
       <c r="AB69" t="s">
         <v>39</v>
@@ -7723,13 +7855,13 @@
     </row>
     <row r="70" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>399</v>
+        <v>550</v>
       </c>
       <c r="C70" t="s">
-        <v>400</v>
+        <v>551</v>
       </c>
       <c r="D70" t="s">
-        <v>411</v>
+        <v>552</v>
       </c>
       <c r="E70" t="s">
         <v>33</v>
@@ -7747,13 +7879,13 @@
         <v>54</v>
       </c>
       <c r="K70" t="s">
-        <v>340</v>
+        <v>40</v>
       </c>
       <c r="L70" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="M70" t="s">
-        <v>143</v>
+        <v>42</v>
       </c>
       <c r="N70" t="s">
         <v>33</v>
@@ -7765,16 +7897,16 @@
         <v>38</v>
       </c>
       <c r="Q70">
-        <v>44.99</v>
+        <v>59.99</v>
       </c>
       <c r="R70">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="Y70" t="s">
-        <v>401</v>
+        <v>553</v>
       </c>
       <c r="AA70" t="s">
-        <v>402</v>
+        <v>554</v>
       </c>
       <c r="AB70" t="s">
         <v>39</v>
@@ -7788,13 +7920,13 @@
     </row>
     <row r="71" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>394</v>
+        <v>555</v>
       </c>
       <c r="C71" t="s">
-        <v>395</v>
+        <v>556</v>
       </c>
       <c r="D71" t="s">
-        <v>412</v>
+        <v>557</v>
       </c>
       <c r="E71" t="s">
         <v>33</v>
@@ -7812,13 +7944,13 @@
         <v>54</v>
       </c>
       <c r="K71" t="s">
-        <v>340</v>
+        <v>40</v>
       </c>
       <c r="L71" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="M71" t="s">
-        <v>143</v>
+        <v>42</v>
       </c>
       <c r="N71" t="s">
         <v>33</v>
@@ -7830,19 +7962,16 @@
         <v>38</v>
       </c>
       <c r="Q71">
-        <v>44.99</v>
+        <v>59.99</v>
       </c>
       <c r="R71">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="Y71" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z71" t="s">
-        <v>397</v>
+        <v>558</v>
       </c>
       <c r="AA71" t="s">
-        <v>398</v>
+        <v>559</v>
       </c>
       <c r="AB71" t="s">
         <v>39</v>
@@ -7856,13 +7985,13 @@
     </row>
     <row r="72" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>338</v>
+        <v>418</v>
       </c>
       <c r="C72" t="s">
-        <v>339</v>
+        <v>419</v>
       </c>
       <c r="D72" t="s">
-        <v>662</v>
+        <v>560</v>
       </c>
       <c r="E72" t="s">
         <v>33</v>
@@ -7880,13 +8009,13 @@
         <v>54</v>
       </c>
       <c r="K72" t="s">
-        <v>340</v>
+        <v>40</v>
       </c>
       <c r="L72" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="M72" t="s">
-        <v>143</v>
+        <v>42</v>
       </c>
       <c r="N72" t="s">
         <v>33</v>
@@ -7898,16 +8027,16 @@
         <v>38</v>
       </c>
       <c r="Q72">
-        <v>44.99</v>
+        <v>59.99</v>
       </c>
       <c r="R72">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="Y72" t="s">
-        <v>341</v>
+        <v>420</v>
       </c>
       <c r="AA72" t="s">
-        <v>342</v>
+        <v>421</v>
       </c>
       <c r="AB72" t="s">
         <v>39</v>
@@ -7921,13 +8050,13 @@
     </row>
     <row r="73" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>663</v>
+        <v>561</v>
       </c>
       <c r="C73" t="s">
-        <v>664</v>
+        <v>562</v>
       </c>
       <c r="D73" t="s">
-        <v>665</v>
+        <v>563</v>
       </c>
       <c r="E73" t="s">
         <v>33</v>
@@ -7969,19 +8098,19 @@
         <v>10</v>
       </c>
       <c r="Y73" t="s">
-        <v>62</v>
+        <v>564</v>
       </c>
       <c r="Z73" t="s">
-        <v>666</v>
+        <v>565</v>
       </c>
       <c r="AA73" t="s">
-        <v>667</v>
+        <v>566</v>
       </c>
       <c r="AB73" t="s">
         <v>39</v>
       </c>
       <c r="AD73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG73" t="b">
         <v>0</v>
@@ -7989,13 +8118,13 @@
     </row>
     <row r="74" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>334</v>
+        <v>567</v>
       </c>
       <c r="C74" t="s">
-        <v>335</v>
+        <v>568</v>
       </c>
       <c r="D74" t="s">
-        <v>668</v>
+        <v>569</v>
       </c>
       <c r="E74" t="s">
         <v>33</v>
@@ -8013,13 +8142,13 @@
         <v>54</v>
       </c>
       <c r="K74" t="s">
-        <v>203</v>
+        <v>94</v>
       </c>
       <c r="L74" t="s">
-        <v>204</v>
+        <v>82</v>
       </c>
       <c r="M74" t="s">
-        <v>205</v>
+        <v>83</v>
       </c>
       <c r="N74" t="s">
         <v>33</v>
@@ -8031,16 +8160,16 @@
         <v>38</v>
       </c>
       <c r="Q74">
-        <v>69.989999999999995</v>
+        <v>14.99</v>
       </c>
       <c r="R74">
-        <v>11.67</v>
+        <v>2.5</v>
       </c>
       <c r="Y74" t="s">
-        <v>336</v>
+        <v>69</v>
       </c>
       <c r="AA74" t="s">
-        <v>337</v>
+        <v>570</v>
       </c>
       <c r="AB74" t="s">
         <v>39</v>
@@ -8054,13 +8183,13 @@
     </row>
     <row r="75" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>326</v>
+        <v>413</v>
       </c>
       <c r="C75" t="s">
-        <v>327</v>
+        <v>414</v>
       </c>
       <c r="D75" t="s">
-        <v>669</v>
+        <v>415</v>
       </c>
       <c r="E75" t="s">
         <v>33</v>
@@ -8078,34 +8207,34 @@
         <v>54</v>
       </c>
       <c r="K75" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L75" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M75" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N75" t="s">
         <v>33</v>
       </c>
       <c r="O75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P75" t="s">
         <v>38</v>
       </c>
       <c r="Q75">
-        <v>75.98</v>
+        <v>59.99</v>
       </c>
       <c r="R75">
-        <v>12.66</v>
+        <v>10</v>
       </c>
       <c r="Y75" t="s">
-        <v>91</v>
+        <v>416</v>
       </c>
       <c r="AA75" t="s">
-        <v>328</v>
+        <v>417</v>
       </c>
       <c r="AB75" t="s">
         <v>39</v>
@@ -8119,13 +8248,13 @@
     </row>
     <row r="76" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>343</v>
+        <v>422</v>
       </c>
       <c r="C76" t="s">
-        <v>344</v>
+        <v>423</v>
       </c>
       <c r="D76" t="s">
-        <v>345</v>
+        <v>424</v>
       </c>
       <c r="E76" t="s">
         <v>33</v>
@@ -8143,13 +8272,13 @@
         <v>54</v>
       </c>
       <c r="K76" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="L76" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="M76" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="N76" t="s">
         <v>33</v>
@@ -8161,16 +8290,16 @@
         <v>38</v>
       </c>
       <c r="Q76">
-        <v>59.99</v>
+        <v>22.99</v>
       </c>
       <c r="R76">
-        <v>10</v>
+        <v>3.83</v>
       </c>
       <c r="Y76" t="s">
-        <v>346</v>
+        <v>425</v>
       </c>
       <c r="AA76" t="s">
-        <v>347</v>
+        <v>426</v>
       </c>
       <c r="AB76" t="s">
         <v>39</v>
@@ -8184,13 +8313,13 @@
     </row>
     <row r="77" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>288</v>
+        <v>427</v>
       </c>
       <c r="C77" t="s">
-        <v>289</v>
+        <v>428</v>
       </c>
       <c r="D77" t="s">
-        <v>348</v>
+        <v>424</v>
       </c>
       <c r="E77" t="s">
         <v>33</v>
@@ -8205,37 +8334,40 @@
         <v>36</v>
       </c>
       <c r="J77" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K77" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L77" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M77" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="N77" t="s">
         <v>33</v>
       </c>
       <c r="O77">
+        <v>1</v>
+      </c>
+      <c r="P77" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q77">
+        <v>11.99</v>
+      </c>
+      <c r="R77">
         <v>2</v>
       </c>
-      <c r="P77" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q77">
-        <v>75.98</v>
-      </c>
-      <c r="R77">
-        <v>12.66</v>
-      </c>
       <c r="Y77" t="s">
-        <v>290</v>
+        <v>96</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>97</v>
       </c>
       <c r="AA77" t="s">
-        <v>291</v>
+        <v>429</v>
       </c>
       <c r="AB77" t="s">
         <v>39</v>
@@ -8249,13 +8381,13 @@
     </row>
     <row r="78" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>349</v>
+        <v>430</v>
       </c>
       <c r="C78" t="s">
-        <v>350</v>
+        <v>431</v>
       </c>
       <c r="D78" t="s">
-        <v>351</v>
+        <v>432</v>
       </c>
       <c r="E78" t="s">
         <v>33</v>
@@ -8273,13 +8405,13 @@
         <v>54</v>
       </c>
       <c r="K78" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="L78" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="M78" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="N78" t="s">
         <v>33</v>
@@ -8291,19 +8423,19 @@
         <v>38</v>
       </c>
       <c r="Q78">
-        <v>37.99</v>
+        <v>38.49</v>
       </c>
       <c r="R78">
-        <v>6.33</v>
+        <v>6.42</v>
       </c>
       <c r="Y78" t="s">
-        <v>352</v>
+        <v>59</v>
       </c>
       <c r="Z78" t="s">
-        <v>353</v>
+        <v>433</v>
       </c>
       <c r="AA78" t="s">
-        <v>354</v>
+        <v>434</v>
       </c>
       <c r="AB78" t="s">
         <v>39</v>
@@ -8317,13 +8449,13 @@
     </row>
     <row r="79" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>355</v>
+        <v>435</v>
       </c>
       <c r="C79" t="s">
-        <v>356</v>
+        <v>436</v>
       </c>
       <c r="D79" t="s">
-        <v>357</v>
+        <v>437</v>
       </c>
       <c r="E79" t="s">
         <v>33</v>
@@ -8341,13 +8473,13 @@
         <v>54</v>
       </c>
       <c r="K79" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="L79" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M79" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="N79" t="s">
         <v>33</v>
@@ -8359,16 +8491,16 @@
         <v>38</v>
       </c>
       <c r="Q79">
-        <v>11.99</v>
+        <v>14.99</v>
       </c>
       <c r="R79">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Y79" t="s">
-        <v>58</v>
+        <v>438</v>
       </c>
       <c r="AA79" t="s">
-        <v>358</v>
+        <v>439</v>
       </c>
       <c r="AB79" t="s">
         <v>39</v>
@@ -8382,13 +8514,13 @@
     </row>
     <row r="80" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>359</v>
+        <v>440</v>
       </c>
       <c r="C80" t="s">
-        <v>360</v>
+        <v>441</v>
       </c>
       <c r="D80" t="s">
-        <v>361</v>
+        <v>442</v>
       </c>
       <c r="E80" t="s">
         <v>33</v>
@@ -8418,25 +8550,22 @@
         <v>33</v>
       </c>
       <c r="O80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P80" t="s">
         <v>38</v>
       </c>
       <c r="Q80">
-        <v>75.98</v>
+        <v>37.99</v>
       </c>
       <c r="R80">
-        <v>12.66</v>
+        <v>6.33</v>
       </c>
       <c r="Y80" t="s">
-        <v>101</v>
-      </c>
-      <c r="Z80" t="s">
-        <v>59</v>
+        <v>443</v>
       </c>
       <c r="AA80" t="s">
-        <v>362</v>
+        <v>444</v>
       </c>
       <c r="AB80" t="s">
         <v>39</v>
@@ -8450,13 +8579,13 @@
     </row>
     <row r="81" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>363</v>
+        <v>445</v>
       </c>
       <c r="C81" t="s">
-        <v>364</v>
+        <v>446</v>
       </c>
       <c r="D81" t="s">
-        <v>365</v>
+        <v>447</v>
       </c>
       <c r="E81" t="s">
         <v>33</v>
@@ -8474,13 +8603,13 @@
         <v>54</v>
       </c>
       <c r="K81" t="s">
-        <v>260</v>
+        <v>40</v>
       </c>
       <c r="L81" t="s">
-        <v>261</v>
+        <v>41</v>
       </c>
       <c r="M81" t="s">
-        <v>262</v>
+        <v>42</v>
       </c>
       <c r="N81" t="s">
         <v>33</v>
@@ -8492,16 +8621,16 @@
         <v>38</v>
       </c>
       <c r="Q81">
-        <v>24.49</v>
+        <v>59.99</v>
       </c>
       <c r="R81">
-        <v>4.08</v>
+        <v>10</v>
       </c>
       <c r="Y81" t="s">
-        <v>366</v>
+        <v>448</v>
       </c>
       <c r="AA81" t="s">
-        <v>367</v>
+        <v>449</v>
       </c>
       <c r="AB81" t="s">
         <v>39</v>
@@ -8515,16 +8644,16 @@
     </row>
     <row r="82" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>265</v>
+        <v>450</v>
       </c>
       <c r="C82" t="s">
-        <v>266</v>
+        <v>451</v>
       </c>
       <c r="D82" t="s">
-        <v>368</v>
+        <v>452</v>
       </c>
       <c r="E82" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F82" t="s">
         <v>34</v>
@@ -8539,34 +8668,22 @@
         <v>54</v>
       </c>
       <c r="K82" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L82" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M82" t="s">
-        <v>50</v>
-      </c>
-      <c r="N82" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O82">
-        <v>1</v>
-      </c>
-      <c r="P82" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q82">
-        <v>37.99</v>
-      </c>
-      <c r="R82">
-        <v>6.33</v>
+        <v>0</v>
       </c>
       <c r="Y82" t="s">
-        <v>267</v>
+        <v>453</v>
       </c>
       <c r="AA82" t="s">
-        <v>268</v>
+        <v>454</v>
       </c>
       <c r="AB82" t="s">
         <v>39</v>
@@ -8580,13 +8697,13 @@
     </row>
     <row r="83" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>369</v>
+        <v>403</v>
       </c>
       <c r="C83" t="s">
-        <v>370</v>
+        <v>404</v>
       </c>
       <c r="D83" t="s">
-        <v>371</v>
+        <v>455</v>
       </c>
       <c r="E83" t="s">
         <v>33</v>
@@ -8604,13 +8721,13 @@
         <v>54</v>
       </c>
       <c r="K83" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L83" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M83" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N83" t="s">
         <v>33</v>
@@ -8622,10 +8739,10 @@
         <v>38</v>
       </c>
       <c r="Q83">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R83">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="S83">
         <v>5.99</v>
@@ -8634,10 +8751,10 @@
         <v>1</v>
       </c>
       <c r="Y83" t="s">
-        <v>84</v>
+        <v>405</v>
       </c>
       <c r="AA83" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="AB83" t="s">
         <v>39</v>
@@ -8651,13 +8768,13 @@
     </row>
     <row r="84" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="C84" t="s">
-        <v>374</v>
+        <v>408</v>
       </c>
       <c r="D84" t="s">
-        <v>375</v>
+        <v>456</v>
       </c>
       <c r="E84" t="s">
         <v>33</v>
@@ -8675,13 +8792,13 @@
         <v>54</v>
       </c>
       <c r="K84" t="s">
-        <v>260</v>
+        <v>79</v>
       </c>
       <c r="L84" t="s">
-        <v>261</v>
+        <v>80</v>
       </c>
       <c r="M84" t="s">
-        <v>262</v>
+        <v>81</v>
       </c>
       <c r="N84" t="s">
         <v>33</v>
@@ -8693,16 +8810,16 @@
         <v>38</v>
       </c>
       <c r="Q84">
-        <v>24.49</v>
+        <v>22.99</v>
       </c>
       <c r="R84">
-        <v>4.08</v>
+        <v>3.83</v>
       </c>
       <c r="Y84" t="s">
-        <v>376</v>
+        <v>409</v>
       </c>
       <c r="AA84" t="s">
-        <v>377</v>
+        <v>410</v>
       </c>
       <c r="AB84" t="s">
         <v>39</v>
@@ -8716,13 +8833,13 @@
     </row>
     <row r="85" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="C85" t="s">
-        <v>379</v>
+        <v>400</v>
       </c>
       <c r="D85" t="s">
-        <v>380</v>
+        <v>411</v>
       </c>
       <c r="E85" t="s">
         <v>33</v>
@@ -8740,13 +8857,13 @@
         <v>54</v>
       </c>
       <c r="K85" t="s">
-        <v>40</v>
+        <v>340</v>
       </c>
       <c r="L85" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="M85" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="N85" t="s">
         <v>33</v>
@@ -8758,16 +8875,16 @@
         <v>38</v>
       </c>
       <c r="Q85">
-        <v>59.99</v>
+        <v>44.99</v>
       </c>
       <c r="R85">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="Y85" t="s">
-        <v>57</v>
+        <v>401</v>
       </c>
       <c r="AA85" t="s">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="AB85" t="s">
         <v>39</v>
@@ -8781,13 +8898,13 @@
     </row>
     <row r="86" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="C86" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="D86" t="s">
-        <v>384</v>
+        <v>412</v>
       </c>
       <c r="E86" t="s">
         <v>33</v>
@@ -8805,13 +8922,13 @@
         <v>54</v>
       </c>
       <c r="K86" t="s">
-        <v>72</v>
+        <v>340</v>
       </c>
       <c r="L86" t="s">
-        <v>73</v>
+        <v>142</v>
       </c>
       <c r="M86" t="s">
-        <v>74</v>
+        <v>143</v>
       </c>
       <c r="N86" t="s">
         <v>33</v>
@@ -8823,16 +8940,19 @@
         <v>38</v>
       </c>
       <c r="Q86">
-        <v>11.99</v>
+        <v>44.99</v>
       </c>
       <c r="R86">
-        <v>2</v>
+        <v>7.5</v>
       </c>
       <c r="Y86" t="s">
-        <v>385</v>
+        <v>396</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>397</v>
       </c>
       <c r="AA86" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="AB86" t="s">
         <v>39</v>
@@ -8846,16 +8966,16 @@
     </row>
     <row r="87" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>387</v>
+        <v>338</v>
       </c>
       <c r="C87" t="s">
-        <v>388</v>
+        <v>339</v>
       </c>
       <c r="D87" t="s">
-        <v>389</v>
+        <v>662</v>
       </c>
       <c r="E87" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F87" t="s">
         <v>34</v>
@@ -8870,25 +8990,34 @@
         <v>54</v>
       </c>
       <c r="K87" t="s">
-        <v>43</v>
+        <v>340</v>
       </c>
       <c r="L87" t="s">
-        <v>44</v>
+        <v>142</v>
       </c>
       <c r="M87" t="s">
-        <v>45</v>
+        <v>143</v>
+      </c>
+      <c r="N87" t="s">
+        <v>33</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P87" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q87">
+        <v>44.99</v>
+      </c>
+      <c r="R87">
+        <v>7.5</v>
       </c>
       <c r="Y87" t="s">
-        <v>390</v>
-      </c>
-      <c r="Z87" t="s">
-        <v>391</v>
+        <v>341</v>
       </c>
       <c r="AA87" t="s">
-        <v>392</v>
+        <v>342</v>
       </c>
       <c r="AB87" t="s">
         <v>39</v>
@@ -8902,13 +9031,13 @@
     </row>
     <row r="88" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>323</v>
+        <v>663</v>
       </c>
       <c r="C88" t="s">
-        <v>324</v>
+        <v>664</v>
       </c>
       <c r="D88" t="s">
-        <v>393</v>
+        <v>665</v>
       </c>
       <c r="E88" t="s">
         <v>33</v>
@@ -8926,13 +9055,13 @@
         <v>54</v>
       </c>
       <c r="K88" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="L88" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="M88" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="N88" t="s">
         <v>33</v>
@@ -8944,22 +9073,25 @@
         <v>38</v>
       </c>
       <c r="Q88">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R88">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y88" t="s">
-        <v>58</v>
+        <v>62</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>666</v>
       </c>
       <c r="AA88" t="s">
-        <v>325</v>
+        <v>667</v>
       </c>
       <c r="AB88" t="s">
         <v>39</v>
       </c>
       <c r="AD88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG88" t="b">
         <v>0</v>
@@ -8967,13 +9099,13 @@
     </row>
     <row r="89" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>318</v>
+        <v>334</v>
       </c>
       <c r="C89" t="s">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c r="D89" t="s">
-        <v>320</v>
+        <v>668</v>
       </c>
       <c r="E89" t="s">
         <v>33</v>
@@ -8991,13 +9123,13 @@
         <v>54</v>
       </c>
       <c r="K89" t="s">
-        <v>72</v>
+        <v>203</v>
       </c>
       <c r="L89" t="s">
-        <v>73</v>
+        <v>204</v>
       </c>
       <c r="M89" t="s">
-        <v>74</v>
+        <v>205</v>
       </c>
       <c r="N89" t="s">
         <v>33</v>
@@ -9009,19 +9141,16 @@
         <v>38</v>
       </c>
       <c r="Q89">
-        <v>11.99</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="R89">
-        <v>2</v>
+        <v>11.67</v>
       </c>
       <c r="Y89" t="s">
-        <v>321</v>
-      </c>
-      <c r="Z89" t="s">
-        <v>65</v>
+        <v>336</v>
       </c>
       <c r="AA89" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="AB89" t="s">
         <v>39</v>
@@ -9035,13 +9164,13 @@
     </row>
     <row r="90" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C90" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D90" t="s">
-        <v>331</v>
+        <v>669</v>
       </c>
       <c r="E90" t="s">
         <v>33</v>
@@ -9059,34 +9188,34 @@
         <v>54</v>
       </c>
       <c r="K90" t="s">
-        <v>260</v>
+        <v>48</v>
       </c>
       <c r="L90" t="s">
-        <v>261</v>
+        <v>49</v>
       </c>
       <c r="M90" t="s">
-        <v>262</v>
+        <v>50</v>
       </c>
       <c r="N90" t="s">
         <v>33</v>
       </c>
       <c r="O90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P90" t="s">
         <v>38</v>
       </c>
       <c r="Q90">
-        <v>24.49</v>
+        <v>75.98</v>
       </c>
       <c r="R90">
-        <v>4.08</v>
+        <v>12.66</v>
       </c>
       <c r="Y90" t="s">
-        <v>332</v>
+        <v>91</v>
       </c>
       <c r="AA90" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="AB90" t="s">
         <v>39</v>
@@ -9100,13 +9229,13 @@
     </row>
     <row r="91" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>670</v>
+        <v>343</v>
       </c>
       <c r="C91" t="s">
-        <v>671</v>
+        <v>344</v>
       </c>
       <c r="D91" t="s">
-        <v>672</v>
+        <v>345</v>
       </c>
       <c r="E91" t="s">
         <v>33</v>
@@ -9148,10 +9277,10 @@
         <v>10</v>
       </c>
       <c r="Y91" t="s">
-        <v>673</v>
+        <v>346</v>
       </c>
       <c r="AA91" t="s">
-        <v>674</v>
+        <v>347</v>
       </c>
       <c r="AB91" t="s">
         <v>39</v>
@@ -9165,13 +9294,13 @@
     </row>
     <row r="92" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>675</v>
+        <v>288</v>
       </c>
       <c r="C92" t="s">
-        <v>676</v>
+        <v>289</v>
       </c>
       <c r="D92" t="s">
-        <v>677</v>
+        <v>348</v>
       </c>
       <c r="E92" t="s">
         <v>33</v>
@@ -9186,7 +9315,7 @@
         <v>36</v>
       </c>
       <c r="J92" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K92" t="s">
         <v>48</v>
@@ -9201,22 +9330,22 @@
         <v>33</v>
       </c>
       <c r="O92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P92" t="s">
         <v>38</v>
       </c>
       <c r="Q92">
-        <v>37.99</v>
+        <v>75.98</v>
       </c>
       <c r="R92">
-        <v>6.33</v>
+        <v>12.66</v>
       </c>
       <c r="Y92" t="s">
-        <v>678</v>
+        <v>290</v>
       </c>
       <c r="AA92" t="s">
-        <v>679</v>
+        <v>291</v>
       </c>
       <c r="AB92" t="s">
         <v>39</v>
@@ -9230,13 +9359,13 @@
     </row>
     <row r="93" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>680</v>
+        <v>349</v>
       </c>
       <c r="C93" t="s">
-        <v>681</v>
+        <v>350</v>
       </c>
       <c r="D93" t="s">
-        <v>682</v>
+        <v>351</v>
       </c>
       <c r="E93" t="s">
         <v>33</v>
@@ -9254,13 +9383,13 @@
         <v>54</v>
       </c>
       <c r="K93" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L93" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M93" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N93" t="s">
         <v>33</v>
@@ -9272,19 +9401,19 @@
         <v>38</v>
       </c>
       <c r="Q93">
-        <v>59.99</v>
+        <v>37.99</v>
       </c>
       <c r="R93">
-        <v>10</v>
+        <v>6.33</v>
       </c>
       <c r="Y93" t="s">
-        <v>683</v>
+        <v>352</v>
       </c>
       <c r="Z93" t="s">
-        <v>76</v>
+        <v>353</v>
       </c>
       <c r="AA93" t="s">
-        <v>684</v>
+        <v>354</v>
       </c>
       <c r="AB93" t="s">
         <v>39</v>
@@ -9298,13 +9427,13 @@
     </row>
     <row r="94" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>685</v>
+        <v>355</v>
       </c>
       <c r="C94" t="s">
-        <v>686</v>
+        <v>356</v>
       </c>
       <c r="D94" t="s">
-        <v>687</v>
+        <v>357</v>
       </c>
       <c r="E94" t="s">
         <v>33</v>
@@ -9322,13 +9451,13 @@
         <v>54</v>
       </c>
       <c r="K94" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L94" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M94" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="N94" t="s">
         <v>33</v>
@@ -9340,16 +9469,16 @@
         <v>38</v>
       </c>
       <c r="Q94">
-        <v>37.99</v>
+        <v>11.99</v>
       </c>
       <c r="R94">
-        <v>6.33</v>
+        <v>2</v>
       </c>
       <c r="Y94" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="AA94" t="s">
-        <v>688</v>
+        <v>358</v>
       </c>
       <c r="AB94" t="s">
         <v>39</v>
@@ -9363,16 +9492,16 @@
     </row>
     <row r="95" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>689</v>
+        <v>359</v>
       </c>
       <c r="C95" t="s">
-        <v>690</v>
+        <v>360</v>
       </c>
       <c r="D95" t="s">
-        <v>691</v>
+        <v>361</v>
       </c>
       <c r="E95" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F95" t="s">
         <v>34</v>
@@ -9384,7 +9513,7 @@
         <v>36</v>
       </c>
       <c r="J95" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K95" t="s">
         <v>48</v>
@@ -9395,17 +9524,29 @@
       <c r="M95" t="s">
         <v>50</v>
       </c>
+      <c r="N95" t="s">
+        <v>33</v>
+      </c>
       <c r="O95">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="P95" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q95">
+        <v>75.98</v>
+      </c>
+      <c r="R95">
+        <v>12.66</v>
       </c>
       <c r="Y95" t="s">
-        <v>692</v>
+        <v>101</v>
       </c>
       <c r="Z95" t="s">
-        <v>693</v>
+        <v>59</v>
       </c>
       <c r="AA95" t="s">
-        <v>694</v>
+        <v>362</v>
       </c>
       <c r="AB95" t="s">
         <v>39</v>
@@ -9419,16 +9560,16 @@
     </row>
     <row r="96" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>695</v>
+        <v>363</v>
       </c>
       <c r="C96" t="s">
-        <v>696</v>
+        <v>364</v>
       </c>
       <c r="D96" t="s">
-        <v>697</v>
+        <v>365</v>
       </c>
       <c r="E96" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F96" t="s">
         <v>34</v>
@@ -9440,28 +9581,37 @@
         <v>36</v>
       </c>
       <c r="J96" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K96" t="s">
-        <v>48</v>
+        <v>260</v>
       </c>
       <c r="L96" t="s">
-        <v>49</v>
+        <v>261</v>
       </c>
       <c r="M96" t="s">
-        <v>50</v>
+        <v>262</v>
+      </c>
+      <c r="N96" t="s">
+        <v>33</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P96" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q96">
+        <v>24.49</v>
+      </c>
+      <c r="R96">
+        <v>4.08</v>
       </c>
       <c r="Y96" t="s">
-        <v>692</v>
-      </c>
-      <c r="Z96" t="s">
-        <v>693</v>
+        <v>366</v>
       </c>
       <c r="AA96" t="s">
-        <v>694</v>
+        <v>367</v>
       </c>
       <c r="AB96" t="s">
         <v>39</v>
@@ -9475,13 +9625,13 @@
     </row>
     <row r="97" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>300</v>
+        <v>265</v>
       </c>
       <c r="C97" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="D97" t="s">
-        <v>698</v>
+        <v>368</v>
       </c>
       <c r="E97" t="s">
         <v>33</v>
@@ -9499,13 +9649,13 @@
         <v>54</v>
       </c>
       <c r="K97" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="L97" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="M97" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="N97" t="s">
         <v>33</v>
@@ -9517,16 +9667,16 @@
         <v>38</v>
       </c>
       <c r="Q97">
-        <v>14.99</v>
+        <v>37.99</v>
       </c>
       <c r="R97">
-        <v>2.5</v>
+        <v>6.33</v>
       </c>
       <c r="Y97" t="s">
-        <v>58</v>
+        <v>267</v>
       </c>
       <c r="AA97" t="s">
-        <v>302</v>
+        <v>268</v>
       </c>
       <c r="AB97" t="s">
         <v>39</v>
@@ -9540,16 +9690,16 @@
     </row>
     <row r="98" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>699</v>
+        <v>369</v>
       </c>
       <c r="C98" t="s">
-        <v>700</v>
+        <v>370</v>
       </c>
       <c r="D98" t="s">
-        <v>701</v>
+        <v>371</v>
       </c>
       <c r="E98" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F98" t="s">
         <v>34</v>
@@ -9564,25 +9714,40 @@
         <v>54</v>
       </c>
       <c r="K98" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L98" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M98" t="s">
-        <v>50</v>
+        <v>74</v>
+      </c>
+      <c r="N98" t="s">
+        <v>33</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P98" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q98">
+        <v>11.99</v>
+      </c>
+      <c r="R98">
+        <v>2</v>
+      </c>
+      <c r="S98">
+        <v>5.99</v>
+      </c>
+      <c r="T98">
+        <v>1</v>
       </c>
       <c r="Y98" t="s">
-        <v>692</v>
-      </c>
-      <c r="Z98" t="s">
-        <v>693</v>
+        <v>84</v>
       </c>
       <c r="AA98" t="s">
-        <v>694</v>
+        <v>372</v>
       </c>
       <c r="AB98" t="s">
         <v>39</v>
@@ -9596,13 +9761,13 @@
     </row>
     <row r="99" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>303</v>
+        <v>373</v>
       </c>
       <c r="C99" t="s">
-        <v>304</v>
+        <v>374</v>
       </c>
       <c r="D99" t="s">
-        <v>702</v>
+        <v>375</v>
       </c>
       <c r="E99" t="s">
         <v>33</v>
@@ -9620,13 +9785,13 @@
         <v>54</v>
       </c>
       <c r="K99" t="s">
-        <v>40</v>
+        <v>260</v>
       </c>
       <c r="L99" t="s">
-        <v>41</v>
+        <v>261</v>
       </c>
       <c r="M99" t="s">
-        <v>42</v>
+        <v>262</v>
       </c>
       <c r="N99" t="s">
         <v>33</v>
@@ -9638,16 +9803,16 @@
         <v>38</v>
       </c>
       <c r="Q99">
-        <v>59.99</v>
+        <v>24.49</v>
       </c>
       <c r="R99">
-        <v>10</v>
+        <v>4.08</v>
       </c>
       <c r="Y99" t="s">
-        <v>305</v>
+        <v>376</v>
       </c>
       <c r="AA99" t="s">
-        <v>306</v>
+        <v>377</v>
       </c>
       <c r="AB99" t="s">
         <v>39</v>
@@ -9661,13 +9826,13 @@
     </row>
     <row r="100" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>292</v>
+        <v>378</v>
       </c>
       <c r="C100" t="s">
-        <v>293</v>
+        <v>379</v>
       </c>
       <c r="D100" t="s">
-        <v>294</v>
+        <v>380</v>
       </c>
       <c r="E100" t="s">
         <v>33</v>
@@ -9682,7 +9847,7 @@
         <v>36</v>
       </c>
       <c r="J100" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K100" t="s">
         <v>40</v>
@@ -9709,13 +9874,10 @@
         <v>10</v>
       </c>
       <c r="Y100" t="s">
-        <v>77</v>
-      </c>
-      <c r="Z100" t="s">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="AA100" t="s">
-        <v>295</v>
+        <v>381</v>
       </c>
       <c r="AB100" t="s">
         <v>39</v>
@@ -9729,13 +9891,13 @@
     </row>
     <row r="101" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>296</v>
+        <v>382</v>
       </c>
       <c r="C101" t="s">
-        <v>297</v>
+        <v>383</v>
       </c>
       <c r="D101" t="s">
-        <v>298</v>
+        <v>384</v>
       </c>
       <c r="E101" t="s">
         <v>33</v>
@@ -9750,16 +9912,16 @@
         <v>36</v>
       </c>
       <c r="J101" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K101" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L101" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M101" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N101" t="s">
         <v>33</v>
@@ -9771,19 +9933,16 @@
         <v>38</v>
       </c>
       <c r="Q101">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R101">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y101" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z101" t="s">
-        <v>51</v>
+        <v>385</v>
       </c>
       <c r="AA101" t="s">
-        <v>299</v>
+        <v>386</v>
       </c>
       <c r="AB101" t="s">
         <v>39</v>
@@ -9797,16 +9956,16 @@
     </row>
     <row r="102" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>307</v>
+        <v>387</v>
       </c>
       <c r="C102" t="s">
-        <v>308</v>
+        <v>388</v>
       </c>
       <c r="D102" t="s">
-        <v>309</v>
+        <v>389</v>
       </c>
       <c r="E102" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F102" t="s">
         <v>34</v>
@@ -9818,37 +9977,28 @@
         <v>36</v>
       </c>
       <c r="J102" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K102" t="s">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="L102" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="M102" t="s">
-        <v>89</v>
-      </c>
-      <c r="N102" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O102">
-        <v>1</v>
-      </c>
-      <c r="P102" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q102">
-        <v>20.49</v>
-      </c>
-      <c r="R102">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="Y102" t="s">
-        <v>310</v>
+        <v>390</v>
+      </c>
+      <c r="Z102" t="s">
+        <v>391</v>
       </c>
       <c r="AA102" t="s">
-        <v>311</v>
+        <v>392</v>
       </c>
       <c r="AB102" t="s">
         <v>39</v>
@@ -9862,13 +10012,13 @@
     </row>
     <row r="103" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="C103" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="D103" t="s">
-        <v>314</v>
+        <v>393</v>
       </c>
       <c r="E103" t="s">
         <v>33</v>
@@ -9883,16 +10033,16 @@
         <v>36</v>
       </c>
       <c r="J103" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K103" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="L103" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="M103" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="N103" t="s">
         <v>33</v>
@@ -9904,19 +10054,16 @@
         <v>38</v>
       </c>
       <c r="Q103">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="R103">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="Y103" t="s">
-        <v>100</v>
-      </c>
-      <c r="Z103" t="s">
-        <v>315</v>
+        <v>58</v>
       </c>
       <c r="AA103" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="AB103" t="s">
         <v>39</v>
@@ -9930,13 +10077,13 @@
     </row>
     <row r="104" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>253</v>
+        <v>318</v>
       </c>
       <c r="C104" t="s">
-        <v>254</v>
+        <v>319</v>
       </c>
       <c r="D104" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E104" t="s">
         <v>33</v>
@@ -9954,13 +10101,13 @@
         <v>54</v>
       </c>
       <c r="K104" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L104" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M104" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N104" t="s">
         <v>33</v>
@@ -9972,19 +10119,19 @@
         <v>38</v>
       </c>
       <c r="Q104">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R104">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y104" t="s">
-        <v>255</v>
+        <v>321</v>
       </c>
       <c r="Z104" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="AA104" t="s">
-        <v>256</v>
+        <v>322</v>
       </c>
       <c r="AB104" t="s">
         <v>39</v>
@@ -9998,13 +10145,13 @@
     </row>
     <row r="105" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>257</v>
+        <v>329</v>
       </c>
       <c r="C105" t="s">
-        <v>258</v>
+        <v>330</v>
       </c>
       <c r="D105" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="E105" t="s">
         <v>33</v>
@@ -10046,13 +10193,10 @@
         <v>4.08</v>
       </c>
       <c r="Y105" t="s">
-        <v>263</v>
-      </c>
-      <c r="Z105" t="s">
-        <v>64</v>
+        <v>332</v>
       </c>
       <c r="AA105" t="s">
-        <v>264</v>
+        <v>333</v>
       </c>
       <c r="AB105" t="s">
         <v>39</v>
@@ -10066,13 +10210,13 @@
     </row>
     <row r="106" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>269</v>
+        <v>670</v>
       </c>
       <c r="C106" t="s">
-        <v>270</v>
+        <v>671</v>
       </c>
       <c r="D106" t="s">
-        <v>271</v>
+        <v>672</v>
       </c>
       <c r="E106" t="s">
         <v>33</v>
@@ -10114,10 +10258,10 @@
         <v>10</v>
       </c>
       <c r="Y106" t="s">
-        <v>272</v>
+        <v>673</v>
       </c>
       <c r="AA106" t="s">
-        <v>273</v>
+        <v>674</v>
       </c>
       <c r="AB106" t="s">
         <v>39</v>
@@ -10131,13 +10275,13 @@
     </row>
     <row r="107" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>149</v>
+        <v>675</v>
       </c>
       <c r="C107" t="s">
-        <v>150</v>
+        <v>676</v>
       </c>
       <c r="D107" t="s">
-        <v>274</v>
+        <v>677</v>
       </c>
       <c r="E107" t="s">
         <v>33</v>
@@ -10155,13 +10299,13 @@
         <v>54</v>
       </c>
       <c r="K107" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L107" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M107" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N107" t="s">
         <v>33</v>
@@ -10173,16 +10317,16 @@
         <v>38</v>
       </c>
       <c r="Q107">
-        <v>59.99</v>
+        <v>37.99</v>
       </c>
       <c r="R107">
-        <v>10</v>
+        <v>6.33</v>
       </c>
       <c r="Y107" t="s">
-        <v>63</v>
+        <v>678</v>
       </c>
       <c r="AA107" t="s">
-        <v>151</v>
+        <v>679</v>
       </c>
       <c r="AB107" t="s">
         <v>39</v>
@@ -10196,13 +10340,13 @@
     </row>
     <row r="108" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>275</v>
+        <v>680</v>
       </c>
       <c r="C108" t="s">
-        <v>276</v>
+        <v>681</v>
       </c>
       <c r="D108" t="s">
-        <v>277</v>
+        <v>682</v>
       </c>
       <c r="E108" t="s">
         <v>33</v>
@@ -10232,25 +10376,25 @@
         <v>33</v>
       </c>
       <c r="O108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P108" t="s">
         <v>38</v>
       </c>
       <c r="Q108">
-        <v>119.98</v>
+        <v>59.99</v>
       </c>
       <c r="R108">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Y108" t="s">
-        <v>278</v>
+        <v>683</v>
       </c>
       <c r="Z108" t="s">
-        <v>279</v>
+        <v>76</v>
       </c>
       <c r="AA108" t="s">
-        <v>280</v>
+        <v>684</v>
       </c>
       <c r="AB108" t="s">
         <v>39</v>
@@ -10264,13 +10408,13 @@
     </row>
     <row r="109" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>281</v>
+        <v>685</v>
       </c>
       <c r="C109" t="s">
-        <v>282</v>
+        <v>686</v>
       </c>
       <c r="D109" t="s">
-        <v>283</v>
+        <v>687</v>
       </c>
       <c r="E109" t="s">
         <v>33</v>
@@ -10285,16 +10429,16 @@
         <v>36</v>
       </c>
       <c r="J109" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K109" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L109" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M109" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N109" t="s">
         <v>33</v>
@@ -10306,16 +10450,16 @@
         <v>38</v>
       </c>
       <c r="Q109">
-        <v>11.99</v>
+        <v>37.99</v>
       </c>
       <c r="R109">
-        <v>2</v>
+        <v>6.33</v>
       </c>
       <c r="Y109" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="AA109" t="s">
-        <v>284</v>
+        <v>688</v>
       </c>
       <c r="AB109" t="s">
         <v>39</v>
@@ -10329,13 +10473,13 @@
     </row>
     <row r="110" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>238</v>
+        <v>689</v>
       </c>
       <c r="C110" t="s">
-        <v>239</v>
+        <v>690</v>
       </c>
       <c r="D110" t="s">
-        <v>285</v>
+        <v>691</v>
       </c>
       <c r="E110" t="s">
         <v>53</v>
@@ -10350,25 +10494,28 @@
         <v>36</v>
       </c>
       <c r="J110" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K110" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L110" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M110" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="O110">
         <v>0</v>
       </c>
       <c r="Y110" t="s">
-        <v>240</v>
+        <v>692</v>
+      </c>
+      <c r="Z110" t="s">
+        <v>693</v>
       </c>
       <c r="AA110" t="s">
-        <v>241</v>
+        <v>694</v>
       </c>
       <c r="AB110" t="s">
         <v>39</v>
@@ -10382,16 +10529,16 @@
     </row>
     <row r="111" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>224</v>
+        <v>695</v>
       </c>
       <c r="C111" t="s">
-        <v>225</v>
+        <v>696</v>
       </c>
       <c r="D111" t="s">
-        <v>286</v>
+        <v>697</v>
       </c>
       <c r="E111" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F111" t="s">
         <v>34</v>
@@ -10403,37 +10550,28 @@
         <v>36</v>
       </c>
       <c r="J111" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K111" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L111" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M111" t="s">
-        <v>42</v>
-      </c>
-      <c r="N111" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="O111">
-        <v>1</v>
-      </c>
-      <c r="P111" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q111">
-        <v>59.99</v>
-      </c>
-      <c r="R111">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y111" t="s">
-        <v>226</v>
+        <v>692</v>
+      </c>
+      <c r="Z111" t="s">
+        <v>693</v>
       </c>
       <c r="AA111" t="s">
-        <v>227</v>
+        <v>694</v>
       </c>
       <c r="AB111" t="s">
         <v>39</v>
@@ -10447,13 +10585,13 @@
     </row>
     <row r="112" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>213</v>
+        <v>300</v>
       </c>
       <c r="C112" t="s">
-        <v>214</v>
+        <v>301</v>
       </c>
       <c r="D112" t="s">
-        <v>287</v>
+        <v>698</v>
       </c>
       <c r="E112" t="s">
         <v>33</v>
@@ -10471,13 +10609,13 @@
         <v>54</v>
       </c>
       <c r="K112" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="L112" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="M112" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="N112" t="s">
         <v>33</v>
@@ -10489,19 +10627,16 @@
         <v>38</v>
       </c>
       <c r="Q112">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="R112">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="Y112" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z112" t="s">
-        <v>216</v>
+        <v>58</v>
       </c>
       <c r="AA112" t="s">
-        <v>217</v>
+        <v>302</v>
       </c>
       <c r="AB112" t="s">
         <v>39</v>
@@ -10515,16 +10650,16 @@
     </row>
     <row r="113" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>218</v>
+        <v>699</v>
       </c>
       <c r="C113" t="s">
-        <v>219</v>
+        <v>700</v>
       </c>
       <c r="D113" t="s">
-        <v>220</v>
+        <v>701</v>
       </c>
       <c r="E113" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F113" t="s">
         <v>34</v>
@@ -10539,37 +10674,25 @@
         <v>54</v>
       </c>
       <c r="K113" t="s">
-        <v>203</v>
+        <v>48</v>
       </c>
       <c r="L113" t="s">
-        <v>204</v>
+        <v>49</v>
       </c>
       <c r="M113" t="s">
-        <v>205</v>
-      </c>
-      <c r="N113" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="O113">
-        <v>1</v>
-      </c>
-      <c r="P113" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q113">
-        <v>69.989999999999995</v>
-      </c>
-      <c r="R113">
-        <v>11.67</v>
+        <v>0</v>
       </c>
       <c r="Y113" t="s">
-        <v>221</v>
+        <v>692</v>
       </c>
       <c r="Z113" t="s">
-        <v>222</v>
+        <v>693</v>
       </c>
       <c r="AA113" t="s">
-        <v>223</v>
+        <v>694</v>
       </c>
       <c r="AB113" t="s">
         <v>39</v>
@@ -10583,13 +10706,13 @@
     </row>
     <row r="114" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>228</v>
+        <v>303</v>
       </c>
       <c r="C114" t="s">
-        <v>229</v>
+        <v>304</v>
       </c>
       <c r="D114" t="s">
-        <v>230</v>
+        <v>702</v>
       </c>
       <c r="E114" t="s">
         <v>33</v>
@@ -10631,10 +10754,10 @@
         <v>10</v>
       </c>
       <c r="Y114" t="s">
-        <v>231</v>
+        <v>305</v>
       </c>
       <c r="AA114" t="s">
-        <v>232</v>
+        <v>306</v>
       </c>
       <c r="AB114" t="s">
         <v>39</v>
@@ -10648,13 +10771,13 @@
     </row>
     <row r="115" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>233</v>
+        <v>292</v>
       </c>
       <c r="C115" t="s">
-        <v>234</v>
+        <v>293</v>
       </c>
       <c r="D115" t="s">
-        <v>235</v>
+        <v>294</v>
       </c>
       <c r="E115" t="s">
         <v>33</v>
@@ -10669,16 +10792,16 @@
         <v>36</v>
       </c>
       <c r="J115" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K115" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="L115" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="M115" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="N115" t="s">
         <v>33</v>
@@ -10690,16 +10813,19 @@
         <v>38</v>
       </c>
       <c r="Q115">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R115">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y115" t="s">
-        <v>236</v>
+        <v>77</v>
+      </c>
+      <c r="Z115" t="s">
+        <v>92</v>
       </c>
       <c r="AA115" t="s">
-        <v>237</v>
+        <v>295</v>
       </c>
       <c r="AB115" t="s">
         <v>39</v>
@@ -10713,16 +10839,16 @@
     </row>
     <row r="116" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>242</v>
+        <v>296</v>
       </c>
       <c r="C116" t="s">
-        <v>243</v>
+        <v>297</v>
       </c>
       <c r="D116" t="s">
-        <v>244</v>
+        <v>298</v>
       </c>
       <c r="E116" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F116" t="s">
         <v>34</v>
@@ -10734,7 +10860,7 @@
         <v>36</v>
       </c>
       <c r="J116" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K116" t="s">
         <v>40</v>
@@ -10745,14 +10871,29 @@
       <c r="M116" t="s">
         <v>42</v>
       </c>
+      <c r="N116" t="s">
+        <v>33</v>
+      </c>
       <c r="O116">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P116" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q116">
+        <v>59.99</v>
+      </c>
+      <c r="R116">
+        <v>10</v>
       </c>
       <c r="Y116" t="s">
-        <v>240</v>
+        <v>62</v>
+      </c>
+      <c r="Z116" t="s">
+        <v>51</v>
       </c>
       <c r="AA116" t="s">
-        <v>241</v>
+        <v>299</v>
       </c>
       <c r="AB116" t="s">
         <v>39</v>
@@ -10766,13 +10907,13 @@
     </row>
     <row r="117" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>245</v>
+        <v>307</v>
       </c>
       <c r="C117" t="s">
-        <v>246</v>
+        <v>308</v>
       </c>
       <c r="D117" t="s">
-        <v>247</v>
+        <v>309</v>
       </c>
       <c r="E117" t="s">
         <v>33</v>
@@ -10790,13 +10931,13 @@
         <v>37</v>
       </c>
       <c r="K117" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="L117" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="M117" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="N117" t="s">
         <v>33</v>
@@ -10808,16 +10949,16 @@
         <v>38</v>
       </c>
       <c r="Q117">
-        <v>59.99</v>
+        <v>20.49</v>
       </c>
       <c r="R117">
-        <v>10</v>
+        <v>3.42</v>
       </c>
       <c r="Y117" t="s">
-        <v>248</v>
+        <v>310</v>
       </c>
       <c r="AA117" t="s">
-        <v>249</v>
+        <v>311</v>
       </c>
       <c r="AB117" t="s">
         <v>39</v>
@@ -10831,13 +10972,13 @@
     </row>
     <row r="118" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>188</v>
+        <v>312</v>
       </c>
       <c r="C118" t="s">
-        <v>189</v>
+        <v>313</v>
       </c>
       <c r="D118" t="s">
-        <v>250</v>
+        <v>314</v>
       </c>
       <c r="E118" t="s">
         <v>33</v>
@@ -10855,13 +10996,13 @@
         <v>37</v>
       </c>
       <c r="K118" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L118" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M118" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N118" t="s">
         <v>33</v>
@@ -10873,16 +11014,19 @@
         <v>38</v>
       </c>
       <c r="Q118">
-        <v>37.99</v>
+        <v>59.99</v>
       </c>
       <c r="R118">
-        <v>6.33</v>
+        <v>10</v>
       </c>
       <c r="Y118" t="s">
-        <v>52</v>
+        <v>100</v>
+      </c>
+      <c r="Z118" t="s">
+        <v>315</v>
       </c>
       <c r="AA118" t="s">
-        <v>190</v>
+        <v>316</v>
       </c>
       <c r="AB118" t="s">
         <v>39</v>
@@ -10896,13 +11040,13 @@
     </row>
     <row r="119" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>191</v>
+        <v>253</v>
       </c>
       <c r="C119" t="s">
-        <v>192</v>
+        <v>254</v>
       </c>
       <c r="D119" t="s">
-        <v>251</v>
+        <v>317</v>
       </c>
       <c r="E119" t="s">
         <v>33</v>
@@ -10944,10 +11088,13 @@
         <v>10</v>
       </c>
       <c r="Y119" t="s">
-        <v>193</v>
+        <v>255</v>
+      </c>
+      <c r="Z119" t="s">
+        <v>102</v>
       </c>
       <c r="AA119" t="s">
-        <v>194</v>
+        <v>256</v>
       </c>
       <c r="AB119" t="s">
         <v>39</v>
@@ -10961,13 +11108,13 @@
     </row>
     <row r="120" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>201</v>
+        <v>257</v>
       </c>
       <c r="C120" t="s">
-        <v>202</v>
+        <v>258</v>
       </c>
       <c r="D120" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="E120" t="s">
         <v>33</v>
@@ -10985,13 +11132,13 @@
         <v>54</v>
       </c>
       <c r="K120" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="L120" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="M120" t="s">
-        <v>205</v>
+        <v>262</v>
       </c>
       <c r="N120" t="s">
         <v>33</v>
@@ -11003,19 +11150,19 @@
         <v>38</v>
       </c>
       <c r="Q120">
-        <v>69.989999999999995</v>
+        <v>24.49</v>
       </c>
       <c r="R120">
-        <v>11.67</v>
+        <v>4.08</v>
       </c>
       <c r="Y120" t="s">
-        <v>206</v>
+        <v>263</v>
       </c>
       <c r="Z120" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AA120" t="s">
-        <v>207</v>
+        <v>264</v>
       </c>
       <c r="AB120" t="s">
         <v>39</v>
@@ -11029,13 +11176,13 @@
     </row>
     <row r="121" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>195</v>
+        <v>269</v>
       </c>
       <c r="C121" t="s">
-        <v>196</v>
+        <v>270</v>
       </c>
       <c r="D121" t="s">
-        <v>197</v>
+        <v>271</v>
       </c>
       <c r="E121" t="s">
         <v>33</v>
@@ -11050,7 +11197,7 @@
         <v>36</v>
       </c>
       <c r="J121" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K121" t="s">
         <v>40</v>
@@ -11077,13 +11224,10 @@
         <v>10</v>
       </c>
       <c r="Y121" t="s">
-        <v>198</v>
-      </c>
-      <c r="Z121" t="s">
-        <v>199</v>
+        <v>272</v>
       </c>
       <c r="AA121" t="s">
-        <v>200</v>
+        <v>273</v>
       </c>
       <c r="AB121" t="s">
         <v>39</v>
@@ -11097,13 +11241,13 @@
     </row>
     <row r="122" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>208</v>
+        <v>149</v>
       </c>
       <c r="C122" t="s">
-        <v>209</v>
+        <v>150</v>
       </c>
       <c r="D122" t="s">
-        <v>210</v>
+        <v>274</v>
       </c>
       <c r="E122" t="s">
         <v>33</v>
@@ -11118,7 +11262,7 @@
         <v>36</v>
       </c>
       <c r="J122" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K122" t="s">
         <v>40</v>
@@ -11145,10 +11289,10 @@
         <v>10</v>
       </c>
       <c r="Y122" t="s">
-        <v>211</v>
+        <v>63</v>
       </c>
       <c r="AA122" t="s">
-        <v>212</v>
+        <v>151</v>
       </c>
       <c r="AB122" t="s">
         <v>39</v>
@@ -11162,13 +11306,13 @@
     </row>
     <row r="123" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>152</v>
+        <v>275</v>
       </c>
       <c r="C123" t="s">
-        <v>153</v>
+        <v>276</v>
       </c>
       <c r="D123" t="s">
-        <v>154</v>
+        <v>277</v>
       </c>
       <c r="E123" t="s">
         <v>33</v>
@@ -11186,34 +11330,37 @@
         <v>54</v>
       </c>
       <c r="K123" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="L123" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="M123" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="N123" t="s">
         <v>33</v>
       </c>
       <c r="O123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P123" t="s">
         <v>38</v>
       </c>
       <c r="Q123">
-        <v>14.99</v>
+        <v>119.98</v>
       </c>
       <c r="R123">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="Y123" t="s">
-        <v>155</v>
+        <v>278</v>
+      </c>
+      <c r="Z123" t="s">
+        <v>279</v>
       </c>
       <c r="AA123" t="s">
-        <v>156</v>
+        <v>280</v>
       </c>
       <c r="AB123" t="s">
         <v>39</v>
@@ -11227,13 +11374,13 @@
     </row>
     <row r="124" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>157</v>
+        <v>281</v>
       </c>
       <c r="C124" t="s">
-        <v>158</v>
+        <v>282</v>
       </c>
       <c r="D124" t="s">
-        <v>159</v>
+        <v>283</v>
       </c>
       <c r="E124" t="s">
         <v>33</v>
@@ -11248,7 +11395,7 @@
         <v>36</v>
       </c>
       <c r="J124" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K124" t="s">
         <v>72</v>
@@ -11275,10 +11422,10 @@
         <v>2</v>
       </c>
       <c r="Y124" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="AA124" t="s">
-        <v>160</v>
+        <v>284</v>
       </c>
       <c r="AB124" t="s">
         <v>39</v>
@@ -11292,13 +11439,13 @@
     </row>
     <row r="125" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>161</v>
+        <v>238</v>
       </c>
       <c r="C125" t="s">
-        <v>162</v>
+        <v>239</v>
       </c>
       <c r="D125" t="s">
-        <v>163</v>
+        <v>285</v>
       </c>
       <c r="E125" t="s">
         <v>53</v>
@@ -11328,10 +11475,10 @@
         <v>0</v>
       </c>
       <c r="Y125" t="s">
-        <v>63</v>
+        <v>240</v>
       </c>
       <c r="AA125" t="s">
-        <v>151</v>
+        <v>241</v>
       </c>
       <c r="AB125" t="s">
         <v>39</v>
@@ -11345,13 +11492,13 @@
     </row>
     <row r="126" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>164</v>
+        <v>224</v>
       </c>
       <c r="C126" t="s">
-        <v>165</v>
+        <v>225</v>
       </c>
       <c r="D126" t="s">
-        <v>166</v>
+        <v>286</v>
       </c>
       <c r="E126" t="s">
         <v>33</v>
@@ -11369,13 +11516,13 @@
         <v>54</v>
       </c>
       <c r="K126" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L126" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M126" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N126" t="s">
         <v>33</v>
@@ -11387,16 +11534,16 @@
         <v>38</v>
       </c>
       <c r="Q126">
-        <v>37.99</v>
+        <v>59.99</v>
       </c>
       <c r="R126">
-        <v>6.33</v>
+        <v>10</v>
       </c>
       <c r="Y126" t="s">
-        <v>100</v>
+        <v>226</v>
       </c>
       <c r="AA126" t="s">
-        <v>167</v>
+        <v>227</v>
       </c>
       <c r="AB126" t="s">
         <v>39</v>
@@ -11410,13 +11557,13 @@
     </row>
     <row r="127" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>168</v>
+        <v>213</v>
       </c>
       <c r="C127" t="s">
-        <v>169</v>
+        <v>214</v>
       </c>
       <c r="D127" t="s">
-        <v>170</v>
+        <v>287</v>
       </c>
       <c r="E127" t="s">
         <v>33</v>
@@ -11434,13 +11581,13 @@
         <v>54</v>
       </c>
       <c r="K127" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L127" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M127" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N127" t="s">
         <v>33</v>
@@ -11452,16 +11599,19 @@
         <v>38</v>
       </c>
       <c r="Q127">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R127">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y127" t="s">
-        <v>66</v>
+        <v>215</v>
+      </c>
+      <c r="Z127" t="s">
+        <v>216</v>
       </c>
       <c r="AA127" t="s">
-        <v>171</v>
+        <v>217</v>
       </c>
       <c r="AB127" t="s">
         <v>39</v>
@@ -11475,13 +11625,13 @@
     </row>
     <row r="128" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>172</v>
+        <v>218</v>
       </c>
       <c r="C128" t="s">
-        <v>173</v>
+        <v>219</v>
       </c>
       <c r="D128" t="s">
-        <v>174</v>
+        <v>220</v>
       </c>
       <c r="E128" t="s">
         <v>33</v>
@@ -11499,13 +11649,13 @@
         <v>54</v>
       </c>
       <c r="K128" t="s">
-        <v>94</v>
+        <v>203</v>
       </c>
       <c r="L128" t="s">
-        <v>82</v>
+        <v>204</v>
       </c>
       <c r="M128" t="s">
-        <v>83</v>
+        <v>205</v>
       </c>
       <c r="N128" t="s">
         <v>33</v>
@@ -11517,16 +11667,19 @@
         <v>38</v>
       </c>
       <c r="Q128">
-        <v>14.99</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="R128">
-        <v>2.5</v>
+        <v>11.67</v>
       </c>
       <c r="Y128" t="s">
-        <v>175</v>
+        <v>221</v>
+      </c>
+      <c r="Z128" t="s">
+        <v>222</v>
       </c>
       <c r="AA128" t="s">
-        <v>176</v>
+        <v>223</v>
       </c>
       <c r="AB128" t="s">
         <v>39</v>
@@ -11540,13 +11693,13 @@
     </row>
     <row r="129" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>177</v>
+        <v>228</v>
       </c>
       <c r="C129" t="s">
-        <v>178</v>
+        <v>229</v>
       </c>
       <c r="D129" t="s">
-        <v>179</v>
+        <v>230</v>
       </c>
       <c r="E129" t="s">
         <v>33</v>
@@ -11564,13 +11717,13 @@
         <v>54</v>
       </c>
       <c r="K129" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L129" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M129" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N129" t="s">
         <v>33</v>
@@ -11582,19 +11735,16 @@
         <v>38</v>
       </c>
       <c r="Q129">
-        <v>37.99</v>
+        <v>59.99</v>
       </c>
       <c r="R129">
-        <v>6.33</v>
+        <v>10</v>
       </c>
       <c r="Y129" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z129" t="s">
-        <v>181</v>
+        <v>231</v>
       </c>
       <c r="AA129" t="s">
-        <v>182</v>
+        <v>232</v>
       </c>
       <c r="AB129" t="s">
         <v>39</v>
@@ -11608,13 +11758,13 @@
     </row>
     <row r="130" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>183</v>
+        <v>233</v>
       </c>
       <c r="C130" t="s">
-        <v>184</v>
+        <v>234</v>
       </c>
       <c r="D130" t="s">
-        <v>179</v>
+        <v>235</v>
       </c>
       <c r="E130" t="s">
         <v>33</v>
@@ -11632,37 +11782,34 @@
         <v>54</v>
       </c>
       <c r="K130" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="L130" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="M130" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="N130" t="s">
         <v>33</v>
       </c>
       <c r="O130">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P130" t="s">
         <v>38</v>
       </c>
       <c r="Q130">
-        <v>75.98</v>
+        <v>14.99</v>
       </c>
       <c r="R130">
-        <v>12.66</v>
+        <v>2.5</v>
       </c>
       <c r="Y130" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z130" t="s">
-        <v>47</v>
+        <v>236</v>
       </c>
       <c r="AA130" t="s">
-        <v>185</v>
+        <v>237</v>
       </c>
       <c r="AB130" t="s">
         <v>39</v>
@@ -11676,16 +11823,16 @@
     </row>
     <row r="131" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>133</v>
+        <v>242</v>
       </c>
       <c r="C131" t="s">
-        <v>134</v>
+        <v>243</v>
       </c>
       <c r="D131" t="s">
-        <v>186</v>
+        <v>244</v>
       </c>
       <c r="E131" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F131" t="s">
         <v>34</v>
@@ -11700,34 +11847,22 @@
         <v>54</v>
       </c>
       <c r="K131" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L131" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M131" t="s">
-        <v>74</v>
-      </c>
-      <c r="N131" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O131">
-        <v>1</v>
-      </c>
-      <c r="P131" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q131">
-        <v>11.99</v>
-      </c>
-      <c r="R131">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y131" t="s">
-        <v>69</v>
+        <v>240</v>
       </c>
       <c r="AA131" t="s">
-        <v>135</v>
+        <v>241</v>
       </c>
       <c r="AB131" t="s">
         <v>39</v>
@@ -11741,13 +11876,13 @@
     </row>
     <row r="132" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>117</v>
+        <v>245</v>
       </c>
       <c r="C132" t="s">
-        <v>118</v>
+        <v>246</v>
       </c>
       <c r="D132" t="s">
-        <v>119</v>
+        <v>247</v>
       </c>
       <c r="E132" t="s">
         <v>33</v>
@@ -11762,16 +11897,16 @@
         <v>36</v>
       </c>
       <c r="J132" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K132" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L132" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M132" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="N132" t="s">
         <v>33</v>
@@ -11783,19 +11918,16 @@
         <v>38</v>
       </c>
       <c r="Q132">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R132">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y132" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z132" t="s">
-        <v>121</v>
+        <v>248</v>
       </c>
       <c r="AA132" t="s">
-        <v>122</v>
+        <v>249</v>
       </c>
       <c r="AB132" t="s">
         <v>39</v>
@@ -11809,13 +11941,13 @@
     </row>
     <row r="133" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>123</v>
+        <v>188</v>
       </c>
       <c r="C133" t="s">
-        <v>124</v>
+        <v>189</v>
       </c>
       <c r="D133" t="s">
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="E133" t="s">
         <v>33</v>
@@ -11830,16 +11962,16 @@
         <v>36</v>
       </c>
       <c r="J133" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K133" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L133" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M133" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N133" t="s">
         <v>33</v>
@@ -11851,19 +11983,16 @@
         <v>38</v>
       </c>
       <c r="Q133">
-        <v>59.99</v>
+        <v>37.99</v>
       </c>
       <c r="R133">
-        <v>10</v>
+        <v>6.33</v>
       </c>
       <c r="Y133" t="s">
-        <v>126</v>
-      </c>
-      <c r="Z133" t="s">
-        <v>127</v>
+        <v>52</v>
       </c>
       <c r="AA133" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="AB133" t="s">
         <v>39</v>
@@ -11877,13 +12006,13 @@
     </row>
     <row r="134" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>129</v>
+        <v>191</v>
       </c>
       <c r="C134" t="s">
-        <v>130</v>
+        <v>192</v>
       </c>
       <c r="D134" t="s">
-        <v>131</v>
+        <v>251</v>
       </c>
       <c r="E134" t="s">
         <v>33</v>
@@ -11901,13 +12030,13 @@
         <v>54</v>
       </c>
       <c r="K134" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L134" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M134" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N134" t="s">
         <v>33</v>
@@ -11919,16 +12048,16 @@
         <v>38</v>
       </c>
       <c r="Q134">
-        <v>38.49</v>
+        <v>59.99</v>
       </c>
       <c r="R134">
-        <v>6.42</v>
+        <v>10</v>
       </c>
       <c r="Y134" t="s">
-        <v>78</v>
+        <v>193</v>
       </c>
       <c r="AA134" t="s">
-        <v>132</v>
+        <v>194</v>
       </c>
       <c r="AB134" t="s">
         <v>39</v>
@@ -11942,16 +12071,16 @@
     </row>
     <row r="135" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>105</v>
+        <v>201</v>
       </c>
       <c r="C135" t="s">
-        <v>106</v>
+        <v>202</v>
       </c>
       <c r="D135" t="s">
-        <v>136</v>
+        <v>252</v>
       </c>
       <c r="E135" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F135" t="s">
         <v>34</v>
@@ -11966,22 +12095,37 @@
         <v>54</v>
       </c>
       <c r="K135" t="s">
-        <v>94</v>
+        <v>203</v>
       </c>
       <c r="L135" t="s">
-        <v>82</v>
+        <v>204</v>
       </c>
       <c r="M135" t="s">
-        <v>83</v>
+        <v>205</v>
+      </c>
+      <c r="N135" t="s">
+        <v>33</v>
       </c>
       <c r="O135">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P135" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q135">
+        <v>69.989999999999995</v>
+      </c>
+      <c r="R135">
+        <v>11.67</v>
       </c>
       <c r="Y135" t="s">
-        <v>103</v>
+        <v>206</v>
+      </c>
+      <c r="Z135" t="s">
+        <v>60</v>
       </c>
       <c r="AA135" t="s">
-        <v>104</v>
+        <v>207</v>
       </c>
       <c r="AB135" t="s">
         <v>39</v>
@@ -11995,13 +12139,13 @@
     </row>
     <row r="136" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>107</v>
+        <v>195</v>
       </c>
       <c r="C136" t="s">
-        <v>108</v>
+        <v>196</v>
       </c>
       <c r="D136" t="s">
-        <v>137</v>
+        <v>197</v>
       </c>
       <c r="E136" t="s">
         <v>33</v>
@@ -12016,16 +12160,16 @@
         <v>36</v>
       </c>
       <c r="J136" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K136" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L136" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M136" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N136" t="s">
         <v>33</v>
@@ -12037,19 +12181,19 @@
         <v>38</v>
       </c>
       <c r="Q136">
-        <v>37.99</v>
+        <v>59.99</v>
       </c>
       <c r="R136">
-        <v>6.33</v>
+        <v>10</v>
       </c>
       <c r="Y136" t="s">
-        <v>109</v>
+        <v>198</v>
       </c>
       <c r="Z136" t="s">
-        <v>110</v>
+        <v>199</v>
       </c>
       <c r="AA136" t="s">
-        <v>111</v>
+        <v>200</v>
       </c>
       <c r="AB136" t="s">
         <v>39</v>
@@ -12063,13 +12207,13 @@
     </row>
     <row r="137" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>112</v>
+        <v>208</v>
       </c>
       <c r="C137" t="s">
-        <v>113</v>
+        <v>209</v>
       </c>
       <c r="D137" t="s">
-        <v>114</v>
+        <v>210</v>
       </c>
       <c r="E137" t="s">
         <v>33</v>
@@ -12111,13 +12255,10 @@
         <v>10</v>
       </c>
       <c r="Y137" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z137" t="s">
-        <v>76</v>
+        <v>211</v>
       </c>
       <c r="AA137" t="s">
-        <v>116</v>
+        <v>212</v>
       </c>
       <c r="AB137" t="s">
         <v>39</v>
@@ -12131,13 +12272,13 @@
     </row>
     <row r="138" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>703</v>
+        <v>152</v>
       </c>
       <c r="C138" t="s">
-        <v>704</v>
+        <v>153</v>
       </c>
       <c r="D138" t="s">
-        <v>705</v>
+        <v>154</v>
       </c>
       <c r="E138" t="s">
         <v>33</v>
@@ -12155,13 +12296,13 @@
         <v>54</v>
       </c>
       <c r="K138" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="L138" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M138" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="N138" t="s">
         <v>33</v>
@@ -12173,24 +12314,993 @@
         <v>38</v>
       </c>
       <c r="Q138">
+        <v>14.99</v>
+      </c>
+      <c r="R138">
+        <v>2.5</v>
+      </c>
+      <c r="Y138" t="s">
+        <v>155</v>
+      </c>
+      <c r="AA138" t="s">
+        <v>156</v>
+      </c>
+      <c r="AB138" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>157</v>
+      </c>
+      <c r="C139" t="s">
+        <v>158</v>
+      </c>
+      <c r="D139" t="s">
+        <v>159</v>
+      </c>
+      <c r="E139" t="s">
+        <v>33</v>
+      </c>
+      <c r="F139" t="s">
+        <v>34</v>
+      </c>
+      <c r="G139" t="s">
+        <v>35</v>
+      </c>
+      <c r="H139" t="s">
+        <v>36</v>
+      </c>
+      <c r="J139" t="s">
+        <v>54</v>
+      </c>
+      <c r="K139" t="s">
+        <v>72</v>
+      </c>
+      <c r="L139" t="s">
+        <v>73</v>
+      </c>
+      <c r="M139" t="s">
+        <v>74</v>
+      </c>
+      <c r="N139" t="s">
+        <v>33</v>
+      </c>
+      <c r="O139">
+        <v>1</v>
+      </c>
+      <c r="P139" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q139">
         <v>11.99</v>
       </c>
-      <c r="R138">
+      <c r="R139">
         <v>2</v>
       </c>
-      <c r="Y138" t="s">
+      <c r="Y139" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA139" t="s">
+        <v>160</v>
+      </c>
+      <c r="AB139" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>161</v>
+      </c>
+      <c r="C140" t="s">
+        <v>162</v>
+      </c>
+      <c r="D140" t="s">
+        <v>163</v>
+      </c>
+      <c r="E140" t="s">
+        <v>53</v>
+      </c>
+      <c r="F140" t="s">
+        <v>34</v>
+      </c>
+      <c r="G140" t="s">
+        <v>35</v>
+      </c>
+      <c r="H140" t="s">
+        <v>36</v>
+      </c>
+      <c r="J140" t="s">
+        <v>54</v>
+      </c>
+      <c r="K140" t="s">
+        <v>40</v>
+      </c>
+      <c r="L140" t="s">
+        <v>41</v>
+      </c>
+      <c r="M140" t="s">
+        <v>42</v>
+      </c>
+      <c r="O140">
+        <v>0</v>
+      </c>
+      <c r="Y140" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA140" t="s">
+        <v>151</v>
+      </c>
+      <c r="AB140" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>164</v>
+      </c>
+      <c r="C141" t="s">
+        <v>165</v>
+      </c>
+      <c r="D141" t="s">
+        <v>166</v>
+      </c>
+      <c r="E141" t="s">
+        <v>33</v>
+      </c>
+      <c r="F141" t="s">
+        <v>34</v>
+      </c>
+      <c r="G141" t="s">
+        <v>35</v>
+      </c>
+      <c r="H141" t="s">
+        <v>36</v>
+      </c>
+      <c r="J141" t="s">
+        <v>54</v>
+      </c>
+      <c r="K141" t="s">
+        <v>48</v>
+      </c>
+      <c r="L141" t="s">
+        <v>49</v>
+      </c>
+      <c r="M141" t="s">
+        <v>50</v>
+      </c>
+      <c r="N141" t="s">
+        <v>33</v>
+      </c>
+      <c r="O141">
+        <v>1</v>
+      </c>
+      <c r="P141" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q141">
+        <v>37.99</v>
+      </c>
+      <c r="R141">
+        <v>6.33</v>
+      </c>
+      <c r="Y141" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA141" t="s">
+        <v>167</v>
+      </c>
+      <c r="AB141" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>168</v>
+      </c>
+      <c r="C142" t="s">
+        <v>169</v>
+      </c>
+      <c r="D142" t="s">
+        <v>170</v>
+      </c>
+      <c r="E142" t="s">
+        <v>33</v>
+      </c>
+      <c r="F142" t="s">
+        <v>34</v>
+      </c>
+      <c r="G142" t="s">
+        <v>35</v>
+      </c>
+      <c r="H142" t="s">
+        <v>36</v>
+      </c>
+      <c r="J142" t="s">
+        <v>54</v>
+      </c>
+      <c r="K142" t="s">
+        <v>72</v>
+      </c>
+      <c r="L142" t="s">
+        <v>73</v>
+      </c>
+      <c r="M142" t="s">
+        <v>74</v>
+      </c>
+      <c r="N142" t="s">
+        <v>33</v>
+      </c>
+      <c r="O142">
+        <v>1</v>
+      </c>
+      <c r="P142" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q142">
+        <v>11.99</v>
+      </c>
+      <c r="R142">
+        <v>2</v>
+      </c>
+      <c r="Y142" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA142" t="s">
+        <v>171</v>
+      </c>
+      <c r="AB142" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>172</v>
+      </c>
+      <c r="C143" t="s">
+        <v>173</v>
+      </c>
+      <c r="D143" t="s">
+        <v>174</v>
+      </c>
+      <c r="E143" t="s">
+        <v>33</v>
+      </c>
+      <c r="F143" t="s">
+        <v>34</v>
+      </c>
+      <c r="G143" t="s">
+        <v>35</v>
+      </c>
+      <c r="H143" t="s">
+        <v>36</v>
+      </c>
+      <c r="J143" t="s">
+        <v>54</v>
+      </c>
+      <c r="K143" t="s">
+        <v>94</v>
+      </c>
+      <c r="L143" t="s">
+        <v>82</v>
+      </c>
+      <c r="M143" t="s">
+        <v>83</v>
+      </c>
+      <c r="N143" t="s">
+        <v>33</v>
+      </c>
+      <c r="O143">
+        <v>1</v>
+      </c>
+      <c r="P143" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q143">
+        <v>14.99</v>
+      </c>
+      <c r="R143">
+        <v>2.5</v>
+      </c>
+      <c r="Y143" t="s">
+        <v>175</v>
+      </c>
+      <c r="AA143" t="s">
+        <v>176</v>
+      </c>
+      <c r="AB143" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>177</v>
+      </c>
+      <c r="C144" t="s">
+        <v>178</v>
+      </c>
+      <c r="D144" t="s">
+        <v>179</v>
+      </c>
+      <c r="E144" t="s">
+        <v>33</v>
+      </c>
+      <c r="F144" t="s">
+        <v>34</v>
+      </c>
+      <c r="G144" t="s">
+        <v>35</v>
+      </c>
+      <c r="H144" t="s">
+        <v>36</v>
+      </c>
+      <c r="J144" t="s">
+        <v>54</v>
+      </c>
+      <c r="K144" t="s">
+        <v>48</v>
+      </c>
+      <c r="L144" t="s">
+        <v>49</v>
+      </c>
+      <c r="M144" t="s">
+        <v>50</v>
+      </c>
+      <c r="N144" t="s">
+        <v>33</v>
+      </c>
+      <c r="O144">
+        <v>1</v>
+      </c>
+      <c r="P144" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q144">
+        <v>37.99</v>
+      </c>
+      <c r="R144">
+        <v>6.33</v>
+      </c>
+      <c r="Y144" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z144" t="s">
+        <v>181</v>
+      </c>
+      <c r="AA144" t="s">
+        <v>182</v>
+      </c>
+      <c r="AB144" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>183</v>
+      </c>
+      <c r="C145" t="s">
+        <v>184</v>
+      </c>
+      <c r="D145" t="s">
+        <v>179</v>
+      </c>
+      <c r="E145" t="s">
+        <v>33</v>
+      </c>
+      <c r="F145" t="s">
+        <v>34</v>
+      </c>
+      <c r="G145" t="s">
+        <v>35</v>
+      </c>
+      <c r="H145" t="s">
+        <v>36</v>
+      </c>
+      <c r="J145" t="s">
+        <v>54</v>
+      </c>
+      <c r="K145" t="s">
+        <v>48</v>
+      </c>
+      <c r="L145" t="s">
+        <v>49</v>
+      </c>
+      <c r="M145" t="s">
+        <v>50</v>
+      </c>
+      <c r="N145" t="s">
+        <v>33</v>
+      </c>
+      <c r="O145">
+        <v>2</v>
+      </c>
+      <c r="P145" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q145">
+        <v>75.98</v>
+      </c>
+      <c r="R145">
+        <v>12.66</v>
+      </c>
+      <c r="Y145" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z145" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA145" t="s">
+        <v>185</v>
+      </c>
+      <c r="AB145" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>133</v>
+      </c>
+      <c r="C146" t="s">
+        <v>134</v>
+      </c>
+      <c r="D146" t="s">
+        <v>186</v>
+      </c>
+      <c r="E146" t="s">
+        <v>33</v>
+      </c>
+      <c r="F146" t="s">
+        <v>34</v>
+      </c>
+      <c r="G146" t="s">
+        <v>35</v>
+      </c>
+      <c r="H146" t="s">
+        <v>36</v>
+      </c>
+      <c r="J146" t="s">
+        <v>54</v>
+      </c>
+      <c r="K146" t="s">
+        <v>72</v>
+      </c>
+      <c r="L146" t="s">
+        <v>73</v>
+      </c>
+      <c r="M146" t="s">
+        <v>74</v>
+      </c>
+      <c r="N146" t="s">
+        <v>33</v>
+      </c>
+      <c r="O146">
+        <v>1</v>
+      </c>
+      <c r="P146" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q146">
+        <v>11.99</v>
+      </c>
+      <c r="R146">
+        <v>2</v>
+      </c>
+      <c r="Y146" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA146" t="s">
+        <v>135</v>
+      </c>
+      <c r="AB146" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>117</v>
+      </c>
+      <c r="C147" t="s">
+        <v>118</v>
+      </c>
+      <c r="D147" t="s">
+        <v>119</v>
+      </c>
+      <c r="E147" t="s">
+        <v>33</v>
+      </c>
+      <c r="F147" t="s">
+        <v>34</v>
+      </c>
+      <c r="G147" t="s">
+        <v>35</v>
+      </c>
+      <c r="H147" t="s">
+        <v>36</v>
+      </c>
+      <c r="J147" t="s">
+        <v>54</v>
+      </c>
+      <c r="K147" t="s">
+        <v>94</v>
+      </c>
+      <c r="L147" t="s">
+        <v>82</v>
+      </c>
+      <c r="M147" t="s">
+        <v>83</v>
+      </c>
+      <c r="N147" t="s">
+        <v>33</v>
+      </c>
+      <c r="O147">
+        <v>1</v>
+      </c>
+      <c r="P147" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q147">
+        <v>14.99</v>
+      </c>
+      <c r="R147">
+        <v>2.5</v>
+      </c>
+      <c r="Y147" t="s">
+        <v>120</v>
+      </c>
+      <c r="Z147" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA147" t="s">
+        <v>122</v>
+      </c>
+      <c r="AB147" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>123</v>
+      </c>
+      <c r="C148" t="s">
+        <v>124</v>
+      </c>
+      <c r="D148" t="s">
+        <v>125</v>
+      </c>
+      <c r="E148" t="s">
+        <v>33</v>
+      </c>
+      <c r="F148" t="s">
+        <v>34</v>
+      </c>
+      <c r="G148" t="s">
+        <v>35</v>
+      </c>
+      <c r="H148" t="s">
+        <v>36</v>
+      </c>
+      <c r="J148" t="s">
+        <v>54</v>
+      </c>
+      <c r="K148" t="s">
+        <v>40</v>
+      </c>
+      <c r="L148" t="s">
+        <v>41</v>
+      </c>
+      <c r="M148" t="s">
+        <v>42</v>
+      </c>
+      <c r="N148" t="s">
+        <v>33</v>
+      </c>
+      <c r="O148">
+        <v>1</v>
+      </c>
+      <c r="P148" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q148">
+        <v>59.99</v>
+      </c>
+      <c r="R148">
+        <v>10</v>
+      </c>
+      <c r="Y148" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z148" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA148" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB148" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>129</v>
+      </c>
+      <c r="C149" t="s">
+        <v>130</v>
+      </c>
+      <c r="D149" t="s">
+        <v>131</v>
+      </c>
+      <c r="E149" t="s">
+        <v>33</v>
+      </c>
+      <c r="F149" t="s">
+        <v>34</v>
+      </c>
+      <c r="G149" t="s">
+        <v>35</v>
+      </c>
+      <c r="H149" t="s">
+        <v>36</v>
+      </c>
+      <c r="J149" t="s">
+        <v>54</v>
+      </c>
+      <c r="K149" t="s">
+        <v>43</v>
+      </c>
+      <c r="L149" t="s">
+        <v>44</v>
+      </c>
+      <c r="M149" t="s">
+        <v>45</v>
+      </c>
+      <c r="N149" t="s">
+        <v>33</v>
+      </c>
+      <c r="O149">
+        <v>1</v>
+      </c>
+      <c r="P149" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q149">
+        <v>38.49</v>
+      </c>
+      <c r="R149">
+        <v>6.42</v>
+      </c>
+      <c r="Y149" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA149" t="s">
+        <v>132</v>
+      </c>
+      <c r="AB149" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>105</v>
+      </c>
+      <c r="C150" t="s">
+        <v>106</v>
+      </c>
+      <c r="D150" t="s">
+        <v>136</v>
+      </c>
+      <c r="E150" t="s">
+        <v>53</v>
+      </c>
+      <c r="F150" t="s">
+        <v>34</v>
+      </c>
+      <c r="G150" t="s">
+        <v>35</v>
+      </c>
+      <c r="H150" t="s">
+        <v>36</v>
+      </c>
+      <c r="J150" t="s">
+        <v>54</v>
+      </c>
+      <c r="K150" t="s">
+        <v>94</v>
+      </c>
+      <c r="L150" t="s">
+        <v>82</v>
+      </c>
+      <c r="M150" t="s">
+        <v>83</v>
+      </c>
+      <c r="O150">
+        <v>0</v>
+      </c>
+      <c r="Y150" t="s">
+        <v>103</v>
+      </c>
+      <c r="AA150" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB150" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>107</v>
+      </c>
+      <c r="C151" t="s">
+        <v>108</v>
+      </c>
+      <c r="D151" t="s">
+        <v>137</v>
+      </c>
+      <c r="E151" t="s">
+        <v>33</v>
+      </c>
+      <c r="F151" t="s">
+        <v>34</v>
+      </c>
+      <c r="G151" t="s">
+        <v>35</v>
+      </c>
+      <c r="H151" t="s">
+        <v>36</v>
+      </c>
+      <c r="J151" t="s">
+        <v>54</v>
+      </c>
+      <c r="K151" t="s">
+        <v>48</v>
+      </c>
+      <c r="L151" t="s">
+        <v>49</v>
+      </c>
+      <c r="M151" t="s">
+        <v>50</v>
+      </c>
+      <c r="N151" t="s">
+        <v>33</v>
+      </c>
+      <c r="O151">
+        <v>1</v>
+      </c>
+      <c r="P151" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q151">
+        <v>37.99</v>
+      </c>
+      <c r="R151">
+        <v>6.33</v>
+      </c>
+      <c r="Y151" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z151" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA151" t="s">
+        <v>111</v>
+      </c>
+      <c r="AB151" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>112</v>
+      </c>
+      <c r="C152" t="s">
+        <v>113</v>
+      </c>
+      <c r="D152" t="s">
+        <v>114</v>
+      </c>
+      <c r="E152" t="s">
+        <v>33</v>
+      </c>
+      <c r="F152" t="s">
+        <v>34</v>
+      </c>
+      <c r="G152" t="s">
+        <v>35</v>
+      </c>
+      <c r="H152" t="s">
+        <v>36</v>
+      </c>
+      <c r="J152" t="s">
+        <v>37</v>
+      </c>
+      <c r="K152" t="s">
+        <v>40</v>
+      </c>
+      <c r="L152" t="s">
+        <v>41</v>
+      </c>
+      <c r="M152" t="s">
+        <v>42</v>
+      </c>
+      <c r="N152" t="s">
+        <v>33</v>
+      </c>
+      <c r="O152">
+        <v>1</v>
+      </c>
+      <c r="P152" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q152">
+        <v>59.99</v>
+      </c>
+      <c r="R152">
+        <v>10</v>
+      </c>
+      <c r="Y152" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z152" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA152" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB152" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>703</v>
+      </c>
+      <c r="C153" t="s">
+        <v>704</v>
+      </c>
+      <c r="D153" t="s">
+        <v>705</v>
+      </c>
+      <c r="E153" t="s">
+        <v>33</v>
+      </c>
+      <c r="F153" t="s">
+        <v>34</v>
+      </c>
+      <c r="G153" t="s">
+        <v>35</v>
+      </c>
+      <c r="H153" t="s">
+        <v>36</v>
+      </c>
+      <c r="J153" t="s">
+        <v>54</v>
+      </c>
+      <c r="K153" t="s">
+        <v>72</v>
+      </c>
+      <c r="L153" t="s">
+        <v>73</v>
+      </c>
+      <c r="M153" t="s">
+        <v>74</v>
+      </c>
+      <c r="N153" t="s">
+        <v>33</v>
+      </c>
+      <c r="O153">
+        <v>1</v>
+      </c>
+      <c r="P153" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q153">
+        <v>11.99</v>
+      </c>
+      <c r="R153">
+        <v>2</v>
+      </c>
+      <c r="Y153" t="s">
         <v>706</v>
       </c>
-      <c r="AA138" t="s">
+      <c r="AA153" t="s">
         <v>707</v>
       </c>
-      <c r="AB138" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD138" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG138" t="b">
+      <c r="AB153" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Raw Sales Data/Amazon.xlsx
+++ b/Raw Sales Data/Amazon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2491" uniqueCount="819">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2556" uniqueCount="837">
   <si>
     <t>amazon-order-id</t>
   </si>
@@ -2476,6 +2476,60 @@
   </si>
   <si>
     <t>2026-03-03T11:24:47+00:00</t>
+  </si>
+  <si>
+    <t>203-6517611-2390711</t>
+  </si>
+  <si>
+    <t>2026-03-05T20:08:18+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-05T20:38:45+00:00</t>
+  </si>
+  <si>
+    <t>204-4155230-8837914</t>
+  </si>
+  <si>
+    <t>2026-03-05T19:01:06+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-05T19:30:21+00:00</t>
+  </si>
+  <si>
+    <t>BLACKBURN</t>
+  </si>
+  <si>
+    <t>BB2 4SZ</t>
+  </si>
+  <si>
+    <t>203-0140415-0828308</t>
+  </si>
+  <si>
+    <t>2026-03-05T15:37:23+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-05T15:55:42+00:00</t>
+  </si>
+  <si>
+    <t>ARMAGH</t>
+  </si>
+  <si>
+    <t>BT61 8NB</t>
+  </si>
+  <si>
+    <t>206-9599271-3563502</t>
+  </si>
+  <si>
+    <t>2026-03-05T10:32:27+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-05T13:31:55+00:00</t>
+  </si>
+  <si>
+    <t>BRISTOL</t>
+  </si>
+  <si>
+    <t>BS13 9PB</t>
   </si>
 </sst>
 </file>
@@ -3282,7 +3336,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG153"/>
+  <dimension ref="A1:AG157"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
@@ -3393,16 +3447,16 @@
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>780</v>
+        <v>819</v>
       </c>
       <c r="C2" t="s">
-        <v>781</v>
+        <v>820</v>
       </c>
       <c r="D2" t="s">
-        <v>782</v>
+        <v>821</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F2" t="s">
         <v>34</v>
@@ -3417,16 +3471,16 @@
         <v>54</v>
       </c>
       <c r="K2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L2" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N2" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O2">
         <v>1</v>
@@ -3435,16 +3489,19 @@
         <v>38</v>
       </c>
       <c r="Q2">
-        <v>65.989999999999995</v>
+        <v>40.99</v>
       </c>
       <c r="R2">
-        <v>11</v>
+        <v>6.83</v>
       </c>
       <c r="Y2" t="s">
-        <v>783</v>
+        <v>618</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>619</v>
       </c>
       <c r="AA2" t="s">
-        <v>784</v>
+        <v>620</v>
       </c>
       <c r="AB2" t="s">
         <v>39</v>
@@ -3458,16 +3515,16 @@
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>785</v>
+        <v>822</v>
       </c>
       <c r="C3" t="s">
-        <v>786</v>
+        <v>823</v>
       </c>
       <c r="D3" t="s">
-        <v>787</v>
+        <v>824</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F3" t="s">
         <v>34</v>
@@ -3482,16 +3539,16 @@
         <v>54</v>
       </c>
       <c r="K3" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L3" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M3" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="N3" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O3">
         <v>1</v>
@@ -3500,16 +3557,16 @@
         <v>38</v>
       </c>
       <c r="Q3">
-        <v>40.99</v>
+        <v>14.99</v>
       </c>
       <c r="R3">
-        <v>6.83</v>
+        <v>2.5</v>
       </c>
       <c r="Y3" t="s">
-        <v>788</v>
+        <v>825</v>
       </c>
       <c r="AA3" t="s">
-        <v>789</v>
+        <v>826</v>
       </c>
       <c r="AB3" t="s">
         <v>39</v>
@@ -3523,16 +3580,16 @@
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>790</v>
+        <v>827</v>
       </c>
       <c r="C4" t="s">
-        <v>791</v>
+        <v>828</v>
       </c>
       <c r="D4" t="s">
-        <v>792</v>
+        <v>829</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F4" t="s">
         <v>34</v>
@@ -3556,7 +3613,7 @@
         <v>42</v>
       </c>
       <c r="N4" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O4">
         <v>1</v>
@@ -3567,14 +3624,14 @@
       <c r="Q4">
         <v>65.989999999999995</v>
       </c>
-      <c r="R4">
-        <v>11</v>
+      <c r="S4">
+        <v>6.99</v>
       </c>
       <c r="Y4" t="s">
-        <v>793</v>
+        <v>830</v>
       </c>
       <c r="AA4" t="s">
-        <v>794</v>
+        <v>831</v>
       </c>
       <c r="AB4" t="s">
         <v>39</v>
@@ -3588,13 +3645,13 @@
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>795</v>
+        <v>832</v>
       </c>
       <c r="C5" t="s">
-        <v>796</v>
+        <v>833</v>
       </c>
       <c r="D5" t="s">
-        <v>797</v>
+        <v>834</v>
       </c>
       <c r="E5" t="s">
         <v>33</v>
@@ -3612,13 +3669,13 @@
         <v>54</v>
       </c>
       <c r="K5" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L5" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M5" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N5" t="s">
         <v>33</v>
@@ -3630,16 +3687,16 @@
         <v>38</v>
       </c>
       <c r="Q5">
-        <v>14.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R5">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="Y5" t="s">
-        <v>798</v>
+        <v>835</v>
       </c>
       <c r="AA5" t="s">
-        <v>799</v>
+        <v>836</v>
       </c>
       <c r="AB5" t="s">
         <v>39</v>
@@ -3653,13 +3710,13 @@
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>800</v>
+        <v>780</v>
       </c>
       <c r="C6" t="s">
-        <v>801</v>
+        <v>781</v>
       </c>
       <c r="D6" t="s">
-        <v>802</v>
+        <v>782</v>
       </c>
       <c r="E6" t="s">
         <v>33</v>
@@ -3677,13 +3734,13 @@
         <v>54</v>
       </c>
       <c r="K6" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L6" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M6" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N6" t="s">
         <v>33</v>
@@ -3695,16 +3752,16 @@
         <v>38</v>
       </c>
       <c r="Q6">
-        <v>14.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R6">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="Y6" t="s">
-        <v>68</v>
+        <v>783</v>
       </c>
       <c r="AA6" t="s">
-        <v>803</v>
+        <v>784</v>
       </c>
       <c r="AB6" t="s">
         <v>39</v>
@@ -3718,13 +3775,13 @@
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>804</v>
+        <v>785</v>
       </c>
       <c r="C7" t="s">
-        <v>805</v>
+        <v>786</v>
       </c>
       <c r="D7" t="s">
-        <v>802</v>
+        <v>787</v>
       </c>
       <c r="E7" t="s">
         <v>33</v>
@@ -3742,13 +3799,13 @@
         <v>54</v>
       </c>
       <c r="K7" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L7" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M7" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N7" t="s">
         <v>33</v>
@@ -3760,16 +3817,16 @@
         <v>38</v>
       </c>
       <c r="Q7">
-        <v>11.99</v>
+        <v>40.99</v>
       </c>
       <c r="R7">
-        <v>2</v>
+        <v>6.83</v>
       </c>
       <c r="Y7" t="s">
-        <v>806</v>
+        <v>788</v>
       </c>
       <c r="AA7" t="s">
-        <v>807</v>
+        <v>789</v>
       </c>
       <c r="AB7" t="s">
         <v>39</v>
@@ -3783,13 +3840,13 @@
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>808</v>
+        <v>790</v>
       </c>
       <c r="C8" t="s">
-        <v>809</v>
+        <v>791</v>
       </c>
       <c r="D8" t="s">
-        <v>810</v>
+        <v>792</v>
       </c>
       <c r="E8" t="s">
         <v>33</v>
@@ -3807,13 +3864,13 @@
         <v>54</v>
       </c>
       <c r="K8" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L8" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M8" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N8" t="s">
         <v>33</v>
@@ -3825,16 +3882,16 @@
         <v>38</v>
       </c>
       <c r="Q8">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R8">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y8" t="s">
-        <v>66</v>
+        <v>793</v>
       </c>
       <c r="AA8" t="s">
-        <v>811</v>
+        <v>794</v>
       </c>
       <c r="AB8" t="s">
         <v>39</v>
@@ -3848,13 +3905,13 @@
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>812</v>
+        <v>795</v>
       </c>
       <c r="C9" t="s">
-        <v>813</v>
+        <v>796</v>
       </c>
       <c r="D9" t="s">
-        <v>814</v>
+        <v>797</v>
       </c>
       <c r="E9" t="s">
         <v>33</v>
@@ -3872,13 +3929,13 @@
         <v>54</v>
       </c>
       <c r="K9" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="L9" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="M9" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="N9" t="s">
         <v>33</v>
@@ -3890,16 +3947,16 @@
         <v>38</v>
       </c>
       <c r="Q9">
-        <v>40.99</v>
+        <v>14.99</v>
       </c>
       <c r="R9">
-        <v>6.83</v>
+        <v>2.5</v>
       </c>
       <c r="Y9" t="s">
-        <v>815</v>
+        <v>798</v>
       </c>
       <c r="AA9" t="s">
-        <v>816</v>
+        <v>799</v>
       </c>
       <c r="AB9" t="s">
         <v>39</v>
@@ -3913,13 +3970,13 @@
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>745</v>
+        <v>800</v>
       </c>
       <c r="C10" t="s">
-        <v>746</v>
+        <v>801</v>
       </c>
       <c r="D10" t="s">
-        <v>817</v>
+        <v>802</v>
       </c>
       <c r="E10" t="s">
         <v>33</v>
@@ -3955,16 +4012,16 @@
         <v>38</v>
       </c>
       <c r="Q10">
-        <v>11.99</v>
+        <v>14.99</v>
       </c>
       <c r="R10">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Y10" t="s">
-        <v>748</v>
+        <v>68</v>
       </c>
       <c r="AA10" t="s">
-        <v>749</v>
+        <v>803</v>
       </c>
       <c r="AB10" t="s">
         <v>39</v>
@@ -3978,13 +4035,13 @@
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>750</v>
+        <v>804</v>
       </c>
       <c r="C11" t="s">
-        <v>751</v>
+        <v>805</v>
       </c>
       <c r="D11" t="s">
-        <v>752</v>
+        <v>802</v>
       </c>
       <c r="E11" t="s">
         <v>33</v>
@@ -4002,13 +4059,13 @@
         <v>54</v>
       </c>
       <c r="K11" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L11" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M11" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N11" t="s">
         <v>33</v>
@@ -4020,16 +4077,16 @@
         <v>38</v>
       </c>
       <c r="Q11">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R11">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="s">
-        <v>753</v>
+        <v>806</v>
       </c>
       <c r="AA11" t="s">
-        <v>754</v>
+        <v>807</v>
       </c>
       <c r="AB11" t="s">
         <v>39</v>
@@ -4043,13 +4100,13 @@
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>755</v>
+        <v>808</v>
       </c>
       <c r="C12" t="s">
-        <v>756</v>
+        <v>809</v>
       </c>
       <c r="D12" t="s">
-        <v>818</v>
+        <v>810</v>
       </c>
       <c r="E12" t="s">
         <v>33</v>
@@ -4067,13 +4124,13 @@
         <v>54</v>
       </c>
       <c r="K12" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L12" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M12" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N12" t="s">
         <v>33</v>
@@ -4085,25 +4142,16 @@
         <v>38</v>
       </c>
       <c r="Q12">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R12">
-        <v>11</v>
-      </c>
-      <c r="S12">
-        <v>6.99</v>
-      </c>
-      <c r="T12">
-        <v>1.17</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="s">
-        <v>758</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>759</v>
+        <v>66</v>
       </c>
       <c r="AA12" t="s">
-        <v>760</v>
+        <v>811</v>
       </c>
       <c r="AB12" t="s">
         <v>39</v>
@@ -4117,13 +4165,13 @@
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>761</v>
+        <v>812</v>
       </c>
       <c r="C13" t="s">
-        <v>762</v>
+        <v>813</v>
       </c>
       <c r="D13" t="s">
-        <v>763</v>
+        <v>814</v>
       </c>
       <c r="E13" t="s">
         <v>33</v>
@@ -4141,13 +4189,13 @@
         <v>54</v>
       </c>
       <c r="K13" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="L13" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="M13" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="N13" t="s">
         <v>33</v>
@@ -4159,19 +4207,16 @@
         <v>38</v>
       </c>
       <c r="Q13">
-        <v>11.99</v>
+        <v>40.99</v>
       </c>
       <c r="R13">
-        <v>2</v>
+        <v>6.83</v>
       </c>
       <c r="Y13" t="s">
-        <v>764</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>279</v>
+        <v>815</v>
       </c>
       <c r="AA13" t="s">
-        <v>765</v>
+        <v>816</v>
       </c>
       <c r="AB13" t="s">
         <v>39</v>
@@ -4185,13 +4230,13 @@
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="C14" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="D14" t="s">
-        <v>768</v>
+        <v>817</v>
       </c>
       <c r="E14" t="s">
         <v>33</v>
@@ -4233,13 +4278,10 @@
         <v>2</v>
       </c>
       <c r="Y14" t="s">
-        <v>91</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>121</v>
+        <v>748</v>
       </c>
       <c r="AA14" t="s">
-        <v>769</v>
+        <v>749</v>
       </c>
       <c r="AB14" t="s">
         <v>39</v>
@@ -4253,13 +4295,13 @@
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>770</v>
+        <v>750</v>
       </c>
       <c r="C15" t="s">
-        <v>771</v>
+        <v>751</v>
       </c>
       <c r="D15" t="s">
-        <v>772</v>
+        <v>752</v>
       </c>
       <c r="E15" t="s">
         <v>33</v>
@@ -4301,13 +4343,10 @@
         <v>11</v>
       </c>
       <c r="Y15" t="s">
-        <v>773</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>64</v>
+        <v>753</v>
       </c>
       <c r="AA15" t="s">
-        <v>774</v>
+        <v>754</v>
       </c>
       <c r="AB15" t="s">
         <v>39</v>
@@ -4321,13 +4360,13 @@
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>775</v>
+        <v>755</v>
       </c>
       <c r="C16" t="s">
-        <v>776</v>
+        <v>756</v>
       </c>
       <c r="D16" t="s">
-        <v>777</v>
+        <v>818</v>
       </c>
       <c r="E16" t="s">
         <v>33</v>
@@ -4368,11 +4407,20 @@
       <c r="R16">
         <v>11</v>
       </c>
+      <c r="S16">
+        <v>6.99</v>
+      </c>
+      <c r="T16">
+        <v>1.17</v>
+      </c>
       <c r="Y16" t="s">
-        <v>778</v>
+        <v>758</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>759</v>
       </c>
       <c r="AA16" t="s">
-        <v>779</v>
+        <v>760</v>
       </c>
       <c r="AB16" t="s">
         <v>39</v>
@@ -4386,16 +4434,16 @@
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>745</v>
+        <v>761</v>
       </c>
       <c r="C17" t="s">
-        <v>746</v>
+        <v>762</v>
       </c>
       <c r="D17" t="s">
-        <v>747</v>
+        <v>763</v>
       </c>
       <c r="E17" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F17" t="s">
         <v>34</v>
@@ -4419,7 +4467,7 @@
         <v>74</v>
       </c>
       <c r="N17" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O17">
         <v>1</v>
@@ -4434,10 +4482,13 @@
         <v>2</v>
       </c>
       <c r="Y17" t="s">
-        <v>748</v>
+        <v>764</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>279</v>
       </c>
       <c r="AA17" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="AB17" t="s">
         <v>39</v>
@@ -4451,13 +4502,13 @@
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>750</v>
+        <v>766</v>
       </c>
       <c r="C18" t="s">
-        <v>751</v>
+        <v>767</v>
       </c>
       <c r="D18" t="s">
-        <v>752</v>
+        <v>768</v>
       </c>
       <c r="E18" t="s">
         <v>33</v>
@@ -4475,13 +4526,13 @@
         <v>54</v>
       </c>
       <c r="K18" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L18" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M18" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N18" t="s">
         <v>33</v>
@@ -4493,16 +4544,19 @@
         <v>38</v>
       </c>
       <c r="Q18">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R18">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="s">
-        <v>753</v>
+        <v>91</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>121</v>
       </c>
       <c r="AA18" t="s">
-        <v>754</v>
+        <v>769</v>
       </c>
       <c r="AB18" t="s">
         <v>39</v>
@@ -4516,16 +4570,16 @@
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>755</v>
+        <v>770</v>
       </c>
       <c r="C19" t="s">
-        <v>756</v>
+        <v>771</v>
       </c>
       <c r="D19" t="s">
-        <v>757</v>
+        <v>772</v>
       </c>
       <c r="E19" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F19" t="s">
         <v>34</v>
@@ -4549,7 +4603,7 @@
         <v>42</v>
       </c>
       <c r="N19" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O19">
         <v>1</v>
@@ -4563,20 +4617,14 @@
       <c r="R19">
         <v>11</v>
       </c>
-      <c r="S19">
-        <v>6.99</v>
-      </c>
-      <c r="T19">
-        <v>1.17</v>
-      </c>
       <c r="Y19" t="s">
-        <v>758</v>
+        <v>773</v>
       </c>
       <c r="Z19" t="s">
-        <v>759</v>
+        <v>64</v>
       </c>
       <c r="AA19" t="s">
-        <v>760</v>
+        <v>774</v>
       </c>
       <c r="AB19" t="s">
         <v>39</v>
@@ -4590,13 +4638,13 @@
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>761</v>
+        <v>775</v>
       </c>
       <c r="C20" t="s">
-        <v>762</v>
+        <v>776</v>
       </c>
       <c r="D20" t="s">
-        <v>763</v>
+        <v>777</v>
       </c>
       <c r="E20" t="s">
         <v>33</v>
@@ -4614,13 +4662,13 @@
         <v>54</v>
       </c>
       <c r="K20" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L20" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M20" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N20" t="s">
         <v>33</v>
@@ -4632,19 +4680,16 @@
         <v>38</v>
       </c>
       <c r="Q20">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R20">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y20" t="s">
-        <v>764</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>279</v>
+        <v>778</v>
       </c>
       <c r="AA20" t="s">
-        <v>765</v>
+        <v>779</v>
       </c>
       <c r="AB20" t="s">
         <v>39</v>
@@ -4658,16 +4703,16 @@
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="C21" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="D21" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="E21" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F21" t="s">
         <v>34</v>
@@ -4691,7 +4736,7 @@
         <v>74</v>
       </c>
       <c r="N21" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O21">
         <v>1</v>
@@ -4706,13 +4751,10 @@
         <v>2</v>
       </c>
       <c r="Y21" t="s">
-        <v>91</v>
-      </c>
-      <c r="Z21" t="s">
-        <v>121</v>
+        <v>748</v>
       </c>
       <c r="AA21" t="s">
-        <v>769</v>
+        <v>749</v>
       </c>
       <c r="AB21" t="s">
         <v>39</v>
@@ -4726,13 +4768,13 @@
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>770</v>
+        <v>750</v>
       </c>
       <c r="C22" t="s">
-        <v>771</v>
+        <v>751</v>
       </c>
       <c r="D22" t="s">
-        <v>772</v>
+        <v>752</v>
       </c>
       <c r="E22" t="s">
         <v>33</v>
@@ -4774,13 +4816,10 @@
         <v>11</v>
       </c>
       <c r="Y22" t="s">
-        <v>773</v>
-      </c>
-      <c r="Z22" t="s">
-        <v>64</v>
+        <v>753</v>
       </c>
       <c r="AA22" t="s">
-        <v>774</v>
+        <v>754</v>
       </c>
       <c r="AB22" t="s">
         <v>39</v>
@@ -4794,16 +4833,16 @@
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>775</v>
+        <v>755</v>
       </c>
       <c r="C23" t="s">
-        <v>776</v>
+        <v>756</v>
       </c>
       <c r="D23" t="s">
-        <v>777</v>
+        <v>757</v>
       </c>
       <c r="E23" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F23" t="s">
         <v>34</v>
@@ -4827,7 +4866,7 @@
         <v>42</v>
       </c>
       <c r="N23" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O23">
         <v>1</v>
@@ -4841,11 +4880,20 @@
       <c r="R23">
         <v>11</v>
       </c>
+      <c r="S23">
+        <v>6.99</v>
+      </c>
+      <c r="T23">
+        <v>1.17</v>
+      </c>
       <c r="Y23" t="s">
-        <v>778</v>
+        <v>758</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>759</v>
       </c>
       <c r="AA23" t="s">
-        <v>779</v>
+        <v>760</v>
       </c>
       <c r="AB23" t="s">
         <v>39</v>
@@ -4859,16 +4907,16 @@
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>714</v>
+        <v>761</v>
       </c>
       <c r="C24" t="s">
-        <v>715</v>
+        <v>762</v>
       </c>
       <c r="D24" t="s">
-        <v>716</v>
+        <v>763</v>
       </c>
       <c r="E24" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F24" t="s">
         <v>34</v>
@@ -4892,7 +4940,7 @@
         <v>74</v>
       </c>
       <c r="N24" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O24">
         <v>1</v>
@@ -4907,13 +4955,13 @@
         <v>2</v>
       </c>
       <c r="Y24" t="s">
-        <v>717</v>
+        <v>764</v>
       </c>
       <c r="Z24" t="s">
-        <v>51</v>
+        <v>279</v>
       </c>
       <c r="AA24" t="s">
-        <v>718</v>
+        <v>765</v>
       </c>
       <c r="AB24" t="s">
         <v>39</v>
@@ -4927,13 +4975,13 @@
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>719</v>
+        <v>766</v>
       </c>
       <c r="C25" t="s">
-        <v>720</v>
+        <v>767</v>
       </c>
       <c r="D25" t="s">
-        <v>721</v>
+        <v>768</v>
       </c>
       <c r="E25" t="s">
         <v>33</v>
@@ -4951,13 +4999,13 @@
         <v>54</v>
       </c>
       <c r="K25" t="s">
-        <v>722</v>
+        <v>72</v>
       </c>
       <c r="L25" t="s">
-        <v>723</v>
+        <v>73</v>
       </c>
       <c r="M25" t="s">
-        <v>724</v>
+        <v>74</v>
       </c>
       <c r="N25" t="s">
         <v>33</v>
@@ -4969,19 +5017,19 @@
         <v>38</v>
       </c>
       <c r="Q25">
-        <v>12.99</v>
+        <v>11.99</v>
       </c>
       <c r="R25">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="Y25" t="s">
-        <v>725</v>
+        <v>91</v>
       </c>
       <c r="Z25" t="s">
-        <v>726</v>
+        <v>121</v>
       </c>
       <c r="AA25" t="s">
-        <v>727</v>
+        <v>769</v>
       </c>
       <c r="AB25" t="s">
         <v>39</v>
@@ -4995,13 +5043,13 @@
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>728</v>
+        <v>770</v>
       </c>
       <c r="C26" t="s">
-        <v>729</v>
+        <v>771</v>
       </c>
       <c r="D26" t="s">
-        <v>730</v>
+        <v>772</v>
       </c>
       <c r="E26" t="s">
         <v>33</v>
@@ -5019,13 +5067,13 @@
         <v>54</v>
       </c>
       <c r="K26" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L26" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M26" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N26" t="s">
         <v>33</v>
@@ -5037,16 +5085,19 @@
         <v>38</v>
       </c>
       <c r="Q26">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R26">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y26" t="s">
-        <v>731</v>
+        <v>773</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>64</v>
       </c>
       <c r="AA26" t="s">
-        <v>732</v>
+        <v>774</v>
       </c>
       <c r="AB26" t="s">
         <v>39</v>
@@ -5060,13 +5111,13 @@
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>733</v>
+        <v>775</v>
       </c>
       <c r="C27" t="s">
-        <v>734</v>
+        <v>776</v>
       </c>
       <c r="D27" t="s">
-        <v>735</v>
+        <v>777</v>
       </c>
       <c r="E27" t="s">
         <v>33</v>
@@ -5084,13 +5135,13 @@
         <v>54</v>
       </c>
       <c r="K27" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L27" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M27" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N27" t="s">
         <v>33</v>
@@ -5102,16 +5153,16 @@
         <v>38</v>
       </c>
       <c r="Q27">
-        <v>40.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R27">
-        <v>6.83</v>
+        <v>11</v>
       </c>
       <c r="Y27" t="s">
-        <v>736</v>
+        <v>778</v>
       </c>
       <c r="AA27" t="s">
-        <v>737</v>
+        <v>779</v>
       </c>
       <c r="AB27" t="s">
         <v>39</v>
@@ -5125,16 +5176,16 @@
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>738</v>
+        <v>714</v>
       </c>
       <c r="C28" t="s">
-        <v>739</v>
+        <v>715</v>
       </c>
       <c r="D28" t="s">
-        <v>740</v>
+        <v>716</v>
       </c>
       <c r="E28" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F28" t="s">
         <v>34</v>
@@ -5149,16 +5200,16 @@
         <v>54</v>
       </c>
       <c r="K28" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L28" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M28" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="N28" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O28">
         <v>1</v>
@@ -5167,16 +5218,19 @@
         <v>38</v>
       </c>
       <c r="Q28">
-        <v>40.99</v>
+        <v>11.99</v>
       </c>
       <c r="R28">
-        <v>6.83</v>
+        <v>2</v>
       </c>
       <c r="Y28" t="s">
-        <v>741</v>
+        <v>717</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>51</v>
       </c>
       <c r="AA28" t="s">
-        <v>742</v>
+        <v>718</v>
       </c>
       <c r="AB28" t="s">
         <v>39</v>
@@ -5190,13 +5244,13 @@
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>708</v>
+        <v>719</v>
       </c>
       <c r="C29" t="s">
-        <v>709</v>
+        <v>720</v>
       </c>
       <c r="D29" t="s">
-        <v>743</v>
+        <v>721</v>
       </c>
       <c r="E29" t="s">
         <v>33</v>
@@ -5214,13 +5268,13 @@
         <v>54</v>
       </c>
       <c r="K29" t="s">
-        <v>40</v>
+        <v>722</v>
       </c>
       <c r="L29" t="s">
-        <v>41</v>
+        <v>723</v>
       </c>
       <c r="M29" t="s">
-        <v>42</v>
+        <v>724</v>
       </c>
       <c r="N29" t="s">
         <v>33</v>
@@ -5232,19 +5286,19 @@
         <v>38</v>
       </c>
       <c r="Q29">
-        <v>65.989999999999995</v>
+        <v>12.99</v>
       </c>
       <c r="R29">
-        <v>11</v>
+        <v>2.17</v>
       </c>
       <c r="Y29" t="s">
-        <v>711</v>
+        <v>725</v>
       </c>
       <c r="Z29" t="s">
-        <v>712</v>
+        <v>726</v>
       </c>
       <c r="AA29" t="s">
-        <v>713</v>
+        <v>727</v>
       </c>
       <c r="AB29" t="s">
         <v>39</v>
@@ -5258,13 +5312,13 @@
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>643</v>
+        <v>728</v>
       </c>
       <c r="C30" t="s">
-        <v>644</v>
+        <v>729</v>
       </c>
       <c r="D30" t="s">
-        <v>744</v>
+        <v>730</v>
       </c>
       <c r="E30" t="s">
         <v>33</v>
@@ -5282,13 +5336,13 @@
         <v>54</v>
       </c>
       <c r="K30" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L30" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M30" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="N30" t="s">
         <v>33</v>
@@ -5300,16 +5354,16 @@
         <v>38</v>
       </c>
       <c r="Q30">
-        <v>14.99</v>
+        <v>11.99</v>
       </c>
       <c r="R30">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Y30" t="s">
-        <v>646</v>
+        <v>731</v>
       </c>
       <c r="AA30" t="s">
-        <v>647</v>
+        <v>732</v>
       </c>
       <c r="AB30" t="s">
         <v>39</v>
@@ -5323,16 +5377,16 @@
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>708</v>
+        <v>733</v>
       </c>
       <c r="C31" t="s">
-        <v>709</v>
+        <v>734</v>
       </c>
       <c r="D31" t="s">
-        <v>710</v>
+        <v>735</v>
       </c>
       <c r="E31" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F31" t="s">
         <v>34</v>
@@ -5347,16 +5401,16 @@
         <v>54</v>
       </c>
       <c r="K31" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L31" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M31" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N31" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O31">
         <v>1</v>
@@ -5365,19 +5419,16 @@
         <v>38</v>
       </c>
       <c r="Q31">
-        <v>65.989999999999995</v>
+        <v>40.99</v>
       </c>
       <c r="R31">
-        <v>11</v>
+        <v>6.83</v>
       </c>
       <c r="Y31" t="s">
-        <v>711</v>
-      </c>
-      <c r="Z31" t="s">
-        <v>712</v>
+        <v>736</v>
       </c>
       <c r="AA31" t="s">
-        <v>713</v>
+        <v>737</v>
       </c>
       <c r="AB31" t="s">
         <v>39</v>
@@ -5391,22 +5442,22 @@
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>138</v>
+        <v>738</v>
       </c>
       <c r="C32" t="s">
-        <v>139</v>
+        <v>739</v>
       </c>
       <c r="D32" t="s">
-        <v>187</v>
+        <v>740</v>
       </c>
       <c r="E32" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F32" t="s">
         <v>34</v>
       </c>
       <c r="G32" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="H32" t="s">
         <v>36</v>
@@ -5415,25 +5466,37 @@
         <v>54</v>
       </c>
       <c r="K32" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="L32" t="s">
-        <v>142</v>
+        <v>49</v>
       </c>
       <c r="M32" t="s">
-        <v>143</v>
+        <v>50</v>
+      </c>
+      <c r="N32" t="s">
+        <v>33</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P32" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q32">
+        <v>40.99</v>
+      </c>
+      <c r="R32">
+        <v>6.83</v>
       </c>
       <c r="Y32" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA32">
-        <v>80100</v>
+        <v>741</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>742</v>
       </c>
       <c r="AB32" t="s">
-        <v>145</v>
+        <v>39</v>
       </c>
       <c r="AD32" t="b">
         <v>0</v>
@@ -5444,22 +5507,22 @@
     </row>
     <row r="33" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>146</v>
+        <v>708</v>
       </c>
       <c r="C33" t="s">
-        <v>147</v>
+        <v>709</v>
       </c>
       <c r="D33" t="s">
-        <v>148</v>
+        <v>743</v>
       </c>
       <c r="E33" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F33" t="s">
         <v>34</v>
       </c>
       <c r="G33" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="H33" t="s">
         <v>36</v>
@@ -5468,25 +5531,40 @@
         <v>54</v>
       </c>
       <c r="K33" t="s">
-        <v>141</v>
+        <v>40</v>
       </c>
       <c r="L33" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="M33" t="s">
-        <v>143</v>
+        <v>42</v>
+      </c>
+      <c r="N33" t="s">
+        <v>33</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P33" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q33">
+        <v>65.989999999999995</v>
+      </c>
+      <c r="R33">
+        <v>11</v>
       </c>
       <c r="Y33" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA33">
-        <v>80100</v>
+        <v>711</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>712</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>713</v>
       </c>
       <c r="AB33" t="s">
-        <v>145</v>
+        <v>39</v>
       </c>
       <c r="AD33" t="b">
         <v>0</v>
@@ -5497,22 +5575,22 @@
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>632</v>
+        <v>643</v>
       </c>
       <c r="C34" t="s">
-        <v>633</v>
+        <v>644</v>
       </c>
       <c r="D34" t="s">
-        <v>634</v>
+        <v>744</v>
       </c>
       <c r="E34" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F34" t="s">
         <v>34</v>
       </c>
       <c r="G34" t="s">
-        <v>635</v>
+        <v>35</v>
       </c>
       <c r="H34" t="s">
         <v>36</v>
@@ -5521,37 +5599,37 @@
         <v>54</v>
       </c>
       <c r="K34" t="s">
-        <v>636</v>
+        <v>94</v>
       </c>
       <c r="L34" t="s">
-        <v>637</v>
+        <v>82</v>
       </c>
       <c r="M34" t="s">
-        <v>638</v>
+        <v>83</v>
+      </c>
+      <c r="N34" t="s">
+        <v>33</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="Q34">
-        <v>22.9</v>
+        <v>14.99</v>
       </c>
       <c r="R34">
-        <v>4.8099999999999996</v>
+        <v>2.5</v>
       </c>
       <c r="Y34" t="s">
-        <v>639</v>
-      </c>
-      <c r="Z34" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="AA34" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="AB34" t="s">
-        <v>642</v>
+        <v>39</v>
       </c>
       <c r="AD34" t="b">
         <v>0</v>
@@ -5562,13 +5640,13 @@
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>643</v>
+        <v>708</v>
       </c>
       <c r="C35" t="s">
-        <v>644</v>
+        <v>709</v>
       </c>
       <c r="D35" t="s">
-        <v>645</v>
+        <v>710</v>
       </c>
       <c r="E35" t="s">
         <v>98</v>
@@ -5586,13 +5664,13 @@
         <v>54</v>
       </c>
       <c r="K35" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L35" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M35" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="N35" t="s">
         <v>99</v>
@@ -5604,16 +5682,19 @@
         <v>38</v>
       </c>
       <c r="Q35">
-        <v>14.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R35">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="Y35" t="s">
-        <v>646</v>
+        <v>711</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>712</v>
       </c>
       <c r="AA35" t="s">
-        <v>647</v>
+        <v>713</v>
       </c>
       <c r="AB35" t="s">
         <v>39</v>
@@ -5627,22 +5708,22 @@
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>609</v>
+        <v>138</v>
       </c>
       <c r="C36" t="s">
-        <v>610</v>
+        <v>139</v>
       </c>
       <c r="D36" t="s">
-        <v>611</v>
+        <v>187</v>
       </c>
       <c r="E36" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F36" t="s">
         <v>34</v>
       </c>
       <c r="G36" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="H36" t="s">
         <v>36</v>
@@ -5651,40 +5732,25 @@
         <v>54</v>
       </c>
       <c r="K36" t="s">
-        <v>94</v>
+        <v>141</v>
       </c>
       <c r="L36" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="M36" t="s">
-        <v>83</v>
-      </c>
-      <c r="N36" t="s">
-        <v>33</v>
+        <v>143</v>
       </c>
       <c r="O36">
-        <v>1</v>
-      </c>
-      <c r="P36" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q36">
-        <v>14.99</v>
-      </c>
-      <c r="R36">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="s">
-        <v>612</v>
-      </c>
-      <c r="Z36" t="s">
-        <v>613</v>
-      </c>
-      <c r="AA36" t="s">
-        <v>614</v>
+        <v>144</v>
+      </c>
+      <c r="AA36">
+        <v>80100</v>
       </c>
       <c r="AB36" t="s">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="AD36" t="b">
         <v>0</v>
@@ -5695,13 +5761,13 @@
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>493</v>
+        <v>146</v>
       </c>
       <c r="C37" t="s">
-        <v>494</v>
+        <v>147</v>
       </c>
       <c r="D37" t="s">
-        <v>648</v>
+        <v>148</v>
       </c>
       <c r="E37" t="s">
         <v>53</v>
@@ -5710,7 +5776,7 @@
         <v>34</v>
       </c>
       <c r="G37" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="H37" t="s">
         <v>36</v>
@@ -5719,25 +5785,25 @@
         <v>54</v>
       </c>
       <c r="K37" t="s">
-        <v>40</v>
+        <v>141</v>
       </c>
       <c r="L37" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="M37" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="O37">
         <v>0</v>
       </c>
       <c r="Y37" t="s">
-        <v>495</v>
-      </c>
-      <c r="AA37" t="s">
-        <v>496</v>
+        <v>144</v>
+      </c>
+      <c r="AA37">
+        <v>80100</v>
       </c>
       <c r="AB37" t="s">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="AD37" t="b">
         <v>0</v>
@@ -5748,22 +5814,22 @@
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>615</v>
+        <v>632</v>
       </c>
       <c r="C38" t="s">
-        <v>616</v>
+        <v>633</v>
       </c>
       <c r="D38" t="s">
-        <v>617</v>
+        <v>634</v>
       </c>
       <c r="E38" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="F38" t="s">
         <v>34</v>
       </c>
       <c r="G38" t="s">
-        <v>35</v>
+        <v>635</v>
       </c>
       <c r="H38" t="s">
         <v>36</v>
@@ -5772,37 +5838,37 @@
         <v>54</v>
       </c>
       <c r="K38" t="s">
-        <v>48</v>
+        <v>636</v>
       </c>
       <c r="L38" t="s">
-        <v>49</v>
+        <v>637</v>
       </c>
       <c r="M38" t="s">
-        <v>50</v>
-      </c>
-      <c r="N38" t="s">
-        <v>99</v>
+        <v>638</v>
       </c>
       <c r="O38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P38" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="Q38">
-        <v>40.99</v>
+        <v>22.9</v>
+      </c>
+      <c r="R38">
+        <v>4.8099999999999996</v>
       </c>
       <c r="Y38" t="s">
-        <v>618</v>
+        <v>639</v>
       </c>
       <c r="Z38" t="s">
-        <v>619</v>
+        <v>640</v>
       </c>
       <c r="AA38" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="AB38" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="AD38" t="b">
         <v>0</v>
@@ -5813,16 +5879,16 @@
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>621</v>
+        <v>643</v>
       </c>
       <c r="C39" t="s">
-        <v>622</v>
+        <v>644</v>
       </c>
       <c r="D39" t="s">
-        <v>623</v>
+        <v>645</v>
       </c>
       <c r="E39" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F39" t="s">
         <v>34</v>
@@ -5837,16 +5903,16 @@
         <v>54</v>
       </c>
       <c r="K39" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L39" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M39" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="N39" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O39">
         <v>1</v>
@@ -5855,25 +5921,16 @@
         <v>38</v>
       </c>
       <c r="Q39">
-        <v>64.989999999999995</v>
+        <v>14.99</v>
       </c>
       <c r="R39">
-        <v>10.83</v>
-      </c>
-      <c r="S39">
-        <v>6.99</v>
-      </c>
-      <c r="T39">
-        <v>1.17</v>
+        <v>2.5</v>
       </c>
       <c r="Y39" t="s">
-        <v>624</v>
-      </c>
-      <c r="Z39" t="s">
-        <v>625</v>
+        <v>646</v>
       </c>
       <c r="AA39" t="s">
-        <v>626</v>
+        <v>647</v>
       </c>
       <c r="AB39" t="s">
         <v>39</v>
@@ -5887,13 +5944,13 @@
     </row>
     <row r="40" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>627</v>
+        <v>609</v>
       </c>
       <c r="C40" t="s">
-        <v>628</v>
+        <v>610</v>
       </c>
       <c r="D40" t="s">
-        <v>629</v>
+        <v>611</v>
       </c>
       <c r="E40" t="s">
         <v>33</v>
@@ -5911,13 +5968,13 @@
         <v>54</v>
       </c>
       <c r="K40" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="L40" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="M40" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="N40" t="s">
         <v>33</v>
@@ -5929,16 +5986,19 @@
         <v>38</v>
       </c>
       <c r="Q40">
-        <v>11.99</v>
+        <v>14.99</v>
       </c>
       <c r="R40">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Y40" t="s">
-        <v>630</v>
+        <v>612</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>613</v>
       </c>
       <c r="AA40" t="s">
-        <v>631</v>
+        <v>614</v>
       </c>
       <c r="AB40" t="s">
         <v>39</v>
@@ -5952,16 +6012,16 @@
     </row>
     <row r="41" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>649</v>
+        <v>493</v>
       </c>
       <c r="C41" t="s">
-        <v>650</v>
+        <v>494</v>
       </c>
       <c r="D41" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="E41" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F41" t="s">
         <v>34</v>
@@ -5976,37 +6036,22 @@
         <v>54</v>
       </c>
       <c r="K41" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L41" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M41" t="s">
-        <v>50</v>
-      </c>
-      <c r="N41" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O41">
-        <v>1</v>
-      </c>
-      <c r="P41" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q41">
-        <v>39.99</v>
-      </c>
-      <c r="R41">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="s">
-        <v>652</v>
-      </c>
-      <c r="Z41" t="s">
-        <v>653</v>
+        <v>495</v>
       </c>
       <c r="AA41" t="s">
-        <v>654</v>
+        <v>496</v>
       </c>
       <c r="AB41" t="s">
         <v>39</v>
@@ -6020,16 +6065,16 @@
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>655</v>
+        <v>615</v>
       </c>
       <c r="C42" t="s">
-        <v>656</v>
+        <v>616</v>
       </c>
       <c r="D42" t="s">
-        <v>657</v>
+        <v>617</v>
       </c>
       <c r="E42" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F42" t="s">
         <v>34</v>
@@ -6044,16 +6089,16 @@
         <v>54</v>
       </c>
       <c r="K42" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="L42" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="M42" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="N42" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O42">
         <v>1</v>
@@ -6062,16 +6107,16 @@
         <v>38</v>
       </c>
       <c r="Q42">
-        <v>14.99</v>
-      </c>
-      <c r="R42">
-        <v>2.5</v>
+        <v>40.99</v>
       </c>
       <c r="Y42" t="s">
-        <v>658</v>
+        <v>618</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>619</v>
       </c>
       <c r="AA42" t="s">
-        <v>659</v>
+        <v>620</v>
       </c>
       <c r="AB42" t="s">
         <v>39</v>
@@ -6085,13 +6130,13 @@
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>571</v>
+        <v>621</v>
       </c>
       <c r="C43" t="s">
-        <v>572</v>
+        <v>622</v>
       </c>
       <c r="D43" t="s">
-        <v>660</v>
+        <v>623</v>
       </c>
       <c r="E43" t="s">
         <v>33</v>
@@ -6132,11 +6177,20 @@
       <c r="R43">
         <v>10.83</v>
       </c>
+      <c r="S43">
+        <v>6.99</v>
+      </c>
+      <c r="T43">
+        <v>1.17</v>
+      </c>
       <c r="Y43" t="s">
-        <v>573</v>
+        <v>624</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>625</v>
       </c>
       <c r="AA43" t="s">
-        <v>574</v>
+        <v>626</v>
       </c>
       <c r="AB43" t="s">
         <v>39</v>
@@ -6150,13 +6204,13 @@
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>599</v>
+        <v>627</v>
       </c>
       <c r="C44" t="s">
-        <v>600</v>
+        <v>628</v>
       </c>
       <c r="D44" t="s">
-        <v>601</v>
+        <v>629</v>
       </c>
       <c r="E44" t="s">
         <v>33</v>
@@ -6174,13 +6228,13 @@
         <v>54</v>
       </c>
       <c r="K44" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L44" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M44" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="N44" t="s">
         <v>33</v>
@@ -6192,16 +6246,16 @@
         <v>38</v>
       </c>
       <c r="Q44">
-        <v>14.99</v>
+        <v>11.99</v>
       </c>
       <c r="R44">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Y44" t="s">
-        <v>61</v>
+        <v>630</v>
       </c>
       <c r="AA44" t="s">
-        <v>602</v>
+        <v>631</v>
       </c>
       <c r="AB44" t="s">
         <v>39</v>
@@ -6215,13 +6269,13 @@
     </row>
     <row r="45" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>589</v>
+        <v>649</v>
       </c>
       <c r="C45" t="s">
-        <v>590</v>
+        <v>650</v>
       </c>
       <c r="D45" t="s">
-        <v>591</v>
+        <v>651</v>
       </c>
       <c r="E45" t="s">
         <v>33</v>
@@ -6239,13 +6293,13 @@
         <v>54</v>
       </c>
       <c r="K45" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L45" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M45" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N45" t="s">
         <v>33</v>
@@ -6257,16 +6311,19 @@
         <v>38</v>
       </c>
       <c r="Q45">
-        <v>64.989999999999995</v>
+        <v>39.99</v>
       </c>
       <c r="R45">
-        <v>10.83</v>
+        <v>6.67</v>
       </c>
       <c r="Y45" t="s">
-        <v>592</v>
+        <v>652</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>653</v>
       </c>
       <c r="AA45" t="s">
-        <v>593</v>
+        <v>654</v>
       </c>
       <c r="AB45" t="s">
         <v>39</v>
@@ -6280,13 +6337,13 @@
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>594</v>
+        <v>655</v>
       </c>
       <c r="C46" t="s">
-        <v>595</v>
+        <v>656</v>
       </c>
       <c r="D46" t="s">
-        <v>596</v>
+        <v>657</v>
       </c>
       <c r="E46" t="s">
         <v>33</v>
@@ -6304,13 +6361,13 @@
         <v>54</v>
       </c>
       <c r="K46" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L46" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M46" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="N46" t="s">
         <v>33</v>
@@ -6322,16 +6379,16 @@
         <v>38</v>
       </c>
       <c r="Q46">
-        <v>64.989999999999995</v>
+        <v>14.99</v>
       </c>
       <c r="R46">
-        <v>10.83</v>
+        <v>2.5</v>
       </c>
       <c r="Y46" t="s">
-        <v>597</v>
+        <v>658</v>
       </c>
       <c r="AA46" t="s">
-        <v>598</v>
+        <v>659</v>
       </c>
       <c r="AB46" t="s">
         <v>39</v>
@@ -6345,13 +6402,13 @@
     </row>
     <row r="47" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>603</v>
+        <v>571</v>
       </c>
       <c r="C47" t="s">
-        <v>604</v>
+        <v>572</v>
       </c>
       <c r="D47" t="s">
-        <v>605</v>
+        <v>660</v>
       </c>
       <c r="E47" t="s">
         <v>33</v>
@@ -6393,13 +6450,10 @@
         <v>10.83</v>
       </c>
       <c r="Y47" t="s">
-        <v>606</v>
-      </c>
-      <c r="Z47" t="s">
-        <v>607</v>
+        <v>573</v>
       </c>
       <c r="AA47" t="s">
-        <v>608</v>
+        <v>574</v>
       </c>
       <c r="AB47" t="s">
         <v>39</v>
@@ -6413,13 +6467,13 @@
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>578</v>
+        <v>599</v>
       </c>
       <c r="C48" t="s">
-        <v>579</v>
+        <v>600</v>
       </c>
       <c r="D48" t="s">
-        <v>661</v>
+        <v>601</v>
       </c>
       <c r="E48" t="s">
         <v>33</v>
@@ -6437,13 +6491,13 @@
         <v>54</v>
       </c>
       <c r="K48" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L48" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M48" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="N48" t="s">
         <v>33</v>
@@ -6455,19 +6509,16 @@
         <v>38</v>
       </c>
       <c r="Q48">
-        <v>64.989999999999995</v>
+        <v>14.99</v>
       </c>
       <c r="R48">
-        <v>10.83</v>
+        <v>2.5</v>
       </c>
       <c r="Y48" t="s">
-        <v>580</v>
-      </c>
-      <c r="Z48" t="s">
-        <v>581</v>
+        <v>61</v>
       </c>
       <c r="AA48" t="s">
-        <v>582</v>
+        <v>602</v>
       </c>
       <c r="AB48" t="s">
         <v>39</v>
@@ -6481,16 +6532,16 @@
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>575</v>
+        <v>589</v>
       </c>
       <c r="C49" t="s">
-        <v>576</v>
+        <v>590</v>
       </c>
       <c r="D49" t="s">
-        <v>577</v>
+        <v>591</v>
       </c>
       <c r="E49" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F49" t="s">
         <v>34</v>
@@ -6513,14 +6564,26 @@
       <c r="M49" t="s">
         <v>42</v>
       </c>
+      <c r="N49" t="s">
+        <v>33</v>
+      </c>
       <c r="O49">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P49" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q49">
+        <v>64.989999999999995</v>
+      </c>
+      <c r="R49">
+        <v>10.83</v>
       </c>
       <c r="Y49" t="s">
-        <v>573</v>
+        <v>592</v>
       </c>
       <c r="AA49" t="s">
-        <v>574</v>
+        <v>593</v>
       </c>
       <c r="AB49" t="s">
         <v>39</v>
@@ -6534,13 +6597,13 @@
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>518</v>
+        <v>594</v>
       </c>
       <c r="C50" t="s">
-        <v>519</v>
+        <v>595</v>
       </c>
       <c r="D50" t="s">
-        <v>583</v>
+        <v>596</v>
       </c>
       <c r="E50" t="s">
         <v>33</v>
@@ -6558,13 +6621,13 @@
         <v>54</v>
       </c>
       <c r="K50" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L50" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M50" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N50" t="s">
         <v>33</v>
@@ -6576,22 +6639,16 @@
         <v>38</v>
       </c>
       <c r="Q50">
-        <v>37.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R50">
-        <v>6.33</v>
-      </c>
-      <c r="S50">
-        <v>6.99</v>
-      </c>
-      <c r="T50">
-        <v>1.17</v>
+        <v>10.83</v>
       </c>
       <c r="Y50" t="s">
-        <v>46</v>
+        <v>597</v>
       </c>
       <c r="AA50" t="s">
-        <v>520</v>
+        <v>598</v>
       </c>
       <c r="AB50" t="s">
         <v>39</v>
@@ -6605,13 +6662,13 @@
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>584</v>
+        <v>603</v>
       </c>
       <c r="C51" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="D51" t="s">
-        <v>586</v>
+        <v>605</v>
       </c>
       <c r="E51" t="s">
         <v>33</v>
@@ -6653,10 +6710,13 @@
         <v>10.83</v>
       </c>
       <c r="Y51" t="s">
-        <v>587</v>
+        <v>606</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>607</v>
       </c>
       <c r="AA51" t="s">
-        <v>588</v>
+        <v>608</v>
       </c>
       <c r="AB51" t="s">
         <v>39</v>
@@ -6670,13 +6730,13 @@
     </row>
     <row r="52" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>457</v>
+        <v>578</v>
       </c>
       <c r="C52" t="s">
-        <v>458</v>
+        <v>579</v>
       </c>
       <c r="D52" t="s">
-        <v>459</v>
+        <v>661</v>
       </c>
       <c r="E52" t="s">
         <v>33</v>
@@ -6718,13 +6778,13 @@
         <v>10.83</v>
       </c>
       <c r="Y52" t="s">
-        <v>460</v>
+        <v>580</v>
       </c>
       <c r="Z52" t="s">
-        <v>279</v>
+        <v>581</v>
       </c>
       <c r="AA52" t="s">
-        <v>461</v>
+        <v>582</v>
       </c>
       <c r="AB52" t="s">
         <v>39</v>
@@ -6738,16 +6798,16 @@
     </row>
     <row r="53" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>462</v>
+        <v>575</v>
       </c>
       <c r="C53" t="s">
-        <v>463</v>
+        <v>576</v>
       </c>
       <c r="D53" t="s">
-        <v>459</v>
+        <v>577</v>
       </c>
       <c r="E53" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F53" t="s">
         <v>34</v>
@@ -6770,26 +6830,14 @@
       <c r="M53" t="s">
         <v>42</v>
       </c>
-      <c r="N53" t="s">
-        <v>33</v>
-      </c>
       <c r="O53">
-        <v>1</v>
-      </c>
-      <c r="P53" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q53">
-        <v>64.989999999999995</v>
-      </c>
-      <c r="R53">
-        <v>10.83</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="s">
-        <v>56</v>
+        <v>573</v>
       </c>
       <c r="AA53" t="s">
-        <v>464</v>
+        <v>574</v>
       </c>
       <c r="AB53" t="s">
         <v>39</v>
@@ -6803,13 +6851,13 @@
     </row>
     <row r="54" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>465</v>
+        <v>518</v>
       </c>
       <c r="C54" t="s">
-        <v>466</v>
+        <v>519</v>
       </c>
       <c r="D54" t="s">
-        <v>467</v>
+        <v>583</v>
       </c>
       <c r="E54" t="s">
         <v>33</v>
@@ -6839,22 +6887,28 @@
         <v>33</v>
       </c>
       <c r="O54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P54" t="s">
         <v>38</v>
       </c>
       <c r="Q54">
-        <v>79.98</v>
+        <v>37.99</v>
       </c>
       <c r="R54">
-        <v>13.34</v>
+        <v>6.33</v>
+      </c>
+      <c r="S54">
+        <v>6.99</v>
+      </c>
+      <c r="T54">
+        <v>1.17</v>
       </c>
       <c r="Y54" t="s">
-        <v>468</v>
+        <v>46</v>
       </c>
       <c r="AA54" t="s">
-        <v>469</v>
+        <v>520</v>
       </c>
       <c r="AB54" t="s">
         <v>39</v>
@@ -6868,13 +6922,13 @@
     </row>
     <row r="55" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>470</v>
+        <v>584</v>
       </c>
       <c r="C55" t="s">
-        <v>471</v>
+        <v>585</v>
       </c>
       <c r="D55" t="s">
-        <v>472</v>
+        <v>586</v>
       </c>
       <c r="E55" t="s">
         <v>33</v>
@@ -6892,13 +6946,13 @@
         <v>54</v>
       </c>
       <c r="K55" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L55" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M55" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N55" t="s">
         <v>33</v>
@@ -6910,16 +6964,16 @@
         <v>38</v>
       </c>
       <c r="Q55">
-        <v>37.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R55">
-        <v>6.33</v>
+        <v>10.83</v>
       </c>
       <c r="Y55" t="s">
-        <v>473</v>
+        <v>587</v>
       </c>
       <c r="AA55" t="s">
-        <v>474</v>
+        <v>588</v>
       </c>
       <c r="AB55" t="s">
         <v>39</v>
@@ -6933,16 +6987,16 @@
     </row>
     <row r="56" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>475</v>
+        <v>457</v>
       </c>
       <c r="C56" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
       <c r="D56" t="s">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="E56" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F56" t="s">
         <v>34</v>
@@ -6965,17 +7019,29 @@
       <c r="M56" t="s">
         <v>42</v>
       </c>
+      <c r="N56" t="s">
+        <v>33</v>
+      </c>
       <c r="O56">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P56" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q56">
+        <v>64.989999999999995</v>
+      </c>
+      <c r="R56">
+        <v>10.83</v>
       </c>
       <c r="Y56" t="s">
-        <v>478</v>
+        <v>460</v>
       </c>
       <c r="Z56" t="s">
         <v>279</v>
       </c>
       <c r="AA56" t="s">
-        <v>479</v>
+        <v>461</v>
       </c>
       <c r="AB56" t="s">
         <v>39</v>
@@ -6989,13 +7055,13 @@
     </row>
     <row r="57" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>480</v>
+        <v>462</v>
       </c>
       <c r="C57" t="s">
-        <v>481</v>
+        <v>463</v>
       </c>
       <c r="D57" t="s">
-        <v>482</v>
+        <v>459</v>
       </c>
       <c r="E57" t="s">
         <v>33</v>
@@ -7013,13 +7079,13 @@
         <v>54</v>
       </c>
       <c r="K57" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L57" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M57" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N57" t="s">
         <v>33</v>
@@ -7031,16 +7097,16 @@
         <v>38</v>
       </c>
       <c r="Q57">
-        <v>11.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R57">
-        <v>2</v>
+        <v>10.83</v>
       </c>
       <c r="Y57" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="AA57" t="s">
-        <v>483</v>
+        <v>464</v>
       </c>
       <c r="AB57" t="s">
         <v>39</v>
@@ -7054,13 +7120,13 @@
     </row>
     <row r="58" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>484</v>
+        <v>465</v>
       </c>
       <c r="C58" t="s">
-        <v>485</v>
+        <v>466</v>
       </c>
       <c r="D58" t="s">
-        <v>486</v>
+        <v>467</v>
       </c>
       <c r="E58" t="s">
         <v>33</v>
@@ -7078,34 +7144,34 @@
         <v>54</v>
       </c>
       <c r="K58" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L58" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M58" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N58" t="s">
         <v>33</v>
       </c>
       <c r="O58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P58" t="s">
         <v>38</v>
       </c>
       <c r="Q58">
-        <v>64.989999999999995</v>
+        <v>79.98</v>
       </c>
       <c r="R58">
-        <v>10.83</v>
+        <v>13.34</v>
       </c>
       <c r="Y58" t="s">
-        <v>67</v>
+        <v>468</v>
       </c>
       <c r="AA58" t="s">
-        <v>487</v>
+        <v>469</v>
       </c>
       <c r="AB58" t="s">
         <v>39</v>
@@ -7119,13 +7185,13 @@
     </row>
     <row r="59" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>488</v>
+        <v>470</v>
       </c>
       <c r="C59" t="s">
-        <v>489</v>
+        <v>471</v>
       </c>
       <c r="D59" t="s">
-        <v>490</v>
+        <v>472</v>
       </c>
       <c r="E59" t="s">
         <v>33</v>
@@ -7155,25 +7221,22 @@
         <v>33</v>
       </c>
       <c r="O59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P59" t="s">
         <v>38</v>
       </c>
       <c r="Q59">
-        <v>79.98</v>
+        <v>37.99</v>
       </c>
       <c r="R59">
-        <v>13.34</v>
+        <v>6.33</v>
       </c>
       <c r="Y59" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z59" t="s">
-        <v>491</v>
+        <v>473</v>
       </c>
       <c r="AA59" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="AB59" t="s">
         <v>39</v>
@@ -7187,16 +7250,16 @@
     </row>
     <row r="60" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>497</v>
+        <v>475</v>
       </c>
       <c r="C60" t="s">
-        <v>498</v>
+        <v>476</v>
       </c>
       <c r="D60" t="s">
-        <v>499</v>
+        <v>477</v>
       </c>
       <c r="E60" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F60" t="s">
         <v>34</v>
@@ -7219,29 +7282,17 @@
       <c r="M60" t="s">
         <v>42</v>
       </c>
-      <c r="N60" t="s">
-        <v>33</v>
-      </c>
       <c r="O60">
-        <v>1</v>
-      </c>
-      <c r="P60" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q60">
-        <v>59.99</v>
-      </c>
-      <c r="R60">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y60" t="s">
-        <v>500</v>
+        <v>478</v>
       </c>
       <c r="Z60" t="s">
-        <v>501</v>
+        <v>279</v>
       </c>
       <c r="AA60" t="s">
-        <v>502</v>
+        <v>479</v>
       </c>
       <c r="AB60" t="s">
         <v>39</v>
@@ -7255,13 +7306,13 @@
     </row>
     <row r="61" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>503</v>
+        <v>480</v>
       </c>
       <c r="C61" t="s">
-        <v>504</v>
+        <v>481</v>
       </c>
       <c r="D61" t="s">
-        <v>499</v>
+        <v>482</v>
       </c>
       <c r="E61" t="s">
         <v>33</v>
@@ -7279,13 +7330,13 @@
         <v>54</v>
       </c>
       <c r="K61" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L61" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M61" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N61" t="s">
         <v>33</v>
@@ -7297,19 +7348,16 @@
         <v>38</v>
       </c>
       <c r="Q61">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R61">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y61" t="s">
-        <v>505</v>
-      </c>
-      <c r="Z61" t="s">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="AA61" t="s">
-        <v>506</v>
+        <v>483</v>
       </c>
       <c r="AB61" t="s">
         <v>39</v>
@@ -7323,13 +7371,13 @@
     </row>
     <row r="62" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>507</v>
+        <v>484</v>
       </c>
       <c r="C62" t="s">
-        <v>508</v>
+        <v>485</v>
       </c>
       <c r="D62" t="s">
-        <v>509</v>
+        <v>486</v>
       </c>
       <c r="E62" t="s">
         <v>33</v>
@@ -7365,16 +7413,16 @@
         <v>38</v>
       </c>
       <c r="Q62">
-        <v>59.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R62">
-        <v>10</v>
+        <v>10.83</v>
       </c>
       <c r="Y62" t="s">
-        <v>510</v>
+        <v>67</v>
       </c>
       <c r="AA62" t="s">
-        <v>511</v>
+        <v>487</v>
       </c>
       <c r="AB62" t="s">
         <v>39</v>
@@ -7388,13 +7436,13 @@
     </row>
     <row r="63" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>512</v>
+        <v>488</v>
       </c>
       <c r="C63" t="s">
-        <v>513</v>
+        <v>489</v>
       </c>
       <c r="D63" t="s">
-        <v>514</v>
+        <v>490</v>
       </c>
       <c r="E63" t="s">
         <v>33</v>
@@ -7412,37 +7460,37 @@
         <v>54</v>
       </c>
       <c r="K63" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L63" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M63" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N63" t="s">
         <v>33</v>
       </c>
       <c r="O63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P63" t="s">
         <v>38</v>
       </c>
       <c r="Q63">
-        <v>59.99</v>
+        <v>79.98</v>
       </c>
       <c r="R63">
-        <v>10</v>
+        <v>13.34</v>
       </c>
       <c r="Y63" t="s">
-        <v>515</v>
+        <v>63</v>
       </c>
       <c r="Z63" t="s">
-        <v>516</v>
+        <v>491</v>
       </c>
       <c r="AA63" t="s">
-        <v>517</v>
+        <v>492</v>
       </c>
       <c r="AB63" t="s">
         <v>39</v>
@@ -7456,13 +7504,13 @@
     </row>
     <row r="64" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>521</v>
+        <v>497</v>
       </c>
       <c r="C64" t="s">
-        <v>522</v>
+        <v>498</v>
       </c>
       <c r="D64" t="s">
-        <v>523</v>
+        <v>499</v>
       </c>
       <c r="E64" t="s">
         <v>33</v>
@@ -7480,13 +7528,13 @@
         <v>54</v>
       </c>
       <c r="K64" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L64" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M64" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="N64" t="s">
         <v>33</v>
@@ -7498,16 +7546,19 @@
         <v>38</v>
       </c>
       <c r="Q64">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R64">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y64" t="s">
-        <v>58</v>
+        <v>500</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>501</v>
       </c>
       <c r="AA64" t="s">
-        <v>524</v>
+        <v>502</v>
       </c>
       <c r="AB64" t="s">
         <v>39</v>
@@ -7521,13 +7572,13 @@
     </row>
     <row r="65" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>525</v>
+        <v>503</v>
       </c>
       <c r="C65" t="s">
-        <v>526</v>
+        <v>504</v>
       </c>
       <c r="D65" t="s">
-        <v>527</v>
+        <v>499</v>
       </c>
       <c r="E65" t="s">
         <v>33</v>
@@ -7569,10 +7620,13 @@
         <v>10</v>
       </c>
       <c r="Y65" t="s">
-        <v>90</v>
+        <v>505</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>93</v>
       </c>
       <c r="AA65" t="s">
-        <v>528</v>
+        <v>506</v>
       </c>
       <c r="AB65" t="s">
         <v>39</v>
@@ -7586,13 +7640,13 @@
     </row>
     <row r="66" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>529</v>
+        <v>507</v>
       </c>
       <c r="C66" t="s">
-        <v>530</v>
+        <v>508</v>
       </c>
       <c r="D66" t="s">
-        <v>527</v>
+        <v>509</v>
       </c>
       <c r="E66" t="s">
         <v>33</v>
@@ -7634,10 +7688,10 @@
         <v>10</v>
       </c>
       <c r="Y66" t="s">
-        <v>531</v>
+        <v>510</v>
       </c>
       <c r="AA66" t="s">
-        <v>532</v>
+        <v>511</v>
       </c>
       <c r="AB66" t="s">
         <v>39</v>
@@ -7651,13 +7705,13 @@
     </row>
     <row r="67" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>533</v>
+        <v>512</v>
       </c>
       <c r="C67" t="s">
-        <v>534</v>
+        <v>513</v>
       </c>
       <c r="D67" t="s">
-        <v>535</v>
+        <v>514</v>
       </c>
       <c r="E67" t="s">
         <v>33</v>
@@ -7675,13 +7729,13 @@
         <v>54</v>
       </c>
       <c r="K67" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L67" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M67" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N67" t="s">
         <v>33</v>
@@ -7693,19 +7747,19 @@
         <v>38</v>
       </c>
       <c r="Q67">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R67">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y67" t="s">
-        <v>536</v>
+        <v>515</v>
       </c>
       <c r="Z67" t="s">
-        <v>537</v>
+        <v>516</v>
       </c>
       <c r="AA67" t="s">
-        <v>538</v>
+        <v>517</v>
       </c>
       <c r="AB67" t="s">
         <v>39</v>
@@ -7719,13 +7773,13 @@
     </row>
     <row r="68" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>539</v>
+        <v>521</v>
       </c>
       <c r="C68" t="s">
-        <v>540</v>
+        <v>522</v>
       </c>
       <c r="D68" t="s">
-        <v>541</v>
+        <v>523</v>
       </c>
       <c r="E68" t="s">
         <v>33</v>
@@ -7743,13 +7797,13 @@
         <v>54</v>
       </c>
       <c r="K68" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L68" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M68" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="N68" t="s">
         <v>33</v>
@@ -7761,19 +7815,16 @@
         <v>38</v>
       </c>
       <c r="Q68">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="R68">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="Y68" t="s">
-        <v>71</v>
-      </c>
-      <c r="Z68" t="s">
-        <v>542</v>
+        <v>58</v>
       </c>
       <c r="AA68" t="s">
-        <v>543</v>
+        <v>524</v>
       </c>
       <c r="AB68" t="s">
         <v>39</v>
@@ -7787,13 +7838,13 @@
     </row>
     <row r="69" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>544</v>
+        <v>525</v>
       </c>
       <c r="C69" t="s">
-        <v>545</v>
+        <v>526</v>
       </c>
       <c r="D69" t="s">
-        <v>546</v>
+        <v>527</v>
       </c>
       <c r="E69" t="s">
         <v>33</v>
@@ -7811,37 +7862,34 @@
         <v>54</v>
       </c>
       <c r="K69" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L69" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M69" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N69" t="s">
         <v>33</v>
       </c>
       <c r="O69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P69" t="s">
         <v>38</v>
       </c>
       <c r="Q69">
-        <v>76.98</v>
+        <v>59.99</v>
       </c>
       <c r="R69">
-        <v>12.84</v>
+        <v>10</v>
       </c>
       <c r="Y69" t="s">
-        <v>547</v>
-      </c>
-      <c r="Z69" t="s">
-        <v>548</v>
+        <v>90</v>
       </c>
       <c r="AA69" t="s">
-        <v>549</v>
+        <v>528</v>
       </c>
       <c r="AB69" t="s">
         <v>39</v>
@@ -7855,13 +7903,13 @@
     </row>
     <row r="70" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>550</v>
+        <v>529</v>
       </c>
       <c r="C70" t="s">
-        <v>551</v>
+        <v>530</v>
       </c>
       <c r="D70" t="s">
-        <v>552</v>
+        <v>527</v>
       </c>
       <c r="E70" t="s">
         <v>33</v>
@@ -7903,10 +7951,10 @@
         <v>10</v>
       </c>
       <c r="Y70" t="s">
-        <v>553</v>
+        <v>531</v>
       </c>
       <c r="AA70" t="s">
-        <v>554</v>
+        <v>532</v>
       </c>
       <c r="AB70" t="s">
         <v>39</v>
@@ -7920,13 +7968,13 @@
     </row>
     <row r="71" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>555</v>
+        <v>533</v>
       </c>
       <c r="C71" t="s">
-        <v>556</v>
+        <v>534</v>
       </c>
       <c r="D71" t="s">
-        <v>557</v>
+        <v>535</v>
       </c>
       <c r="E71" t="s">
         <v>33</v>
@@ -7944,13 +7992,13 @@
         <v>54</v>
       </c>
       <c r="K71" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L71" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M71" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N71" t="s">
         <v>33</v>
@@ -7962,16 +8010,19 @@
         <v>38</v>
       </c>
       <c r="Q71">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R71">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y71" t="s">
-        <v>558</v>
+        <v>536</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>537</v>
       </c>
       <c r="AA71" t="s">
-        <v>559</v>
+        <v>538</v>
       </c>
       <c r="AB71" t="s">
         <v>39</v>
@@ -7985,13 +8036,13 @@
     </row>
     <row r="72" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>418</v>
+        <v>539</v>
       </c>
       <c r="C72" t="s">
-        <v>419</v>
+        <v>540</v>
       </c>
       <c r="D72" t="s">
-        <v>560</v>
+        <v>541</v>
       </c>
       <c r="E72" t="s">
         <v>33</v>
@@ -8033,10 +8084,13 @@
         <v>10</v>
       </c>
       <c r="Y72" t="s">
-        <v>420</v>
+        <v>71</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>542</v>
       </c>
       <c r="AA72" t="s">
-        <v>421</v>
+        <v>543</v>
       </c>
       <c r="AB72" t="s">
         <v>39</v>
@@ -8050,13 +8104,13 @@
     </row>
     <row r="73" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>561</v>
+        <v>544</v>
       </c>
       <c r="C73" t="s">
-        <v>562</v>
+        <v>545</v>
       </c>
       <c r="D73" t="s">
-        <v>563</v>
+        <v>546</v>
       </c>
       <c r="E73" t="s">
         <v>33</v>
@@ -8074,37 +8128,37 @@
         <v>54</v>
       </c>
       <c r="K73" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L73" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M73" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N73" t="s">
         <v>33</v>
       </c>
       <c r="O73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P73" t="s">
         <v>38</v>
       </c>
       <c r="Q73">
-        <v>59.99</v>
+        <v>76.98</v>
       </c>
       <c r="R73">
-        <v>10</v>
+        <v>12.84</v>
       </c>
       <c r="Y73" t="s">
-        <v>564</v>
+        <v>547</v>
       </c>
       <c r="Z73" t="s">
-        <v>565</v>
+        <v>548</v>
       </c>
       <c r="AA73" t="s">
-        <v>566</v>
+        <v>549</v>
       </c>
       <c r="AB73" t="s">
         <v>39</v>
@@ -8118,13 +8172,13 @@
     </row>
     <row r="74" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>567</v>
+        <v>550</v>
       </c>
       <c r="C74" t="s">
-        <v>568</v>
+        <v>551</v>
       </c>
       <c r="D74" t="s">
-        <v>569</v>
+        <v>552</v>
       </c>
       <c r="E74" t="s">
         <v>33</v>
@@ -8142,13 +8196,13 @@
         <v>54</v>
       </c>
       <c r="K74" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L74" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M74" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="N74" t="s">
         <v>33</v>
@@ -8160,16 +8214,16 @@
         <v>38</v>
       </c>
       <c r="Q74">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R74">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y74" t="s">
-        <v>69</v>
+        <v>553</v>
       </c>
       <c r="AA74" t="s">
-        <v>570</v>
+        <v>554</v>
       </c>
       <c r="AB74" t="s">
         <v>39</v>
@@ -8183,13 +8237,13 @@
     </row>
     <row r="75" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>413</v>
+        <v>555</v>
       </c>
       <c r="C75" t="s">
-        <v>414</v>
+        <v>556</v>
       </c>
       <c r="D75" t="s">
-        <v>415</v>
+        <v>557</v>
       </c>
       <c r="E75" t="s">
         <v>33</v>
@@ -8231,10 +8285,10 @@
         <v>10</v>
       </c>
       <c r="Y75" t="s">
-        <v>416</v>
+        <v>558</v>
       </c>
       <c r="AA75" t="s">
-        <v>417</v>
+        <v>559</v>
       </c>
       <c r="AB75" t="s">
         <v>39</v>
@@ -8248,13 +8302,13 @@
     </row>
     <row r="76" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="C76" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="D76" t="s">
-        <v>424</v>
+        <v>560</v>
       </c>
       <c r="E76" t="s">
         <v>33</v>
@@ -8272,13 +8326,13 @@
         <v>54</v>
       </c>
       <c r="K76" t="s">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="L76" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="M76" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="N76" t="s">
         <v>33</v>
@@ -8290,16 +8344,16 @@
         <v>38</v>
       </c>
       <c r="Q76">
-        <v>22.99</v>
+        <v>59.99</v>
       </c>
       <c r="R76">
-        <v>3.83</v>
+        <v>10</v>
       </c>
       <c r="Y76" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="AA76" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="AB76" t="s">
         <v>39</v>
@@ -8313,13 +8367,13 @@
     </row>
     <row r="77" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>427</v>
+        <v>561</v>
       </c>
       <c r="C77" t="s">
-        <v>428</v>
+        <v>562</v>
       </c>
       <c r="D77" t="s">
-        <v>424</v>
+        <v>563</v>
       </c>
       <c r="E77" t="s">
         <v>33</v>
@@ -8337,13 +8391,13 @@
         <v>54</v>
       </c>
       <c r="K77" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L77" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M77" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N77" t="s">
         <v>33</v>
@@ -8355,19 +8409,19 @@
         <v>38</v>
       </c>
       <c r="Q77">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R77">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y77" t="s">
-        <v>96</v>
+        <v>564</v>
       </c>
       <c r="Z77" t="s">
-        <v>97</v>
+        <v>565</v>
       </c>
       <c r="AA77" t="s">
-        <v>429</v>
+        <v>566</v>
       </c>
       <c r="AB77" t="s">
         <v>39</v>
@@ -8381,13 +8435,13 @@
     </row>
     <row r="78" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>430</v>
+        <v>567</v>
       </c>
       <c r="C78" t="s">
-        <v>431</v>
+        <v>568</v>
       </c>
       <c r="D78" t="s">
-        <v>432</v>
+        <v>569</v>
       </c>
       <c r="E78" t="s">
         <v>33</v>
@@ -8405,13 +8459,13 @@
         <v>54</v>
       </c>
       <c r="K78" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="L78" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="M78" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="N78" t="s">
         <v>33</v>
@@ -8423,19 +8477,16 @@
         <v>38</v>
       </c>
       <c r="Q78">
-        <v>38.49</v>
+        <v>14.99</v>
       </c>
       <c r="R78">
-        <v>6.42</v>
+        <v>2.5</v>
       </c>
       <c r="Y78" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z78" t="s">
-        <v>433</v>
+        <v>69</v>
       </c>
       <c r="AA78" t="s">
-        <v>434</v>
+        <v>570</v>
       </c>
       <c r="AB78" t="s">
         <v>39</v>
@@ -8449,13 +8500,13 @@
     </row>
     <row r="79" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>435</v>
+        <v>413</v>
       </c>
       <c r="C79" t="s">
-        <v>436</v>
+        <v>414</v>
       </c>
       <c r="D79" t="s">
-        <v>437</v>
+        <v>415</v>
       </c>
       <c r="E79" t="s">
         <v>33</v>
@@ -8473,13 +8524,13 @@
         <v>54</v>
       </c>
       <c r="K79" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="L79" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="M79" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="N79" t="s">
         <v>33</v>
@@ -8491,16 +8542,16 @@
         <v>38</v>
       </c>
       <c r="Q79">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R79">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y79" t="s">
-        <v>438</v>
+        <v>416</v>
       </c>
       <c r="AA79" t="s">
-        <v>439</v>
+        <v>417</v>
       </c>
       <c r="AB79" t="s">
         <v>39</v>
@@ -8514,13 +8565,13 @@
     </row>
     <row r="80" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="C80" t="s">
-        <v>441</v>
+        <v>423</v>
       </c>
       <c r="D80" t="s">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="E80" t="s">
         <v>33</v>
@@ -8538,13 +8589,13 @@
         <v>54</v>
       </c>
       <c r="K80" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="L80" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="M80" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="N80" t="s">
         <v>33</v>
@@ -8556,16 +8607,16 @@
         <v>38</v>
       </c>
       <c r="Q80">
-        <v>37.99</v>
+        <v>22.99</v>
       </c>
       <c r="R80">
-        <v>6.33</v>
+        <v>3.83</v>
       </c>
       <c r="Y80" t="s">
-        <v>443</v>
+        <v>425</v>
       </c>
       <c r="AA80" t="s">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="AB80" t="s">
         <v>39</v>
@@ -8579,13 +8630,13 @@
     </row>
     <row r="81" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="C81" t="s">
-        <v>446</v>
+        <v>428</v>
       </c>
       <c r="D81" t="s">
-        <v>447</v>
+        <v>424</v>
       </c>
       <c r="E81" t="s">
         <v>33</v>
@@ -8603,13 +8654,13 @@
         <v>54</v>
       </c>
       <c r="K81" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L81" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M81" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N81" t="s">
         <v>33</v>
@@ -8621,16 +8672,19 @@
         <v>38</v>
       </c>
       <c r="Q81">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R81">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y81" t="s">
-        <v>448</v>
+        <v>96</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>97</v>
       </c>
       <c r="AA81" t="s">
-        <v>449</v>
+        <v>429</v>
       </c>
       <c r="AB81" t="s">
         <v>39</v>
@@ -8644,16 +8698,16 @@
     </row>
     <row r="82" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="C82" t="s">
-        <v>451</v>
+        <v>431</v>
       </c>
       <c r="D82" t="s">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="E82" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F82" t="s">
         <v>34</v>
@@ -8668,22 +8722,37 @@
         <v>54</v>
       </c>
       <c r="K82" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L82" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M82" t="s">
-        <v>42</v>
+        <v>45</v>
+      </c>
+      <c r="N82" t="s">
+        <v>33</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P82" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q82">
+        <v>38.49</v>
+      </c>
+      <c r="R82">
+        <v>6.42</v>
       </c>
       <c r="Y82" t="s">
-        <v>453</v>
+        <v>59</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>433</v>
       </c>
       <c r="AA82" t="s">
-        <v>454</v>
+        <v>434</v>
       </c>
       <c r="AB82" t="s">
         <v>39</v>
@@ -8697,13 +8766,13 @@
     </row>
     <row r="83" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>403</v>
+        <v>435</v>
       </c>
       <c r="C83" t="s">
-        <v>404</v>
+        <v>436</v>
       </c>
       <c r="D83" t="s">
-        <v>455</v>
+        <v>437</v>
       </c>
       <c r="E83" t="s">
         <v>33</v>
@@ -8721,13 +8790,13 @@
         <v>54</v>
       </c>
       <c r="K83" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="L83" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="M83" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="N83" t="s">
         <v>33</v>
@@ -8739,22 +8808,16 @@
         <v>38</v>
       </c>
       <c r="Q83">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="R83">
-        <v>10</v>
-      </c>
-      <c r="S83">
-        <v>5.99</v>
-      </c>
-      <c r="T83">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="Y83" t="s">
-        <v>405</v>
+        <v>438</v>
       </c>
       <c r="AA83" t="s">
-        <v>406</v>
+        <v>439</v>
       </c>
       <c r="AB83" t="s">
         <v>39</v>
@@ -8768,13 +8831,13 @@
     </row>
     <row r="84" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>407</v>
+        <v>440</v>
       </c>
       <c r="C84" t="s">
-        <v>408</v>
+        <v>441</v>
       </c>
       <c r="D84" t="s">
-        <v>456</v>
+        <v>442</v>
       </c>
       <c r="E84" t="s">
         <v>33</v>
@@ -8792,13 +8855,13 @@
         <v>54</v>
       </c>
       <c r="K84" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="L84" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="M84" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="N84" t="s">
         <v>33</v>
@@ -8810,16 +8873,16 @@
         <v>38</v>
       </c>
       <c r="Q84">
-        <v>22.99</v>
+        <v>37.99</v>
       </c>
       <c r="R84">
-        <v>3.83</v>
+        <v>6.33</v>
       </c>
       <c r="Y84" t="s">
-        <v>409</v>
+        <v>443</v>
       </c>
       <c r="AA84" t="s">
-        <v>410</v>
+        <v>444</v>
       </c>
       <c r="AB84" t="s">
         <v>39</v>
@@ -8833,13 +8896,13 @@
     </row>
     <row r="85" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>399</v>
+        <v>445</v>
       </c>
       <c r="C85" t="s">
-        <v>400</v>
+        <v>446</v>
       </c>
       <c r="D85" t="s">
-        <v>411</v>
+        <v>447</v>
       </c>
       <c r="E85" t="s">
         <v>33</v>
@@ -8857,13 +8920,13 @@
         <v>54</v>
       </c>
       <c r="K85" t="s">
-        <v>340</v>
+        <v>40</v>
       </c>
       <c r="L85" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="M85" t="s">
-        <v>143</v>
+        <v>42</v>
       </c>
       <c r="N85" t="s">
         <v>33</v>
@@ -8875,16 +8938,16 @@
         <v>38</v>
       </c>
       <c r="Q85">
-        <v>44.99</v>
+        <v>59.99</v>
       </c>
       <c r="R85">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="Y85" t="s">
-        <v>401</v>
+        <v>448</v>
       </c>
       <c r="AA85" t="s">
-        <v>402</v>
+        <v>449</v>
       </c>
       <c r="AB85" t="s">
         <v>39</v>
@@ -8898,16 +8961,16 @@
     </row>
     <row r="86" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>394</v>
+        <v>450</v>
       </c>
       <c r="C86" t="s">
-        <v>395</v>
+        <v>451</v>
       </c>
       <c r="D86" t="s">
-        <v>412</v>
+        <v>452</v>
       </c>
       <c r="E86" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F86" t="s">
         <v>34</v>
@@ -8922,37 +8985,22 @@
         <v>54</v>
       </c>
       <c r="K86" t="s">
-        <v>340</v>
+        <v>40</v>
       </c>
       <c r="L86" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="M86" t="s">
-        <v>143</v>
-      </c>
-      <c r="N86" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O86">
-        <v>1</v>
-      </c>
-      <c r="P86" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q86">
-        <v>44.99</v>
-      </c>
-      <c r="R86">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Y86" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z86" t="s">
-        <v>397</v>
+        <v>453</v>
       </c>
       <c r="AA86" t="s">
-        <v>398</v>
+        <v>454</v>
       </c>
       <c r="AB86" t="s">
         <v>39</v>
@@ -8966,13 +9014,13 @@
     </row>
     <row r="87" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>338</v>
+        <v>403</v>
       </c>
       <c r="C87" t="s">
-        <v>339</v>
+        <v>404</v>
       </c>
       <c r="D87" t="s">
-        <v>662</v>
+        <v>455</v>
       </c>
       <c r="E87" t="s">
         <v>33</v>
@@ -8990,13 +9038,13 @@
         <v>54</v>
       </c>
       <c r="K87" t="s">
-        <v>340</v>
+        <v>40</v>
       </c>
       <c r="L87" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="M87" t="s">
-        <v>143</v>
+        <v>42</v>
       </c>
       <c r="N87" t="s">
         <v>33</v>
@@ -9008,16 +9056,22 @@
         <v>38</v>
       </c>
       <c r="Q87">
-        <v>44.99</v>
+        <v>59.99</v>
       </c>
       <c r="R87">
-        <v>7.5</v>
+        <v>10</v>
+      </c>
+      <c r="S87">
+        <v>5.99</v>
+      </c>
+      <c r="T87">
+        <v>1</v>
       </c>
       <c r="Y87" t="s">
-        <v>341</v>
+        <v>405</v>
       </c>
       <c r="AA87" t="s">
-        <v>342</v>
+        <v>406</v>
       </c>
       <c r="AB87" t="s">
         <v>39</v>
@@ -9031,13 +9085,13 @@
     </row>
     <row r="88" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>663</v>
+        <v>407</v>
       </c>
       <c r="C88" t="s">
-        <v>664</v>
+        <v>408</v>
       </c>
       <c r="D88" t="s">
-        <v>665</v>
+        <v>456</v>
       </c>
       <c r="E88" t="s">
         <v>33</v>
@@ -9055,13 +9109,13 @@
         <v>54</v>
       </c>
       <c r="K88" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="L88" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="M88" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="N88" t="s">
         <v>33</v>
@@ -9073,25 +9127,22 @@
         <v>38</v>
       </c>
       <c r="Q88">
-        <v>59.99</v>
+        <v>22.99</v>
       </c>
       <c r="R88">
-        <v>10</v>
+        <v>3.83</v>
       </c>
       <c r="Y88" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z88" t="s">
-        <v>666</v>
+        <v>409</v>
       </c>
       <c r="AA88" t="s">
-        <v>667</v>
+        <v>410</v>
       </c>
       <c r="AB88" t="s">
         <v>39</v>
       </c>
       <c r="AD88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="b">
         <v>0</v>
@@ -9099,13 +9150,13 @@
     </row>
     <row r="89" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>334</v>
+        <v>399</v>
       </c>
       <c r="C89" t="s">
-        <v>335</v>
+        <v>400</v>
       </c>
       <c r="D89" t="s">
-        <v>668</v>
+        <v>411</v>
       </c>
       <c r="E89" t="s">
         <v>33</v>
@@ -9123,13 +9174,13 @@
         <v>54</v>
       </c>
       <c r="K89" t="s">
-        <v>203</v>
+        <v>340</v>
       </c>
       <c r="L89" t="s">
-        <v>204</v>
+        <v>142</v>
       </c>
       <c r="M89" t="s">
-        <v>205</v>
+        <v>143</v>
       </c>
       <c r="N89" t="s">
         <v>33</v>
@@ -9141,16 +9192,16 @@
         <v>38</v>
       </c>
       <c r="Q89">
-        <v>69.989999999999995</v>
+        <v>44.99</v>
       </c>
       <c r="R89">
-        <v>11.67</v>
+        <v>7.5</v>
       </c>
       <c r="Y89" t="s">
-        <v>336</v>
+        <v>401</v>
       </c>
       <c r="AA89" t="s">
-        <v>337</v>
+        <v>402</v>
       </c>
       <c r="AB89" t="s">
         <v>39</v>
@@ -9164,13 +9215,13 @@
     </row>
     <row r="90" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="C90" t="s">
-        <v>327</v>
+        <v>395</v>
       </c>
       <c r="D90" t="s">
-        <v>669</v>
+        <v>412</v>
       </c>
       <c r="E90" t="s">
         <v>33</v>
@@ -9188,34 +9239,37 @@
         <v>54</v>
       </c>
       <c r="K90" t="s">
-        <v>48</v>
+        <v>340</v>
       </c>
       <c r="L90" t="s">
-        <v>49</v>
+        <v>142</v>
       </c>
       <c r="M90" t="s">
-        <v>50</v>
+        <v>143</v>
       </c>
       <c r="N90" t="s">
         <v>33</v>
       </c>
       <c r="O90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P90" t="s">
         <v>38</v>
       </c>
       <c r="Q90">
-        <v>75.98</v>
+        <v>44.99</v>
       </c>
       <c r="R90">
-        <v>12.66</v>
+        <v>7.5</v>
       </c>
       <c r="Y90" t="s">
-        <v>91</v>
+        <v>396</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>397</v>
       </c>
       <c r="AA90" t="s">
-        <v>328</v>
+        <v>398</v>
       </c>
       <c r="AB90" t="s">
         <v>39</v>
@@ -9229,13 +9283,13 @@
     </row>
     <row r="91" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="C91" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="D91" t="s">
-        <v>345</v>
+        <v>662</v>
       </c>
       <c r="E91" t="s">
         <v>33</v>
@@ -9253,13 +9307,13 @@
         <v>54</v>
       </c>
       <c r="K91" t="s">
-        <v>40</v>
+        <v>340</v>
       </c>
       <c r="L91" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="M91" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="N91" t="s">
         <v>33</v>
@@ -9271,16 +9325,16 @@
         <v>38</v>
       </c>
       <c r="Q91">
-        <v>59.99</v>
+        <v>44.99</v>
       </c>
       <c r="R91">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="Y91" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="AA91" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="AB91" t="s">
         <v>39</v>
@@ -9294,13 +9348,13 @@
     </row>
     <row r="92" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>288</v>
+        <v>663</v>
       </c>
       <c r="C92" t="s">
-        <v>289</v>
+        <v>664</v>
       </c>
       <c r="D92" t="s">
-        <v>348</v>
+        <v>665</v>
       </c>
       <c r="E92" t="s">
         <v>33</v>
@@ -9315,43 +9369,46 @@
         <v>36</v>
       </c>
       <c r="J92" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K92" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L92" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M92" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N92" t="s">
         <v>33</v>
       </c>
       <c r="O92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P92" t="s">
         <v>38</v>
       </c>
       <c r="Q92">
-        <v>75.98</v>
+        <v>59.99</v>
       </c>
       <c r="R92">
-        <v>12.66</v>
+        <v>10</v>
       </c>
       <c r="Y92" t="s">
-        <v>290</v>
+        <v>62</v>
+      </c>
+      <c r="Z92" t="s">
+        <v>666</v>
       </c>
       <c r="AA92" t="s">
-        <v>291</v>
+        <v>667</v>
       </c>
       <c r="AB92" t="s">
         <v>39</v>
       </c>
       <c r="AD92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG92" t="b">
         <v>0</v>
@@ -9359,13 +9416,13 @@
     </row>
     <row r="93" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="C93" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="D93" t="s">
-        <v>351</v>
+        <v>668</v>
       </c>
       <c r="E93" t="s">
         <v>33</v>
@@ -9383,13 +9440,13 @@
         <v>54</v>
       </c>
       <c r="K93" t="s">
-        <v>48</v>
+        <v>203</v>
       </c>
       <c r="L93" t="s">
-        <v>49</v>
+        <v>204</v>
       </c>
       <c r="M93" t="s">
-        <v>50</v>
+        <v>205</v>
       </c>
       <c r="N93" t="s">
         <v>33</v>
@@ -9401,19 +9458,16 @@
         <v>38</v>
       </c>
       <c r="Q93">
-        <v>37.99</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="R93">
-        <v>6.33</v>
+        <v>11.67</v>
       </c>
       <c r="Y93" t="s">
-        <v>352</v>
-      </c>
-      <c r="Z93" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="AA93" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="AB93" t="s">
         <v>39</v>
@@ -9427,13 +9481,13 @@
     </row>
     <row r="94" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>355</v>
+        <v>326</v>
       </c>
       <c r="C94" t="s">
-        <v>356</v>
+        <v>327</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>669</v>
       </c>
       <c r="E94" t="s">
         <v>33</v>
@@ -9451,34 +9505,34 @@
         <v>54</v>
       </c>
       <c r="K94" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L94" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M94" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N94" t="s">
         <v>33</v>
       </c>
       <c r="O94">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P94" t="s">
         <v>38</v>
       </c>
       <c r="Q94">
-        <v>11.99</v>
+        <v>75.98</v>
       </c>
       <c r="R94">
-        <v>2</v>
+        <v>12.66</v>
       </c>
       <c r="Y94" t="s">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="AA94" t="s">
-        <v>358</v>
+        <v>328</v>
       </c>
       <c r="AB94" t="s">
         <v>39</v>
@@ -9492,13 +9546,13 @@
     </row>
     <row r="95" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>359</v>
+        <v>343</v>
       </c>
       <c r="C95" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="D95" t="s">
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="E95" t="s">
         <v>33</v>
@@ -9516,37 +9570,34 @@
         <v>54</v>
       </c>
       <c r="K95" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L95" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M95" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N95" t="s">
         <v>33</v>
       </c>
       <c r="O95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P95" t="s">
         <v>38</v>
       </c>
       <c r="Q95">
-        <v>75.98</v>
+        <v>59.99</v>
       </c>
       <c r="R95">
-        <v>12.66</v>
+        <v>10</v>
       </c>
       <c r="Y95" t="s">
-        <v>101</v>
-      </c>
-      <c r="Z95" t="s">
-        <v>59</v>
+        <v>346</v>
       </c>
       <c r="AA95" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="AB95" t="s">
         <v>39</v>
@@ -9560,13 +9611,13 @@
     </row>
     <row r="96" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>363</v>
+        <v>288</v>
       </c>
       <c r="C96" t="s">
-        <v>364</v>
+        <v>289</v>
       </c>
       <c r="D96" t="s">
-        <v>365</v>
+        <v>348</v>
       </c>
       <c r="E96" t="s">
         <v>33</v>
@@ -9581,37 +9632,37 @@
         <v>36</v>
       </c>
       <c r="J96" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K96" t="s">
-        <v>260</v>
+        <v>48</v>
       </c>
       <c r="L96" t="s">
-        <v>261</v>
+        <v>49</v>
       </c>
       <c r="M96" t="s">
-        <v>262</v>
+        <v>50</v>
       </c>
       <c r="N96" t="s">
         <v>33</v>
       </c>
       <c r="O96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P96" t="s">
         <v>38</v>
       </c>
       <c r="Q96">
-        <v>24.49</v>
+        <v>75.98</v>
       </c>
       <c r="R96">
-        <v>4.08</v>
+        <v>12.66</v>
       </c>
       <c r="Y96" t="s">
-        <v>366</v>
+        <v>290</v>
       </c>
       <c r="AA96" t="s">
-        <v>367</v>
+        <v>291</v>
       </c>
       <c r="AB96" t="s">
         <v>39</v>
@@ -9625,13 +9676,13 @@
     </row>
     <row r="97" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>265</v>
+        <v>349</v>
       </c>
       <c r="C97" t="s">
-        <v>266</v>
+        <v>350</v>
       </c>
       <c r="D97" t="s">
-        <v>368</v>
+        <v>351</v>
       </c>
       <c r="E97" t="s">
         <v>33</v>
@@ -9673,10 +9724,13 @@
         <v>6.33</v>
       </c>
       <c r="Y97" t="s">
-        <v>267</v>
+        <v>352</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>353</v>
       </c>
       <c r="AA97" t="s">
-        <v>268</v>
+        <v>354</v>
       </c>
       <c r="AB97" t="s">
         <v>39</v>
@@ -9690,13 +9744,13 @@
     </row>
     <row r="98" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="C98" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="D98" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="E98" t="s">
         <v>33</v>
@@ -9737,17 +9791,11 @@
       <c r="R98">
         <v>2</v>
       </c>
-      <c r="S98">
-        <v>5.99</v>
-      </c>
-      <c r="T98">
-        <v>1</v>
-      </c>
       <c r="Y98" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="AA98" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="AB98" t="s">
         <v>39</v>
@@ -9761,13 +9809,13 @@
     </row>
     <row r="99" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>373</v>
+        <v>359</v>
       </c>
       <c r="C99" t="s">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="D99" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="E99" t="s">
         <v>33</v>
@@ -9785,34 +9833,37 @@
         <v>54</v>
       </c>
       <c r="K99" t="s">
-        <v>260</v>
+        <v>48</v>
       </c>
       <c r="L99" t="s">
-        <v>261</v>
+        <v>49</v>
       </c>
       <c r="M99" t="s">
-        <v>262</v>
+        <v>50</v>
       </c>
       <c r="N99" t="s">
         <v>33</v>
       </c>
       <c r="O99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P99" t="s">
         <v>38</v>
       </c>
       <c r="Q99">
-        <v>24.49</v>
+        <v>75.98</v>
       </c>
       <c r="R99">
-        <v>4.08</v>
+        <v>12.66</v>
       </c>
       <c r="Y99" t="s">
-        <v>376</v>
+        <v>101</v>
+      </c>
+      <c r="Z99" t="s">
+        <v>59</v>
       </c>
       <c r="AA99" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="AB99" t="s">
         <v>39</v>
@@ -9826,13 +9877,13 @@
     </row>
     <row r="100" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="C100" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="D100" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="E100" t="s">
         <v>33</v>
@@ -9850,13 +9901,13 @@
         <v>54</v>
       </c>
       <c r="K100" t="s">
-        <v>40</v>
+        <v>260</v>
       </c>
       <c r="L100" t="s">
-        <v>41</v>
+        <v>261</v>
       </c>
       <c r="M100" t="s">
-        <v>42</v>
+        <v>262</v>
       </c>
       <c r="N100" t="s">
         <v>33</v>
@@ -9868,16 +9919,16 @@
         <v>38</v>
       </c>
       <c r="Q100">
-        <v>59.99</v>
+        <v>24.49</v>
       </c>
       <c r="R100">
-        <v>10</v>
+        <v>4.08</v>
       </c>
       <c r="Y100" t="s">
-        <v>57</v>
+        <v>366</v>
       </c>
       <c r="AA100" t="s">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="AB100" t="s">
         <v>39</v>
@@ -9891,13 +9942,13 @@
     </row>
     <row r="101" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>382</v>
+        <v>265</v>
       </c>
       <c r="C101" t="s">
-        <v>383</v>
+        <v>266</v>
       </c>
       <c r="D101" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
       <c r="E101" t="s">
         <v>33</v>
@@ -9915,13 +9966,13 @@
         <v>54</v>
       </c>
       <c r="K101" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L101" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M101" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N101" t="s">
         <v>33</v>
@@ -9933,16 +9984,16 @@
         <v>38</v>
       </c>
       <c r="Q101">
-        <v>11.99</v>
+        <v>37.99</v>
       </c>
       <c r="R101">
-        <v>2</v>
+        <v>6.33</v>
       </c>
       <c r="Y101" t="s">
-        <v>385</v>
+        <v>267</v>
       </c>
       <c r="AA101" t="s">
-        <v>386</v>
+        <v>268</v>
       </c>
       <c r="AB101" t="s">
         <v>39</v>
@@ -9956,16 +10007,16 @@
     </row>
     <row r="102" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="C102" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="D102" t="s">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="E102" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F102" t="s">
         <v>34</v>
@@ -9980,25 +10031,40 @@
         <v>54</v>
       </c>
       <c r="K102" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="L102" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="M102" t="s">
-        <v>45</v>
+        <v>74</v>
+      </c>
+      <c r="N102" t="s">
+        <v>33</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P102" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q102">
+        <v>11.99</v>
+      </c>
+      <c r="R102">
+        <v>2</v>
+      </c>
+      <c r="S102">
+        <v>5.99</v>
+      </c>
+      <c r="T102">
+        <v>1</v>
       </c>
       <c r="Y102" t="s">
-        <v>390</v>
-      </c>
-      <c r="Z102" t="s">
-        <v>391</v>
+        <v>84</v>
       </c>
       <c r="AA102" t="s">
-        <v>392</v>
+        <v>372</v>
       </c>
       <c r="AB102" t="s">
         <v>39</v>
@@ -10012,13 +10078,13 @@
     </row>
     <row r="103" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>323</v>
+        <v>373</v>
       </c>
       <c r="C103" t="s">
-        <v>324</v>
+        <v>374</v>
       </c>
       <c r="D103" t="s">
-        <v>393</v>
+        <v>375</v>
       </c>
       <c r="E103" t="s">
         <v>33</v>
@@ -10036,13 +10102,13 @@
         <v>54</v>
       </c>
       <c r="K103" t="s">
-        <v>95</v>
+        <v>260</v>
       </c>
       <c r="L103" t="s">
-        <v>85</v>
+        <v>261</v>
       </c>
       <c r="M103" t="s">
-        <v>86</v>
+        <v>262</v>
       </c>
       <c r="N103" t="s">
         <v>33</v>
@@ -10054,16 +10120,16 @@
         <v>38</v>
       </c>
       <c r="Q103">
-        <v>14.99</v>
+        <v>24.49</v>
       </c>
       <c r="R103">
-        <v>2.5</v>
+        <v>4.08</v>
       </c>
       <c r="Y103" t="s">
-        <v>58</v>
+        <v>376</v>
       </c>
       <c r="AA103" t="s">
-        <v>325</v>
+        <v>377</v>
       </c>
       <c r="AB103" t="s">
         <v>39</v>
@@ -10077,13 +10143,13 @@
     </row>
     <row r="104" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>318</v>
+        <v>378</v>
       </c>
       <c r="C104" t="s">
-        <v>319</v>
+        <v>379</v>
       </c>
       <c r="D104" t="s">
-        <v>320</v>
+        <v>380</v>
       </c>
       <c r="E104" t="s">
         <v>33</v>
@@ -10101,13 +10167,13 @@
         <v>54</v>
       </c>
       <c r="K104" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L104" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M104" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N104" t="s">
         <v>33</v>
@@ -10119,19 +10185,16 @@
         <v>38</v>
       </c>
       <c r="Q104">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R104">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y104" t="s">
-        <v>321</v>
-      </c>
-      <c r="Z104" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="AA104" t="s">
-        <v>322</v>
+        <v>381</v>
       </c>
       <c r="AB104" t="s">
         <v>39</v>
@@ -10145,13 +10208,13 @@
     </row>
     <row r="105" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>329</v>
+        <v>382</v>
       </c>
       <c r="C105" t="s">
-        <v>330</v>
+        <v>383</v>
       </c>
       <c r="D105" t="s">
-        <v>331</v>
+        <v>384</v>
       </c>
       <c r="E105" t="s">
         <v>33</v>
@@ -10169,13 +10232,13 @@
         <v>54</v>
       </c>
       <c r="K105" t="s">
-        <v>260</v>
+        <v>72</v>
       </c>
       <c r="L105" t="s">
-        <v>261</v>
+        <v>73</v>
       </c>
       <c r="M105" t="s">
-        <v>262</v>
+        <v>74</v>
       </c>
       <c r="N105" t="s">
         <v>33</v>
@@ -10187,16 +10250,16 @@
         <v>38</v>
       </c>
       <c r="Q105">
-        <v>24.49</v>
+        <v>11.99</v>
       </c>
       <c r="R105">
-        <v>4.08</v>
+        <v>2</v>
       </c>
       <c r="Y105" t="s">
-        <v>332</v>
+        <v>385</v>
       </c>
       <c r="AA105" t="s">
-        <v>333</v>
+        <v>386</v>
       </c>
       <c r="AB105" t="s">
         <v>39</v>
@@ -10210,16 +10273,16 @@
     </row>
     <row r="106" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>670</v>
+        <v>387</v>
       </c>
       <c r="C106" t="s">
-        <v>671</v>
+        <v>388</v>
       </c>
       <c r="D106" t="s">
-        <v>672</v>
+        <v>389</v>
       </c>
       <c r="E106" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F106" t="s">
         <v>34</v>
@@ -10234,34 +10297,25 @@
         <v>54</v>
       </c>
       <c r="K106" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L106" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M106" t="s">
-        <v>42</v>
-      </c>
-      <c r="N106" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O106">
-        <v>1</v>
-      </c>
-      <c r="P106" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q106">
-        <v>59.99</v>
-      </c>
-      <c r="R106">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y106" t="s">
-        <v>673</v>
+        <v>390</v>
+      </c>
+      <c r="Z106" t="s">
+        <v>391</v>
       </c>
       <c r="AA106" t="s">
-        <v>674</v>
+        <v>392</v>
       </c>
       <c r="AB106" t="s">
         <v>39</v>
@@ -10275,13 +10329,13 @@
     </row>
     <row r="107" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>675</v>
+        <v>323</v>
       </c>
       <c r="C107" t="s">
-        <v>676</v>
+        <v>324</v>
       </c>
       <c r="D107" t="s">
-        <v>677</v>
+        <v>393</v>
       </c>
       <c r="E107" t="s">
         <v>33</v>
@@ -10299,13 +10353,13 @@
         <v>54</v>
       </c>
       <c r="K107" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="L107" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="M107" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="N107" t="s">
         <v>33</v>
@@ -10317,16 +10371,16 @@
         <v>38</v>
       </c>
       <c r="Q107">
-        <v>37.99</v>
+        <v>14.99</v>
       </c>
       <c r="R107">
-        <v>6.33</v>
+        <v>2.5</v>
       </c>
       <c r="Y107" t="s">
-        <v>678</v>
+        <v>58</v>
       </c>
       <c r="AA107" t="s">
-        <v>679</v>
+        <v>325</v>
       </c>
       <c r="AB107" t="s">
         <v>39</v>
@@ -10340,13 +10394,13 @@
     </row>
     <row r="108" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>680</v>
+        <v>318</v>
       </c>
       <c r="C108" t="s">
-        <v>681</v>
+        <v>319</v>
       </c>
       <c r="D108" t="s">
-        <v>682</v>
+        <v>320</v>
       </c>
       <c r="E108" t="s">
         <v>33</v>
@@ -10364,13 +10418,13 @@
         <v>54</v>
       </c>
       <c r="K108" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L108" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M108" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N108" t="s">
         <v>33</v>
@@ -10382,19 +10436,19 @@
         <v>38</v>
       </c>
       <c r="Q108">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R108">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y108" t="s">
-        <v>683</v>
+        <v>321</v>
       </c>
       <c r="Z108" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="AA108" t="s">
-        <v>684</v>
+        <v>322</v>
       </c>
       <c r="AB108" t="s">
         <v>39</v>
@@ -10408,13 +10462,13 @@
     </row>
     <row r="109" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>685</v>
+        <v>329</v>
       </c>
       <c r="C109" t="s">
-        <v>686</v>
+        <v>330</v>
       </c>
       <c r="D109" t="s">
-        <v>687</v>
+        <v>331</v>
       </c>
       <c r="E109" t="s">
         <v>33</v>
@@ -10432,13 +10486,13 @@
         <v>54</v>
       </c>
       <c r="K109" t="s">
-        <v>48</v>
+        <v>260</v>
       </c>
       <c r="L109" t="s">
-        <v>49</v>
+        <v>261</v>
       </c>
       <c r="M109" t="s">
-        <v>50</v>
+        <v>262</v>
       </c>
       <c r="N109" t="s">
         <v>33</v>
@@ -10450,16 +10504,16 @@
         <v>38</v>
       </c>
       <c r="Q109">
-        <v>37.99</v>
+        <v>24.49</v>
       </c>
       <c r="R109">
-        <v>6.33</v>
+        <v>4.08</v>
       </c>
       <c r="Y109" t="s">
-        <v>52</v>
+        <v>332</v>
       </c>
       <c r="AA109" t="s">
-        <v>688</v>
+        <v>333</v>
       </c>
       <c r="AB109" t="s">
         <v>39</v>
@@ -10473,16 +10527,16 @@
     </row>
     <row r="110" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="C110" t="s">
-        <v>690</v>
+        <v>671</v>
       </c>
       <c r="D110" t="s">
-        <v>691</v>
+        <v>672</v>
       </c>
       <c r="E110" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F110" t="s">
         <v>34</v>
@@ -10494,28 +10548,37 @@
         <v>36</v>
       </c>
       <c r="J110" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K110" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L110" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M110" t="s">
-        <v>50</v>
+        <v>42</v>
+      </c>
+      <c r="N110" t="s">
+        <v>33</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P110" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q110">
+        <v>59.99</v>
+      </c>
+      <c r="R110">
+        <v>10</v>
       </c>
       <c r="Y110" t="s">
-        <v>692</v>
-      </c>
-      <c r="Z110" t="s">
-        <v>693</v>
+        <v>673</v>
       </c>
       <c r="AA110" t="s">
-        <v>694</v>
+        <v>674</v>
       </c>
       <c r="AB110" t="s">
         <v>39</v>
@@ -10529,16 +10592,16 @@
     </row>
     <row r="111" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
       <c r="C111" t="s">
-        <v>696</v>
+        <v>676</v>
       </c>
       <c r="D111" t="s">
-        <v>697</v>
+        <v>677</v>
       </c>
       <c r="E111" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F111" t="s">
         <v>34</v>
@@ -10550,7 +10613,7 @@
         <v>36</v>
       </c>
       <c r="J111" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K111" t="s">
         <v>48</v>
@@ -10561,17 +10624,26 @@
       <c r="M111" t="s">
         <v>50</v>
       </c>
+      <c r="N111" t="s">
+        <v>33</v>
+      </c>
       <c r="O111">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P111" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q111">
+        <v>37.99</v>
+      </c>
+      <c r="R111">
+        <v>6.33</v>
       </c>
       <c r="Y111" t="s">
-        <v>692</v>
-      </c>
-      <c r="Z111" t="s">
-        <v>693</v>
+        <v>678</v>
       </c>
       <c r="AA111" t="s">
-        <v>694</v>
+        <v>679</v>
       </c>
       <c r="AB111" t="s">
         <v>39</v>
@@ -10585,13 +10657,13 @@
     </row>
     <row r="112" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>300</v>
+        <v>680</v>
       </c>
       <c r="C112" t="s">
-        <v>301</v>
+        <v>681</v>
       </c>
       <c r="D112" t="s">
-        <v>698</v>
+        <v>682</v>
       </c>
       <c r="E112" t="s">
         <v>33</v>
@@ -10609,13 +10681,13 @@
         <v>54</v>
       </c>
       <c r="K112" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="L112" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="M112" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="N112" t="s">
         <v>33</v>
@@ -10627,16 +10699,19 @@
         <v>38</v>
       </c>
       <c r="Q112">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R112">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y112" t="s">
-        <v>58</v>
+        <v>683</v>
+      </c>
+      <c r="Z112" t="s">
+        <v>76</v>
       </c>
       <c r="AA112" t="s">
-        <v>302</v>
+        <v>684</v>
       </c>
       <c r="AB112" t="s">
         <v>39</v>
@@ -10650,16 +10725,16 @@
     </row>
     <row r="113" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="C113" t="s">
-        <v>700</v>
+        <v>686</v>
       </c>
       <c r="D113" t="s">
-        <v>701</v>
+        <v>687</v>
       </c>
       <c r="E113" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F113" t="s">
         <v>34</v>
@@ -10682,17 +10757,26 @@
       <c r="M113" t="s">
         <v>50</v>
       </c>
+      <c r="N113" t="s">
+        <v>33</v>
+      </c>
       <c r="O113">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P113" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q113">
+        <v>37.99</v>
+      </c>
+      <c r="R113">
+        <v>6.33</v>
       </c>
       <c r="Y113" t="s">
-        <v>692</v>
-      </c>
-      <c r="Z113" t="s">
-        <v>693</v>
+        <v>52</v>
       </c>
       <c r="AA113" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="AB113" t="s">
         <v>39</v>
@@ -10706,16 +10790,16 @@
     </row>
     <row r="114" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>303</v>
+        <v>689</v>
       </c>
       <c r="C114" t="s">
-        <v>304</v>
+        <v>690</v>
       </c>
       <c r="D114" t="s">
-        <v>702</v>
+        <v>691</v>
       </c>
       <c r="E114" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F114" t="s">
         <v>34</v>
@@ -10727,37 +10811,28 @@
         <v>36</v>
       </c>
       <c r="J114" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K114" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L114" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M114" t="s">
-        <v>42</v>
-      </c>
-      <c r="N114" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="O114">
-        <v>1</v>
-      </c>
-      <c r="P114" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q114">
-        <v>59.99</v>
-      </c>
-      <c r="R114">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y114" t="s">
-        <v>305</v>
+        <v>692</v>
+      </c>
+      <c r="Z114" t="s">
+        <v>693</v>
       </c>
       <c r="AA114" t="s">
-        <v>306</v>
+        <v>694</v>
       </c>
       <c r="AB114" t="s">
         <v>39</v>
@@ -10771,16 +10846,16 @@
     </row>
     <row r="115" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>292</v>
+        <v>695</v>
       </c>
       <c r="C115" t="s">
-        <v>293</v>
+        <v>696</v>
       </c>
       <c r="D115" t="s">
-        <v>294</v>
+        <v>697</v>
       </c>
       <c r="E115" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F115" t="s">
         <v>34</v>
@@ -10795,37 +10870,25 @@
         <v>37</v>
       </c>
       <c r="K115" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L115" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M115" t="s">
-        <v>42</v>
-      </c>
-      <c r="N115" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="O115">
-        <v>1</v>
-      </c>
-      <c r="P115" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q115">
-        <v>59.99</v>
-      </c>
-      <c r="R115">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y115" t="s">
-        <v>77</v>
+        <v>692</v>
       </c>
       <c r="Z115" t="s">
-        <v>92</v>
+        <v>693</v>
       </c>
       <c r="AA115" t="s">
-        <v>295</v>
+        <v>694</v>
       </c>
       <c r="AB115" t="s">
         <v>39</v>
@@ -10839,13 +10902,13 @@
     </row>
     <row r="116" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C116" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D116" t="s">
-        <v>298</v>
+        <v>698</v>
       </c>
       <c r="E116" t="s">
         <v>33</v>
@@ -10860,16 +10923,16 @@
         <v>36</v>
       </c>
       <c r="J116" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K116" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="L116" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="M116" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="N116" t="s">
         <v>33</v>
@@ -10881,19 +10944,16 @@
         <v>38</v>
       </c>
       <c r="Q116">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="R116">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="Y116" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z116" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="AA116" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AB116" t="s">
         <v>39</v>
@@ -10907,16 +10967,16 @@
     </row>
     <row r="117" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>307</v>
+        <v>699</v>
       </c>
       <c r="C117" t="s">
-        <v>308</v>
+        <v>700</v>
       </c>
       <c r="D117" t="s">
-        <v>309</v>
+        <v>701</v>
       </c>
       <c r="E117" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F117" t="s">
         <v>34</v>
@@ -10928,37 +10988,28 @@
         <v>36</v>
       </c>
       <c r="J117" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K117" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="L117" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="M117" t="s">
-        <v>89</v>
-      </c>
-      <c r="N117" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="O117">
-        <v>1</v>
-      </c>
-      <c r="P117" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q117">
-        <v>20.49</v>
-      </c>
-      <c r="R117">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="Y117" t="s">
-        <v>310</v>
+        <v>692</v>
+      </c>
+      <c r="Z117" t="s">
+        <v>693</v>
       </c>
       <c r="AA117" t="s">
-        <v>311</v>
+        <v>694</v>
       </c>
       <c r="AB117" t="s">
         <v>39</v>
@@ -10972,13 +11023,13 @@
     </row>
     <row r="118" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="C118" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="D118" t="s">
-        <v>314</v>
+        <v>702</v>
       </c>
       <c r="E118" t="s">
         <v>33</v>
@@ -10993,7 +11044,7 @@
         <v>36</v>
       </c>
       <c r="J118" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K118" t="s">
         <v>40</v>
@@ -11020,13 +11071,10 @@
         <v>10</v>
       </c>
       <c r="Y118" t="s">
-        <v>100</v>
-      </c>
-      <c r="Z118" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="AA118" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="AB118" t="s">
         <v>39</v>
@@ -11040,13 +11088,13 @@
     </row>
     <row r="119" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>253</v>
+        <v>292</v>
       </c>
       <c r="C119" t="s">
-        <v>254</v>
+        <v>293</v>
       </c>
       <c r="D119" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="E119" t="s">
         <v>33</v>
@@ -11061,7 +11109,7 @@
         <v>36</v>
       </c>
       <c r="J119" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K119" t="s">
         <v>40</v>
@@ -11088,13 +11136,13 @@
         <v>10</v>
       </c>
       <c r="Y119" t="s">
-        <v>255</v>
+        <v>77</v>
       </c>
       <c r="Z119" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="AA119" t="s">
-        <v>256</v>
+        <v>295</v>
       </c>
       <c r="AB119" t="s">
         <v>39</v>
@@ -11108,13 +11156,13 @@
     </row>
     <row r="120" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>257</v>
+        <v>296</v>
       </c>
       <c r="C120" t="s">
-        <v>258</v>
+        <v>297</v>
       </c>
       <c r="D120" t="s">
-        <v>259</v>
+        <v>298</v>
       </c>
       <c r="E120" t="s">
         <v>33</v>
@@ -11129,16 +11177,16 @@
         <v>36</v>
       </c>
       <c r="J120" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K120" t="s">
-        <v>260</v>
+        <v>40</v>
       </c>
       <c r="L120" t="s">
-        <v>261</v>
+        <v>41</v>
       </c>
       <c r="M120" t="s">
-        <v>262</v>
+        <v>42</v>
       </c>
       <c r="N120" t="s">
         <v>33</v>
@@ -11150,19 +11198,19 @@
         <v>38</v>
       </c>
       <c r="Q120">
-        <v>24.49</v>
+        <v>59.99</v>
       </c>
       <c r="R120">
-        <v>4.08</v>
+        <v>10</v>
       </c>
       <c r="Y120" t="s">
-        <v>263</v>
+        <v>62</v>
       </c>
       <c r="Z120" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="AA120" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="AB120" t="s">
         <v>39</v>
@@ -11176,13 +11224,13 @@
     </row>
     <row r="121" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>269</v>
+        <v>307</v>
       </c>
       <c r="C121" t="s">
-        <v>270</v>
+        <v>308</v>
       </c>
       <c r="D121" t="s">
-        <v>271</v>
+        <v>309</v>
       </c>
       <c r="E121" t="s">
         <v>33</v>
@@ -11197,16 +11245,16 @@
         <v>36</v>
       </c>
       <c r="J121" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K121" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="L121" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="M121" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="N121" t="s">
         <v>33</v>
@@ -11218,16 +11266,16 @@
         <v>38</v>
       </c>
       <c r="Q121">
-        <v>59.99</v>
+        <v>20.49</v>
       </c>
       <c r="R121">
-        <v>10</v>
+        <v>3.42</v>
       </c>
       <c r="Y121" t="s">
-        <v>272</v>
+        <v>310</v>
       </c>
       <c r="AA121" t="s">
-        <v>273</v>
+        <v>311</v>
       </c>
       <c r="AB121" t="s">
         <v>39</v>
@@ -11241,13 +11289,13 @@
     </row>
     <row r="122" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>149</v>
+        <v>312</v>
       </c>
       <c r="C122" t="s">
-        <v>150</v>
+        <v>313</v>
       </c>
       <c r="D122" t="s">
-        <v>274</v>
+        <v>314</v>
       </c>
       <c r="E122" t="s">
         <v>33</v>
@@ -11262,7 +11310,7 @@
         <v>36</v>
       </c>
       <c r="J122" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K122" t="s">
         <v>40</v>
@@ -11289,10 +11337,13 @@
         <v>10</v>
       </c>
       <c r="Y122" t="s">
-        <v>63</v>
+        <v>100</v>
+      </c>
+      <c r="Z122" t="s">
+        <v>315</v>
       </c>
       <c r="AA122" t="s">
-        <v>151</v>
+        <v>316</v>
       </c>
       <c r="AB122" t="s">
         <v>39</v>
@@ -11306,13 +11357,13 @@
     </row>
     <row r="123" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="C123" t="s">
-        <v>276</v>
+        <v>254</v>
       </c>
       <c r="D123" t="s">
-        <v>277</v>
+        <v>317</v>
       </c>
       <c r="E123" t="s">
         <v>33</v>
@@ -11342,25 +11393,25 @@
         <v>33</v>
       </c>
       <c r="O123">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P123" t="s">
         <v>38</v>
       </c>
       <c r="Q123">
-        <v>119.98</v>
+        <v>59.99</v>
       </c>
       <c r="R123">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Y123" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="Z123" t="s">
-        <v>279</v>
+        <v>102</v>
       </c>
       <c r="AA123" t="s">
-        <v>280</v>
+        <v>256</v>
       </c>
       <c r="AB123" t="s">
         <v>39</v>
@@ -11374,13 +11425,13 @@
     </row>
     <row r="124" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>281</v>
+        <v>257</v>
       </c>
       <c r="C124" t="s">
-        <v>282</v>
+        <v>258</v>
       </c>
       <c r="D124" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="E124" t="s">
         <v>33</v>
@@ -11395,16 +11446,16 @@
         <v>36</v>
       </c>
       <c r="J124" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K124" t="s">
-        <v>72</v>
+        <v>260</v>
       </c>
       <c r="L124" t="s">
-        <v>73</v>
+        <v>261</v>
       </c>
       <c r="M124" t="s">
-        <v>74</v>
+        <v>262</v>
       </c>
       <c r="N124" t="s">
         <v>33</v>
@@ -11416,16 +11467,19 @@
         <v>38</v>
       </c>
       <c r="Q124">
-        <v>11.99</v>
+        <v>24.49</v>
       </c>
       <c r="R124">
-        <v>2</v>
+        <v>4.08</v>
       </c>
       <c r="Y124" t="s">
-        <v>75</v>
+        <v>263</v>
+      </c>
+      <c r="Z124" t="s">
+        <v>64</v>
       </c>
       <c r="AA124" t="s">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="AB124" t="s">
         <v>39</v>
@@ -11439,16 +11493,16 @@
     </row>
     <row r="125" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>238</v>
+        <v>269</v>
       </c>
       <c r="C125" t="s">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="D125" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="E125" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F125" t="s">
         <v>34</v>
@@ -11471,14 +11525,26 @@
       <c r="M125" t="s">
         <v>42</v>
       </c>
+      <c r="N125" t="s">
+        <v>33</v>
+      </c>
       <c r="O125">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P125" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q125">
+        <v>59.99</v>
+      </c>
+      <c r="R125">
+        <v>10</v>
       </c>
       <c r="Y125" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="AA125" t="s">
-        <v>241</v>
+        <v>273</v>
       </c>
       <c r="AB125" t="s">
         <v>39</v>
@@ -11492,13 +11558,13 @@
     </row>
     <row r="126" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>224</v>
+        <v>149</v>
       </c>
       <c r="C126" t="s">
-        <v>225</v>
+        <v>150</v>
       </c>
       <c r="D126" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="E126" t="s">
         <v>33</v>
@@ -11540,10 +11606,10 @@
         <v>10</v>
       </c>
       <c r="Y126" t="s">
-        <v>226</v>
+        <v>63</v>
       </c>
       <c r="AA126" t="s">
-        <v>227</v>
+        <v>151</v>
       </c>
       <c r="AB126" t="s">
         <v>39</v>
@@ -11557,13 +11623,13 @@
     </row>
     <row r="127" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>213</v>
+        <v>275</v>
       </c>
       <c r="C127" t="s">
-        <v>214</v>
+        <v>276</v>
       </c>
       <c r="D127" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="E127" t="s">
         <v>33</v>
@@ -11593,25 +11659,25 @@
         <v>33</v>
       </c>
       <c r="O127">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P127" t="s">
         <v>38</v>
       </c>
       <c r="Q127">
-        <v>59.99</v>
+        <v>119.98</v>
       </c>
       <c r="R127">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y127" t="s">
-        <v>215</v>
+        <v>278</v>
       </c>
       <c r="Z127" t="s">
-        <v>216</v>
+        <v>279</v>
       </c>
       <c r="AA127" t="s">
-        <v>217</v>
+        <v>280</v>
       </c>
       <c r="AB127" t="s">
         <v>39</v>
@@ -11625,13 +11691,13 @@
     </row>
     <row r="128" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>218</v>
+        <v>281</v>
       </c>
       <c r="C128" t="s">
-        <v>219</v>
+        <v>282</v>
       </c>
       <c r="D128" t="s">
-        <v>220</v>
+        <v>283</v>
       </c>
       <c r="E128" t="s">
         <v>33</v>
@@ -11646,16 +11712,16 @@
         <v>36</v>
       </c>
       <c r="J128" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K128" t="s">
-        <v>203</v>
+        <v>72</v>
       </c>
       <c r="L128" t="s">
-        <v>204</v>
+        <v>73</v>
       </c>
       <c r="M128" t="s">
-        <v>205</v>
+        <v>74</v>
       </c>
       <c r="N128" t="s">
         <v>33</v>
@@ -11667,19 +11733,16 @@
         <v>38</v>
       </c>
       <c r="Q128">
-        <v>69.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R128">
-        <v>11.67</v>
+        <v>2</v>
       </c>
       <c r="Y128" t="s">
-        <v>221</v>
-      </c>
-      <c r="Z128" t="s">
-        <v>222</v>
+        <v>75</v>
       </c>
       <c r="AA128" t="s">
-        <v>223</v>
+        <v>284</v>
       </c>
       <c r="AB128" t="s">
         <v>39</v>
@@ -11693,16 +11756,16 @@
     </row>
     <row r="129" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="C129" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="D129" t="s">
-        <v>230</v>
+        <v>285</v>
       </c>
       <c r="E129" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F129" t="s">
         <v>34</v>
@@ -11725,26 +11788,14 @@
       <c r="M129" t="s">
         <v>42</v>
       </c>
-      <c r="N129" t="s">
-        <v>33</v>
-      </c>
       <c r="O129">
-        <v>1</v>
-      </c>
-      <c r="P129" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q129">
-        <v>59.99</v>
-      </c>
-      <c r="R129">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y129" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="AA129" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="AB129" t="s">
         <v>39</v>
@@ -11758,13 +11809,13 @@
     </row>
     <row r="130" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="C130" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="D130" t="s">
-        <v>235</v>
+        <v>286</v>
       </c>
       <c r="E130" t="s">
         <v>33</v>
@@ -11782,13 +11833,13 @@
         <v>54</v>
       </c>
       <c r="K130" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="L130" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="M130" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="N130" t="s">
         <v>33</v>
@@ -11800,16 +11851,16 @@
         <v>38</v>
       </c>
       <c r="Q130">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R130">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y130" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="AA130" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="AB130" t="s">
         <v>39</v>
@@ -11823,16 +11874,16 @@
     </row>
     <row r="131" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>242</v>
+        <v>213</v>
       </c>
       <c r="C131" t="s">
-        <v>243</v>
+        <v>214</v>
       </c>
       <c r="D131" t="s">
-        <v>244</v>
+        <v>287</v>
       </c>
       <c r="E131" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F131" t="s">
         <v>34</v>
@@ -11855,14 +11906,29 @@
       <c r="M131" t="s">
         <v>42</v>
       </c>
+      <c r="N131" t="s">
+        <v>33</v>
+      </c>
       <c r="O131">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P131" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q131">
+        <v>59.99</v>
+      </c>
+      <c r="R131">
+        <v>10</v>
       </c>
       <c r="Y131" t="s">
-        <v>240</v>
+        <v>215</v>
+      </c>
+      <c r="Z131" t="s">
+        <v>216</v>
       </c>
       <c r="AA131" t="s">
-        <v>241</v>
+        <v>217</v>
       </c>
       <c r="AB131" t="s">
         <v>39</v>
@@ -11876,13 +11942,13 @@
     </row>
     <row r="132" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>245</v>
+        <v>218</v>
       </c>
       <c r="C132" t="s">
-        <v>246</v>
+        <v>219</v>
       </c>
       <c r="D132" t="s">
-        <v>247</v>
+        <v>220</v>
       </c>
       <c r="E132" t="s">
         <v>33</v>
@@ -11897,16 +11963,16 @@
         <v>36</v>
       </c>
       <c r="J132" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K132" t="s">
-        <v>40</v>
+        <v>203</v>
       </c>
       <c r="L132" t="s">
-        <v>41</v>
+        <v>204</v>
       </c>
       <c r="M132" t="s">
-        <v>42</v>
+        <v>205</v>
       </c>
       <c r="N132" t="s">
         <v>33</v>
@@ -11918,16 +11984,19 @@
         <v>38</v>
       </c>
       <c r="Q132">
-        <v>59.99</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="R132">
-        <v>10</v>
+        <v>11.67</v>
       </c>
       <c r="Y132" t="s">
-        <v>248</v>
+        <v>221</v>
+      </c>
+      <c r="Z132" t="s">
+        <v>222</v>
       </c>
       <c r="AA132" t="s">
-        <v>249</v>
+        <v>223</v>
       </c>
       <c r="AB132" t="s">
         <v>39</v>
@@ -11941,13 +12010,13 @@
     </row>
     <row r="133" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>188</v>
+        <v>228</v>
       </c>
       <c r="C133" t="s">
-        <v>189</v>
+        <v>229</v>
       </c>
       <c r="D133" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="E133" t="s">
         <v>33</v>
@@ -11962,16 +12031,16 @@
         <v>36</v>
       </c>
       <c r="J133" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K133" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L133" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M133" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N133" t="s">
         <v>33</v>
@@ -11983,16 +12052,16 @@
         <v>38</v>
       </c>
       <c r="Q133">
-        <v>37.99</v>
+        <v>59.99</v>
       </c>
       <c r="R133">
-        <v>6.33</v>
+        <v>10</v>
       </c>
       <c r="Y133" t="s">
-        <v>52</v>
+        <v>231</v>
       </c>
       <c r="AA133" t="s">
-        <v>190</v>
+        <v>232</v>
       </c>
       <c r="AB133" t="s">
         <v>39</v>
@@ -12006,13 +12075,13 @@
     </row>
     <row r="134" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>191</v>
+        <v>233</v>
       </c>
       <c r="C134" t="s">
-        <v>192</v>
+        <v>234</v>
       </c>
       <c r="D134" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="E134" t="s">
         <v>33</v>
@@ -12030,13 +12099,13 @@
         <v>54</v>
       </c>
       <c r="K134" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="L134" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="M134" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="N134" t="s">
         <v>33</v>
@@ -12048,16 +12117,16 @@
         <v>38</v>
       </c>
       <c r="Q134">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="R134">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="Y134" t="s">
-        <v>193</v>
+        <v>236</v>
       </c>
       <c r="AA134" t="s">
-        <v>194</v>
+        <v>237</v>
       </c>
       <c r="AB134" t="s">
         <v>39</v>
@@ -12071,16 +12140,16 @@
     </row>
     <row r="135" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>201</v>
+        <v>242</v>
       </c>
       <c r="C135" t="s">
-        <v>202</v>
+        <v>243</v>
       </c>
       <c r="D135" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="E135" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F135" t="s">
         <v>34</v>
@@ -12095,37 +12164,22 @@
         <v>54</v>
       </c>
       <c r="K135" t="s">
-        <v>203</v>
+        <v>40</v>
       </c>
       <c r="L135" t="s">
-        <v>204</v>
+        <v>41</v>
       </c>
       <c r="M135" t="s">
-        <v>205</v>
-      </c>
-      <c r="N135" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O135">
-        <v>1</v>
-      </c>
-      <c r="P135" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q135">
-        <v>69.989999999999995</v>
-      </c>
-      <c r="R135">
-        <v>11.67</v>
+        <v>0</v>
       </c>
       <c r="Y135" t="s">
-        <v>206</v>
-      </c>
-      <c r="Z135" t="s">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="AA135" t="s">
-        <v>207</v>
+        <v>241</v>
       </c>
       <c r="AB135" t="s">
         <v>39</v>
@@ -12139,13 +12193,13 @@
     </row>
     <row r="136" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>195</v>
+        <v>245</v>
       </c>
       <c r="C136" t="s">
-        <v>196</v>
+        <v>246</v>
       </c>
       <c r="D136" t="s">
-        <v>197</v>
+        <v>247</v>
       </c>
       <c r="E136" t="s">
         <v>33</v>
@@ -12187,13 +12241,10 @@
         <v>10</v>
       </c>
       <c r="Y136" t="s">
-        <v>198</v>
-      </c>
-      <c r="Z136" t="s">
-        <v>199</v>
+        <v>248</v>
       </c>
       <c r="AA136" t="s">
-        <v>200</v>
+        <v>249</v>
       </c>
       <c r="AB136" t="s">
         <v>39</v>
@@ -12207,13 +12258,13 @@
     </row>
     <row r="137" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="C137" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="D137" t="s">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="E137" t="s">
         <v>33</v>
@@ -12231,13 +12282,13 @@
         <v>37</v>
       </c>
       <c r="K137" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L137" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M137" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N137" t="s">
         <v>33</v>
@@ -12249,16 +12300,16 @@
         <v>38</v>
       </c>
       <c r="Q137">
-        <v>59.99</v>
+        <v>37.99</v>
       </c>
       <c r="R137">
-        <v>10</v>
+        <v>6.33</v>
       </c>
       <c r="Y137" t="s">
-        <v>211</v>
+        <v>52</v>
       </c>
       <c r="AA137" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="AB137" t="s">
         <v>39</v>
@@ -12272,13 +12323,13 @@
     </row>
     <row r="138" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>152</v>
+        <v>191</v>
       </c>
       <c r="C138" t="s">
-        <v>153</v>
+        <v>192</v>
       </c>
       <c r="D138" t="s">
-        <v>154</v>
+        <v>251</v>
       </c>
       <c r="E138" t="s">
         <v>33</v>
@@ -12296,13 +12347,13 @@
         <v>54</v>
       </c>
       <c r="K138" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="L138" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="M138" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="N138" t="s">
         <v>33</v>
@@ -12314,16 +12365,16 @@
         <v>38</v>
       </c>
       <c r="Q138">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R138">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y138" t="s">
-        <v>155</v>
+        <v>193</v>
       </c>
       <c r="AA138" t="s">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="AB138" t="s">
         <v>39</v>
@@ -12337,13 +12388,13 @@
     </row>
     <row r="139" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>157</v>
+        <v>201</v>
       </c>
       <c r="C139" t="s">
-        <v>158</v>
+        <v>202</v>
       </c>
       <c r="D139" t="s">
-        <v>159</v>
+        <v>252</v>
       </c>
       <c r="E139" t="s">
         <v>33</v>
@@ -12361,13 +12412,13 @@
         <v>54</v>
       </c>
       <c r="K139" t="s">
-        <v>72</v>
+        <v>203</v>
       </c>
       <c r="L139" t="s">
-        <v>73</v>
+        <v>204</v>
       </c>
       <c r="M139" t="s">
-        <v>74</v>
+        <v>205</v>
       </c>
       <c r="N139" t="s">
         <v>33</v>
@@ -12379,16 +12430,19 @@
         <v>38</v>
       </c>
       <c r="Q139">
-        <v>11.99</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="R139">
-        <v>2</v>
+        <v>11.67</v>
       </c>
       <c r="Y139" t="s">
-        <v>68</v>
+        <v>206</v>
+      </c>
+      <c r="Z139" t="s">
+        <v>60</v>
       </c>
       <c r="AA139" t="s">
-        <v>160</v>
+        <v>207</v>
       </c>
       <c r="AB139" t="s">
         <v>39</v>
@@ -12402,16 +12456,16 @@
     </row>
     <row r="140" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="C140" t="s">
-        <v>162</v>
+        <v>196</v>
       </c>
       <c r="D140" t="s">
-        <v>163</v>
+        <v>197</v>
       </c>
       <c r="E140" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F140" t="s">
         <v>34</v>
@@ -12423,7 +12477,7 @@
         <v>36</v>
       </c>
       <c r="J140" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K140" t="s">
         <v>40</v>
@@ -12434,14 +12488,29 @@
       <c r="M140" t="s">
         <v>42</v>
       </c>
+      <c r="N140" t="s">
+        <v>33</v>
+      </c>
       <c r="O140">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P140" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q140">
+        <v>59.99</v>
+      </c>
+      <c r="R140">
+        <v>10</v>
       </c>
       <c r="Y140" t="s">
-        <v>63</v>
+        <v>198</v>
+      </c>
+      <c r="Z140" t="s">
+        <v>199</v>
       </c>
       <c r="AA140" t="s">
-        <v>151</v>
+        <v>200</v>
       </c>
       <c r="AB140" t="s">
         <v>39</v>
@@ -12455,13 +12524,13 @@
     </row>
     <row r="141" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>164</v>
+        <v>208</v>
       </c>
       <c r="C141" t="s">
-        <v>165</v>
+        <v>209</v>
       </c>
       <c r="D141" t="s">
-        <v>166</v>
+        <v>210</v>
       </c>
       <c r="E141" t="s">
         <v>33</v>
@@ -12476,16 +12545,16 @@
         <v>36</v>
       </c>
       <c r="J141" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K141" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L141" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M141" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N141" t="s">
         <v>33</v>
@@ -12497,16 +12566,16 @@
         <v>38</v>
       </c>
       <c r="Q141">
-        <v>37.99</v>
+        <v>59.99</v>
       </c>
       <c r="R141">
-        <v>6.33</v>
+        <v>10</v>
       </c>
       <c r="Y141" t="s">
-        <v>100</v>
+        <v>211</v>
       </c>
       <c r="AA141" t="s">
-        <v>167</v>
+        <v>212</v>
       </c>
       <c r="AB141" t="s">
         <v>39</v>
@@ -12520,13 +12589,13 @@
     </row>
     <row r="142" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="C142" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="D142" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="E142" t="s">
         <v>33</v>
@@ -12544,13 +12613,13 @@
         <v>54</v>
       </c>
       <c r="K142" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="L142" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M142" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="N142" t="s">
         <v>33</v>
@@ -12562,16 +12631,16 @@
         <v>38</v>
       </c>
       <c r="Q142">
-        <v>11.99</v>
+        <v>14.99</v>
       </c>
       <c r="R142">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Y142" t="s">
-        <v>66</v>
+        <v>155</v>
       </c>
       <c r="AA142" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="AB142" t="s">
         <v>39</v>
@@ -12585,13 +12654,13 @@
     </row>
     <row r="143" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="C143" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="D143" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="E143" t="s">
         <v>33</v>
@@ -12609,13 +12678,13 @@
         <v>54</v>
       </c>
       <c r="K143" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L143" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M143" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="N143" t="s">
         <v>33</v>
@@ -12627,16 +12696,16 @@
         <v>38</v>
       </c>
       <c r="Q143">
-        <v>14.99</v>
+        <v>11.99</v>
       </c>
       <c r="R143">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Y143" t="s">
-        <v>175</v>
+        <v>68</v>
       </c>
       <c r="AA143" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="AB143" t="s">
         <v>39</v>
@@ -12650,16 +12719,16 @@
     </row>
     <row r="144" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="C144" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="D144" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="E144" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F144" t="s">
         <v>34</v>
@@ -12674,37 +12743,22 @@
         <v>54</v>
       </c>
       <c r="K144" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L144" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M144" t="s">
-        <v>50</v>
-      </c>
-      <c r="N144" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O144">
-        <v>1</v>
-      </c>
-      <c r="P144" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q144">
-        <v>37.99</v>
-      </c>
-      <c r="R144">
-        <v>6.33</v>
+        <v>0</v>
       </c>
       <c r="Y144" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z144" t="s">
-        <v>181</v>
+        <v>63</v>
       </c>
       <c r="AA144" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="AB144" t="s">
         <v>39</v>
@@ -12718,13 +12772,13 @@
     </row>
     <row r="145" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="C145" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="D145" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="E145" t="s">
         <v>33</v>
@@ -12754,25 +12808,22 @@
         <v>33</v>
       </c>
       <c r="O145">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P145" t="s">
         <v>38</v>
       </c>
       <c r="Q145">
-        <v>75.98</v>
+        <v>37.99</v>
       </c>
       <c r="R145">
-        <v>12.66</v>
+        <v>6.33</v>
       </c>
       <c r="Y145" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z145" t="s">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="AA145" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="AB145" t="s">
         <v>39</v>
@@ -12786,13 +12837,13 @@
     </row>
     <row r="146" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="C146" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="D146" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="E146" t="s">
         <v>33</v>
@@ -12834,10 +12885,10 @@
         <v>2</v>
       </c>
       <c r="Y146" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="AA146" t="s">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="AB146" t="s">
         <v>39</v>
@@ -12851,13 +12902,13 @@
     </row>
     <row r="147" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>117</v>
+        <v>172</v>
       </c>
       <c r="C147" t="s">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="D147" t="s">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="E147" t="s">
         <v>33</v>
@@ -12899,13 +12950,10 @@
         <v>2.5</v>
       </c>
       <c r="Y147" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z147" t="s">
-        <v>121</v>
+        <v>175</v>
       </c>
       <c r="AA147" t="s">
-        <v>122</v>
+        <v>176</v>
       </c>
       <c r="AB147" t="s">
         <v>39</v>
@@ -12919,13 +12967,13 @@
     </row>
     <row r="148" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>123</v>
+        <v>177</v>
       </c>
       <c r="C148" t="s">
-        <v>124</v>
+        <v>178</v>
       </c>
       <c r="D148" t="s">
-        <v>125</v>
+        <v>179</v>
       </c>
       <c r="E148" t="s">
         <v>33</v>
@@ -12943,13 +12991,13 @@
         <v>54</v>
       </c>
       <c r="K148" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L148" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M148" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N148" t="s">
         <v>33</v>
@@ -12961,19 +13009,19 @@
         <v>38</v>
       </c>
       <c r="Q148">
-        <v>59.99</v>
+        <v>37.99</v>
       </c>
       <c r="R148">
-        <v>10</v>
+        <v>6.33</v>
       </c>
       <c r="Y148" t="s">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="Z148" t="s">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="AA148" t="s">
-        <v>128</v>
+        <v>182</v>
       </c>
       <c r="AB148" t="s">
         <v>39</v>
@@ -12987,13 +13035,13 @@
     </row>
     <row r="149" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>129</v>
+        <v>183</v>
       </c>
       <c r="C149" t="s">
-        <v>130</v>
+        <v>184</v>
       </c>
       <c r="D149" t="s">
-        <v>131</v>
+        <v>179</v>
       </c>
       <c r="E149" t="s">
         <v>33</v>
@@ -13011,34 +13059,37 @@
         <v>54</v>
       </c>
       <c r="K149" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="L149" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M149" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="N149" t="s">
         <v>33</v>
       </c>
       <c r="O149">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P149" t="s">
         <v>38</v>
       </c>
       <c r="Q149">
-        <v>38.49</v>
+        <v>75.98</v>
       </c>
       <c r="R149">
-        <v>6.42</v>
+        <v>12.66</v>
       </c>
       <c r="Y149" t="s">
-        <v>78</v>
+        <v>70</v>
+      </c>
+      <c r="Z149" t="s">
+        <v>47</v>
       </c>
       <c r="AA149" t="s">
-        <v>132</v>
+        <v>185</v>
       </c>
       <c r="AB149" t="s">
         <v>39</v>
@@ -13052,16 +13103,16 @@
     </row>
     <row r="150" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="C150" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="D150" t="s">
-        <v>136</v>
+        <v>186</v>
       </c>
       <c r="E150" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F150" t="s">
         <v>34</v>
@@ -13076,22 +13127,34 @@
         <v>54</v>
       </c>
       <c r="K150" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L150" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M150" t="s">
-        <v>83</v>
+        <v>74</v>
+      </c>
+      <c r="N150" t="s">
+        <v>33</v>
       </c>
       <c r="O150">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P150" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q150">
+        <v>11.99</v>
+      </c>
+      <c r="R150">
+        <v>2</v>
       </c>
       <c r="Y150" t="s">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="AA150" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="AB150" t="s">
         <v>39</v>
@@ -13105,13 +13168,13 @@
     </row>
     <row r="151" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C151" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="D151" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="E151" t="s">
         <v>33</v>
@@ -13129,13 +13192,13 @@
         <v>54</v>
       </c>
       <c r="K151" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="L151" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="M151" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="N151" t="s">
         <v>33</v>
@@ -13147,19 +13210,19 @@
         <v>38</v>
       </c>
       <c r="Q151">
-        <v>37.99</v>
+        <v>14.99</v>
       </c>
       <c r="R151">
-        <v>6.33</v>
+        <v>2.5</v>
       </c>
       <c r="Y151" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="Z151" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AA151" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="AB151" t="s">
         <v>39</v>
@@ -13173,13 +13236,13 @@
     </row>
     <row r="152" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="C152" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D152" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E152" t="s">
         <v>33</v>
@@ -13194,7 +13257,7 @@
         <v>36</v>
       </c>
       <c r="J152" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K152" t="s">
         <v>40</v>
@@ -13221,13 +13284,13 @@
         <v>10</v>
       </c>
       <c r="Y152" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="Z152" t="s">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="AA152" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="AB152" t="s">
         <v>39</v>
@@ -13241,13 +13304,13 @@
     </row>
     <row r="153" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>703</v>
+        <v>129</v>
       </c>
       <c r="C153" t="s">
-        <v>704</v>
+        <v>130</v>
       </c>
       <c r="D153" t="s">
-        <v>705</v>
+        <v>131</v>
       </c>
       <c r="E153" t="s">
         <v>33</v>
@@ -13265,13 +13328,13 @@
         <v>54</v>
       </c>
       <c r="K153" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="L153" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="M153" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="N153" t="s">
         <v>33</v>
@@ -13283,24 +13346,278 @@
         <v>38</v>
       </c>
       <c r="Q153">
+        <v>38.49</v>
+      </c>
+      <c r="R153">
+        <v>6.42</v>
+      </c>
+      <c r="Y153" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA153" t="s">
+        <v>132</v>
+      </c>
+      <c r="AB153" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>105</v>
+      </c>
+      <c r="C154" t="s">
+        <v>106</v>
+      </c>
+      <c r="D154" t="s">
+        <v>136</v>
+      </c>
+      <c r="E154" t="s">
+        <v>53</v>
+      </c>
+      <c r="F154" t="s">
+        <v>34</v>
+      </c>
+      <c r="G154" t="s">
+        <v>35</v>
+      </c>
+      <c r="H154" t="s">
+        <v>36</v>
+      </c>
+      <c r="J154" t="s">
+        <v>54</v>
+      </c>
+      <c r="K154" t="s">
+        <v>94</v>
+      </c>
+      <c r="L154" t="s">
+        <v>82</v>
+      </c>
+      <c r="M154" t="s">
+        <v>83</v>
+      </c>
+      <c r="O154">
+        <v>0</v>
+      </c>
+      <c r="Y154" t="s">
+        <v>103</v>
+      </c>
+      <c r="AA154" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB154" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>107</v>
+      </c>
+      <c r="C155" t="s">
+        <v>108</v>
+      </c>
+      <c r="D155" t="s">
+        <v>137</v>
+      </c>
+      <c r="E155" t="s">
+        <v>33</v>
+      </c>
+      <c r="F155" t="s">
+        <v>34</v>
+      </c>
+      <c r="G155" t="s">
+        <v>35</v>
+      </c>
+      <c r="H155" t="s">
+        <v>36</v>
+      </c>
+      <c r="J155" t="s">
+        <v>54</v>
+      </c>
+      <c r="K155" t="s">
+        <v>48</v>
+      </c>
+      <c r="L155" t="s">
+        <v>49</v>
+      </c>
+      <c r="M155" t="s">
+        <v>50</v>
+      </c>
+      <c r="N155" t="s">
+        <v>33</v>
+      </c>
+      <c r="O155">
+        <v>1</v>
+      </c>
+      <c r="P155" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q155">
+        <v>37.99</v>
+      </c>
+      <c r="R155">
+        <v>6.33</v>
+      </c>
+      <c r="Y155" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z155" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA155" t="s">
+        <v>111</v>
+      </c>
+      <c r="AB155" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>112</v>
+      </c>
+      <c r="C156" t="s">
+        <v>113</v>
+      </c>
+      <c r="D156" t="s">
+        <v>114</v>
+      </c>
+      <c r="E156" t="s">
+        <v>33</v>
+      </c>
+      <c r="F156" t="s">
+        <v>34</v>
+      </c>
+      <c r="G156" t="s">
+        <v>35</v>
+      </c>
+      <c r="H156" t="s">
+        <v>36</v>
+      </c>
+      <c r="J156" t="s">
+        <v>37</v>
+      </c>
+      <c r="K156" t="s">
+        <v>40</v>
+      </c>
+      <c r="L156" t="s">
+        <v>41</v>
+      </c>
+      <c r="M156" t="s">
+        <v>42</v>
+      </c>
+      <c r="N156" t="s">
+        <v>33</v>
+      </c>
+      <c r="O156">
+        <v>1</v>
+      </c>
+      <c r="P156" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q156">
+        <v>59.99</v>
+      </c>
+      <c r="R156">
+        <v>10</v>
+      </c>
+      <c r="Y156" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z156" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA156" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB156" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>703</v>
+      </c>
+      <c r="C157" t="s">
+        <v>704</v>
+      </c>
+      <c r="D157" t="s">
+        <v>705</v>
+      </c>
+      <c r="E157" t="s">
+        <v>33</v>
+      </c>
+      <c r="F157" t="s">
+        <v>34</v>
+      </c>
+      <c r="G157" t="s">
+        <v>35</v>
+      </c>
+      <c r="H157" t="s">
+        <v>36</v>
+      </c>
+      <c r="J157" t="s">
+        <v>54</v>
+      </c>
+      <c r="K157" t="s">
+        <v>72</v>
+      </c>
+      <c r="L157" t="s">
+        <v>73</v>
+      </c>
+      <c r="M157" t="s">
+        <v>74</v>
+      </c>
+      <c r="N157" t="s">
+        <v>33</v>
+      </c>
+      <c r="O157">
+        <v>1</v>
+      </c>
+      <c r="P157" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q157">
         <v>11.99</v>
       </c>
-      <c r="R153">
+      <c r="R157">
         <v>2</v>
       </c>
-      <c r="Y153" t="s">
+      <c r="Y157" t="s">
         <v>706</v>
       </c>
-      <c r="AA153" t="s">
+      <c r="AA157" t="s">
         <v>707</v>
       </c>
-      <c r="AB153" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD153" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG153" t="b">
+      <c r="AB157" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Raw Sales Data/Amazon.xlsx
+++ b/Raw Sales Data/Amazon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2556" uniqueCount="837">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2588" uniqueCount="846">
   <si>
     <t>amazon-order-id</t>
   </si>
@@ -2530,6 +2530,33 @@
   </si>
   <si>
     <t>BS13 9PB</t>
+  </si>
+  <si>
+    <t>204-7174760-2007506</t>
+  </si>
+  <si>
+    <t>2026-03-06T23:04:18+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-06T23:34:51+00:00</t>
+  </si>
+  <si>
+    <t>LL57 2HE</t>
+  </si>
+  <si>
+    <t>203-0830771-9113131</t>
+  </si>
+  <si>
+    <t>2026-03-06T17:04:14+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-06T17:28:53+00:00</t>
+  </si>
+  <si>
+    <t>Highland</t>
+  </si>
+  <si>
+    <t>IV180PU</t>
   </si>
 </sst>
 </file>
@@ -3336,7 +3363,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG157"/>
+  <dimension ref="A1:AG159"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
@@ -3447,13 +3474,13 @@
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>819</v>
+        <v>837</v>
       </c>
       <c r="C2" t="s">
-        <v>820</v>
+        <v>838</v>
       </c>
       <c r="D2" t="s">
-        <v>821</v>
+        <v>839</v>
       </c>
       <c r="E2" t="s">
         <v>98</v>
@@ -3495,13 +3522,10 @@
         <v>6.83</v>
       </c>
       <c r="Y2" t="s">
-        <v>618</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>619</v>
+        <v>305</v>
       </c>
       <c r="AA2" t="s">
-        <v>620</v>
+        <v>840</v>
       </c>
       <c r="AB2" t="s">
         <v>39</v>
@@ -3515,13 +3539,13 @@
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>822</v>
+        <v>841</v>
       </c>
       <c r="C3" t="s">
-        <v>823</v>
+        <v>842</v>
       </c>
       <c r="D3" t="s">
-        <v>824</v>
+        <v>843</v>
       </c>
       <c r="E3" t="s">
         <v>98</v>
@@ -3539,13 +3563,13 @@
         <v>54</v>
       </c>
       <c r="K3" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L3" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M3" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N3" t="s">
         <v>99</v>
@@ -3557,16 +3581,22 @@
         <v>38</v>
       </c>
       <c r="Q3">
-        <v>14.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R3">
-        <v>2.5</v>
+        <v>11</v>
+      </c>
+      <c r="S3">
+        <v>6.99</v>
+      </c>
+      <c r="T3">
+        <v>1.17</v>
       </c>
       <c r="Y3" t="s">
-        <v>825</v>
+        <v>844</v>
       </c>
       <c r="AA3" t="s">
-        <v>826</v>
+        <v>845</v>
       </c>
       <c r="AB3" t="s">
         <v>39</v>
@@ -3580,13 +3610,13 @@
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>827</v>
+        <v>819</v>
       </c>
       <c r="C4" t="s">
-        <v>828</v>
+        <v>820</v>
       </c>
       <c r="D4" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
       <c r="E4" t="s">
         <v>98</v>
@@ -3604,13 +3634,13 @@
         <v>54</v>
       </c>
       <c r="K4" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L4" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M4" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N4" t="s">
         <v>99</v>
@@ -3622,16 +3652,19 @@
         <v>38</v>
       </c>
       <c r="Q4">
-        <v>65.989999999999995</v>
-      </c>
-      <c r="S4">
-        <v>6.99</v>
+        <v>40.99</v>
+      </c>
+      <c r="R4">
+        <v>6.83</v>
       </c>
       <c r="Y4" t="s">
-        <v>830</v>
+        <v>618</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>619</v>
       </c>
       <c r="AA4" t="s">
-        <v>831</v>
+        <v>620</v>
       </c>
       <c r="AB4" t="s">
         <v>39</v>
@@ -3645,16 +3678,16 @@
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>832</v>
+        <v>822</v>
       </c>
       <c r="C5" t="s">
-        <v>833</v>
+        <v>823</v>
       </c>
       <c r="D5" t="s">
-        <v>834</v>
+        <v>824</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F5" t="s">
         <v>34</v>
@@ -3669,16 +3702,16 @@
         <v>54</v>
       </c>
       <c r="K5" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M5" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N5" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O5">
         <v>1</v>
@@ -3687,16 +3720,16 @@
         <v>38</v>
       </c>
       <c r="Q5">
-        <v>65.989999999999995</v>
+        <v>14.99</v>
       </c>
       <c r="R5">
-        <v>11</v>
+        <v>2.5</v>
       </c>
       <c r="Y5" t="s">
-        <v>835</v>
+        <v>825</v>
       </c>
       <c r="AA5" t="s">
-        <v>836</v>
+        <v>826</v>
       </c>
       <c r="AB5" t="s">
         <v>39</v>
@@ -3710,16 +3743,16 @@
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>780</v>
+        <v>827</v>
       </c>
       <c r="C6" t="s">
-        <v>781</v>
+        <v>828</v>
       </c>
       <c r="D6" t="s">
-        <v>782</v>
+        <v>829</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F6" t="s">
         <v>34</v>
@@ -3743,7 +3776,7 @@
         <v>42</v>
       </c>
       <c r="N6" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O6">
         <v>1</v>
@@ -3754,14 +3787,14 @@
       <c r="Q6">
         <v>65.989999999999995</v>
       </c>
-      <c r="R6">
-        <v>11</v>
+      <c r="S6">
+        <v>6.99</v>
       </c>
       <c r="Y6" t="s">
-        <v>783</v>
+        <v>830</v>
       </c>
       <c r="AA6" t="s">
-        <v>784</v>
+        <v>831</v>
       </c>
       <c r="AB6" t="s">
         <v>39</v>
@@ -3775,13 +3808,13 @@
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>785</v>
+        <v>832</v>
       </c>
       <c r="C7" t="s">
-        <v>786</v>
+        <v>833</v>
       </c>
       <c r="D7" t="s">
-        <v>787</v>
+        <v>834</v>
       </c>
       <c r="E7" t="s">
         <v>33</v>
@@ -3799,13 +3832,13 @@
         <v>54</v>
       </c>
       <c r="K7" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L7" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M7" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N7" t="s">
         <v>33</v>
@@ -3817,16 +3850,16 @@
         <v>38</v>
       </c>
       <c r="Q7">
-        <v>40.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R7">
-        <v>6.83</v>
+        <v>11</v>
       </c>
       <c r="Y7" t="s">
-        <v>788</v>
+        <v>835</v>
       </c>
       <c r="AA7" t="s">
-        <v>789</v>
+        <v>836</v>
       </c>
       <c r="AB7" t="s">
         <v>39</v>
@@ -3840,13 +3873,13 @@
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>790</v>
+        <v>780</v>
       </c>
       <c r="C8" t="s">
-        <v>791</v>
+        <v>781</v>
       </c>
       <c r="D8" t="s">
-        <v>792</v>
+        <v>782</v>
       </c>
       <c r="E8" t="s">
         <v>33</v>
@@ -3888,10 +3921,10 @@
         <v>11</v>
       </c>
       <c r="Y8" t="s">
-        <v>793</v>
+        <v>783</v>
       </c>
       <c r="AA8" t="s">
-        <v>794</v>
+        <v>784</v>
       </c>
       <c r="AB8" t="s">
         <v>39</v>
@@ -3905,13 +3938,13 @@
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>795</v>
+        <v>785</v>
       </c>
       <c r="C9" t="s">
-        <v>796</v>
+        <v>786</v>
       </c>
       <c r="D9" t="s">
-        <v>797</v>
+        <v>787</v>
       </c>
       <c r="E9" t="s">
         <v>33</v>
@@ -3929,13 +3962,13 @@
         <v>54</v>
       </c>
       <c r="K9" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L9" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M9" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N9" t="s">
         <v>33</v>
@@ -3947,16 +3980,16 @@
         <v>38</v>
       </c>
       <c r="Q9">
-        <v>14.99</v>
+        <v>40.99</v>
       </c>
       <c r="R9">
-        <v>2.5</v>
+        <v>6.83</v>
       </c>
       <c r="Y9" t="s">
-        <v>798</v>
+        <v>788</v>
       </c>
       <c r="AA9" t="s">
-        <v>799</v>
+        <v>789</v>
       </c>
       <c r="AB9" t="s">
         <v>39</v>
@@ -3970,13 +4003,13 @@
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>800</v>
+        <v>790</v>
       </c>
       <c r="C10" t="s">
-        <v>801</v>
+        <v>791</v>
       </c>
       <c r="D10" t="s">
-        <v>802</v>
+        <v>792</v>
       </c>
       <c r="E10" t="s">
         <v>33</v>
@@ -3994,13 +4027,13 @@
         <v>54</v>
       </c>
       <c r="K10" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L10" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M10" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N10" t="s">
         <v>33</v>
@@ -4012,16 +4045,16 @@
         <v>38</v>
       </c>
       <c r="Q10">
-        <v>14.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R10">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="Y10" t="s">
-        <v>68</v>
+        <v>793</v>
       </c>
       <c r="AA10" t="s">
-        <v>803</v>
+        <v>794</v>
       </c>
       <c r="AB10" t="s">
         <v>39</v>
@@ -4035,13 +4068,13 @@
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>804</v>
+        <v>795</v>
       </c>
       <c r="C11" t="s">
-        <v>805</v>
+        <v>796</v>
       </c>
       <c r="D11" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="E11" t="s">
         <v>33</v>
@@ -4077,16 +4110,16 @@
         <v>38</v>
       </c>
       <c r="Q11">
-        <v>11.99</v>
+        <v>14.99</v>
       </c>
       <c r="R11">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Y11" t="s">
-        <v>806</v>
+        <v>798</v>
       </c>
       <c r="AA11" t="s">
-        <v>807</v>
+        <v>799</v>
       </c>
       <c r="AB11" t="s">
         <v>39</v>
@@ -4100,13 +4133,13 @@
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>808</v>
+        <v>800</v>
       </c>
       <c r="C12" t="s">
-        <v>809</v>
+        <v>801</v>
       </c>
       <c r="D12" t="s">
-        <v>810</v>
+        <v>802</v>
       </c>
       <c r="E12" t="s">
         <v>33</v>
@@ -4142,16 +4175,16 @@
         <v>38</v>
       </c>
       <c r="Q12">
-        <v>11.99</v>
+        <v>14.99</v>
       </c>
       <c r="R12">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Y12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AA12" t="s">
-        <v>811</v>
+        <v>803</v>
       </c>
       <c r="AB12" t="s">
         <v>39</v>
@@ -4165,13 +4198,13 @@
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>812</v>
+        <v>804</v>
       </c>
       <c r="C13" t="s">
-        <v>813</v>
+        <v>805</v>
       </c>
       <c r="D13" t="s">
-        <v>814</v>
+        <v>802</v>
       </c>
       <c r="E13" t="s">
         <v>33</v>
@@ -4189,13 +4222,13 @@
         <v>54</v>
       </c>
       <c r="K13" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="L13" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="M13" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="N13" t="s">
         <v>33</v>
@@ -4207,16 +4240,16 @@
         <v>38</v>
       </c>
       <c r="Q13">
-        <v>40.99</v>
+        <v>11.99</v>
       </c>
       <c r="R13">
-        <v>6.83</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="s">
-        <v>815</v>
+        <v>806</v>
       </c>
       <c r="AA13" t="s">
-        <v>816</v>
+        <v>807</v>
       </c>
       <c r="AB13" t="s">
         <v>39</v>
@@ -4230,13 +4263,13 @@
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>745</v>
+        <v>808</v>
       </c>
       <c r="C14" t="s">
-        <v>746</v>
+        <v>809</v>
       </c>
       <c r="D14" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="E14" t="s">
         <v>33</v>
@@ -4278,10 +4311,10 @@
         <v>2</v>
       </c>
       <c r="Y14" t="s">
-        <v>748</v>
+        <v>66</v>
       </c>
       <c r="AA14" t="s">
-        <v>749</v>
+        <v>811</v>
       </c>
       <c r="AB14" t="s">
         <v>39</v>
@@ -4295,13 +4328,13 @@
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>750</v>
+        <v>812</v>
       </c>
       <c r="C15" t="s">
-        <v>751</v>
+        <v>813</v>
       </c>
       <c r="D15" t="s">
-        <v>752</v>
+        <v>814</v>
       </c>
       <c r="E15" t="s">
         <v>33</v>
@@ -4319,13 +4352,13 @@
         <v>54</v>
       </c>
       <c r="K15" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L15" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M15" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N15" t="s">
         <v>33</v>
@@ -4337,16 +4370,16 @@
         <v>38</v>
       </c>
       <c r="Q15">
-        <v>65.989999999999995</v>
+        <v>40.99</v>
       </c>
       <c r="R15">
-        <v>11</v>
+        <v>6.83</v>
       </c>
       <c r="Y15" t="s">
-        <v>753</v>
+        <v>815</v>
       </c>
       <c r="AA15" t="s">
-        <v>754</v>
+        <v>816</v>
       </c>
       <c r="AB15" t="s">
         <v>39</v>
@@ -4360,13 +4393,13 @@
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>755</v>
+        <v>745</v>
       </c>
       <c r="C16" t="s">
-        <v>756</v>
+        <v>746</v>
       </c>
       <c r="D16" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="E16" t="s">
         <v>33</v>
@@ -4384,13 +4417,13 @@
         <v>54</v>
       </c>
       <c r="K16" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L16" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M16" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N16" t="s">
         <v>33</v>
@@ -4402,25 +4435,16 @@
         <v>38</v>
       </c>
       <c r="Q16">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R16">
-        <v>11</v>
-      </c>
-      <c r="S16">
-        <v>6.99</v>
-      </c>
-      <c r="T16">
-        <v>1.17</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="s">
-        <v>758</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>759</v>
+        <v>748</v>
       </c>
       <c r="AA16" t="s">
-        <v>760</v>
+        <v>749</v>
       </c>
       <c r="AB16" t="s">
         <v>39</v>
@@ -4434,13 +4458,13 @@
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>761</v>
+        <v>750</v>
       </c>
       <c r="C17" t="s">
-        <v>762</v>
+        <v>751</v>
       </c>
       <c r="D17" t="s">
-        <v>763</v>
+        <v>752</v>
       </c>
       <c r="E17" t="s">
         <v>33</v>
@@ -4458,13 +4482,13 @@
         <v>54</v>
       </c>
       <c r="K17" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L17" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M17" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N17" t="s">
         <v>33</v>
@@ -4476,19 +4500,16 @@
         <v>38</v>
       </c>
       <c r="Q17">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R17">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y17" t="s">
-        <v>764</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>279</v>
+        <v>753</v>
       </c>
       <c r="AA17" t="s">
-        <v>765</v>
+        <v>754</v>
       </c>
       <c r="AB17" t="s">
         <v>39</v>
@@ -4502,13 +4523,13 @@
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>766</v>
+        <v>755</v>
       </c>
       <c r="C18" t="s">
-        <v>767</v>
+        <v>756</v>
       </c>
       <c r="D18" t="s">
-        <v>768</v>
+        <v>818</v>
       </c>
       <c r="E18" t="s">
         <v>33</v>
@@ -4526,13 +4547,13 @@
         <v>54</v>
       </c>
       <c r="K18" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L18" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M18" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N18" t="s">
         <v>33</v>
@@ -4544,19 +4565,25 @@
         <v>38</v>
       </c>
       <c r="Q18">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R18">
-        <v>2</v>
+        <v>11</v>
+      </c>
+      <c r="S18">
+        <v>6.99</v>
+      </c>
+      <c r="T18">
+        <v>1.17</v>
       </c>
       <c r="Y18" t="s">
-        <v>91</v>
+        <v>758</v>
       </c>
       <c r="Z18" t="s">
-        <v>121</v>
+        <v>759</v>
       </c>
       <c r="AA18" t="s">
-        <v>769</v>
+        <v>760</v>
       </c>
       <c r="AB18" t="s">
         <v>39</v>
@@ -4570,13 +4597,13 @@
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>770</v>
+        <v>761</v>
       </c>
       <c r="C19" t="s">
-        <v>771</v>
+        <v>762</v>
       </c>
       <c r="D19" t="s">
-        <v>772</v>
+        <v>763</v>
       </c>
       <c r="E19" t="s">
         <v>33</v>
@@ -4594,13 +4621,13 @@
         <v>54</v>
       </c>
       <c r="K19" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L19" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M19" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N19" t="s">
         <v>33</v>
@@ -4612,19 +4639,19 @@
         <v>38</v>
       </c>
       <c r="Q19">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R19">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="s">
-        <v>773</v>
+        <v>764</v>
       </c>
       <c r="Z19" t="s">
-        <v>64</v>
+        <v>279</v>
       </c>
       <c r="AA19" t="s">
-        <v>774</v>
+        <v>765</v>
       </c>
       <c r="AB19" t="s">
         <v>39</v>
@@ -4638,13 +4665,13 @@
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>775</v>
+        <v>766</v>
       </c>
       <c r="C20" t="s">
-        <v>776</v>
+        <v>767</v>
       </c>
       <c r="D20" t="s">
-        <v>777</v>
+        <v>768</v>
       </c>
       <c r="E20" t="s">
         <v>33</v>
@@ -4662,13 +4689,13 @@
         <v>54</v>
       </c>
       <c r="K20" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L20" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M20" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N20" t="s">
         <v>33</v>
@@ -4680,16 +4707,19 @@
         <v>38</v>
       </c>
       <c r="Q20">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R20">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="s">
-        <v>778</v>
+        <v>91</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>121</v>
       </c>
       <c r="AA20" t="s">
-        <v>779</v>
+        <v>769</v>
       </c>
       <c r="AB20" t="s">
         <v>39</v>
@@ -4703,16 +4733,16 @@
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>745</v>
+        <v>770</v>
       </c>
       <c r="C21" t="s">
-        <v>746</v>
+        <v>771</v>
       </c>
       <c r="D21" t="s">
-        <v>747</v>
+        <v>772</v>
       </c>
       <c r="E21" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F21" t="s">
         <v>34</v>
@@ -4727,16 +4757,16 @@
         <v>54</v>
       </c>
       <c r="K21" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L21" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M21" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N21" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O21">
         <v>1</v>
@@ -4745,16 +4775,19 @@
         <v>38</v>
       </c>
       <c r="Q21">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R21">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y21" t="s">
-        <v>748</v>
+        <v>773</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>64</v>
       </c>
       <c r="AA21" t="s">
-        <v>749</v>
+        <v>774</v>
       </c>
       <c r="AB21" t="s">
         <v>39</v>
@@ -4768,13 +4801,13 @@
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>750</v>
+        <v>775</v>
       </c>
       <c r="C22" t="s">
-        <v>751</v>
+        <v>776</v>
       </c>
       <c r="D22" t="s">
-        <v>752</v>
+        <v>777</v>
       </c>
       <c r="E22" t="s">
         <v>33</v>
@@ -4816,10 +4849,10 @@
         <v>11</v>
       </c>
       <c r="Y22" t="s">
-        <v>753</v>
+        <v>778</v>
       </c>
       <c r="AA22" t="s">
-        <v>754</v>
+        <v>779</v>
       </c>
       <c r="AB22" t="s">
         <v>39</v>
@@ -4833,13 +4866,13 @@
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>755</v>
+        <v>745</v>
       </c>
       <c r="C23" t="s">
-        <v>756</v>
+        <v>746</v>
       </c>
       <c r="D23" t="s">
-        <v>757</v>
+        <v>747</v>
       </c>
       <c r="E23" t="s">
         <v>98</v>
@@ -4857,13 +4890,13 @@
         <v>54</v>
       </c>
       <c r="K23" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L23" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M23" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N23" t="s">
         <v>99</v>
@@ -4875,25 +4908,16 @@
         <v>38</v>
       </c>
       <c r="Q23">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R23">
-        <v>11</v>
-      </c>
-      <c r="S23">
-        <v>6.99</v>
-      </c>
-      <c r="T23">
-        <v>1.17</v>
+        <v>2</v>
       </c>
       <c r="Y23" t="s">
-        <v>758</v>
-      </c>
-      <c r="Z23" t="s">
-        <v>759</v>
+        <v>748</v>
       </c>
       <c r="AA23" t="s">
-        <v>760</v>
+        <v>749</v>
       </c>
       <c r="AB23" t="s">
         <v>39</v>
@@ -4907,13 +4931,13 @@
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>761</v>
+        <v>750</v>
       </c>
       <c r="C24" t="s">
-        <v>762</v>
+        <v>751</v>
       </c>
       <c r="D24" t="s">
-        <v>763</v>
+        <v>752</v>
       </c>
       <c r="E24" t="s">
         <v>33</v>
@@ -4931,13 +4955,13 @@
         <v>54</v>
       </c>
       <c r="K24" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L24" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M24" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N24" t="s">
         <v>33</v>
@@ -4949,19 +4973,16 @@
         <v>38</v>
       </c>
       <c r="Q24">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R24">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y24" t="s">
-        <v>764</v>
-      </c>
-      <c r="Z24" t="s">
-        <v>279</v>
+        <v>753</v>
       </c>
       <c r="AA24" t="s">
-        <v>765</v>
+        <v>754</v>
       </c>
       <c r="AB24" t="s">
         <v>39</v>
@@ -4975,16 +4996,16 @@
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>766</v>
+        <v>755</v>
       </c>
       <c r="C25" t="s">
-        <v>767</v>
+        <v>756</v>
       </c>
       <c r="D25" t="s">
-        <v>768</v>
+        <v>757</v>
       </c>
       <c r="E25" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F25" t="s">
         <v>34</v>
@@ -4999,16 +5020,16 @@
         <v>54</v>
       </c>
       <c r="K25" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L25" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M25" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N25" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O25">
         <v>1</v>
@@ -5017,19 +5038,25 @@
         <v>38</v>
       </c>
       <c r="Q25">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R25">
-        <v>2</v>
+        <v>11</v>
+      </c>
+      <c r="S25">
+        <v>6.99</v>
+      </c>
+      <c r="T25">
+        <v>1.17</v>
       </c>
       <c r="Y25" t="s">
-        <v>91</v>
+        <v>758</v>
       </c>
       <c r="Z25" t="s">
-        <v>121</v>
+        <v>759</v>
       </c>
       <c r="AA25" t="s">
-        <v>769</v>
+        <v>760</v>
       </c>
       <c r="AB25" t="s">
         <v>39</v>
@@ -5043,13 +5070,13 @@
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>770</v>
+        <v>761</v>
       </c>
       <c r="C26" t="s">
-        <v>771</v>
+        <v>762</v>
       </c>
       <c r="D26" t="s">
-        <v>772</v>
+        <v>763</v>
       </c>
       <c r="E26" t="s">
         <v>33</v>
@@ -5067,13 +5094,13 @@
         <v>54</v>
       </c>
       <c r="K26" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L26" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M26" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N26" t="s">
         <v>33</v>
@@ -5085,19 +5112,19 @@
         <v>38</v>
       </c>
       <c r="Q26">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R26">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y26" t="s">
-        <v>773</v>
+        <v>764</v>
       </c>
       <c r="Z26" t="s">
-        <v>64</v>
+        <v>279</v>
       </c>
       <c r="AA26" t="s">
-        <v>774</v>
+        <v>765</v>
       </c>
       <c r="AB26" t="s">
         <v>39</v>
@@ -5111,13 +5138,13 @@
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>775</v>
+        <v>766</v>
       </c>
       <c r="C27" t="s">
-        <v>776</v>
+        <v>767</v>
       </c>
       <c r="D27" t="s">
-        <v>777</v>
+        <v>768</v>
       </c>
       <c r="E27" t="s">
         <v>33</v>
@@ -5135,13 +5162,13 @@
         <v>54</v>
       </c>
       <c r="K27" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L27" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M27" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N27" t="s">
         <v>33</v>
@@ -5153,16 +5180,19 @@
         <v>38</v>
       </c>
       <c r="Q27">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R27">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y27" t="s">
-        <v>778</v>
+        <v>91</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>121</v>
       </c>
       <c r="AA27" t="s">
-        <v>779</v>
+        <v>769</v>
       </c>
       <c r="AB27" t="s">
         <v>39</v>
@@ -5176,16 +5206,16 @@
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>714</v>
+        <v>770</v>
       </c>
       <c r="C28" t="s">
-        <v>715</v>
+        <v>771</v>
       </c>
       <c r="D28" t="s">
-        <v>716</v>
+        <v>772</v>
       </c>
       <c r="E28" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F28" t="s">
         <v>34</v>
@@ -5200,16 +5230,16 @@
         <v>54</v>
       </c>
       <c r="K28" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L28" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M28" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N28" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O28">
         <v>1</v>
@@ -5218,19 +5248,19 @@
         <v>38</v>
       </c>
       <c r="Q28">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R28">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y28" t="s">
-        <v>717</v>
+        <v>773</v>
       </c>
       <c r="Z28" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="AA28" t="s">
-        <v>718</v>
+        <v>774</v>
       </c>
       <c r="AB28" t="s">
         <v>39</v>
@@ -5244,13 +5274,13 @@
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>719</v>
+        <v>775</v>
       </c>
       <c r="C29" t="s">
-        <v>720</v>
+        <v>776</v>
       </c>
       <c r="D29" t="s">
-        <v>721</v>
+        <v>777</v>
       </c>
       <c r="E29" t="s">
         <v>33</v>
@@ -5268,13 +5298,13 @@
         <v>54</v>
       </c>
       <c r="K29" t="s">
-        <v>722</v>
+        <v>40</v>
       </c>
       <c r="L29" t="s">
-        <v>723</v>
+        <v>41</v>
       </c>
       <c r="M29" t="s">
-        <v>724</v>
+        <v>42</v>
       </c>
       <c r="N29" t="s">
         <v>33</v>
@@ -5286,19 +5316,16 @@
         <v>38</v>
       </c>
       <c r="Q29">
-        <v>12.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R29">
-        <v>2.17</v>
+        <v>11</v>
       </c>
       <c r="Y29" t="s">
-        <v>725</v>
-      </c>
-      <c r="Z29" t="s">
-        <v>726</v>
+        <v>778</v>
       </c>
       <c r="AA29" t="s">
-        <v>727</v>
+        <v>779</v>
       </c>
       <c r="AB29" t="s">
         <v>39</v>
@@ -5312,16 +5339,16 @@
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="C30" t="s">
-        <v>729</v>
+        <v>715</v>
       </c>
       <c r="D30" t="s">
-        <v>730</v>
+        <v>716</v>
       </c>
       <c r="E30" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F30" t="s">
         <v>34</v>
@@ -5345,7 +5372,7 @@
         <v>74</v>
       </c>
       <c r="N30" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O30">
         <v>1</v>
@@ -5360,10 +5387,13 @@
         <v>2</v>
       </c>
       <c r="Y30" t="s">
-        <v>731</v>
+        <v>717</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>51</v>
       </c>
       <c r="AA30" t="s">
-        <v>732</v>
+        <v>718</v>
       </c>
       <c r="AB30" t="s">
         <v>39</v>
@@ -5377,13 +5407,13 @@
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>733</v>
+        <v>719</v>
       </c>
       <c r="C31" t="s">
-        <v>734</v>
+        <v>720</v>
       </c>
       <c r="D31" t="s">
-        <v>735</v>
+        <v>721</v>
       </c>
       <c r="E31" t="s">
         <v>33</v>
@@ -5401,13 +5431,13 @@
         <v>54</v>
       </c>
       <c r="K31" t="s">
-        <v>43</v>
+        <v>722</v>
       </c>
       <c r="L31" t="s">
-        <v>44</v>
+        <v>723</v>
       </c>
       <c r="M31" t="s">
-        <v>45</v>
+        <v>724</v>
       </c>
       <c r="N31" t="s">
         <v>33</v>
@@ -5419,16 +5449,19 @@
         <v>38</v>
       </c>
       <c r="Q31">
-        <v>40.99</v>
+        <v>12.99</v>
       </c>
       <c r="R31">
-        <v>6.83</v>
+        <v>2.17</v>
       </c>
       <c r="Y31" t="s">
-        <v>736</v>
+        <v>725</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>726</v>
       </c>
       <c r="AA31" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
       <c r="AB31" t="s">
         <v>39</v>
@@ -5442,13 +5475,13 @@
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>738</v>
+        <v>728</v>
       </c>
       <c r="C32" t="s">
-        <v>739</v>
+        <v>729</v>
       </c>
       <c r="D32" t="s">
-        <v>740</v>
+        <v>730</v>
       </c>
       <c r="E32" t="s">
         <v>33</v>
@@ -5466,13 +5499,13 @@
         <v>54</v>
       </c>
       <c r="K32" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L32" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M32" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="N32" t="s">
         <v>33</v>
@@ -5484,16 +5517,16 @@
         <v>38</v>
       </c>
       <c r="Q32">
-        <v>40.99</v>
+        <v>11.99</v>
       </c>
       <c r="R32">
-        <v>6.83</v>
+        <v>2</v>
       </c>
       <c r="Y32" t="s">
-        <v>741</v>
+        <v>731</v>
       </c>
       <c r="AA32" t="s">
-        <v>742</v>
+        <v>732</v>
       </c>
       <c r="AB32" t="s">
         <v>39</v>
@@ -5507,13 +5540,13 @@
     </row>
     <row r="33" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>708</v>
+        <v>733</v>
       </c>
       <c r="C33" t="s">
-        <v>709</v>
+        <v>734</v>
       </c>
       <c r="D33" t="s">
-        <v>743</v>
+        <v>735</v>
       </c>
       <c r="E33" t="s">
         <v>33</v>
@@ -5531,13 +5564,13 @@
         <v>54</v>
       </c>
       <c r="K33" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L33" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M33" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N33" t="s">
         <v>33</v>
@@ -5549,19 +5582,16 @@
         <v>38</v>
       </c>
       <c r="Q33">
-        <v>65.989999999999995</v>
+        <v>40.99</v>
       </c>
       <c r="R33">
-        <v>11</v>
+        <v>6.83</v>
       </c>
       <c r="Y33" t="s">
-        <v>711</v>
-      </c>
-      <c r="Z33" t="s">
-        <v>712</v>
+        <v>736</v>
       </c>
       <c r="AA33" t="s">
-        <v>713</v>
+        <v>737</v>
       </c>
       <c r="AB33" t="s">
         <v>39</v>
@@ -5575,13 +5605,13 @@
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>643</v>
+        <v>738</v>
       </c>
       <c r="C34" t="s">
-        <v>644</v>
+        <v>739</v>
       </c>
       <c r="D34" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="E34" t="s">
         <v>33</v>
@@ -5599,13 +5629,13 @@
         <v>54</v>
       </c>
       <c r="K34" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="L34" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="M34" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="N34" t="s">
         <v>33</v>
@@ -5617,16 +5647,16 @@
         <v>38</v>
       </c>
       <c r="Q34">
-        <v>14.99</v>
+        <v>40.99</v>
       </c>
       <c r="R34">
-        <v>2.5</v>
+        <v>6.83</v>
       </c>
       <c r="Y34" t="s">
-        <v>646</v>
+        <v>741</v>
       </c>
       <c r="AA34" t="s">
-        <v>647</v>
+        <v>742</v>
       </c>
       <c r="AB34" t="s">
         <v>39</v>
@@ -5646,10 +5676,10 @@
         <v>709</v>
       </c>
       <c r="D35" t="s">
-        <v>710</v>
+        <v>743</v>
       </c>
       <c r="E35" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F35" t="s">
         <v>34</v>
@@ -5673,7 +5703,7 @@
         <v>42</v>
       </c>
       <c r="N35" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O35">
         <v>1</v>
@@ -5708,22 +5738,22 @@
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>138</v>
+        <v>643</v>
       </c>
       <c r="C36" t="s">
-        <v>139</v>
+        <v>644</v>
       </c>
       <c r="D36" t="s">
-        <v>187</v>
+        <v>744</v>
       </c>
       <c r="E36" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F36" t="s">
         <v>34</v>
       </c>
       <c r="G36" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="H36" t="s">
         <v>36</v>
@@ -5732,25 +5762,37 @@
         <v>54</v>
       </c>
       <c r="K36" t="s">
-        <v>141</v>
+        <v>94</v>
       </c>
       <c r="L36" t="s">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="M36" t="s">
-        <v>143</v>
+        <v>83</v>
+      </c>
+      <c r="N36" t="s">
+        <v>33</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P36" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q36">
+        <v>14.99</v>
+      </c>
+      <c r="R36">
+        <v>2.5</v>
       </c>
       <c r="Y36" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA36">
-        <v>80100</v>
+        <v>646</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>647</v>
       </c>
       <c r="AB36" t="s">
-        <v>145</v>
+        <v>39</v>
       </c>
       <c r="AD36" t="b">
         <v>0</v>
@@ -5761,22 +5803,22 @@
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>146</v>
+        <v>708</v>
       </c>
       <c r="C37" t="s">
-        <v>147</v>
+        <v>709</v>
       </c>
       <c r="D37" t="s">
-        <v>148</v>
+        <v>710</v>
       </c>
       <c r="E37" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="F37" t="s">
         <v>34</v>
       </c>
       <c r="G37" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="H37" t="s">
         <v>36</v>
@@ -5785,25 +5827,40 @@
         <v>54</v>
       </c>
       <c r="K37" t="s">
-        <v>141</v>
+        <v>40</v>
       </c>
       <c r="L37" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="M37" t="s">
-        <v>143</v>
+        <v>42</v>
+      </c>
+      <c r="N37" t="s">
+        <v>99</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P37" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q37">
+        <v>65.989999999999995</v>
+      </c>
+      <c r="R37">
+        <v>11</v>
       </c>
       <c r="Y37" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA37">
-        <v>80100</v>
+        <v>711</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>712</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>713</v>
       </c>
       <c r="AB37" t="s">
-        <v>145</v>
+        <v>39</v>
       </c>
       <c r="AD37" t="b">
         <v>0</v>
@@ -5814,13 +5871,13 @@
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>632</v>
+        <v>138</v>
       </c>
       <c r="C38" t="s">
-        <v>633</v>
+        <v>139</v>
       </c>
       <c r="D38" t="s">
-        <v>634</v>
+        <v>187</v>
       </c>
       <c r="E38" t="s">
         <v>53</v>
@@ -5829,7 +5886,7 @@
         <v>34</v>
       </c>
       <c r="G38" t="s">
-        <v>635</v>
+        <v>140</v>
       </c>
       <c r="H38" t="s">
         <v>36</v>
@@ -5838,37 +5895,25 @@
         <v>54</v>
       </c>
       <c r="K38" t="s">
-        <v>636</v>
+        <v>141</v>
       </c>
       <c r="L38" t="s">
-        <v>637</v>
+        <v>142</v>
       </c>
       <c r="M38" t="s">
-        <v>638</v>
+        <v>143</v>
       </c>
       <c r="O38">
         <v>0</v>
       </c>
-      <c r="P38" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q38">
-        <v>22.9</v>
-      </c>
-      <c r="R38">
-        <v>4.8099999999999996</v>
-      </c>
       <c r="Y38" t="s">
-        <v>639</v>
-      </c>
-      <c r="Z38" t="s">
-        <v>640</v>
-      </c>
-      <c r="AA38" t="s">
-        <v>641</v>
+        <v>144</v>
+      </c>
+      <c r="AA38">
+        <v>80100</v>
       </c>
       <c r="AB38" t="s">
-        <v>642</v>
+        <v>145</v>
       </c>
       <c r="AD38" t="b">
         <v>0</v>
@@ -5879,22 +5924,22 @@
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>643</v>
+        <v>146</v>
       </c>
       <c r="C39" t="s">
-        <v>644</v>
+        <v>147</v>
       </c>
       <c r="D39" t="s">
-        <v>645</v>
+        <v>148</v>
       </c>
       <c r="E39" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="F39" t="s">
         <v>34</v>
       </c>
       <c r="G39" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="H39" t="s">
         <v>36</v>
@@ -5903,37 +5948,25 @@
         <v>54</v>
       </c>
       <c r="K39" t="s">
-        <v>94</v>
+        <v>141</v>
       </c>
       <c r="L39" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="M39" t="s">
-        <v>83</v>
-      </c>
-      <c r="N39" t="s">
-        <v>99</v>
+        <v>143</v>
       </c>
       <c r="O39">
-        <v>1</v>
-      </c>
-      <c r="P39" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q39">
-        <v>14.99</v>
-      </c>
-      <c r="R39">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="s">
-        <v>646</v>
-      </c>
-      <c r="AA39" t="s">
-        <v>647</v>
+        <v>144</v>
+      </c>
+      <c r="AA39">
+        <v>80100</v>
       </c>
       <c r="AB39" t="s">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="AD39" t="b">
         <v>0</v>
@@ -5944,22 +5977,22 @@
     </row>
     <row r="40" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>609</v>
+        <v>632</v>
       </c>
       <c r="C40" t="s">
-        <v>610</v>
+        <v>633</v>
       </c>
       <c r="D40" t="s">
-        <v>611</v>
+        <v>634</v>
       </c>
       <c r="E40" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F40" t="s">
         <v>34</v>
       </c>
       <c r="G40" t="s">
-        <v>35</v>
+        <v>635</v>
       </c>
       <c r="H40" t="s">
         <v>36</v>
@@ -5968,40 +6001,37 @@
         <v>54</v>
       </c>
       <c r="K40" t="s">
-        <v>94</v>
+        <v>636</v>
       </c>
       <c r="L40" t="s">
-        <v>82</v>
+        <v>637</v>
       </c>
       <c r="M40" t="s">
-        <v>83</v>
-      </c>
-      <c r="N40" t="s">
-        <v>33</v>
+        <v>638</v>
       </c>
       <c r="O40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P40" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="Q40">
-        <v>14.99</v>
+        <v>22.9</v>
       </c>
       <c r="R40">
-        <v>2.5</v>
+        <v>4.8099999999999996</v>
       </c>
       <c r="Y40" t="s">
-        <v>612</v>
+        <v>639</v>
       </c>
       <c r="Z40" t="s">
-        <v>613</v>
+        <v>640</v>
       </c>
       <c r="AA40" t="s">
-        <v>614</v>
+        <v>641</v>
       </c>
       <c r="AB40" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="AD40" t="b">
         <v>0</v>
@@ -6012,16 +6042,16 @@
     </row>
     <row r="41" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>493</v>
+        <v>643</v>
       </c>
       <c r="C41" t="s">
-        <v>494</v>
+        <v>644</v>
       </c>
       <c r="D41" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="E41" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="F41" t="s">
         <v>34</v>
@@ -6036,22 +6066,34 @@
         <v>54</v>
       </c>
       <c r="K41" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L41" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M41" t="s">
-        <v>42</v>
+        <v>83</v>
+      </c>
+      <c r="N41" t="s">
+        <v>99</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P41" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q41">
+        <v>14.99</v>
+      </c>
+      <c r="R41">
+        <v>2.5</v>
       </c>
       <c r="Y41" t="s">
-        <v>495</v>
+        <v>646</v>
       </c>
       <c r="AA41" t="s">
-        <v>496</v>
+        <v>647</v>
       </c>
       <c r="AB41" t="s">
         <v>39</v>
@@ -6065,16 +6107,16 @@
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="C42" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="D42" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="E42" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F42" t="s">
         <v>34</v>
@@ -6089,16 +6131,16 @@
         <v>54</v>
       </c>
       <c r="K42" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="L42" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="M42" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="N42" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O42">
         <v>1</v>
@@ -6107,16 +6149,19 @@
         <v>38</v>
       </c>
       <c r="Q42">
-        <v>40.99</v>
+        <v>14.99</v>
+      </c>
+      <c r="R42">
+        <v>2.5</v>
       </c>
       <c r="Y42" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="Z42" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="AA42" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="AB42" t="s">
         <v>39</v>
@@ -6130,16 +6175,16 @@
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>621</v>
+        <v>493</v>
       </c>
       <c r="C43" t="s">
-        <v>622</v>
+        <v>494</v>
       </c>
       <c r="D43" t="s">
-        <v>623</v>
+        <v>648</v>
       </c>
       <c r="E43" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F43" t="s">
         <v>34</v>
@@ -6162,35 +6207,14 @@
       <c r="M43" t="s">
         <v>42</v>
       </c>
-      <c r="N43" t="s">
-        <v>33</v>
-      </c>
       <c r="O43">
-        <v>1</v>
-      </c>
-      <c r="P43" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q43">
-        <v>64.989999999999995</v>
-      </c>
-      <c r="R43">
-        <v>10.83</v>
-      </c>
-      <c r="S43">
-        <v>6.99</v>
-      </c>
-      <c r="T43">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="s">
-        <v>624</v>
-      </c>
-      <c r="Z43" t="s">
-        <v>625</v>
+        <v>495</v>
       </c>
       <c r="AA43" t="s">
-        <v>626</v>
+        <v>496</v>
       </c>
       <c r="AB43" t="s">
         <v>39</v>
@@ -6204,16 +6228,16 @@
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="C44" t="s">
-        <v>628</v>
+        <v>616</v>
       </c>
       <c r="D44" t="s">
-        <v>629</v>
+        <v>617</v>
       </c>
       <c r="E44" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F44" t="s">
         <v>34</v>
@@ -6228,16 +6252,16 @@
         <v>54</v>
       </c>
       <c r="K44" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L44" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M44" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N44" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O44">
         <v>1</v>
@@ -6246,16 +6270,16 @@
         <v>38</v>
       </c>
       <c r="Q44">
-        <v>11.99</v>
-      </c>
-      <c r="R44">
-        <v>2</v>
+        <v>40.99</v>
       </c>
       <c r="Y44" t="s">
-        <v>630</v>
+        <v>618</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>619</v>
       </c>
       <c r="AA44" t="s">
-        <v>631</v>
+        <v>620</v>
       </c>
       <c r="AB44" t="s">
         <v>39</v>
@@ -6269,13 +6293,13 @@
     </row>
     <row r="45" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>649</v>
+        <v>621</v>
       </c>
       <c r="C45" t="s">
-        <v>650</v>
+        <v>622</v>
       </c>
       <c r="D45" t="s">
-        <v>651</v>
+        <v>623</v>
       </c>
       <c r="E45" t="s">
         <v>33</v>
@@ -6293,13 +6317,13 @@
         <v>54</v>
       </c>
       <c r="K45" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L45" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M45" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N45" t="s">
         <v>33</v>
@@ -6311,19 +6335,25 @@
         <v>38</v>
       </c>
       <c r="Q45">
-        <v>39.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R45">
-        <v>6.67</v>
+        <v>10.83</v>
+      </c>
+      <c r="S45">
+        <v>6.99</v>
+      </c>
+      <c r="T45">
+        <v>1.17</v>
       </c>
       <c r="Y45" t="s">
-        <v>652</v>
+        <v>624</v>
       </c>
       <c r="Z45" t="s">
-        <v>653</v>
+        <v>625</v>
       </c>
       <c r="AA45" t="s">
-        <v>654</v>
+        <v>626</v>
       </c>
       <c r="AB45" t="s">
         <v>39</v>
@@ -6337,13 +6367,13 @@
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>655</v>
+        <v>627</v>
       </c>
       <c r="C46" t="s">
-        <v>656</v>
+        <v>628</v>
       </c>
       <c r="D46" t="s">
-        <v>657</v>
+        <v>629</v>
       </c>
       <c r="E46" t="s">
         <v>33</v>
@@ -6361,13 +6391,13 @@
         <v>54</v>
       </c>
       <c r="K46" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L46" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M46" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="N46" t="s">
         <v>33</v>
@@ -6379,16 +6409,16 @@
         <v>38</v>
       </c>
       <c r="Q46">
-        <v>14.99</v>
+        <v>11.99</v>
       </c>
       <c r="R46">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Y46" t="s">
-        <v>658</v>
+        <v>630</v>
       </c>
       <c r="AA46" t="s">
-        <v>659</v>
+        <v>631</v>
       </c>
       <c r="AB46" t="s">
         <v>39</v>
@@ -6402,13 +6432,13 @@
     </row>
     <row r="47" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>571</v>
+        <v>649</v>
       </c>
       <c r="C47" t="s">
-        <v>572</v>
+        <v>650</v>
       </c>
       <c r="D47" t="s">
-        <v>660</v>
+        <v>651</v>
       </c>
       <c r="E47" t="s">
         <v>33</v>
@@ -6426,13 +6456,13 @@
         <v>54</v>
       </c>
       <c r="K47" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L47" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M47" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N47" t="s">
         <v>33</v>
@@ -6444,16 +6474,19 @@
         <v>38</v>
       </c>
       <c r="Q47">
-        <v>64.989999999999995</v>
+        <v>39.99</v>
       </c>
       <c r="R47">
-        <v>10.83</v>
+        <v>6.67</v>
       </c>
       <c r="Y47" t="s">
-        <v>573</v>
+        <v>652</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>653</v>
       </c>
       <c r="AA47" t="s">
-        <v>574</v>
+        <v>654</v>
       </c>
       <c r="AB47" t="s">
         <v>39</v>
@@ -6467,13 +6500,13 @@
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>599</v>
+        <v>655</v>
       </c>
       <c r="C48" t="s">
-        <v>600</v>
+        <v>656</v>
       </c>
       <c r="D48" t="s">
-        <v>601</v>
+        <v>657</v>
       </c>
       <c r="E48" t="s">
         <v>33</v>
@@ -6515,10 +6548,10 @@
         <v>2.5</v>
       </c>
       <c r="Y48" t="s">
-        <v>61</v>
+        <v>658</v>
       </c>
       <c r="AA48" t="s">
-        <v>602</v>
+        <v>659</v>
       </c>
       <c r="AB48" t="s">
         <v>39</v>
@@ -6532,13 +6565,13 @@
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>589</v>
+        <v>571</v>
       </c>
       <c r="C49" t="s">
-        <v>590</v>
+        <v>572</v>
       </c>
       <c r="D49" t="s">
-        <v>591</v>
+        <v>660</v>
       </c>
       <c r="E49" t="s">
         <v>33</v>
@@ -6580,10 +6613,10 @@
         <v>10.83</v>
       </c>
       <c r="Y49" t="s">
-        <v>592</v>
+        <v>573</v>
       </c>
       <c r="AA49" t="s">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="AB49" t="s">
         <v>39</v>
@@ -6597,13 +6630,13 @@
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="C50" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="D50" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="E50" t="s">
         <v>33</v>
@@ -6621,13 +6654,13 @@
         <v>54</v>
       </c>
       <c r="K50" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L50" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M50" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="N50" t="s">
         <v>33</v>
@@ -6639,16 +6672,16 @@
         <v>38</v>
       </c>
       <c r="Q50">
-        <v>64.989999999999995</v>
+        <v>14.99</v>
       </c>
       <c r="R50">
-        <v>10.83</v>
+        <v>2.5</v>
       </c>
       <c r="Y50" t="s">
-        <v>597</v>
+        <v>61</v>
       </c>
       <c r="AA50" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="AB50" t="s">
         <v>39</v>
@@ -6662,13 +6695,13 @@
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>603</v>
+        <v>589</v>
       </c>
       <c r="C51" t="s">
-        <v>604</v>
+        <v>590</v>
       </c>
       <c r="D51" t="s">
-        <v>605</v>
+        <v>591</v>
       </c>
       <c r="E51" t="s">
         <v>33</v>
@@ -6710,13 +6743,10 @@
         <v>10.83</v>
       </c>
       <c r="Y51" t="s">
-        <v>606</v>
-      </c>
-      <c r="Z51" t="s">
-        <v>607</v>
+        <v>592</v>
       </c>
       <c r="AA51" t="s">
-        <v>608</v>
+        <v>593</v>
       </c>
       <c r="AB51" t="s">
         <v>39</v>
@@ -6730,13 +6760,13 @@
     </row>
     <row r="52" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>578</v>
+        <v>594</v>
       </c>
       <c r="C52" t="s">
-        <v>579</v>
+        <v>595</v>
       </c>
       <c r="D52" t="s">
-        <v>661</v>
+        <v>596</v>
       </c>
       <c r="E52" t="s">
         <v>33</v>
@@ -6778,13 +6808,10 @@
         <v>10.83</v>
       </c>
       <c r="Y52" t="s">
-        <v>580</v>
-      </c>
-      <c r="Z52" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="AA52" t="s">
-        <v>582</v>
+        <v>598</v>
       </c>
       <c r="AB52" t="s">
         <v>39</v>
@@ -6798,16 +6825,16 @@
     </row>
     <row r="53" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>575</v>
+        <v>603</v>
       </c>
       <c r="C53" t="s">
-        <v>576</v>
+        <v>604</v>
       </c>
       <c r="D53" t="s">
-        <v>577</v>
+        <v>605</v>
       </c>
       <c r="E53" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F53" t="s">
         <v>34</v>
@@ -6830,14 +6857,29 @@
       <c r="M53" t="s">
         <v>42</v>
       </c>
+      <c r="N53" t="s">
+        <v>33</v>
+      </c>
       <c r="O53">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P53" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q53">
+        <v>64.989999999999995</v>
+      </c>
+      <c r="R53">
+        <v>10.83</v>
       </c>
       <c r="Y53" t="s">
-        <v>573</v>
+        <v>606</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>607</v>
       </c>
       <c r="AA53" t="s">
-        <v>574</v>
+        <v>608</v>
       </c>
       <c r="AB53" t="s">
         <v>39</v>
@@ -6851,13 +6893,13 @@
     </row>
     <row r="54" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>518</v>
+        <v>578</v>
       </c>
       <c r="C54" t="s">
-        <v>519</v>
+        <v>579</v>
       </c>
       <c r="D54" t="s">
-        <v>583</v>
+        <v>661</v>
       </c>
       <c r="E54" t="s">
         <v>33</v>
@@ -6875,13 +6917,13 @@
         <v>54</v>
       </c>
       <c r="K54" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L54" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M54" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N54" t="s">
         <v>33</v>
@@ -6893,22 +6935,19 @@
         <v>38</v>
       </c>
       <c r="Q54">
-        <v>37.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R54">
-        <v>6.33</v>
-      </c>
-      <c r="S54">
-        <v>6.99</v>
-      </c>
-      <c r="T54">
-        <v>1.17</v>
+        <v>10.83</v>
       </c>
       <c r="Y54" t="s">
-        <v>46</v>
+        <v>580</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>581</v>
       </c>
       <c r="AA54" t="s">
-        <v>520</v>
+        <v>582</v>
       </c>
       <c r="AB54" t="s">
         <v>39</v>
@@ -6922,16 +6961,16 @@
     </row>
     <row r="55" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="C55" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="D55" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="E55" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F55" t="s">
         <v>34</v>
@@ -6954,26 +6993,14 @@
       <c r="M55" t="s">
         <v>42</v>
       </c>
-      <c r="N55" t="s">
-        <v>33</v>
-      </c>
       <c r="O55">
-        <v>1</v>
-      </c>
-      <c r="P55" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q55">
-        <v>64.989999999999995</v>
-      </c>
-      <c r="R55">
-        <v>10.83</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="s">
-        <v>587</v>
+        <v>573</v>
       </c>
       <c r="AA55" t="s">
-        <v>588</v>
+        <v>574</v>
       </c>
       <c r="AB55" t="s">
         <v>39</v>
@@ -6987,13 +7014,13 @@
     </row>
     <row r="56" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>457</v>
+        <v>518</v>
       </c>
       <c r="C56" t="s">
-        <v>458</v>
+        <v>519</v>
       </c>
       <c r="D56" t="s">
-        <v>459</v>
+        <v>583</v>
       </c>
       <c r="E56" t="s">
         <v>33</v>
@@ -7011,13 +7038,13 @@
         <v>54</v>
       </c>
       <c r="K56" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L56" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M56" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N56" t="s">
         <v>33</v>
@@ -7029,19 +7056,22 @@
         <v>38</v>
       </c>
       <c r="Q56">
-        <v>64.989999999999995</v>
+        <v>37.99</v>
       </c>
       <c r="R56">
-        <v>10.83</v>
+        <v>6.33</v>
+      </c>
+      <c r="S56">
+        <v>6.99</v>
+      </c>
+      <c r="T56">
+        <v>1.17</v>
       </c>
       <c r="Y56" t="s">
-        <v>460</v>
-      </c>
-      <c r="Z56" t="s">
-        <v>279</v>
+        <v>46</v>
       </c>
       <c r="AA56" t="s">
-        <v>461</v>
+        <v>520</v>
       </c>
       <c r="AB56" t="s">
         <v>39</v>
@@ -7055,13 +7085,13 @@
     </row>
     <row r="57" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>462</v>
+        <v>584</v>
       </c>
       <c r="C57" t="s">
-        <v>463</v>
+        <v>585</v>
       </c>
       <c r="D57" t="s">
-        <v>459</v>
+        <v>586</v>
       </c>
       <c r="E57" t="s">
         <v>33</v>
@@ -7103,10 +7133,10 @@
         <v>10.83</v>
       </c>
       <c r="Y57" t="s">
-        <v>56</v>
+        <v>587</v>
       </c>
       <c r="AA57" t="s">
-        <v>464</v>
+        <v>588</v>
       </c>
       <c r="AB57" t="s">
         <v>39</v>
@@ -7120,13 +7150,13 @@
     </row>
     <row r="58" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="C58" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D58" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="E58" t="s">
         <v>33</v>
@@ -7144,34 +7174,37 @@
         <v>54</v>
       </c>
       <c r="K58" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L58" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M58" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N58" t="s">
         <v>33</v>
       </c>
       <c r="O58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P58" t="s">
         <v>38</v>
       </c>
       <c r="Q58">
-        <v>79.98</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R58">
-        <v>13.34</v>
+        <v>10.83</v>
       </c>
       <c r="Y58" t="s">
-        <v>468</v>
+        <v>460</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>279</v>
       </c>
       <c r="AA58" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="AB58" t="s">
         <v>39</v>
@@ -7185,13 +7218,13 @@
     </row>
     <row r="59" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="C59" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="D59" t="s">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="E59" t="s">
         <v>33</v>
@@ -7209,13 +7242,13 @@
         <v>54</v>
       </c>
       <c r="K59" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L59" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M59" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N59" t="s">
         <v>33</v>
@@ -7227,16 +7260,16 @@
         <v>38</v>
       </c>
       <c r="Q59">
-        <v>37.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R59">
-        <v>6.33</v>
+        <v>10.83</v>
       </c>
       <c r="Y59" t="s">
-        <v>473</v>
+        <v>56</v>
       </c>
       <c r="AA59" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="AB59" t="s">
         <v>39</v>
@@ -7250,16 +7283,16 @@
     </row>
     <row r="60" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="C60" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="D60" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="E60" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F60" t="s">
         <v>34</v>
@@ -7274,25 +7307,34 @@
         <v>54</v>
       </c>
       <c r="K60" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L60" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M60" t="s">
-        <v>42</v>
+        <v>50</v>
+      </c>
+      <c r="N60" t="s">
+        <v>33</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="P60" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q60">
+        <v>79.98</v>
+      </c>
+      <c r="R60">
+        <v>13.34</v>
       </c>
       <c r="Y60" t="s">
-        <v>478</v>
-      </c>
-      <c r="Z60" t="s">
-        <v>279</v>
+        <v>468</v>
       </c>
       <c r="AA60" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="AB60" t="s">
         <v>39</v>
@@ -7306,13 +7348,13 @@
     </row>
     <row r="61" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="C61" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="D61" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="E61" t="s">
         <v>33</v>
@@ -7330,13 +7372,13 @@
         <v>54</v>
       </c>
       <c r="K61" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L61" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M61" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N61" t="s">
         <v>33</v>
@@ -7348,16 +7390,16 @@
         <v>38</v>
       </c>
       <c r="Q61">
-        <v>11.99</v>
+        <v>37.99</v>
       </c>
       <c r="R61">
-        <v>2</v>
+        <v>6.33</v>
       </c>
       <c r="Y61" t="s">
-        <v>61</v>
+        <v>473</v>
       </c>
       <c r="AA61" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="AB61" t="s">
         <v>39</v>
@@ -7371,16 +7413,16 @@
     </row>
     <row r="62" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="C62" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="D62" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="E62" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F62" t="s">
         <v>34</v>
@@ -7403,26 +7445,17 @@
       <c r="M62" t="s">
         <v>42</v>
       </c>
-      <c r="N62" t="s">
-        <v>33</v>
-      </c>
       <c r="O62">
-        <v>1</v>
-      </c>
-      <c r="P62" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q62">
-        <v>64.989999999999995</v>
-      </c>
-      <c r="R62">
-        <v>10.83</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="s">
-        <v>67</v>
+        <v>478</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>279</v>
       </c>
       <c r="AA62" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="AB62" t="s">
         <v>39</v>
@@ -7436,13 +7469,13 @@
     </row>
     <row r="63" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="C63" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="D63" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="E63" t="s">
         <v>33</v>
@@ -7460,37 +7493,34 @@
         <v>54</v>
       </c>
       <c r="K63" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L63" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M63" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="N63" t="s">
         <v>33</v>
       </c>
       <c r="O63">
+        <v>1</v>
+      </c>
+      <c r="P63" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q63">
+        <v>11.99</v>
+      </c>
+      <c r="R63">
         <v>2</v>
       </c>
-      <c r="P63" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q63">
-        <v>79.98</v>
-      </c>
-      <c r="R63">
-        <v>13.34</v>
-      </c>
       <c r="Y63" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z63" t="s">
-        <v>491</v>
+        <v>61</v>
       </c>
       <c r="AA63" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="AB63" t="s">
         <v>39</v>
@@ -7504,13 +7534,13 @@
     </row>
     <row r="64" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="C64" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="D64" t="s">
-        <v>499</v>
+        <v>486</v>
       </c>
       <c r="E64" t="s">
         <v>33</v>
@@ -7546,19 +7576,16 @@
         <v>38</v>
       </c>
       <c r="Q64">
-        <v>59.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R64">
-        <v>10</v>
+        <v>10.83</v>
       </c>
       <c r="Y64" t="s">
-        <v>500</v>
-      </c>
-      <c r="Z64" t="s">
-        <v>501</v>
+        <v>67</v>
       </c>
       <c r="AA64" t="s">
-        <v>502</v>
+        <v>487</v>
       </c>
       <c r="AB64" t="s">
         <v>39</v>
@@ -7572,13 +7599,13 @@
     </row>
     <row r="65" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>503</v>
+        <v>488</v>
       </c>
       <c r="C65" t="s">
-        <v>504</v>
+        <v>489</v>
       </c>
       <c r="D65" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="E65" t="s">
         <v>33</v>
@@ -7596,37 +7623,37 @@
         <v>54</v>
       </c>
       <c r="K65" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L65" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M65" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N65" t="s">
         <v>33</v>
       </c>
       <c r="O65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P65" t="s">
         <v>38</v>
       </c>
       <c r="Q65">
-        <v>59.99</v>
+        <v>79.98</v>
       </c>
       <c r="R65">
-        <v>10</v>
+        <v>13.34</v>
       </c>
       <c r="Y65" t="s">
-        <v>505</v>
+        <v>63</v>
       </c>
       <c r="Z65" t="s">
-        <v>93</v>
+        <v>491</v>
       </c>
       <c r="AA65" t="s">
-        <v>506</v>
+        <v>492</v>
       </c>
       <c r="AB65" t="s">
         <v>39</v>
@@ -7640,13 +7667,13 @@
     </row>
     <row r="66" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="C66" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="D66" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="E66" t="s">
         <v>33</v>
@@ -7688,10 +7715,13 @@
         <v>10</v>
       </c>
       <c r="Y66" t="s">
-        <v>510</v>
+        <v>500</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>501</v>
       </c>
       <c r="AA66" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="AB66" t="s">
         <v>39</v>
@@ -7705,13 +7735,13 @@
     </row>
     <row r="67" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="C67" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="D67" t="s">
-        <v>514</v>
+        <v>499</v>
       </c>
       <c r="E67" t="s">
         <v>33</v>
@@ -7753,13 +7783,13 @@
         <v>10</v>
       </c>
       <c r="Y67" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="Z67" t="s">
-        <v>516</v>
+        <v>93</v>
       </c>
       <c r="AA67" t="s">
-        <v>517</v>
+        <v>506</v>
       </c>
       <c r="AB67" t="s">
         <v>39</v>
@@ -7773,13 +7803,13 @@
     </row>
     <row r="68" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>521</v>
+        <v>507</v>
       </c>
       <c r="C68" t="s">
-        <v>522</v>
+        <v>508</v>
       </c>
       <c r="D68" t="s">
-        <v>523</v>
+        <v>509</v>
       </c>
       <c r="E68" t="s">
         <v>33</v>
@@ -7797,13 +7827,13 @@
         <v>54</v>
       </c>
       <c r="K68" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L68" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M68" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="N68" t="s">
         <v>33</v>
@@ -7815,16 +7845,16 @@
         <v>38</v>
       </c>
       <c r="Q68">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R68">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y68" t="s">
-        <v>58</v>
+        <v>510</v>
       </c>
       <c r="AA68" t="s">
-        <v>524</v>
+        <v>511</v>
       </c>
       <c r="AB68" t="s">
         <v>39</v>
@@ -7838,13 +7868,13 @@
     </row>
     <row r="69" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="C69" t="s">
-        <v>526</v>
+        <v>513</v>
       </c>
       <c r="D69" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
       <c r="E69" t="s">
         <v>33</v>
@@ -7886,10 +7916,13 @@
         <v>10</v>
       </c>
       <c r="Y69" t="s">
-        <v>90</v>
+        <v>515</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>516</v>
       </c>
       <c r="AA69" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="AB69" t="s">
         <v>39</v>
@@ -7903,13 +7936,13 @@
     </row>
     <row r="70" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="C70" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="D70" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="E70" t="s">
         <v>33</v>
@@ -7927,13 +7960,13 @@
         <v>54</v>
       </c>
       <c r="K70" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L70" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M70" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="N70" t="s">
         <v>33</v>
@@ -7945,16 +7978,16 @@
         <v>38</v>
       </c>
       <c r="Q70">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="R70">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="Y70" t="s">
-        <v>531</v>
+        <v>58</v>
       </c>
       <c r="AA70" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="AB70" t="s">
         <v>39</v>
@@ -7968,13 +8001,13 @@
     </row>
     <row r="71" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="C71" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="D71" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="E71" t="s">
         <v>33</v>
@@ -7992,13 +8025,13 @@
         <v>54</v>
       </c>
       <c r="K71" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L71" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M71" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N71" t="s">
         <v>33</v>
@@ -8010,19 +8043,16 @@
         <v>38</v>
       </c>
       <c r="Q71">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R71">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y71" t="s">
-        <v>536</v>
-      </c>
-      <c r="Z71" t="s">
-        <v>537</v>
+        <v>90</v>
       </c>
       <c r="AA71" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="AB71" t="s">
         <v>39</v>
@@ -8036,13 +8066,13 @@
     </row>
     <row r="72" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="C72" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="D72" t="s">
-        <v>541</v>
+        <v>527</v>
       </c>
       <c r="E72" t="s">
         <v>33</v>
@@ -8084,13 +8114,10 @@
         <v>10</v>
       </c>
       <c r="Y72" t="s">
-        <v>71</v>
-      </c>
-      <c r="Z72" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="AA72" t="s">
-        <v>543</v>
+        <v>532</v>
       </c>
       <c r="AB72" t="s">
         <v>39</v>
@@ -8104,13 +8131,13 @@
     </row>
     <row r="73" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
       <c r="C73" t="s">
-        <v>545</v>
+        <v>534</v>
       </c>
       <c r="D73" t="s">
-        <v>546</v>
+        <v>535</v>
       </c>
       <c r="E73" t="s">
         <v>33</v>
@@ -8128,37 +8155,37 @@
         <v>54</v>
       </c>
       <c r="K73" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="L73" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="M73" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="N73" t="s">
         <v>33</v>
       </c>
       <c r="O73">
+        <v>1</v>
+      </c>
+      <c r="P73" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q73">
+        <v>11.99</v>
+      </c>
+      <c r="R73">
         <v>2</v>
       </c>
-      <c r="P73" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q73">
-        <v>76.98</v>
-      </c>
-      <c r="R73">
-        <v>12.84</v>
-      </c>
       <c r="Y73" t="s">
-        <v>547</v>
+        <v>536</v>
       </c>
       <c r="Z73" t="s">
-        <v>548</v>
+        <v>537</v>
       </c>
       <c r="AA73" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="AB73" t="s">
         <v>39</v>
@@ -8172,13 +8199,13 @@
     </row>
     <row r="74" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>550</v>
+        <v>539</v>
       </c>
       <c r="C74" t="s">
-        <v>551</v>
+        <v>540</v>
       </c>
       <c r="D74" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="E74" t="s">
         <v>33</v>
@@ -8220,10 +8247,13 @@
         <v>10</v>
       </c>
       <c r="Y74" t="s">
-        <v>553</v>
+        <v>71</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>542</v>
       </c>
       <c r="AA74" t="s">
-        <v>554</v>
+        <v>543</v>
       </c>
       <c r="AB74" t="s">
         <v>39</v>
@@ -8237,13 +8267,13 @@
     </row>
     <row r="75" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>555</v>
+        <v>544</v>
       </c>
       <c r="C75" t="s">
-        <v>556</v>
+        <v>545</v>
       </c>
       <c r="D75" t="s">
-        <v>557</v>
+        <v>546</v>
       </c>
       <c r="E75" t="s">
         <v>33</v>
@@ -8261,34 +8291,37 @@
         <v>54</v>
       </c>
       <c r="K75" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L75" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M75" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N75" t="s">
         <v>33</v>
       </c>
       <c r="O75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P75" t="s">
         <v>38</v>
       </c>
       <c r="Q75">
-        <v>59.99</v>
+        <v>76.98</v>
       </c>
       <c r="R75">
-        <v>10</v>
+        <v>12.84</v>
       </c>
       <c r="Y75" t="s">
-        <v>558</v>
+        <v>547</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>548</v>
       </c>
       <c r="AA75" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
       <c r="AB75" t="s">
         <v>39</v>
@@ -8302,13 +8335,13 @@
     </row>
     <row r="76" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>418</v>
+        <v>550</v>
       </c>
       <c r="C76" t="s">
-        <v>419</v>
+        <v>551</v>
       </c>
       <c r="D76" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="E76" t="s">
         <v>33</v>
@@ -8350,10 +8383,10 @@
         <v>10</v>
       </c>
       <c r="Y76" t="s">
-        <v>420</v>
+        <v>553</v>
       </c>
       <c r="AA76" t="s">
-        <v>421</v>
+        <v>554</v>
       </c>
       <c r="AB76" t="s">
         <v>39</v>
@@ -8367,13 +8400,13 @@
     </row>
     <row r="77" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="C77" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="D77" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="E77" t="s">
         <v>33</v>
@@ -8415,13 +8448,10 @@
         <v>10</v>
       </c>
       <c r="Y77" t="s">
-        <v>564</v>
-      </c>
-      <c r="Z77" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="AA77" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="AB77" t="s">
         <v>39</v>
@@ -8435,13 +8465,13 @@
     </row>
     <row r="78" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>567</v>
+        <v>418</v>
       </c>
       <c r="C78" t="s">
-        <v>568</v>
+        <v>419</v>
       </c>
       <c r="D78" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="E78" t="s">
         <v>33</v>
@@ -8459,13 +8489,13 @@
         <v>54</v>
       </c>
       <c r="K78" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L78" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M78" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="N78" t="s">
         <v>33</v>
@@ -8477,16 +8507,16 @@
         <v>38</v>
       </c>
       <c r="Q78">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R78">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y78" t="s">
-        <v>69</v>
+        <v>420</v>
       </c>
       <c r="AA78" t="s">
-        <v>570</v>
+        <v>421</v>
       </c>
       <c r="AB78" t="s">
         <v>39</v>
@@ -8500,13 +8530,13 @@
     </row>
     <row r="79" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>413</v>
+        <v>561</v>
       </c>
       <c r="C79" t="s">
-        <v>414</v>
+        <v>562</v>
       </c>
       <c r="D79" t="s">
-        <v>415</v>
+        <v>563</v>
       </c>
       <c r="E79" t="s">
         <v>33</v>
@@ -8548,10 +8578,13 @@
         <v>10</v>
       </c>
       <c r="Y79" t="s">
-        <v>416</v>
+        <v>564</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>565</v>
       </c>
       <c r="AA79" t="s">
-        <v>417</v>
+        <v>566</v>
       </c>
       <c r="AB79" t="s">
         <v>39</v>
@@ -8565,13 +8598,13 @@
     </row>
     <row r="80" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>422</v>
+        <v>567</v>
       </c>
       <c r="C80" t="s">
-        <v>423</v>
+        <v>568</v>
       </c>
       <c r="D80" t="s">
-        <v>424</v>
+        <v>569</v>
       </c>
       <c r="E80" t="s">
         <v>33</v>
@@ -8589,13 +8622,13 @@
         <v>54</v>
       </c>
       <c r="K80" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="L80" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M80" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="N80" t="s">
         <v>33</v>
@@ -8607,16 +8640,16 @@
         <v>38</v>
       </c>
       <c r="Q80">
-        <v>22.99</v>
+        <v>14.99</v>
       </c>
       <c r="R80">
-        <v>3.83</v>
+        <v>2.5</v>
       </c>
       <c r="Y80" t="s">
-        <v>425</v>
+        <v>69</v>
       </c>
       <c r="AA80" t="s">
-        <v>426</v>
+        <v>570</v>
       </c>
       <c r="AB80" t="s">
         <v>39</v>
@@ -8630,13 +8663,13 @@
     </row>
     <row r="81" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="C81" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="D81" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="E81" t="s">
         <v>33</v>
@@ -8654,13 +8687,13 @@
         <v>54</v>
       </c>
       <c r="K81" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L81" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M81" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N81" t="s">
         <v>33</v>
@@ -8672,19 +8705,16 @@
         <v>38</v>
       </c>
       <c r="Q81">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R81">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y81" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z81" t="s">
-        <v>97</v>
+        <v>416</v>
       </c>
       <c r="AA81" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="AB81" t="s">
         <v>39</v>
@@ -8698,13 +8728,13 @@
     </row>
     <row r="82" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="C82" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="D82" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="E82" t="s">
         <v>33</v>
@@ -8722,13 +8752,13 @@
         <v>54</v>
       </c>
       <c r="K82" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="L82" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="M82" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="N82" t="s">
         <v>33</v>
@@ -8740,19 +8770,16 @@
         <v>38</v>
       </c>
       <c r="Q82">
-        <v>38.49</v>
+        <v>22.99</v>
       </c>
       <c r="R82">
-        <v>6.42</v>
+        <v>3.83</v>
       </c>
       <c r="Y82" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z82" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="AA82" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="AB82" t="s">
         <v>39</v>
@@ -8766,13 +8793,13 @@
     </row>
     <row r="83" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="C83" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="D83" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="E83" t="s">
         <v>33</v>
@@ -8790,13 +8817,13 @@
         <v>54</v>
       </c>
       <c r="K83" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="L83" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="M83" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="N83" t="s">
         <v>33</v>
@@ -8808,16 +8835,19 @@
         <v>38</v>
       </c>
       <c r="Q83">
-        <v>14.99</v>
+        <v>11.99</v>
       </c>
       <c r="R83">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Y83" t="s">
-        <v>438</v>
+        <v>96</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>97</v>
       </c>
       <c r="AA83" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="AB83" t="s">
         <v>39</v>
@@ -8831,13 +8861,13 @@
     </row>
     <row r="84" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="C84" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="D84" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="E84" t="s">
         <v>33</v>
@@ -8855,13 +8885,13 @@
         <v>54</v>
       </c>
       <c r="K84" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="L84" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="M84" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="N84" t="s">
         <v>33</v>
@@ -8873,16 +8903,19 @@
         <v>38</v>
       </c>
       <c r="Q84">
-        <v>37.99</v>
+        <v>38.49</v>
       </c>
       <c r="R84">
-        <v>6.33</v>
+        <v>6.42</v>
       </c>
       <c r="Y84" t="s">
-        <v>443</v>
+        <v>59</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>433</v>
       </c>
       <c r="AA84" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="AB84" t="s">
         <v>39</v>
@@ -8896,13 +8929,13 @@
     </row>
     <row r="85" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="C85" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="D85" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="E85" t="s">
         <v>33</v>
@@ -8920,13 +8953,13 @@
         <v>54</v>
       </c>
       <c r="K85" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="L85" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="M85" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="N85" t="s">
         <v>33</v>
@@ -8938,16 +8971,16 @@
         <v>38</v>
       </c>
       <c r="Q85">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="R85">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="Y85" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="AA85" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="AB85" t="s">
         <v>39</v>
@@ -8961,16 +8994,16 @@
     </row>
     <row r="86" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="C86" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="D86" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="E86" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F86" t="s">
         <v>34</v>
@@ -8985,22 +9018,34 @@
         <v>54</v>
       </c>
       <c r="K86" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L86" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M86" t="s">
-        <v>42</v>
+        <v>50</v>
+      </c>
+      <c r="N86" t="s">
+        <v>33</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P86" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q86">
+        <v>37.99</v>
+      </c>
+      <c r="R86">
+        <v>6.33</v>
       </c>
       <c r="Y86" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="AA86" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="AB86" t="s">
         <v>39</v>
@@ -9014,13 +9059,13 @@
     </row>
     <row r="87" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>403</v>
+        <v>445</v>
       </c>
       <c r="C87" t="s">
-        <v>404</v>
+        <v>446</v>
       </c>
       <c r="D87" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="E87" t="s">
         <v>33</v>
@@ -9061,17 +9106,11 @@
       <c r="R87">
         <v>10</v>
       </c>
-      <c r="S87">
-        <v>5.99</v>
-      </c>
-      <c r="T87">
-        <v>1</v>
-      </c>
       <c r="Y87" t="s">
-        <v>405</v>
+        <v>448</v>
       </c>
       <c r="AA87" t="s">
-        <v>406</v>
+        <v>449</v>
       </c>
       <c r="AB87" t="s">
         <v>39</v>
@@ -9085,16 +9124,16 @@
     </row>
     <row r="88" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>407</v>
+        <v>450</v>
       </c>
       <c r="C88" t="s">
-        <v>408</v>
+        <v>451</v>
       </c>
       <c r="D88" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="E88" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F88" t="s">
         <v>34</v>
@@ -9109,34 +9148,22 @@
         <v>54</v>
       </c>
       <c r="K88" t="s">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="L88" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="M88" t="s">
-        <v>81</v>
-      </c>
-      <c r="N88" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O88">
-        <v>1</v>
-      </c>
-      <c r="P88" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q88">
-        <v>22.99</v>
-      </c>
-      <c r="R88">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="Y88" t="s">
-        <v>409</v>
+        <v>453</v>
       </c>
       <c r="AA88" t="s">
-        <v>410</v>
+        <v>454</v>
       </c>
       <c r="AB88" t="s">
         <v>39</v>
@@ -9150,13 +9177,13 @@
     </row>
     <row r="89" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C89" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="D89" t="s">
-        <v>411</v>
+        <v>455</v>
       </c>
       <c r="E89" t="s">
         <v>33</v>
@@ -9174,13 +9201,13 @@
         <v>54</v>
       </c>
       <c r="K89" t="s">
-        <v>340</v>
+        <v>40</v>
       </c>
       <c r="L89" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="M89" t="s">
-        <v>143</v>
+        <v>42</v>
       </c>
       <c r="N89" t="s">
         <v>33</v>
@@ -9192,16 +9219,22 @@
         <v>38</v>
       </c>
       <c r="Q89">
-        <v>44.99</v>
+        <v>59.99</v>
       </c>
       <c r="R89">
-        <v>7.5</v>
+        <v>10</v>
+      </c>
+      <c r="S89">
+        <v>5.99</v>
+      </c>
+      <c r="T89">
+        <v>1</v>
       </c>
       <c r="Y89" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="AA89" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="AB89" t="s">
         <v>39</v>
@@ -9215,13 +9248,13 @@
     </row>
     <row r="90" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="C90" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="D90" t="s">
-        <v>412</v>
+        <v>456</v>
       </c>
       <c r="E90" t="s">
         <v>33</v>
@@ -9239,13 +9272,13 @@
         <v>54</v>
       </c>
       <c r="K90" t="s">
-        <v>340</v>
+        <v>79</v>
       </c>
       <c r="L90" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="M90" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
       <c r="N90" t="s">
         <v>33</v>
@@ -9257,19 +9290,16 @@
         <v>38</v>
       </c>
       <c r="Q90">
-        <v>44.99</v>
+        <v>22.99</v>
       </c>
       <c r="R90">
-        <v>7.5</v>
+        <v>3.83</v>
       </c>
       <c r="Y90" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z90" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="AA90" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="AB90" t="s">
         <v>39</v>
@@ -9283,13 +9313,13 @@
     </row>
     <row r="91" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>338</v>
+        <v>399</v>
       </c>
       <c r="C91" t="s">
-        <v>339</v>
+        <v>400</v>
       </c>
       <c r="D91" t="s">
-        <v>662</v>
+        <v>411</v>
       </c>
       <c r="E91" t="s">
         <v>33</v>
@@ -9331,10 +9361,10 @@
         <v>7.5</v>
       </c>
       <c r="Y91" t="s">
-        <v>341</v>
+        <v>401</v>
       </c>
       <c r="AA91" t="s">
-        <v>342</v>
+        <v>402</v>
       </c>
       <c r="AB91" t="s">
         <v>39</v>
@@ -9348,13 +9378,13 @@
     </row>
     <row r="92" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>663</v>
+        <v>394</v>
       </c>
       <c r="C92" t="s">
-        <v>664</v>
+        <v>395</v>
       </c>
       <c r="D92" t="s">
-        <v>665</v>
+        <v>412</v>
       </c>
       <c r="E92" t="s">
         <v>33</v>
@@ -9372,13 +9402,13 @@
         <v>54</v>
       </c>
       <c r="K92" t="s">
-        <v>40</v>
+        <v>340</v>
       </c>
       <c r="L92" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="M92" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="N92" t="s">
         <v>33</v>
@@ -9390,25 +9420,25 @@
         <v>38</v>
       </c>
       <c r="Q92">
-        <v>59.99</v>
+        <v>44.99</v>
       </c>
       <c r="R92">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="Y92" t="s">
-        <v>62</v>
+        <v>396</v>
       </c>
       <c r="Z92" t="s">
-        <v>666</v>
+        <v>397</v>
       </c>
       <c r="AA92" t="s">
-        <v>667</v>
+        <v>398</v>
       </c>
       <c r="AB92" t="s">
         <v>39</v>
       </c>
       <c r="AD92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="b">
         <v>0</v>
@@ -9416,13 +9446,13 @@
     </row>
     <row r="93" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C93" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D93" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="E93" t="s">
         <v>33</v>
@@ -9440,13 +9470,13 @@
         <v>54</v>
       </c>
       <c r="K93" t="s">
-        <v>203</v>
+        <v>340</v>
       </c>
       <c r="L93" t="s">
-        <v>204</v>
+        <v>142</v>
       </c>
       <c r="M93" t="s">
-        <v>205</v>
+        <v>143</v>
       </c>
       <c r="N93" t="s">
         <v>33</v>
@@ -9458,16 +9488,16 @@
         <v>38</v>
       </c>
       <c r="Q93">
-        <v>69.989999999999995</v>
+        <v>44.99</v>
       </c>
       <c r="R93">
-        <v>11.67</v>
+        <v>7.5</v>
       </c>
       <c r="Y93" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="AA93" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="AB93" t="s">
         <v>39</v>
@@ -9481,13 +9511,13 @@
     </row>
     <row r="94" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>326</v>
+        <v>663</v>
       </c>
       <c r="C94" t="s">
-        <v>327</v>
+        <v>664</v>
       </c>
       <c r="D94" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="E94" t="s">
         <v>33</v>
@@ -9505,40 +9535,43 @@
         <v>54</v>
       </c>
       <c r="K94" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L94" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M94" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N94" t="s">
         <v>33</v>
       </c>
       <c r="O94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P94" t="s">
         <v>38</v>
       </c>
       <c r="Q94">
-        <v>75.98</v>
+        <v>59.99</v>
       </c>
       <c r="R94">
-        <v>12.66</v>
+        <v>10</v>
       </c>
       <c r="Y94" t="s">
-        <v>91</v>
+        <v>62</v>
+      </c>
+      <c r="Z94" t="s">
+        <v>666</v>
       </c>
       <c r="AA94" t="s">
-        <v>328</v>
+        <v>667</v>
       </c>
       <c r="AB94" t="s">
         <v>39</v>
       </c>
       <c r="AD94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG94" t="b">
         <v>0</v>
@@ -9546,13 +9579,13 @@
     </row>
     <row r="95" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="C95" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D95" t="s">
-        <v>345</v>
+        <v>668</v>
       </c>
       <c r="E95" t="s">
         <v>33</v>
@@ -9570,13 +9603,13 @@
         <v>54</v>
       </c>
       <c r="K95" t="s">
-        <v>40</v>
+        <v>203</v>
       </c>
       <c r="L95" t="s">
-        <v>41</v>
+        <v>204</v>
       </c>
       <c r="M95" t="s">
-        <v>42</v>
+        <v>205</v>
       </c>
       <c r="N95" t="s">
         <v>33</v>
@@ -9588,16 +9621,16 @@
         <v>38</v>
       </c>
       <c r="Q95">
-        <v>59.99</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="R95">
-        <v>10</v>
+        <v>11.67</v>
       </c>
       <c r="Y95" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="AA95" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="AB95" t="s">
         <v>39</v>
@@ -9611,13 +9644,13 @@
     </row>
     <row r="96" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="C96" t="s">
-        <v>289</v>
+        <v>327</v>
       </c>
       <c r="D96" t="s">
-        <v>348</v>
+        <v>669</v>
       </c>
       <c r="E96" t="s">
         <v>33</v>
@@ -9632,7 +9665,7 @@
         <v>36</v>
       </c>
       <c r="J96" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K96" t="s">
         <v>48</v>
@@ -9659,10 +9692,10 @@
         <v>12.66</v>
       </c>
       <c r="Y96" t="s">
-        <v>290</v>
+        <v>91</v>
       </c>
       <c r="AA96" t="s">
-        <v>291</v>
+        <v>328</v>
       </c>
       <c r="AB96" t="s">
         <v>39</v>
@@ -9676,13 +9709,13 @@
     </row>
     <row r="97" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="C97" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="D97" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="E97" t="s">
         <v>33</v>
@@ -9700,13 +9733,13 @@
         <v>54</v>
       </c>
       <c r="K97" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L97" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M97" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N97" t="s">
         <v>33</v>
@@ -9718,19 +9751,16 @@
         <v>38</v>
       </c>
       <c r="Q97">
-        <v>37.99</v>
+        <v>59.99</v>
       </c>
       <c r="R97">
-        <v>6.33</v>
+        <v>10</v>
       </c>
       <c r="Y97" t="s">
-        <v>352</v>
-      </c>
-      <c r="Z97" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="AA97" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="AB97" t="s">
         <v>39</v>
@@ -9744,13 +9774,13 @@
     </row>
     <row r="98" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>355</v>
+        <v>288</v>
       </c>
       <c r="C98" t="s">
-        <v>356</v>
+        <v>289</v>
       </c>
       <c r="D98" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="E98" t="s">
         <v>33</v>
@@ -9765,37 +9795,37 @@
         <v>36</v>
       </c>
       <c r="J98" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K98" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L98" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M98" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N98" t="s">
         <v>33</v>
       </c>
       <c r="O98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P98" t="s">
         <v>38</v>
       </c>
       <c r="Q98">
-        <v>11.99</v>
+        <v>75.98</v>
       </c>
       <c r="R98">
-        <v>2</v>
+        <v>12.66</v>
       </c>
       <c r="Y98" t="s">
-        <v>58</v>
+        <v>290</v>
       </c>
       <c r="AA98" t="s">
-        <v>358</v>
+        <v>291</v>
       </c>
       <c r="AB98" t="s">
         <v>39</v>
@@ -9809,13 +9839,13 @@
     </row>
     <row r="99" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="C99" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="E99" t="s">
         <v>33</v>
@@ -9845,25 +9875,25 @@
         <v>33</v>
       </c>
       <c r="O99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P99" t="s">
         <v>38</v>
       </c>
       <c r="Q99">
-        <v>75.98</v>
+        <v>37.99</v>
       </c>
       <c r="R99">
-        <v>12.66</v>
+        <v>6.33</v>
       </c>
       <c r="Y99" t="s">
-        <v>101</v>
+        <v>352</v>
       </c>
       <c r="Z99" t="s">
-        <v>59</v>
+        <v>353</v>
       </c>
       <c r="AA99" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="AB99" t="s">
         <v>39</v>
@@ -9877,13 +9907,13 @@
     </row>
     <row r="100" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="C100" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="D100" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="E100" t="s">
         <v>33</v>
@@ -9901,13 +9931,13 @@
         <v>54</v>
       </c>
       <c r="K100" t="s">
-        <v>260</v>
+        <v>72</v>
       </c>
       <c r="L100" t="s">
-        <v>261</v>
+        <v>73</v>
       </c>
       <c r="M100" t="s">
-        <v>262</v>
+        <v>74</v>
       </c>
       <c r="N100" t="s">
         <v>33</v>
@@ -9919,16 +9949,16 @@
         <v>38</v>
       </c>
       <c r="Q100">
-        <v>24.49</v>
+        <v>11.99</v>
       </c>
       <c r="R100">
-        <v>4.08</v>
+        <v>2</v>
       </c>
       <c r="Y100" t="s">
-        <v>366</v>
+        <v>58</v>
       </c>
       <c r="AA100" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="AB100" t="s">
         <v>39</v>
@@ -9942,13 +9972,13 @@
     </row>
     <row r="101" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>265</v>
+        <v>359</v>
       </c>
       <c r="C101" t="s">
-        <v>266</v>
+        <v>360</v>
       </c>
       <c r="D101" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="E101" t="s">
         <v>33</v>
@@ -9978,22 +10008,25 @@
         <v>33</v>
       </c>
       <c r="O101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P101" t="s">
         <v>38</v>
       </c>
       <c r="Q101">
-        <v>37.99</v>
+        <v>75.98</v>
       </c>
       <c r="R101">
-        <v>6.33</v>
+        <v>12.66</v>
       </c>
       <c r="Y101" t="s">
-        <v>267</v>
+        <v>101</v>
+      </c>
+      <c r="Z101" t="s">
+        <v>59</v>
       </c>
       <c r="AA101" t="s">
-        <v>268</v>
+        <v>362</v>
       </c>
       <c r="AB101" t="s">
         <v>39</v>
@@ -10007,13 +10040,13 @@
     </row>
     <row r="102" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="C102" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="D102" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="E102" t="s">
         <v>33</v>
@@ -10031,13 +10064,13 @@
         <v>54</v>
       </c>
       <c r="K102" t="s">
-        <v>72</v>
+        <v>260</v>
       </c>
       <c r="L102" t="s">
-        <v>73</v>
+        <v>261</v>
       </c>
       <c r="M102" t="s">
-        <v>74</v>
+        <v>262</v>
       </c>
       <c r="N102" t="s">
         <v>33</v>
@@ -10049,22 +10082,16 @@
         <v>38</v>
       </c>
       <c r="Q102">
-        <v>11.99</v>
+        <v>24.49</v>
       </c>
       <c r="R102">
-        <v>2</v>
-      </c>
-      <c r="S102">
-        <v>5.99</v>
-      </c>
-      <c r="T102">
-        <v>1</v>
+        <v>4.08</v>
       </c>
       <c r="Y102" t="s">
-        <v>84</v>
+        <v>366</v>
       </c>
       <c r="AA102" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="AB102" t="s">
         <v>39</v>
@@ -10078,13 +10105,13 @@
     </row>
     <row r="103" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>373</v>
+        <v>265</v>
       </c>
       <c r="C103" t="s">
-        <v>374</v>
+        <v>266</v>
       </c>
       <c r="D103" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="E103" t="s">
         <v>33</v>
@@ -10102,13 +10129,13 @@
         <v>54</v>
       </c>
       <c r="K103" t="s">
-        <v>260</v>
+        <v>48</v>
       </c>
       <c r="L103" t="s">
-        <v>261</v>
+        <v>49</v>
       </c>
       <c r="M103" t="s">
-        <v>262</v>
+        <v>50</v>
       </c>
       <c r="N103" t="s">
         <v>33</v>
@@ -10120,16 +10147,16 @@
         <v>38</v>
       </c>
       <c r="Q103">
-        <v>24.49</v>
+        <v>37.99</v>
       </c>
       <c r="R103">
-        <v>4.08</v>
+        <v>6.33</v>
       </c>
       <c r="Y103" t="s">
-        <v>376</v>
+        <v>267</v>
       </c>
       <c r="AA103" t="s">
-        <v>377</v>
+        <v>268</v>
       </c>
       <c r="AB103" t="s">
         <v>39</v>
@@ -10143,13 +10170,13 @@
     </row>
     <row r="104" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="C104" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="D104" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="E104" t="s">
         <v>33</v>
@@ -10167,13 +10194,13 @@
         <v>54</v>
       </c>
       <c r="K104" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L104" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M104" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N104" t="s">
         <v>33</v>
@@ -10185,16 +10212,22 @@
         <v>38</v>
       </c>
       <c r="Q104">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R104">
-        <v>10</v>
+        <v>2</v>
+      </c>
+      <c r="S104">
+        <v>5.99</v>
+      </c>
+      <c r="T104">
+        <v>1</v>
       </c>
       <c r="Y104" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="AA104" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="AB104" t="s">
         <v>39</v>
@@ -10208,13 +10241,13 @@
     </row>
     <row r="105" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="C105" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="D105" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="E105" t="s">
         <v>33</v>
@@ -10232,13 +10265,13 @@
         <v>54</v>
       </c>
       <c r="K105" t="s">
-        <v>72</v>
+        <v>260</v>
       </c>
       <c r="L105" t="s">
-        <v>73</v>
+        <v>261</v>
       </c>
       <c r="M105" t="s">
-        <v>74</v>
+        <v>262</v>
       </c>
       <c r="N105" t="s">
         <v>33</v>
@@ -10250,16 +10283,16 @@
         <v>38</v>
       </c>
       <c r="Q105">
-        <v>11.99</v>
+        <v>24.49</v>
       </c>
       <c r="R105">
-        <v>2</v>
+        <v>4.08</v>
       </c>
       <c r="Y105" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="AA105" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="AB105" t="s">
         <v>39</v>
@@ -10273,16 +10306,16 @@
     </row>
     <row r="106" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="C106" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="D106" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="E106" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F106" t="s">
         <v>34</v>
@@ -10297,25 +10330,34 @@
         <v>54</v>
       </c>
       <c r="K106" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L106" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M106" t="s">
-        <v>45</v>
+        <v>42</v>
+      </c>
+      <c r="N106" t="s">
+        <v>33</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P106" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q106">
+        <v>59.99</v>
+      </c>
+      <c r="R106">
+        <v>10</v>
       </c>
       <c r="Y106" t="s">
-        <v>390</v>
-      </c>
-      <c r="Z106" t="s">
-        <v>391</v>
+        <v>57</v>
       </c>
       <c r="AA106" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="AB106" t="s">
         <v>39</v>
@@ -10329,13 +10371,13 @@
     </row>
     <row r="107" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>323</v>
+        <v>382</v>
       </c>
       <c r="C107" t="s">
-        <v>324</v>
+        <v>383</v>
       </c>
       <c r="D107" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="E107" t="s">
         <v>33</v>
@@ -10353,13 +10395,13 @@
         <v>54</v>
       </c>
       <c r="K107" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="L107" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="M107" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="N107" t="s">
         <v>33</v>
@@ -10371,16 +10413,16 @@
         <v>38</v>
       </c>
       <c r="Q107">
-        <v>14.99</v>
+        <v>11.99</v>
       </c>
       <c r="R107">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Y107" t="s">
-        <v>58</v>
+        <v>385</v>
       </c>
       <c r="AA107" t="s">
-        <v>325</v>
+        <v>386</v>
       </c>
       <c r="AB107" t="s">
         <v>39</v>
@@ -10394,16 +10436,16 @@
     </row>
     <row r="108" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>318</v>
+        <v>387</v>
       </c>
       <c r="C108" t="s">
-        <v>319</v>
+        <v>388</v>
       </c>
       <c r="D108" t="s">
-        <v>320</v>
+        <v>389</v>
       </c>
       <c r="E108" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F108" t="s">
         <v>34</v>
@@ -10418,37 +10460,25 @@
         <v>54</v>
       </c>
       <c r="K108" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="L108" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="M108" t="s">
-        <v>74</v>
-      </c>
-      <c r="N108" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O108">
-        <v>1</v>
-      </c>
-      <c r="P108" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q108">
-        <v>11.99</v>
-      </c>
-      <c r="R108">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y108" t="s">
-        <v>321</v>
+        <v>390</v>
       </c>
       <c r="Z108" t="s">
-        <v>65</v>
+        <v>391</v>
       </c>
       <c r="AA108" t="s">
-        <v>322</v>
+        <v>392</v>
       </c>
       <c r="AB108" t="s">
         <v>39</v>
@@ -10462,13 +10492,13 @@
     </row>
     <row r="109" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C109" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="D109" t="s">
-        <v>331</v>
+        <v>393</v>
       </c>
       <c r="E109" t="s">
         <v>33</v>
@@ -10486,13 +10516,13 @@
         <v>54</v>
       </c>
       <c r="K109" t="s">
-        <v>260</v>
+        <v>95</v>
       </c>
       <c r="L109" t="s">
-        <v>261</v>
+        <v>85</v>
       </c>
       <c r="M109" t="s">
-        <v>262</v>
+        <v>86</v>
       </c>
       <c r="N109" t="s">
         <v>33</v>
@@ -10504,16 +10534,16 @@
         <v>38</v>
       </c>
       <c r="Q109">
-        <v>24.49</v>
+        <v>14.99</v>
       </c>
       <c r="R109">
-        <v>4.08</v>
+        <v>2.5</v>
       </c>
       <c r="Y109" t="s">
-        <v>332</v>
+        <v>58</v>
       </c>
       <c r="AA109" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="AB109" t="s">
         <v>39</v>
@@ -10527,13 +10557,13 @@
     </row>
     <row r="110" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>670</v>
+        <v>318</v>
       </c>
       <c r="C110" t="s">
-        <v>671</v>
+        <v>319</v>
       </c>
       <c r="D110" t="s">
-        <v>672</v>
+        <v>320</v>
       </c>
       <c r="E110" t="s">
         <v>33</v>
@@ -10551,13 +10581,13 @@
         <v>54</v>
       </c>
       <c r="K110" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L110" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M110" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N110" t="s">
         <v>33</v>
@@ -10569,16 +10599,19 @@
         <v>38</v>
       </c>
       <c r="Q110">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R110">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y110" t="s">
-        <v>673</v>
+        <v>321</v>
+      </c>
+      <c r="Z110" t="s">
+        <v>65</v>
       </c>
       <c r="AA110" t="s">
-        <v>674</v>
+        <v>322</v>
       </c>
       <c r="AB110" t="s">
         <v>39</v>
@@ -10592,13 +10625,13 @@
     </row>
     <row r="111" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>675</v>
+        <v>329</v>
       </c>
       <c r="C111" t="s">
-        <v>676</v>
+        <v>330</v>
       </c>
       <c r="D111" t="s">
-        <v>677</v>
+        <v>331</v>
       </c>
       <c r="E111" t="s">
         <v>33</v>
@@ -10616,13 +10649,13 @@
         <v>54</v>
       </c>
       <c r="K111" t="s">
-        <v>48</v>
+        <v>260</v>
       </c>
       <c r="L111" t="s">
-        <v>49</v>
+        <v>261</v>
       </c>
       <c r="M111" t="s">
-        <v>50</v>
+        <v>262</v>
       </c>
       <c r="N111" t="s">
         <v>33</v>
@@ -10634,16 +10667,16 @@
         <v>38</v>
       </c>
       <c r="Q111">
-        <v>37.99</v>
+        <v>24.49</v>
       </c>
       <c r="R111">
-        <v>6.33</v>
+        <v>4.08</v>
       </c>
       <c r="Y111" t="s">
-        <v>678</v>
+        <v>332</v>
       </c>
       <c r="AA111" t="s">
-        <v>679</v>
+        <v>333</v>
       </c>
       <c r="AB111" t="s">
         <v>39</v>
@@ -10657,13 +10690,13 @@
     </row>
     <row r="112" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="C112" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="D112" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="E112" t="s">
         <v>33</v>
@@ -10705,13 +10738,10 @@
         <v>10</v>
       </c>
       <c r="Y112" t="s">
-        <v>683</v>
-      </c>
-      <c r="Z112" t="s">
-        <v>76</v>
+        <v>673</v>
       </c>
       <c r="AA112" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="AB112" t="s">
         <v>39</v>
@@ -10725,13 +10755,13 @@
     </row>
     <row r="113" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="C113" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D113" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
       <c r="E113" t="s">
         <v>33</v>
@@ -10773,10 +10803,10 @@
         <v>6.33</v>
       </c>
       <c r="Y113" t="s">
-        <v>52</v>
+        <v>678</v>
       </c>
       <c r="AA113" t="s">
-        <v>688</v>
+        <v>679</v>
       </c>
       <c r="AB113" t="s">
         <v>39</v>
@@ -10790,16 +10820,16 @@
     </row>
     <row r="114" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
       <c r="C114" t="s">
-        <v>690</v>
+        <v>681</v>
       </c>
       <c r="D114" t="s">
-        <v>691</v>
+        <v>682</v>
       </c>
       <c r="E114" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F114" t="s">
         <v>34</v>
@@ -10811,28 +10841,40 @@
         <v>36</v>
       </c>
       <c r="J114" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K114" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L114" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M114" t="s">
-        <v>50</v>
+        <v>42</v>
+      </c>
+      <c r="N114" t="s">
+        <v>33</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P114" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q114">
+        <v>59.99</v>
+      </c>
+      <c r="R114">
+        <v>10</v>
       </c>
       <c r="Y114" t="s">
-        <v>692</v>
+        <v>683</v>
       </c>
       <c r="Z114" t="s">
-        <v>693</v>
+        <v>76</v>
       </c>
       <c r="AA114" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="AB114" t="s">
         <v>39</v>
@@ -10846,16 +10888,16 @@
     </row>
     <row r="115" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="C115" t="s">
-        <v>696</v>
+        <v>686</v>
       </c>
       <c r="D115" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="E115" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F115" t="s">
         <v>34</v>
@@ -10867,7 +10909,7 @@
         <v>36</v>
       </c>
       <c r="J115" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K115" t="s">
         <v>48</v>
@@ -10878,17 +10920,26 @@
       <c r="M115" t="s">
         <v>50</v>
       </c>
+      <c r="N115" t="s">
+        <v>33</v>
+      </c>
       <c r="O115">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P115" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q115">
+        <v>37.99</v>
+      </c>
+      <c r="R115">
+        <v>6.33</v>
       </c>
       <c r="Y115" t="s">
-        <v>692</v>
-      </c>
-      <c r="Z115" t="s">
-        <v>693</v>
+        <v>52</v>
       </c>
       <c r="AA115" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="AB115" t="s">
         <v>39</v>
@@ -10902,16 +10953,16 @@
     </row>
     <row r="116" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>300</v>
+        <v>689</v>
       </c>
       <c r="C116" t="s">
-        <v>301</v>
+        <v>690</v>
       </c>
       <c r="D116" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="E116" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F116" t="s">
         <v>34</v>
@@ -10923,37 +10974,28 @@
         <v>36</v>
       </c>
       <c r="J116" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K116" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="L116" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="M116" t="s">
-        <v>86</v>
-      </c>
-      <c r="N116" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="O116">
-        <v>1</v>
-      </c>
-      <c r="P116" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q116">
-        <v>14.99</v>
-      </c>
-      <c r="R116">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y116" t="s">
-        <v>58</v>
+        <v>692</v>
+      </c>
+      <c r="Z116" t="s">
+        <v>693</v>
       </c>
       <c r="AA116" t="s">
-        <v>302</v>
+        <v>694</v>
       </c>
       <c r="AB116" t="s">
         <v>39</v>
@@ -10967,13 +11009,13 @@
     </row>
     <row r="117" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="C117" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="D117" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="E117" t="s">
         <v>53</v>
@@ -10988,7 +11030,7 @@
         <v>36</v>
       </c>
       <c r="J117" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K117" t="s">
         <v>48</v>
@@ -11023,13 +11065,13 @@
     </row>
     <row r="118" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C118" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D118" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="E118" t="s">
         <v>33</v>
@@ -11047,13 +11089,13 @@
         <v>54</v>
       </c>
       <c r="K118" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="L118" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="M118" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="N118" t="s">
         <v>33</v>
@@ -11065,16 +11107,16 @@
         <v>38</v>
       </c>
       <c r="Q118">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="R118">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="Y118" t="s">
-        <v>305</v>
+        <v>58</v>
       </c>
       <c r="AA118" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="AB118" t="s">
         <v>39</v>
@@ -11088,16 +11130,16 @@
     </row>
     <row r="119" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>292</v>
+        <v>699</v>
       </c>
       <c r="C119" t="s">
-        <v>293</v>
+        <v>700</v>
       </c>
       <c r="D119" t="s">
-        <v>294</v>
+        <v>701</v>
       </c>
       <c r="E119" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F119" t="s">
         <v>34</v>
@@ -11109,40 +11151,28 @@
         <v>36</v>
       </c>
       <c r="J119" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K119" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L119" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M119" t="s">
-        <v>42</v>
-      </c>
-      <c r="N119" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="O119">
-        <v>1</v>
-      </c>
-      <c r="P119" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q119">
-        <v>59.99</v>
-      </c>
-      <c r="R119">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y119" t="s">
-        <v>77</v>
+        <v>692</v>
       </c>
       <c r="Z119" t="s">
-        <v>92</v>
+        <v>693</v>
       </c>
       <c r="AA119" t="s">
-        <v>295</v>
+        <v>694</v>
       </c>
       <c r="AB119" t="s">
         <v>39</v>
@@ -11156,13 +11186,13 @@
     </row>
     <row r="120" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C120" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="D120" t="s">
-        <v>298</v>
+        <v>702</v>
       </c>
       <c r="E120" t="s">
         <v>33</v>
@@ -11177,7 +11207,7 @@
         <v>36</v>
       </c>
       <c r="J120" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K120" t="s">
         <v>40</v>
@@ -11204,13 +11234,10 @@
         <v>10</v>
       </c>
       <c r="Y120" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z120" t="s">
-        <v>51</v>
+        <v>305</v>
       </c>
       <c r="AA120" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="AB120" t="s">
         <v>39</v>
@@ -11224,13 +11251,13 @@
     </row>
     <row r="121" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="C121" t="s">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="D121" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="E121" t="s">
         <v>33</v>
@@ -11248,13 +11275,13 @@
         <v>37</v>
       </c>
       <c r="K121" t="s">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="L121" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="M121" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="N121" t="s">
         <v>33</v>
@@ -11266,16 +11293,19 @@
         <v>38</v>
       </c>
       <c r="Q121">
-        <v>20.49</v>
+        <v>59.99</v>
       </c>
       <c r="R121">
-        <v>3.42</v>
+        <v>10</v>
       </c>
       <c r="Y121" t="s">
-        <v>310</v>
+        <v>77</v>
+      </c>
+      <c r="Z121" t="s">
+        <v>92</v>
       </c>
       <c r="AA121" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="AB121" t="s">
         <v>39</v>
@@ -11289,13 +11319,13 @@
     </row>
     <row r="122" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>312</v>
+        <v>296</v>
       </c>
       <c r="C122" t="s">
-        <v>313</v>
+        <v>297</v>
       </c>
       <c r="D122" t="s">
-        <v>314</v>
+        <v>298</v>
       </c>
       <c r="E122" t="s">
         <v>33</v>
@@ -11337,13 +11367,13 @@
         <v>10</v>
       </c>
       <c r="Y122" t="s">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="Z122" t="s">
-        <v>315</v>
+        <v>51</v>
       </c>
       <c r="AA122" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
       <c r="AB122" t="s">
         <v>39</v>
@@ -11357,13 +11387,13 @@
     </row>
     <row r="123" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>253</v>
+        <v>307</v>
       </c>
       <c r="C123" t="s">
-        <v>254</v>
+        <v>308</v>
       </c>
       <c r="D123" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="E123" t="s">
         <v>33</v>
@@ -11378,16 +11408,16 @@
         <v>36</v>
       </c>
       <c r="J123" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K123" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="L123" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="M123" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="N123" t="s">
         <v>33</v>
@@ -11399,19 +11429,16 @@
         <v>38</v>
       </c>
       <c r="Q123">
-        <v>59.99</v>
+        <v>20.49</v>
       </c>
       <c r="R123">
-        <v>10</v>
+        <v>3.42</v>
       </c>
       <c r="Y123" t="s">
-        <v>255</v>
-      </c>
-      <c r="Z123" t="s">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="AA123" t="s">
-        <v>256</v>
+        <v>311</v>
       </c>
       <c r="AB123" t="s">
         <v>39</v>
@@ -11425,13 +11452,13 @@
     </row>
     <row r="124" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>257</v>
+        <v>312</v>
       </c>
       <c r="C124" t="s">
-        <v>258</v>
+        <v>313</v>
       </c>
       <c r="D124" t="s">
-        <v>259</v>
+        <v>314</v>
       </c>
       <c r="E124" t="s">
         <v>33</v>
@@ -11446,16 +11473,16 @@
         <v>36</v>
       </c>
       <c r="J124" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K124" t="s">
-        <v>260</v>
+        <v>40</v>
       </c>
       <c r="L124" t="s">
-        <v>261</v>
+        <v>41</v>
       </c>
       <c r="M124" t="s">
-        <v>262</v>
+        <v>42</v>
       </c>
       <c r="N124" t="s">
         <v>33</v>
@@ -11467,19 +11494,19 @@
         <v>38</v>
       </c>
       <c r="Q124">
-        <v>24.49</v>
+        <v>59.99</v>
       </c>
       <c r="R124">
-        <v>4.08</v>
+        <v>10</v>
       </c>
       <c r="Y124" t="s">
-        <v>263</v>
+        <v>100</v>
       </c>
       <c r="Z124" t="s">
-        <v>64</v>
+        <v>315</v>
       </c>
       <c r="AA124" t="s">
-        <v>264</v>
+        <v>316</v>
       </c>
       <c r="AB124" t="s">
         <v>39</v>
@@ -11493,13 +11520,13 @@
     </row>
     <row r="125" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>269</v>
+        <v>253</v>
       </c>
       <c r="C125" t="s">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="D125" t="s">
-        <v>271</v>
+        <v>317</v>
       </c>
       <c r="E125" t="s">
         <v>33</v>
@@ -11541,10 +11568,13 @@
         <v>10</v>
       </c>
       <c r="Y125" t="s">
-        <v>272</v>
+        <v>255</v>
+      </c>
+      <c r="Z125" t="s">
+        <v>102</v>
       </c>
       <c r="AA125" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="AB125" t="s">
         <v>39</v>
@@ -11558,13 +11588,13 @@
     </row>
     <row r="126" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>149</v>
+        <v>257</v>
       </c>
       <c r="C126" t="s">
-        <v>150</v>
+        <v>258</v>
       </c>
       <c r="D126" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="E126" t="s">
         <v>33</v>
@@ -11582,13 +11612,13 @@
         <v>54</v>
       </c>
       <c r="K126" t="s">
-        <v>40</v>
+        <v>260</v>
       </c>
       <c r="L126" t="s">
-        <v>41</v>
+        <v>261</v>
       </c>
       <c r="M126" t="s">
-        <v>42</v>
+        <v>262</v>
       </c>
       <c r="N126" t="s">
         <v>33</v>
@@ -11600,16 +11630,19 @@
         <v>38</v>
       </c>
       <c r="Q126">
-        <v>59.99</v>
+        <v>24.49</v>
       </c>
       <c r="R126">
-        <v>10</v>
+        <v>4.08</v>
       </c>
       <c r="Y126" t="s">
-        <v>63</v>
+        <v>263</v>
+      </c>
+      <c r="Z126" t="s">
+        <v>64</v>
       </c>
       <c r="AA126" t="s">
-        <v>151</v>
+        <v>264</v>
       </c>
       <c r="AB126" t="s">
         <v>39</v>
@@ -11623,13 +11656,13 @@
     </row>
     <row r="127" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="C127" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="D127" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="E127" t="s">
         <v>33</v>
@@ -11659,25 +11692,22 @@
         <v>33</v>
       </c>
       <c r="O127">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P127" t="s">
         <v>38</v>
       </c>
       <c r="Q127">
-        <v>119.98</v>
+        <v>59.99</v>
       </c>
       <c r="R127">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Y127" t="s">
-        <v>278</v>
-      </c>
-      <c r="Z127" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="AA127" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="AB127" t="s">
         <v>39</v>
@@ -11691,13 +11721,13 @@
     </row>
     <row r="128" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>281</v>
+        <v>149</v>
       </c>
       <c r="C128" t="s">
-        <v>282</v>
+        <v>150</v>
       </c>
       <c r="D128" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="E128" t="s">
         <v>33</v>
@@ -11712,16 +11742,16 @@
         <v>36</v>
       </c>
       <c r="J128" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K128" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L128" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M128" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N128" t="s">
         <v>33</v>
@@ -11733,16 +11763,16 @@
         <v>38</v>
       </c>
       <c r="Q128">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R128">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y128" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="AA128" t="s">
-        <v>284</v>
+        <v>151</v>
       </c>
       <c r="AB128" t="s">
         <v>39</v>
@@ -11756,16 +11786,16 @@
     </row>
     <row r="129" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>238</v>
+        <v>275</v>
       </c>
       <c r="C129" t="s">
-        <v>239</v>
+        <v>276</v>
       </c>
       <c r="D129" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="E129" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F129" t="s">
         <v>34</v>
@@ -11788,14 +11818,29 @@
       <c r="M129" t="s">
         <v>42</v>
       </c>
+      <c r="N129" t="s">
+        <v>33</v>
+      </c>
       <c r="O129">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="P129" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q129">
+        <v>119.98</v>
+      </c>
+      <c r="R129">
+        <v>20</v>
       </c>
       <c r="Y129" t="s">
-        <v>240</v>
+        <v>278</v>
+      </c>
+      <c r="Z129" t="s">
+        <v>279</v>
       </c>
       <c r="AA129" t="s">
-        <v>241</v>
+        <v>280</v>
       </c>
       <c r="AB129" t="s">
         <v>39</v>
@@ -11809,13 +11854,13 @@
     </row>
     <row r="130" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>224</v>
+        <v>281</v>
       </c>
       <c r="C130" t="s">
-        <v>225</v>
+        <v>282</v>
       </c>
       <c r="D130" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="E130" t="s">
         <v>33</v>
@@ -11830,16 +11875,16 @@
         <v>36</v>
       </c>
       <c r="J130" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K130" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L130" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M130" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N130" t="s">
         <v>33</v>
@@ -11851,16 +11896,16 @@
         <v>38</v>
       </c>
       <c r="Q130">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R130">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y130" t="s">
-        <v>226</v>
+        <v>75</v>
       </c>
       <c r="AA130" t="s">
-        <v>227</v>
+        <v>284</v>
       </c>
       <c r="AB130" t="s">
         <v>39</v>
@@ -11874,16 +11919,16 @@
     </row>
     <row r="131" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>213</v>
+        <v>238</v>
       </c>
       <c r="C131" t="s">
-        <v>214</v>
+        <v>239</v>
       </c>
       <c r="D131" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E131" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F131" t="s">
         <v>34</v>
@@ -11906,29 +11951,14 @@
       <c r="M131" t="s">
         <v>42</v>
       </c>
-      <c r="N131" t="s">
-        <v>33</v>
-      </c>
       <c r="O131">
-        <v>1</v>
-      </c>
-      <c r="P131" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q131">
-        <v>59.99</v>
-      </c>
-      <c r="R131">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y131" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z131" t="s">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="AA131" t="s">
-        <v>217</v>
+        <v>241</v>
       </c>
       <c r="AB131" t="s">
         <v>39</v>
@@ -11942,13 +11972,13 @@
     </row>
     <row r="132" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C132" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="D132" t="s">
-        <v>220</v>
+        <v>286</v>
       </c>
       <c r="E132" t="s">
         <v>33</v>
@@ -11966,13 +11996,13 @@
         <v>54</v>
       </c>
       <c r="K132" t="s">
-        <v>203</v>
+        <v>40</v>
       </c>
       <c r="L132" t="s">
-        <v>204</v>
+        <v>41</v>
       </c>
       <c r="M132" t="s">
-        <v>205</v>
+        <v>42</v>
       </c>
       <c r="N132" t="s">
         <v>33</v>
@@ -11984,19 +12014,16 @@
         <v>38</v>
       </c>
       <c r="Q132">
-        <v>69.989999999999995</v>
+        <v>59.99</v>
       </c>
       <c r="R132">
-        <v>11.67</v>
+        <v>10</v>
       </c>
       <c r="Y132" t="s">
-        <v>221</v>
-      </c>
-      <c r="Z132" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AA132" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="AB132" t="s">
         <v>39</v>
@@ -12010,13 +12037,13 @@
     </row>
     <row r="133" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="C133" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="D133" t="s">
-        <v>230</v>
+        <v>287</v>
       </c>
       <c r="E133" t="s">
         <v>33</v>
@@ -12058,10 +12085,13 @@
         <v>10</v>
       </c>
       <c r="Y133" t="s">
-        <v>231</v>
+        <v>215</v>
+      </c>
+      <c r="Z133" t="s">
+        <v>216</v>
       </c>
       <c r="AA133" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="AB133" t="s">
         <v>39</v>
@@ -12075,13 +12105,13 @@
     </row>
     <row r="134" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="C134" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="D134" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="E134" t="s">
         <v>33</v>
@@ -12099,13 +12129,13 @@
         <v>54</v>
       </c>
       <c r="K134" t="s">
-        <v>95</v>
+        <v>203</v>
       </c>
       <c r="L134" t="s">
-        <v>85</v>
+        <v>204</v>
       </c>
       <c r="M134" t="s">
-        <v>86</v>
+        <v>205</v>
       </c>
       <c r="N134" t="s">
         <v>33</v>
@@ -12117,16 +12147,19 @@
         <v>38</v>
       </c>
       <c r="Q134">
-        <v>14.99</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="R134">
-        <v>2.5</v>
+        <v>11.67</v>
       </c>
       <c r="Y134" t="s">
-        <v>236</v>
+        <v>221</v>
+      </c>
+      <c r="Z134" t="s">
+        <v>222</v>
       </c>
       <c r="AA134" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="AB134" t="s">
         <v>39</v>
@@ -12140,16 +12173,16 @@
     </row>
     <row r="135" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="C135" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="D135" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="E135" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F135" t="s">
         <v>34</v>
@@ -12172,14 +12205,26 @@
       <c r="M135" t="s">
         <v>42</v>
       </c>
+      <c r="N135" t="s">
+        <v>33</v>
+      </c>
       <c r="O135">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P135" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q135">
+        <v>59.99</v>
+      </c>
+      <c r="R135">
+        <v>10</v>
       </c>
       <c r="Y135" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="AA135" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="AB135" t="s">
         <v>39</v>
@@ -12193,13 +12238,13 @@
     </row>
     <row r="136" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="C136" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D136" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="E136" t="s">
         <v>33</v>
@@ -12214,16 +12259,16 @@
         <v>36</v>
       </c>
       <c r="J136" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K136" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="L136" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="M136" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="N136" t="s">
         <v>33</v>
@@ -12235,16 +12280,16 @@
         <v>38</v>
       </c>
       <c r="Q136">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="R136">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="Y136" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="AA136" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="AB136" t="s">
         <v>39</v>
@@ -12258,16 +12303,16 @@
     </row>
     <row r="137" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>188</v>
+        <v>242</v>
       </c>
       <c r="C137" t="s">
-        <v>189</v>
+        <v>243</v>
       </c>
       <c r="D137" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="E137" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F137" t="s">
         <v>34</v>
@@ -12279,37 +12324,25 @@
         <v>36</v>
       </c>
       <c r="J137" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K137" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L137" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M137" t="s">
-        <v>50</v>
-      </c>
-      <c r="N137" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O137">
-        <v>1</v>
-      </c>
-      <c r="P137" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q137">
-        <v>37.99</v>
-      </c>
-      <c r="R137">
-        <v>6.33</v>
+        <v>0</v>
       </c>
       <c r="Y137" t="s">
-        <v>52</v>
+        <v>240</v>
       </c>
       <c r="AA137" t="s">
-        <v>190</v>
+        <v>241</v>
       </c>
       <c r="AB137" t="s">
         <v>39</v>
@@ -12323,13 +12356,13 @@
     </row>
     <row r="138" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>191</v>
+        <v>245</v>
       </c>
       <c r="C138" t="s">
-        <v>192</v>
+        <v>246</v>
       </c>
       <c r="D138" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="E138" t="s">
         <v>33</v>
@@ -12344,7 +12377,7 @@
         <v>36</v>
       </c>
       <c r="J138" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K138" t="s">
         <v>40</v>
@@ -12371,10 +12404,10 @@
         <v>10</v>
       </c>
       <c r="Y138" t="s">
-        <v>193</v>
+        <v>248</v>
       </c>
       <c r="AA138" t="s">
-        <v>194</v>
+        <v>249</v>
       </c>
       <c r="AB138" t="s">
         <v>39</v>
@@ -12388,13 +12421,13 @@
     </row>
     <row r="139" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="C139" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="D139" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E139" t="s">
         <v>33</v>
@@ -12409,16 +12442,16 @@
         <v>36</v>
       </c>
       <c r="J139" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K139" t="s">
-        <v>203</v>
+        <v>48</v>
       </c>
       <c r="L139" t="s">
-        <v>204</v>
+        <v>49</v>
       </c>
       <c r="M139" t="s">
-        <v>205</v>
+        <v>50</v>
       </c>
       <c r="N139" t="s">
         <v>33</v>
@@ -12430,19 +12463,16 @@
         <v>38</v>
       </c>
       <c r="Q139">
-        <v>69.989999999999995</v>
+        <v>37.99</v>
       </c>
       <c r="R139">
-        <v>11.67</v>
+        <v>6.33</v>
       </c>
       <c r="Y139" t="s">
-        <v>206</v>
-      </c>
-      <c r="Z139" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="AA139" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="AB139" t="s">
         <v>39</v>
@@ -12456,13 +12486,13 @@
     </row>
     <row r="140" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C140" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D140" t="s">
-        <v>197</v>
+        <v>251</v>
       </c>
       <c r="E140" t="s">
         <v>33</v>
@@ -12477,7 +12507,7 @@
         <v>36</v>
       </c>
       <c r="J140" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K140" t="s">
         <v>40</v>
@@ -12504,13 +12534,10 @@
         <v>10</v>
       </c>
       <c r="Y140" t="s">
-        <v>198</v>
-      </c>
-      <c r="Z140" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="AA140" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="AB140" t="s">
         <v>39</v>
@@ -12524,13 +12551,13 @@
     </row>
     <row r="141" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="C141" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="D141" t="s">
-        <v>210</v>
+        <v>252</v>
       </c>
       <c r="E141" t="s">
         <v>33</v>
@@ -12545,16 +12572,16 @@
         <v>36</v>
       </c>
       <c r="J141" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K141" t="s">
-        <v>40</v>
+        <v>203</v>
       </c>
       <c r="L141" t="s">
-        <v>41</v>
+        <v>204</v>
       </c>
       <c r="M141" t="s">
-        <v>42</v>
+        <v>205</v>
       </c>
       <c r="N141" t="s">
         <v>33</v>
@@ -12566,16 +12593,19 @@
         <v>38</v>
       </c>
       <c r="Q141">
-        <v>59.99</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="R141">
-        <v>10</v>
+        <v>11.67</v>
       </c>
       <c r="Y141" t="s">
-        <v>211</v>
+        <v>206</v>
+      </c>
+      <c r="Z141" t="s">
+        <v>60</v>
       </c>
       <c r="AA141" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="AB141" t="s">
         <v>39</v>
@@ -12589,13 +12619,13 @@
     </row>
     <row r="142" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>152</v>
+        <v>195</v>
       </c>
       <c r="C142" t="s">
-        <v>153</v>
+        <v>196</v>
       </c>
       <c r="D142" t="s">
-        <v>154</v>
+        <v>197</v>
       </c>
       <c r="E142" t="s">
         <v>33</v>
@@ -12610,16 +12640,16 @@
         <v>36</v>
       </c>
       <c r="J142" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K142" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="L142" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="M142" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="N142" t="s">
         <v>33</v>
@@ -12631,16 +12661,19 @@
         <v>38</v>
       </c>
       <c r="Q142">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R142">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y142" t="s">
-        <v>155</v>
+        <v>198</v>
+      </c>
+      <c r="Z142" t="s">
+        <v>199</v>
       </c>
       <c r="AA142" t="s">
-        <v>156</v>
+        <v>200</v>
       </c>
       <c r="AB142" t="s">
         <v>39</v>
@@ -12654,13 +12687,13 @@
     </row>
     <row r="143" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>157</v>
+        <v>208</v>
       </c>
       <c r="C143" t="s">
-        <v>158</v>
+        <v>209</v>
       </c>
       <c r="D143" t="s">
-        <v>159</v>
+        <v>210</v>
       </c>
       <c r="E143" t="s">
         <v>33</v>
@@ -12675,16 +12708,16 @@
         <v>36</v>
       </c>
       <c r="J143" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K143" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L143" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M143" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N143" t="s">
         <v>33</v>
@@ -12696,16 +12729,16 @@
         <v>38</v>
       </c>
       <c r="Q143">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R143">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y143" t="s">
-        <v>68</v>
+        <v>211</v>
       </c>
       <c r="AA143" t="s">
-        <v>160</v>
+        <v>212</v>
       </c>
       <c r="AB143" t="s">
         <v>39</v>
@@ -12719,16 +12752,16 @@
     </row>
     <row r="144" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="C144" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D144" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="E144" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F144" t="s">
         <v>34</v>
@@ -12743,22 +12776,34 @@
         <v>54</v>
       </c>
       <c r="K144" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="L144" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="M144" t="s">
-        <v>42</v>
+        <v>86</v>
+      </c>
+      <c r="N144" t="s">
+        <v>33</v>
       </c>
       <c r="O144">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P144" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q144">
+        <v>14.99</v>
+      </c>
+      <c r="R144">
+        <v>2.5</v>
       </c>
       <c r="Y144" t="s">
-        <v>63</v>
+        <v>155</v>
       </c>
       <c r="AA144" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="AB144" t="s">
         <v>39</v>
@@ -12772,13 +12817,13 @@
     </row>
     <row r="145" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C145" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D145" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E145" t="s">
         <v>33</v>
@@ -12796,13 +12841,13 @@
         <v>54</v>
       </c>
       <c r="K145" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L145" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M145" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="N145" t="s">
         <v>33</v>
@@ -12814,16 +12859,16 @@
         <v>38</v>
       </c>
       <c r="Q145">
-        <v>37.99</v>
+        <v>11.99</v>
       </c>
       <c r="R145">
-        <v>6.33</v>
+        <v>2</v>
       </c>
       <c r="Y145" t="s">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="AA145" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="AB145" t="s">
         <v>39</v>
@@ -12837,16 +12882,16 @@
     </row>
     <row r="146" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C146" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="D146" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="E146" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F146" t="s">
         <v>34</v>
@@ -12861,34 +12906,22 @@
         <v>54</v>
       </c>
       <c r="K146" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L146" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M146" t="s">
-        <v>74</v>
-      </c>
-      <c r="N146" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O146">
-        <v>1</v>
-      </c>
-      <c r="P146" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q146">
-        <v>11.99</v>
-      </c>
-      <c r="R146">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y146" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="AA146" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="AB146" t="s">
         <v>39</v>
@@ -12902,13 +12935,13 @@
     </row>
     <row r="147" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C147" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="D147" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="E147" t="s">
         <v>33</v>
@@ -12926,13 +12959,13 @@
         <v>54</v>
       </c>
       <c r="K147" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="L147" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="M147" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="N147" t="s">
         <v>33</v>
@@ -12944,16 +12977,16 @@
         <v>38</v>
       </c>
       <c r="Q147">
-        <v>14.99</v>
+        <v>37.99</v>
       </c>
       <c r="R147">
-        <v>2.5</v>
+        <v>6.33</v>
       </c>
       <c r="Y147" t="s">
-        <v>175</v>
+        <v>100</v>
       </c>
       <c r="AA147" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="AB147" t="s">
         <v>39</v>
@@ -12967,13 +13000,13 @@
     </row>
     <row r="148" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="C148" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="D148" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="E148" t="s">
         <v>33</v>
@@ -12991,13 +13024,13 @@
         <v>54</v>
       </c>
       <c r="K148" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L148" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M148" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="N148" t="s">
         <v>33</v>
@@ -13009,19 +13042,16 @@
         <v>38</v>
       </c>
       <c r="Q148">
-        <v>37.99</v>
+        <v>11.99</v>
       </c>
       <c r="R148">
-        <v>6.33</v>
+        <v>2</v>
       </c>
       <c r="Y148" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z148" t="s">
-        <v>181</v>
+        <v>66</v>
       </c>
       <c r="AA148" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="AB148" t="s">
         <v>39</v>
@@ -13035,13 +13065,13 @@
     </row>
     <row r="149" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="C149" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="D149" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="E149" t="s">
         <v>33</v>
@@ -13059,37 +13089,34 @@
         <v>54</v>
       </c>
       <c r="K149" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="L149" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="M149" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="N149" t="s">
         <v>33</v>
       </c>
       <c r="O149">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P149" t="s">
         <v>38</v>
       </c>
       <c r="Q149">
-        <v>75.98</v>
+        <v>14.99</v>
       </c>
       <c r="R149">
-        <v>12.66</v>
+        <v>2.5</v>
       </c>
       <c r="Y149" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z149" t="s">
-        <v>47</v>
+        <v>175</v>
       </c>
       <c r="AA149" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="AB149" t="s">
         <v>39</v>
@@ -13103,13 +13130,13 @@
     </row>
     <row r="150" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>133</v>
+        <v>177</v>
       </c>
       <c r="C150" t="s">
-        <v>134</v>
+        <v>178</v>
       </c>
       <c r="D150" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="E150" t="s">
         <v>33</v>
@@ -13127,13 +13154,13 @@
         <v>54</v>
       </c>
       <c r="K150" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L150" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M150" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N150" t="s">
         <v>33</v>
@@ -13145,16 +13172,19 @@
         <v>38</v>
       </c>
       <c r="Q150">
-        <v>11.99</v>
+        <v>37.99</v>
       </c>
       <c r="R150">
-        <v>2</v>
+        <v>6.33</v>
       </c>
       <c r="Y150" t="s">
-        <v>69</v>
+        <v>180</v>
+      </c>
+      <c r="Z150" t="s">
+        <v>181</v>
       </c>
       <c r="AA150" t="s">
-        <v>135</v>
+        <v>182</v>
       </c>
       <c r="AB150" t="s">
         <v>39</v>
@@ -13168,13 +13198,13 @@
     </row>
     <row r="151" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>117</v>
+        <v>183</v>
       </c>
       <c r="C151" t="s">
-        <v>118</v>
+        <v>184</v>
       </c>
       <c r="D151" t="s">
-        <v>119</v>
+        <v>179</v>
       </c>
       <c r="E151" t="s">
         <v>33</v>
@@ -13192,37 +13222,37 @@
         <v>54</v>
       </c>
       <c r="K151" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="L151" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="M151" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="N151" t="s">
         <v>33</v>
       </c>
       <c r="O151">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P151" t="s">
         <v>38</v>
       </c>
       <c r="Q151">
-        <v>14.99</v>
+        <v>75.98</v>
       </c>
       <c r="R151">
-        <v>2.5</v>
+        <v>12.66</v>
       </c>
       <c r="Y151" t="s">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="Z151" t="s">
-        <v>121</v>
+        <v>47</v>
       </c>
       <c r="AA151" t="s">
-        <v>122</v>
+        <v>185</v>
       </c>
       <c r="AB151" t="s">
         <v>39</v>
@@ -13236,13 +13266,13 @@
     </row>
     <row r="152" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="C152" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="D152" t="s">
-        <v>125</v>
+        <v>186</v>
       </c>
       <c r="E152" t="s">
         <v>33</v>
@@ -13260,13 +13290,13 @@
         <v>54</v>
       </c>
       <c r="K152" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L152" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M152" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N152" t="s">
         <v>33</v>
@@ -13278,19 +13308,16 @@
         <v>38</v>
       </c>
       <c r="Q152">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R152">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y152" t="s">
-        <v>126</v>
-      </c>
-      <c r="Z152" t="s">
-        <v>127</v>
+        <v>69</v>
       </c>
       <c r="AA152" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="AB152" t="s">
         <v>39</v>
@@ -13304,13 +13331,13 @@
     </row>
     <row r="153" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="C153" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="D153" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="E153" t="s">
         <v>33</v>
@@ -13328,13 +13355,13 @@
         <v>54</v>
       </c>
       <c r="K153" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="L153" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="M153" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="N153" t="s">
         <v>33</v>
@@ -13346,16 +13373,19 @@
         <v>38</v>
       </c>
       <c r="Q153">
-        <v>38.49</v>
+        <v>14.99</v>
       </c>
       <c r="R153">
-        <v>6.42</v>
+        <v>2.5</v>
       </c>
       <c r="Y153" t="s">
-        <v>78</v>
+        <v>120</v>
+      </c>
+      <c r="Z153" t="s">
+        <v>121</v>
       </c>
       <c r="AA153" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="AB153" t="s">
         <v>39</v>
@@ -13369,16 +13399,16 @@
     </row>
     <row r="154" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="C154" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="D154" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E154" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F154" t="s">
         <v>34</v>
@@ -13393,22 +13423,37 @@
         <v>54</v>
       </c>
       <c r="K154" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L154" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M154" t="s">
-        <v>83</v>
+        <v>42</v>
+      </c>
+      <c r="N154" t="s">
+        <v>33</v>
       </c>
       <c r="O154">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P154" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q154">
+        <v>59.99</v>
+      </c>
+      <c r="R154">
+        <v>10</v>
       </c>
       <c r="Y154" t="s">
-        <v>103</v>
+        <v>126</v>
+      </c>
+      <c r="Z154" t="s">
+        <v>127</v>
       </c>
       <c r="AA154" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="AB154" t="s">
         <v>39</v>
@@ -13422,13 +13467,13 @@
     </row>
     <row r="155" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="C155" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="D155" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="E155" t="s">
         <v>33</v>
@@ -13446,13 +13491,13 @@
         <v>54</v>
       </c>
       <c r="K155" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="L155" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="M155" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="N155" t="s">
         <v>33</v>
@@ -13464,19 +13509,16 @@
         <v>38</v>
       </c>
       <c r="Q155">
-        <v>37.99</v>
+        <v>38.49</v>
       </c>
       <c r="R155">
-        <v>6.33</v>
+        <v>6.42</v>
       </c>
       <c r="Y155" t="s">
-        <v>109</v>
-      </c>
-      <c r="Z155" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="AA155" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="AB155" t="s">
         <v>39</v>
@@ -13490,16 +13532,16 @@
     </row>
     <row r="156" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C156" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D156" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="E156" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F156" t="s">
         <v>34</v>
@@ -13511,40 +13553,25 @@
         <v>36</v>
       </c>
       <c r="J156" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K156" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L156" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M156" t="s">
-        <v>42</v>
-      </c>
-      <c r="N156" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="O156">
-        <v>1</v>
-      </c>
-      <c r="P156" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q156">
-        <v>59.99</v>
-      </c>
-      <c r="R156">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y156" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z156" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="AA156" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="AB156" t="s">
         <v>39</v>
@@ -13558,66 +13585,202 @@
     </row>
     <row r="157" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
+        <v>107</v>
+      </c>
+      <c r="C157" t="s">
+        <v>108</v>
+      </c>
+      <c r="D157" t="s">
+        <v>137</v>
+      </c>
+      <c r="E157" t="s">
+        <v>33</v>
+      </c>
+      <c r="F157" t="s">
+        <v>34</v>
+      </c>
+      <c r="G157" t="s">
+        <v>35</v>
+      </c>
+      <c r="H157" t="s">
+        <v>36</v>
+      </c>
+      <c r="J157" t="s">
+        <v>54</v>
+      </c>
+      <c r="K157" t="s">
+        <v>48</v>
+      </c>
+      <c r="L157" t="s">
+        <v>49</v>
+      </c>
+      <c r="M157" t="s">
+        <v>50</v>
+      </c>
+      <c r="N157" t="s">
+        <v>33</v>
+      </c>
+      <c r="O157">
+        <v>1</v>
+      </c>
+      <c r="P157" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q157">
+        <v>37.99</v>
+      </c>
+      <c r="R157">
+        <v>6.33</v>
+      </c>
+      <c r="Y157" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z157" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA157" t="s">
+        <v>111</v>
+      </c>
+      <c r="AB157" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>112</v>
+      </c>
+      <c r="C158" t="s">
+        <v>113</v>
+      </c>
+      <c r="D158" t="s">
+        <v>114</v>
+      </c>
+      <c r="E158" t="s">
+        <v>33</v>
+      </c>
+      <c r="F158" t="s">
+        <v>34</v>
+      </c>
+      <c r="G158" t="s">
+        <v>35</v>
+      </c>
+      <c r="H158" t="s">
+        <v>36</v>
+      </c>
+      <c r="J158" t="s">
+        <v>37</v>
+      </c>
+      <c r="K158" t="s">
+        <v>40</v>
+      </c>
+      <c r="L158" t="s">
+        <v>41</v>
+      </c>
+      <c r="M158" t="s">
+        <v>42</v>
+      </c>
+      <c r="N158" t="s">
+        <v>33</v>
+      </c>
+      <c r="O158">
+        <v>1</v>
+      </c>
+      <c r="P158" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q158">
+        <v>59.99</v>
+      </c>
+      <c r="R158">
+        <v>10</v>
+      </c>
+      <c r="Y158" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z158" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA158" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB158" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
         <v>703</v>
       </c>
-      <c r="C157" t="s">
+      <c r="C159" t="s">
         <v>704</v>
       </c>
-      <c r="D157" t="s">
+      <c r="D159" t="s">
         <v>705</v>
       </c>
-      <c r="E157" t="s">
-        <v>33</v>
-      </c>
-      <c r="F157" t="s">
-        <v>34</v>
-      </c>
-      <c r="G157" t="s">
-        <v>35</v>
-      </c>
-      <c r="H157" t="s">
-        <v>36</v>
-      </c>
-      <c r="J157" t="s">
-        <v>54</v>
-      </c>
-      <c r="K157" t="s">
+      <c r="E159" t="s">
+        <v>33</v>
+      </c>
+      <c r="F159" t="s">
+        <v>34</v>
+      </c>
+      <c r="G159" t="s">
+        <v>35</v>
+      </c>
+      <c r="H159" t="s">
+        <v>36</v>
+      </c>
+      <c r="J159" t="s">
+        <v>54</v>
+      </c>
+      <c r="K159" t="s">
         <v>72</v>
       </c>
-      <c r="L157" t="s">
+      <c r="L159" t="s">
         <v>73</v>
       </c>
-      <c r="M157" t="s">
+      <c r="M159" t="s">
         <v>74</v>
       </c>
-      <c r="N157" t="s">
-        <v>33</v>
-      </c>
-      <c r="O157">
-        <v>1</v>
-      </c>
-      <c r="P157" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q157">
+      <c r="N159" t="s">
+        <v>33</v>
+      </c>
+      <c r="O159">
+        <v>1</v>
+      </c>
+      <c r="P159" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q159">
         <v>11.99</v>
       </c>
-      <c r="R157">
+      <c r="R159">
         <v>2</v>
       </c>
-      <c r="Y157" t="s">
+      <c r="Y159" t="s">
         <v>706</v>
       </c>
-      <c r="AA157" t="s">
+      <c r="AA159" t="s">
         <v>707</v>
       </c>
-      <c r="AB157" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD157" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG157" t="b">
+      <c r="AB159" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Raw Sales Data/Amazon.xlsx
+++ b/Raw Sales Data/Amazon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2588" uniqueCount="846">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2667" uniqueCount="864">
   <si>
     <t>amazon-order-id</t>
   </si>
@@ -2557,6 +2557,60 @@
   </si>
   <si>
     <t>IV180PU</t>
+  </si>
+  <si>
+    <t>203-6160260-8343558</t>
+  </si>
+  <si>
+    <t>2026-03-08T21:26:44+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-09T00:13:42+00:00</t>
+  </si>
+  <si>
+    <t>Wick</t>
+  </si>
+  <si>
+    <t>Caithness</t>
+  </si>
+  <si>
+    <t>KW1 5YW</t>
+  </si>
+  <si>
+    <t>205-1639328-1558715</t>
+  </si>
+  <si>
+    <t>2026-03-07T14:58:26+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-07T15:04:49+00:00</t>
+  </si>
+  <si>
+    <t>NORTHWICH</t>
+  </si>
+  <si>
+    <t>CW9 7XJ</t>
+  </si>
+  <si>
+    <t>206-3714610-7096320</t>
+  </si>
+  <si>
+    <t>2026-03-07T12:00:57+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-07T19:12:53+00:00</t>
+  </si>
+  <si>
+    <t>HOLSWORTHY</t>
+  </si>
+  <si>
+    <t>EX22 7YA</t>
+  </si>
+  <si>
+    <t>2026-03-07T09:40:38+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-07T09:39:56+00:00</t>
   </si>
 </sst>
 </file>
@@ -3363,7 +3417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG159"/>
+  <dimension ref="A1:AG164"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
@@ -3474,16 +3528,16 @@
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>837</v>
+        <v>846</v>
       </c>
       <c r="C2" t="s">
-        <v>838</v>
+        <v>847</v>
       </c>
       <c r="D2" t="s">
-        <v>839</v>
+        <v>848</v>
       </c>
       <c r="E2" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F2" t="s">
         <v>34</v>
@@ -3498,16 +3552,16 @@
         <v>54</v>
       </c>
       <c r="K2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L2" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N2" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O2">
         <v>1</v>
@@ -3516,16 +3570,25 @@
         <v>38</v>
       </c>
       <c r="Q2">
-        <v>40.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R2">
-        <v>6.83</v>
+        <v>11</v>
+      </c>
+      <c r="S2">
+        <v>6.99</v>
+      </c>
+      <c r="T2">
+        <v>1.17</v>
       </c>
       <c r="Y2" t="s">
-        <v>305</v>
+        <v>849</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>850</v>
       </c>
       <c r="AA2" t="s">
-        <v>840</v>
+        <v>851</v>
       </c>
       <c r="AB2" t="s">
         <v>39</v>
@@ -3539,16 +3602,16 @@
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>841</v>
+        <v>852</v>
       </c>
       <c r="C3" t="s">
-        <v>842</v>
+        <v>853</v>
       </c>
       <c r="D3" t="s">
-        <v>843</v>
+        <v>854</v>
       </c>
       <c r="E3" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="F3" t="s">
         <v>34</v>
@@ -3571,32 +3634,14 @@
       <c r="M3" t="s">
         <v>42</v>
       </c>
-      <c r="N3" t="s">
-        <v>99</v>
-      </c>
       <c r="O3">
-        <v>1</v>
-      </c>
-      <c r="P3" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q3">
-        <v>65.989999999999995</v>
-      </c>
-      <c r="R3">
-        <v>11</v>
-      </c>
-      <c r="S3">
-        <v>6.99</v>
-      </c>
-      <c r="T3">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="s">
-        <v>844</v>
+        <v>855</v>
       </c>
       <c r="AA3" t="s">
-        <v>845</v>
+        <v>856</v>
       </c>
       <c r="AB3" t="s">
         <v>39</v>
@@ -3610,16 +3655,16 @@
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>819</v>
+        <v>857</v>
       </c>
       <c r="C4" t="s">
-        <v>820</v>
+        <v>858</v>
       </c>
       <c r="D4" t="s">
-        <v>821</v>
+        <v>859</v>
       </c>
       <c r="E4" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F4" t="s">
         <v>34</v>
@@ -3634,16 +3679,16 @@
         <v>54</v>
       </c>
       <c r="K4" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L4" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M4" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N4" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O4">
         <v>1</v>
@@ -3652,19 +3697,16 @@
         <v>38</v>
       </c>
       <c r="Q4">
-        <v>40.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R4">
-        <v>6.83</v>
+        <v>11</v>
       </c>
       <c r="Y4" t="s">
-        <v>618</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>619</v>
+        <v>860</v>
       </c>
       <c r="AA4" t="s">
-        <v>620</v>
+        <v>861</v>
       </c>
       <c r="AB4" t="s">
         <v>39</v>
@@ -3678,16 +3720,16 @@
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>822</v>
+        <v>837</v>
       </c>
       <c r="C5" t="s">
-        <v>823</v>
+        <v>838</v>
       </c>
       <c r="D5" t="s">
-        <v>824</v>
+        <v>862</v>
       </c>
       <c r="E5" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F5" t="s">
         <v>34</v>
@@ -3702,16 +3744,16 @@
         <v>54</v>
       </c>
       <c r="K5" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L5" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M5" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N5" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O5">
         <v>1</v>
@@ -3720,16 +3762,16 @@
         <v>38</v>
       </c>
       <c r="Q5">
-        <v>14.99</v>
+        <v>40.99</v>
       </c>
       <c r="R5">
-        <v>2.5</v>
+        <v>6.83</v>
       </c>
       <c r="Y5" t="s">
-        <v>825</v>
+        <v>305</v>
       </c>
       <c r="AA5" t="s">
-        <v>826</v>
+        <v>840</v>
       </c>
       <c r="AB5" t="s">
         <v>39</v>
@@ -3743,16 +3785,16 @@
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>827</v>
+        <v>841</v>
       </c>
       <c r="C6" t="s">
-        <v>828</v>
+        <v>842</v>
       </c>
       <c r="D6" t="s">
-        <v>829</v>
+        <v>863</v>
       </c>
       <c r="E6" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
         <v>34</v>
@@ -3776,7 +3818,7 @@
         <v>42</v>
       </c>
       <c r="N6" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O6">
         <v>1</v>
@@ -3787,14 +3829,20 @@
       <c r="Q6">
         <v>65.989999999999995</v>
       </c>
+      <c r="R6">
+        <v>11</v>
+      </c>
       <c r="S6">
         <v>6.99</v>
       </c>
+      <c r="T6">
+        <v>1.17</v>
+      </c>
       <c r="Y6" t="s">
-        <v>830</v>
+        <v>844</v>
       </c>
       <c r="AA6" t="s">
-        <v>831</v>
+        <v>845</v>
       </c>
       <c r="AB6" t="s">
         <v>39</v>
@@ -3808,16 +3856,16 @@
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="C7" t="s">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="D7" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F7" t="s">
         <v>34</v>
@@ -3832,16 +3880,16 @@
         <v>54</v>
       </c>
       <c r="K7" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L7" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M7" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N7" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O7">
         <v>1</v>
@@ -3850,16 +3898,16 @@
         <v>38</v>
       </c>
       <c r="Q7">
-        <v>65.989999999999995</v>
+        <v>40.99</v>
       </c>
       <c r="R7">
-        <v>11</v>
+        <v>6.83</v>
       </c>
       <c r="Y7" t="s">
-        <v>835</v>
+        <v>305</v>
       </c>
       <c r="AA7" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="AB7" t="s">
         <v>39</v>
@@ -3873,16 +3921,16 @@
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>780</v>
+        <v>841</v>
       </c>
       <c r="C8" t="s">
-        <v>781</v>
+        <v>842</v>
       </c>
       <c r="D8" t="s">
-        <v>782</v>
+        <v>843</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F8" t="s">
         <v>34</v>
@@ -3906,7 +3954,7 @@
         <v>42</v>
       </c>
       <c r="N8" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O8">
         <v>1</v>
@@ -3920,11 +3968,17 @@
       <c r="R8">
         <v>11</v>
       </c>
+      <c r="S8">
+        <v>6.99</v>
+      </c>
+      <c r="T8">
+        <v>1.17</v>
+      </c>
       <c r="Y8" t="s">
-        <v>783</v>
+        <v>844</v>
       </c>
       <c r="AA8" t="s">
-        <v>784</v>
+        <v>845</v>
       </c>
       <c r="AB8" t="s">
         <v>39</v>
@@ -3938,16 +3992,16 @@
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>785</v>
+        <v>819</v>
       </c>
       <c r="C9" t="s">
-        <v>786</v>
+        <v>820</v>
       </c>
       <c r="D9" t="s">
-        <v>787</v>
+        <v>821</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F9" t="s">
         <v>34</v>
@@ -3971,7 +4025,7 @@
         <v>50</v>
       </c>
       <c r="N9" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O9">
         <v>1</v>
@@ -3986,10 +4040,13 @@
         <v>6.83</v>
       </c>
       <c r="Y9" t="s">
-        <v>788</v>
+        <v>618</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>619</v>
       </c>
       <c r="AA9" t="s">
-        <v>789</v>
+        <v>620</v>
       </c>
       <c r="AB9" t="s">
         <v>39</v>
@@ -4003,16 +4060,16 @@
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>790</v>
+        <v>822</v>
       </c>
       <c r="C10" t="s">
-        <v>791</v>
+        <v>823</v>
       </c>
       <c r="D10" t="s">
-        <v>792</v>
+        <v>824</v>
       </c>
       <c r="E10" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F10" t="s">
         <v>34</v>
@@ -4027,16 +4084,16 @@
         <v>54</v>
       </c>
       <c r="K10" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L10" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M10" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N10" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O10">
         <v>1</v>
@@ -4045,16 +4102,16 @@
         <v>38</v>
       </c>
       <c r="Q10">
-        <v>65.989999999999995</v>
+        <v>14.99</v>
       </c>
       <c r="R10">
-        <v>11</v>
+        <v>2.5</v>
       </c>
       <c r="Y10" t="s">
-        <v>793</v>
+        <v>825</v>
       </c>
       <c r="AA10" t="s">
-        <v>794</v>
+        <v>826</v>
       </c>
       <c r="AB10" t="s">
         <v>39</v>
@@ -4068,16 +4125,16 @@
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>795</v>
+        <v>827</v>
       </c>
       <c r="C11" t="s">
-        <v>796</v>
+        <v>828</v>
       </c>
       <c r="D11" t="s">
-        <v>797</v>
+        <v>829</v>
       </c>
       <c r="E11" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F11" t="s">
         <v>34</v>
@@ -4092,16 +4149,16 @@
         <v>54</v>
       </c>
       <c r="K11" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L11" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M11" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N11" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O11">
         <v>1</v>
@@ -4110,16 +4167,16 @@
         <v>38</v>
       </c>
       <c r="Q11">
-        <v>14.99</v>
-      </c>
-      <c r="R11">
-        <v>2.5</v>
+        <v>65.989999999999995</v>
+      </c>
+      <c r="S11">
+        <v>6.99</v>
       </c>
       <c r="Y11" t="s">
-        <v>798</v>
+        <v>830</v>
       </c>
       <c r="AA11" t="s">
-        <v>799</v>
+        <v>831</v>
       </c>
       <c r="AB11" t="s">
         <v>39</v>
@@ -4133,13 +4190,13 @@
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>800</v>
+        <v>832</v>
       </c>
       <c r="C12" t="s">
-        <v>801</v>
+        <v>833</v>
       </c>
       <c r="D12" t="s">
-        <v>802</v>
+        <v>834</v>
       </c>
       <c r="E12" t="s">
         <v>33</v>
@@ -4157,13 +4214,13 @@
         <v>54</v>
       </c>
       <c r="K12" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L12" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M12" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N12" t="s">
         <v>33</v>
@@ -4175,16 +4232,16 @@
         <v>38</v>
       </c>
       <c r="Q12">
-        <v>14.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R12">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="Y12" t="s">
-        <v>68</v>
+        <v>835</v>
       </c>
       <c r="AA12" t="s">
-        <v>803</v>
+        <v>836</v>
       </c>
       <c r="AB12" t="s">
         <v>39</v>
@@ -4198,13 +4255,13 @@
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>804</v>
+        <v>780</v>
       </c>
       <c r="C13" t="s">
-        <v>805</v>
+        <v>781</v>
       </c>
       <c r="D13" t="s">
-        <v>802</v>
+        <v>782</v>
       </c>
       <c r="E13" t="s">
         <v>33</v>
@@ -4222,13 +4279,13 @@
         <v>54</v>
       </c>
       <c r="K13" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L13" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M13" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N13" t="s">
         <v>33</v>
@@ -4240,16 +4297,16 @@
         <v>38</v>
       </c>
       <c r="Q13">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R13">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y13" t="s">
-        <v>806</v>
+        <v>783</v>
       </c>
       <c r="AA13" t="s">
-        <v>807</v>
+        <v>784</v>
       </c>
       <c r="AB13" t="s">
         <v>39</v>
@@ -4263,13 +4320,13 @@
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>808</v>
+        <v>785</v>
       </c>
       <c r="C14" t="s">
-        <v>809</v>
+        <v>786</v>
       </c>
       <c r="D14" t="s">
-        <v>810</v>
+        <v>787</v>
       </c>
       <c r="E14" t="s">
         <v>33</v>
@@ -4287,13 +4344,13 @@
         <v>54</v>
       </c>
       <c r="K14" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L14" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M14" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N14" t="s">
         <v>33</v>
@@ -4305,16 +4362,16 @@
         <v>38</v>
       </c>
       <c r="Q14">
-        <v>11.99</v>
+        <v>40.99</v>
       </c>
       <c r="R14">
-        <v>2</v>
+        <v>6.83</v>
       </c>
       <c r="Y14" t="s">
-        <v>66</v>
+        <v>788</v>
       </c>
       <c r="AA14" t="s">
-        <v>811</v>
+        <v>789</v>
       </c>
       <c r="AB14" t="s">
         <v>39</v>
@@ -4328,13 +4385,13 @@
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>812</v>
+        <v>790</v>
       </c>
       <c r="C15" t="s">
-        <v>813</v>
+        <v>791</v>
       </c>
       <c r="D15" t="s">
-        <v>814</v>
+        <v>792</v>
       </c>
       <c r="E15" t="s">
         <v>33</v>
@@ -4352,13 +4409,13 @@
         <v>54</v>
       </c>
       <c r="K15" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L15" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M15" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N15" t="s">
         <v>33</v>
@@ -4370,16 +4427,16 @@
         <v>38</v>
       </c>
       <c r="Q15">
-        <v>40.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R15">
-        <v>6.83</v>
+        <v>11</v>
       </c>
       <c r="Y15" t="s">
-        <v>815</v>
+        <v>793</v>
       </c>
       <c r="AA15" t="s">
-        <v>816</v>
+        <v>794</v>
       </c>
       <c r="AB15" t="s">
         <v>39</v>
@@ -4393,13 +4450,13 @@
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>745</v>
+        <v>795</v>
       </c>
       <c r="C16" t="s">
-        <v>746</v>
+        <v>796</v>
       </c>
       <c r="D16" t="s">
-        <v>817</v>
+        <v>797</v>
       </c>
       <c r="E16" t="s">
         <v>33</v>
@@ -4435,16 +4492,16 @@
         <v>38</v>
       </c>
       <c r="Q16">
-        <v>11.99</v>
+        <v>14.99</v>
       </c>
       <c r="R16">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Y16" t="s">
-        <v>748</v>
+        <v>798</v>
       </c>
       <c r="AA16" t="s">
-        <v>749</v>
+        <v>799</v>
       </c>
       <c r="AB16" t="s">
         <v>39</v>
@@ -4458,13 +4515,13 @@
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="C17" t="s">
-        <v>751</v>
+        <v>801</v>
       </c>
       <c r="D17" t="s">
-        <v>752</v>
+        <v>802</v>
       </c>
       <c r="E17" t="s">
         <v>33</v>
@@ -4482,13 +4539,13 @@
         <v>54</v>
       </c>
       <c r="K17" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L17" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M17" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N17" t="s">
         <v>33</v>
@@ -4500,16 +4557,16 @@
         <v>38</v>
       </c>
       <c r="Q17">
-        <v>65.989999999999995</v>
+        <v>14.99</v>
       </c>
       <c r="R17">
-        <v>11</v>
+        <v>2.5</v>
       </c>
       <c r="Y17" t="s">
-        <v>753</v>
+        <v>68</v>
       </c>
       <c r="AA17" t="s">
-        <v>754</v>
+        <v>803</v>
       </c>
       <c r="AB17" t="s">
         <v>39</v>
@@ -4523,13 +4580,13 @@
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>755</v>
+        <v>804</v>
       </c>
       <c r="C18" t="s">
-        <v>756</v>
+        <v>805</v>
       </c>
       <c r="D18" t="s">
-        <v>818</v>
+        <v>802</v>
       </c>
       <c r="E18" t="s">
         <v>33</v>
@@ -4547,13 +4604,13 @@
         <v>54</v>
       </c>
       <c r="K18" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L18" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M18" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N18" t="s">
         <v>33</v>
@@ -4565,25 +4622,16 @@
         <v>38</v>
       </c>
       <c r="Q18">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R18">
-        <v>11</v>
-      </c>
-      <c r="S18">
-        <v>6.99</v>
-      </c>
-      <c r="T18">
-        <v>1.17</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="s">
-        <v>758</v>
-      </c>
-      <c r="Z18" t="s">
-        <v>759</v>
+        <v>806</v>
       </c>
       <c r="AA18" t="s">
-        <v>760</v>
+        <v>807</v>
       </c>
       <c r="AB18" t="s">
         <v>39</v>
@@ -4597,13 +4645,13 @@
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="C19" t="s">
-        <v>762</v>
+        <v>809</v>
       </c>
       <c r="D19" t="s">
-        <v>763</v>
+        <v>810</v>
       </c>
       <c r="E19" t="s">
         <v>33</v>
@@ -4645,13 +4693,10 @@
         <v>2</v>
       </c>
       <c r="Y19" t="s">
-        <v>764</v>
-      </c>
-      <c r="Z19" t="s">
-        <v>279</v>
+        <v>66</v>
       </c>
       <c r="AA19" t="s">
-        <v>765</v>
+        <v>811</v>
       </c>
       <c r="AB19" t="s">
         <v>39</v>
@@ -4665,13 +4710,13 @@
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>766</v>
+        <v>812</v>
       </c>
       <c r="C20" t="s">
-        <v>767</v>
+        <v>813</v>
       </c>
       <c r="D20" t="s">
-        <v>768</v>
+        <v>814</v>
       </c>
       <c r="E20" t="s">
         <v>33</v>
@@ -4689,13 +4734,13 @@
         <v>54</v>
       </c>
       <c r="K20" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="L20" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="M20" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="N20" t="s">
         <v>33</v>
@@ -4707,19 +4752,16 @@
         <v>38</v>
       </c>
       <c r="Q20">
-        <v>11.99</v>
+        <v>40.99</v>
       </c>
       <c r="R20">
-        <v>2</v>
+        <v>6.83</v>
       </c>
       <c r="Y20" t="s">
-        <v>91</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>121</v>
+        <v>815</v>
       </c>
       <c r="AA20" t="s">
-        <v>769</v>
+        <v>816</v>
       </c>
       <c r="AB20" t="s">
         <v>39</v>
@@ -4733,13 +4775,13 @@
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>770</v>
+        <v>745</v>
       </c>
       <c r="C21" t="s">
-        <v>771</v>
+        <v>746</v>
       </c>
       <c r="D21" t="s">
-        <v>772</v>
+        <v>817</v>
       </c>
       <c r="E21" t="s">
         <v>33</v>
@@ -4757,13 +4799,13 @@
         <v>54</v>
       </c>
       <c r="K21" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L21" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M21" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N21" t="s">
         <v>33</v>
@@ -4775,19 +4817,16 @@
         <v>38</v>
       </c>
       <c r="Q21">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R21">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="s">
-        <v>773</v>
-      </c>
-      <c r="Z21" t="s">
-        <v>64</v>
+        <v>748</v>
       </c>
       <c r="AA21" t="s">
-        <v>774</v>
+        <v>749</v>
       </c>
       <c r="AB21" t="s">
         <v>39</v>
@@ -4801,13 +4840,13 @@
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>775</v>
+        <v>750</v>
       </c>
       <c r="C22" t="s">
-        <v>776</v>
+        <v>751</v>
       </c>
       <c r="D22" t="s">
-        <v>777</v>
+        <v>752</v>
       </c>
       <c r="E22" t="s">
         <v>33</v>
@@ -4849,10 +4888,10 @@
         <v>11</v>
       </c>
       <c r="Y22" t="s">
-        <v>778</v>
+        <v>753</v>
       </c>
       <c r="AA22" t="s">
-        <v>779</v>
+        <v>754</v>
       </c>
       <c r="AB22" t="s">
         <v>39</v>
@@ -4866,16 +4905,16 @@
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>745</v>
+        <v>755</v>
       </c>
       <c r="C23" t="s">
-        <v>746</v>
+        <v>756</v>
       </c>
       <c r="D23" t="s">
-        <v>747</v>
+        <v>818</v>
       </c>
       <c r="E23" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F23" t="s">
         <v>34</v>
@@ -4890,16 +4929,16 @@
         <v>54</v>
       </c>
       <c r="K23" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L23" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M23" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N23" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O23">
         <v>1</v>
@@ -4908,16 +4947,25 @@
         <v>38</v>
       </c>
       <c r="Q23">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R23">
-        <v>2</v>
+        <v>11</v>
+      </c>
+      <c r="S23">
+        <v>6.99</v>
+      </c>
+      <c r="T23">
+        <v>1.17</v>
       </c>
       <c r="Y23" t="s">
-        <v>748</v>
+        <v>758</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>759</v>
       </c>
       <c r="AA23" t="s">
-        <v>749</v>
+        <v>760</v>
       </c>
       <c r="AB23" t="s">
         <v>39</v>
@@ -4931,13 +4979,13 @@
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>750</v>
+        <v>761</v>
       </c>
       <c r="C24" t="s">
-        <v>751</v>
+        <v>762</v>
       </c>
       <c r="D24" t="s">
-        <v>752</v>
+        <v>763</v>
       </c>
       <c r="E24" t="s">
         <v>33</v>
@@ -4955,13 +5003,13 @@
         <v>54</v>
       </c>
       <c r="K24" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L24" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M24" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N24" t="s">
         <v>33</v>
@@ -4973,16 +5021,19 @@
         <v>38</v>
       </c>
       <c r="Q24">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R24">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y24" t="s">
-        <v>753</v>
+        <v>764</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>279</v>
       </c>
       <c r="AA24" t="s">
-        <v>754</v>
+        <v>765</v>
       </c>
       <c r="AB24" t="s">
         <v>39</v>
@@ -4996,16 +5047,16 @@
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>755</v>
+        <v>766</v>
       </c>
       <c r="C25" t="s">
-        <v>756</v>
+        <v>767</v>
       </c>
       <c r="D25" t="s">
-        <v>757</v>
+        <v>768</v>
       </c>
       <c r="E25" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F25" t="s">
         <v>34</v>
@@ -5020,16 +5071,16 @@
         <v>54</v>
       </c>
       <c r="K25" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L25" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M25" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N25" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O25">
         <v>1</v>
@@ -5038,25 +5089,19 @@
         <v>38</v>
       </c>
       <c r="Q25">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R25">
-        <v>11</v>
-      </c>
-      <c r="S25">
-        <v>6.99</v>
-      </c>
-      <c r="T25">
-        <v>1.17</v>
+        <v>2</v>
       </c>
       <c r="Y25" t="s">
-        <v>758</v>
+        <v>91</v>
       </c>
       <c r="Z25" t="s">
-        <v>759</v>
+        <v>121</v>
       </c>
       <c r="AA25" t="s">
-        <v>760</v>
+        <v>769</v>
       </c>
       <c r="AB25" t="s">
         <v>39</v>
@@ -5070,13 +5115,13 @@
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>761</v>
+        <v>770</v>
       </c>
       <c r="C26" t="s">
-        <v>762</v>
+        <v>771</v>
       </c>
       <c r="D26" t="s">
-        <v>763</v>
+        <v>772</v>
       </c>
       <c r="E26" t="s">
         <v>33</v>
@@ -5094,13 +5139,13 @@
         <v>54</v>
       </c>
       <c r="K26" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L26" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M26" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N26" t="s">
         <v>33</v>
@@ -5112,19 +5157,19 @@
         <v>38</v>
       </c>
       <c r="Q26">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R26">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y26" t="s">
-        <v>764</v>
+        <v>773</v>
       </c>
       <c r="Z26" t="s">
-        <v>279</v>
+        <v>64</v>
       </c>
       <c r="AA26" t="s">
-        <v>765</v>
+        <v>774</v>
       </c>
       <c r="AB26" t="s">
         <v>39</v>
@@ -5138,13 +5183,13 @@
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>766</v>
+        <v>775</v>
       </c>
       <c r="C27" t="s">
-        <v>767</v>
+        <v>776</v>
       </c>
       <c r="D27" t="s">
-        <v>768</v>
+        <v>777</v>
       </c>
       <c r="E27" t="s">
         <v>33</v>
@@ -5162,13 +5207,13 @@
         <v>54</v>
       </c>
       <c r="K27" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L27" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M27" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N27" t="s">
         <v>33</v>
@@ -5180,19 +5225,16 @@
         <v>38</v>
       </c>
       <c r="Q27">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R27">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y27" t="s">
-        <v>91</v>
-      </c>
-      <c r="Z27" t="s">
-        <v>121</v>
+        <v>778</v>
       </c>
       <c r="AA27" t="s">
-        <v>769</v>
+        <v>779</v>
       </c>
       <c r="AB27" t="s">
         <v>39</v>
@@ -5206,16 +5248,16 @@
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>770</v>
+        <v>745</v>
       </c>
       <c r="C28" t="s">
-        <v>771</v>
+        <v>746</v>
       </c>
       <c r="D28" t="s">
-        <v>772</v>
+        <v>747</v>
       </c>
       <c r="E28" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F28" t="s">
         <v>34</v>
@@ -5230,16 +5272,16 @@
         <v>54</v>
       </c>
       <c r="K28" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L28" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M28" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N28" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O28">
         <v>1</v>
@@ -5248,19 +5290,16 @@
         <v>38</v>
       </c>
       <c r="Q28">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R28">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y28" t="s">
-        <v>773</v>
-      </c>
-      <c r="Z28" t="s">
-        <v>64</v>
+        <v>748</v>
       </c>
       <c r="AA28" t="s">
-        <v>774</v>
+        <v>749</v>
       </c>
       <c r="AB28" t="s">
         <v>39</v>
@@ -5274,13 +5313,13 @@
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>775</v>
+        <v>750</v>
       </c>
       <c r="C29" t="s">
-        <v>776</v>
+        <v>751</v>
       </c>
       <c r="D29" t="s">
-        <v>777</v>
+        <v>752</v>
       </c>
       <c r="E29" t="s">
         <v>33</v>
@@ -5322,10 +5361,10 @@
         <v>11</v>
       </c>
       <c r="Y29" t="s">
-        <v>778</v>
+        <v>753</v>
       </c>
       <c r="AA29" t="s">
-        <v>779</v>
+        <v>754</v>
       </c>
       <c r="AB29" t="s">
         <v>39</v>
@@ -5339,13 +5378,13 @@
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>714</v>
+        <v>755</v>
       </c>
       <c r="C30" t="s">
-        <v>715</v>
+        <v>756</v>
       </c>
       <c r="D30" t="s">
-        <v>716</v>
+        <v>757</v>
       </c>
       <c r="E30" t="s">
         <v>98</v>
@@ -5363,13 +5402,13 @@
         <v>54</v>
       </c>
       <c r="K30" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L30" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M30" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N30" t="s">
         <v>99</v>
@@ -5381,19 +5420,25 @@
         <v>38</v>
       </c>
       <c r="Q30">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R30">
-        <v>2</v>
+        <v>11</v>
+      </c>
+      <c r="S30">
+        <v>6.99</v>
+      </c>
+      <c r="T30">
+        <v>1.17</v>
       </c>
       <c r="Y30" t="s">
-        <v>717</v>
+        <v>758</v>
       </c>
       <c r="Z30" t="s">
-        <v>51</v>
+        <v>759</v>
       </c>
       <c r="AA30" t="s">
-        <v>718</v>
+        <v>760</v>
       </c>
       <c r="AB30" t="s">
         <v>39</v>
@@ -5407,13 +5452,13 @@
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>719</v>
+        <v>761</v>
       </c>
       <c r="C31" t="s">
-        <v>720</v>
+        <v>762</v>
       </c>
       <c r="D31" t="s">
-        <v>721</v>
+        <v>763</v>
       </c>
       <c r="E31" t="s">
         <v>33</v>
@@ -5431,13 +5476,13 @@
         <v>54</v>
       </c>
       <c r="K31" t="s">
-        <v>722</v>
+        <v>72</v>
       </c>
       <c r="L31" t="s">
-        <v>723</v>
+        <v>73</v>
       </c>
       <c r="M31" t="s">
-        <v>724</v>
+        <v>74</v>
       </c>
       <c r="N31" t="s">
         <v>33</v>
@@ -5449,19 +5494,19 @@
         <v>38</v>
       </c>
       <c r="Q31">
-        <v>12.99</v>
+        <v>11.99</v>
       </c>
       <c r="R31">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="Y31" t="s">
-        <v>725</v>
+        <v>764</v>
       </c>
       <c r="Z31" t="s">
-        <v>726</v>
+        <v>279</v>
       </c>
       <c r="AA31" t="s">
-        <v>727</v>
+        <v>765</v>
       </c>
       <c r="AB31" t="s">
         <v>39</v>
@@ -5475,13 +5520,13 @@
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>728</v>
+        <v>766</v>
       </c>
       <c r="C32" t="s">
-        <v>729</v>
+        <v>767</v>
       </c>
       <c r="D32" t="s">
-        <v>730</v>
+        <v>768</v>
       </c>
       <c r="E32" t="s">
         <v>33</v>
@@ -5523,10 +5568,13 @@
         <v>2</v>
       </c>
       <c r="Y32" t="s">
-        <v>731</v>
+        <v>91</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>121</v>
       </c>
       <c r="AA32" t="s">
-        <v>732</v>
+        <v>769</v>
       </c>
       <c r="AB32" t="s">
         <v>39</v>
@@ -5540,13 +5588,13 @@
     </row>
     <row r="33" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>733</v>
+        <v>770</v>
       </c>
       <c r="C33" t="s">
-        <v>734</v>
+        <v>771</v>
       </c>
       <c r="D33" t="s">
-        <v>735</v>
+        <v>772</v>
       </c>
       <c r="E33" t="s">
         <v>33</v>
@@ -5564,13 +5612,13 @@
         <v>54</v>
       </c>
       <c r="K33" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L33" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M33" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N33" t="s">
         <v>33</v>
@@ -5582,16 +5630,19 @@
         <v>38</v>
       </c>
       <c r="Q33">
-        <v>40.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R33">
-        <v>6.83</v>
+        <v>11</v>
       </c>
       <c r="Y33" t="s">
-        <v>736</v>
+        <v>773</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>64</v>
       </c>
       <c r="AA33" t="s">
-        <v>737</v>
+        <v>774</v>
       </c>
       <c r="AB33" t="s">
         <v>39</v>
@@ -5605,13 +5656,13 @@
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>738</v>
+        <v>775</v>
       </c>
       <c r="C34" t="s">
-        <v>739</v>
+        <v>776</v>
       </c>
       <c r="D34" t="s">
-        <v>740</v>
+        <v>777</v>
       </c>
       <c r="E34" t="s">
         <v>33</v>
@@ -5629,13 +5680,13 @@
         <v>54</v>
       </c>
       <c r="K34" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L34" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M34" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N34" t="s">
         <v>33</v>
@@ -5647,16 +5698,16 @@
         <v>38</v>
       </c>
       <c r="Q34">
-        <v>40.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R34">
-        <v>6.83</v>
+        <v>11</v>
       </c>
       <c r="Y34" t="s">
-        <v>741</v>
+        <v>778</v>
       </c>
       <c r="AA34" t="s">
-        <v>742</v>
+        <v>779</v>
       </c>
       <c r="AB34" t="s">
         <v>39</v>
@@ -5670,16 +5721,16 @@
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="C35" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="D35" t="s">
-        <v>743</v>
+        <v>716</v>
       </c>
       <c r="E35" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F35" t="s">
         <v>34</v>
@@ -5694,16 +5745,16 @@
         <v>54</v>
       </c>
       <c r="K35" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L35" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M35" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N35" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O35">
         <v>1</v>
@@ -5712,19 +5763,19 @@
         <v>38</v>
       </c>
       <c r="Q35">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R35">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y35" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="Z35" t="s">
-        <v>712</v>
+        <v>51</v>
       </c>
       <c r="AA35" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="AB35" t="s">
         <v>39</v>
@@ -5738,13 +5789,13 @@
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>643</v>
+        <v>719</v>
       </c>
       <c r="C36" t="s">
-        <v>644</v>
+        <v>720</v>
       </c>
       <c r="D36" t="s">
-        <v>744</v>
+        <v>721</v>
       </c>
       <c r="E36" t="s">
         <v>33</v>
@@ -5762,13 +5813,13 @@
         <v>54</v>
       </c>
       <c r="K36" t="s">
-        <v>94</v>
+        <v>722</v>
       </c>
       <c r="L36" t="s">
-        <v>82</v>
+        <v>723</v>
       </c>
       <c r="M36" t="s">
-        <v>83</v>
+        <v>724</v>
       </c>
       <c r="N36" t="s">
         <v>33</v>
@@ -5780,16 +5831,19 @@
         <v>38</v>
       </c>
       <c r="Q36">
-        <v>14.99</v>
+        <v>12.99</v>
       </c>
       <c r="R36">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="Y36" t="s">
-        <v>646</v>
+        <v>725</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>726</v>
       </c>
       <c r="AA36" t="s">
-        <v>647</v>
+        <v>727</v>
       </c>
       <c r="AB36" t="s">
         <v>39</v>
@@ -5803,16 +5857,16 @@
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>708</v>
+        <v>728</v>
       </c>
       <c r="C37" t="s">
-        <v>709</v>
+        <v>729</v>
       </c>
       <c r="D37" t="s">
-        <v>710</v>
+        <v>730</v>
       </c>
       <c r="E37" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F37" t="s">
         <v>34</v>
@@ -5827,16 +5881,16 @@
         <v>54</v>
       </c>
       <c r="K37" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L37" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M37" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N37" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O37">
         <v>1</v>
@@ -5845,19 +5899,16 @@
         <v>38</v>
       </c>
       <c r="Q37">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R37">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y37" t="s">
-        <v>711</v>
-      </c>
-      <c r="Z37" t="s">
-        <v>712</v>
+        <v>731</v>
       </c>
       <c r="AA37" t="s">
-        <v>713</v>
+        <v>732</v>
       </c>
       <c r="AB37" t="s">
         <v>39</v>
@@ -5871,22 +5922,22 @@
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>138</v>
+        <v>733</v>
       </c>
       <c r="C38" t="s">
-        <v>139</v>
+        <v>734</v>
       </c>
       <c r="D38" t="s">
-        <v>187</v>
+        <v>735</v>
       </c>
       <c r="E38" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F38" t="s">
         <v>34</v>
       </c>
       <c r="G38" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="H38" t="s">
         <v>36</v>
@@ -5895,25 +5946,37 @@
         <v>54</v>
       </c>
       <c r="K38" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="L38" t="s">
-        <v>142</v>
+        <v>44</v>
       </c>
       <c r="M38" t="s">
-        <v>143</v>
+        <v>45</v>
+      </c>
+      <c r="N38" t="s">
+        <v>33</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P38" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q38">
+        <v>40.99</v>
+      </c>
+      <c r="R38">
+        <v>6.83</v>
       </c>
       <c r="Y38" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA38">
-        <v>80100</v>
+        <v>736</v>
+      </c>
+      <c r="AA38" t="s">
+        <v>737</v>
       </c>
       <c r="AB38" t="s">
-        <v>145</v>
+        <v>39</v>
       </c>
       <c r="AD38" t="b">
         <v>0</v>
@@ -5924,22 +5987,22 @@
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>146</v>
+        <v>738</v>
       </c>
       <c r="C39" t="s">
-        <v>147</v>
+        <v>739</v>
       </c>
       <c r="D39" t="s">
-        <v>148</v>
+        <v>740</v>
       </c>
       <c r="E39" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F39" t="s">
         <v>34</v>
       </c>
       <c r="G39" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="H39" t="s">
         <v>36</v>
@@ -5948,25 +6011,37 @@
         <v>54</v>
       </c>
       <c r="K39" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="L39" t="s">
-        <v>142</v>
+        <v>49</v>
       </c>
       <c r="M39" t="s">
-        <v>143</v>
+        <v>50</v>
+      </c>
+      <c r="N39" t="s">
+        <v>33</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P39" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q39">
+        <v>40.99</v>
+      </c>
+      <c r="R39">
+        <v>6.83</v>
       </c>
       <c r="Y39" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA39">
-        <v>80100</v>
+        <v>741</v>
+      </c>
+      <c r="AA39" t="s">
+        <v>742</v>
       </c>
       <c r="AB39" t="s">
-        <v>145</v>
+        <v>39</v>
       </c>
       <c r="AD39" t="b">
         <v>0</v>
@@ -5977,22 +6052,22 @@
     </row>
     <row r="40" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>632</v>
+        <v>708</v>
       </c>
       <c r="C40" t="s">
-        <v>633</v>
+        <v>709</v>
       </c>
       <c r="D40" t="s">
-        <v>634</v>
+        <v>743</v>
       </c>
       <c r="E40" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F40" t="s">
         <v>34</v>
       </c>
       <c r="G40" t="s">
-        <v>635</v>
+        <v>35</v>
       </c>
       <c r="H40" t="s">
         <v>36</v>
@@ -6001,37 +6076,40 @@
         <v>54</v>
       </c>
       <c r="K40" t="s">
-        <v>636</v>
+        <v>40</v>
       </c>
       <c r="L40" t="s">
-        <v>637</v>
+        <v>41</v>
       </c>
       <c r="M40" t="s">
-        <v>638</v>
+        <v>42</v>
+      </c>
+      <c r="N40" t="s">
+        <v>33</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="Q40">
-        <v>22.9</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R40">
-        <v>4.8099999999999996</v>
+        <v>11</v>
       </c>
       <c r="Y40" t="s">
-        <v>639</v>
+        <v>711</v>
       </c>
       <c r="Z40" t="s">
-        <v>640</v>
+        <v>712</v>
       </c>
       <c r="AA40" t="s">
-        <v>641</v>
+        <v>713</v>
       </c>
       <c r="AB40" t="s">
-        <v>642</v>
+        <v>39</v>
       </c>
       <c r="AD40" t="b">
         <v>0</v>
@@ -6048,10 +6126,10 @@
         <v>644</v>
       </c>
       <c r="D41" t="s">
-        <v>645</v>
+        <v>744</v>
       </c>
       <c r="E41" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F41" t="s">
         <v>34</v>
@@ -6075,7 +6153,7 @@
         <v>83</v>
       </c>
       <c r="N41" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O41">
         <v>1</v>
@@ -6107,16 +6185,16 @@
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>609</v>
+        <v>708</v>
       </c>
       <c r="C42" t="s">
-        <v>610</v>
+        <v>709</v>
       </c>
       <c r="D42" t="s">
-        <v>611</v>
+        <v>710</v>
       </c>
       <c r="E42" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F42" t="s">
         <v>34</v>
@@ -6131,16 +6209,16 @@
         <v>54</v>
       </c>
       <c r="K42" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L42" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M42" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="N42" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O42">
         <v>1</v>
@@ -6149,19 +6227,19 @@
         <v>38</v>
       </c>
       <c r="Q42">
-        <v>14.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R42">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="Y42" t="s">
-        <v>612</v>
+        <v>711</v>
       </c>
       <c r="Z42" t="s">
-        <v>613</v>
+        <v>712</v>
       </c>
       <c r="AA42" t="s">
-        <v>614</v>
+        <v>713</v>
       </c>
       <c r="AB42" t="s">
         <v>39</v>
@@ -6175,13 +6253,13 @@
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>493</v>
+        <v>138</v>
       </c>
       <c r="C43" t="s">
-        <v>494</v>
+        <v>139</v>
       </c>
       <c r="D43" t="s">
-        <v>648</v>
+        <v>187</v>
       </c>
       <c r="E43" t="s">
         <v>53</v>
@@ -6190,7 +6268,7 @@
         <v>34</v>
       </c>
       <c r="G43" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="H43" t="s">
         <v>36</v>
@@ -6199,25 +6277,25 @@
         <v>54</v>
       </c>
       <c r="K43" t="s">
-        <v>40</v>
+        <v>141</v>
       </c>
       <c r="L43" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="M43" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="O43">
         <v>0</v>
       </c>
       <c r="Y43" t="s">
-        <v>495</v>
-      </c>
-      <c r="AA43" t="s">
-        <v>496</v>
+        <v>144</v>
+      </c>
+      <c r="AA43">
+        <v>80100</v>
       </c>
       <c r="AB43" t="s">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="AD43" t="b">
         <v>0</v>
@@ -6228,22 +6306,22 @@
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>615</v>
+        <v>146</v>
       </c>
       <c r="C44" t="s">
-        <v>616</v>
+        <v>147</v>
       </c>
       <c r="D44" t="s">
-        <v>617</v>
+        <v>148</v>
       </c>
       <c r="E44" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="F44" t="s">
         <v>34</v>
       </c>
       <c r="G44" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="H44" t="s">
         <v>36</v>
@@ -6252,37 +6330,25 @@
         <v>54</v>
       </c>
       <c r="K44" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="L44" t="s">
-        <v>49</v>
+        <v>142</v>
       </c>
       <c r="M44" t="s">
-        <v>50</v>
-      </c>
-      <c r="N44" t="s">
-        <v>99</v>
+        <v>143</v>
       </c>
       <c r="O44">
-        <v>1</v>
-      </c>
-      <c r="P44" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q44">
-        <v>40.99</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="s">
-        <v>618</v>
-      </c>
-      <c r="Z44" t="s">
-        <v>619</v>
-      </c>
-      <c r="AA44" t="s">
-        <v>620</v>
+        <v>144</v>
+      </c>
+      <c r="AA44">
+        <v>80100</v>
       </c>
       <c r="AB44" t="s">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="AD44" t="b">
         <v>0</v>
@@ -6293,22 +6359,22 @@
     </row>
     <row r="45" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>621</v>
+        <v>632</v>
       </c>
       <c r="C45" t="s">
-        <v>622</v>
+        <v>633</v>
       </c>
       <c r="D45" t="s">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="E45" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F45" t="s">
         <v>34</v>
       </c>
       <c r="G45" t="s">
-        <v>35</v>
+        <v>635</v>
       </c>
       <c r="H45" t="s">
         <v>36</v>
@@ -6317,46 +6383,37 @@
         <v>54</v>
       </c>
       <c r="K45" t="s">
-        <v>40</v>
+        <v>636</v>
       </c>
       <c r="L45" t="s">
-        <v>41</v>
+        <v>637</v>
       </c>
       <c r="M45" t="s">
-        <v>42</v>
-      </c>
-      <c r="N45" t="s">
-        <v>33</v>
+        <v>638</v>
       </c>
       <c r="O45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P45" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="Q45">
-        <v>64.989999999999995</v>
+        <v>22.9</v>
       </c>
       <c r="R45">
-        <v>10.83</v>
-      </c>
-      <c r="S45">
-        <v>6.99</v>
-      </c>
-      <c r="T45">
-        <v>1.17</v>
+        <v>4.8099999999999996</v>
       </c>
       <c r="Y45" t="s">
-        <v>624</v>
+        <v>639</v>
       </c>
       <c r="Z45" t="s">
-        <v>625</v>
+        <v>640</v>
       </c>
       <c r="AA45" t="s">
-        <v>626</v>
+        <v>641</v>
       </c>
       <c r="AB45" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="AD45" t="b">
         <v>0</v>
@@ -6367,16 +6424,16 @@
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>627</v>
+        <v>643</v>
       </c>
       <c r="C46" t="s">
-        <v>628</v>
+        <v>644</v>
       </c>
       <c r="D46" t="s">
-        <v>629</v>
+        <v>645</v>
       </c>
       <c r="E46" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F46" t="s">
         <v>34</v>
@@ -6391,16 +6448,16 @@
         <v>54</v>
       </c>
       <c r="K46" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="L46" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="M46" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="N46" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O46">
         <v>1</v>
@@ -6409,16 +6466,16 @@
         <v>38</v>
       </c>
       <c r="Q46">
-        <v>11.99</v>
+        <v>14.99</v>
       </c>
       <c r="R46">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Y46" t="s">
-        <v>630</v>
+        <v>646</v>
       </c>
       <c r="AA46" t="s">
-        <v>631</v>
+        <v>647</v>
       </c>
       <c r="AB46" t="s">
         <v>39</v>
@@ -6432,13 +6489,13 @@
     </row>
     <row r="47" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>649</v>
+        <v>609</v>
       </c>
       <c r="C47" t="s">
-        <v>650</v>
+        <v>610</v>
       </c>
       <c r="D47" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="E47" t="s">
         <v>33</v>
@@ -6456,13 +6513,13 @@
         <v>54</v>
       </c>
       <c r="K47" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="L47" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="M47" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="N47" t="s">
         <v>33</v>
@@ -6474,19 +6531,19 @@
         <v>38</v>
       </c>
       <c r="Q47">
-        <v>39.99</v>
+        <v>14.99</v>
       </c>
       <c r="R47">
-        <v>6.67</v>
+        <v>2.5</v>
       </c>
       <c r="Y47" t="s">
-        <v>652</v>
+        <v>612</v>
       </c>
       <c r="Z47" t="s">
-        <v>653</v>
+        <v>613</v>
       </c>
       <c r="AA47" t="s">
-        <v>654</v>
+        <v>614</v>
       </c>
       <c r="AB47" t="s">
         <v>39</v>
@@ -6500,16 +6557,16 @@
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>655</v>
+        <v>493</v>
       </c>
       <c r="C48" t="s">
-        <v>656</v>
+        <v>494</v>
       </c>
       <c r="D48" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="E48" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F48" t="s">
         <v>34</v>
@@ -6524,34 +6581,22 @@
         <v>54</v>
       </c>
       <c r="K48" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L48" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M48" t="s">
-        <v>83</v>
-      </c>
-      <c r="N48" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O48">
-        <v>1</v>
-      </c>
-      <c r="P48" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q48">
-        <v>14.99</v>
-      </c>
-      <c r="R48">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="s">
-        <v>658</v>
+        <v>495</v>
       </c>
       <c r="AA48" t="s">
-        <v>659</v>
+        <v>496</v>
       </c>
       <c r="AB48" t="s">
         <v>39</v>
@@ -6565,16 +6610,16 @@
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>571</v>
+        <v>615</v>
       </c>
       <c r="C49" t="s">
-        <v>572</v>
+        <v>616</v>
       </c>
       <c r="D49" t="s">
-        <v>660</v>
+        <v>617</v>
       </c>
       <c r="E49" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F49" t="s">
         <v>34</v>
@@ -6589,16 +6634,16 @@
         <v>54</v>
       </c>
       <c r="K49" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L49" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M49" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N49" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O49">
         <v>1</v>
@@ -6607,16 +6652,16 @@
         <v>38</v>
       </c>
       <c r="Q49">
-        <v>64.989999999999995</v>
-      </c>
-      <c r="R49">
-        <v>10.83</v>
+        <v>40.99</v>
       </c>
       <c r="Y49" t="s">
-        <v>573</v>
+        <v>618</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>619</v>
       </c>
       <c r="AA49" t="s">
-        <v>574</v>
+        <v>620</v>
       </c>
       <c r="AB49" t="s">
         <v>39</v>
@@ -6630,13 +6675,13 @@
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>599</v>
+        <v>621</v>
       </c>
       <c r="C50" t="s">
-        <v>600</v>
+        <v>622</v>
       </c>
       <c r="D50" t="s">
-        <v>601</v>
+        <v>623</v>
       </c>
       <c r="E50" t="s">
         <v>33</v>
@@ -6654,13 +6699,13 @@
         <v>54</v>
       </c>
       <c r="K50" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L50" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M50" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="N50" t="s">
         <v>33</v>
@@ -6672,16 +6717,25 @@
         <v>38</v>
       </c>
       <c r="Q50">
-        <v>14.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R50">
-        <v>2.5</v>
+        <v>10.83</v>
+      </c>
+      <c r="S50">
+        <v>6.99</v>
+      </c>
+      <c r="T50">
+        <v>1.17</v>
       </c>
       <c r="Y50" t="s">
-        <v>61</v>
+        <v>624</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>625</v>
       </c>
       <c r="AA50" t="s">
-        <v>602</v>
+        <v>626</v>
       </c>
       <c r="AB50" t="s">
         <v>39</v>
@@ -6695,13 +6749,13 @@
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>589</v>
+        <v>627</v>
       </c>
       <c r="C51" t="s">
-        <v>590</v>
+        <v>628</v>
       </c>
       <c r="D51" t="s">
-        <v>591</v>
+        <v>629</v>
       </c>
       <c r="E51" t="s">
         <v>33</v>
@@ -6719,13 +6773,13 @@
         <v>54</v>
       </c>
       <c r="K51" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L51" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M51" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N51" t="s">
         <v>33</v>
@@ -6737,16 +6791,16 @@
         <v>38</v>
       </c>
       <c r="Q51">
-        <v>64.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R51">
-        <v>10.83</v>
+        <v>2</v>
       </c>
       <c r="Y51" t="s">
-        <v>592</v>
+        <v>630</v>
       </c>
       <c r="AA51" t="s">
-        <v>593</v>
+        <v>631</v>
       </c>
       <c r="AB51" t="s">
         <v>39</v>
@@ -6760,13 +6814,13 @@
     </row>
     <row r="52" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>594</v>
+        <v>649</v>
       </c>
       <c r="C52" t="s">
-        <v>595</v>
+        <v>650</v>
       </c>
       <c r="D52" t="s">
-        <v>596</v>
+        <v>651</v>
       </c>
       <c r="E52" t="s">
         <v>33</v>
@@ -6784,13 +6838,13 @@
         <v>54</v>
       </c>
       <c r="K52" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L52" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M52" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N52" t="s">
         <v>33</v>
@@ -6802,16 +6856,19 @@
         <v>38</v>
       </c>
       <c r="Q52">
-        <v>64.989999999999995</v>
+        <v>39.99</v>
       </c>
       <c r="R52">
-        <v>10.83</v>
+        <v>6.67</v>
       </c>
       <c r="Y52" t="s">
-        <v>597</v>
+        <v>652</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>653</v>
       </c>
       <c r="AA52" t="s">
-        <v>598</v>
+        <v>654</v>
       </c>
       <c r="AB52" t="s">
         <v>39</v>
@@ -6825,13 +6882,13 @@
     </row>
     <row r="53" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>603</v>
+        <v>655</v>
       </c>
       <c r="C53" t="s">
-        <v>604</v>
+        <v>656</v>
       </c>
       <c r="D53" t="s">
-        <v>605</v>
+        <v>657</v>
       </c>
       <c r="E53" t="s">
         <v>33</v>
@@ -6849,13 +6906,13 @@
         <v>54</v>
       </c>
       <c r="K53" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L53" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M53" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="N53" t="s">
         <v>33</v>
@@ -6867,19 +6924,16 @@
         <v>38</v>
       </c>
       <c r="Q53">
-        <v>64.989999999999995</v>
+        <v>14.99</v>
       </c>
       <c r="R53">
-        <v>10.83</v>
+        <v>2.5</v>
       </c>
       <c r="Y53" t="s">
-        <v>606</v>
-      </c>
-      <c r="Z53" t="s">
-        <v>607</v>
+        <v>658</v>
       </c>
       <c r="AA53" t="s">
-        <v>608</v>
+        <v>659</v>
       </c>
       <c r="AB53" t="s">
         <v>39</v>
@@ -6893,13 +6947,13 @@
     </row>
     <row r="54" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="C54" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="D54" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E54" t="s">
         <v>33</v>
@@ -6941,13 +6995,10 @@
         <v>10.83</v>
       </c>
       <c r="Y54" t="s">
-        <v>580</v>
-      </c>
-      <c r="Z54" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="AA54" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="AB54" t="s">
         <v>39</v>
@@ -6961,16 +7012,16 @@
     </row>
     <row r="55" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>575</v>
+        <v>599</v>
       </c>
       <c r="C55" t="s">
-        <v>576</v>
+        <v>600</v>
       </c>
       <c r="D55" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="E55" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F55" t="s">
         <v>34</v>
@@ -6985,22 +7036,34 @@
         <v>54</v>
       </c>
       <c r="K55" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L55" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M55" t="s">
-        <v>42</v>
+        <v>83</v>
+      </c>
+      <c r="N55" t="s">
+        <v>33</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P55" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q55">
+        <v>14.99</v>
+      </c>
+      <c r="R55">
+        <v>2.5</v>
       </c>
       <c r="Y55" t="s">
-        <v>573</v>
+        <v>61</v>
       </c>
       <c r="AA55" t="s">
-        <v>574</v>
+        <v>602</v>
       </c>
       <c r="AB55" t="s">
         <v>39</v>
@@ -7014,13 +7077,13 @@
     </row>
     <row r="56" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>518</v>
+        <v>589</v>
       </c>
       <c r="C56" t="s">
-        <v>519</v>
+        <v>590</v>
       </c>
       <c r="D56" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="E56" t="s">
         <v>33</v>
@@ -7038,13 +7101,13 @@
         <v>54</v>
       </c>
       <c r="K56" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L56" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M56" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N56" t="s">
         <v>33</v>
@@ -7056,22 +7119,16 @@
         <v>38</v>
       </c>
       <c r="Q56">
-        <v>37.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R56">
-        <v>6.33</v>
-      </c>
-      <c r="S56">
-        <v>6.99</v>
-      </c>
-      <c r="T56">
-        <v>1.17</v>
+        <v>10.83</v>
       </c>
       <c r="Y56" t="s">
-        <v>46</v>
+        <v>592</v>
       </c>
       <c r="AA56" t="s">
-        <v>520</v>
+        <v>593</v>
       </c>
       <c r="AB56" t="s">
         <v>39</v>
@@ -7085,13 +7142,13 @@
     </row>
     <row r="57" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>584</v>
+        <v>594</v>
       </c>
       <c r="C57" t="s">
-        <v>585</v>
+        <v>595</v>
       </c>
       <c r="D57" t="s">
-        <v>586</v>
+        <v>596</v>
       </c>
       <c r="E57" t="s">
         <v>33</v>
@@ -7133,10 +7190,10 @@
         <v>10.83</v>
       </c>
       <c r="Y57" t="s">
-        <v>587</v>
+        <v>597</v>
       </c>
       <c r="AA57" t="s">
-        <v>588</v>
+        <v>598</v>
       </c>
       <c r="AB57" t="s">
         <v>39</v>
@@ -7150,13 +7207,13 @@
     </row>
     <row r="58" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>457</v>
+        <v>603</v>
       </c>
       <c r="C58" t="s">
-        <v>458</v>
+        <v>604</v>
       </c>
       <c r="D58" t="s">
-        <v>459</v>
+        <v>605</v>
       </c>
       <c r="E58" t="s">
         <v>33</v>
@@ -7198,13 +7255,13 @@
         <v>10.83</v>
       </c>
       <c r="Y58" t="s">
-        <v>460</v>
+        <v>606</v>
       </c>
       <c r="Z58" t="s">
-        <v>279</v>
+        <v>607</v>
       </c>
       <c r="AA58" t="s">
-        <v>461</v>
+        <v>608</v>
       </c>
       <c r="AB58" t="s">
         <v>39</v>
@@ -7218,13 +7275,13 @@
     </row>
     <row r="59" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>462</v>
+        <v>578</v>
       </c>
       <c r="C59" t="s">
-        <v>463</v>
+        <v>579</v>
       </c>
       <c r="D59" t="s">
-        <v>459</v>
+        <v>661</v>
       </c>
       <c r="E59" t="s">
         <v>33</v>
@@ -7266,10 +7323,13 @@
         <v>10.83</v>
       </c>
       <c r="Y59" t="s">
-        <v>56</v>
+        <v>580</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>581</v>
       </c>
       <c r="AA59" t="s">
-        <v>464</v>
+        <v>582</v>
       </c>
       <c r="AB59" t="s">
         <v>39</v>
@@ -7283,16 +7343,16 @@
     </row>
     <row r="60" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>465</v>
+        <v>575</v>
       </c>
       <c r="C60" t="s">
-        <v>466</v>
+        <v>576</v>
       </c>
       <c r="D60" t="s">
-        <v>467</v>
+        <v>577</v>
       </c>
       <c r="E60" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F60" t="s">
         <v>34</v>
@@ -7307,34 +7367,22 @@
         <v>54</v>
       </c>
       <c r="K60" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L60" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M60" t="s">
-        <v>50</v>
-      </c>
-      <c r="N60" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O60">
-        <v>2</v>
-      </c>
-      <c r="P60" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q60">
-        <v>79.98</v>
-      </c>
-      <c r="R60">
-        <v>13.34</v>
+        <v>0</v>
       </c>
       <c r="Y60" t="s">
-        <v>468</v>
+        <v>573</v>
       </c>
       <c r="AA60" t="s">
-        <v>469</v>
+        <v>574</v>
       </c>
       <c r="AB60" t="s">
         <v>39</v>
@@ -7348,13 +7396,13 @@
     </row>
     <row r="61" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>470</v>
+        <v>518</v>
       </c>
       <c r="C61" t="s">
-        <v>471</v>
+        <v>519</v>
       </c>
       <c r="D61" t="s">
-        <v>472</v>
+        <v>583</v>
       </c>
       <c r="E61" t="s">
         <v>33</v>
@@ -7395,11 +7443,17 @@
       <c r="R61">
         <v>6.33</v>
       </c>
+      <c r="S61">
+        <v>6.99</v>
+      </c>
+      <c r="T61">
+        <v>1.17</v>
+      </c>
       <c r="Y61" t="s">
-        <v>473</v>
+        <v>46</v>
       </c>
       <c r="AA61" t="s">
-        <v>474</v>
+        <v>520</v>
       </c>
       <c r="AB61" t="s">
         <v>39</v>
@@ -7413,16 +7467,16 @@
     </row>
     <row r="62" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>475</v>
+        <v>584</v>
       </c>
       <c r="C62" t="s">
-        <v>476</v>
+        <v>585</v>
       </c>
       <c r="D62" t="s">
-        <v>477</v>
+        <v>586</v>
       </c>
       <c r="E62" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F62" t="s">
         <v>34</v>
@@ -7445,17 +7499,26 @@
       <c r="M62" t="s">
         <v>42</v>
       </c>
+      <c r="N62" t="s">
+        <v>33</v>
+      </c>
       <c r="O62">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P62" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q62">
+        <v>64.989999999999995</v>
+      </c>
+      <c r="R62">
+        <v>10.83</v>
       </c>
       <c r="Y62" t="s">
-        <v>478</v>
-      </c>
-      <c r="Z62" t="s">
-        <v>279</v>
+        <v>587</v>
       </c>
       <c r="AA62" t="s">
-        <v>479</v>
+        <v>588</v>
       </c>
       <c r="AB62" t="s">
         <v>39</v>
@@ -7469,13 +7532,13 @@
     </row>
     <row r="63" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>480</v>
+        <v>457</v>
       </c>
       <c r="C63" t="s">
-        <v>481</v>
+        <v>458</v>
       </c>
       <c r="D63" t="s">
-        <v>482</v>
+        <v>459</v>
       </c>
       <c r="E63" t="s">
         <v>33</v>
@@ -7493,13 +7556,13 @@
         <v>54</v>
       </c>
       <c r="K63" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L63" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M63" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N63" t="s">
         <v>33</v>
@@ -7511,16 +7574,19 @@
         <v>38</v>
       </c>
       <c r="Q63">
-        <v>11.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R63">
-        <v>2</v>
+        <v>10.83</v>
       </c>
       <c r="Y63" t="s">
-        <v>61</v>
+        <v>460</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>279</v>
       </c>
       <c r="AA63" t="s">
-        <v>483</v>
+        <v>461</v>
       </c>
       <c r="AB63" t="s">
         <v>39</v>
@@ -7534,13 +7600,13 @@
     </row>
     <row r="64" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>484</v>
+        <v>462</v>
       </c>
       <c r="C64" t="s">
-        <v>485</v>
+        <v>463</v>
       </c>
       <c r="D64" t="s">
-        <v>486</v>
+        <v>459</v>
       </c>
       <c r="E64" t="s">
         <v>33</v>
@@ -7582,10 +7648,10 @@
         <v>10.83</v>
       </c>
       <c r="Y64" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="AA64" t="s">
-        <v>487</v>
+        <v>464</v>
       </c>
       <c r="AB64" t="s">
         <v>39</v>
@@ -7599,13 +7665,13 @@
     </row>
     <row r="65" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>488</v>
+        <v>465</v>
       </c>
       <c r="C65" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="D65" t="s">
-        <v>490</v>
+        <v>467</v>
       </c>
       <c r="E65" t="s">
         <v>33</v>
@@ -7647,13 +7713,10 @@
         <v>13.34</v>
       </c>
       <c r="Y65" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z65" t="s">
-        <v>491</v>
+        <v>468</v>
       </c>
       <c r="AA65" t="s">
-        <v>492</v>
+        <v>469</v>
       </c>
       <c r="AB65" t="s">
         <v>39</v>
@@ -7667,13 +7730,13 @@
     </row>
     <row r="66" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>497</v>
+        <v>470</v>
       </c>
       <c r="C66" t="s">
-        <v>498</v>
+        <v>471</v>
       </c>
       <c r="D66" t="s">
-        <v>499</v>
+        <v>472</v>
       </c>
       <c r="E66" t="s">
         <v>33</v>
@@ -7691,13 +7754,13 @@
         <v>54</v>
       </c>
       <c r="K66" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L66" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M66" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N66" t="s">
         <v>33</v>
@@ -7709,19 +7772,16 @@
         <v>38</v>
       </c>
       <c r="Q66">
-        <v>59.99</v>
+        <v>37.99</v>
       </c>
       <c r="R66">
-        <v>10</v>
+        <v>6.33</v>
       </c>
       <c r="Y66" t="s">
-        <v>500</v>
-      </c>
-      <c r="Z66" t="s">
-        <v>501</v>
+        <v>473</v>
       </c>
       <c r="AA66" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
       <c r="AB66" t="s">
         <v>39</v>
@@ -7735,16 +7795,16 @@
     </row>
     <row r="67" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>503</v>
+        <v>475</v>
       </c>
       <c r="C67" t="s">
-        <v>504</v>
+        <v>476</v>
       </c>
       <c r="D67" t="s">
-        <v>499</v>
+        <v>477</v>
       </c>
       <c r="E67" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F67" t="s">
         <v>34</v>
@@ -7767,29 +7827,17 @@
       <c r="M67" t="s">
         <v>42</v>
       </c>
-      <c r="N67" t="s">
-        <v>33</v>
-      </c>
       <c r="O67">
-        <v>1</v>
-      </c>
-      <c r="P67" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q67">
-        <v>59.99</v>
-      </c>
-      <c r="R67">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y67" t="s">
-        <v>505</v>
+        <v>478</v>
       </c>
       <c r="Z67" t="s">
-        <v>93</v>
+        <v>279</v>
       </c>
       <c r="AA67" t="s">
-        <v>506</v>
+        <v>479</v>
       </c>
       <c r="AB67" t="s">
         <v>39</v>
@@ -7803,13 +7851,13 @@
     </row>
     <row r="68" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>507</v>
+        <v>480</v>
       </c>
       <c r="C68" t="s">
-        <v>508</v>
+        <v>481</v>
       </c>
       <c r="D68" t="s">
-        <v>509</v>
+        <v>482</v>
       </c>
       <c r="E68" t="s">
         <v>33</v>
@@ -7827,13 +7875,13 @@
         <v>54</v>
       </c>
       <c r="K68" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L68" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M68" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N68" t="s">
         <v>33</v>
@@ -7845,16 +7893,16 @@
         <v>38</v>
       </c>
       <c r="Q68">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R68">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y68" t="s">
-        <v>510</v>
+        <v>61</v>
       </c>
       <c r="AA68" t="s">
-        <v>511</v>
+        <v>483</v>
       </c>
       <c r="AB68" t="s">
         <v>39</v>
@@ -7868,13 +7916,13 @@
     </row>
     <row r="69" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>512</v>
+        <v>484</v>
       </c>
       <c r="C69" t="s">
-        <v>513</v>
+        <v>485</v>
       </c>
       <c r="D69" t="s">
-        <v>514</v>
+        <v>486</v>
       </c>
       <c r="E69" t="s">
         <v>33</v>
@@ -7910,19 +7958,16 @@
         <v>38</v>
       </c>
       <c r="Q69">
-        <v>59.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R69">
-        <v>10</v>
+        <v>10.83</v>
       </c>
       <c r="Y69" t="s">
-        <v>515</v>
-      </c>
-      <c r="Z69" t="s">
-        <v>516</v>
+        <v>67</v>
       </c>
       <c r="AA69" t="s">
-        <v>517</v>
+        <v>487</v>
       </c>
       <c r="AB69" t="s">
         <v>39</v>
@@ -7936,13 +7981,13 @@
     </row>
     <row r="70" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>521</v>
+        <v>488</v>
       </c>
       <c r="C70" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="D70" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="E70" t="s">
         <v>33</v>
@@ -7960,34 +8005,37 @@
         <v>54</v>
       </c>
       <c r="K70" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="L70" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="M70" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="N70" t="s">
         <v>33</v>
       </c>
       <c r="O70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P70" t="s">
         <v>38</v>
       </c>
       <c r="Q70">
-        <v>14.99</v>
+        <v>79.98</v>
       </c>
       <c r="R70">
-        <v>2.5</v>
+        <v>13.34</v>
       </c>
       <c r="Y70" t="s">
-        <v>58</v>
+        <v>63</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>491</v>
       </c>
       <c r="AA70" t="s">
-        <v>524</v>
+        <v>492</v>
       </c>
       <c r="AB70" t="s">
         <v>39</v>
@@ -8001,13 +8049,13 @@
     </row>
     <row r="71" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>525</v>
+        <v>497</v>
       </c>
       <c r="C71" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="D71" t="s">
-        <v>527</v>
+        <v>499</v>
       </c>
       <c r="E71" t="s">
         <v>33</v>
@@ -8049,10 +8097,13 @@
         <v>10</v>
       </c>
       <c r="Y71" t="s">
-        <v>90</v>
+        <v>500</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>501</v>
       </c>
       <c r="AA71" t="s">
-        <v>528</v>
+        <v>502</v>
       </c>
       <c r="AB71" t="s">
         <v>39</v>
@@ -8066,13 +8117,13 @@
     </row>
     <row r="72" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>529</v>
+        <v>503</v>
       </c>
       <c r="C72" t="s">
-        <v>530</v>
+        <v>504</v>
       </c>
       <c r="D72" t="s">
-        <v>527</v>
+        <v>499</v>
       </c>
       <c r="E72" t="s">
         <v>33</v>
@@ -8114,10 +8165,13 @@
         <v>10</v>
       </c>
       <c r="Y72" t="s">
-        <v>531</v>
+        <v>505</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>93</v>
       </c>
       <c r="AA72" t="s">
-        <v>532</v>
+        <v>506</v>
       </c>
       <c r="AB72" t="s">
         <v>39</v>
@@ -8131,13 +8185,13 @@
     </row>
     <row r="73" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>533</v>
+        <v>507</v>
       </c>
       <c r="C73" t="s">
-        <v>534</v>
+        <v>508</v>
       </c>
       <c r="D73" t="s">
-        <v>535</v>
+        <v>509</v>
       </c>
       <c r="E73" t="s">
         <v>33</v>
@@ -8155,13 +8209,13 @@
         <v>54</v>
       </c>
       <c r="K73" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L73" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M73" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N73" t="s">
         <v>33</v>
@@ -8173,19 +8227,16 @@
         <v>38</v>
       </c>
       <c r="Q73">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R73">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y73" t="s">
-        <v>536</v>
-      </c>
-      <c r="Z73" t="s">
-        <v>537</v>
+        <v>510</v>
       </c>
       <c r="AA73" t="s">
-        <v>538</v>
+        <v>511</v>
       </c>
       <c r="AB73" t="s">
         <v>39</v>
@@ -8199,13 +8250,13 @@
     </row>
     <row r="74" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>539</v>
+        <v>512</v>
       </c>
       <c r="C74" t="s">
-        <v>540</v>
+        <v>513</v>
       </c>
       <c r="D74" t="s">
-        <v>541</v>
+        <v>514</v>
       </c>
       <c r="E74" t="s">
         <v>33</v>
@@ -8247,13 +8298,13 @@
         <v>10</v>
       </c>
       <c r="Y74" t="s">
-        <v>71</v>
+        <v>515</v>
       </c>
       <c r="Z74" t="s">
-        <v>542</v>
+        <v>516</v>
       </c>
       <c r="AA74" t="s">
-        <v>543</v>
+        <v>517</v>
       </c>
       <c r="AB74" t="s">
         <v>39</v>
@@ -8267,13 +8318,13 @@
     </row>
     <row r="75" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>544</v>
+        <v>521</v>
       </c>
       <c r="C75" t="s">
-        <v>545</v>
+        <v>522</v>
       </c>
       <c r="D75" t="s">
-        <v>546</v>
+        <v>523</v>
       </c>
       <c r="E75" t="s">
         <v>33</v>
@@ -8291,37 +8342,34 @@
         <v>54</v>
       </c>
       <c r="K75" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="L75" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="M75" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="N75" t="s">
         <v>33</v>
       </c>
       <c r="O75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P75" t="s">
         <v>38</v>
       </c>
       <c r="Q75">
-        <v>76.98</v>
+        <v>14.99</v>
       </c>
       <c r="R75">
-        <v>12.84</v>
+        <v>2.5</v>
       </c>
       <c r="Y75" t="s">
-        <v>547</v>
-      </c>
-      <c r="Z75" t="s">
-        <v>548</v>
+        <v>58</v>
       </c>
       <c r="AA75" t="s">
-        <v>549</v>
+        <v>524</v>
       </c>
       <c r="AB75" t="s">
         <v>39</v>
@@ -8335,13 +8383,13 @@
     </row>
     <row r="76" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>550</v>
+        <v>525</v>
       </c>
       <c r="C76" t="s">
-        <v>551</v>
+        <v>526</v>
       </c>
       <c r="D76" t="s">
-        <v>552</v>
+        <v>527</v>
       </c>
       <c r="E76" t="s">
         <v>33</v>
@@ -8383,10 +8431,10 @@
         <v>10</v>
       </c>
       <c r="Y76" t="s">
-        <v>553</v>
+        <v>90</v>
       </c>
       <c r="AA76" t="s">
-        <v>554</v>
+        <v>528</v>
       </c>
       <c r="AB76" t="s">
         <v>39</v>
@@ -8400,13 +8448,13 @@
     </row>
     <row r="77" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>555</v>
+        <v>529</v>
       </c>
       <c r="C77" t="s">
-        <v>556</v>
+        <v>530</v>
       </c>
       <c r="D77" t="s">
-        <v>557</v>
+        <v>527</v>
       </c>
       <c r="E77" t="s">
         <v>33</v>
@@ -8448,10 +8496,10 @@
         <v>10</v>
       </c>
       <c r="Y77" t="s">
-        <v>558</v>
+        <v>531</v>
       </c>
       <c r="AA77" t="s">
-        <v>559</v>
+        <v>532</v>
       </c>
       <c r="AB77" t="s">
         <v>39</v>
@@ -8465,13 +8513,13 @@
     </row>
     <row r="78" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>418</v>
+        <v>533</v>
       </c>
       <c r="C78" t="s">
-        <v>419</v>
+        <v>534</v>
       </c>
       <c r="D78" t="s">
-        <v>560</v>
+        <v>535</v>
       </c>
       <c r="E78" t="s">
         <v>33</v>
@@ -8489,13 +8537,13 @@
         <v>54</v>
       </c>
       <c r="K78" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L78" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M78" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N78" t="s">
         <v>33</v>
@@ -8507,16 +8555,19 @@
         <v>38</v>
       </c>
       <c r="Q78">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R78">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y78" t="s">
-        <v>420</v>
+        <v>536</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>537</v>
       </c>
       <c r="AA78" t="s">
-        <v>421</v>
+        <v>538</v>
       </c>
       <c r="AB78" t="s">
         <v>39</v>
@@ -8530,13 +8581,13 @@
     </row>
     <row r="79" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>561</v>
+        <v>539</v>
       </c>
       <c r="C79" t="s">
-        <v>562</v>
+        <v>540</v>
       </c>
       <c r="D79" t="s">
-        <v>563</v>
+        <v>541</v>
       </c>
       <c r="E79" t="s">
         <v>33</v>
@@ -8578,13 +8629,13 @@
         <v>10</v>
       </c>
       <c r="Y79" t="s">
-        <v>564</v>
+        <v>71</v>
       </c>
       <c r="Z79" t="s">
-        <v>565</v>
+        <v>542</v>
       </c>
       <c r="AA79" t="s">
-        <v>566</v>
+        <v>543</v>
       </c>
       <c r="AB79" t="s">
         <v>39</v>
@@ -8598,13 +8649,13 @@
     </row>
     <row r="80" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>567</v>
+        <v>544</v>
       </c>
       <c r="C80" t="s">
-        <v>568</v>
+        <v>545</v>
       </c>
       <c r="D80" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="E80" t="s">
         <v>33</v>
@@ -8622,34 +8673,37 @@
         <v>54</v>
       </c>
       <c r="K80" t="s">
-        <v>94</v>
+        <v>43</v>
       </c>
       <c r="L80" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="M80" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="N80" t="s">
         <v>33</v>
       </c>
       <c r="O80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P80" t="s">
         <v>38</v>
       </c>
       <c r="Q80">
-        <v>14.99</v>
+        <v>76.98</v>
       </c>
       <c r="R80">
-        <v>2.5</v>
+        <v>12.84</v>
       </c>
       <c r="Y80" t="s">
-        <v>69</v>
+        <v>547</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>548</v>
       </c>
       <c r="AA80" t="s">
-        <v>570</v>
+        <v>549</v>
       </c>
       <c r="AB80" t="s">
         <v>39</v>
@@ -8663,13 +8717,13 @@
     </row>
     <row r="81" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>413</v>
+        <v>550</v>
       </c>
       <c r="C81" t="s">
-        <v>414</v>
+        <v>551</v>
       </c>
       <c r="D81" t="s">
-        <v>415</v>
+        <v>552</v>
       </c>
       <c r="E81" t="s">
         <v>33</v>
@@ -8711,10 +8765,10 @@
         <v>10</v>
       </c>
       <c r="Y81" t="s">
-        <v>416</v>
+        <v>553</v>
       </c>
       <c r="AA81" t="s">
-        <v>417</v>
+        <v>554</v>
       </c>
       <c r="AB81" t="s">
         <v>39</v>
@@ -8728,13 +8782,13 @@
     </row>
     <row r="82" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="C82" t="s">
-        <v>423</v>
+        <v>556</v>
       </c>
       <c r="D82" t="s">
-        <v>424</v>
+        <v>557</v>
       </c>
       <c r="E82" t="s">
         <v>33</v>
@@ -8752,13 +8806,13 @@
         <v>54</v>
       </c>
       <c r="K82" t="s">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="L82" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="M82" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="N82" t="s">
         <v>33</v>
@@ -8770,16 +8824,16 @@
         <v>38</v>
       </c>
       <c r="Q82">
-        <v>22.99</v>
+        <v>59.99</v>
       </c>
       <c r="R82">
-        <v>3.83</v>
+        <v>10</v>
       </c>
       <c r="Y82" t="s">
-        <v>425</v>
+        <v>558</v>
       </c>
       <c r="AA82" t="s">
-        <v>426</v>
+        <v>559</v>
       </c>
       <c r="AB82" t="s">
         <v>39</v>
@@ -8793,13 +8847,13 @@
     </row>
     <row r="83" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="C83" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="D83" t="s">
-        <v>424</v>
+        <v>560</v>
       </c>
       <c r="E83" t="s">
         <v>33</v>
@@ -8817,13 +8871,13 @@
         <v>54</v>
       </c>
       <c r="K83" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L83" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M83" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N83" t="s">
         <v>33</v>
@@ -8835,19 +8889,16 @@
         <v>38</v>
       </c>
       <c r="Q83">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R83">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y83" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z83" t="s">
-        <v>97</v>
+        <v>420</v>
       </c>
       <c r="AA83" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="AB83" t="s">
         <v>39</v>
@@ -8861,13 +8912,13 @@
     </row>
     <row r="84" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>430</v>
+        <v>561</v>
       </c>
       <c r="C84" t="s">
-        <v>431</v>
+        <v>562</v>
       </c>
       <c r="D84" t="s">
-        <v>432</v>
+        <v>563</v>
       </c>
       <c r="E84" t="s">
         <v>33</v>
@@ -8885,13 +8936,13 @@
         <v>54</v>
       </c>
       <c r="K84" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L84" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M84" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N84" t="s">
         <v>33</v>
@@ -8903,19 +8954,19 @@
         <v>38</v>
       </c>
       <c r="Q84">
-        <v>38.49</v>
+        <v>59.99</v>
       </c>
       <c r="R84">
-        <v>6.42</v>
+        <v>10</v>
       </c>
       <c r="Y84" t="s">
-        <v>59</v>
+        <v>564</v>
       </c>
       <c r="Z84" t="s">
-        <v>433</v>
+        <v>565</v>
       </c>
       <c r="AA84" t="s">
-        <v>434</v>
+        <v>566</v>
       </c>
       <c r="AB84" t="s">
         <v>39</v>
@@ -8929,13 +8980,13 @@
     </row>
     <row r="85" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>435</v>
+        <v>567</v>
       </c>
       <c r="C85" t="s">
-        <v>436</v>
+        <v>568</v>
       </c>
       <c r="D85" t="s">
-        <v>437</v>
+        <v>569</v>
       </c>
       <c r="E85" t="s">
         <v>33</v>
@@ -8953,13 +9004,13 @@
         <v>54</v>
       </c>
       <c r="K85" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L85" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="M85" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="N85" t="s">
         <v>33</v>
@@ -8977,10 +9028,10 @@
         <v>2.5</v>
       </c>
       <c r="Y85" t="s">
-        <v>438</v>
+        <v>69</v>
       </c>
       <c r="AA85" t="s">
-        <v>439</v>
+        <v>570</v>
       </c>
       <c r="AB85" t="s">
         <v>39</v>
@@ -8994,13 +9045,13 @@
     </row>
     <row r="86" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>440</v>
+        <v>413</v>
       </c>
       <c r="C86" t="s">
-        <v>441</v>
+        <v>414</v>
       </c>
       <c r="D86" t="s">
-        <v>442</v>
+        <v>415</v>
       </c>
       <c r="E86" t="s">
         <v>33</v>
@@ -9018,13 +9069,13 @@
         <v>54</v>
       </c>
       <c r="K86" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L86" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M86" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N86" t="s">
         <v>33</v>
@@ -9036,16 +9087,16 @@
         <v>38</v>
       </c>
       <c r="Q86">
-        <v>37.99</v>
+        <v>59.99</v>
       </c>
       <c r="R86">
-        <v>6.33</v>
+        <v>10</v>
       </c>
       <c r="Y86" t="s">
-        <v>443</v>
+        <v>416</v>
       </c>
       <c r="AA86" t="s">
-        <v>444</v>
+        <v>417</v>
       </c>
       <c r="AB86" t="s">
         <v>39</v>
@@ -9059,13 +9110,13 @@
     </row>
     <row r="87" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>445</v>
+        <v>422</v>
       </c>
       <c r="C87" t="s">
-        <v>446</v>
+        <v>423</v>
       </c>
       <c r="D87" t="s">
-        <v>447</v>
+        <v>424</v>
       </c>
       <c r="E87" t="s">
         <v>33</v>
@@ -9083,13 +9134,13 @@
         <v>54</v>
       </c>
       <c r="K87" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="L87" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="M87" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="N87" t="s">
         <v>33</v>
@@ -9101,16 +9152,16 @@
         <v>38</v>
       </c>
       <c r="Q87">
-        <v>59.99</v>
+        <v>22.99</v>
       </c>
       <c r="R87">
-        <v>10</v>
+        <v>3.83</v>
       </c>
       <c r="Y87" t="s">
-        <v>448</v>
+        <v>425</v>
       </c>
       <c r="AA87" t="s">
-        <v>449</v>
+        <v>426</v>
       </c>
       <c r="AB87" t="s">
         <v>39</v>
@@ -9124,16 +9175,16 @@
     </row>
     <row r="88" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>450</v>
+        <v>427</v>
       </c>
       <c r="C88" t="s">
-        <v>451</v>
+        <v>428</v>
       </c>
       <c r="D88" t="s">
-        <v>452</v>
+        <v>424</v>
       </c>
       <c r="E88" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F88" t="s">
         <v>34</v>
@@ -9148,22 +9199,37 @@
         <v>54</v>
       </c>
       <c r="K88" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L88" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M88" t="s">
-        <v>42</v>
+        <v>74</v>
+      </c>
+      <c r="N88" t="s">
+        <v>33</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P88" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q88">
+        <v>11.99</v>
+      </c>
+      <c r="R88">
+        <v>2</v>
       </c>
       <c r="Y88" t="s">
-        <v>453</v>
+        <v>96</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>97</v>
       </c>
       <c r="AA88" t="s">
-        <v>454</v>
+        <v>429</v>
       </c>
       <c r="AB88" t="s">
         <v>39</v>
@@ -9177,13 +9243,13 @@
     </row>
     <row r="89" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>403</v>
+        <v>430</v>
       </c>
       <c r="C89" t="s">
-        <v>404</v>
+        <v>431</v>
       </c>
       <c r="D89" t="s">
-        <v>455</v>
+        <v>432</v>
       </c>
       <c r="E89" t="s">
         <v>33</v>
@@ -9201,13 +9267,13 @@
         <v>54</v>
       </c>
       <c r="K89" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L89" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M89" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N89" t="s">
         <v>33</v>
@@ -9219,22 +9285,19 @@
         <v>38</v>
       </c>
       <c r="Q89">
-        <v>59.99</v>
+        <v>38.49</v>
       </c>
       <c r="R89">
-        <v>10</v>
-      </c>
-      <c r="S89">
-        <v>5.99</v>
-      </c>
-      <c r="T89">
-        <v>1</v>
+        <v>6.42</v>
       </c>
       <c r="Y89" t="s">
-        <v>405</v>
+        <v>59</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>433</v>
       </c>
       <c r="AA89" t="s">
-        <v>406</v>
+        <v>434</v>
       </c>
       <c r="AB89" t="s">
         <v>39</v>
@@ -9248,13 +9311,13 @@
     </row>
     <row r="90" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>407</v>
+        <v>435</v>
       </c>
       <c r="C90" t="s">
-        <v>408</v>
+        <v>436</v>
       </c>
       <c r="D90" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="E90" t="s">
         <v>33</v>
@@ -9272,13 +9335,13 @@
         <v>54</v>
       </c>
       <c r="K90" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="L90" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="M90" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="N90" t="s">
         <v>33</v>
@@ -9290,16 +9353,16 @@
         <v>38</v>
       </c>
       <c r="Q90">
-        <v>22.99</v>
+        <v>14.99</v>
       </c>
       <c r="R90">
-        <v>3.83</v>
+        <v>2.5</v>
       </c>
       <c r="Y90" t="s">
-        <v>409</v>
+        <v>438</v>
       </c>
       <c r="AA90" t="s">
-        <v>410</v>
+        <v>439</v>
       </c>
       <c r="AB90" t="s">
         <v>39</v>
@@ -9313,13 +9376,13 @@
     </row>
     <row r="91" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>399</v>
+        <v>440</v>
       </c>
       <c r="C91" t="s">
-        <v>400</v>
+        <v>441</v>
       </c>
       <c r="D91" t="s">
-        <v>411</v>
+        <v>442</v>
       </c>
       <c r="E91" t="s">
         <v>33</v>
@@ -9337,13 +9400,13 @@
         <v>54</v>
       </c>
       <c r="K91" t="s">
-        <v>340</v>
+        <v>48</v>
       </c>
       <c r="L91" t="s">
-        <v>142</v>
+        <v>49</v>
       </c>
       <c r="M91" t="s">
-        <v>143</v>
+        <v>50</v>
       </c>
       <c r="N91" t="s">
         <v>33</v>
@@ -9355,16 +9418,16 @@
         <v>38</v>
       </c>
       <c r="Q91">
-        <v>44.99</v>
+        <v>37.99</v>
       </c>
       <c r="R91">
-        <v>7.5</v>
+        <v>6.33</v>
       </c>
       <c r="Y91" t="s">
-        <v>401</v>
+        <v>443</v>
       </c>
       <c r="AA91" t="s">
-        <v>402</v>
+        <v>444</v>
       </c>
       <c r="AB91" t="s">
         <v>39</v>
@@ -9378,13 +9441,13 @@
     </row>
     <row r="92" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>394</v>
+        <v>445</v>
       </c>
       <c r="C92" t="s">
-        <v>395</v>
+        <v>446</v>
       </c>
       <c r="D92" t="s">
-        <v>412</v>
+        <v>447</v>
       </c>
       <c r="E92" t="s">
         <v>33</v>
@@ -9402,13 +9465,13 @@
         <v>54</v>
       </c>
       <c r="K92" t="s">
-        <v>340</v>
+        <v>40</v>
       </c>
       <c r="L92" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="M92" t="s">
-        <v>143</v>
+        <v>42</v>
       </c>
       <c r="N92" t="s">
         <v>33</v>
@@ -9420,19 +9483,16 @@
         <v>38</v>
       </c>
       <c r="Q92">
-        <v>44.99</v>
+        <v>59.99</v>
       </c>
       <c r="R92">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="Y92" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z92" t="s">
-        <v>397</v>
+        <v>448</v>
       </c>
       <c r="AA92" t="s">
-        <v>398</v>
+        <v>449</v>
       </c>
       <c r="AB92" t="s">
         <v>39</v>
@@ -9446,16 +9506,16 @@
     </row>
     <row r="93" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>338</v>
+        <v>450</v>
       </c>
       <c r="C93" t="s">
-        <v>339</v>
+        <v>451</v>
       </c>
       <c r="D93" t="s">
-        <v>662</v>
+        <v>452</v>
       </c>
       <c r="E93" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F93" t="s">
         <v>34</v>
@@ -9470,34 +9530,22 @@
         <v>54</v>
       </c>
       <c r="K93" t="s">
-        <v>340</v>
+        <v>40</v>
       </c>
       <c r="L93" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="M93" t="s">
-        <v>143</v>
-      </c>
-      <c r="N93" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O93">
-        <v>1</v>
-      </c>
-      <c r="P93" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q93">
-        <v>44.99</v>
-      </c>
-      <c r="R93">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Y93" t="s">
-        <v>341</v>
+        <v>453</v>
       </c>
       <c r="AA93" t="s">
-        <v>342</v>
+        <v>454</v>
       </c>
       <c r="AB93" t="s">
         <v>39</v>
@@ -9511,13 +9559,13 @@
     </row>
     <row r="94" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>663</v>
+        <v>403</v>
       </c>
       <c r="C94" t="s">
-        <v>664</v>
+        <v>404</v>
       </c>
       <c r="D94" t="s">
-        <v>665</v>
+        <v>455</v>
       </c>
       <c r="E94" t="s">
         <v>33</v>
@@ -9558,20 +9606,23 @@
       <c r="R94">
         <v>10</v>
       </c>
+      <c r="S94">
+        <v>5.99</v>
+      </c>
+      <c r="T94">
+        <v>1</v>
+      </c>
       <c r="Y94" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z94" t="s">
-        <v>666</v>
+        <v>405</v>
       </c>
       <c r="AA94" t="s">
-        <v>667</v>
+        <v>406</v>
       </c>
       <c r="AB94" t="s">
         <v>39</v>
       </c>
       <c r="AD94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG94" t="b">
         <v>0</v>
@@ -9579,13 +9630,13 @@
     </row>
     <row r="95" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>334</v>
+        <v>407</v>
       </c>
       <c r="C95" t="s">
-        <v>335</v>
+        <v>408</v>
       </c>
       <c r="D95" t="s">
-        <v>668</v>
+        <v>456</v>
       </c>
       <c r="E95" t="s">
         <v>33</v>
@@ -9603,13 +9654,13 @@
         <v>54</v>
       </c>
       <c r="K95" t="s">
-        <v>203</v>
+        <v>79</v>
       </c>
       <c r="L95" t="s">
-        <v>204</v>
+        <v>80</v>
       </c>
       <c r="M95" t="s">
-        <v>205</v>
+        <v>81</v>
       </c>
       <c r="N95" t="s">
         <v>33</v>
@@ -9621,16 +9672,16 @@
         <v>38</v>
       </c>
       <c r="Q95">
-        <v>69.989999999999995</v>
+        <v>22.99</v>
       </c>
       <c r="R95">
-        <v>11.67</v>
+        <v>3.83</v>
       </c>
       <c r="Y95" t="s">
-        <v>336</v>
+        <v>409</v>
       </c>
       <c r="AA95" t="s">
-        <v>337</v>
+        <v>410</v>
       </c>
       <c r="AB95" t="s">
         <v>39</v>
@@ -9644,13 +9695,13 @@
     </row>
     <row r="96" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>326</v>
+        <v>399</v>
       </c>
       <c r="C96" t="s">
-        <v>327</v>
+        <v>400</v>
       </c>
       <c r="D96" t="s">
-        <v>669</v>
+        <v>411</v>
       </c>
       <c r="E96" t="s">
         <v>33</v>
@@ -9668,34 +9719,34 @@
         <v>54</v>
       </c>
       <c r="K96" t="s">
-        <v>48</v>
+        <v>340</v>
       </c>
       <c r="L96" t="s">
-        <v>49</v>
+        <v>142</v>
       </c>
       <c r="M96" t="s">
-        <v>50</v>
+        <v>143</v>
       </c>
       <c r="N96" t="s">
         <v>33</v>
       </c>
       <c r="O96">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P96" t="s">
         <v>38</v>
       </c>
       <c r="Q96">
-        <v>75.98</v>
+        <v>44.99</v>
       </c>
       <c r="R96">
-        <v>12.66</v>
+        <v>7.5</v>
       </c>
       <c r="Y96" t="s">
-        <v>91</v>
+        <v>401</v>
       </c>
       <c r="AA96" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="AB96" t="s">
         <v>39</v>
@@ -9709,13 +9760,13 @@
     </row>
     <row r="97" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>343</v>
+        <v>394</v>
       </c>
       <c r="C97" t="s">
-        <v>344</v>
+        <v>395</v>
       </c>
       <c r="D97" t="s">
-        <v>345</v>
+        <v>412</v>
       </c>
       <c r="E97" t="s">
         <v>33</v>
@@ -9733,13 +9784,13 @@
         <v>54</v>
       </c>
       <c r="K97" t="s">
-        <v>40</v>
+        <v>340</v>
       </c>
       <c r="L97" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="M97" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="N97" t="s">
         <v>33</v>
@@ -9751,16 +9802,19 @@
         <v>38</v>
       </c>
       <c r="Q97">
-        <v>59.99</v>
+        <v>44.99</v>
       </c>
       <c r="R97">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="Y97" t="s">
-        <v>346</v>
+        <v>396</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>397</v>
       </c>
       <c r="AA97" t="s">
-        <v>347</v>
+        <v>398</v>
       </c>
       <c r="AB97" t="s">
         <v>39</v>
@@ -9774,13 +9828,13 @@
     </row>
     <row r="98" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>288</v>
+        <v>338</v>
       </c>
       <c r="C98" t="s">
-        <v>289</v>
+        <v>339</v>
       </c>
       <c r="D98" t="s">
-        <v>348</v>
+        <v>662</v>
       </c>
       <c r="E98" t="s">
         <v>33</v>
@@ -9795,37 +9849,37 @@
         <v>36</v>
       </c>
       <c r="J98" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K98" t="s">
-        <v>48</v>
+        <v>340</v>
       </c>
       <c r="L98" t="s">
-        <v>49</v>
+        <v>142</v>
       </c>
       <c r="M98" t="s">
-        <v>50</v>
+        <v>143</v>
       </c>
       <c r="N98" t="s">
         <v>33</v>
       </c>
       <c r="O98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P98" t="s">
         <v>38</v>
       </c>
       <c r="Q98">
-        <v>75.98</v>
+        <v>44.99</v>
       </c>
       <c r="R98">
-        <v>12.66</v>
+        <v>7.5</v>
       </c>
       <c r="Y98" t="s">
-        <v>290</v>
+        <v>341</v>
       </c>
       <c r="AA98" t="s">
-        <v>291</v>
+        <v>342</v>
       </c>
       <c r="AB98" t="s">
         <v>39</v>
@@ -9839,13 +9893,13 @@
     </row>
     <row r="99" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>349</v>
+        <v>663</v>
       </c>
       <c r="C99" t="s">
-        <v>350</v>
+        <v>664</v>
       </c>
       <c r="D99" t="s">
-        <v>351</v>
+        <v>665</v>
       </c>
       <c r="E99" t="s">
         <v>33</v>
@@ -9863,13 +9917,13 @@
         <v>54</v>
       </c>
       <c r="K99" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L99" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M99" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N99" t="s">
         <v>33</v>
@@ -9881,25 +9935,25 @@
         <v>38</v>
       </c>
       <c r="Q99">
-        <v>37.99</v>
+        <v>59.99</v>
       </c>
       <c r="R99">
-        <v>6.33</v>
+        <v>10</v>
       </c>
       <c r="Y99" t="s">
-        <v>352</v>
+        <v>62</v>
       </c>
       <c r="Z99" t="s">
-        <v>353</v>
+        <v>666</v>
       </c>
       <c r="AA99" t="s">
-        <v>354</v>
+        <v>667</v>
       </c>
       <c r="AB99" t="s">
         <v>39</v>
       </c>
       <c r="AD99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG99" t="b">
         <v>0</v>
@@ -9907,13 +9961,13 @@
     </row>
     <row r="100" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>355</v>
+        <v>334</v>
       </c>
       <c r="C100" t="s">
-        <v>356</v>
+        <v>335</v>
       </c>
       <c r="D100" t="s">
-        <v>357</v>
+        <v>668</v>
       </c>
       <c r="E100" t="s">
         <v>33</v>
@@ -9931,13 +9985,13 @@
         <v>54</v>
       </c>
       <c r="K100" t="s">
-        <v>72</v>
+        <v>203</v>
       </c>
       <c r="L100" t="s">
-        <v>73</v>
+        <v>204</v>
       </c>
       <c r="M100" t="s">
-        <v>74</v>
+        <v>205</v>
       </c>
       <c r="N100" t="s">
         <v>33</v>
@@ -9949,16 +10003,16 @@
         <v>38</v>
       </c>
       <c r="Q100">
-        <v>11.99</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="R100">
-        <v>2</v>
+        <v>11.67</v>
       </c>
       <c r="Y100" t="s">
-        <v>58</v>
+        <v>336</v>
       </c>
       <c r="AA100" t="s">
-        <v>358</v>
+        <v>337</v>
       </c>
       <c r="AB100" t="s">
         <v>39</v>
@@ -9972,13 +10026,13 @@
     </row>
     <row r="101" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>359</v>
+        <v>326</v>
       </c>
       <c r="C101" t="s">
-        <v>360</v>
+        <v>327</v>
       </c>
       <c r="D101" t="s">
-        <v>361</v>
+        <v>669</v>
       </c>
       <c r="E101" t="s">
         <v>33</v>
@@ -10020,13 +10074,10 @@
         <v>12.66</v>
       </c>
       <c r="Y101" t="s">
-        <v>101</v>
-      </c>
-      <c r="Z101" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="AA101" t="s">
-        <v>362</v>
+        <v>328</v>
       </c>
       <c r="AB101" t="s">
         <v>39</v>
@@ -10040,13 +10091,13 @@
     </row>
     <row r="102" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>363</v>
+        <v>343</v>
       </c>
       <c r="C102" t="s">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>345</v>
       </c>
       <c r="E102" t="s">
         <v>33</v>
@@ -10064,13 +10115,13 @@
         <v>54</v>
       </c>
       <c r="K102" t="s">
-        <v>260</v>
+        <v>40</v>
       </c>
       <c r="L102" t="s">
-        <v>261</v>
+        <v>41</v>
       </c>
       <c r="M102" t="s">
-        <v>262</v>
+        <v>42</v>
       </c>
       <c r="N102" t="s">
         <v>33</v>
@@ -10082,16 +10133,16 @@
         <v>38</v>
       </c>
       <c r="Q102">
-        <v>24.49</v>
+        <v>59.99</v>
       </c>
       <c r="R102">
-        <v>4.08</v>
+        <v>10</v>
       </c>
       <c r="Y102" t="s">
-        <v>366</v>
+        <v>346</v>
       </c>
       <c r="AA102" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="AB102" t="s">
         <v>39</v>
@@ -10105,13 +10156,13 @@
     </row>
     <row r="103" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>265</v>
+        <v>288</v>
       </c>
       <c r="C103" t="s">
-        <v>266</v>
+        <v>289</v>
       </c>
       <c r="D103" t="s">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="E103" t="s">
         <v>33</v>
@@ -10126,7 +10177,7 @@
         <v>36</v>
       </c>
       <c r="J103" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K103" t="s">
         <v>48</v>
@@ -10141,22 +10192,22 @@
         <v>33</v>
       </c>
       <c r="O103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P103" t="s">
         <v>38</v>
       </c>
       <c r="Q103">
-        <v>37.99</v>
+        <v>75.98</v>
       </c>
       <c r="R103">
-        <v>6.33</v>
+        <v>12.66</v>
       </c>
       <c r="Y103" t="s">
-        <v>267</v>
+        <v>290</v>
       </c>
       <c r="AA103" t="s">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="AB103" t="s">
         <v>39</v>
@@ -10170,13 +10221,13 @@
     </row>
     <row r="104" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>369</v>
+        <v>349</v>
       </c>
       <c r="C104" t="s">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="D104" t="s">
-        <v>371</v>
+        <v>351</v>
       </c>
       <c r="E104" t="s">
         <v>33</v>
@@ -10194,13 +10245,13 @@
         <v>54</v>
       </c>
       <c r="K104" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L104" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M104" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N104" t="s">
         <v>33</v>
@@ -10212,22 +10263,19 @@
         <v>38</v>
       </c>
       <c r="Q104">
-        <v>11.99</v>
+        <v>37.99</v>
       </c>
       <c r="R104">
-        <v>2</v>
-      </c>
-      <c r="S104">
-        <v>5.99</v>
-      </c>
-      <c r="T104">
-        <v>1</v>
+        <v>6.33</v>
       </c>
       <c r="Y104" t="s">
-        <v>84</v>
+        <v>352</v>
+      </c>
+      <c r="Z104" t="s">
+        <v>353</v>
       </c>
       <c r="AA104" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="AB104" t="s">
         <v>39</v>
@@ -10241,13 +10289,13 @@
     </row>
     <row r="105" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="C105" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="D105" t="s">
-        <v>375</v>
+        <v>357</v>
       </c>
       <c r="E105" t="s">
         <v>33</v>
@@ -10265,13 +10313,13 @@
         <v>54</v>
       </c>
       <c r="K105" t="s">
-        <v>260</v>
+        <v>72</v>
       </c>
       <c r="L105" t="s">
-        <v>261</v>
+        <v>73</v>
       </c>
       <c r="M105" t="s">
-        <v>262</v>
+        <v>74</v>
       </c>
       <c r="N105" t="s">
         <v>33</v>
@@ -10283,16 +10331,16 @@
         <v>38</v>
       </c>
       <c r="Q105">
-        <v>24.49</v>
+        <v>11.99</v>
       </c>
       <c r="R105">
-        <v>4.08</v>
+        <v>2</v>
       </c>
       <c r="Y105" t="s">
-        <v>376</v>
+        <v>58</v>
       </c>
       <c r="AA105" t="s">
-        <v>377</v>
+        <v>358</v>
       </c>
       <c r="AB105" t="s">
         <v>39</v>
@@ -10306,13 +10354,13 @@
     </row>
     <row r="106" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>378</v>
+        <v>359</v>
       </c>
       <c r="C106" t="s">
-        <v>379</v>
+        <v>360</v>
       </c>
       <c r="D106" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="E106" t="s">
         <v>33</v>
@@ -10330,34 +10378,37 @@
         <v>54</v>
       </c>
       <c r="K106" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L106" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M106" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N106" t="s">
         <v>33</v>
       </c>
       <c r="O106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P106" t="s">
         <v>38</v>
       </c>
       <c r="Q106">
-        <v>59.99</v>
+        <v>75.98</v>
       </c>
       <c r="R106">
-        <v>10</v>
+        <v>12.66</v>
       </c>
       <c r="Y106" t="s">
-        <v>57</v>
+        <v>101</v>
+      </c>
+      <c r="Z106" t="s">
+        <v>59</v>
       </c>
       <c r="AA106" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="AB106" t="s">
         <v>39</v>
@@ -10371,13 +10422,13 @@
     </row>
     <row r="107" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="C107" t="s">
-        <v>383</v>
+        <v>364</v>
       </c>
       <c r="D107" t="s">
-        <v>384</v>
+        <v>365</v>
       </c>
       <c r="E107" t="s">
         <v>33</v>
@@ -10395,13 +10446,13 @@
         <v>54</v>
       </c>
       <c r="K107" t="s">
-        <v>72</v>
+        <v>260</v>
       </c>
       <c r="L107" t="s">
-        <v>73</v>
+        <v>261</v>
       </c>
       <c r="M107" t="s">
-        <v>74</v>
+        <v>262</v>
       </c>
       <c r="N107" t="s">
         <v>33</v>
@@ -10413,16 +10464,16 @@
         <v>38</v>
       </c>
       <c r="Q107">
-        <v>11.99</v>
+        <v>24.49</v>
       </c>
       <c r="R107">
-        <v>2</v>
+        <v>4.08</v>
       </c>
       <c r="Y107" t="s">
-        <v>385</v>
+        <v>366</v>
       </c>
       <c r="AA107" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="AB107" t="s">
         <v>39</v>
@@ -10436,16 +10487,16 @@
     </row>
     <row r="108" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>387</v>
+        <v>265</v>
       </c>
       <c r="C108" t="s">
-        <v>388</v>
+        <v>266</v>
       </c>
       <c r="D108" t="s">
-        <v>389</v>
+        <v>368</v>
       </c>
       <c r="E108" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F108" t="s">
         <v>34</v>
@@ -10460,25 +10511,34 @@
         <v>54</v>
       </c>
       <c r="K108" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="L108" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M108" t="s">
-        <v>45</v>
+        <v>50</v>
+      </c>
+      <c r="N108" t="s">
+        <v>33</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P108" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q108">
+        <v>37.99</v>
+      </c>
+      <c r="R108">
+        <v>6.33</v>
       </c>
       <c r="Y108" t="s">
-        <v>390</v>
-      </c>
-      <c r="Z108" t="s">
-        <v>391</v>
+        <v>267</v>
       </c>
       <c r="AA108" t="s">
-        <v>392</v>
+        <v>268</v>
       </c>
       <c r="AB108" t="s">
         <v>39</v>
@@ -10492,13 +10552,13 @@
     </row>
     <row r="109" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>323</v>
+        <v>369</v>
       </c>
       <c r="C109" t="s">
-        <v>324</v>
+        <v>370</v>
       </c>
       <c r="D109" t="s">
-        <v>393</v>
+        <v>371</v>
       </c>
       <c r="E109" t="s">
         <v>33</v>
@@ -10516,13 +10576,13 @@
         <v>54</v>
       </c>
       <c r="K109" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="L109" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="M109" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="N109" t="s">
         <v>33</v>
@@ -10534,16 +10594,22 @@
         <v>38</v>
       </c>
       <c r="Q109">
-        <v>14.99</v>
+        <v>11.99</v>
       </c>
       <c r="R109">
-        <v>2.5</v>
+        <v>2</v>
+      </c>
+      <c r="S109">
+        <v>5.99</v>
+      </c>
+      <c r="T109">
+        <v>1</v>
       </c>
       <c r="Y109" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="AA109" t="s">
-        <v>325</v>
+        <v>372</v>
       </c>
       <c r="AB109" t="s">
         <v>39</v>
@@ -10557,13 +10623,13 @@
     </row>
     <row r="110" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>318</v>
+        <v>373</v>
       </c>
       <c r="C110" t="s">
-        <v>319</v>
+        <v>374</v>
       </c>
       <c r="D110" t="s">
-        <v>320</v>
+        <v>375</v>
       </c>
       <c r="E110" t="s">
         <v>33</v>
@@ -10581,13 +10647,13 @@
         <v>54</v>
       </c>
       <c r="K110" t="s">
-        <v>72</v>
+        <v>260</v>
       </c>
       <c r="L110" t="s">
-        <v>73</v>
+        <v>261</v>
       </c>
       <c r="M110" t="s">
-        <v>74</v>
+        <v>262</v>
       </c>
       <c r="N110" t="s">
         <v>33</v>
@@ -10599,19 +10665,16 @@
         <v>38</v>
       </c>
       <c r="Q110">
-        <v>11.99</v>
+        <v>24.49</v>
       </c>
       <c r="R110">
-        <v>2</v>
+        <v>4.08</v>
       </c>
       <c r="Y110" t="s">
-        <v>321</v>
-      </c>
-      <c r="Z110" t="s">
-        <v>65</v>
+        <v>376</v>
       </c>
       <c r="AA110" t="s">
-        <v>322</v>
+        <v>377</v>
       </c>
       <c r="AB110" t="s">
         <v>39</v>
@@ -10625,13 +10688,13 @@
     </row>
     <row r="111" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>329</v>
+        <v>378</v>
       </c>
       <c r="C111" t="s">
-        <v>330</v>
+        <v>379</v>
       </c>
       <c r="D111" t="s">
-        <v>331</v>
+        <v>380</v>
       </c>
       <c r="E111" t="s">
         <v>33</v>
@@ -10649,13 +10712,13 @@
         <v>54</v>
       </c>
       <c r="K111" t="s">
-        <v>260</v>
+        <v>40</v>
       </c>
       <c r="L111" t="s">
-        <v>261</v>
+        <v>41</v>
       </c>
       <c r="M111" t="s">
-        <v>262</v>
+        <v>42</v>
       </c>
       <c r="N111" t="s">
         <v>33</v>
@@ -10667,16 +10730,16 @@
         <v>38</v>
       </c>
       <c r="Q111">
-        <v>24.49</v>
+        <v>59.99</v>
       </c>
       <c r="R111">
-        <v>4.08</v>
+        <v>10</v>
       </c>
       <c r="Y111" t="s">
-        <v>332</v>
+        <v>57</v>
       </c>
       <c r="AA111" t="s">
-        <v>333</v>
+        <v>381</v>
       </c>
       <c r="AB111" t="s">
         <v>39</v>
@@ -10690,13 +10753,13 @@
     </row>
     <row r="112" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>670</v>
+        <v>382</v>
       </c>
       <c r="C112" t="s">
-        <v>671</v>
+        <v>383</v>
       </c>
       <c r="D112" t="s">
-        <v>672</v>
+        <v>384</v>
       </c>
       <c r="E112" t="s">
         <v>33</v>
@@ -10714,13 +10777,13 @@
         <v>54</v>
       </c>
       <c r="K112" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L112" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M112" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N112" t="s">
         <v>33</v>
@@ -10732,16 +10795,16 @@
         <v>38</v>
       </c>
       <c r="Q112">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R112">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y112" t="s">
-        <v>673</v>
+        <v>385</v>
       </c>
       <c r="AA112" t="s">
-        <v>674</v>
+        <v>386</v>
       </c>
       <c r="AB112" t="s">
         <v>39</v>
@@ -10755,16 +10818,16 @@
     </row>
     <row r="113" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>675</v>
+        <v>387</v>
       </c>
       <c r="C113" t="s">
-        <v>676</v>
+        <v>388</v>
       </c>
       <c r="D113" t="s">
-        <v>677</v>
+        <v>389</v>
       </c>
       <c r="E113" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F113" t="s">
         <v>34</v>
@@ -10779,34 +10842,25 @@
         <v>54</v>
       </c>
       <c r="K113" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="L113" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="M113" t="s">
-        <v>50</v>
-      </c>
-      <c r="N113" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O113">
-        <v>1</v>
-      </c>
-      <c r="P113" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q113">
-        <v>37.99</v>
-      </c>
-      <c r="R113">
-        <v>6.33</v>
+        <v>0</v>
       </c>
       <c r="Y113" t="s">
-        <v>678</v>
+        <v>390</v>
+      </c>
+      <c r="Z113" t="s">
+        <v>391</v>
       </c>
       <c r="AA113" t="s">
-        <v>679</v>
+        <v>392</v>
       </c>
       <c r="AB113" t="s">
         <v>39</v>
@@ -10820,13 +10874,13 @@
     </row>
     <row r="114" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>680</v>
+        <v>323</v>
       </c>
       <c r="C114" t="s">
-        <v>681</v>
+        <v>324</v>
       </c>
       <c r="D114" t="s">
-        <v>682</v>
+        <v>393</v>
       </c>
       <c r="E114" t="s">
         <v>33</v>
@@ -10844,13 +10898,13 @@
         <v>54</v>
       </c>
       <c r="K114" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="L114" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="M114" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="N114" t="s">
         <v>33</v>
@@ -10862,19 +10916,16 @@
         <v>38</v>
       </c>
       <c r="Q114">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="R114">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="Y114" t="s">
-        <v>683</v>
-      </c>
-      <c r="Z114" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="AA114" t="s">
-        <v>684</v>
+        <v>325</v>
       </c>
       <c r="AB114" t="s">
         <v>39</v>
@@ -10888,13 +10939,13 @@
     </row>
     <row r="115" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>685</v>
+        <v>318</v>
       </c>
       <c r="C115" t="s">
-        <v>686</v>
+        <v>319</v>
       </c>
       <c r="D115" t="s">
-        <v>687</v>
+        <v>320</v>
       </c>
       <c r="E115" t="s">
         <v>33</v>
@@ -10912,13 +10963,13 @@
         <v>54</v>
       </c>
       <c r="K115" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L115" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M115" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="N115" t="s">
         <v>33</v>
@@ -10930,16 +10981,19 @@
         <v>38</v>
       </c>
       <c r="Q115">
-        <v>37.99</v>
+        <v>11.99</v>
       </c>
       <c r="R115">
-        <v>6.33</v>
+        <v>2</v>
       </c>
       <c r="Y115" t="s">
-        <v>52</v>
+        <v>321</v>
+      </c>
+      <c r="Z115" t="s">
+        <v>65</v>
       </c>
       <c r="AA115" t="s">
-        <v>688</v>
+        <v>322</v>
       </c>
       <c r="AB115" t="s">
         <v>39</v>
@@ -10953,16 +11007,16 @@
     </row>
     <row r="116" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>689</v>
+        <v>329</v>
       </c>
       <c r="C116" t="s">
-        <v>690</v>
+        <v>330</v>
       </c>
       <c r="D116" t="s">
-        <v>691</v>
+        <v>331</v>
       </c>
       <c r="E116" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F116" t="s">
         <v>34</v>
@@ -10974,28 +11028,37 @@
         <v>36</v>
       </c>
       <c r="J116" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K116" t="s">
-        <v>48</v>
+        <v>260</v>
       </c>
       <c r="L116" t="s">
-        <v>49</v>
+        <v>261</v>
       </c>
       <c r="M116" t="s">
-        <v>50</v>
+        <v>262</v>
+      </c>
+      <c r="N116" t="s">
+        <v>33</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P116" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q116">
+        <v>24.49</v>
+      </c>
+      <c r="R116">
+        <v>4.08</v>
       </c>
       <c r="Y116" t="s">
-        <v>692</v>
-      </c>
-      <c r="Z116" t="s">
-        <v>693</v>
+        <v>332</v>
       </c>
       <c r="AA116" t="s">
-        <v>694</v>
+        <v>333</v>
       </c>
       <c r="AB116" t="s">
         <v>39</v>
@@ -11009,16 +11072,16 @@
     </row>
     <row r="117" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>695</v>
+        <v>670</v>
       </c>
       <c r="C117" t="s">
-        <v>696</v>
+        <v>671</v>
       </c>
       <c r="D117" t="s">
-        <v>697</v>
+        <v>672</v>
       </c>
       <c r="E117" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F117" t="s">
         <v>34</v>
@@ -11030,28 +11093,37 @@
         <v>36</v>
       </c>
       <c r="J117" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K117" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L117" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M117" t="s">
-        <v>50</v>
+        <v>42</v>
+      </c>
+      <c r="N117" t="s">
+        <v>33</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P117" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q117">
+        <v>59.99</v>
+      </c>
+      <c r="R117">
+        <v>10</v>
       </c>
       <c r="Y117" t="s">
-        <v>692</v>
-      </c>
-      <c r="Z117" t="s">
-        <v>693</v>
+        <v>673</v>
       </c>
       <c r="AA117" t="s">
-        <v>694</v>
+        <v>674</v>
       </c>
       <c r="AB117" t="s">
         <v>39</v>
@@ -11065,13 +11137,13 @@
     </row>
     <row r="118" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>300</v>
+        <v>675</v>
       </c>
       <c r="C118" t="s">
-        <v>301</v>
+        <v>676</v>
       </c>
       <c r="D118" t="s">
-        <v>698</v>
+        <v>677</v>
       </c>
       <c r="E118" t="s">
         <v>33</v>
@@ -11089,13 +11161,13 @@
         <v>54</v>
       </c>
       <c r="K118" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="L118" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="M118" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="N118" t="s">
         <v>33</v>
@@ -11107,16 +11179,16 @@
         <v>38</v>
       </c>
       <c r="Q118">
-        <v>14.99</v>
+        <v>37.99</v>
       </c>
       <c r="R118">
-        <v>2.5</v>
+        <v>6.33</v>
       </c>
       <c r="Y118" t="s">
-        <v>58</v>
+        <v>678</v>
       </c>
       <c r="AA118" t="s">
-        <v>302</v>
+        <v>679</v>
       </c>
       <c r="AB118" t="s">
         <v>39</v>
@@ -11130,16 +11202,16 @@
     </row>
     <row r="119" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>699</v>
+        <v>680</v>
       </c>
       <c r="C119" t="s">
-        <v>700</v>
+        <v>681</v>
       </c>
       <c r="D119" t="s">
-        <v>701</v>
+        <v>682</v>
       </c>
       <c r="E119" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F119" t="s">
         <v>34</v>
@@ -11154,25 +11226,37 @@
         <v>54</v>
       </c>
       <c r="K119" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L119" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M119" t="s">
-        <v>50</v>
+        <v>42</v>
+      </c>
+      <c r="N119" t="s">
+        <v>33</v>
       </c>
       <c r="O119">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P119" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q119">
+        <v>59.99</v>
+      </c>
+      <c r="R119">
+        <v>10</v>
       </c>
       <c r="Y119" t="s">
-        <v>692</v>
+        <v>683</v>
       </c>
       <c r="Z119" t="s">
-        <v>693</v>
+        <v>76</v>
       </c>
       <c r="AA119" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="AB119" t="s">
         <v>39</v>
@@ -11186,13 +11270,13 @@
     </row>
     <row r="120" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>303</v>
+        <v>685</v>
       </c>
       <c r="C120" t="s">
-        <v>304</v>
+        <v>686</v>
       </c>
       <c r="D120" t="s">
-        <v>702</v>
+        <v>687</v>
       </c>
       <c r="E120" t="s">
         <v>33</v>
@@ -11210,13 +11294,13 @@
         <v>54</v>
       </c>
       <c r="K120" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L120" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M120" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N120" t="s">
         <v>33</v>
@@ -11228,16 +11312,16 @@
         <v>38</v>
       </c>
       <c r="Q120">
-        <v>59.99</v>
+        <v>37.99</v>
       </c>
       <c r="R120">
-        <v>10</v>
+        <v>6.33</v>
       </c>
       <c r="Y120" t="s">
-        <v>305</v>
+        <v>52</v>
       </c>
       <c r="AA120" t="s">
-        <v>306</v>
+        <v>688</v>
       </c>
       <c r="AB120" t="s">
         <v>39</v>
@@ -11251,16 +11335,16 @@
     </row>
     <row r="121" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>292</v>
+        <v>689</v>
       </c>
       <c r="C121" t="s">
-        <v>293</v>
+        <v>690</v>
       </c>
       <c r="D121" t="s">
-        <v>294</v>
+        <v>691</v>
       </c>
       <c r="E121" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F121" t="s">
         <v>34</v>
@@ -11275,37 +11359,25 @@
         <v>37</v>
       </c>
       <c r="K121" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L121" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M121" t="s">
-        <v>42</v>
-      </c>
-      <c r="N121" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="O121">
-        <v>1</v>
-      </c>
-      <c r="P121" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q121">
-        <v>59.99</v>
-      </c>
-      <c r="R121">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y121" t="s">
-        <v>77</v>
+        <v>692</v>
       </c>
       <c r="Z121" t="s">
-        <v>92</v>
+        <v>693</v>
       </c>
       <c r="AA121" t="s">
-        <v>295</v>
+        <v>694</v>
       </c>
       <c r="AB121" t="s">
         <v>39</v>
@@ -11319,16 +11391,16 @@
     </row>
     <row r="122" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>296</v>
+        <v>695</v>
       </c>
       <c r="C122" t="s">
-        <v>297</v>
+        <v>696</v>
       </c>
       <c r="D122" t="s">
-        <v>298</v>
+        <v>697</v>
       </c>
       <c r="E122" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F122" t="s">
         <v>34</v>
@@ -11343,37 +11415,25 @@
         <v>37</v>
       </c>
       <c r="K122" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L122" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M122" t="s">
-        <v>42</v>
-      </c>
-      <c r="N122" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="O122">
-        <v>1</v>
-      </c>
-      <c r="P122" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q122">
-        <v>59.99</v>
-      </c>
-      <c r="R122">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y122" t="s">
-        <v>62</v>
+        <v>692</v>
       </c>
       <c r="Z122" t="s">
-        <v>51</v>
+        <v>693</v>
       </c>
       <c r="AA122" t="s">
-        <v>299</v>
+        <v>694</v>
       </c>
       <c r="AB122" t="s">
         <v>39</v>
@@ -11387,13 +11447,13 @@
     </row>
     <row r="123" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="C123" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="D123" t="s">
-        <v>309</v>
+        <v>698</v>
       </c>
       <c r="E123" t="s">
         <v>33</v>
@@ -11408,16 +11468,16 @@
         <v>36</v>
       </c>
       <c r="J123" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K123" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="L123" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M123" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="N123" t="s">
         <v>33</v>
@@ -11429,16 +11489,16 @@
         <v>38</v>
       </c>
       <c r="Q123">
-        <v>20.49</v>
+        <v>14.99</v>
       </c>
       <c r="R123">
-        <v>3.42</v>
+        <v>2.5</v>
       </c>
       <c r="Y123" t="s">
-        <v>310</v>
+        <v>58</v>
       </c>
       <c r="AA123" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="AB123" t="s">
         <v>39</v>
@@ -11452,16 +11512,16 @@
     </row>
     <row r="124" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>312</v>
+        <v>699</v>
       </c>
       <c r="C124" t="s">
-        <v>313</v>
+        <v>700</v>
       </c>
       <c r="D124" t="s">
-        <v>314</v>
+        <v>701</v>
       </c>
       <c r="E124" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F124" t="s">
         <v>34</v>
@@ -11473,40 +11533,28 @@
         <v>36</v>
       </c>
       <c r="J124" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K124" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L124" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M124" t="s">
-        <v>42</v>
-      </c>
-      <c r="N124" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="O124">
-        <v>1</v>
-      </c>
-      <c r="P124" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q124">
-        <v>59.99</v>
-      </c>
-      <c r="R124">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y124" t="s">
-        <v>100</v>
+        <v>692</v>
       </c>
       <c r="Z124" t="s">
-        <v>315</v>
+        <v>693</v>
       </c>
       <c r="AA124" t="s">
-        <v>316</v>
+        <v>694</v>
       </c>
       <c r="AB124" t="s">
         <v>39</v>
@@ -11520,13 +11568,13 @@
     </row>
     <row r="125" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>253</v>
+        <v>303</v>
       </c>
       <c r="C125" t="s">
-        <v>254</v>
+        <v>304</v>
       </c>
       <c r="D125" t="s">
-        <v>317</v>
+        <v>702</v>
       </c>
       <c r="E125" t="s">
         <v>33</v>
@@ -11568,13 +11616,10 @@
         <v>10</v>
       </c>
       <c r="Y125" t="s">
-        <v>255</v>
-      </c>
-      <c r="Z125" t="s">
-        <v>102</v>
+        <v>305</v>
       </c>
       <c r="AA125" t="s">
-        <v>256</v>
+        <v>306</v>
       </c>
       <c r="AB125" t="s">
         <v>39</v>
@@ -11588,13 +11633,13 @@
     </row>
     <row r="126" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>257</v>
+        <v>292</v>
       </c>
       <c r="C126" t="s">
-        <v>258</v>
+        <v>293</v>
       </c>
       <c r="D126" t="s">
-        <v>259</v>
+        <v>294</v>
       </c>
       <c r="E126" t="s">
         <v>33</v>
@@ -11609,16 +11654,16 @@
         <v>36</v>
       </c>
       <c r="J126" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K126" t="s">
-        <v>260</v>
+        <v>40</v>
       </c>
       <c r="L126" t="s">
-        <v>261</v>
+        <v>41</v>
       </c>
       <c r="M126" t="s">
-        <v>262</v>
+        <v>42</v>
       </c>
       <c r="N126" t="s">
         <v>33</v>
@@ -11630,19 +11675,19 @@
         <v>38</v>
       </c>
       <c r="Q126">
-        <v>24.49</v>
+        <v>59.99</v>
       </c>
       <c r="R126">
-        <v>4.08</v>
+        <v>10</v>
       </c>
       <c r="Y126" t="s">
-        <v>263</v>
+        <v>77</v>
       </c>
       <c r="Z126" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="AA126" t="s">
-        <v>264</v>
+        <v>295</v>
       </c>
       <c r="AB126" t="s">
         <v>39</v>
@@ -11656,13 +11701,13 @@
     </row>
     <row r="127" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>269</v>
+        <v>296</v>
       </c>
       <c r="C127" t="s">
-        <v>270</v>
+        <v>297</v>
       </c>
       <c r="D127" t="s">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="E127" t="s">
         <v>33</v>
@@ -11677,7 +11722,7 @@
         <v>36</v>
       </c>
       <c r="J127" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K127" t="s">
         <v>40</v>
@@ -11704,10 +11749,13 @@
         <v>10</v>
       </c>
       <c r="Y127" t="s">
-        <v>272</v>
+        <v>62</v>
+      </c>
+      <c r="Z127" t="s">
+        <v>51</v>
       </c>
       <c r="AA127" t="s">
-        <v>273</v>
+        <v>299</v>
       </c>
       <c r="AB127" t="s">
         <v>39</v>
@@ -11721,13 +11769,13 @@
     </row>
     <row r="128" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>149</v>
+        <v>307</v>
       </c>
       <c r="C128" t="s">
-        <v>150</v>
+        <v>308</v>
       </c>
       <c r="D128" t="s">
-        <v>274</v>
+        <v>309</v>
       </c>
       <c r="E128" t="s">
         <v>33</v>
@@ -11742,16 +11790,16 @@
         <v>36</v>
       </c>
       <c r="J128" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K128" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="L128" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="M128" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="N128" t="s">
         <v>33</v>
@@ -11763,16 +11811,16 @@
         <v>38</v>
       </c>
       <c r="Q128">
-        <v>59.99</v>
+        <v>20.49</v>
       </c>
       <c r="R128">
-        <v>10</v>
+        <v>3.42</v>
       </c>
       <c r="Y128" t="s">
-        <v>63</v>
+        <v>310</v>
       </c>
       <c r="AA128" t="s">
-        <v>151</v>
+        <v>311</v>
       </c>
       <c r="AB128" t="s">
         <v>39</v>
@@ -11786,13 +11834,13 @@
     </row>
     <row r="129" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>275</v>
+        <v>312</v>
       </c>
       <c r="C129" t="s">
-        <v>276</v>
+        <v>313</v>
       </c>
       <c r="D129" t="s">
-        <v>277</v>
+        <v>314</v>
       </c>
       <c r="E129" t="s">
         <v>33</v>
@@ -11807,7 +11855,7 @@
         <v>36</v>
       </c>
       <c r="J129" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K129" t="s">
         <v>40</v>
@@ -11822,25 +11870,25 @@
         <v>33</v>
       </c>
       <c r="O129">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P129" t="s">
         <v>38</v>
       </c>
       <c r="Q129">
-        <v>119.98</v>
+        <v>59.99</v>
       </c>
       <c r="R129">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Y129" t="s">
-        <v>278</v>
+        <v>100</v>
       </c>
       <c r="Z129" t="s">
-        <v>279</v>
+        <v>315</v>
       </c>
       <c r="AA129" t="s">
-        <v>280</v>
+        <v>316</v>
       </c>
       <c r="AB129" t="s">
         <v>39</v>
@@ -11854,13 +11902,13 @@
     </row>
     <row r="130" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>281</v>
+        <v>253</v>
       </c>
       <c r="C130" t="s">
-        <v>282</v>
+        <v>254</v>
       </c>
       <c r="D130" t="s">
-        <v>283</v>
+        <v>317</v>
       </c>
       <c r="E130" t="s">
         <v>33</v>
@@ -11875,16 +11923,16 @@
         <v>36</v>
       </c>
       <c r="J130" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K130" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L130" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M130" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N130" t="s">
         <v>33</v>
@@ -11896,16 +11944,19 @@
         <v>38</v>
       </c>
       <c r="Q130">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R130">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y130" t="s">
-        <v>75</v>
+        <v>255</v>
+      </c>
+      <c r="Z130" t="s">
+        <v>102</v>
       </c>
       <c r="AA130" t="s">
-        <v>284</v>
+        <v>256</v>
       </c>
       <c r="AB130" t="s">
         <v>39</v>
@@ -11919,16 +11970,16 @@
     </row>
     <row r="131" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>238</v>
+        <v>257</v>
       </c>
       <c r="C131" t="s">
-        <v>239</v>
+        <v>258</v>
       </c>
       <c r="D131" t="s">
-        <v>285</v>
+        <v>259</v>
       </c>
       <c r="E131" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F131" t="s">
         <v>34</v>
@@ -11943,22 +11994,37 @@
         <v>54</v>
       </c>
       <c r="K131" t="s">
-        <v>40</v>
+        <v>260</v>
       </c>
       <c r="L131" t="s">
-        <v>41</v>
+        <v>261</v>
       </c>
       <c r="M131" t="s">
-        <v>42</v>
+        <v>262</v>
+      </c>
+      <c r="N131" t="s">
+        <v>33</v>
       </c>
       <c r="O131">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P131" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q131">
+        <v>24.49</v>
+      </c>
+      <c r="R131">
+        <v>4.08</v>
       </c>
       <c r="Y131" t="s">
-        <v>240</v>
+        <v>263</v>
+      </c>
+      <c r="Z131" t="s">
+        <v>64</v>
       </c>
       <c r="AA131" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="AB131" t="s">
         <v>39</v>
@@ -11972,13 +12038,13 @@
     </row>
     <row r="132" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>224</v>
+        <v>269</v>
       </c>
       <c r="C132" t="s">
-        <v>225</v>
+        <v>270</v>
       </c>
       <c r="D132" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="E132" t="s">
         <v>33</v>
@@ -12020,10 +12086,10 @@
         <v>10</v>
       </c>
       <c r="Y132" t="s">
-        <v>226</v>
+        <v>272</v>
       </c>
       <c r="AA132" t="s">
-        <v>227</v>
+        <v>273</v>
       </c>
       <c r="AB132" t="s">
         <v>39</v>
@@ -12037,13 +12103,13 @@
     </row>
     <row r="133" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>213</v>
+        <v>149</v>
       </c>
       <c r="C133" t="s">
-        <v>214</v>
+        <v>150</v>
       </c>
       <c r="D133" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="E133" t="s">
         <v>33</v>
@@ -12085,13 +12151,10 @@
         <v>10</v>
       </c>
       <c r="Y133" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z133" t="s">
-        <v>216</v>
+        <v>63</v>
       </c>
       <c r="AA133" t="s">
-        <v>217</v>
+        <v>151</v>
       </c>
       <c r="AB133" t="s">
         <v>39</v>
@@ -12105,13 +12168,13 @@
     </row>
     <row r="134" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>218</v>
+        <v>275</v>
       </c>
       <c r="C134" t="s">
-        <v>219</v>
+        <v>276</v>
       </c>
       <c r="D134" t="s">
-        <v>220</v>
+        <v>277</v>
       </c>
       <c r="E134" t="s">
         <v>33</v>
@@ -12129,37 +12192,37 @@
         <v>54</v>
       </c>
       <c r="K134" t="s">
-        <v>203</v>
+        <v>40</v>
       </c>
       <c r="L134" t="s">
-        <v>204</v>
+        <v>41</v>
       </c>
       <c r="M134" t="s">
-        <v>205</v>
+        <v>42</v>
       </c>
       <c r="N134" t="s">
         <v>33</v>
       </c>
       <c r="O134">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P134" t="s">
         <v>38</v>
       </c>
       <c r="Q134">
-        <v>69.989999999999995</v>
+        <v>119.98</v>
       </c>
       <c r="R134">
-        <v>11.67</v>
+        <v>20</v>
       </c>
       <c r="Y134" t="s">
-        <v>221</v>
+        <v>278</v>
       </c>
       <c r="Z134" t="s">
-        <v>222</v>
+        <v>279</v>
       </c>
       <c r="AA134" t="s">
-        <v>223</v>
+        <v>280</v>
       </c>
       <c r="AB134" t="s">
         <v>39</v>
@@ -12173,13 +12236,13 @@
     </row>
     <row r="135" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>228</v>
+        <v>281</v>
       </c>
       <c r="C135" t="s">
-        <v>229</v>
+        <v>282</v>
       </c>
       <c r="D135" t="s">
-        <v>230</v>
+        <v>283</v>
       </c>
       <c r="E135" t="s">
         <v>33</v>
@@ -12194,16 +12257,16 @@
         <v>36</v>
       </c>
       <c r="J135" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K135" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L135" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M135" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N135" t="s">
         <v>33</v>
@@ -12215,16 +12278,16 @@
         <v>38</v>
       </c>
       <c r="Q135">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R135">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y135" t="s">
-        <v>231</v>
+        <v>75</v>
       </c>
       <c r="AA135" t="s">
-        <v>232</v>
+        <v>284</v>
       </c>
       <c r="AB135" t="s">
         <v>39</v>
@@ -12238,16 +12301,16 @@
     </row>
     <row r="136" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C136" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="D136" t="s">
-        <v>235</v>
+        <v>285</v>
       </c>
       <c r="E136" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F136" t="s">
         <v>34</v>
@@ -12262,34 +12325,22 @@
         <v>54</v>
       </c>
       <c r="K136" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="L136" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="M136" t="s">
-        <v>86</v>
-      </c>
-      <c r="N136" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O136">
-        <v>1</v>
-      </c>
-      <c r="P136" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q136">
-        <v>14.99</v>
-      </c>
-      <c r="R136">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y136" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AA136" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="AB136" t="s">
         <v>39</v>
@@ -12303,16 +12354,16 @@
     </row>
     <row r="137" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="C137" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="D137" t="s">
-        <v>244</v>
+        <v>286</v>
       </c>
       <c r="E137" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F137" t="s">
         <v>34</v>
@@ -12335,14 +12386,26 @@
       <c r="M137" t="s">
         <v>42</v>
       </c>
+      <c r="N137" t="s">
+        <v>33</v>
+      </c>
       <c r="O137">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P137" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q137">
+        <v>59.99</v>
+      </c>
+      <c r="R137">
+        <v>10</v>
       </c>
       <c r="Y137" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="AA137" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="AB137" t="s">
         <v>39</v>
@@ -12356,13 +12419,13 @@
     </row>
     <row r="138" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="C138" t="s">
-        <v>246</v>
+        <v>214</v>
       </c>
       <c r="D138" t="s">
-        <v>247</v>
+        <v>287</v>
       </c>
       <c r="E138" t="s">
         <v>33</v>
@@ -12377,7 +12440,7 @@
         <v>36</v>
       </c>
       <c r="J138" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K138" t="s">
         <v>40</v>
@@ -12404,10 +12467,13 @@
         <v>10</v>
       </c>
       <c r="Y138" t="s">
-        <v>248</v>
+        <v>215</v>
+      </c>
+      <c r="Z138" t="s">
+        <v>216</v>
       </c>
       <c r="AA138" t="s">
-        <v>249</v>
+        <v>217</v>
       </c>
       <c r="AB138" t="s">
         <v>39</v>
@@ -12421,13 +12487,13 @@
     </row>
     <row r="139" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>188</v>
+        <v>218</v>
       </c>
       <c r="C139" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="D139" t="s">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="E139" t="s">
         <v>33</v>
@@ -12442,16 +12508,16 @@
         <v>36</v>
       </c>
       <c r="J139" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K139" t="s">
-        <v>48</v>
+        <v>203</v>
       </c>
       <c r="L139" t="s">
-        <v>49</v>
+        <v>204</v>
       </c>
       <c r="M139" t="s">
-        <v>50</v>
+        <v>205</v>
       </c>
       <c r="N139" t="s">
         <v>33</v>
@@ -12463,16 +12529,19 @@
         <v>38</v>
       </c>
       <c r="Q139">
-        <v>37.99</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="R139">
-        <v>6.33</v>
+        <v>11.67</v>
       </c>
       <c r="Y139" t="s">
-        <v>52</v>
+        <v>221</v>
+      </c>
+      <c r="Z139" t="s">
+        <v>222</v>
       </c>
       <c r="AA139" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
       <c r="AB139" t="s">
         <v>39</v>
@@ -12486,13 +12555,13 @@
     </row>
     <row r="140" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>191</v>
+        <v>228</v>
       </c>
       <c r="C140" t="s">
-        <v>192</v>
+        <v>229</v>
       </c>
       <c r="D140" t="s">
-        <v>251</v>
+        <v>230</v>
       </c>
       <c r="E140" t="s">
         <v>33</v>
@@ -12534,10 +12603,10 @@
         <v>10</v>
       </c>
       <c r="Y140" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
       <c r="AA140" t="s">
-        <v>194</v>
+        <v>232</v>
       </c>
       <c r="AB140" t="s">
         <v>39</v>
@@ -12551,13 +12620,13 @@
     </row>
     <row r="141" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="C141" t="s">
-        <v>202</v>
+        <v>234</v>
       </c>
       <c r="D141" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="E141" t="s">
         <v>33</v>
@@ -12575,13 +12644,13 @@
         <v>54</v>
       </c>
       <c r="K141" t="s">
-        <v>203</v>
+        <v>95</v>
       </c>
       <c r="L141" t="s">
-        <v>204</v>
+        <v>85</v>
       </c>
       <c r="M141" t="s">
-        <v>205</v>
+        <v>86</v>
       </c>
       <c r="N141" t="s">
         <v>33</v>
@@ -12593,19 +12662,16 @@
         <v>38</v>
       </c>
       <c r="Q141">
-        <v>69.989999999999995</v>
+        <v>14.99</v>
       </c>
       <c r="R141">
-        <v>11.67</v>
+        <v>2.5</v>
       </c>
       <c r="Y141" t="s">
-        <v>206</v>
-      </c>
-      <c r="Z141" t="s">
-        <v>60</v>
+        <v>236</v>
       </c>
       <c r="AA141" t="s">
-        <v>207</v>
+        <v>237</v>
       </c>
       <c r="AB141" t="s">
         <v>39</v>
@@ -12619,16 +12685,16 @@
     </row>
     <row r="142" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>195</v>
+        <v>242</v>
       </c>
       <c r="C142" t="s">
-        <v>196</v>
+        <v>243</v>
       </c>
       <c r="D142" t="s">
-        <v>197</v>
+        <v>244</v>
       </c>
       <c r="E142" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F142" t="s">
         <v>34</v>
@@ -12640,7 +12706,7 @@
         <v>36</v>
       </c>
       <c r="J142" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K142" t="s">
         <v>40</v>
@@ -12651,29 +12717,14 @@
       <c r="M142" t="s">
         <v>42</v>
       </c>
-      <c r="N142" t="s">
-        <v>33</v>
-      </c>
       <c r="O142">
-        <v>1</v>
-      </c>
-      <c r="P142" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q142">
-        <v>59.99</v>
-      </c>
-      <c r="R142">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y142" t="s">
-        <v>198</v>
-      </c>
-      <c r="Z142" t="s">
-        <v>199</v>
+        <v>240</v>
       </c>
       <c r="AA142" t="s">
-        <v>200</v>
+        <v>241</v>
       </c>
       <c r="AB142" t="s">
         <v>39</v>
@@ -12687,13 +12738,13 @@
     </row>
     <row r="143" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>208</v>
+        <v>245</v>
       </c>
       <c r="C143" t="s">
-        <v>209</v>
+        <v>246</v>
       </c>
       <c r="D143" t="s">
-        <v>210</v>
+        <v>247</v>
       </c>
       <c r="E143" t="s">
         <v>33</v>
@@ -12735,10 +12786,10 @@
         <v>10</v>
       </c>
       <c r="Y143" t="s">
-        <v>211</v>
+        <v>248</v>
       </c>
       <c r="AA143" t="s">
-        <v>212</v>
+        <v>249</v>
       </c>
       <c r="AB143" t="s">
         <v>39</v>
@@ -12752,13 +12803,13 @@
     </row>
     <row r="144" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>152</v>
+        <v>188</v>
       </c>
       <c r="C144" t="s">
-        <v>153</v>
+        <v>189</v>
       </c>
       <c r="D144" t="s">
-        <v>154</v>
+        <v>250</v>
       </c>
       <c r="E144" t="s">
         <v>33</v>
@@ -12773,16 +12824,16 @@
         <v>36</v>
       </c>
       <c r="J144" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K144" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="L144" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="M144" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="N144" t="s">
         <v>33</v>
@@ -12794,16 +12845,16 @@
         <v>38</v>
       </c>
       <c r="Q144">
-        <v>14.99</v>
+        <v>37.99</v>
       </c>
       <c r="R144">
-        <v>2.5</v>
+        <v>6.33</v>
       </c>
       <c r="Y144" t="s">
-        <v>155</v>
+        <v>52</v>
       </c>
       <c r="AA144" t="s">
-        <v>156</v>
+        <v>190</v>
       </c>
       <c r="AB144" t="s">
         <v>39</v>
@@ -12817,13 +12868,13 @@
     </row>
     <row r="145" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>157</v>
+        <v>191</v>
       </c>
       <c r="C145" t="s">
-        <v>158</v>
+        <v>192</v>
       </c>
       <c r="D145" t="s">
-        <v>159</v>
+        <v>251</v>
       </c>
       <c r="E145" t="s">
         <v>33</v>
@@ -12841,13 +12892,13 @@
         <v>54</v>
       </c>
       <c r="K145" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L145" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M145" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N145" t="s">
         <v>33</v>
@@ -12859,16 +12910,16 @@
         <v>38</v>
       </c>
       <c r="Q145">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R145">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y145" t="s">
-        <v>68</v>
+        <v>193</v>
       </c>
       <c r="AA145" t="s">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="AB145" t="s">
         <v>39</v>
@@ -12882,16 +12933,16 @@
     </row>
     <row r="146" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>161</v>
+        <v>201</v>
       </c>
       <c r="C146" t="s">
-        <v>162</v>
+        <v>202</v>
       </c>
       <c r="D146" t="s">
-        <v>163</v>
+        <v>252</v>
       </c>
       <c r="E146" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F146" t="s">
         <v>34</v>
@@ -12906,22 +12957,37 @@
         <v>54</v>
       </c>
       <c r="K146" t="s">
-        <v>40</v>
+        <v>203</v>
       </c>
       <c r="L146" t="s">
-        <v>41</v>
+        <v>204</v>
       </c>
       <c r="M146" t="s">
-        <v>42</v>
+        <v>205</v>
+      </c>
+      <c r="N146" t="s">
+        <v>33</v>
       </c>
       <c r="O146">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P146" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q146">
+        <v>69.989999999999995</v>
+      </c>
+      <c r="R146">
+        <v>11.67</v>
       </c>
       <c r="Y146" t="s">
-        <v>63</v>
+        <v>206</v>
+      </c>
+      <c r="Z146" t="s">
+        <v>60</v>
       </c>
       <c r="AA146" t="s">
-        <v>151</v>
+        <v>207</v>
       </c>
       <c r="AB146" t="s">
         <v>39</v>
@@ -12935,13 +13001,13 @@
     </row>
     <row r="147" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="C147" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="D147" t="s">
-        <v>166</v>
+        <v>197</v>
       </c>
       <c r="E147" t="s">
         <v>33</v>
@@ -12956,16 +13022,16 @@
         <v>36</v>
       </c>
       <c r="J147" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K147" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L147" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M147" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N147" t="s">
         <v>33</v>
@@ -12977,16 +13043,19 @@
         <v>38</v>
       </c>
       <c r="Q147">
-        <v>37.99</v>
+        <v>59.99</v>
       </c>
       <c r="R147">
-        <v>6.33</v>
+        <v>10</v>
       </c>
       <c r="Y147" t="s">
-        <v>100</v>
+        <v>198</v>
+      </c>
+      <c r="Z147" t="s">
+        <v>199</v>
       </c>
       <c r="AA147" t="s">
-        <v>167</v>
+        <v>200</v>
       </c>
       <c r="AB147" t="s">
         <v>39</v>
@@ -13000,13 +13069,13 @@
     </row>
     <row r="148" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>168</v>
+        <v>208</v>
       </c>
       <c r="C148" t="s">
-        <v>169</v>
+        <v>209</v>
       </c>
       <c r="D148" t="s">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="E148" t="s">
         <v>33</v>
@@ -13021,16 +13090,16 @@
         <v>36</v>
       </c>
       <c r="J148" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K148" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L148" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M148" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N148" t="s">
         <v>33</v>
@@ -13042,16 +13111,16 @@
         <v>38</v>
       </c>
       <c r="Q148">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R148">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y148" t="s">
-        <v>66</v>
+        <v>211</v>
       </c>
       <c r="AA148" t="s">
-        <v>171</v>
+        <v>212</v>
       </c>
       <c r="AB148" t="s">
         <v>39</v>
@@ -13065,13 +13134,13 @@
     </row>
     <row r="149" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="C149" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="D149" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="E149" t="s">
         <v>33</v>
@@ -13089,13 +13158,13 @@
         <v>54</v>
       </c>
       <c r="K149" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L149" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="M149" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="N149" t="s">
         <v>33</v>
@@ -13113,10 +13182,10 @@
         <v>2.5</v>
       </c>
       <c r="Y149" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="AA149" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="AB149" t="s">
         <v>39</v>
@@ -13130,13 +13199,13 @@
     </row>
     <row r="150" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="C150" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="D150" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="E150" t="s">
         <v>33</v>
@@ -13154,13 +13223,13 @@
         <v>54</v>
       </c>
       <c r="K150" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L150" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M150" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="N150" t="s">
         <v>33</v>
@@ -13172,19 +13241,16 @@
         <v>38</v>
       </c>
       <c r="Q150">
-        <v>37.99</v>
+        <v>11.99</v>
       </c>
       <c r="R150">
-        <v>6.33</v>
+        <v>2</v>
       </c>
       <c r="Y150" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z150" t="s">
-        <v>181</v>
+        <v>68</v>
       </c>
       <c r="AA150" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="AB150" t="s">
         <v>39</v>
@@ -13198,16 +13264,16 @@
     </row>
     <row r="151" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="C151" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="D151" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="E151" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F151" t="s">
         <v>34</v>
@@ -13222,37 +13288,22 @@
         <v>54</v>
       </c>
       <c r="K151" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L151" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M151" t="s">
-        <v>50</v>
-      </c>
-      <c r="N151" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O151">
-        <v>2</v>
-      </c>
-      <c r="P151" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q151">
-        <v>75.98</v>
-      </c>
-      <c r="R151">
-        <v>12.66</v>
+        <v>0</v>
       </c>
       <c r="Y151" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z151" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="AA151" t="s">
-        <v>185</v>
+        <v>151</v>
       </c>
       <c r="AB151" t="s">
         <v>39</v>
@@ -13266,13 +13317,13 @@
     </row>
     <row r="152" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="C152" t="s">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="D152" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="E152" t="s">
         <v>33</v>
@@ -13290,13 +13341,13 @@
         <v>54</v>
       </c>
       <c r="K152" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L152" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M152" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N152" t="s">
         <v>33</v>
@@ -13308,16 +13359,16 @@
         <v>38</v>
       </c>
       <c r="Q152">
-        <v>11.99</v>
+        <v>37.99</v>
       </c>
       <c r="R152">
-        <v>2</v>
+        <v>6.33</v>
       </c>
       <c r="Y152" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="AA152" t="s">
-        <v>135</v>
+        <v>167</v>
       </c>
       <c r="AB152" t="s">
         <v>39</v>
@@ -13331,13 +13382,13 @@
     </row>
     <row r="153" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>117</v>
+        <v>168</v>
       </c>
       <c r="C153" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D153" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="E153" t="s">
         <v>33</v>
@@ -13355,13 +13406,13 @@
         <v>54</v>
       </c>
       <c r="K153" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L153" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M153" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="N153" t="s">
         <v>33</v>
@@ -13373,19 +13424,16 @@
         <v>38</v>
       </c>
       <c r="Q153">
-        <v>14.99</v>
+        <v>11.99</v>
       </c>
       <c r="R153">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Y153" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z153" t="s">
-        <v>121</v>
+        <v>66</v>
       </c>
       <c r="AA153" t="s">
-        <v>122</v>
+        <v>171</v>
       </c>
       <c r="AB153" t="s">
         <v>39</v>
@@ -13399,13 +13447,13 @@
     </row>
     <row r="154" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>123</v>
+        <v>172</v>
       </c>
       <c r="C154" t="s">
-        <v>124</v>
+        <v>173</v>
       </c>
       <c r="D154" t="s">
-        <v>125</v>
+        <v>174</v>
       </c>
       <c r="E154" t="s">
         <v>33</v>
@@ -13423,13 +13471,13 @@
         <v>54</v>
       </c>
       <c r="K154" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L154" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M154" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="N154" t="s">
         <v>33</v>
@@ -13441,19 +13489,16 @@
         <v>38</v>
       </c>
       <c r="Q154">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="R154">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="Y154" t="s">
-        <v>126</v>
-      </c>
-      <c r="Z154" t="s">
-        <v>127</v>
+        <v>175</v>
       </c>
       <c r="AA154" t="s">
-        <v>128</v>
+        <v>176</v>
       </c>
       <c r="AB154" t="s">
         <v>39</v>
@@ -13467,13 +13512,13 @@
     </row>
     <row r="155" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>129</v>
+        <v>177</v>
       </c>
       <c r="C155" t="s">
-        <v>130</v>
+        <v>178</v>
       </c>
       <c r="D155" t="s">
-        <v>131</v>
+        <v>179</v>
       </c>
       <c r="E155" t="s">
         <v>33</v>
@@ -13491,13 +13536,13 @@
         <v>54</v>
       </c>
       <c r="K155" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="L155" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M155" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="N155" t="s">
         <v>33</v>
@@ -13509,16 +13554,19 @@
         <v>38</v>
       </c>
       <c r="Q155">
-        <v>38.49</v>
+        <v>37.99</v>
       </c>
       <c r="R155">
-        <v>6.42</v>
+        <v>6.33</v>
       </c>
       <c r="Y155" t="s">
-        <v>78</v>
+        <v>180</v>
+      </c>
+      <c r="Z155" t="s">
+        <v>181</v>
       </c>
       <c r="AA155" t="s">
-        <v>132</v>
+        <v>182</v>
       </c>
       <c r="AB155" t="s">
         <v>39</v>
@@ -13532,16 +13580,16 @@
     </row>
     <row r="156" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>105</v>
+        <v>183</v>
       </c>
       <c r="C156" t="s">
-        <v>106</v>
+        <v>184</v>
       </c>
       <c r="D156" t="s">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="E156" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F156" t="s">
         <v>34</v>
@@ -13556,22 +13604,37 @@
         <v>54</v>
       </c>
       <c r="K156" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="L156" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="M156" t="s">
-        <v>83</v>
+        <v>50</v>
+      </c>
+      <c r="N156" t="s">
+        <v>33</v>
       </c>
       <c r="O156">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="P156" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q156">
+        <v>75.98</v>
+      </c>
+      <c r="R156">
+        <v>12.66</v>
       </c>
       <c r="Y156" t="s">
-        <v>103</v>
+        <v>70</v>
+      </c>
+      <c r="Z156" t="s">
+        <v>47</v>
       </c>
       <c r="AA156" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="AB156" t="s">
         <v>39</v>
@@ -13585,13 +13648,13 @@
     </row>
     <row r="157" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="C157" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="D157" t="s">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="E157" t="s">
         <v>33</v>
@@ -13609,13 +13672,13 @@
         <v>54</v>
       </c>
       <c r="K157" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L157" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M157" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="N157" t="s">
         <v>33</v>
@@ -13627,19 +13690,16 @@
         <v>38</v>
       </c>
       <c r="Q157">
-        <v>37.99</v>
+        <v>11.99</v>
       </c>
       <c r="R157">
-        <v>6.33</v>
+        <v>2</v>
       </c>
       <c r="Y157" t="s">
-        <v>109</v>
-      </c>
-      <c r="Z157" t="s">
-        <v>110</v>
+        <v>69</v>
       </c>
       <c r="AA157" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="AB157" t="s">
         <v>39</v>
@@ -13653,13 +13713,13 @@
     </row>
     <row r="158" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C158" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D158" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E158" t="s">
         <v>33</v>
@@ -13674,16 +13734,16 @@
         <v>36</v>
       </c>
       <c r="J158" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K158" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L158" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M158" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="N158" t="s">
         <v>33</v>
@@ -13695,19 +13755,19 @@
         <v>38</v>
       </c>
       <c r="Q158">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="R158">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="Y158" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="Z158" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="AA158" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="AB158" t="s">
         <v>39</v>
@@ -13721,66 +13781,388 @@
     </row>
     <row r="159" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
+        <v>123</v>
+      </c>
+      <c r="C159" t="s">
+        <v>124</v>
+      </c>
+      <c r="D159" t="s">
+        <v>125</v>
+      </c>
+      <c r="E159" t="s">
+        <v>33</v>
+      </c>
+      <c r="F159" t="s">
+        <v>34</v>
+      </c>
+      <c r="G159" t="s">
+        <v>35</v>
+      </c>
+      <c r="H159" t="s">
+        <v>36</v>
+      </c>
+      <c r="J159" t="s">
+        <v>54</v>
+      </c>
+      <c r="K159" t="s">
+        <v>40</v>
+      </c>
+      <c r="L159" t="s">
+        <v>41</v>
+      </c>
+      <c r="M159" t="s">
+        <v>42</v>
+      </c>
+      <c r="N159" t="s">
+        <v>33</v>
+      </c>
+      <c r="O159">
+        <v>1</v>
+      </c>
+      <c r="P159" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q159">
+        <v>59.99</v>
+      </c>
+      <c r="R159">
+        <v>10</v>
+      </c>
+      <c r="Y159" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z159" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA159" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB159" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>129</v>
+      </c>
+      <c r="C160" t="s">
+        <v>130</v>
+      </c>
+      <c r="D160" t="s">
+        <v>131</v>
+      </c>
+      <c r="E160" t="s">
+        <v>33</v>
+      </c>
+      <c r="F160" t="s">
+        <v>34</v>
+      </c>
+      <c r="G160" t="s">
+        <v>35</v>
+      </c>
+      <c r="H160" t="s">
+        <v>36</v>
+      </c>
+      <c r="J160" t="s">
+        <v>54</v>
+      </c>
+      <c r="K160" t="s">
+        <v>43</v>
+      </c>
+      <c r="L160" t="s">
+        <v>44</v>
+      </c>
+      <c r="M160" t="s">
+        <v>45</v>
+      </c>
+      <c r="N160" t="s">
+        <v>33</v>
+      </c>
+      <c r="O160">
+        <v>1</v>
+      </c>
+      <c r="P160" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q160">
+        <v>38.49</v>
+      </c>
+      <c r="R160">
+        <v>6.42</v>
+      </c>
+      <c r="Y160" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA160" t="s">
+        <v>132</v>
+      </c>
+      <c r="AB160" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG160" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>105</v>
+      </c>
+      <c r="C161" t="s">
+        <v>106</v>
+      </c>
+      <c r="D161" t="s">
+        <v>136</v>
+      </c>
+      <c r="E161" t="s">
+        <v>53</v>
+      </c>
+      <c r="F161" t="s">
+        <v>34</v>
+      </c>
+      <c r="G161" t="s">
+        <v>35</v>
+      </c>
+      <c r="H161" t="s">
+        <v>36</v>
+      </c>
+      <c r="J161" t="s">
+        <v>54</v>
+      </c>
+      <c r="K161" t="s">
+        <v>94</v>
+      </c>
+      <c r="L161" t="s">
+        <v>82</v>
+      </c>
+      <c r="M161" t="s">
+        <v>83</v>
+      </c>
+      <c r="O161">
+        <v>0</v>
+      </c>
+      <c r="Y161" t="s">
+        <v>103</v>
+      </c>
+      <c r="AA161" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB161" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG161" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>107</v>
+      </c>
+      <c r="C162" t="s">
+        <v>108</v>
+      </c>
+      <c r="D162" t="s">
+        <v>137</v>
+      </c>
+      <c r="E162" t="s">
+        <v>33</v>
+      </c>
+      <c r="F162" t="s">
+        <v>34</v>
+      </c>
+      <c r="G162" t="s">
+        <v>35</v>
+      </c>
+      <c r="H162" t="s">
+        <v>36</v>
+      </c>
+      <c r="J162" t="s">
+        <v>54</v>
+      </c>
+      <c r="K162" t="s">
+        <v>48</v>
+      </c>
+      <c r="L162" t="s">
+        <v>49</v>
+      </c>
+      <c r="M162" t="s">
+        <v>50</v>
+      </c>
+      <c r="N162" t="s">
+        <v>33</v>
+      </c>
+      <c r="O162">
+        <v>1</v>
+      </c>
+      <c r="P162" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q162">
+        <v>37.99</v>
+      </c>
+      <c r="R162">
+        <v>6.33</v>
+      </c>
+      <c r="Y162" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z162" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA162" t="s">
+        <v>111</v>
+      </c>
+      <c r="AB162" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG162" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>112</v>
+      </c>
+      <c r="C163" t="s">
+        <v>113</v>
+      </c>
+      <c r="D163" t="s">
+        <v>114</v>
+      </c>
+      <c r="E163" t="s">
+        <v>33</v>
+      </c>
+      <c r="F163" t="s">
+        <v>34</v>
+      </c>
+      <c r="G163" t="s">
+        <v>35</v>
+      </c>
+      <c r="H163" t="s">
+        <v>36</v>
+      </c>
+      <c r="J163" t="s">
+        <v>37</v>
+      </c>
+      <c r="K163" t="s">
+        <v>40</v>
+      </c>
+      <c r="L163" t="s">
+        <v>41</v>
+      </c>
+      <c r="M163" t="s">
+        <v>42</v>
+      </c>
+      <c r="N163" t="s">
+        <v>33</v>
+      </c>
+      <c r="O163">
+        <v>1</v>
+      </c>
+      <c r="P163" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q163">
+        <v>59.99</v>
+      </c>
+      <c r="R163">
+        <v>10</v>
+      </c>
+      <c r="Y163" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z163" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA163" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB163" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG163" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
         <v>703</v>
       </c>
-      <c r="C159" t="s">
+      <c r="C164" t="s">
         <v>704</v>
       </c>
-      <c r="D159" t="s">
+      <c r="D164" t="s">
         <v>705</v>
       </c>
-      <c r="E159" t="s">
-        <v>33</v>
-      </c>
-      <c r="F159" t="s">
-        <v>34</v>
-      </c>
-      <c r="G159" t="s">
-        <v>35</v>
-      </c>
-      <c r="H159" t="s">
-        <v>36</v>
-      </c>
-      <c r="J159" t="s">
-        <v>54</v>
-      </c>
-      <c r="K159" t="s">
+      <c r="E164" t="s">
+        <v>33</v>
+      </c>
+      <c r="F164" t="s">
+        <v>34</v>
+      </c>
+      <c r="G164" t="s">
+        <v>35</v>
+      </c>
+      <c r="H164" t="s">
+        <v>36</v>
+      </c>
+      <c r="J164" t="s">
+        <v>54</v>
+      </c>
+      <c r="K164" t="s">
         <v>72</v>
       </c>
-      <c r="L159" t="s">
+      <c r="L164" t="s">
         <v>73</v>
       </c>
-      <c r="M159" t="s">
+      <c r="M164" t="s">
         <v>74</v>
       </c>
-      <c r="N159" t="s">
-        <v>33</v>
-      </c>
-      <c r="O159">
-        <v>1</v>
-      </c>
-      <c r="P159" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q159">
+      <c r="N164" t="s">
+        <v>33</v>
+      </c>
+      <c r="O164">
+        <v>1</v>
+      </c>
+      <c r="P164" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q164">
         <v>11.99</v>
       </c>
-      <c r="R159">
+      <c r="R164">
         <v>2</v>
       </c>
-      <c r="Y159" t="s">
+      <c r="Y164" t="s">
         <v>706</v>
       </c>
-      <c r="AA159" t="s">
+      <c r="AA164" t="s">
         <v>707</v>
       </c>
-      <c r="AB159" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD159" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG159" t="b">
+      <c r="AB164" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG164" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Raw Sales Data/Amazon.xlsx
+++ b/Raw Sales Data/Amazon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2667" uniqueCount="864">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2683" uniqueCount="869">
   <si>
     <t>amazon-order-id</t>
   </si>
@@ -2611,6 +2611,21 @@
   </si>
   <si>
     <t>2026-03-07T09:39:56+00:00</t>
+  </si>
+  <si>
+    <t>206-3232272-3937914</t>
+  </si>
+  <si>
+    <t>2026-03-09T15:06:16+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-10T01:09:08+00:00</t>
+  </si>
+  <si>
+    <t>LEVEN</t>
+  </si>
+  <si>
+    <t>KY8 4SF</t>
   </si>
 </sst>
 </file>
@@ -3417,7 +3432,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG164"/>
+  <dimension ref="A1:AG165"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
@@ -3528,13 +3543,13 @@
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>846</v>
+        <v>864</v>
       </c>
       <c r="C2" t="s">
-        <v>847</v>
+        <v>865</v>
       </c>
       <c r="D2" t="s">
-        <v>848</v>
+        <v>866</v>
       </c>
       <c r="E2" t="s">
         <v>33</v>
@@ -3575,20 +3590,11 @@
       <c r="R2">
         <v>11</v>
       </c>
-      <c r="S2">
-        <v>6.99</v>
-      </c>
-      <c r="T2">
-        <v>1.17</v>
-      </c>
       <c r="Y2" t="s">
-        <v>849</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>850</v>
+        <v>867</v>
       </c>
       <c r="AA2" t="s">
-        <v>851</v>
+        <v>868</v>
       </c>
       <c r="AB2" t="s">
         <v>39</v>
@@ -3602,16 +3608,16 @@
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>852</v>
+        <v>846</v>
       </c>
       <c r="C3" t="s">
-        <v>853</v>
+        <v>847</v>
       </c>
       <c r="D3" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="E3" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F3" t="s">
         <v>34</v>
@@ -3634,14 +3640,35 @@
       <c r="M3" t="s">
         <v>42</v>
       </c>
+      <c r="N3" t="s">
+        <v>33</v>
+      </c>
       <c r="O3">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P3" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q3">
+        <v>65.989999999999995</v>
+      </c>
+      <c r="R3">
+        <v>11</v>
+      </c>
+      <c r="S3">
+        <v>6.99</v>
+      </c>
+      <c r="T3">
+        <v>1.17</v>
       </c>
       <c r="Y3" t="s">
-        <v>855</v>
+        <v>849</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>850</v>
       </c>
       <c r="AA3" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="AB3" t="s">
         <v>39</v>
@@ -3655,16 +3682,16 @@
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="C4" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="D4" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F4" t="s">
         <v>34</v>
@@ -3687,26 +3714,14 @@
       <c r="M4" t="s">
         <v>42</v>
       </c>
-      <c r="N4" t="s">
-        <v>33</v>
-      </c>
       <c r="O4">
-        <v>1</v>
-      </c>
-      <c r="P4" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q4">
-        <v>65.989999999999995</v>
-      </c>
-      <c r="R4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="AA4" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="AB4" t="s">
         <v>39</v>
@@ -3720,13 +3735,13 @@
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>837</v>
+        <v>857</v>
       </c>
       <c r="C5" t="s">
-        <v>838</v>
+        <v>858</v>
       </c>
       <c r="D5" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="E5" t="s">
         <v>33</v>
@@ -3744,13 +3759,13 @@
         <v>54</v>
       </c>
       <c r="K5" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L5" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M5" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N5" t="s">
         <v>33</v>
@@ -3762,16 +3777,16 @@
         <v>38</v>
       </c>
       <c r="Q5">
-        <v>40.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R5">
-        <v>6.83</v>
+        <v>11</v>
       </c>
       <c r="Y5" t="s">
-        <v>305</v>
+        <v>860</v>
       </c>
       <c r="AA5" t="s">
-        <v>840</v>
+        <v>861</v>
       </c>
       <c r="AB5" t="s">
         <v>39</v>
@@ -3785,13 +3800,13 @@
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="C6" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="D6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="E6" t="s">
         <v>33</v>
@@ -3809,13 +3824,13 @@
         <v>54</v>
       </c>
       <c r="K6" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M6" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N6" t="s">
         <v>33</v>
@@ -3827,22 +3842,16 @@
         <v>38</v>
       </c>
       <c r="Q6">
-        <v>65.989999999999995</v>
+        <v>40.99</v>
       </c>
       <c r="R6">
-        <v>11</v>
-      </c>
-      <c r="S6">
-        <v>6.99</v>
-      </c>
-      <c r="T6">
-        <v>1.17</v>
+        <v>6.83</v>
       </c>
       <c r="Y6" t="s">
-        <v>844</v>
+        <v>305</v>
       </c>
       <c r="AA6" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="AB6" t="s">
         <v>39</v>
@@ -3856,16 +3865,16 @@
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="C7" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="D7" t="s">
-        <v>839</v>
+        <v>863</v>
       </c>
       <c r="E7" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F7" t="s">
         <v>34</v>
@@ -3880,16 +3889,16 @@
         <v>54</v>
       </c>
       <c r="K7" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L7" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M7" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N7" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O7">
         <v>1</v>
@@ -3898,16 +3907,22 @@
         <v>38</v>
       </c>
       <c r="Q7">
-        <v>40.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R7">
-        <v>6.83</v>
+        <v>11</v>
+      </c>
+      <c r="S7">
+        <v>6.99</v>
+      </c>
+      <c r="T7">
+        <v>1.17</v>
       </c>
       <c r="Y7" t="s">
-        <v>305</v>
+        <v>844</v>
       </c>
       <c r="AA7" t="s">
-        <v>840</v>
+        <v>845</v>
       </c>
       <c r="AB7" t="s">
         <v>39</v>
@@ -3921,13 +3936,13 @@
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="C8" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="D8" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="E8" t="s">
         <v>98</v>
@@ -3945,13 +3960,13 @@
         <v>54</v>
       </c>
       <c r="K8" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L8" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M8" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N8" t="s">
         <v>99</v>
@@ -3963,22 +3978,16 @@
         <v>38</v>
       </c>
       <c r="Q8">
-        <v>65.989999999999995</v>
+        <v>40.99</v>
       </c>
       <c r="R8">
-        <v>11</v>
-      </c>
-      <c r="S8">
-        <v>6.99</v>
-      </c>
-      <c r="T8">
-        <v>1.17</v>
+        <v>6.83</v>
       </c>
       <c r="Y8" t="s">
-        <v>844</v>
+        <v>305</v>
       </c>
       <c r="AA8" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="AB8" t="s">
         <v>39</v>
@@ -3992,13 +4001,13 @@
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>819</v>
+        <v>841</v>
       </c>
       <c r="C9" t="s">
-        <v>820</v>
+        <v>842</v>
       </c>
       <c r="D9" t="s">
-        <v>821</v>
+        <v>843</v>
       </c>
       <c r="E9" t="s">
         <v>98</v>
@@ -4016,13 +4025,13 @@
         <v>54</v>
       </c>
       <c r="K9" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L9" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M9" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N9" t="s">
         <v>99</v>
@@ -4034,19 +4043,22 @@
         <v>38</v>
       </c>
       <c r="Q9">
-        <v>40.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R9">
-        <v>6.83</v>
+        <v>11</v>
+      </c>
+      <c r="S9">
+        <v>6.99</v>
+      </c>
+      <c r="T9">
+        <v>1.17</v>
       </c>
       <c r="Y9" t="s">
-        <v>618</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>619</v>
+        <v>844</v>
       </c>
       <c r="AA9" t="s">
-        <v>620</v>
+        <v>845</v>
       </c>
       <c r="AB9" t="s">
         <v>39</v>
@@ -4060,13 +4072,13 @@
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="C10" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="D10" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="E10" t="s">
         <v>98</v>
@@ -4084,13 +4096,13 @@
         <v>54</v>
       </c>
       <c r="K10" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L10" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M10" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N10" t="s">
         <v>99</v>
@@ -4102,16 +4114,19 @@
         <v>38</v>
       </c>
       <c r="Q10">
-        <v>14.99</v>
+        <v>40.99</v>
       </c>
       <c r="R10">
-        <v>2.5</v>
+        <v>6.83</v>
       </c>
       <c r="Y10" t="s">
-        <v>825</v>
+        <v>618</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>619</v>
       </c>
       <c r="AA10" t="s">
-        <v>826</v>
+        <v>620</v>
       </c>
       <c r="AB10" t="s">
         <v>39</v>
@@ -4125,13 +4140,13 @@
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="C11" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="D11" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="E11" t="s">
         <v>98</v>
@@ -4149,13 +4164,13 @@
         <v>54</v>
       </c>
       <c r="K11" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L11" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M11" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N11" t="s">
         <v>99</v>
@@ -4167,16 +4182,16 @@
         <v>38</v>
       </c>
       <c r="Q11">
-        <v>65.989999999999995</v>
-      </c>
-      <c r="S11">
-        <v>6.99</v>
+        <v>14.99</v>
+      </c>
+      <c r="R11">
+        <v>2.5</v>
       </c>
       <c r="Y11" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="AA11" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="AB11" t="s">
         <v>39</v>
@@ -4190,16 +4205,16 @@
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="C12" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="D12" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="E12" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F12" t="s">
         <v>34</v>
@@ -4223,7 +4238,7 @@
         <v>42</v>
       </c>
       <c r="N12" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O12">
         <v>1</v>
@@ -4234,14 +4249,14 @@
       <c r="Q12">
         <v>65.989999999999995</v>
       </c>
-      <c r="R12">
-        <v>11</v>
+      <c r="S12">
+        <v>6.99</v>
       </c>
       <c r="Y12" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="AA12" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="AB12" t="s">
         <v>39</v>
@@ -4255,13 +4270,13 @@
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>780</v>
+        <v>832</v>
       </c>
       <c r="C13" t="s">
-        <v>781</v>
+        <v>833</v>
       </c>
       <c r="D13" t="s">
-        <v>782</v>
+        <v>834</v>
       </c>
       <c r="E13" t="s">
         <v>33</v>
@@ -4303,10 +4318,10 @@
         <v>11</v>
       </c>
       <c r="Y13" t="s">
-        <v>783</v>
+        <v>835</v>
       </c>
       <c r="AA13" t="s">
-        <v>784</v>
+        <v>836</v>
       </c>
       <c r="AB13" t="s">
         <v>39</v>
@@ -4320,13 +4335,13 @@
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="C14" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="D14" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="E14" t="s">
         <v>33</v>
@@ -4344,13 +4359,13 @@
         <v>54</v>
       </c>
       <c r="K14" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L14" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M14" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N14" t="s">
         <v>33</v>
@@ -4362,16 +4377,16 @@
         <v>38</v>
       </c>
       <c r="Q14">
-        <v>40.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R14">
-        <v>6.83</v>
+        <v>11</v>
       </c>
       <c r="Y14" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="AA14" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="AB14" t="s">
         <v>39</v>
@@ -4385,13 +4400,13 @@
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="C15" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="D15" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="E15" t="s">
         <v>33</v>
@@ -4409,13 +4424,13 @@
         <v>54</v>
       </c>
       <c r="K15" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L15" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M15" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N15" t="s">
         <v>33</v>
@@ -4427,16 +4442,16 @@
         <v>38</v>
       </c>
       <c r="Q15">
-        <v>65.989999999999995</v>
+        <v>40.99</v>
       </c>
       <c r="R15">
-        <v>11</v>
+        <v>6.83</v>
       </c>
       <c r="Y15" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="AA15" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="AB15" t="s">
         <v>39</v>
@@ -4450,13 +4465,13 @@
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="C16" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="D16" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="E16" t="s">
         <v>33</v>
@@ -4474,13 +4489,13 @@
         <v>54</v>
       </c>
       <c r="K16" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L16" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M16" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N16" t="s">
         <v>33</v>
@@ -4492,16 +4507,16 @@
         <v>38</v>
       </c>
       <c r="Q16">
-        <v>14.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R16">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="Y16" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="AA16" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="AB16" t="s">
         <v>39</v>
@@ -4515,13 +4530,13 @@
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="C17" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="D17" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="E17" t="s">
         <v>33</v>
@@ -4563,10 +4578,10 @@
         <v>2.5</v>
       </c>
       <c r="Y17" t="s">
-        <v>68</v>
+        <v>798</v>
       </c>
       <c r="AA17" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="AB17" t="s">
         <v>39</v>
@@ -4580,10 +4595,10 @@
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="C18" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="D18" t="s">
         <v>802</v>
@@ -4622,16 +4637,16 @@
         <v>38</v>
       </c>
       <c r="Q18">
-        <v>11.99</v>
+        <v>14.99</v>
       </c>
       <c r="R18">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Y18" t="s">
-        <v>806</v>
+        <v>68</v>
       </c>
       <c r="AA18" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="AB18" t="s">
         <v>39</v>
@@ -4645,13 +4660,13 @@
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="C19" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="D19" t="s">
-        <v>810</v>
+        <v>802</v>
       </c>
       <c r="E19" t="s">
         <v>33</v>
@@ -4693,10 +4708,10 @@
         <v>2</v>
       </c>
       <c r="Y19" t="s">
-        <v>66</v>
+        <v>806</v>
       </c>
       <c r="AA19" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="AB19" t="s">
         <v>39</v>
@@ -4710,13 +4725,13 @@
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="C20" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="D20" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="E20" t="s">
         <v>33</v>
@@ -4734,13 +4749,13 @@
         <v>54</v>
       </c>
       <c r="K20" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="L20" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="M20" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="N20" t="s">
         <v>33</v>
@@ -4752,16 +4767,16 @@
         <v>38</v>
       </c>
       <c r="Q20">
-        <v>40.99</v>
+        <v>11.99</v>
       </c>
       <c r="R20">
-        <v>6.83</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="s">
-        <v>815</v>
+        <v>66</v>
       </c>
       <c r="AA20" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="AB20" t="s">
         <v>39</v>
@@ -4775,13 +4790,13 @@
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>745</v>
+        <v>812</v>
       </c>
       <c r="C21" t="s">
-        <v>746</v>
+        <v>813</v>
       </c>
       <c r="D21" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="E21" t="s">
         <v>33</v>
@@ -4799,13 +4814,13 @@
         <v>54</v>
       </c>
       <c r="K21" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="L21" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="M21" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="N21" t="s">
         <v>33</v>
@@ -4817,16 +4832,16 @@
         <v>38</v>
       </c>
       <c r="Q21">
-        <v>11.99</v>
+        <v>40.99</v>
       </c>
       <c r="R21">
-        <v>2</v>
+        <v>6.83</v>
       </c>
       <c r="Y21" t="s">
-        <v>748</v>
+        <v>815</v>
       </c>
       <c r="AA21" t="s">
-        <v>749</v>
+        <v>816</v>
       </c>
       <c r="AB21" t="s">
         <v>39</v>
@@ -4840,13 +4855,13 @@
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="C22" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="D22" t="s">
-        <v>752</v>
+        <v>817</v>
       </c>
       <c r="E22" t="s">
         <v>33</v>
@@ -4864,13 +4879,13 @@
         <v>54</v>
       </c>
       <c r="K22" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L22" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M22" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N22" t="s">
         <v>33</v>
@@ -4882,16 +4897,16 @@
         <v>38</v>
       </c>
       <c r="Q22">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R22">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="AA22" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="AB22" t="s">
         <v>39</v>
@@ -4905,13 +4920,13 @@
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="C23" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="D23" t="s">
-        <v>818</v>
+        <v>752</v>
       </c>
       <c r="E23" t="s">
         <v>33</v>
@@ -4952,20 +4967,11 @@
       <c r="R23">
         <v>11</v>
       </c>
-      <c r="S23">
-        <v>6.99</v>
-      </c>
-      <c r="T23">
-        <v>1.17</v>
-      </c>
       <c r="Y23" t="s">
-        <v>758</v>
-      </c>
-      <c r="Z23" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="AA23" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="AB23" t="s">
         <v>39</v>
@@ -4979,13 +4985,13 @@
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="C24" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="D24" t="s">
-        <v>763</v>
+        <v>818</v>
       </c>
       <c r="E24" t="s">
         <v>33</v>
@@ -5003,13 +5009,13 @@
         <v>54</v>
       </c>
       <c r="K24" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L24" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M24" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N24" t="s">
         <v>33</v>
@@ -5021,19 +5027,25 @@
         <v>38</v>
       </c>
       <c r="Q24">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R24">
-        <v>2</v>
+        <v>11</v>
+      </c>
+      <c r="S24">
+        <v>6.99</v>
+      </c>
+      <c r="T24">
+        <v>1.17</v>
       </c>
       <c r="Y24" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="Z24" t="s">
-        <v>279</v>
+        <v>759</v>
       </c>
       <c r="AA24" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="AB24" t="s">
         <v>39</v>
@@ -5047,13 +5059,13 @@
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="C25" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="D25" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="E25" t="s">
         <v>33</v>
@@ -5095,13 +5107,13 @@
         <v>2</v>
       </c>
       <c r="Y25" t="s">
-        <v>91</v>
+        <v>764</v>
       </c>
       <c r="Z25" t="s">
-        <v>121</v>
+        <v>279</v>
       </c>
       <c r="AA25" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="AB25" t="s">
         <v>39</v>
@@ -5115,13 +5127,13 @@
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="C26" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="D26" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="E26" t="s">
         <v>33</v>
@@ -5139,13 +5151,13 @@
         <v>54</v>
       </c>
       <c r="K26" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L26" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M26" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N26" t="s">
         <v>33</v>
@@ -5157,19 +5169,19 @@
         <v>38</v>
       </c>
       <c r="Q26">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R26">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y26" t="s">
-        <v>773</v>
+        <v>91</v>
       </c>
       <c r="Z26" t="s">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="AA26" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="AB26" t="s">
         <v>39</v>
@@ -5183,13 +5195,13 @@
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="C27" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="D27" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="E27" t="s">
         <v>33</v>
@@ -5231,10 +5243,13 @@
         <v>11</v>
       </c>
       <c r="Y27" t="s">
-        <v>778</v>
+        <v>773</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>64</v>
       </c>
       <c r="AA27" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="AB27" t="s">
         <v>39</v>
@@ -5248,16 +5263,16 @@
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>745</v>
+        <v>775</v>
       </c>
       <c r="C28" t="s">
-        <v>746</v>
+        <v>776</v>
       </c>
       <c r="D28" t="s">
-        <v>747</v>
+        <v>777</v>
       </c>
       <c r="E28" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F28" t="s">
         <v>34</v>
@@ -5272,16 +5287,16 @@
         <v>54</v>
       </c>
       <c r="K28" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L28" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M28" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N28" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O28">
         <v>1</v>
@@ -5290,16 +5305,16 @@
         <v>38</v>
       </c>
       <c r="Q28">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R28">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y28" t="s">
-        <v>748</v>
+        <v>778</v>
       </c>
       <c r="AA28" t="s">
-        <v>749</v>
+        <v>779</v>
       </c>
       <c r="AB28" t="s">
         <v>39</v>
@@ -5313,16 +5328,16 @@
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="C29" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="D29" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="E29" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F29" t="s">
         <v>34</v>
@@ -5337,16 +5352,16 @@
         <v>54</v>
       </c>
       <c r="K29" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L29" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M29" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N29" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O29">
         <v>1</v>
@@ -5355,16 +5370,16 @@
         <v>38</v>
       </c>
       <c r="Q29">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R29">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y29" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="AA29" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="AB29" t="s">
         <v>39</v>
@@ -5378,16 +5393,16 @@
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="C30" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="D30" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="E30" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F30" t="s">
         <v>34</v>
@@ -5411,7 +5426,7 @@
         <v>42</v>
       </c>
       <c r="N30" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O30">
         <v>1</v>
@@ -5425,20 +5440,11 @@
       <c r="R30">
         <v>11</v>
       </c>
-      <c r="S30">
-        <v>6.99</v>
-      </c>
-      <c r="T30">
-        <v>1.17</v>
-      </c>
       <c r="Y30" t="s">
-        <v>758</v>
-      </c>
-      <c r="Z30" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="AA30" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="AB30" t="s">
         <v>39</v>
@@ -5452,16 +5458,16 @@
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="C31" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="D31" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="E31" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F31" t="s">
         <v>34</v>
@@ -5476,16 +5482,16 @@
         <v>54</v>
       </c>
       <c r="K31" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L31" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M31" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N31" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O31">
         <v>1</v>
@@ -5494,19 +5500,25 @@
         <v>38</v>
       </c>
       <c r="Q31">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R31">
-        <v>2</v>
+        <v>11</v>
+      </c>
+      <c r="S31">
+        <v>6.99</v>
+      </c>
+      <c r="T31">
+        <v>1.17</v>
       </c>
       <c r="Y31" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="Z31" t="s">
-        <v>279</v>
+        <v>759</v>
       </c>
       <c r="AA31" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="AB31" t="s">
         <v>39</v>
@@ -5520,13 +5532,13 @@
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="C32" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="D32" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="E32" t="s">
         <v>33</v>
@@ -5568,13 +5580,13 @@
         <v>2</v>
       </c>
       <c r="Y32" t="s">
-        <v>91</v>
+        <v>764</v>
       </c>
       <c r="Z32" t="s">
-        <v>121</v>
+        <v>279</v>
       </c>
       <c r="AA32" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="AB32" t="s">
         <v>39</v>
@@ -5588,13 +5600,13 @@
     </row>
     <row r="33" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="C33" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="D33" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="E33" t="s">
         <v>33</v>
@@ -5612,13 +5624,13 @@
         <v>54</v>
       </c>
       <c r="K33" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L33" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N33" t="s">
         <v>33</v>
@@ -5630,19 +5642,19 @@
         <v>38</v>
       </c>
       <c r="Q33">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R33">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y33" t="s">
-        <v>773</v>
+        <v>91</v>
       </c>
       <c r="Z33" t="s">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="AA33" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="AB33" t="s">
         <v>39</v>
@@ -5656,13 +5668,13 @@
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="C34" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="D34" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="E34" t="s">
         <v>33</v>
@@ -5704,10 +5716,13 @@
         <v>11</v>
       </c>
       <c r="Y34" t="s">
-        <v>778</v>
+        <v>773</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>64</v>
       </c>
       <c r="AA34" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="AB34" t="s">
         <v>39</v>
@@ -5721,16 +5736,16 @@
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>714</v>
+        <v>775</v>
       </c>
       <c r="C35" t="s">
-        <v>715</v>
+        <v>776</v>
       </c>
       <c r="D35" t="s">
-        <v>716</v>
+        <v>777</v>
       </c>
       <c r="E35" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F35" t="s">
         <v>34</v>
@@ -5745,16 +5760,16 @@
         <v>54</v>
       </c>
       <c r="K35" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L35" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M35" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N35" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O35">
         <v>1</v>
@@ -5763,19 +5778,16 @@
         <v>38</v>
       </c>
       <c r="Q35">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R35">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y35" t="s">
-        <v>717</v>
-      </c>
-      <c r="Z35" t="s">
-        <v>51</v>
+        <v>778</v>
       </c>
       <c r="AA35" t="s">
-        <v>718</v>
+        <v>779</v>
       </c>
       <c r="AB35" t="s">
         <v>39</v>
@@ -5789,16 +5801,16 @@
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="C36" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="D36" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="E36" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F36" t="s">
         <v>34</v>
@@ -5813,16 +5825,16 @@
         <v>54</v>
       </c>
       <c r="K36" t="s">
-        <v>722</v>
+        <v>72</v>
       </c>
       <c r="L36" t="s">
-        <v>723</v>
+        <v>73</v>
       </c>
       <c r="M36" t="s">
-        <v>724</v>
+        <v>74</v>
       </c>
       <c r="N36" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O36">
         <v>1</v>
@@ -5831,19 +5843,19 @@
         <v>38</v>
       </c>
       <c r="Q36">
-        <v>12.99</v>
+        <v>11.99</v>
       </c>
       <c r="R36">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="Y36" t="s">
-        <v>725</v>
+        <v>717</v>
       </c>
       <c r="Z36" t="s">
-        <v>726</v>
+        <v>51</v>
       </c>
       <c r="AA36" t="s">
-        <v>727</v>
+        <v>718</v>
       </c>
       <c r="AB36" t="s">
         <v>39</v>
@@ -5857,13 +5869,13 @@
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>728</v>
+        <v>719</v>
       </c>
       <c r="C37" t="s">
-        <v>729</v>
+        <v>720</v>
       </c>
       <c r="D37" t="s">
-        <v>730</v>
+        <v>721</v>
       </c>
       <c r="E37" t="s">
         <v>33</v>
@@ -5881,13 +5893,13 @@
         <v>54</v>
       </c>
       <c r="K37" t="s">
-        <v>72</v>
+        <v>722</v>
       </c>
       <c r="L37" t="s">
-        <v>73</v>
+        <v>723</v>
       </c>
       <c r="M37" t="s">
-        <v>74</v>
+        <v>724</v>
       </c>
       <c r="N37" t="s">
         <v>33</v>
@@ -5899,16 +5911,19 @@
         <v>38</v>
       </c>
       <c r="Q37">
-        <v>11.99</v>
+        <v>12.99</v>
       </c>
       <c r="R37">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="Y37" t="s">
-        <v>731</v>
+        <v>725</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>726</v>
       </c>
       <c r="AA37" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="AB37" t="s">
         <v>39</v>
@@ -5922,13 +5937,13 @@
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="C38" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="D38" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="E38" t="s">
         <v>33</v>
@@ -5946,13 +5961,13 @@
         <v>54</v>
       </c>
       <c r="K38" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="L38" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="M38" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="N38" t="s">
         <v>33</v>
@@ -5964,16 +5979,16 @@
         <v>38</v>
       </c>
       <c r="Q38">
-        <v>40.99</v>
+        <v>11.99</v>
       </c>
       <c r="R38">
-        <v>6.83</v>
+        <v>2</v>
       </c>
       <c r="Y38" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="AA38" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="AB38" t="s">
         <v>39</v>
@@ -5987,13 +6002,13 @@
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="C39" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="D39" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="E39" t="s">
         <v>33</v>
@@ -6011,13 +6026,13 @@
         <v>54</v>
       </c>
       <c r="K39" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="L39" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="M39" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="N39" t="s">
         <v>33</v>
@@ -6035,10 +6050,10 @@
         <v>6.83</v>
       </c>
       <c r="Y39" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="AA39" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="AB39" t="s">
         <v>39</v>
@@ -6052,13 +6067,13 @@
     </row>
     <row r="40" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>708</v>
+        <v>738</v>
       </c>
       <c r="C40" t="s">
-        <v>709</v>
+        <v>739</v>
       </c>
       <c r="D40" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="E40" t="s">
         <v>33</v>
@@ -6076,13 +6091,13 @@
         <v>54</v>
       </c>
       <c r="K40" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L40" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M40" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N40" t="s">
         <v>33</v>
@@ -6094,19 +6109,16 @@
         <v>38</v>
       </c>
       <c r="Q40">
-        <v>65.989999999999995</v>
+        <v>40.99</v>
       </c>
       <c r="R40">
-        <v>11</v>
+        <v>6.83</v>
       </c>
       <c r="Y40" t="s">
-        <v>711</v>
-      </c>
-      <c r="Z40" t="s">
-        <v>712</v>
+        <v>741</v>
       </c>
       <c r="AA40" t="s">
-        <v>713</v>
+        <v>742</v>
       </c>
       <c r="AB40" t="s">
         <v>39</v>
@@ -6120,13 +6132,13 @@
     </row>
     <row r="41" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>643</v>
+        <v>708</v>
       </c>
       <c r="C41" t="s">
-        <v>644</v>
+        <v>709</v>
       </c>
       <c r="D41" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E41" t="s">
         <v>33</v>
@@ -6144,13 +6156,13 @@
         <v>54</v>
       </c>
       <c r="K41" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L41" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M41" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="N41" t="s">
         <v>33</v>
@@ -6162,16 +6174,19 @@
         <v>38</v>
       </c>
       <c r="Q41">
-        <v>14.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R41">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="Y41" t="s">
-        <v>646</v>
+        <v>711</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>712</v>
       </c>
       <c r="AA41" t="s">
-        <v>647</v>
+        <v>713</v>
       </c>
       <c r="AB41" t="s">
         <v>39</v>
@@ -6185,16 +6200,16 @@
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>708</v>
+        <v>643</v>
       </c>
       <c r="C42" t="s">
-        <v>709</v>
+        <v>644</v>
       </c>
       <c r="D42" t="s">
-        <v>710</v>
+        <v>744</v>
       </c>
       <c r="E42" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F42" t="s">
         <v>34</v>
@@ -6209,16 +6224,16 @@
         <v>54</v>
       </c>
       <c r="K42" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L42" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M42" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="N42" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O42">
         <v>1</v>
@@ -6227,19 +6242,16 @@
         <v>38</v>
       </c>
       <c r="Q42">
-        <v>65.989999999999995</v>
+        <v>14.99</v>
       </c>
       <c r="R42">
-        <v>11</v>
+        <v>2.5</v>
       </c>
       <c r="Y42" t="s">
-        <v>711</v>
-      </c>
-      <c r="Z42" t="s">
-        <v>712</v>
+        <v>646</v>
       </c>
       <c r="AA42" t="s">
-        <v>713</v>
+        <v>647</v>
       </c>
       <c r="AB42" t="s">
         <v>39</v>
@@ -6253,22 +6265,22 @@
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>138</v>
+        <v>708</v>
       </c>
       <c r="C43" t="s">
-        <v>139</v>
+        <v>709</v>
       </c>
       <c r="D43" t="s">
-        <v>187</v>
+        <v>710</v>
       </c>
       <c r="E43" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="F43" t="s">
         <v>34</v>
       </c>
       <c r="G43" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="H43" t="s">
         <v>36</v>
@@ -6277,25 +6289,40 @@
         <v>54</v>
       </c>
       <c r="K43" t="s">
-        <v>141</v>
+        <v>40</v>
       </c>
       <c r="L43" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="M43" t="s">
-        <v>143</v>
+        <v>42</v>
+      </c>
+      <c r="N43" t="s">
+        <v>99</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P43" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q43">
+        <v>65.989999999999995</v>
+      </c>
+      <c r="R43">
+        <v>11</v>
       </c>
       <c r="Y43" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA43">
-        <v>80100</v>
+        <v>711</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>712</v>
+      </c>
+      <c r="AA43" t="s">
+        <v>713</v>
       </c>
       <c r="AB43" t="s">
-        <v>145</v>
+        <v>39</v>
       </c>
       <c r="AD43" t="b">
         <v>0</v>
@@ -6306,13 +6333,13 @@
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C44" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D44" t="s">
-        <v>148</v>
+        <v>187</v>
       </c>
       <c r="E44" t="s">
         <v>53</v>
@@ -6359,13 +6386,13 @@
     </row>
     <row r="45" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>632</v>
+        <v>146</v>
       </c>
       <c r="C45" t="s">
-        <v>633</v>
+        <v>147</v>
       </c>
       <c r="D45" t="s">
-        <v>634</v>
+        <v>148</v>
       </c>
       <c r="E45" t="s">
         <v>53</v>
@@ -6374,7 +6401,7 @@
         <v>34</v>
       </c>
       <c r="G45" t="s">
-        <v>635</v>
+        <v>140</v>
       </c>
       <c r="H45" t="s">
         <v>36</v>
@@ -6383,37 +6410,25 @@
         <v>54</v>
       </c>
       <c r="K45" t="s">
-        <v>636</v>
+        <v>141</v>
       </c>
       <c r="L45" t="s">
-        <v>637</v>
+        <v>142</v>
       </c>
       <c r="M45" t="s">
-        <v>638</v>
+        <v>143</v>
       </c>
       <c r="O45">
         <v>0</v>
       </c>
-      <c r="P45" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q45">
-        <v>22.9</v>
-      </c>
-      <c r="R45">
-        <v>4.8099999999999996</v>
-      </c>
       <c r="Y45" t="s">
-        <v>639</v>
-      </c>
-      <c r="Z45" t="s">
-        <v>640</v>
-      </c>
-      <c r="AA45" t="s">
-        <v>641</v>
+        <v>144</v>
+      </c>
+      <c r="AA45">
+        <v>80100</v>
       </c>
       <c r="AB45" t="s">
-        <v>642</v>
+        <v>145</v>
       </c>
       <c r="AD45" t="b">
         <v>0</v>
@@ -6424,22 +6439,22 @@
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>643</v>
+        <v>632</v>
       </c>
       <c r="C46" t="s">
-        <v>644</v>
+        <v>633</v>
       </c>
       <c r="D46" t="s">
-        <v>645</v>
+        <v>634</v>
       </c>
       <c r="E46" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="F46" t="s">
         <v>34</v>
       </c>
       <c r="G46" t="s">
-        <v>35</v>
+        <v>635</v>
       </c>
       <c r="H46" t="s">
         <v>36</v>
@@ -6448,37 +6463,37 @@
         <v>54</v>
       </c>
       <c r="K46" t="s">
-        <v>94</v>
+        <v>636</v>
       </c>
       <c r="L46" t="s">
-        <v>82</v>
+        <v>637</v>
       </c>
       <c r="M46" t="s">
-        <v>83</v>
-      </c>
-      <c r="N46" t="s">
-        <v>99</v>
+        <v>638</v>
       </c>
       <c r="O46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P46" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="Q46">
-        <v>14.99</v>
+        <v>22.9</v>
       </c>
       <c r="R46">
-        <v>2.5</v>
+        <v>4.8099999999999996</v>
       </c>
       <c r="Y46" t="s">
-        <v>646</v>
+        <v>639</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>640</v>
       </c>
       <c r="AA46" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="AB46" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="AD46" t="b">
         <v>0</v>
@@ -6489,16 +6504,16 @@
     </row>
     <row r="47" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>609</v>
+        <v>643</v>
       </c>
       <c r="C47" t="s">
-        <v>610</v>
+        <v>644</v>
       </c>
       <c r="D47" t="s">
-        <v>611</v>
+        <v>645</v>
       </c>
       <c r="E47" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F47" t="s">
         <v>34</v>
@@ -6522,7 +6537,7 @@
         <v>83</v>
       </c>
       <c r="N47" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O47">
         <v>1</v>
@@ -6537,13 +6552,10 @@
         <v>2.5</v>
       </c>
       <c r="Y47" t="s">
-        <v>612</v>
-      </c>
-      <c r="Z47" t="s">
-        <v>613</v>
+        <v>646</v>
       </c>
       <c r="AA47" t="s">
-        <v>614</v>
+        <v>647</v>
       </c>
       <c r="AB47" t="s">
         <v>39</v>
@@ -6557,16 +6569,16 @@
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>493</v>
+        <v>609</v>
       </c>
       <c r="C48" t="s">
-        <v>494</v>
+        <v>610</v>
       </c>
       <c r="D48" t="s">
-        <v>648</v>
+        <v>611</v>
       </c>
       <c r="E48" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F48" t="s">
         <v>34</v>
@@ -6581,22 +6593,37 @@
         <v>54</v>
       </c>
       <c r="K48" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L48" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M48" t="s">
-        <v>42</v>
+        <v>83</v>
+      </c>
+      <c r="N48" t="s">
+        <v>33</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P48" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q48">
+        <v>14.99</v>
+      </c>
+      <c r="R48">
+        <v>2.5</v>
       </c>
       <c r="Y48" t="s">
-        <v>495</v>
+        <v>612</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>613</v>
       </c>
       <c r="AA48" t="s">
-        <v>496</v>
+        <v>614</v>
       </c>
       <c r="AB48" t="s">
         <v>39</v>
@@ -6610,16 +6637,16 @@
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>615</v>
+        <v>493</v>
       </c>
       <c r="C49" t="s">
-        <v>616</v>
+        <v>494</v>
       </c>
       <c r="D49" t="s">
-        <v>617</v>
+        <v>648</v>
       </c>
       <c r="E49" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="F49" t="s">
         <v>34</v>
@@ -6634,34 +6661,22 @@
         <v>54</v>
       </c>
       <c r="K49" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L49" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M49" t="s">
-        <v>50</v>
-      </c>
-      <c r="N49" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="O49">
-        <v>1</v>
-      </c>
-      <c r="P49" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q49">
-        <v>40.99</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="s">
-        <v>618</v>
-      </c>
-      <c r="Z49" t="s">
-        <v>619</v>
+        <v>495</v>
       </c>
       <c r="AA49" t="s">
-        <v>620</v>
+        <v>496</v>
       </c>
       <c r="AB49" t="s">
         <v>39</v>
@@ -6675,16 +6690,16 @@
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="C50" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="D50" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="E50" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F50" t="s">
         <v>34</v>
@@ -6699,16 +6714,16 @@
         <v>54</v>
       </c>
       <c r="K50" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L50" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M50" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N50" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O50">
         <v>1</v>
@@ -6717,25 +6732,16 @@
         <v>38</v>
       </c>
       <c r="Q50">
-        <v>64.989999999999995</v>
-      </c>
-      <c r="R50">
-        <v>10.83</v>
-      </c>
-      <c r="S50">
-        <v>6.99</v>
-      </c>
-      <c r="T50">
-        <v>1.17</v>
+        <v>40.99</v>
       </c>
       <c r="Y50" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="Z50" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="AA50" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="AB50" t="s">
         <v>39</v>
@@ -6749,13 +6755,13 @@
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="C51" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="D51" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="E51" t="s">
         <v>33</v>
@@ -6773,13 +6779,13 @@
         <v>54</v>
       </c>
       <c r="K51" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L51" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M51" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N51" t="s">
         <v>33</v>
@@ -6791,16 +6797,25 @@
         <v>38</v>
       </c>
       <c r="Q51">
-        <v>11.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R51">
-        <v>2</v>
+        <v>10.83</v>
+      </c>
+      <c r="S51">
+        <v>6.99</v>
+      </c>
+      <c r="T51">
+        <v>1.17</v>
       </c>
       <c r="Y51" t="s">
-        <v>630</v>
+        <v>624</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>625</v>
       </c>
       <c r="AA51" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="AB51" t="s">
         <v>39</v>
@@ -6814,13 +6829,13 @@
     </row>
     <row r="52" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>649</v>
+        <v>627</v>
       </c>
       <c r="C52" t="s">
-        <v>650</v>
+        <v>628</v>
       </c>
       <c r="D52" t="s">
-        <v>651</v>
+        <v>629</v>
       </c>
       <c r="E52" t="s">
         <v>33</v>
@@ -6838,13 +6853,13 @@
         <v>54</v>
       </c>
       <c r="K52" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L52" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M52" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="N52" t="s">
         <v>33</v>
@@ -6856,19 +6871,16 @@
         <v>38</v>
       </c>
       <c r="Q52">
-        <v>39.99</v>
+        <v>11.99</v>
       </c>
       <c r="R52">
-        <v>6.67</v>
+        <v>2</v>
       </c>
       <c r="Y52" t="s">
-        <v>652</v>
-      </c>
-      <c r="Z52" t="s">
-        <v>653</v>
+        <v>630</v>
       </c>
       <c r="AA52" t="s">
-        <v>654</v>
+        <v>631</v>
       </c>
       <c r="AB52" t="s">
         <v>39</v>
@@ -6882,13 +6894,13 @@
     </row>
     <row r="53" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="C53" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="D53" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="E53" t="s">
         <v>33</v>
@@ -6906,13 +6918,13 @@
         <v>54</v>
       </c>
       <c r="K53" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="L53" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="M53" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="N53" t="s">
         <v>33</v>
@@ -6924,16 +6936,19 @@
         <v>38</v>
       </c>
       <c r="Q53">
-        <v>14.99</v>
+        <v>39.99</v>
       </c>
       <c r="R53">
-        <v>2.5</v>
+        <v>6.67</v>
       </c>
       <c r="Y53" t="s">
-        <v>658</v>
+        <v>652</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>653</v>
       </c>
       <c r="AA53" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="AB53" t="s">
         <v>39</v>
@@ -6947,13 +6962,13 @@
     </row>
     <row r="54" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>571</v>
+        <v>655</v>
       </c>
       <c r="C54" t="s">
-        <v>572</v>
+        <v>656</v>
       </c>
       <c r="D54" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="E54" t="s">
         <v>33</v>
@@ -6971,13 +6986,13 @@
         <v>54</v>
       </c>
       <c r="K54" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L54" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M54" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="N54" t="s">
         <v>33</v>
@@ -6989,16 +7004,16 @@
         <v>38</v>
       </c>
       <c r="Q54">
-        <v>64.989999999999995</v>
+        <v>14.99</v>
       </c>
       <c r="R54">
-        <v>10.83</v>
+        <v>2.5</v>
       </c>
       <c r="Y54" t="s">
-        <v>573</v>
+        <v>658</v>
       </c>
       <c r="AA54" t="s">
-        <v>574</v>
+        <v>659</v>
       </c>
       <c r="AB54" t="s">
         <v>39</v>
@@ -7012,13 +7027,13 @@
     </row>
     <row r="55" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>599</v>
+        <v>571</v>
       </c>
       <c r="C55" t="s">
-        <v>600</v>
+        <v>572</v>
       </c>
       <c r="D55" t="s">
-        <v>601</v>
+        <v>660</v>
       </c>
       <c r="E55" t="s">
         <v>33</v>
@@ -7036,13 +7051,13 @@
         <v>54</v>
       </c>
       <c r="K55" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L55" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M55" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="N55" t="s">
         <v>33</v>
@@ -7054,16 +7069,16 @@
         <v>38</v>
       </c>
       <c r="Q55">
-        <v>14.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R55">
-        <v>2.5</v>
+        <v>10.83</v>
       </c>
       <c r="Y55" t="s">
-        <v>61</v>
+        <v>573</v>
       </c>
       <c r="AA55" t="s">
-        <v>602</v>
+        <v>574</v>
       </c>
       <c r="AB55" t="s">
         <v>39</v>
@@ -7077,13 +7092,13 @@
     </row>
     <row r="56" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>589</v>
+        <v>599</v>
       </c>
       <c r="C56" t="s">
-        <v>590</v>
+        <v>600</v>
       </c>
       <c r="D56" t="s">
-        <v>591</v>
+        <v>601</v>
       </c>
       <c r="E56" t="s">
         <v>33</v>
@@ -7101,13 +7116,13 @@
         <v>54</v>
       </c>
       <c r="K56" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L56" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M56" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="N56" t="s">
         <v>33</v>
@@ -7119,16 +7134,16 @@
         <v>38</v>
       </c>
       <c r="Q56">
-        <v>64.989999999999995</v>
+        <v>14.99</v>
       </c>
       <c r="R56">
-        <v>10.83</v>
+        <v>2.5</v>
       </c>
       <c r="Y56" t="s">
-        <v>592</v>
+        <v>61</v>
       </c>
       <c r="AA56" t="s">
-        <v>593</v>
+        <v>602</v>
       </c>
       <c r="AB56" t="s">
         <v>39</v>
@@ -7142,13 +7157,13 @@
     </row>
     <row r="57" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="C57" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="D57" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="E57" t="s">
         <v>33</v>
@@ -7190,10 +7205,10 @@
         <v>10.83</v>
       </c>
       <c r="Y57" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="AA57" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="AB57" t="s">
         <v>39</v>
@@ -7207,13 +7222,13 @@
     </row>
     <row r="58" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="C58" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="D58" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="E58" t="s">
         <v>33</v>
@@ -7255,13 +7270,10 @@
         <v>10.83</v>
       </c>
       <c r="Y58" t="s">
-        <v>606</v>
-      </c>
-      <c r="Z58" t="s">
-        <v>607</v>
+        <v>597</v>
       </c>
       <c r="AA58" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="AB58" t="s">
         <v>39</v>
@@ -7275,13 +7287,13 @@
     </row>
     <row r="59" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>578</v>
+        <v>603</v>
       </c>
       <c r="C59" t="s">
-        <v>579</v>
+        <v>604</v>
       </c>
       <c r="D59" t="s">
-        <v>661</v>
+        <v>605</v>
       </c>
       <c r="E59" t="s">
         <v>33</v>
@@ -7323,13 +7335,13 @@
         <v>10.83</v>
       </c>
       <c r="Y59" t="s">
-        <v>580</v>
+        <v>606</v>
       </c>
       <c r="Z59" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="AA59" t="s">
-        <v>582</v>
+        <v>608</v>
       </c>
       <c r="AB59" t="s">
         <v>39</v>
@@ -7343,16 +7355,16 @@
     </row>
     <row r="60" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="C60" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="D60" t="s">
-        <v>577</v>
+        <v>661</v>
       </c>
       <c r="E60" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F60" t="s">
         <v>34</v>
@@ -7375,14 +7387,29 @@
       <c r="M60" t="s">
         <v>42</v>
       </c>
+      <c r="N60" t="s">
+        <v>33</v>
+      </c>
       <c r="O60">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P60" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q60">
+        <v>64.989999999999995</v>
+      </c>
+      <c r="R60">
+        <v>10.83</v>
       </c>
       <c r="Y60" t="s">
-        <v>573</v>
+        <v>580</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>581</v>
       </c>
       <c r="AA60" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="AB60" t="s">
         <v>39</v>
@@ -7396,16 +7423,16 @@
     </row>
     <row r="61" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>518</v>
+        <v>575</v>
       </c>
       <c r="C61" t="s">
-        <v>519</v>
+        <v>576</v>
       </c>
       <c r="D61" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="E61" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F61" t="s">
         <v>34</v>
@@ -7420,40 +7447,22 @@
         <v>54</v>
       </c>
       <c r="K61" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L61" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M61" t="s">
-        <v>50</v>
-      </c>
-      <c r="N61" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O61">
-        <v>1</v>
-      </c>
-      <c r="P61" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q61">
-        <v>37.99</v>
-      </c>
-      <c r="R61">
-        <v>6.33</v>
-      </c>
-      <c r="S61">
-        <v>6.99</v>
-      </c>
-      <c r="T61">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Y61" t="s">
-        <v>46</v>
+        <v>573</v>
       </c>
       <c r="AA61" t="s">
-        <v>520</v>
+        <v>574</v>
       </c>
       <c r="AB61" t="s">
         <v>39</v>
@@ -7467,13 +7476,13 @@
     </row>
     <row r="62" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>584</v>
+        <v>518</v>
       </c>
       <c r="C62" t="s">
-        <v>585</v>
+        <v>519</v>
       </c>
       <c r="D62" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="E62" t="s">
         <v>33</v>
@@ -7491,13 +7500,13 @@
         <v>54</v>
       </c>
       <c r="K62" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L62" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M62" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N62" t="s">
         <v>33</v>
@@ -7509,16 +7518,22 @@
         <v>38</v>
       </c>
       <c r="Q62">
-        <v>64.989999999999995</v>
+        <v>37.99</v>
       </c>
       <c r="R62">
-        <v>10.83</v>
+        <v>6.33</v>
+      </c>
+      <c r="S62">
+        <v>6.99</v>
+      </c>
+      <c r="T62">
+        <v>1.17</v>
       </c>
       <c r="Y62" t="s">
-        <v>587</v>
+        <v>46</v>
       </c>
       <c r="AA62" t="s">
-        <v>588</v>
+        <v>520</v>
       </c>
       <c r="AB62" t="s">
         <v>39</v>
@@ -7532,13 +7547,13 @@
     </row>
     <row r="63" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>457</v>
+        <v>584</v>
       </c>
       <c r="C63" t="s">
-        <v>458</v>
+        <v>585</v>
       </c>
       <c r="D63" t="s">
-        <v>459</v>
+        <v>586</v>
       </c>
       <c r="E63" t="s">
         <v>33</v>
@@ -7580,13 +7595,10 @@
         <v>10.83</v>
       </c>
       <c r="Y63" t="s">
-        <v>460</v>
-      </c>
-      <c r="Z63" t="s">
-        <v>279</v>
+        <v>587</v>
       </c>
       <c r="AA63" t="s">
-        <v>461</v>
+        <v>588</v>
       </c>
       <c r="AB63" t="s">
         <v>39</v>
@@ -7600,10 +7612,10 @@
     </row>
     <row r="64" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="C64" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="D64" t="s">
         <v>459</v>
@@ -7648,10 +7660,13 @@
         <v>10.83</v>
       </c>
       <c r="Y64" t="s">
-        <v>56</v>
+        <v>460</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>279</v>
       </c>
       <c r="AA64" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AB64" t="s">
         <v>39</v>
@@ -7665,13 +7680,13 @@
     </row>
     <row r="65" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C65" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="D65" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="E65" t="s">
         <v>33</v>
@@ -7689,34 +7704,34 @@
         <v>54</v>
       </c>
       <c r="K65" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L65" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M65" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N65" t="s">
         <v>33</v>
       </c>
       <c r="O65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P65" t="s">
         <v>38</v>
       </c>
       <c r="Q65">
-        <v>79.98</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R65">
-        <v>13.34</v>
+        <v>10.83</v>
       </c>
       <c r="Y65" t="s">
-        <v>468</v>
+        <v>56</v>
       </c>
       <c r="AA65" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="AB65" t="s">
         <v>39</v>
@@ -7730,13 +7745,13 @@
     </row>
     <row r="66" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="C66" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="D66" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="E66" t="s">
         <v>33</v>
@@ -7766,22 +7781,22 @@
         <v>33</v>
       </c>
       <c r="O66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P66" t="s">
         <v>38</v>
       </c>
       <c r="Q66">
-        <v>37.99</v>
+        <v>79.98</v>
       </c>
       <c r="R66">
-        <v>6.33</v>
+        <v>13.34</v>
       </c>
       <c r="Y66" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="AA66" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="AB66" t="s">
         <v>39</v>
@@ -7795,16 +7810,16 @@
     </row>
     <row r="67" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="C67" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="D67" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="E67" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F67" t="s">
         <v>34</v>
@@ -7819,25 +7834,34 @@
         <v>54</v>
       </c>
       <c r="K67" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L67" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M67" t="s">
-        <v>42</v>
+        <v>50</v>
+      </c>
+      <c r="N67" t="s">
+        <v>33</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P67" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q67">
+        <v>37.99</v>
+      </c>
+      <c r="R67">
+        <v>6.33</v>
       </c>
       <c r="Y67" t="s">
-        <v>478</v>
-      </c>
-      <c r="Z67" t="s">
-        <v>279</v>
+        <v>473</v>
       </c>
       <c r="AA67" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="AB67" t="s">
         <v>39</v>
@@ -7851,16 +7875,16 @@
     </row>
     <row r="68" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="C68" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="D68" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="E68" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F68" t="s">
         <v>34</v>
@@ -7875,34 +7899,25 @@
         <v>54</v>
       </c>
       <c r="K68" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L68" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M68" t="s">
-        <v>74</v>
-      </c>
-      <c r="N68" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O68">
-        <v>1</v>
-      </c>
-      <c r="P68" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q68">
-        <v>11.99</v>
-      </c>
-      <c r="R68">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y68" t="s">
-        <v>61</v>
+        <v>478</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>279</v>
       </c>
       <c r="AA68" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="AB68" t="s">
         <v>39</v>
@@ -7916,13 +7931,13 @@
     </row>
     <row r="69" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="C69" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="D69" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="E69" t="s">
         <v>33</v>
@@ -7940,13 +7955,13 @@
         <v>54</v>
       </c>
       <c r="K69" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L69" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M69" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N69" t="s">
         <v>33</v>
@@ -7958,16 +7973,16 @@
         <v>38</v>
       </c>
       <c r="Q69">
-        <v>64.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R69">
-        <v>10.83</v>
+        <v>2</v>
       </c>
       <c r="Y69" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="AA69" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="AB69" t="s">
         <v>39</v>
@@ -7981,13 +7996,13 @@
     </row>
     <row r="70" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="C70" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D70" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="E70" t="s">
         <v>33</v>
@@ -8005,37 +8020,34 @@
         <v>54</v>
       </c>
       <c r="K70" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L70" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M70" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N70" t="s">
         <v>33</v>
       </c>
       <c r="O70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P70" t="s">
         <v>38</v>
       </c>
       <c r="Q70">
-        <v>79.98</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R70">
-        <v>13.34</v>
+        <v>10.83</v>
       </c>
       <c r="Y70" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z70" t="s">
-        <v>491</v>
+        <v>67</v>
       </c>
       <c r="AA70" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="AB70" t="s">
         <v>39</v>
@@ -8049,13 +8061,13 @@
     </row>
     <row r="71" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="C71" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="D71" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="E71" t="s">
         <v>33</v>
@@ -8073,37 +8085,37 @@
         <v>54</v>
       </c>
       <c r="K71" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L71" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M71" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N71" t="s">
         <v>33</v>
       </c>
       <c r="O71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P71" t="s">
         <v>38</v>
       </c>
       <c r="Q71">
-        <v>59.99</v>
+        <v>79.98</v>
       </c>
       <c r="R71">
-        <v>10</v>
+        <v>13.34</v>
       </c>
       <c r="Y71" t="s">
-        <v>500</v>
+        <v>63</v>
       </c>
       <c r="Z71" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="AA71" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="AB71" t="s">
         <v>39</v>
@@ -8117,10 +8129,10 @@
     </row>
     <row r="72" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="C72" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="D72" t="s">
         <v>499</v>
@@ -8165,13 +8177,13 @@
         <v>10</v>
       </c>
       <c r="Y72" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="Z72" t="s">
-        <v>93</v>
+        <v>501</v>
       </c>
       <c r="AA72" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="AB72" t="s">
         <v>39</v>
@@ -8185,13 +8197,13 @@
     </row>
     <row r="73" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="C73" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="D73" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="E73" t="s">
         <v>33</v>
@@ -8233,10 +8245,13 @@
         <v>10</v>
       </c>
       <c r="Y73" t="s">
-        <v>510</v>
+        <v>505</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>93</v>
       </c>
       <c r="AA73" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="AB73" t="s">
         <v>39</v>
@@ -8250,13 +8265,13 @@
     </row>
     <row r="74" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="C74" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="D74" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="E74" t="s">
         <v>33</v>
@@ -8298,13 +8313,10 @@
         <v>10</v>
       </c>
       <c r="Y74" t="s">
-        <v>515</v>
-      </c>
-      <c r="Z74" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="AA74" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="AB74" t="s">
         <v>39</v>
@@ -8318,13 +8330,13 @@
     </row>
     <row r="75" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="C75" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="D75" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="E75" t="s">
         <v>33</v>
@@ -8342,13 +8354,13 @@
         <v>54</v>
       </c>
       <c r="K75" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L75" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M75" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="N75" t="s">
         <v>33</v>
@@ -8360,16 +8372,19 @@
         <v>38</v>
       </c>
       <c r="Q75">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R75">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y75" t="s">
-        <v>58</v>
+        <v>515</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>516</v>
       </c>
       <c r="AA75" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="AB75" t="s">
         <v>39</v>
@@ -8383,13 +8398,13 @@
     </row>
     <row r="76" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="C76" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="D76" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="E76" t="s">
         <v>33</v>
@@ -8407,13 +8422,13 @@
         <v>54</v>
       </c>
       <c r="K76" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L76" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M76" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="N76" t="s">
         <v>33</v>
@@ -8425,16 +8440,16 @@
         <v>38</v>
       </c>
       <c r="Q76">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="R76">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="Y76" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="AA76" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="AB76" t="s">
         <v>39</v>
@@ -8448,10 +8463,10 @@
     </row>
     <row r="77" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="C77" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="D77" t="s">
         <v>527</v>
@@ -8496,10 +8511,10 @@
         <v>10</v>
       </c>
       <c r="Y77" t="s">
-        <v>531</v>
+        <v>90</v>
       </c>
       <c r="AA77" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="AB77" t="s">
         <v>39</v>
@@ -8513,13 +8528,13 @@
     </row>
     <row r="78" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="C78" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="D78" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="E78" t="s">
         <v>33</v>
@@ -8537,13 +8552,13 @@
         <v>54</v>
       </c>
       <c r="K78" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L78" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M78" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N78" t="s">
         <v>33</v>
@@ -8555,19 +8570,16 @@
         <v>38</v>
       </c>
       <c r="Q78">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R78">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y78" t="s">
-        <v>536</v>
-      </c>
-      <c r="Z78" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="AA78" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="AB78" t="s">
         <v>39</v>
@@ -8581,13 +8593,13 @@
     </row>
     <row r="79" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="C79" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="D79" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="E79" t="s">
         <v>33</v>
@@ -8605,13 +8617,13 @@
         <v>54</v>
       </c>
       <c r="K79" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L79" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M79" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N79" t="s">
         <v>33</v>
@@ -8623,19 +8635,19 @@
         <v>38</v>
       </c>
       <c r="Q79">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R79">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y79" t="s">
-        <v>71</v>
+        <v>536</v>
       </c>
       <c r="Z79" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="AA79" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="AB79" t="s">
         <v>39</v>
@@ -8649,13 +8661,13 @@
     </row>
     <row r="80" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="C80" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="D80" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="E80" t="s">
         <v>33</v>
@@ -8673,37 +8685,37 @@
         <v>54</v>
       </c>
       <c r="K80" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L80" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M80" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N80" t="s">
         <v>33</v>
       </c>
       <c r="O80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P80" t="s">
         <v>38</v>
       </c>
       <c r="Q80">
-        <v>76.98</v>
+        <v>59.99</v>
       </c>
       <c r="R80">
-        <v>12.84</v>
+        <v>10</v>
       </c>
       <c r="Y80" t="s">
-        <v>547</v>
+        <v>71</v>
       </c>
       <c r="Z80" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="AA80" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="AB80" t="s">
         <v>39</v>
@@ -8717,13 +8729,13 @@
     </row>
     <row r="81" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="C81" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="D81" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="E81" t="s">
         <v>33</v>
@@ -8741,34 +8753,37 @@
         <v>54</v>
       </c>
       <c r="K81" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L81" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M81" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N81" t="s">
         <v>33</v>
       </c>
       <c r="O81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P81" t="s">
         <v>38</v>
       </c>
       <c r="Q81">
-        <v>59.99</v>
+        <v>76.98</v>
       </c>
       <c r="R81">
-        <v>10</v>
+        <v>12.84</v>
       </c>
       <c r="Y81" t="s">
-        <v>553</v>
+        <v>547</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>548</v>
       </c>
       <c r="AA81" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="AB81" t="s">
         <v>39</v>
@@ -8782,13 +8797,13 @@
     </row>
     <row r="82" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="C82" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="D82" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="E82" t="s">
         <v>33</v>
@@ -8830,10 +8845,10 @@
         <v>10</v>
       </c>
       <c r="Y82" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="AA82" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="AB82" t="s">
         <v>39</v>
@@ -8847,13 +8862,13 @@
     </row>
     <row r="83" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>418</v>
+        <v>555</v>
       </c>
       <c r="C83" t="s">
-        <v>419</v>
+        <v>556</v>
       </c>
       <c r="D83" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="E83" t="s">
         <v>33</v>
@@ -8895,10 +8910,10 @@
         <v>10</v>
       </c>
       <c r="Y83" t="s">
-        <v>420</v>
+        <v>558</v>
       </c>
       <c r="AA83" t="s">
-        <v>421</v>
+        <v>559</v>
       </c>
       <c r="AB83" t="s">
         <v>39</v>
@@ -8912,13 +8927,13 @@
     </row>
     <row r="84" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>561</v>
+        <v>418</v>
       </c>
       <c r="C84" t="s">
-        <v>562</v>
+        <v>419</v>
       </c>
       <c r="D84" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="E84" t="s">
         <v>33</v>
@@ -8960,13 +8975,10 @@
         <v>10</v>
       </c>
       <c r="Y84" t="s">
-        <v>564</v>
-      </c>
-      <c r="Z84" t="s">
-        <v>565</v>
+        <v>420</v>
       </c>
       <c r="AA84" t="s">
-        <v>566</v>
+        <v>421</v>
       </c>
       <c r="AB84" t="s">
         <v>39</v>
@@ -8980,13 +8992,13 @@
     </row>
     <row r="85" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="C85" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="D85" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="E85" t="s">
         <v>33</v>
@@ -9004,13 +9016,13 @@
         <v>54</v>
       </c>
       <c r="K85" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L85" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M85" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="N85" t="s">
         <v>33</v>
@@ -9022,16 +9034,19 @@
         <v>38</v>
       </c>
       <c r="Q85">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R85">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y85" t="s">
-        <v>69</v>
+        <v>564</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>565</v>
       </c>
       <c r="AA85" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="AB85" t="s">
         <v>39</v>
@@ -9045,13 +9060,13 @@
     </row>
     <row r="86" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>413</v>
+        <v>567</v>
       </c>
       <c r="C86" t="s">
-        <v>414</v>
+        <v>568</v>
       </c>
       <c r="D86" t="s">
-        <v>415</v>
+        <v>569</v>
       </c>
       <c r="E86" t="s">
         <v>33</v>
@@ -9069,13 +9084,13 @@
         <v>54</v>
       </c>
       <c r="K86" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L86" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M86" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="N86" t="s">
         <v>33</v>
@@ -9087,16 +9102,16 @@
         <v>38</v>
       </c>
       <c r="Q86">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="R86">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="Y86" t="s">
-        <v>416</v>
+        <v>69</v>
       </c>
       <c r="AA86" t="s">
-        <v>417</v>
+        <v>570</v>
       </c>
       <c r="AB86" t="s">
         <v>39</v>
@@ -9110,13 +9125,13 @@
     </row>
     <row r="87" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="C87" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="D87" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="E87" t="s">
         <v>33</v>
@@ -9134,13 +9149,13 @@
         <v>54</v>
       </c>
       <c r="K87" t="s">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="L87" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="M87" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="N87" t="s">
         <v>33</v>
@@ -9152,16 +9167,16 @@
         <v>38</v>
       </c>
       <c r="Q87">
-        <v>22.99</v>
+        <v>59.99</v>
       </c>
       <c r="R87">
-        <v>3.83</v>
+        <v>10</v>
       </c>
       <c r="Y87" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="AA87" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="AB87" t="s">
         <v>39</v>
@@ -9175,10 +9190,10 @@
     </row>
     <row r="88" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="C88" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="D88" t="s">
         <v>424</v>
@@ -9199,13 +9214,13 @@
         <v>54</v>
       </c>
       <c r="K88" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="L88" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="M88" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="N88" t="s">
         <v>33</v>
@@ -9217,19 +9232,16 @@
         <v>38</v>
       </c>
       <c r="Q88">
-        <v>11.99</v>
+        <v>22.99</v>
       </c>
       <c r="R88">
-        <v>2</v>
+        <v>3.83</v>
       </c>
       <c r="Y88" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z88" t="s">
-        <v>97</v>
+        <v>425</v>
       </c>
       <c r="AA88" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AB88" t="s">
         <v>39</v>
@@ -9243,13 +9255,13 @@
     </row>
     <row r="89" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C89" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D89" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="E89" t="s">
         <v>33</v>
@@ -9267,13 +9279,13 @@
         <v>54</v>
       </c>
       <c r="K89" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="L89" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="M89" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="N89" t="s">
         <v>33</v>
@@ -9285,19 +9297,19 @@
         <v>38</v>
       </c>
       <c r="Q89">
-        <v>38.49</v>
+        <v>11.99</v>
       </c>
       <c r="R89">
-        <v>6.42</v>
+        <v>2</v>
       </c>
       <c r="Y89" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="Z89" t="s">
-        <v>433</v>
+        <v>97</v>
       </c>
       <c r="AA89" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="AB89" t="s">
         <v>39</v>
@@ -9311,13 +9323,13 @@
     </row>
     <row r="90" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="C90" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="D90" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="E90" t="s">
         <v>33</v>
@@ -9335,13 +9347,13 @@
         <v>54</v>
       </c>
       <c r="K90" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="L90" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="M90" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="N90" t="s">
         <v>33</v>
@@ -9353,16 +9365,19 @@
         <v>38</v>
       </c>
       <c r="Q90">
-        <v>14.99</v>
+        <v>38.49</v>
       </c>
       <c r="R90">
-        <v>2.5</v>
+        <v>6.42</v>
       </c>
       <c r="Y90" t="s">
-        <v>438</v>
+        <v>59</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>433</v>
       </c>
       <c r="AA90" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="AB90" t="s">
         <v>39</v>
@@ -9376,13 +9391,13 @@
     </row>
     <row r="91" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C91" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D91" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="E91" t="s">
         <v>33</v>
@@ -9400,13 +9415,13 @@
         <v>54</v>
       </c>
       <c r="K91" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="L91" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="M91" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="N91" t="s">
         <v>33</v>
@@ -9418,16 +9433,16 @@
         <v>38</v>
       </c>
       <c r="Q91">
-        <v>37.99</v>
+        <v>14.99</v>
       </c>
       <c r="R91">
-        <v>6.33</v>
+        <v>2.5</v>
       </c>
       <c r="Y91" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="AA91" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="AB91" t="s">
         <v>39</v>
@@ -9441,13 +9456,13 @@
     </row>
     <row r="92" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C92" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="D92" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="E92" t="s">
         <v>33</v>
@@ -9465,13 +9480,13 @@
         <v>54</v>
       </c>
       <c r="K92" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L92" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M92" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N92" t="s">
         <v>33</v>
@@ -9483,16 +9498,16 @@
         <v>38</v>
       </c>
       <c r="Q92">
-        <v>59.99</v>
+        <v>37.99</v>
       </c>
       <c r="R92">
-        <v>10</v>
+        <v>6.33</v>
       </c>
       <c r="Y92" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="AA92" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="AB92" t="s">
         <v>39</v>
@@ -9506,16 +9521,16 @@
     </row>
     <row r="93" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="C93" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="D93" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E93" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F93" t="s">
         <v>34</v>
@@ -9538,14 +9553,26 @@
       <c r="M93" t="s">
         <v>42</v>
       </c>
+      <c r="N93" t="s">
+        <v>33</v>
+      </c>
       <c r="O93">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P93" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q93">
+        <v>59.99</v>
+      </c>
+      <c r="R93">
+        <v>10</v>
       </c>
       <c r="Y93" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="AA93" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="AB93" t="s">
         <v>39</v>
@@ -9559,16 +9586,16 @@
     </row>
     <row r="94" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>403</v>
+        <v>450</v>
       </c>
       <c r="C94" t="s">
-        <v>404</v>
+        <v>451</v>
       </c>
       <c r="D94" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E94" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F94" t="s">
         <v>34</v>
@@ -9591,32 +9618,14 @@
       <c r="M94" t="s">
         <v>42</v>
       </c>
-      <c r="N94" t="s">
-        <v>33</v>
-      </c>
       <c r="O94">
-        <v>1</v>
-      </c>
-      <c r="P94" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q94">
-        <v>59.99</v>
-      </c>
-      <c r="R94">
-        <v>10</v>
-      </c>
-      <c r="S94">
-        <v>5.99</v>
-      </c>
-      <c r="T94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y94" t="s">
-        <v>405</v>
+        <v>453</v>
       </c>
       <c r="AA94" t="s">
-        <v>406</v>
+        <v>454</v>
       </c>
       <c r="AB94" t="s">
         <v>39</v>
@@ -9630,13 +9639,13 @@
     </row>
     <row r="95" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C95" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D95" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E95" t="s">
         <v>33</v>
@@ -9654,13 +9663,13 @@
         <v>54</v>
       </c>
       <c r="K95" t="s">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="L95" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="M95" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="N95" t="s">
         <v>33</v>
@@ -9672,16 +9681,22 @@
         <v>38</v>
       </c>
       <c r="Q95">
-        <v>22.99</v>
+        <v>59.99</v>
       </c>
       <c r="R95">
-        <v>3.83</v>
+        <v>10</v>
+      </c>
+      <c r="S95">
+        <v>5.99</v>
+      </c>
+      <c r="T95">
+        <v>1</v>
       </c>
       <c r="Y95" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="AA95" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="AB95" t="s">
         <v>39</v>
@@ -9695,13 +9710,13 @@
     </row>
     <row r="96" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="C96" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="D96" t="s">
-        <v>411</v>
+        <v>456</v>
       </c>
       <c r="E96" t="s">
         <v>33</v>
@@ -9719,13 +9734,13 @@
         <v>54</v>
       </c>
       <c r="K96" t="s">
-        <v>340</v>
+        <v>79</v>
       </c>
       <c r="L96" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="M96" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
       <c r="N96" t="s">
         <v>33</v>
@@ -9737,16 +9752,16 @@
         <v>38</v>
       </c>
       <c r="Q96">
-        <v>44.99</v>
+        <v>22.99</v>
       </c>
       <c r="R96">
-        <v>7.5</v>
+        <v>3.83</v>
       </c>
       <c r="Y96" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="AA96" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="AB96" t="s">
         <v>39</v>
@@ -9760,13 +9775,13 @@
     </row>
     <row r="97" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="C97" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="D97" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E97" t="s">
         <v>33</v>
@@ -9808,13 +9823,10 @@
         <v>7.5</v>
       </c>
       <c r="Y97" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z97" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="AA97" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="AB97" t="s">
         <v>39</v>
@@ -9828,13 +9840,13 @@
     </row>
     <row r="98" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>338</v>
+        <v>394</v>
       </c>
       <c r="C98" t="s">
-        <v>339</v>
+        <v>395</v>
       </c>
       <c r="D98" t="s">
-        <v>662</v>
+        <v>412</v>
       </c>
       <c r="E98" t="s">
         <v>33</v>
@@ -9876,10 +9888,13 @@
         <v>7.5</v>
       </c>
       <c r="Y98" t="s">
-        <v>341</v>
+        <v>396</v>
+      </c>
+      <c r="Z98" t="s">
+        <v>397</v>
       </c>
       <c r="AA98" t="s">
-        <v>342</v>
+        <v>398</v>
       </c>
       <c r="AB98" t="s">
         <v>39</v>
@@ -9893,13 +9908,13 @@
     </row>
     <row r="99" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>663</v>
+        <v>338</v>
       </c>
       <c r="C99" t="s">
-        <v>664</v>
+        <v>339</v>
       </c>
       <c r="D99" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="E99" t="s">
         <v>33</v>
@@ -9917,13 +9932,13 @@
         <v>54</v>
       </c>
       <c r="K99" t="s">
-        <v>40</v>
+        <v>340</v>
       </c>
       <c r="L99" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="M99" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="N99" t="s">
         <v>33</v>
@@ -9935,25 +9950,22 @@
         <v>38</v>
       </c>
       <c r="Q99">
-        <v>59.99</v>
+        <v>44.99</v>
       </c>
       <c r="R99">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="Y99" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z99" t="s">
-        <v>666</v>
+        <v>341</v>
       </c>
       <c r="AA99" t="s">
-        <v>667</v>
+        <v>342</v>
       </c>
       <c r="AB99" t="s">
         <v>39</v>
       </c>
       <c r="AD99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG99" t="b">
         <v>0</v>
@@ -9961,13 +9973,13 @@
     </row>
     <row r="100" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>334</v>
+        <v>663</v>
       </c>
       <c r="C100" t="s">
-        <v>335</v>
+        <v>664</v>
       </c>
       <c r="D100" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="E100" t="s">
         <v>33</v>
@@ -9985,13 +9997,13 @@
         <v>54</v>
       </c>
       <c r="K100" t="s">
-        <v>203</v>
+        <v>40</v>
       </c>
       <c r="L100" t="s">
-        <v>204</v>
+        <v>41</v>
       </c>
       <c r="M100" t="s">
-        <v>205</v>
+        <v>42</v>
       </c>
       <c r="N100" t="s">
         <v>33</v>
@@ -10003,22 +10015,25 @@
         <v>38</v>
       </c>
       <c r="Q100">
-        <v>69.989999999999995</v>
+        <v>59.99</v>
       </c>
       <c r="R100">
-        <v>11.67</v>
+        <v>10</v>
       </c>
       <c r="Y100" t="s">
-        <v>336</v>
+        <v>62</v>
+      </c>
+      <c r="Z100" t="s">
+        <v>666</v>
       </c>
       <c r="AA100" t="s">
-        <v>337</v>
+        <v>667</v>
       </c>
       <c r="AB100" t="s">
         <v>39</v>
       </c>
       <c r="AD100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG100" t="b">
         <v>0</v>
@@ -10026,13 +10041,13 @@
     </row>
     <row r="101" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="C101" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="D101" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E101" t="s">
         <v>33</v>
@@ -10050,34 +10065,34 @@
         <v>54</v>
       </c>
       <c r="K101" t="s">
-        <v>48</v>
+        <v>203</v>
       </c>
       <c r="L101" t="s">
-        <v>49</v>
+        <v>204</v>
       </c>
       <c r="M101" t="s">
-        <v>50</v>
+        <v>205</v>
       </c>
       <c r="N101" t="s">
         <v>33</v>
       </c>
       <c r="O101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P101" t="s">
         <v>38</v>
       </c>
       <c r="Q101">
-        <v>75.98</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="R101">
-        <v>12.66</v>
+        <v>11.67</v>
       </c>
       <c r="Y101" t="s">
-        <v>91</v>
+        <v>336</v>
       </c>
       <c r="AA101" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="AB101" t="s">
         <v>39</v>
@@ -10091,13 +10106,13 @@
     </row>
     <row r="102" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="C102" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="D102" t="s">
-        <v>345</v>
+        <v>669</v>
       </c>
       <c r="E102" t="s">
         <v>33</v>
@@ -10115,34 +10130,34 @@
         <v>54</v>
       </c>
       <c r="K102" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L102" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M102" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N102" t="s">
         <v>33</v>
       </c>
       <c r="O102">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P102" t="s">
         <v>38</v>
       </c>
       <c r="Q102">
-        <v>59.99</v>
+        <v>75.98</v>
       </c>
       <c r="R102">
-        <v>10</v>
+        <v>12.66</v>
       </c>
       <c r="Y102" t="s">
-        <v>346</v>
+        <v>91</v>
       </c>
       <c r="AA102" t="s">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="AB102" t="s">
         <v>39</v>
@@ -10156,13 +10171,13 @@
     </row>
     <row r="103" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>288</v>
+        <v>343</v>
       </c>
       <c r="C103" t="s">
-        <v>289</v>
+        <v>344</v>
       </c>
       <c r="D103" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E103" t="s">
         <v>33</v>
@@ -10177,37 +10192,37 @@
         <v>36</v>
       </c>
       <c r="J103" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K103" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L103" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M103" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N103" t="s">
         <v>33</v>
       </c>
       <c r="O103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P103" t="s">
         <v>38</v>
       </c>
       <c r="Q103">
-        <v>75.98</v>
+        <v>59.99</v>
       </c>
       <c r="R103">
-        <v>12.66</v>
+        <v>10</v>
       </c>
       <c r="Y103" t="s">
-        <v>290</v>
+        <v>346</v>
       </c>
       <c r="AA103" t="s">
-        <v>291</v>
+        <v>347</v>
       </c>
       <c r="AB103" t="s">
         <v>39</v>
@@ -10221,13 +10236,13 @@
     </row>
     <row r="104" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>349</v>
+        <v>288</v>
       </c>
       <c r="C104" t="s">
-        <v>350</v>
+        <v>289</v>
       </c>
       <c r="D104" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="E104" t="s">
         <v>33</v>
@@ -10242,7 +10257,7 @@
         <v>36</v>
       </c>
       <c r="J104" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K104" t="s">
         <v>48</v>
@@ -10257,25 +10272,22 @@
         <v>33</v>
       </c>
       <c r="O104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P104" t="s">
         <v>38</v>
       </c>
       <c r="Q104">
-        <v>37.99</v>
+        <v>75.98</v>
       </c>
       <c r="R104">
-        <v>6.33</v>
+        <v>12.66</v>
       </c>
       <c r="Y104" t="s">
-        <v>352</v>
-      </c>
-      <c r="Z104" t="s">
-        <v>353</v>
+        <v>290</v>
       </c>
       <c r="AA104" t="s">
-        <v>354</v>
+        <v>291</v>
       </c>
       <c r="AB104" t="s">
         <v>39</v>
@@ -10289,13 +10301,13 @@
     </row>
     <row r="105" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="C105" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="D105" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="E105" t="s">
         <v>33</v>
@@ -10313,13 +10325,13 @@
         <v>54</v>
       </c>
       <c r="K105" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L105" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M105" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N105" t="s">
         <v>33</v>
@@ -10331,16 +10343,19 @@
         <v>38</v>
       </c>
       <c r="Q105">
-        <v>11.99</v>
+        <v>37.99</v>
       </c>
       <c r="R105">
-        <v>2</v>
+        <v>6.33</v>
       </c>
       <c r="Y105" t="s">
-        <v>58</v>
+        <v>352</v>
+      </c>
+      <c r="Z105" t="s">
+        <v>353</v>
       </c>
       <c r="AA105" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="AB105" t="s">
         <v>39</v>
@@ -10354,13 +10369,13 @@
     </row>
     <row r="106" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C106" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="D106" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="E106" t="s">
         <v>33</v>
@@ -10378,37 +10393,34 @@
         <v>54</v>
       </c>
       <c r="K106" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L106" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M106" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="N106" t="s">
         <v>33</v>
       </c>
       <c r="O106">
+        <v>1</v>
+      </c>
+      <c r="P106" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q106">
+        <v>11.99</v>
+      </c>
+      <c r="R106">
         <v>2</v>
       </c>
-      <c r="P106" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q106">
-        <v>75.98</v>
-      </c>
-      <c r="R106">
-        <v>12.66</v>
-      </c>
       <c r="Y106" t="s">
-        <v>101</v>
-      </c>
-      <c r="Z106" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="AA106" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="AB106" t="s">
         <v>39</v>
@@ -10422,13 +10434,13 @@
     </row>
     <row r="107" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="C107" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="D107" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="E107" t="s">
         <v>33</v>
@@ -10446,34 +10458,37 @@
         <v>54</v>
       </c>
       <c r="K107" t="s">
-        <v>260</v>
+        <v>48</v>
       </c>
       <c r="L107" t="s">
-        <v>261</v>
+        <v>49</v>
       </c>
       <c r="M107" t="s">
-        <v>262</v>
+        <v>50</v>
       </c>
       <c r="N107" t="s">
         <v>33</v>
       </c>
       <c r="O107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P107" t="s">
         <v>38</v>
       </c>
       <c r="Q107">
-        <v>24.49</v>
+        <v>75.98</v>
       </c>
       <c r="R107">
-        <v>4.08</v>
+        <v>12.66</v>
       </c>
       <c r="Y107" t="s">
-        <v>366</v>
+        <v>101</v>
+      </c>
+      <c r="Z107" t="s">
+        <v>59</v>
       </c>
       <c r="AA107" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="AB107" t="s">
         <v>39</v>
@@ -10487,13 +10502,13 @@
     </row>
     <row r="108" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>265</v>
+        <v>363</v>
       </c>
       <c r="C108" t="s">
-        <v>266</v>
+        <v>364</v>
       </c>
       <c r="D108" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="E108" t="s">
         <v>33</v>
@@ -10511,13 +10526,13 @@
         <v>54</v>
       </c>
       <c r="K108" t="s">
-        <v>48</v>
+        <v>260</v>
       </c>
       <c r="L108" t="s">
-        <v>49</v>
+        <v>261</v>
       </c>
       <c r="M108" t="s">
-        <v>50</v>
+        <v>262</v>
       </c>
       <c r="N108" t="s">
         <v>33</v>
@@ -10529,16 +10544,16 @@
         <v>38</v>
       </c>
       <c r="Q108">
-        <v>37.99</v>
+        <v>24.49</v>
       </c>
       <c r="R108">
-        <v>6.33</v>
+        <v>4.08</v>
       </c>
       <c r="Y108" t="s">
-        <v>267</v>
+        <v>366</v>
       </c>
       <c r="AA108" t="s">
-        <v>268</v>
+        <v>367</v>
       </c>
       <c r="AB108" t="s">
         <v>39</v>
@@ -10552,13 +10567,13 @@
     </row>
     <row r="109" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>369</v>
+        <v>265</v>
       </c>
       <c r="C109" t="s">
-        <v>370</v>
+        <v>266</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E109" t="s">
         <v>33</v>
@@ -10576,13 +10591,13 @@
         <v>54</v>
       </c>
       <c r="K109" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L109" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M109" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N109" t="s">
         <v>33</v>
@@ -10594,22 +10609,16 @@
         <v>38</v>
       </c>
       <c r="Q109">
-        <v>11.99</v>
+        <v>37.99</v>
       </c>
       <c r="R109">
-        <v>2</v>
-      </c>
-      <c r="S109">
-        <v>5.99</v>
-      </c>
-      <c r="T109">
-        <v>1</v>
+        <v>6.33</v>
       </c>
       <c r="Y109" t="s">
-        <v>84</v>
+        <v>267</v>
       </c>
       <c r="AA109" t="s">
-        <v>372</v>
+        <v>268</v>
       </c>
       <c r="AB109" t="s">
         <v>39</v>
@@ -10623,13 +10632,13 @@
     </row>
     <row r="110" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="C110" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D110" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="E110" t="s">
         <v>33</v>
@@ -10647,13 +10656,13 @@
         <v>54</v>
       </c>
       <c r="K110" t="s">
-        <v>260</v>
+        <v>72</v>
       </c>
       <c r="L110" t="s">
-        <v>261</v>
+        <v>73</v>
       </c>
       <c r="M110" t="s">
-        <v>262</v>
+        <v>74</v>
       </c>
       <c r="N110" t="s">
         <v>33</v>
@@ -10665,16 +10674,22 @@
         <v>38</v>
       </c>
       <c r="Q110">
-        <v>24.49</v>
+        <v>11.99</v>
       </c>
       <c r="R110">
-        <v>4.08</v>
+        <v>2</v>
+      </c>
+      <c r="S110">
+        <v>5.99</v>
+      </c>
+      <c r="T110">
+        <v>1</v>
       </c>
       <c r="Y110" t="s">
-        <v>376</v>
+        <v>84</v>
       </c>
       <c r="AA110" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="AB110" t="s">
         <v>39</v>
@@ -10688,13 +10703,13 @@
     </row>
     <row r="111" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C111" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="D111" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="E111" t="s">
         <v>33</v>
@@ -10712,13 +10727,13 @@
         <v>54</v>
       </c>
       <c r="K111" t="s">
-        <v>40</v>
+        <v>260</v>
       </c>
       <c r="L111" t="s">
-        <v>41</v>
+        <v>261</v>
       </c>
       <c r="M111" t="s">
-        <v>42</v>
+        <v>262</v>
       </c>
       <c r="N111" t="s">
         <v>33</v>
@@ -10730,16 +10745,16 @@
         <v>38</v>
       </c>
       <c r="Q111">
-        <v>59.99</v>
+        <v>24.49</v>
       </c>
       <c r="R111">
-        <v>10</v>
+        <v>4.08</v>
       </c>
       <c r="Y111" t="s">
-        <v>57</v>
+        <v>376</v>
       </c>
       <c r="AA111" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="AB111" t="s">
         <v>39</v>
@@ -10753,13 +10768,13 @@
     </row>
     <row r="112" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C112" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="D112" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="E112" t="s">
         <v>33</v>
@@ -10777,13 +10792,13 @@
         <v>54</v>
       </c>
       <c r="K112" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L112" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M112" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N112" t="s">
         <v>33</v>
@@ -10795,16 +10810,16 @@
         <v>38</v>
       </c>
       <c r="Q112">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R112">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y112" t="s">
-        <v>385</v>
+        <v>57</v>
       </c>
       <c r="AA112" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="AB112" t="s">
         <v>39</v>
@@ -10818,16 +10833,16 @@
     </row>
     <row r="113" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C113" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="D113" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="E113" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F113" t="s">
         <v>34</v>
@@ -10842,25 +10857,34 @@
         <v>54</v>
       </c>
       <c r="K113" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="L113" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="M113" t="s">
-        <v>45</v>
+        <v>74</v>
+      </c>
+      <c r="N113" t="s">
+        <v>33</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P113" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q113">
+        <v>11.99</v>
+      </c>
+      <c r="R113">
+        <v>2</v>
       </c>
       <c r="Y113" t="s">
-        <v>390</v>
-      </c>
-      <c r="Z113" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="AA113" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="AB113" t="s">
         <v>39</v>
@@ -10874,16 +10898,16 @@
     </row>
     <row r="114" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>323</v>
+        <v>387</v>
       </c>
       <c r="C114" t="s">
-        <v>324</v>
+        <v>388</v>
       </c>
       <c r="D114" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="E114" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F114" t="s">
         <v>34</v>
@@ -10898,34 +10922,25 @@
         <v>54</v>
       </c>
       <c r="K114" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="L114" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="M114" t="s">
-        <v>86</v>
-      </c>
-      <c r="N114" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O114">
-        <v>1</v>
-      </c>
-      <c r="P114" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q114">
-        <v>14.99</v>
-      </c>
-      <c r="R114">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y114" t="s">
-        <v>58</v>
+        <v>390</v>
+      </c>
+      <c r="Z114" t="s">
+        <v>391</v>
       </c>
       <c r="AA114" t="s">
-        <v>325</v>
+        <v>392</v>
       </c>
       <c r="AB114" t="s">
         <v>39</v>
@@ -10939,13 +10954,13 @@
     </row>
     <row r="115" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="C115" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="D115" t="s">
-        <v>320</v>
+        <v>393</v>
       </c>
       <c r="E115" t="s">
         <v>33</v>
@@ -10963,13 +10978,13 @@
         <v>54</v>
       </c>
       <c r="K115" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="L115" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M115" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="N115" t="s">
         <v>33</v>
@@ -10981,19 +10996,16 @@
         <v>38</v>
       </c>
       <c r="Q115">
-        <v>11.99</v>
+        <v>14.99</v>
       </c>
       <c r="R115">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Y115" t="s">
-        <v>321</v>
-      </c>
-      <c r="Z115" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="AA115" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AB115" t="s">
         <v>39</v>
@@ -11007,13 +11019,13 @@
     </row>
     <row r="116" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="C116" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="D116" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="E116" t="s">
         <v>33</v>
@@ -11031,13 +11043,13 @@
         <v>54</v>
       </c>
       <c r="K116" t="s">
-        <v>260</v>
+        <v>72</v>
       </c>
       <c r="L116" t="s">
-        <v>261</v>
+        <v>73</v>
       </c>
       <c r="M116" t="s">
-        <v>262</v>
+        <v>74</v>
       </c>
       <c r="N116" t="s">
         <v>33</v>
@@ -11049,16 +11061,19 @@
         <v>38</v>
       </c>
       <c r="Q116">
-        <v>24.49</v>
+        <v>11.99</v>
       </c>
       <c r="R116">
-        <v>4.08</v>
+        <v>2</v>
       </c>
       <c r="Y116" t="s">
-        <v>332</v>
+        <v>321</v>
+      </c>
+      <c r="Z116" t="s">
+        <v>65</v>
       </c>
       <c r="AA116" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="AB116" t="s">
         <v>39</v>
@@ -11072,13 +11087,13 @@
     </row>
     <row r="117" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>670</v>
+        <v>329</v>
       </c>
       <c r="C117" t="s">
-        <v>671</v>
+        <v>330</v>
       </c>
       <c r="D117" t="s">
-        <v>672</v>
+        <v>331</v>
       </c>
       <c r="E117" t="s">
         <v>33</v>
@@ -11096,13 +11111,13 @@
         <v>54</v>
       </c>
       <c r="K117" t="s">
-        <v>40</v>
+        <v>260</v>
       </c>
       <c r="L117" t="s">
-        <v>41</v>
+        <v>261</v>
       </c>
       <c r="M117" t="s">
-        <v>42</v>
+        <v>262</v>
       </c>
       <c r="N117" t="s">
         <v>33</v>
@@ -11114,16 +11129,16 @@
         <v>38</v>
       </c>
       <c r="Q117">
-        <v>59.99</v>
+        <v>24.49</v>
       </c>
       <c r="R117">
-        <v>10</v>
+        <v>4.08</v>
       </c>
       <c r="Y117" t="s">
-        <v>673</v>
+        <v>332</v>
       </c>
       <c r="AA117" t="s">
-        <v>674</v>
+        <v>333</v>
       </c>
       <c r="AB117" t="s">
         <v>39</v>
@@ -11137,13 +11152,13 @@
     </row>
     <row r="118" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="C118" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="D118" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="E118" t="s">
         <v>33</v>
@@ -11161,13 +11176,13 @@
         <v>54</v>
       </c>
       <c r="K118" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L118" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M118" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N118" t="s">
         <v>33</v>
@@ -11179,16 +11194,16 @@
         <v>38</v>
       </c>
       <c r="Q118">
-        <v>37.99</v>
+        <v>59.99</v>
       </c>
       <c r="R118">
-        <v>6.33</v>
+        <v>10</v>
       </c>
       <c r="Y118" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="AA118" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="AB118" t="s">
         <v>39</v>
@@ -11202,13 +11217,13 @@
     </row>
     <row r="119" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="C119" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="D119" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="E119" t="s">
         <v>33</v>
@@ -11226,13 +11241,13 @@
         <v>54</v>
       </c>
       <c r="K119" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L119" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M119" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N119" t="s">
         <v>33</v>
@@ -11244,19 +11259,16 @@
         <v>38</v>
       </c>
       <c r="Q119">
-        <v>59.99</v>
+        <v>37.99</v>
       </c>
       <c r="R119">
-        <v>10</v>
+        <v>6.33</v>
       </c>
       <c r="Y119" t="s">
-        <v>683</v>
-      </c>
-      <c r="Z119" t="s">
-        <v>76</v>
+        <v>678</v>
       </c>
       <c r="AA119" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="AB119" t="s">
         <v>39</v>
@@ -11270,13 +11282,13 @@
     </row>
     <row r="120" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="C120" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="D120" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="E120" t="s">
         <v>33</v>
@@ -11294,13 +11306,13 @@
         <v>54</v>
       </c>
       <c r="K120" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L120" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M120" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N120" t="s">
         <v>33</v>
@@ -11312,16 +11324,19 @@
         <v>38</v>
       </c>
       <c r="Q120">
-        <v>37.99</v>
+        <v>59.99</v>
       </c>
       <c r="R120">
-        <v>6.33</v>
+        <v>10</v>
       </c>
       <c r="Y120" t="s">
-        <v>52</v>
+        <v>683</v>
+      </c>
+      <c r="Z120" t="s">
+        <v>76</v>
       </c>
       <c r="AA120" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="AB120" t="s">
         <v>39</v>
@@ -11335,16 +11350,16 @@
     </row>
     <row r="121" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="C121" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D121" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="E121" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F121" t="s">
         <v>34</v>
@@ -11356,7 +11371,7 @@
         <v>36</v>
       </c>
       <c r="J121" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K121" t="s">
         <v>48</v>
@@ -11367,17 +11382,26 @@
       <c r="M121" t="s">
         <v>50</v>
       </c>
+      <c r="N121" t="s">
+        <v>33</v>
+      </c>
       <c r="O121">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P121" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q121">
+        <v>37.99</v>
+      </c>
+      <c r="R121">
+        <v>6.33</v>
       </c>
       <c r="Y121" t="s">
-        <v>692</v>
-      </c>
-      <c r="Z121" t="s">
-        <v>693</v>
+        <v>52</v>
       </c>
       <c r="AA121" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="AB121" t="s">
         <v>39</v>
@@ -11391,13 +11415,13 @@
     </row>
     <row r="122" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="C122" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="D122" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="E122" t="s">
         <v>53</v>
@@ -11447,16 +11471,16 @@
     </row>
     <row r="123" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>300</v>
+        <v>695</v>
       </c>
       <c r="C123" t="s">
-        <v>301</v>
+        <v>696</v>
       </c>
       <c r="D123" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="E123" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F123" t="s">
         <v>34</v>
@@ -11468,37 +11492,28 @@
         <v>36</v>
       </c>
       <c r="J123" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K123" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="L123" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="M123" t="s">
-        <v>86</v>
-      </c>
-      <c r="N123" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="O123">
-        <v>1</v>
-      </c>
-      <c r="P123" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q123">
-        <v>14.99</v>
-      </c>
-      <c r="R123">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y123" t="s">
-        <v>58</v>
+        <v>692</v>
+      </c>
+      <c r="Z123" t="s">
+        <v>693</v>
       </c>
       <c r="AA123" t="s">
-        <v>302</v>
+        <v>694</v>
       </c>
       <c r="AB123" t="s">
         <v>39</v>
@@ -11512,16 +11527,16 @@
     </row>
     <row r="124" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>699</v>
+        <v>300</v>
       </c>
       <c r="C124" t="s">
-        <v>700</v>
+        <v>301</v>
       </c>
       <c r="D124" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="E124" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F124" t="s">
         <v>34</v>
@@ -11536,25 +11551,34 @@
         <v>54</v>
       </c>
       <c r="K124" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="L124" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="M124" t="s">
-        <v>50</v>
+        <v>86</v>
+      </c>
+      <c r="N124" t="s">
+        <v>33</v>
       </c>
       <c r="O124">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P124" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q124">
+        <v>14.99</v>
+      </c>
+      <c r="R124">
+        <v>2.5</v>
       </c>
       <c r="Y124" t="s">
-        <v>692</v>
-      </c>
-      <c r="Z124" t="s">
-        <v>693</v>
+        <v>58</v>
       </c>
       <c r="AA124" t="s">
-        <v>694</v>
+        <v>302</v>
       </c>
       <c r="AB124" t="s">
         <v>39</v>
@@ -11568,16 +11592,16 @@
     </row>
     <row r="125" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>303</v>
+        <v>699</v>
       </c>
       <c r="C125" t="s">
-        <v>304</v>
+        <v>700</v>
       </c>
       <c r="D125" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E125" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F125" t="s">
         <v>34</v>
@@ -11592,34 +11616,25 @@
         <v>54</v>
       </c>
       <c r="K125" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L125" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M125" t="s">
-        <v>42</v>
-      </c>
-      <c r="N125" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="O125">
-        <v>1</v>
-      </c>
-      <c r="P125" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q125">
-        <v>59.99</v>
-      </c>
-      <c r="R125">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y125" t="s">
-        <v>305</v>
+        <v>692</v>
+      </c>
+      <c r="Z125" t="s">
+        <v>693</v>
       </c>
       <c r="AA125" t="s">
-        <v>306</v>
+        <v>694</v>
       </c>
       <c r="AB125" t="s">
         <v>39</v>
@@ -11633,13 +11648,13 @@
     </row>
     <row r="126" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="C126" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="D126" t="s">
-        <v>294</v>
+        <v>702</v>
       </c>
       <c r="E126" t="s">
         <v>33</v>
@@ -11654,7 +11669,7 @@
         <v>36</v>
       </c>
       <c r="J126" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K126" t="s">
         <v>40</v>
@@ -11681,13 +11696,10 @@
         <v>10</v>
       </c>
       <c r="Y126" t="s">
-        <v>77</v>
-      </c>
-      <c r="Z126" t="s">
-        <v>92</v>
+        <v>305</v>
       </c>
       <c r="AA126" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="AB126" t="s">
         <v>39</v>
@@ -11701,13 +11713,13 @@
     </row>
     <row r="127" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C127" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D127" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="E127" t="s">
         <v>33</v>
@@ -11749,13 +11761,13 @@
         <v>10</v>
       </c>
       <c r="Y127" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="Z127" t="s">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="AA127" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="AB127" t="s">
         <v>39</v>
@@ -11769,13 +11781,13 @@
     </row>
     <row r="128" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="C128" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="D128" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="E128" t="s">
         <v>33</v>
@@ -11793,13 +11805,13 @@
         <v>37</v>
       </c>
       <c r="K128" t="s">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="L128" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="M128" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="N128" t="s">
         <v>33</v>
@@ -11811,16 +11823,19 @@
         <v>38</v>
       </c>
       <c r="Q128">
-        <v>20.49</v>
+        <v>59.99</v>
       </c>
       <c r="R128">
-        <v>3.42</v>
+        <v>10</v>
       </c>
       <c r="Y128" t="s">
-        <v>310</v>
+        <v>62</v>
+      </c>
+      <c r="Z128" t="s">
+        <v>51</v>
       </c>
       <c r="AA128" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="AB128" t="s">
         <v>39</v>
@@ -11834,13 +11849,13 @@
     </row>
     <row r="129" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C129" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="D129" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="E129" t="s">
         <v>33</v>
@@ -11858,13 +11873,13 @@
         <v>37</v>
       </c>
       <c r="K129" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="L129" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="M129" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="N129" t="s">
         <v>33</v>
@@ -11876,19 +11891,16 @@
         <v>38</v>
       </c>
       <c r="Q129">
-        <v>59.99</v>
+        <v>20.49</v>
       </c>
       <c r="R129">
-        <v>10</v>
+        <v>3.42</v>
       </c>
       <c r="Y129" t="s">
-        <v>100</v>
-      </c>
-      <c r="Z129" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="AA129" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="AB129" t="s">
         <v>39</v>
@@ -11902,13 +11914,13 @@
     </row>
     <row r="130" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>253</v>
+        <v>312</v>
       </c>
       <c r="C130" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="D130" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="E130" t="s">
         <v>33</v>
@@ -11923,7 +11935,7 @@
         <v>36</v>
       </c>
       <c r="J130" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K130" t="s">
         <v>40</v>
@@ -11950,13 +11962,13 @@
         <v>10</v>
       </c>
       <c r="Y130" t="s">
-        <v>255</v>
+        <v>100</v>
       </c>
       <c r="Z130" t="s">
-        <v>102</v>
+        <v>315</v>
       </c>
       <c r="AA130" t="s">
-        <v>256</v>
+        <v>316</v>
       </c>
       <c r="AB130" t="s">
         <v>39</v>
@@ -11970,13 +11982,13 @@
     </row>
     <row r="131" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C131" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D131" t="s">
-        <v>259</v>
+        <v>317</v>
       </c>
       <c r="E131" t="s">
         <v>33</v>
@@ -11994,13 +12006,13 @@
         <v>54</v>
       </c>
       <c r="K131" t="s">
-        <v>260</v>
+        <v>40</v>
       </c>
       <c r="L131" t="s">
-        <v>261</v>
+        <v>41</v>
       </c>
       <c r="M131" t="s">
-        <v>262</v>
+        <v>42</v>
       </c>
       <c r="N131" t="s">
         <v>33</v>
@@ -12012,19 +12024,19 @@
         <v>38</v>
       </c>
       <c r="Q131">
-        <v>24.49</v>
+        <v>59.99</v>
       </c>
       <c r="R131">
-        <v>4.08</v>
+        <v>10</v>
       </c>
       <c r="Y131" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="Z131" t="s">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="AA131" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="AB131" t="s">
         <v>39</v>
@@ -12038,13 +12050,13 @@
     </row>
     <row r="132" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="C132" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="D132" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="E132" t="s">
         <v>33</v>
@@ -12062,13 +12074,13 @@
         <v>54</v>
       </c>
       <c r="K132" t="s">
-        <v>40</v>
+        <v>260</v>
       </c>
       <c r="L132" t="s">
-        <v>41</v>
+        <v>261</v>
       </c>
       <c r="M132" t="s">
-        <v>42</v>
+        <v>262</v>
       </c>
       <c r="N132" t="s">
         <v>33</v>
@@ -12080,16 +12092,19 @@
         <v>38</v>
       </c>
       <c r="Q132">
-        <v>59.99</v>
+        <v>24.49</v>
       </c>
       <c r="R132">
-        <v>10</v>
+        <v>4.08</v>
       </c>
       <c r="Y132" t="s">
-        <v>272</v>
+        <v>263</v>
+      </c>
+      <c r="Z132" t="s">
+        <v>64</v>
       </c>
       <c r="AA132" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="AB132" t="s">
         <v>39</v>
@@ -12103,13 +12118,13 @@
     </row>
     <row r="133" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>149</v>
+        <v>269</v>
       </c>
       <c r="C133" t="s">
-        <v>150</v>
+        <v>270</v>
       </c>
       <c r="D133" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E133" t="s">
         <v>33</v>
@@ -12151,10 +12166,10 @@
         <v>10</v>
       </c>
       <c r="Y133" t="s">
-        <v>63</v>
+        <v>272</v>
       </c>
       <c r="AA133" t="s">
-        <v>151</v>
+        <v>273</v>
       </c>
       <c r="AB133" t="s">
         <v>39</v>
@@ -12168,13 +12183,13 @@
     </row>
     <row r="134" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>275</v>
+        <v>149</v>
       </c>
       <c r="C134" t="s">
-        <v>276</v>
+        <v>150</v>
       </c>
       <c r="D134" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E134" t="s">
         <v>33</v>
@@ -12204,25 +12219,22 @@
         <v>33</v>
       </c>
       <c r="O134">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P134" t="s">
         <v>38</v>
       </c>
       <c r="Q134">
-        <v>119.98</v>
+        <v>59.99</v>
       </c>
       <c r="R134">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Y134" t="s">
-        <v>278</v>
-      </c>
-      <c r="Z134" t="s">
-        <v>279</v>
+        <v>63</v>
       </c>
       <c r="AA134" t="s">
-        <v>280</v>
+        <v>151</v>
       </c>
       <c r="AB134" t="s">
         <v>39</v>
@@ -12236,13 +12248,13 @@
     </row>
     <row r="135" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="C135" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="D135" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="E135" t="s">
         <v>33</v>
@@ -12257,37 +12269,40 @@
         <v>36</v>
       </c>
       <c r="J135" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K135" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L135" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M135" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N135" t="s">
         <v>33</v>
       </c>
       <c r="O135">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P135" t="s">
         <v>38</v>
       </c>
       <c r="Q135">
-        <v>11.99</v>
+        <v>119.98</v>
       </c>
       <c r="R135">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="Y135" t="s">
-        <v>75</v>
+        <v>278</v>
+      </c>
+      <c r="Z135" t="s">
+        <v>279</v>
       </c>
       <c r="AA135" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="AB135" t="s">
         <v>39</v>
@@ -12301,16 +12316,16 @@
     </row>
     <row r="136" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>238</v>
+        <v>281</v>
       </c>
       <c r="C136" t="s">
-        <v>239</v>
+        <v>282</v>
       </c>
       <c r="D136" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E136" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F136" t="s">
         <v>34</v>
@@ -12322,25 +12337,37 @@
         <v>36</v>
       </c>
       <c r="J136" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K136" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L136" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M136" t="s">
-        <v>42</v>
+        <v>74</v>
+      </c>
+      <c r="N136" t="s">
+        <v>33</v>
       </c>
       <c r="O136">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P136" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q136">
+        <v>11.99</v>
+      </c>
+      <c r="R136">
+        <v>2</v>
       </c>
       <c r="Y136" t="s">
-        <v>240</v>
+        <v>75</v>
       </c>
       <c r="AA136" t="s">
-        <v>241</v>
+        <v>284</v>
       </c>
       <c r="AB136" t="s">
         <v>39</v>
@@ -12354,16 +12381,16 @@
     </row>
     <row r="137" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="C137" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="D137" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E137" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F137" t="s">
         <v>34</v>
@@ -12386,26 +12413,14 @@
       <c r="M137" t="s">
         <v>42</v>
       </c>
-      <c r="N137" t="s">
-        <v>33</v>
-      </c>
       <c r="O137">
-        <v>1</v>
-      </c>
-      <c r="P137" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q137">
-        <v>59.99</v>
-      </c>
-      <c r="R137">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y137" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="AA137" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="AB137" t="s">
         <v>39</v>
@@ -12419,13 +12434,13 @@
     </row>
     <row r="138" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="C138" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="D138" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E138" t="s">
         <v>33</v>
@@ -12467,13 +12482,10 @@
         <v>10</v>
       </c>
       <c r="Y138" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z138" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="AA138" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="AB138" t="s">
         <v>39</v>
@@ -12487,13 +12499,13 @@
     </row>
     <row r="139" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C139" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D139" t="s">
-        <v>220</v>
+        <v>287</v>
       </c>
       <c r="E139" t="s">
         <v>33</v>
@@ -12511,13 +12523,13 @@
         <v>54</v>
       </c>
       <c r="K139" t="s">
-        <v>203</v>
+        <v>40</v>
       </c>
       <c r="L139" t="s">
-        <v>204</v>
+        <v>41</v>
       </c>
       <c r="M139" t="s">
-        <v>205</v>
+        <v>42</v>
       </c>
       <c r="N139" t="s">
         <v>33</v>
@@ -12529,19 +12541,19 @@
         <v>38</v>
       </c>
       <c r="Q139">
-        <v>69.989999999999995</v>
+        <v>59.99</v>
       </c>
       <c r="R139">
-        <v>11.67</v>
+        <v>10</v>
       </c>
       <c r="Y139" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="Z139" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="AA139" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="AB139" t="s">
         <v>39</v>
@@ -12555,13 +12567,13 @@
     </row>
     <row r="140" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="C140" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="D140" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="E140" t="s">
         <v>33</v>
@@ -12579,13 +12591,13 @@
         <v>54</v>
       </c>
       <c r="K140" t="s">
-        <v>40</v>
+        <v>203</v>
       </c>
       <c r="L140" t="s">
-        <v>41</v>
+        <v>204</v>
       </c>
       <c r="M140" t="s">
-        <v>42</v>
+        <v>205</v>
       </c>
       <c r="N140" t="s">
         <v>33</v>
@@ -12597,16 +12609,19 @@
         <v>38</v>
       </c>
       <c r="Q140">
-        <v>59.99</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="R140">
-        <v>10</v>
+        <v>11.67</v>
       </c>
       <c r="Y140" t="s">
-        <v>231</v>
+        <v>221</v>
+      </c>
+      <c r="Z140" t="s">
+        <v>222</v>
       </c>
       <c r="AA140" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="AB140" t="s">
         <v>39</v>
@@ -12620,13 +12635,13 @@
     </row>
     <row r="141" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C141" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D141" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="E141" t="s">
         <v>33</v>
@@ -12644,13 +12659,13 @@
         <v>54</v>
       </c>
       <c r="K141" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="L141" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="M141" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="N141" t="s">
         <v>33</v>
@@ -12662,16 +12677,16 @@
         <v>38</v>
       </c>
       <c r="Q141">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R141">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y141" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="AA141" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB141" t="s">
         <v>39</v>
@@ -12685,16 +12700,16 @@
     </row>
     <row r="142" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="C142" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="D142" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="E142" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F142" t="s">
         <v>34</v>
@@ -12709,22 +12724,34 @@
         <v>54</v>
       </c>
       <c r="K142" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="L142" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="M142" t="s">
-        <v>42</v>
+        <v>86</v>
+      </c>
+      <c r="N142" t="s">
+        <v>33</v>
       </c>
       <c r="O142">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P142" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q142">
+        <v>14.99</v>
+      </c>
+      <c r="R142">
+        <v>2.5</v>
       </c>
       <c r="Y142" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="AA142" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="AB142" t="s">
         <v>39</v>
@@ -12738,16 +12765,16 @@
     </row>
     <row r="143" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C143" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D143" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E143" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F143" t="s">
         <v>34</v>
@@ -12759,7 +12786,7 @@
         <v>36</v>
       </c>
       <c r="J143" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K143" t="s">
         <v>40</v>
@@ -12770,26 +12797,14 @@
       <c r="M143" t="s">
         <v>42</v>
       </c>
-      <c r="N143" t="s">
-        <v>33</v>
-      </c>
       <c r="O143">
-        <v>1</v>
-      </c>
-      <c r="P143" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q143">
-        <v>59.99</v>
-      </c>
-      <c r="R143">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y143" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="AA143" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="AB143" t="s">
         <v>39</v>
@@ -12803,13 +12818,13 @@
     </row>
     <row r="144" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>188</v>
+        <v>245</v>
       </c>
       <c r="C144" t="s">
-        <v>189</v>
+        <v>246</v>
       </c>
       <c r="D144" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E144" t="s">
         <v>33</v>
@@ -12827,13 +12842,13 @@
         <v>37</v>
       </c>
       <c r="K144" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L144" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M144" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N144" t="s">
         <v>33</v>
@@ -12845,16 +12860,16 @@
         <v>38</v>
       </c>
       <c r="Q144">
-        <v>37.99</v>
+        <v>59.99</v>
       </c>
       <c r="R144">
-        <v>6.33</v>
+        <v>10</v>
       </c>
       <c r="Y144" t="s">
-        <v>52</v>
+        <v>248</v>
       </c>
       <c r="AA144" t="s">
-        <v>190</v>
+        <v>249</v>
       </c>
       <c r="AB144" t="s">
         <v>39</v>
@@ -12868,13 +12883,13 @@
     </row>
     <row r="145" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C145" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D145" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E145" t="s">
         <v>33</v>
@@ -12889,16 +12904,16 @@
         <v>36</v>
       </c>
       <c r="J145" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K145" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L145" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M145" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N145" t="s">
         <v>33</v>
@@ -12910,16 +12925,16 @@
         <v>38</v>
       </c>
       <c r="Q145">
-        <v>59.99</v>
+        <v>37.99</v>
       </c>
       <c r="R145">
-        <v>10</v>
+        <v>6.33</v>
       </c>
       <c r="Y145" t="s">
-        <v>193</v>
+        <v>52</v>
       </c>
       <c r="AA145" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="AB145" t="s">
         <v>39</v>
@@ -12933,13 +12948,13 @@
     </row>
     <row r="146" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="C146" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="D146" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E146" t="s">
         <v>33</v>
@@ -12957,13 +12972,13 @@
         <v>54</v>
       </c>
       <c r="K146" t="s">
-        <v>203</v>
+        <v>40</v>
       </c>
       <c r="L146" t="s">
-        <v>204</v>
+        <v>41</v>
       </c>
       <c r="M146" t="s">
-        <v>205</v>
+        <v>42</v>
       </c>
       <c r="N146" t="s">
         <v>33</v>
@@ -12975,19 +12990,16 @@
         <v>38</v>
       </c>
       <c r="Q146">
-        <v>69.989999999999995</v>
+        <v>59.99</v>
       </c>
       <c r="R146">
-        <v>11.67</v>
+        <v>10</v>
       </c>
       <c r="Y146" t="s">
-        <v>206</v>
-      </c>
-      <c r="Z146" t="s">
-        <v>60</v>
+        <v>193</v>
       </c>
       <c r="AA146" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="AB146" t="s">
         <v>39</v>
@@ -13001,13 +13013,13 @@
     </row>
     <row r="147" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C147" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="D147" t="s">
-        <v>197</v>
+        <v>252</v>
       </c>
       <c r="E147" t="s">
         <v>33</v>
@@ -13022,16 +13034,16 @@
         <v>36</v>
       </c>
       <c r="J147" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K147" t="s">
-        <v>40</v>
+        <v>203</v>
       </c>
       <c r="L147" t="s">
-        <v>41</v>
+        <v>204</v>
       </c>
       <c r="M147" t="s">
-        <v>42</v>
+        <v>205</v>
       </c>
       <c r="N147" t="s">
         <v>33</v>
@@ -13043,19 +13055,19 @@
         <v>38</v>
       </c>
       <c r="Q147">
-        <v>59.99</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="R147">
-        <v>10</v>
+        <v>11.67</v>
       </c>
       <c r="Y147" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="Z147" t="s">
-        <v>199</v>
+        <v>60</v>
       </c>
       <c r="AA147" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="AB147" t="s">
         <v>39</v>
@@ -13069,13 +13081,13 @@
     </row>
     <row r="148" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="C148" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="D148" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="E148" t="s">
         <v>33</v>
@@ -13117,10 +13129,13 @@
         <v>10</v>
       </c>
       <c r="Y148" t="s">
-        <v>211</v>
+        <v>198</v>
+      </c>
+      <c r="Z148" t="s">
+        <v>199</v>
       </c>
       <c r="AA148" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="AB148" t="s">
         <v>39</v>
@@ -13134,13 +13149,13 @@
     </row>
     <row r="149" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>152</v>
+        <v>208</v>
       </c>
       <c r="C149" t="s">
-        <v>153</v>
+        <v>209</v>
       </c>
       <c r="D149" t="s">
-        <v>154</v>
+        <v>210</v>
       </c>
       <c r="E149" t="s">
         <v>33</v>
@@ -13155,16 +13170,16 @@
         <v>36</v>
       </c>
       <c r="J149" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K149" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="L149" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="M149" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="N149" t="s">
         <v>33</v>
@@ -13176,16 +13191,16 @@
         <v>38</v>
       </c>
       <c r="Q149">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R149">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y149" t="s">
-        <v>155</v>
+        <v>211</v>
       </c>
       <c r="AA149" t="s">
-        <v>156</v>
+        <v>212</v>
       </c>
       <c r="AB149" t="s">
         <v>39</v>
@@ -13199,13 +13214,13 @@
     </row>
     <row r="150" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C150" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D150" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="E150" t="s">
         <v>33</v>
@@ -13223,13 +13238,13 @@
         <v>54</v>
       </c>
       <c r="K150" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="L150" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M150" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="N150" t="s">
         <v>33</v>
@@ -13241,16 +13256,16 @@
         <v>38</v>
       </c>
       <c r="Q150">
-        <v>11.99</v>
+        <v>14.99</v>
       </c>
       <c r="R150">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Y150" t="s">
-        <v>68</v>
+        <v>155</v>
       </c>
       <c r="AA150" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="AB150" t="s">
         <v>39</v>
@@ -13264,16 +13279,16 @@
     </row>
     <row r="151" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C151" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D151" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E151" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F151" t="s">
         <v>34</v>
@@ -13288,22 +13303,34 @@
         <v>54</v>
       </c>
       <c r="K151" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L151" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M151" t="s">
-        <v>42</v>
+        <v>74</v>
+      </c>
+      <c r="N151" t="s">
+        <v>33</v>
       </c>
       <c r="O151">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P151" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q151">
+        <v>11.99</v>
+      </c>
+      <c r="R151">
+        <v>2</v>
       </c>
       <c r="Y151" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="AA151" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="AB151" t="s">
         <v>39</v>
@@ -13317,16 +13344,16 @@
     </row>
     <row r="152" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C152" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D152" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E152" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F152" t="s">
         <v>34</v>
@@ -13341,34 +13368,22 @@
         <v>54</v>
       </c>
       <c r="K152" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L152" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M152" t="s">
-        <v>50</v>
-      </c>
-      <c r="N152" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O152">
-        <v>1</v>
-      </c>
-      <c r="P152" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q152">
-        <v>37.99</v>
-      </c>
-      <c r="R152">
-        <v>6.33</v>
+        <v>0</v>
       </c>
       <c r="Y152" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="AA152" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="AB152" t="s">
         <v>39</v>
@@ -13382,13 +13397,13 @@
     </row>
     <row r="153" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C153" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D153" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E153" t="s">
         <v>33</v>
@@ -13406,13 +13421,13 @@
         <v>54</v>
       </c>
       <c r="K153" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L153" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M153" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N153" t="s">
         <v>33</v>
@@ -13424,16 +13439,16 @@
         <v>38</v>
       </c>
       <c r="Q153">
-        <v>11.99</v>
+        <v>37.99</v>
       </c>
       <c r="R153">
-        <v>2</v>
+        <v>6.33</v>
       </c>
       <c r="Y153" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="AA153" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AB153" t="s">
         <v>39</v>
@@ -13447,13 +13462,13 @@
     </row>
     <row r="154" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C154" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D154" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E154" t="s">
         <v>33</v>
@@ -13471,13 +13486,13 @@
         <v>54</v>
       </c>
       <c r="K154" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L154" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M154" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="N154" t="s">
         <v>33</v>
@@ -13489,16 +13504,16 @@
         <v>38</v>
       </c>
       <c r="Q154">
-        <v>14.99</v>
+        <v>11.99</v>
       </c>
       <c r="R154">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Y154" t="s">
-        <v>175</v>
+        <v>66</v>
       </c>
       <c r="AA154" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="AB154" t="s">
         <v>39</v>
@@ -13512,13 +13527,13 @@
     </row>
     <row r="155" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C155" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D155" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="E155" t="s">
         <v>33</v>
@@ -13536,13 +13551,13 @@
         <v>54</v>
       </c>
       <c r="K155" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="L155" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="M155" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="N155" t="s">
         <v>33</v>
@@ -13554,19 +13569,16 @@
         <v>38</v>
       </c>
       <c r="Q155">
-        <v>37.99</v>
+        <v>14.99</v>
       </c>
       <c r="R155">
-        <v>6.33</v>
+        <v>2.5</v>
       </c>
       <c r="Y155" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z155" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="AA155" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="AB155" t="s">
         <v>39</v>
@@ -13580,10 +13592,10 @@
     </row>
     <row r="156" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C156" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D156" t="s">
         <v>179</v>
@@ -13616,25 +13628,25 @@
         <v>33</v>
       </c>
       <c r="O156">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P156" t="s">
         <v>38</v>
       </c>
       <c r="Q156">
-        <v>75.98</v>
+        <v>37.99</v>
       </c>
       <c r="R156">
-        <v>12.66</v>
+        <v>6.33</v>
       </c>
       <c r="Y156" t="s">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="Z156" t="s">
-        <v>47</v>
+        <v>181</v>
       </c>
       <c r="AA156" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="AB156" t="s">
         <v>39</v>
@@ -13648,13 +13660,13 @@
     </row>
     <row r="157" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>133</v>
+        <v>183</v>
       </c>
       <c r="C157" t="s">
-        <v>134</v>
+        <v>184</v>
       </c>
       <c r="D157" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="E157" t="s">
         <v>33</v>
@@ -13672,34 +13684,37 @@
         <v>54</v>
       </c>
       <c r="K157" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L157" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M157" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N157" t="s">
         <v>33</v>
       </c>
       <c r="O157">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P157" t="s">
         <v>38</v>
       </c>
       <c r="Q157">
-        <v>11.99</v>
+        <v>75.98</v>
       </c>
       <c r="R157">
-        <v>2</v>
+        <v>12.66</v>
       </c>
       <c r="Y157" t="s">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="Z157" t="s">
+        <v>47</v>
       </c>
       <c r="AA157" t="s">
-        <v>135</v>
+        <v>185</v>
       </c>
       <c r="AB157" t="s">
         <v>39</v>
@@ -13713,13 +13728,13 @@
     </row>
     <row r="158" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="C158" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="D158" t="s">
-        <v>119</v>
+        <v>186</v>
       </c>
       <c r="E158" t="s">
         <v>33</v>
@@ -13737,13 +13752,13 @@
         <v>54</v>
       </c>
       <c r="K158" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L158" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M158" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="N158" t="s">
         <v>33</v>
@@ -13755,19 +13770,16 @@
         <v>38</v>
       </c>
       <c r="Q158">
-        <v>14.99</v>
+        <v>11.99</v>
       </c>
       <c r="R158">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Y158" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z158" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
       <c r="AA158" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="AB158" t="s">
         <v>39</v>
@@ -13781,13 +13793,13 @@
     </row>
     <row r="159" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C159" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D159" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="E159" t="s">
         <v>33</v>
@@ -13805,13 +13817,13 @@
         <v>54</v>
       </c>
       <c r="K159" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L159" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M159" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="N159" t="s">
         <v>33</v>
@@ -13823,19 +13835,19 @@
         <v>38</v>
       </c>
       <c r="Q159">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="R159">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="Y159" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="Z159" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="AA159" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="AB159" t="s">
         <v>39</v>
@@ -13849,13 +13861,13 @@
     </row>
     <row r="160" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C160" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D160" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E160" t="s">
         <v>33</v>
@@ -13873,13 +13885,13 @@
         <v>54</v>
       </c>
       <c r="K160" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L160" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M160" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N160" t="s">
         <v>33</v>
@@ -13891,16 +13903,19 @@
         <v>38</v>
       </c>
       <c r="Q160">
-        <v>38.49</v>
+        <v>59.99</v>
       </c>
       <c r="R160">
-        <v>6.42</v>
+        <v>10</v>
       </c>
       <c r="Y160" t="s">
-        <v>78</v>
+        <v>126</v>
+      </c>
+      <c r="Z160" t="s">
+        <v>127</v>
       </c>
       <c r="AA160" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="AB160" t="s">
         <v>39</v>
@@ -13914,16 +13929,16 @@
     </row>
     <row r="161" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="C161" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="D161" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E161" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F161" t="s">
         <v>34</v>
@@ -13938,22 +13953,34 @@
         <v>54</v>
       </c>
       <c r="K161" t="s">
-        <v>94</v>
+        <v>43</v>
       </c>
       <c r="L161" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="M161" t="s">
-        <v>83</v>
+        <v>45</v>
+      </c>
+      <c r="N161" t="s">
+        <v>33</v>
       </c>
       <c r="O161">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P161" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q161">
+        <v>38.49</v>
+      </c>
+      <c r="R161">
+        <v>6.42</v>
       </c>
       <c r="Y161" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="AA161" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="AB161" t="s">
         <v>39</v>
@@ -13967,16 +13994,16 @@
     </row>
     <row r="162" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C162" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D162" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E162" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F162" t="s">
         <v>34</v>
@@ -13991,37 +14018,22 @@
         <v>54</v>
       </c>
       <c r="K162" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="L162" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="M162" t="s">
-        <v>50</v>
-      </c>
-      <c r="N162" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="O162">
-        <v>1</v>
-      </c>
-      <c r="P162" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q162">
-        <v>37.99</v>
-      </c>
-      <c r="R162">
-        <v>6.33</v>
+        <v>0</v>
       </c>
       <c r="Y162" t="s">
-        <v>109</v>
-      </c>
-      <c r="Z162" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="AA162" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="AB162" t="s">
         <v>39</v>
@@ -14035,13 +14047,13 @@
     </row>
     <row r="163" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C163" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D163" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="E163" t="s">
         <v>33</v>
@@ -14056,16 +14068,16 @@
         <v>36</v>
       </c>
       <c r="J163" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K163" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L163" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M163" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N163" t="s">
         <v>33</v>
@@ -14077,19 +14089,19 @@
         <v>38</v>
       </c>
       <c r="Q163">
-        <v>59.99</v>
+        <v>37.99</v>
       </c>
       <c r="R163">
-        <v>10</v>
+        <v>6.33</v>
       </c>
       <c r="Y163" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="Z163" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="AA163" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="AB163" t="s">
         <v>39</v>
@@ -14103,66 +14115,134 @@
     </row>
     <row r="164" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
+        <v>112</v>
+      </c>
+      <c r="C164" t="s">
+        <v>113</v>
+      </c>
+      <c r="D164" t="s">
+        <v>114</v>
+      </c>
+      <c r="E164" t="s">
+        <v>33</v>
+      </c>
+      <c r="F164" t="s">
+        <v>34</v>
+      </c>
+      <c r="G164" t="s">
+        <v>35</v>
+      </c>
+      <c r="H164" t="s">
+        <v>36</v>
+      </c>
+      <c r="J164" t="s">
+        <v>37</v>
+      </c>
+      <c r="K164" t="s">
+        <v>40</v>
+      </c>
+      <c r="L164" t="s">
+        <v>41</v>
+      </c>
+      <c r="M164" t="s">
+        <v>42</v>
+      </c>
+      <c r="N164" t="s">
+        <v>33</v>
+      </c>
+      <c r="O164">
+        <v>1</v>
+      </c>
+      <c r="P164" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q164">
+        <v>59.99</v>
+      </c>
+      <c r="R164">
+        <v>10</v>
+      </c>
+      <c r="Y164" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z164" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA164" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB164" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG164" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
         <v>703</v>
       </c>
-      <c r="C164" t="s">
+      <c r="C165" t="s">
         <v>704</v>
       </c>
-      <c r="D164" t="s">
+      <c r="D165" t="s">
         <v>705</v>
       </c>
-      <c r="E164" t="s">
-        <v>33</v>
-      </c>
-      <c r="F164" t="s">
-        <v>34</v>
-      </c>
-      <c r="G164" t="s">
-        <v>35</v>
-      </c>
-      <c r="H164" t="s">
-        <v>36</v>
-      </c>
-      <c r="J164" t="s">
-        <v>54</v>
-      </c>
-      <c r="K164" t="s">
+      <c r="E165" t="s">
+        <v>33</v>
+      </c>
+      <c r="F165" t="s">
+        <v>34</v>
+      </c>
+      <c r="G165" t="s">
+        <v>35</v>
+      </c>
+      <c r="H165" t="s">
+        <v>36</v>
+      </c>
+      <c r="J165" t="s">
+        <v>54</v>
+      </c>
+      <c r="K165" t="s">
         <v>72</v>
       </c>
-      <c r="L164" t="s">
+      <c r="L165" t="s">
         <v>73</v>
       </c>
-      <c r="M164" t="s">
+      <c r="M165" t="s">
         <v>74</v>
       </c>
-      <c r="N164" t="s">
-        <v>33</v>
-      </c>
-      <c r="O164">
-        <v>1</v>
-      </c>
-      <c r="P164" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q164">
+      <c r="N165" t="s">
+        <v>33</v>
+      </c>
+      <c r="O165">
+        <v>1</v>
+      </c>
+      <c r="P165" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q165">
         <v>11.99</v>
       </c>
-      <c r="R164">
+      <c r="R165">
         <v>2</v>
       </c>
-      <c r="Y164" t="s">
+      <c r="Y165" t="s">
         <v>706</v>
       </c>
-      <c r="AA164" t="s">
+      <c r="AA165" t="s">
         <v>707</v>
       </c>
-      <c r="AB164" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD164" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG164" t="b">
+      <c r="AB165" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG165" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Raw Sales Data/Amazon.xlsx
+++ b/Raw Sales Data/Amazon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2683" uniqueCount="869">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2749" uniqueCount="891">
   <si>
     <t>amazon-order-id</t>
   </si>
@@ -2626,6 +2626,72 @@
   </si>
   <si>
     <t>KY8 4SF</t>
+  </si>
+  <si>
+    <t>206-8939441-3997950</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:46:25+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-10T19:27:03+00:00</t>
+  </si>
+  <si>
+    <t>CARDIFF</t>
+  </si>
+  <si>
+    <t>Wales</t>
+  </si>
+  <si>
+    <t>CF3 5QP</t>
+  </si>
+  <si>
+    <t>026-4795353-6909924</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:21:51+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:12:37+00:00</t>
+  </si>
+  <si>
+    <t>DONCASTER</t>
+  </si>
+  <si>
+    <t>DN8 4NQ</t>
+  </si>
+  <si>
+    <t>203-2144417-8541137</t>
+  </si>
+  <si>
+    <t>2026-03-10T08:47:12+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-10T17:33:49+00:00</t>
+  </si>
+  <si>
+    <t>RHOSLLANERCHRUGOG</t>
+  </si>
+  <si>
+    <t>LL14 2HL</t>
+  </si>
+  <si>
+    <t>204-1873848-5722759</t>
+  </si>
+  <si>
+    <t>2026-03-10T08:37:09+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-10T11:07:29+00:00</t>
+  </si>
+  <si>
+    <t>Gourock</t>
+  </si>
+  <si>
+    <t>Renfrewshire</t>
+  </si>
+  <si>
+    <t>PA19 1HD</t>
   </si>
 </sst>
 </file>
@@ -3432,7 +3498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG165"/>
+  <dimension ref="A1:AG169"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
@@ -3543,13 +3609,13 @@
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>864</v>
+        <v>869</v>
       </c>
       <c r="C2" t="s">
-        <v>865</v>
+        <v>870</v>
       </c>
       <c r="D2" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="E2" t="s">
         <v>33</v>
@@ -3585,16 +3651,19 @@
         <v>38</v>
       </c>
       <c r="Q2">
-        <v>65.989999999999995</v>
+        <v>67.989999999999995</v>
       </c>
       <c r="R2">
-        <v>11</v>
+        <v>11.33</v>
       </c>
       <c r="Y2" t="s">
-        <v>867</v>
+        <v>872</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>873</v>
       </c>
       <c r="AA2" t="s">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="AB2" t="s">
         <v>39</v>
@@ -3608,13 +3677,13 @@
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>846</v>
+        <v>875</v>
       </c>
       <c r="C3" t="s">
-        <v>847</v>
+        <v>876</v>
       </c>
       <c r="D3" t="s">
-        <v>848</v>
+        <v>877</v>
       </c>
       <c r="E3" t="s">
         <v>33</v>
@@ -3650,25 +3719,16 @@
         <v>38</v>
       </c>
       <c r="Q3">
-        <v>65.989999999999995</v>
+        <v>67.989999999999995</v>
       </c>
       <c r="R3">
-        <v>11</v>
-      </c>
-      <c r="S3">
-        <v>6.99</v>
-      </c>
-      <c r="T3">
-        <v>1.17</v>
+        <v>11.33</v>
       </c>
       <c r="Y3" t="s">
-        <v>849</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>850</v>
+        <v>878</v>
       </c>
       <c r="AA3" t="s">
-        <v>851</v>
+        <v>879</v>
       </c>
       <c r="AB3" t="s">
         <v>39</v>
@@ -3682,16 +3742,16 @@
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>852</v>
+        <v>880</v>
       </c>
       <c r="C4" t="s">
-        <v>853</v>
+        <v>881</v>
       </c>
       <c r="D4" t="s">
-        <v>854</v>
+        <v>882</v>
       </c>
       <c r="E4" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F4" t="s">
         <v>34</v>
@@ -3714,14 +3774,26 @@
       <c r="M4" t="s">
         <v>42</v>
       </c>
+      <c r="N4" t="s">
+        <v>33</v>
+      </c>
       <c r="O4">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P4" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q4">
+        <v>65.989999999999995</v>
+      </c>
+      <c r="R4">
+        <v>11</v>
       </c>
       <c r="Y4" t="s">
-        <v>855</v>
+        <v>883</v>
       </c>
       <c r="AA4" t="s">
-        <v>856</v>
+        <v>884</v>
       </c>
       <c r="AB4" t="s">
         <v>39</v>
@@ -3735,13 +3807,13 @@
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>857</v>
+        <v>885</v>
       </c>
       <c r="C5" t="s">
-        <v>858</v>
+        <v>886</v>
       </c>
       <c r="D5" t="s">
-        <v>859</v>
+        <v>887</v>
       </c>
       <c r="E5" t="s">
         <v>33</v>
@@ -3783,10 +3855,13 @@
         <v>11</v>
       </c>
       <c r="Y5" t="s">
-        <v>860</v>
+        <v>888</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>889</v>
       </c>
       <c r="AA5" t="s">
-        <v>861</v>
+        <v>890</v>
       </c>
       <c r="AB5" t="s">
         <v>39</v>
@@ -3800,13 +3875,13 @@
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>837</v>
+        <v>864</v>
       </c>
       <c r="C6" t="s">
-        <v>838</v>
+        <v>865</v>
       </c>
       <c r="D6" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="E6" t="s">
         <v>33</v>
@@ -3824,13 +3899,13 @@
         <v>54</v>
       </c>
       <c r="K6" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L6" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M6" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N6" t="s">
         <v>33</v>
@@ -3842,16 +3917,16 @@
         <v>38</v>
       </c>
       <c r="Q6">
-        <v>40.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R6">
-        <v>6.83</v>
+        <v>11</v>
       </c>
       <c r="Y6" t="s">
-        <v>305</v>
+        <v>867</v>
       </c>
       <c r="AA6" t="s">
-        <v>840</v>
+        <v>868</v>
       </c>
       <c r="AB6" t="s">
         <v>39</v>
@@ -3865,13 +3940,13 @@
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="C7" t="s">
-        <v>842</v>
+        <v>847</v>
       </c>
       <c r="D7" t="s">
-        <v>863</v>
+        <v>848</v>
       </c>
       <c r="E7" t="s">
         <v>33</v>
@@ -3919,10 +3994,13 @@
         <v>1.17</v>
       </c>
       <c r="Y7" t="s">
-        <v>844</v>
+        <v>849</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>850</v>
       </c>
       <c r="AA7" t="s">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="AB7" t="s">
         <v>39</v>
@@ -3936,16 +4014,16 @@
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>837</v>
+        <v>852</v>
       </c>
       <c r="C8" t="s">
-        <v>838</v>
+        <v>853</v>
       </c>
       <c r="D8" t="s">
-        <v>839</v>
+        <v>854</v>
       </c>
       <c r="E8" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="F8" t="s">
         <v>34</v>
@@ -3960,34 +4038,22 @@
         <v>54</v>
       </c>
       <c r="K8" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L8" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M8" t="s">
-        <v>50</v>
-      </c>
-      <c r="N8" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="O8">
-        <v>1</v>
-      </c>
-      <c r="P8" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q8">
-        <v>40.99</v>
-      </c>
-      <c r="R8">
-        <v>6.83</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>305</v>
+        <v>855</v>
       </c>
       <c r="AA8" t="s">
-        <v>840</v>
+        <v>856</v>
       </c>
       <c r="AB8" t="s">
         <v>39</v>
@@ -4001,16 +4067,16 @@
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>841</v>
+        <v>857</v>
       </c>
       <c r="C9" t="s">
-        <v>842</v>
+        <v>858</v>
       </c>
       <c r="D9" t="s">
-        <v>843</v>
+        <v>859</v>
       </c>
       <c r="E9" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s">
         <v>34</v>
@@ -4034,7 +4100,7 @@
         <v>42</v>
       </c>
       <c r="N9" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O9">
         <v>1</v>
@@ -4048,17 +4114,11 @@
       <c r="R9">
         <v>11</v>
       </c>
-      <c r="S9">
-        <v>6.99</v>
-      </c>
-      <c r="T9">
-        <v>1.17</v>
-      </c>
       <c r="Y9" t="s">
-        <v>844</v>
+        <v>860</v>
       </c>
       <c r="AA9" t="s">
-        <v>845</v>
+        <v>861</v>
       </c>
       <c r="AB9" t="s">
         <v>39</v>
@@ -4072,16 +4132,16 @@
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>819</v>
+        <v>837</v>
       </c>
       <c r="C10" t="s">
-        <v>820</v>
+        <v>838</v>
       </c>
       <c r="D10" t="s">
-        <v>821</v>
+        <v>862</v>
       </c>
       <c r="E10" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s">
         <v>34</v>
@@ -4105,7 +4165,7 @@
         <v>50</v>
       </c>
       <c r="N10" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O10">
         <v>1</v>
@@ -4120,13 +4180,10 @@
         <v>6.83</v>
       </c>
       <c r="Y10" t="s">
-        <v>618</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>619</v>
+        <v>305</v>
       </c>
       <c r="AA10" t="s">
-        <v>620</v>
+        <v>840</v>
       </c>
       <c r="AB10" t="s">
         <v>39</v>
@@ -4140,16 +4197,16 @@
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>822</v>
+        <v>841</v>
       </c>
       <c r="C11" t="s">
-        <v>823</v>
+        <v>842</v>
       </c>
       <c r="D11" t="s">
-        <v>824</v>
+        <v>863</v>
       </c>
       <c r="E11" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
         <v>34</v>
@@ -4164,16 +4221,16 @@
         <v>54</v>
       </c>
       <c r="K11" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L11" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M11" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N11" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O11">
         <v>1</v>
@@ -4182,16 +4239,22 @@
         <v>38</v>
       </c>
       <c r="Q11">
-        <v>14.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R11">
-        <v>2.5</v>
+        <v>11</v>
+      </c>
+      <c r="S11">
+        <v>6.99</v>
+      </c>
+      <c r="T11">
+        <v>1.17</v>
       </c>
       <c r="Y11" t="s">
-        <v>825</v>
+        <v>844</v>
       </c>
       <c r="AA11" t="s">
-        <v>826</v>
+        <v>845</v>
       </c>
       <c r="AB11" t="s">
         <v>39</v>
@@ -4205,13 +4268,13 @@
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>827</v>
+        <v>837</v>
       </c>
       <c r="C12" t="s">
-        <v>828</v>
+        <v>838</v>
       </c>
       <c r="D12" t="s">
-        <v>829</v>
+        <v>839</v>
       </c>
       <c r="E12" t="s">
         <v>98</v>
@@ -4229,13 +4292,13 @@
         <v>54</v>
       </c>
       <c r="K12" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L12" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M12" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N12" t="s">
         <v>99</v>
@@ -4247,16 +4310,16 @@
         <v>38</v>
       </c>
       <c r="Q12">
-        <v>65.989999999999995</v>
-      </c>
-      <c r="S12">
-        <v>6.99</v>
+        <v>40.99</v>
+      </c>
+      <c r="R12">
+        <v>6.83</v>
       </c>
       <c r="Y12" t="s">
-        <v>830</v>
+        <v>305</v>
       </c>
       <c r="AA12" t="s">
-        <v>831</v>
+        <v>840</v>
       </c>
       <c r="AB12" t="s">
         <v>39</v>
@@ -4270,16 +4333,16 @@
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>832</v>
+        <v>841</v>
       </c>
       <c r="C13" t="s">
-        <v>833</v>
+        <v>842</v>
       </c>
       <c r="D13" t="s">
-        <v>834</v>
+        <v>843</v>
       </c>
       <c r="E13" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F13" t="s">
         <v>34</v>
@@ -4303,7 +4366,7 @@
         <v>42</v>
       </c>
       <c r="N13" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O13">
         <v>1</v>
@@ -4317,11 +4380,17 @@
       <c r="R13">
         <v>11</v>
       </c>
+      <c r="S13">
+        <v>6.99</v>
+      </c>
+      <c r="T13">
+        <v>1.17</v>
+      </c>
       <c r="Y13" t="s">
-        <v>835</v>
+        <v>844</v>
       </c>
       <c r="AA13" t="s">
-        <v>836</v>
+        <v>845</v>
       </c>
       <c r="AB13" t="s">
         <v>39</v>
@@ -4335,16 +4404,16 @@
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>780</v>
+        <v>819</v>
       </c>
       <c r="C14" t="s">
-        <v>781</v>
+        <v>820</v>
       </c>
       <c r="D14" t="s">
-        <v>782</v>
+        <v>821</v>
       </c>
       <c r="E14" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F14" t="s">
         <v>34</v>
@@ -4359,16 +4428,16 @@
         <v>54</v>
       </c>
       <c r="K14" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L14" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M14" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N14" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O14">
         <v>1</v>
@@ -4377,16 +4446,19 @@
         <v>38</v>
       </c>
       <c r="Q14">
-        <v>65.989999999999995</v>
+        <v>40.99</v>
       </c>
       <c r="R14">
-        <v>11</v>
+        <v>6.83</v>
       </c>
       <c r="Y14" t="s">
-        <v>783</v>
+        <v>618</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>619</v>
       </c>
       <c r="AA14" t="s">
-        <v>784</v>
+        <v>620</v>
       </c>
       <c r="AB14" t="s">
         <v>39</v>
@@ -4400,16 +4472,16 @@
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>785</v>
+        <v>822</v>
       </c>
       <c r="C15" t="s">
-        <v>786</v>
+        <v>823</v>
       </c>
       <c r="D15" t="s">
-        <v>787</v>
+        <v>824</v>
       </c>
       <c r="E15" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F15" t="s">
         <v>34</v>
@@ -4424,16 +4496,16 @@
         <v>54</v>
       </c>
       <c r="K15" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L15" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M15" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="N15" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O15">
         <v>1</v>
@@ -4442,16 +4514,16 @@
         <v>38</v>
       </c>
       <c r="Q15">
-        <v>40.99</v>
+        <v>14.99</v>
       </c>
       <c r="R15">
-        <v>6.83</v>
+        <v>2.5</v>
       </c>
       <c r="Y15" t="s">
-        <v>788</v>
+        <v>825</v>
       </c>
       <c r="AA15" t="s">
-        <v>789</v>
+        <v>826</v>
       </c>
       <c r="AB15" t="s">
         <v>39</v>
@@ -4465,16 +4537,16 @@
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>790</v>
+        <v>827</v>
       </c>
       <c r="C16" t="s">
-        <v>791</v>
+        <v>828</v>
       </c>
       <c r="D16" t="s">
-        <v>792</v>
+        <v>829</v>
       </c>
       <c r="E16" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F16" t="s">
         <v>34</v>
@@ -4498,7 +4570,7 @@
         <v>42</v>
       </c>
       <c r="N16" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O16">
         <v>1</v>
@@ -4509,14 +4581,14 @@
       <c r="Q16">
         <v>65.989999999999995</v>
       </c>
-      <c r="R16">
-        <v>11</v>
+      <c r="S16">
+        <v>6.99</v>
       </c>
       <c r="Y16" t="s">
-        <v>793</v>
+        <v>830</v>
       </c>
       <c r="AA16" t="s">
-        <v>794</v>
+        <v>831</v>
       </c>
       <c r="AB16" t="s">
         <v>39</v>
@@ -4530,13 +4602,13 @@
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>795</v>
+        <v>832</v>
       </c>
       <c r="C17" t="s">
-        <v>796</v>
+        <v>833</v>
       </c>
       <c r="D17" t="s">
-        <v>797</v>
+        <v>834</v>
       </c>
       <c r="E17" t="s">
         <v>33</v>
@@ -4554,13 +4626,13 @@
         <v>54</v>
       </c>
       <c r="K17" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L17" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M17" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N17" t="s">
         <v>33</v>
@@ -4572,16 +4644,16 @@
         <v>38</v>
       </c>
       <c r="Q17">
-        <v>14.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R17">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="Y17" t="s">
-        <v>798</v>
+        <v>835</v>
       </c>
       <c r="AA17" t="s">
-        <v>799</v>
+        <v>836</v>
       </c>
       <c r="AB17" t="s">
         <v>39</v>
@@ -4595,13 +4667,13 @@
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>800</v>
+        <v>780</v>
       </c>
       <c r="C18" t="s">
-        <v>801</v>
+        <v>781</v>
       </c>
       <c r="D18" t="s">
-        <v>802</v>
+        <v>782</v>
       </c>
       <c r="E18" t="s">
         <v>33</v>
@@ -4619,13 +4691,13 @@
         <v>54</v>
       </c>
       <c r="K18" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L18" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M18" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N18" t="s">
         <v>33</v>
@@ -4637,16 +4709,16 @@
         <v>38</v>
       </c>
       <c r="Q18">
-        <v>14.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R18">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="Y18" t="s">
-        <v>68</v>
+        <v>783</v>
       </c>
       <c r="AA18" t="s">
-        <v>803</v>
+        <v>784</v>
       </c>
       <c r="AB18" t="s">
         <v>39</v>
@@ -4660,13 +4732,13 @@
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>804</v>
+        <v>785</v>
       </c>
       <c r="C19" t="s">
-        <v>805</v>
+        <v>786</v>
       </c>
       <c r="D19" t="s">
-        <v>802</v>
+        <v>787</v>
       </c>
       <c r="E19" t="s">
         <v>33</v>
@@ -4684,13 +4756,13 @@
         <v>54</v>
       </c>
       <c r="K19" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L19" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M19" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N19" t="s">
         <v>33</v>
@@ -4702,16 +4774,16 @@
         <v>38</v>
       </c>
       <c r="Q19">
-        <v>11.99</v>
+        <v>40.99</v>
       </c>
       <c r="R19">
-        <v>2</v>
+        <v>6.83</v>
       </c>
       <c r="Y19" t="s">
-        <v>806</v>
+        <v>788</v>
       </c>
       <c r="AA19" t="s">
-        <v>807</v>
+        <v>789</v>
       </c>
       <c r="AB19" t="s">
         <v>39</v>
@@ -4725,13 +4797,13 @@
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>808</v>
+        <v>790</v>
       </c>
       <c r="C20" t="s">
-        <v>809</v>
+        <v>791</v>
       </c>
       <c r="D20" t="s">
-        <v>810</v>
+        <v>792</v>
       </c>
       <c r="E20" t="s">
         <v>33</v>
@@ -4749,13 +4821,13 @@
         <v>54</v>
       </c>
       <c r="K20" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L20" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M20" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N20" t="s">
         <v>33</v>
@@ -4767,16 +4839,16 @@
         <v>38</v>
       </c>
       <c r="Q20">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R20">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y20" t="s">
-        <v>66</v>
+        <v>793</v>
       </c>
       <c r="AA20" t="s">
-        <v>811</v>
+        <v>794</v>
       </c>
       <c r="AB20" t="s">
         <v>39</v>
@@ -4790,13 +4862,13 @@
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>812</v>
+        <v>795</v>
       </c>
       <c r="C21" t="s">
-        <v>813</v>
+        <v>796</v>
       </c>
       <c r="D21" t="s">
-        <v>814</v>
+        <v>797</v>
       </c>
       <c r="E21" t="s">
         <v>33</v>
@@ -4814,13 +4886,13 @@
         <v>54</v>
       </c>
       <c r="K21" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="L21" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="M21" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="N21" t="s">
         <v>33</v>
@@ -4832,16 +4904,16 @@
         <v>38</v>
       </c>
       <c r="Q21">
-        <v>40.99</v>
+        <v>14.99</v>
       </c>
       <c r="R21">
-        <v>6.83</v>
+        <v>2.5</v>
       </c>
       <c r="Y21" t="s">
-        <v>815</v>
+        <v>798</v>
       </c>
       <c r="AA21" t="s">
-        <v>816</v>
+        <v>799</v>
       </c>
       <c r="AB21" t="s">
         <v>39</v>
@@ -4855,13 +4927,13 @@
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>745</v>
+        <v>800</v>
       </c>
       <c r="C22" t="s">
-        <v>746</v>
+        <v>801</v>
       </c>
       <c r="D22" t="s">
-        <v>817</v>
+        <v>802</v>
       </c>
       <c r="E22" t="s">
         <v>33</v>
@@ -4897,16 +4969,16 @@
         <v>38</v>
       </c>
       <c r="Q22">
-        <v>11.99</v>
+        <v>14.99</v>
       </c>
       <c r="R22">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Y22" t="s">
-        <v>748</v>
+        <v>68</v>
       </c>
       <c r="AA22" t="s">
-        <v>749</v>
+        <v>803</v>
       </c>
       <c r="AB22" t="s">
         <v>39</v>
@@ -4920,13 +4992,13 @@
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>750</v>
+        <v>804</v>
       </c>
       <c r="C23" t="s">
-        <v>751</v>
+        <v>805</v>
       </c>
       <c r="D23" t="s">
-        <v>752</v>
+        <v>802</v>
       </c>
       <c r="E23" t="s">
         <v>33</v>
@@ -4944,13 +5016,13 @@
         <v>54</v>
       </c>
       <c r="K23" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L23" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M23" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N23" t="s">
         <v>33</v>
@@ -4962,16 +5034,16 @@
         <v>38</v>
       </c>
       <c r="Q23">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R23">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y23" t="s">
-        <v>753</v>
+        <v>806</v>
       </c>
       <c r="AA23" t="s">
-        <v>754</v>
+        <v>807</v>
       </c>
       <c r="AB23" t="s">
         <v>39</v>
@@ -4985,13 +5057,13 @@
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>755</v>
+        <v>808</v>
       </c>
       <c r="C24" t="s">
-        <v>756</v>
+        <v>809</v>
       </c>
       <c r="D24" t="s">
-        <v>818</v>
+        <v>810</v>
       </c>
       <c r="E24" t="s">
         <v>33</v>
@@ -5009,13 +5081,13 @@
         <v>54</v>
       </c>
       <c r="K24" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L24" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M24" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N24" t="s">
         <v>33</v>
@@ -5027,25 +5099,16 @@
         <v>38</v>
       </c>
       <c r="Q24">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R24">
-        <v>11</v>
-      </c>
-      <c r="S24">
-        <v>6.99</v>
-      </c>
-      <c r="T24">
-        <v>1.17</v>
+        <v>2</v>
       </c>
       <c r="Y24" t="s">
-        <v>758</v>
-      </c>
-      <c r="Z24" t="s">
-        <v>759</v>
+        <v>66</v>
       </c>
       <c r="AA24" t="s">
-        <v>760</v>
+        <v>811</v>
       </c>
       <c r="AB24" t="s">
         <v>39</v>
@@ -5059,13 +5122,13 @@
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>761</v>
+        <v>812</v>
       </c>
       <c r="C25" t="s">
-        <v>762</v>
+        <v>813</v>
       </c>
       <c r="D25" t="s">
-        <v>763</v>
+        <v>814</v>
       </c>
       <c r="E25" t="s">
         <v>33</v>
@@ -5083,13 +5146,13 @@
         <v>54</v>
       </c>
       <c r="K25" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="L25" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="M25" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="N25" t="s">
         <v>33</v>
@@ -5101,19 +5164,16 @@
         <v>38</v>
       </c>
       <c r="Q25">
-        <v>11.99</v>
+        <v>40.99</v>
       </c>
       <c r="R25">
-        <v>2</v>
+        <v>6.83</v>
       </c>
       <c r="Y25" t="s">
-        <v>764</v>
-      </c>
-      <c r="Z25" t="s">
-        <v>279</v>
+        <v>815</v>
       </c>
       <c r="AA25" t="s">
-        <v>765</v>
+        <v>816</v>
       </c>
       <c r="AB25" t="s">
         <v>39</v>
@@ -5127,13 +5187,13 @@
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="C26" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="D26" t="s">
-        <v>768</v>
+        <v>817</v>
       </c>
       <c r="E26" t="s">
         <v>33</v>
@@ -5175,13 +5235,10 @@
         <v>2</v>
       </c>
       <c r="Y26" t="s">
-        <v>91</v>
-      </c>
-      <c r="Z26" t="s">
-        <v>121</v>
+        <v>748</v>
       </c>
       <c r="AA26" t="s">
-        <v>769</v>
+        <v>749</v>
       </c>
       <c r="AB26" t="s">
         <v>39</v>
@@ -5195,13 +5252,13 @@
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>770</v>
+        <v>750</v>
       </c>
       <c r="C27" t="s">
-        <v>771</v>
+        <v>751</v>
       </c>
       <c r="D27" t="s">
-        <v>772</v>
+        <v>752</v>
       </c>
       <c r="E27" t="s">
         <v>33</v>
@@ -5243,13 +5300,10 @@
         <v>11</v>
       </c>
       <c r="Y27" t="s">
-        <v>773</v>
-      </c>
-      <c r="Z27" t="s">
-        <v>64</v>
+        <v>753</v>
       </c>
       <c r="AA27" t="s">
-        <v>774</v>
+        <v>754</v>
       </c>
       <c r="AB27" t="s">
         <v>39</v>
@@ -5263,13 +5317,13 @@
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>775</v>
+        <v>755</v>
       </c>
       <c r="C28" t="s">
-        <v>776</v>
+        <v>756</v>
       </c>
       <c r="D28" t="s">
-        <v>777</v>
+        <v>818</v>
       </c>
       <c r="E28" t="s">
         <v>33</v>
@@ -5310,11 +5364,20 @@
       <c r="R28">
         <v>11</v>
       </c>
+      <c r="S28">
+        <v>6.99</v>
+      </c>
+      <c r="T28">
+        <v>1.17</v>
+      </c>
       <c r="Y28" t="s">
-        <v>778</v>
+        <v>758</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>759</v>
       </c>
       <c r="AA28" t="s">
-        <v>779</v>
+        <v>760</v>
       </c>
       <c r="AB28" t="s">
         <v>39</v>
@@ -5328,16 +5391,16 @@
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>745</v>
+        <v>761</v>
       </c>
       <c r="C29" t="s">
-        <v>746</v>
+        <v>762</v>
       </c>
       <c r="D29" t="s">
-        <v>747</v>
+        <v>763</v>
       </c>
       <c r="E29" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F29" t="s">
         <v>34</v>
@@ -5361,7 +5424,7 @@
         <v>74</v>
       </c>
       <c r="N29" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O29">
         <v>1</v>
@@ -5376,10 +5439,13 @@
         <v>2</v>
       </c>
       <c r="Y29" t="s">
-        <v>748</v>
+        <v>764</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>279</v>
       </c>
       <c r="AA29" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="AB29" t="s">
         <v>39</v>
@@ -5393,13 +5459,13 @@
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>750</v>
+        <v>766</v>
       </c>
       <c r="C30" t="s">
-        <v>751</v>
+        <v>767</v>
       </c>
       <c r="D30" t="s">
-        <v>752</v>
+        <v>768</v>
       </c>
       <c r="E30" t="s">
         <v>33</v>
@@ -5417,13 +5483,13 @@
         <v>54</v>
       </c>
       <c r="K30" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L30" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M30" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N30" t="s">
         <v>33</v>
@@ -5435,16 +5501,19 @@
         <v>38</v>
       </c>
       <c r="Q30">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R30">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y30" t="s">
-        <v>753</v>
+        <v>91</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>121</v>
       </c>
       <c r="AA30" t="s">
-        <v>754</v>
+        <v>769</v>
       </c>
       <c r="AB30" t="s">
         <v>39</v>
@@ -5458,16 +5527,16 @@
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>755</v>
+        <v>770</v>
       </c>
       <c r="C31" t="s">
-        <v>756</v>
+        <v>771</v>
       </c>
       <c r="D31" t="s">
-        <v>757</v>
+        <v>772</v>
       </c>
       <c r="E31" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F31" t="s">
         <v>34</v>
@@ -5491,7 +5560,7 @@
         <v>42</v>
       </c>
       <c r="N31" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O31">
         <v>1</v>
@@ -5505,20 +5574,14 @@
       <c r="R31">
         <v>11</v>
       </c>
-      <c r="S31">
-        <v>6.99</v>
-      </c>
-      <c r="T31">
-        <v>1.17</v>
-      </c>
       <c r="Y31" t="s">
-        <v>758</v>
+        <v>773</v>
       </c>
       <c r="Z31" t="s">
-        <v>759</v>
+        <v>64</v>
       </c>
       <c r="AA31" t="s">
-        <v>760</v>
+        <v>774</v>
       </c>
       <c r="AB31" t="s">
         <v>39</v>
@@ -5532,13 +5595,13 @@
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>761</v>
+        <v>775</v>
       </c>
       <c r="C32" t="s">
-        <v>762</v>
+        <v>776</v>
       </c>
       <c r="D32" t="s">
-        <v>763</v>
+        <v>777</v>
       </c>
       <c r="E32" t="s">
         <v>33</v>
@@ -5556,13 +5619,13 @@
         <v>54</v>
       </c>
       <c r="K32" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L32" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M32" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N32" t="s">
         <v>33</v>
@@ -5574,19 +5637,16 @@
         <v>38</v>
       </c>
       <c r="Q32">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R32">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y32" t="s">
-        <v>764</v>
-      </c>
-      <c r="Z32" t="s">
-        <v>279</v>
+        <v>778</v>
       </c>
       <c r="AA32" t="s">
-        <v>765</v>
+        <v>779</v>
       </c>
       <c r="AB32" t="s">
         <v>39</v>
@@ -5600,16 +5660,16 @@
     </row>
     <row r="33" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="C33" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="D33" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="E33" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F33" t="s">
         <v>34</v>
@@ -5633,7 +5693,7 @@
         <v>74</v>
       </c>
       <c r="N33" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O33">
         <v>1</v>
@@ -5648,13 +5708,10 @@
         <v>2</v>
       </c>
       <c r="Y33" t="s">
-        <v>91</v>
-      </c>
-      <c r="Z33" t="s">
-        <v>121</v>
+        <v>748</v>
       </c>
       <c r="AA33" t="s">
-        <v>769</v>
+        <v>749</v>
       </c>
       <c r="AB33" t="s">
         <v>39</v>
@@ -5668,13 +5725,13 @@
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>770</v>
+        <v>750</v>
       </c>
       <c r="C34" t="s">
-        <v>771</v>
+        <v>751</v>
       </c>
       <c r="D34" t="s">
-        <v>772</v>
+        <v>752</v>
       </c>
       <c r="E34" t="s">
         <v>33</v>
@@ -5716,13 +5773,10 @@
         <v>11</v>
       </c>
       <c r="Y34" t="s">
-        <v>773</v>
-      </c>
-      <c r="Z34" t="s">
-        <v>64</v>
+        <v>753</v>
       </c>
       <c r="AA34" t="s">
-        <v>774</v>
+        <v>754</v>
       </c>
       <c r="AB34" t="s">
         <v>39</v>
@@ -5736,16 +5790,16 @@
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>775</v>
+        <v>755</v>
       </c>
       <c r="C35" t="s">
-        <v>776</v>
+        <v>756</v>
       </c>
       <c r="D35" t="s">
-        <v>777</v>
+        <v>757</v>
       </c>
       <c r="E35" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F35" t="s">
         <v>34</v>
@@ -5769,7 +5823,7 @@
         <v>42</v>
       </c>
       <c r="N35" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O35">
         <v>1</v>
@@ -5783,11 +5837,20 @@
       <c r="R35">
         <v>11</v>
       </c>
+      <c r="S35">
+        <v>6.99</v>
+      </c>
+      <c r="T35">
+        <v>1.17</v>
+      </c>
       <c r="Y35" t="s">
-        <v>778</v>
+        <v>758</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>759</v>
       </c>
       <c r="AA35" t="s">
-        <v>779</v>
+        <v>760</v>
       </c>
       <c r="AB35" t="s">
         <v>39</v>
@@ -5801,16 +5864,16 @@
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>714</v>
+        <v>761</v>
       </c>
       <c r="C36" t="s">
-        <v>715</v>
+        <v>762</v>
       </c>
       <c r="D36" t="s">
-        <v>716</v>
+        <v>763</v>
       </c>
       <c r="E36" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F36" t="s">
         <v>34</v>
@@ -5834,7 +5897,7 @@
         <v>74</v>
       </c>
       <c r="N36" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O36">
         <v>1</v>
@@ -5849,13 +5912,13 @@
         <v>2</v>
       </c>
       <c r="Y36" t="s">
-        <v>717</v>
+        <v>764</v>
       </c>
       <c r="Z36" t="s">
-        <v>51</v>
+        <v>279</v>
       </c>
       <c r="AA36" t="s">
-        <v>718</v>
+        <v>765</v>
       </c>
       <c r="AB36" t="s">
         <v>39</v>
@@ -5869,13 +5932,13 @@
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>719</v>
+        <v>766</v>
       </c>
       <c r="C37" t="s">
-        <v>720</v>
+        <v>767</v>
       </c>
       <c r="D37" t="s">
-        <v>721</v>
+        <v>768</v>
       </c>
       <c r="E37" t="s">
         <v>33</v>
@@ -5893,13 +5956,13 @@
         <v>54</v>
       </c>
       <c r="K37" t="s">
-        <v>722</v>
+        <v>72</v>
       </c>
       <c r="L37" t="s">
-        <v>723</v>
+        <v>73</v>
       </c>
       <c r="M37" t="s">
-        <v>724</v>
+        <v>74</v>
       </c>
       <c r="N37" t="s">
         <v>33</v>
@@ -5911,19 +5974,19 @@
         <v>38</v>
       </c>
       <c r="Q37">
-        <v>12.99</v>
+        <v>11.99</v>
       </c>
       <c r="R37">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="Y37" t="s">
-        <v>725</v>
+        <v>91</v>
       </c>
       <c r="Z37" t="s">
-        <v>726</v>
+        <v>121</v>
       </c>
       <c r="AA37" t="s">
-        <v>727</v>
+        <v>769</v>
       </c>
       <c r="AB37" t="s">
         <v>39</v>
@@ -5937,13 +6000,13 @@
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>728</v>
+        <v>770</v>
       </c>
       <c r="C38" t="s">
-        <v>729</v>
+        <v>771</v>
       </c>
       <c r="D38" t="s">
-        <v>730</v>
+        <v>772</v>
       </c>
       <c r="E38" t="s">
         <v>33</v>
@@ -5961,13 +6024,13 @@
         <v>54</v>
       </c>
       <c r="K38" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L38" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M38" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N38" t="s">
         <v>33</v>
@@ -5979,16 +6042,19 @@
         <v>38</v>
       </c>
       <c r="Q38">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R38">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y38" t="s">
-        <v>731</v>
+        <v>773</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>64</v>
       </c>
       <c r="AA38" t="s">
-        <v>732</v>
+        <v>774</v>
       </c>
       <c r="AB38" t="s">
         <v>39</v>
@@ -6002,13 +6068,13 @@
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>733</v>
+        <v>775</v>
       </c>
       <c r="C39" t="s">
-        <v>734</v>
+        <v>776</v>
       </c>
       <c r="D39" t="s">
-        <v>735</v>
+        <v>777</v>
       </c>
       <c r="E39" t="s">
         <v>33</v>
@@ -6026,13 +6092,13 @@
         <v>54</v>
       </c>
       <c r="K39" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L39" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M39" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N39" t="s">
         <v>33</v>
@@ -6044,16 +6110,16 @@
         <v>38</v>
       </c>
       <c r="Q39">
-        <v>40.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R39">
-        <v>6.83</v>
+        <v>11</v>
       </c>
       <c r="Y39" t="s">
-        <v>736</v>
+        <v>778</v>
       </c>
       <c r="AA39" t="s">
-        <v>737</v>
+        <v>779</v>
       </c>
       <c r="AB39" t="s">
         <v>39</v>
@@ -6067,16 +6133,16 @@
     </row>
     <row r="40" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>738</v>
+        <v>714</v>
       </c>
       <c r="C40" t="s">
-        <v>739</v>
+        <v>715</v>
       </c>
       <c r="D40" t="s">
-        <v>740</v>
+        <v>716</v>
       </c>
       <c r="E40" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F40" t="s">
         <v>34</v>
@@ -6091,16 +6157,16 @@
         <v>54</v>
       </c>
       <c r="K40" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L40" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M40" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O40">
         <v>1</v>
@@ -6109,16 +6175,19 @@
         <v>38</v>
       </c>
       <c r="Q40">
-        <v>40.99</v>
+        <v>11.99</v>
       </c>
       <c r="R40">
-        <v>6.83</v>
+        <v>2</v>
       </c>
       <c r="Y40" t="s">
-        <v>741</v>
+        <v>717</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>51</v>
       </c>
       <c r="AA40" t="s">
-        <v>742</v>
+        <v>718</v>
       </c>
       <c r="AB40" t="s">
         <v>39</v>
@@ -6132,13 +6201,13 @@
     </row>
     <row r="41" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>708</v>
+        <v>719</v>
       </c>
       <c r="C41" t="s">
-        <v>709</v>
+        <v>720</v>
       </c>
       <c r="D41" t="s">
-        <v>743</v>
+        <v>721</v>
       </c>
       <c r="E41" t="s">
         <v>33</v>
@@ -6156,13 +6225,13 @@
         <v>54</v>
       </c>
       <c r="K41" t="s">
-        <v>40</v>
+        <v>722</v>
       </c>
       <c r="L41" t="s">
-        <v>41</v>
+        <v>723</v>
       </c>
       <c r="M41" t="s">
-        <v>42</v>
+        <v>724</v>
       </c>
       <c r="N41" t="s">
         <v>33</v>
@@ -6174,19 +6243,19 @@
         <v>38</v>
       </c>
       <c r="Q41">
-        <v>65.989999999999995</v>
+        <v>12.99</v>
       </c>
       <c r="R41">
-        <v>11</v>
+        <v>2.17</v>
       </c>
       <c r="Y41" t="s">
-        <v>711</v>
+        <v>725</v>
       </c>
       <c r="Z41" t="s">
-        <v>712</v>
+        <v>726</v>
       </c>
       <c r="AA41" t="s">
-        <v>713</v>
+        <v>727</v>
       </c>
       <c r="AB41" t="s">
         <v>39</v>
@@ -6200,13 +6269,13 @@
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>643</v>
+        <v>728</v>
       </c>
       <c r="C42" t="s">
-        <v>644</v>
+        <v>729</v>
       </c>
       <c r="D42" t="s">
-        <v>744</v>
+        <v>730</v>
       </c>
       <c r="E42" t="s">
         <v>33</v>
@@ -6224,13 +6293,13 @@
         <v>54</v>
       </c>
       <c r="K42" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L42" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M42" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="N42" t="s">
         <v>33</v>
@@ -6242,16 +6311,16 @@
         <v>38</v>
       </c>
       <c r="Q42">
-        <v>14.99</v>
+        <v>11.99</v>
       </c>
       <c r="R42">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Y42" t="s">
-        <v>646</v>
+        <v>731</v>
       </c>
       <c r="AA42" t="s">
-        <v>647</v>
+        <v>732</v>
       </c>
       <c r="AB42" t="s">
         <v>39</v>
@@ -6265,16 +6334,16 @@
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>708</v>
+        <v>733</v>
       </c>
       <c r="C43" t="s">
-        <v>709</v>
+        <v>734</v>
       </c>
       <c r="D43" t="s">
-        <v>710</v>
+        <v>735</v>
       </c>
       <c r="E43" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F43" t="s">
         <v>34</v>
@@ -6289,16 +6358,16 @@
         <v>54</v>
       </c>
       <c r="K43" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L43" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M43" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N43" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O43">
         <v>1</v>
@@ -6307,19 +6376,16 @@
         <v>38</v>
       </c>
       <c r="Q43">
-        <v>65.989999999999995</v>
+        <v>40.99</v>
       </c>
       <c r="R43">
-        <v>11</v>
+        <v>6.83</v>
       </c>
       <c r="Y43" t="s">
-        <v>711</v>
-      </c>
-      <c r="Z43" t="s">
-        <v>712</v>
+        <v>736</v>
       </c>
       <c r="AA43" t="s">
-        <v>713</v>
+        <v>737</v>
       </c>
       <c r="AB43" t="s">
         <v>39</v>
@@ -6333,22 +6399,22 @@
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>138</v>
+        <v>738</v>
       </c>
       <c r="C44" t="s">
-        <v>139</v>
+        <v>739</v>
       </c>
       <c r="D44" t="s">
-        <v>187</v>
+        <v>740</v>
       </c>
       <c r="E44" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F44" t="s">
         <v>34</v>
       </c>
       <c r="G44" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="H44" t="s">
         <v>36</v>
@@ -6357,25 +6423,37 @@
         <v>54</v>
       </c>
       <c r="K44" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="L44" t="s">
-        <v>142</v>
+        <v>49</v>
       </c>
       <c r="M44" t="s">
-        <v>143</v>
+        <v>50</v>
+      </c>
+      <c r="N44" t="s">
+        <v>33</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P44" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q44">
+        <v>40.99</v>
+      </c>
+      <c r="R44">
+        <v>6.83</v>
       </c>
       <c r="Y44" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA44">
-        <v>80100</v>
+        <v>741</v>
+      </c>
+      <c r="AA44" t="s">
+        <v>742</v>
       </c>
       <c r="AB44" t="s">
-        <v>145</v>
+        <v>39</v>
       </c>
       <c r="AD44" t="b">
         <v>0</v>
@@ -6386,22 +6464,22 @@
     </row>
     <row r="45" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>146</v>
+        <v>708</v>
       </c>
       <c r="C45" t="s">
-        <v>147</v>
+        <v>709</v>
       </c>
       <c r="D45" t="s">
-        <v>148</v>
+        <v>743</v>
       </c>
       <c r="E45" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F45" t="s">
         <v>34</v>
       </c>
       <c r="G45" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="H45" t="s">
         <v>36</v>
@@ -6410,25 +6488,40 @@
         <v>54</v>
       </c>
       <c r="K45" t="s">
-        <v>141</v>
+        <v>40</v>
       </c>
       <c r="L45" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="M45" t="s">
-        <v>143</v>
+        <v>42</v>
+      </c>
+      <c r="N45" t="s">
+        <v>33</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P45" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q45">
+        <v>65.989999999999995</v>
+      </c>
+      <c r="R45">
+        <v>11</v>
       </c>
       <c r="Y45" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA45">
-        <v>80100</v>
+        <v>711</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>712</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>713</v>
       </c>
       <c r="AB45" t="s">
-        <v>145</v>
+        <v>39</v>
       </c>
       <c r="AD45" t="b">
         <v>0</v>
@@ -6439,22 +6532,22 @@
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>632</v>
+        <v>643</v>
       </c>
       <c r="C46" t="s">
-        <v>633</v>
+        <v>644</v>
       </c>
       <c r="D46" t="s">
-        <v>634</v>
+        <v>744</v>
       </c>
       <c r="E46" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F46" t="s">
         <v>34</v>
       </c>
       <c r="G46" t="s">
-        <v>635</v>
+        <v>35</v>
       </c>
       <c r="H46" t="s">
         <v>36</v>
@@ -6463,37 +6556,37 @@
         <v>54</v>
       </c>
       <c r="K46" t="s">
-        <v>636</v>
+        <v>94</v>
       </c>
       <c r="L46" t="s">
-        <v>637</v>
+        <v>82</v>
       </c>
       <c r="M46" t="s">
-        <v>638</v>
+        <v>83</v>
+      </c>
+      <c r="N46" t="s">
+        <v>33</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="Q46">
-        <v>22.9</v>
+        <v>14.99</v>
       </c>
       <c r="R46">
-        <v>4.8099999999999996</v>
+        <v>2.5</v>
       </c>
       <c r="Y46" t="s">
-        <v>639</v>
-      </c>
-      <c r="Z46" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="AA46" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="AB46" t="s">
-        <v>642</v>
+        <v>39</v>
       </c>
       <c r="AD46" t="b">
         <v>0</v>
@@ -6504,13 +6597,13 @@
     </row>
     <row r="47" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>643</v>
+        <v>708</v>
       </c>
       <c r="C47" t="s">
-        <v>644</v>
+        <v>709</v>
       </c>
       <c r="D47" t="s">
-        <v>645</v>
+        <v>710</v>
       </c>
       <c r="E47" t="s">
         <v>98</v>
@@ -6528,13 +6621,13 @@
         <v>54</v>
       </c>
       <c r="K47" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L47" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M47" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="N47" t="s">
         <v>99</v>
@@ -6546,16 +6639,19 @@
         <v>38</v>
       </c>
       <c r="Q47">
-        <v>14.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R47">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="Y47" t="s">
-        <v>646</v>
+        <v>711</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>712</v>
       </c>
       <c r="AA47" t="s">
-        <v>647</v>
+        <v>713</v>
       </c>
       <c r="AB47" t="s">
         <v>39</v>
@@ -6569,22 +6665,22 @@
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>609</v>
+        <v>138</v>
       </c>
       <c r="C48" t="s">
-        <v>610</v>
+        <v>139</v>
       </c>
       <c r="D48" t="s">
-        <v>611</v>
+        <v>187</v>
       </c>
       <c r="E48" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F48" t="s">
         <v>34</v>
       </c>
       <c r="G48" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="H48" t="s">
         <v>36</v>
@@ -6593,40 +6689,25 @@
         <v>54</v>
       </c>
       <c r="K48" t="s">
-        <v>94</v>
+        <v>141</v>
       </c>
       <c r="L48" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="M48" t="s">
-        <v>83</v>
-      </c>
-      <c r="N48" t="s">
-        <v>33</v>
+        <v>143</v>
       </c>
       <c r="O48">
-        <v>1</v>
-      </c>
-      <c r="P48" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q48">
-        <v>14.99</v>
-      </c>
-      <c r="R48">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="s">
-        <v>612</v>
-      </c>
-      <c r="Z48" t="s">
-        <v>613</v>
-      </c>
-      <c r="AA48" t="s">
-        <v>614</v>
+        <v>144</v>
+      </c>
+      <c r="AA48">
+        <v>80100</v>
       </c>
       <c r="AB48" t="s">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="AD48" t="b">
         <v>0</v>
@@ -6637,13 +6718,13 @@
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>493</v>
+        <v>146</v>
       </c>
       <c r="C49" t="s">
-        <v>494</v>
+        <v>147</v>
       </c>
       <c r="D49" t="s">
-        <v>648</v>
+        <v>148</v>
       </c>
       <c r="E49" t="s">
         <v>53</v>
@@ -6652,7 +6733,7 @@
         <v>34</v>
       </c>
       <c r="G49" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="H49" t="s">
         <v>36</v>
@@ -6661,25 +6742,25 @@
         <v>54</v>
       </c>
       <c r="K49" t="s">
-        <v>40</v>
+        <v>141</v>
       </c>
       <c r="L49" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="M49" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="O49">
         <v>0</v>
       </c>
       <c r="Y49" t="s">
-        <v>495</v>
-      </c>
-      <c r="AA49" t="s">
-        <v>496</v>
+        <v>144</v>
+      </c>
+      <c r="AA49">
+        <v>80100</v>
       </c>
       <c r="AB49" t="s">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="AD49" t="b">
         <v>0</v>
@@ -6690,22 +6771,22 @@
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>615</v>
+        <v>632</v>
       </c>
       <c r="C50" t="s">
-        <v>616</v>
+        <v>633</v>
       </c>
       <c r="D50" t="s">
-        <v>617</v>
+        <v>634</v>
       </c>
       <c r="E50" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="F50" t="s">
         <v>34</v>
       </c>
       <c r="G50" t="s">
-        <v>35</v>
+        <v>635</v>
       </c>
       <c r="H50" t="s">
         <v>36</v>
@@ -6714,37 +6795,37 @@
         <v>54</v>
       </c>
       <c r="K50" t="s">
-        <v>48</v>
+        <v>636</v>
       </c>
       <c r="L50" t="s">
-        <v>49</v>
+        <v>637</v>
       </c>
       <c r="M50" t="s">
-        <v>50</v>
-      </c>
-      <c r="N50" t="s">
-        <v>99</v>
+        <v>638</v>
       </c>
       <c r="O50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P50" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="Q50">
-        <v>40.99</v>
+        <v>22.9</v>
+      </c>
+      <c r="R50">
+        <v>4.8099999999999996</v>
       </c>
       <c r="Y50" t="s">
-        <v>618</v>
+        <v>639</v>
       </c>
       <c r="Z50" t="s">
-        <v>619</v>
+        <v>640</v>
       </c>
       <c r="AA50" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="AB50" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="AD50" t="b">
         <v>0</v>
@@ -6755,16 +6836,16 @@
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>621</v>
+        <v>643</v>
       </c>
       <c r="C51" t="s">
-        <v>622</v>
+        <v>644</v>
       </c>
       <c r="D51" t="s">
-        <v>623</v>
+        <v>645</v>
       </c>
       <c r="E51" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F51" t="s">
         <v>34</v>
@@ -6779,16 +6860,16 @@
         <v>54</v>
       </c>
       <c r="K51" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L51" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M51" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="N51" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O51">
         <v>1</v>
@@ -6797,25 +6878,16 @@
         <v>38</v>
       </c>
       <c r="Q51">
-        <v>64.989999999999995</v>
+        <v>14.99</v>
       </c>
       <c r="R51">
-        <v>10.83</v>
-      </c>
-      <c r="S51">
-        <v>6.99</v>
-      </c>
-      <c r="T51">
-        <v>1.17</v>
+        <v>2.5</v>
       </c>
       <c r="Y51" t="s">
-        <v>624</v>
-      </c>
-      <c r="Z51" t="s">
-        <v>625</v>
+        <v>646</v>
       </c>
       <c r="AA51" t="s">
-        <v>626</v>
+        <v>647</v>
       </c>
       <c r="AB51" t="s">
         <v>39</v>
@@ -6829,13 +6901,13 @@
     </row>
     <row r="52" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>627</v>
+        <v>609</v>
       </c>
       <c r="C52" t="s">
-        <v>628</v>
+        <v>610</v>
       </c>
       <c r="D52" t="s">
-        <v>629</v>
+        <v>611</v>
       </c>
       <c r="E52" t="s">
         <v>33</v>
@@ -6853,13 +6925,13 @@
         <v>54</v>
       </c>
       <c r="K52" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="L52" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="M52" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="N52" t="s">
         <v>33</v>
@@ -6871,16 +6943,19 @@
         <v>38</v>
       </c>
       <c r="Q52">
-        <v>11.99</v>
+        <v>14.99</v>
       </c>
       <c r="R52">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Y52" t="s">
-        <v>630</v>
+        <v>612</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>613</v>
       </c>
       <c r="AA52" t="s">
-        <v>631</v>
+        <v>614</v>
       </c>
       <c r="AB52" t="s">
         <v>39</v>
@@ -6894,16 +6969,16 @@
     </row>
     <row r="53" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>649</v>
+        <v>493</v>
       </c>
       <c r="C53" t="s">
-        <v>650</v>
+        <v>494</v>
       </c>
       <c r="D53" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="E53" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F53" t="s">
         <v>34</v>
@@ -6918,37 +6993,22 @@
         <v>54</v>
       </c>
       <c r="K53" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L53" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M53" t="s">
-        <v>50</v>
-      </c>
-      <c r="N53" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O53">
-        <v>1</v>
-      </c>
-      <c r="P53" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q53">
-        <v>39.99</v>
-      </c>
-      <c r="R53">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="s">
-        <v>652</v>
-      </c>
-      <c r="Z53" t="s">
-        <v>653</v>
+        <v>495</v>
       </c>
       <c r="AA53" t="s">
-        <v>654</v>
+        <v>496</v>
       </c>
       <c r="AB53" t="s">
         <v>39</v>
@@ -6962,16 +7022,16 @@
     </row>
     <row r="54" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>655</v>
+        <v>615</v>
       </c>
       <c r="C54" t="s">
-        <v>656</v>
+        <v>616</v>
       </c>
       <c r="D54" t="s">
-        <v>657</v>
+        <v>617</v>
       </c>
       <c r="E54" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F54" t="s">
         <v>34</v>
@@ -6986,16 +7046,16 @@
         <v>54</v>
       </c>
       <c r="K54" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="L54" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="M54" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="N54" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O54">
         <v>1</v>
@@ -7004,16 +7064,16 @@
         <v>38</v>
       </c>
       <c r="Q54">
-        <v>14.99</v>
-      </c>
-      <c r="R54">
-        <v>2.5</v>
+        <v>40.99</v>
       </c>
       <c r="Y54" t="s">
-        <v>658</v>
+        <v>618</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>619</v>
       </c>
       <c r="AA54" t="s">
-        <v>659</v>
+        <v>620</v>
       </c>
       <c r="AB54" t="s">
         <v>39</v>
@@ -7027,13 +7087,13 @@
     </row>
     <row r="55" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>571</v>
+        <v>621</v>
       </c>
       <c r="C55" t="s">
-        <v>572</v>
+        <v>622</v>
       </c>
       <c r="D55" t="s">
-        <v>660</v>
+        <v>623</v>
       </c>
       <c r="E55" t="s">
         <v>33</v>
@@ -7074,11 +7134,20 @@
       <c r="R55">
         <v>10.83</v>
       </c>
+      <c r="S55">
+        <v>6.99</v>
+      </c>
+      <c r="T55">
+        <v>1.17</v>
+      </c>
       <c r="Y55" t="s">
-        <v>573</v>
+        <v>624</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>625</v>
       </c>
       <c r="AA55" t="s">
-        <v>574</v>
+        <v>626</v>
       </c>
       <c r="AB55" t="s">
         <v>39</v>
@@ -7092,13 +7161,13 @@
     </row>
     <row r="56" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>599</v>
+        <v>627</v>
       </c>
       <c r="C56" t="s">
-        <v>600</v>
+        <v>628</v>
       </c>
       <c r="D56" t="s">
-        <v>601</v>
+        <v>629</v>
       </c>
       <c r="E56" t="s">
         <v>33</v>
@@ -7116,13 +7185,13 @@
         <v>54</v>
       </c>
       <c r="K56" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L56" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M56" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="N56" t="s">
         <v>33</v>
@@ -7134,16 +7203,16 @@
         <v>38</v>
       </c>
       <c r="Q56">
-        <v>14.99</v>
+        <v>11.99</v>
       </c>
       <c r="R56">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Y56" t="s">
-        <v>61</v>
+        <v>630</v>
       </c>
       <c r="AA56" t="s">
-        <v>602</v>
+        <v>631</v>
       </c>
       <c r="AB56" t="s">
         <v>39</v>
@@ -7157,13 +7226,13 @@
     </row>
     <row r="57" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>589</v>
+        <v>649</v>
       </c>
       <c r="C57" t="s">
-        <v>590</v>
+        <v>650</v>
       </c>
       <c r="D57" t="s">
-        <v>591</v>
+        <v>651</v>
       </c>
       <c r="E57" t="s">
         <v>33</v>
@@ -7181,13 +7250,13 @@
         <v>54</v>
       </c>
       <c r="K57" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L57" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M57" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N57" t="s">
         <v>33</v>
@@ -7199,16 +7268,19 @@
         <v>38</v>
       </c>
       <c r="Q57">
-        <v>64.989999999999995</v>
+        <v>39.99</v>
       </c>
       <c r="R57">
-        <v>10.83</v>
+        <v>6.67</v>
       </c>
       <c r="Y57" t="s">
-        <v>592</v>
+        <v>652</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>653</v>
       </c>
       <c r="AA57" t="s">
-        <v>593</v>
+        <v>654</v>
       </c>
       <c r="AB57" t="s">
         <v>39</v>
@@ -7222,13 +7294,13 @@
     </row>
     <row r="58" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>594</v>
+        <v>655</v>
       </c>
       <c r="C58" t="s">
-        <v>595</v>
+        <v>656</v>
       </c>
       <c r="D58" t="s">
-        <v>596</v>
+        <v>657</v>
       </c>
       <c r="E58" t="s">
         <v>33</v>
@@ -7246,13 +7318,13 @@
         <v>54</v>
       </c>
       <c r="K58" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L58" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M58" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="N58" t="s">
         <v>33</v>
@@ -7264,16 +7336,16 @@
         <v>38</v>
       </c>
       <c r="Q58">
-        <v>64.989999999999995</v>
+        <v>14.99</v>
       </c>
       <c r="R58">
-        <v>10.83</v>
+        <v>2.5</v>
       </c>
       <c r="Y58" t="s">
-        <v>597</v>
+        <v>658</v>
       </c>
       <c r="AA58" t="s">
-        <v>598</v>
+        <v>659</v>
       </c>
       <c r="AB58" t="s">
         <v>39</v>
@@ -7287,13 +7359,13 @@
     </row>
     <row r="59" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>603</v>
+        <v>571</v>
       </c>
       <c r="C59" t="s">
-        <v>604</v>
+        <v>572</v>
       </c>
       <c r="D59" t="s">
-        <v>605</v>
+        <v>660</v>
       </c>
       <c r="E59" t="s">
         <v>33</v>
@@ -7335,13 +7407,10 @@
         <v>10.83</v>
       </c>
       <c r="Y59" t="s">
-        <v>606</v>
-      </c>
-      <c r="Z59" t="s">
-        <v>607</v>
+        <v>573</v>
       </c>
       <c r="AA59" t="s">
-        <v>608</v>
+        <v>574</v>
       </c>
       <c r="AB59" t="s">
         <v>39</v>
@@ -7355,13 +7424,13 @@
     </row>
     <row r="60" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>578</v>
+        <v>599</v>
       </c>
       <c r="C60" t="s">
-        <v>579</v>
+        <v>600</v>
       </c>
       <c r="D60" t="s">
-        <v>661</v>
+        <v>601</v>
       </c>
       <c r="E60" t="s">
         <v>33</v>
@@ -7379,13 +7448,13 @@
         <v>54</v>
       </c>
       <c r="K60" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L60" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M60" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="N60" t="s">
         <v>33</v>
@@ -7397,19 +7466,16 @@
         <v>38</v>
       </c>
       <c r="Q60">
-        <v>64.989999999999995</v>
+        <v>14.99</v>
       </c>
       <c r="R60">
-        <v>10.83</v>
+        <v>2.5</v>
       </c>
       <c r="Y60" t="s">
-        <v>580</v>
-      </c>
-      <c r="Z60" t="s">
-        <v>581</v>
+        <v>61</v>
       </c>
       <c r="AA60" t="s">
-        <v>582</v>
+        <v>602</v>
       </c>
       <c r="AB60" t="s">
         <v>39</v>
@@ -7423,16 +7489,16 @@
     </row>
     <row r="61" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>575</v>
+        <v>589</v>
       </c>
       <c r="C61" t="s">
-        <v>576</v>
+        <v>590</v>
       </c>
       <c r="D61" t="s">
-        <v>577</v>
+        <v>591</v>
       </c>
       <c r="E61" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F61" t="s">
         <v>34</v>
@@ -7455,14 +7521,26 @@
       <c r="M61" t="s">
         <v>42</v>
       </c>
+      <c r="N61" t="s">
+        <v>33</v>
+      </c>
       <c r="O61">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P61" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q61">
+        <v>64.989999999999995</v>
+      </c>
+      <c r="R61">
+        <v>10.83</v>
       </c>
       <c r="Y61" t="s">
-        <v>573</v>
+        <v>592</v>
       </c>
       <c r="AA61" t="s">
-        <v>574</v>
+        <v>593</v>
       </c>
       <c r="AB61" t="s">
         <v>39</v>
@@ -7476,13 +7554,13 @@
     </row>
     <row r="62" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>518</v>
+        <v>594</v>
       </c>
       <c r="C62" t="s">
-        <v>519</v>
+        <v>595</v>
       </c>
       <c r="D62" t="s">
-        <v>583</v>
+        <v>596</v>
       </c>
       <c r="E62" t="s">
         <v>33</v>
@@ -7500,13 +7578,13 @@
         <v>54</v>
       </c>
       <c r="K62" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L62" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M62" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N62" t="s">
         <v>33</v>
@@ -7518,22 +7596,16 @@
         <v>38</v>
       </c>
       <c r="Q62">
-        <v>37.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R62">
-        <v>6.33</v>
-      </c>
-      <c r="S62">
-        <v>6.99</v>
-      </c>
-      <c r="T62">
-        <v>1.17</v>
+        <v>10.83</v>
       </c>
       <c r="Y62" t="s">
-        <v>46</v>
+        <v>597</v>
       </c>
       <c r="AA62" t="s">
-        <v>520</v>
+        <v>598</v>
       </c>
       <c r="AB62" t="s">
         <v>39</v>
@@ -7547,13 +7619,13 @@
     </row>
     <row r="63" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>584</v>
+        <v>603</v>
       </c>
       <c r="C63" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="D63" t="s">
-        <v>586</v>
+        <v>605</v>
       </c>
       <c r="E63" t="s">
         <v>33</v>
@@ -7595,10 +7667,13 @@
         <v>10.83</v>
       </c>
       <c r="Y63" t="s">
-        <v>587</v>
+        <v>606</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>607</v>
       </c>
       <c r="AA63" t="s">
-        <v>588</v>
+        <v>608</v>
       </c>
       <c r="AB63" t="s">
         <v>39</v>
@@ -7612,13 +7687,13 @@
     </row>
     <row r="64" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>457</v>
+        <v>578</v>
       </c>
       <c r="C64" t="s">
-        <v>458</v>
+        <v>579</v>
       </c>
       <c r="D64" t="s">
-        <v>459</v>
+        <v>661</v>
       </c>
       <c r="E64" t="s">
         <v>33</v>
@@ -7660,13 +7735,13 @@
         <v>10.83</v>
       </c>
       <c r="Y64" t="s">
-        <v>460</v>
+        <v>580</v>
       </c>
       <c r="Z64" t="s">
-        <v>279</v>
+        <v>581</v>
       </c>
       <c r="AA64" t="s">
-        <v>461</v>
+        <v>582</v>
       </c>
       <c r="AB64" t="s">
         <v>39</v>
@@ -7680,16 +7755,16 @@
     </row>
     <row r="65" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>462</v>
+        <v>575</v>
       </c>
       <c r="C65" t="s">
-        <v>463</v>
+        <v>576</v>
       </c>
       <c r="D65" t="s">
-        <v>459</v>
+        <v>577</v>
       </c>
       <c r="E65" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F65" t="s">
         <v>34</v>
@@ -7712,26 +7787,14 @@
       <c r="M65" t="s">
         <v>42</v>
       </c>
-      <c r="N65" t="s">
-        <v>33</v>
-      </c>
       <c r="O65">
-        <v>1</v>
-      </c>
-      <c r="P65" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q65">
-        <v>64.989999999999995</v>
-      </c>
-      <c r="R65">
-        <v>10.83</v>
+        <v>0</v>
       </c>
       <c r="Y65" t="s">
-        <v>56</v>
+        <v>573</v>
       </c>
       <c r="AA65" t="s">
-        <v>464</v>
+        <v>574</v>
       </c>
       <c r="AB65" t="s">
         <v>39</v>
@@ -7745,13 +7808,13 @@
     </row>
     <row r="66" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>465</v>
+        <v>518</v>
       </c>
       <c r="C66" t="s">
-        <v>466</v>
+        <v>519</v>
       </c>
       <c r="D66" t="s">
-        <v>467</v>
+        <v>583</v>
       </c>
       <c r="E66" t="s">
         <v>33</v>
@@ -7781,22 +7844,28 @@
         <v>33</v>
       </c>
       <c r="O66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P66" t="s">
         <v>38</v>
       </c>
       <c r="Q66">
-        <v>79.98</v>
+        <v>37.99</v>
       </c>
       <c r="R66">
-        <v>13.34</v>
+        <v>6.33</v>
+      </c>
+      <c r="S66">
+        <v>6.99</v>
+      </c>
+      <c r="T66">
+        <v>1.17</v>
       </c>
       <c r="Y66" t="s">
-        <v>468</v>
+        <v>46</v>
       </c>
       <c r="AA66" t="s">
-        <v>469</v>
+        <v>520</v>
       </c>
       <c r="AB66" t="s">
         <v>39</v>
@@ -7810,13 +7879,13 @@
     </row>
     <row r="67" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>470</v>
+        <v>584</v>
       </c>
       <c r="C67" t="s">
-        <v>471</v>
+        <v>585</v>
       </c>
       <c r="D67" t="s">
-        <v>472</v>
+        <v>586</v>
       </c>
       <c r="E67" t="s">
         <v>33</v>
@@ -7834,13 +7903,13 @@
         <v>54</v>
       </c>
       <c r="K67" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L67" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M67" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N67" t="s">
         <v>33</v>
@@ -7852,16 +7921,16 @@
         <v>38</v>
       </c>
       <c r="Q67">
-        <v>37.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R67">
-        <v>6.33</v>
+        <v>10.83</v>
       </c>
       <c r="Y67" t="s">
-        <v>473</v>
+        <v>587</v>
       </c>
       <c r="AA67" t="s">
-        <v>474</v>
+        <v>588</v>
       </c>
       <c r="AB67" t="s">
         <v>39</v>
@@ -7875,16 +7944,16 @@
     </row>
     <row r="68" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>475</v>
+        <v>457</v>
       </c>
       <c r="C68" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
       <c r="D68" t="s">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="E68" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F68" t="s">
         <v>34</v>
@@ -7907,17 +7976,29 @@
       <c r="M68" t="s">
         <v>42</v>
       </c>
+      <c r="N68" t="s">
+        <v>33</v>
+      </c>
       <c r="O68">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P68" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q68">
+        <v>64.989999999999995</v>
+      </c>
+      <c r="R68">
+        <v>10.83</v>
       </c>
       <c r="Y68" t="s">
-        <v>478</v>
+        <v>460</v>
       </c>
       <c r="Z68" t="s">
         <v>279</v>
       </c>
       <c r="AA68" t="s">
-        <v>479</v>
+        <v>461</v>
       </c>
       <c r="AB68" t="s">
         <v>39</v>
@@ -7931,13 +8012,13 @@
     </row>
     <row r="69" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>480</v>
+        <v>462</v>
       </c>
       <c r="C69" t="s">
-        <v>481</v>
+        <v>463</v>
       </c>
       <c r="D69" t="s">
-        <v>482</v>
+        <v>459</v>
       </c>
       <c r="E69" t="s">
         <v>33</v>
@@ -7955,13 +8036,13 @@
         <v>54</v>
       </c>
       <c r="K69" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L69" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M69" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N69" t="s">
         <v>33</v>
@@ -7973,16 +8054,16 @@
         <v>38</v>
       </c>
       <c r="Q69">
-        <v>11.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R69">
-        <v>2</v>
+        <v>10.83</v>
       </c>
       <c r="Y69" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="AA69" t="s">
-        <v>483</v>
+        <v>464</v>
       </c>
       <c r="AB69" t="s">
         <v>39</v>
@@ -7996,13 +8077,13 @@
     </row>
     <row r="70" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>484</v>
+        <v>465</v>
       </c>
       <c r="C70" t="s">
-        <v>485</v>
+        <v>466</v>
       </c>
       <c r="D70" t="s">
-        <v>486</v>
+        <v>467</v>
       </c>
       <c r="E70" t="s">
         <v>33</v>
@@ -8020,34 +8101,34 @@
         <v>54</v>
       </c>
       <c r="K70" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L70" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M70" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N70" t="s">
         <v>33</v>
       </c>
       <c r="O70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P70" t="s">
         <v>38</v>
       </c>
       <c r="Q70">
-        <v>64.989999999999995</v>
+        <v>79.98</v>
       </c>
       <c r="R70">
-        <v>10.83</v>
+        <v>13.34</v>
       </c>
       <c r="Y70" t="s">
-        <v>67</v>
+        <v>468</v>
       </c>
       <c r="AA70" t="s">
-        <v>487</v>
+        <v>469</v>
       </c>
       <c r="AB70" t="s">
         <v>39</v>
@@ -8061,13 +8142,13 @@
     </row>
     <row r="71" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>488</v>
+        <v>470</v>
       </c>
       <c r="C71" t="s">
-        <v>489</v>
+        <v>471</v>
       </c>
       <c r="D71" t="s">
-        <v>490</v>
+        <v>472</v>
       </c>
       <c r="E71" t="s">
         <v>33</v>
@@ -8097,25 +8178,22 @@
         <v>33</v>
       </c>
       <c r="O71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P71" t="s">
         <v>38</v>
       </c>
       <c r="Q71">
-        <v>79.98</v>
+        <v>37.99</v>
       </c>
       <c r="R71">
-        <v>13.34</v>
+        <v>6.33</v>
       </c>
       <c r="Y71" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z71" t="s">
-        <v>491</v>
+        <v>473</v>
       </c>
       <c r="AA71" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="AB71" t="s">
         <v>39</v>
@@ -8129,16 +8207,16 @@
     </row>
     <row r="72" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>497</v>
+        <v>475</v>
       </c>
       <c r="C72" t="s">
-        <v>498</v>
+        <v>476</v>
       </c>
       <c r="D72" t="s">
-        <v>499</v>
+        <v>477</v>
       </c>
       <c r="E72" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F72" t="s">
         <v>34</v>
@@ -8161,29 +8239,17 @@
       <c r="M72" t="s">
         <v>42</v>
       </c>
-      <c r="N72" t="s">
-        <v>33</v>
-      </c>
       <c r="O72">
-        <v>1</v>
-      </c>
-      <c r="P72" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q72">
-        <v>59.99</v>
-      </c>
-      <c r="R72">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y72" t="s">
-        <v>500</v>
+        <v>478</v>
       </c>
       <c r="Z72" t="s">
-        <v>501</v>
+        <v>279</v>
       </c>
       <c r="AA72" t="s">
-        <v>502</v>
+        <v>479</v>
       </c>
       <c r="AB72" t="s">
         <v>39</v>
@@ -8197,13 +8263,13 @@
     </row>
     <row r="73" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>503</v>
+        <v>480</v>
       </c>
       <c r="C73" t="s">
-        <v>504</v>
+        <v>481</v>
       </c>
       <c r="D73" t="s">
-        <v>499</v>
+        <v>482</v>
       </c>
       <c r="E73" t="s">
         <v>33</v>
@@ -8221,13 +8287,13 @@
         <v>54</v>
       </c>
       <c r="K73" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L73" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M73" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N73" t="s">
         <v>33</v>
@@ -8239,19 +8305,16 @@
         <v>38</v>
       </c>
       <c r="Q73">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R73">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y73" t="s">
-        <v>505</v>
-      </c>
-      <c r="Z73" t="s">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="AA73" t="s">
-        <v>506</v>
+        <v>483</v>
       </c>
       <c r="AB73" t="s">
         <v>39</v>
@@ -8265,13 +8328,13 @@
     </row>
     <row r="74" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>507</v>
+        <v>484</v>
       </c>
       <c r="C74" t="s">
-        <v>508</v>
+        <v>485</v>
       </c>
       <c r="D74" t="s">
-        <v>509</v>
+        <v>486</v>
       </c>
       <c r="E74" t="s">
         <v>33</v>
@@ -8307,16 +8370,16 @@
         <v>38</v>
       </c>
       <c r="Q74">
-        <v>59.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R74">
-        <v>10</v>
+        <v>10.83</v>
       </c>
       <c r="Y74" t="s">
-        <v>510</v>
+        <v>67</v>
       </c>
       <c r="AA74" t="s">
-        <v>511</v>
+        <v>487</v>
       </c>
       <c r="AB74" t="s">
         <v>39</v>
@@ -8330,13 +8393,13 @@
     </row>
     <row r="75" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>512</v>
+        <v>488</v>
       </c>
       <c r="C75" t="s">
-        <v>513</v>
+        <v>489</v>
       </c>
       <c r="D75" t="s">
-        <v>514</v>
+        <v>490</v>
       </c>
       <c r="E75" t="s">
         <v>33</v>
@@ -8354,37 +8417,37 @@
         <v>54</v>
       </c>
       <c r="K75" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L75" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M75" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N75" t="s">
         <v>33</v>
       </c>
       <c r="O75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P75" t="s">
         <v>38</v>
       </c>
       <c r="Q75">
-        <v>59.99</v>
+        <v>79.98</v>
       </c>
       <c r="R75">
-        <v>10</v>
+        <v>13.34</v>
       </c>
       <c r="Y75" t="s">
-        <v>515</v>
+        <v>63</v>
       </c>
       <c r="Z75" t="s">
-        <v>516</v>
+        <v>491</v>
       </c>
       <c r="AA75" t="s">
-        <v>517</v>
+        <v>492</v>
       </c>
       <c r="AB75" t="s">
         <v>39</v>
@@ -8398,13 +8461,13 @@
     </row>
     <row r="76" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>521</v>
+        <v>497</v>
       </c>
       <c r="C76" t="s">
-        <v>522</v>
+        <v>498</v>
       </c>
       <c r="D76" t="s">
-        <v>523</v>
+        <v>499</v>
       </c>
       <c r="E76" t="s">
         <v>33</v>
@@ -8422,13 +8485,13 @@
         <v>54</v>
       </c>
       <c r="K76" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L76" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M76" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="N76" t="s">
         <v>33</v>
@@ -8440,16 +8503,19 @@
         <v>38</v>
       </c>
       <c r="Q76">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R76">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y76" t="s">
-        <v>58</v>
+        <v>500</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>501</v>
       </c>
       <c r="AA76" t="s">
-        <v>524</v>
+        <v>502</v>
       </c>
       <c r="AB76" t="s">
         <v>39</v>
@@ -8463,13 +8529,13 @@
     </row>
     <row r="77" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>525</v>
+        <v>503</v>
       </c>
       <c r="C77" t="s">
-        <v>526</v>
+        <v>504</v>
       </c>
       <c r="D77" t="s">
-        <v>527</v>
+        <v>499</v>
       </c>
       <c r="E77" t="s">
         <v>33</v>
@@ -8511,10 +8577,13 @@
         <v>10</v>
       </c>
       <c r="Y77" t="s">
-        <v>90</v>
+        <v>505</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>93</v>
       </c>
       <c r="AA77" t="s">
-        <v>528</v>
+        <v>506</v>
       </c>
       <c r="AB77" t="s">
         <v>39</v>
@@ -8528,13 +8597,13 @@
     </row>
     <row r="78" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>529</v>
+        <v>507</v>
       </c>
       <c r="C78" t="s">
-        <v>530</v>
+        <v>508</v>
       </c>
       <c r="D78" t="s">
-        <v>527</v>
+        <v>509</v>
       </c>
       <c r="E78" t="s">
         <v>33</v>
@@ -8576,10 +8645,10 @@
         <v>10</v>
       </c>
       <c r="Y78" t="s">
-        <v>531</v>
+        <v>510</v>
       </c>
       <c r="AA78" t="s">
-        <v>532</v>
+        <v>511</v>
       </c>
       <c r="AB78" t="s">
         <v>39</v>
@@ -8593,13 +8662,13 @@
     </row>
     <row r="79" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>533</v>
+        <v>512</v>
       </c>
       <c r="C79" t="s">
-        <v>534</v>
+        <v>513</v>
       </c>
       <c r="D79" t="s">
-        <v>535</v>
+        <v>514</v>
       </c>
       <c r="E79" t="s">
         <v>33</v>
@@ -8617,13 +8686,13 @@
         <v>54</v>
       </c>
       <c r="K79" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L79" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M79" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N79" t="s">
         <v>33</v>
@@ -8635,19 +8704,19 @@
         <v>38</v>
       </c>
       <c r="Q79">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R79">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y79" t="s">
-        <v>536</v>
+        <v>515</v>
       </c>
       <c r="Z79" t="s">
-        <v>537</v>
+        <v>516</v>
       </c>
       <c r="AA79" t="s">
-        <v>538</v>
+        <v>517</v>
       </c>
       <c r="AB79" t="s">
         <v>39</v>
@@ -8661,13 +8730,13 @@
     </row>
     <row r="80" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>539</v>
+        <v>521</v>
       </c>
       <c r="C80" t="s">
-        <v>540</v>
+        <v>522</v>
       </c>
       <c r="D80" t="s">
-        <v>541</v>
+        <v>523</v>
       </c>
       <c r="E80" t="s">
         <v>33</v>
@@ -8685,13 +8754,13 @@
         <v>54</v>
       </c>
       <c r="K80" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L80" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M80" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="N80" t="s">
         <v>33</v>
@@ -8703,19 +8772,16 @@
         <v>38</v>
       </c>
       <c r="Q80">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="R80">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="Y80" t="s">
-        <v>71</v>
-      </c>
-      <c r="Z80" t="s">
-        <v>542</v>
+        <v>58</v>
       </c>
       <c r="AA80" t="s">
-        <v>543</v>
+        <v>524</v>
       </c>
       <c r="AB80" t="s">
         <v>39</v>
@@ -8729,13 +8795,13 @@
     </row>
     <row r="81" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>544</v>
+        <v>525</v>
       </c>
       <c r="C81" t="s">
-        <v>545</v>
+        <v>526</v>
       </c>
       <c r="D81" t="s">
-        <v>546</v>
+        <v>527</v>
       </c>
       <c r="E81" t="s">
         <v>33</v>
@@ -8753,37 +8819,34 @@
         <v>54</v>
       </c>
       <c r="K81" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L81" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M81" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N81" t="s">
         <v>33</v>
       </c>
       <c r="O81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P81" t="s">
         <v>38</v>
       </c>
       <c r="Q81">
-        <v>76.98</v>
+        <v>59.99</v>
       </c>
       <c r="R81">
-        <v>12.84</v>
+        <v>10</v>
       </c>
       <c r="Y81" t="s">
-        <v>547</v>
-      </c>
-      <c r="Z81" t="s">
-        <v>548</v>
+        <v>90</v>
       </c>
       <c r="AA81" t="s">
-        <v>549</v>
+        <v>528</v>
       </c>
       <c r="AB81" t="s">
         <v>39</v>
@@ -8797,13 +8860,13 @@
     </row>
     <row r="82" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>550</v>
+        <v>529</v>
       </c>
       <c r="C82" t="s">
-        <v>551</v>
+        <v>530</v>
       </c>
       <c r="D82" t="s">
-        <v>552</v>
+        <v>527</v>
       </c>
       <c r="E82" t="s">
         <v>33</v>
@@ -8845,10 +8908,10 @@
         <v>10</v>
       </c>
       <c r="Y82" t="s">
-        <v>553</v>
+        <v>531</v>
       </c>
       <c r="AA82" t="s">
-        <v>554</v>
+        <v>532</v>
       </c>
       <c r="AB82" t="s">
         <v>39</v>
@@ -8862,13 +8925,13 @@
     </row>
     <row r="83" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>555</v>
+        <v>533</v>
       </c>
       <c r="C83" t="s">
-        <v>556</v>
+        <v>534</v>
       </c>
       <c r="D83" t="s">
-        <v>557</v>
+        <v>535</v>
       </c>
       <c r="E83" t="s">
         <v>33</v>
@@ -8886,13 +8949,13 @@
         <v>54</v>
       </c>
       <c r="K83" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L83" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M83" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N83" t="s">
         <v>33</v>
@@ -8904,16 +8967,19 @@
         <v>38</v>
       </c>
       <c r="Q83">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R83">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y83" t="s">
-        <v>558</v>
+        <v>536</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>537</v>
       </c>
       <c r="AA83" t="s">
-        <v>559</v>
+        <v>538</v>
       </c>
       <c r="AB83" t="s">
         <v>39</v>
@@ -8927,13 +8993,13 @@
     </row>
     <row r="84" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>418</v>
+        <v>539</v>
       </c>
       <c r="C84" t="s">
-        <v>419</v>
+        <v>540</v>
       </c>
       <c r="D84" t="s">
-        <v>560</v>
+        <v>541</v>
       </c>
       <c r="E84" t="s">
         <v>33</v>
@@ -8975,10 +9041,13 @@
         <v>10</v>
       </c>
       <c r="Y84" t="s">
-        <v>420</v>
+        <v>71</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>542</v>
       </c>
       <c r="AA84" t="s">
-        <v>421</v>
+        <v>543</v>
       </c>
       <c r="AB84" t="s">
         <v>39</v>
@@ -8992,13 +9061,13 @@
     </row>
     <row r="85" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>561</v>
+        <v>544</v>
       </c>
       <c r="C85" t="s">
-        <v>562</v>
+        <v>545</v>
       </c>
       <c r="D85" t="s">
-        <v>563</v>
+        <v>546</v>
       </c>
       <c r="E85" t="s">
         <v>33</v>
@@ -9016,37 +9085,37 @@
         <v>54</v>
       </c>
       <c r="K85" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L85" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M85" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N85" t="s">
         <v>33</v>
       </c>
       <c r="O85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P85" t="s">
         <v>38</v>
       </c>
       <c r="Q85">
-        <v>59.99</v>
+        <v>76.98</v>
       </c>
       <c r="R85">
-        <v>10</v>
+        <v>12.84</v>
       </c>
       <c r="Y85" t="s">
-        <v>564</v>
+        <v>547</v>
       </c>
       <c r="Z85" t="s">
-        <v>565</v>
+        <v>548</v>
       </c>
       <c r="AA85" t="s">
-        <v>566</v>
+        <v>549</v>
       </c>
       <c r="AB85" t="s">
         <v>39</v>
@@ -9060,13 +9129,13 @@
     </row>
     <row r="86" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>567</v>
+        <v>550</v>
       </c>
       <c r="C86" t="s">
-        <v>568</v>
+        <v>551</v>
       </c>
       <c r="D86" t="s">
-        <v>569</v>
+        <v>552</v>
       </c>
       <c r="E86" t="s">
         <v>33</v>
@@ -9084,13 +9153,13 @@
         <v>54</v>
       </c>
       <c r="K86" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L86" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M86" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="N86" t="s">
         <v>33</v>
@@ -9102,16 +9171,16 @@
         <v>38</v>
       </c>
       <c r="Q86">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R86">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y86" t="s">
-        <v>69</v>
+        <v>553</v>
       </c>
       <c r="AA86" t="s">
-        <v>570</v>
+        <v>554</v>
       </c>
       <c r="AB86" t="s">
         <v>39</v>
@@ -9125,13 +9194,13 @@
     </row>
     <row r="87" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>413</v>
+        <v>555</v>
       </c>
       <c r="C87" t="s">
-        <v>414</v>
+        <v>556</v>
       </c>
       <c r="D87" t="s">
-        <v>415</v>
+        <v>557</v>
       </c>
       <c r="E87" t="s">
         <v>33</v>
@@ -9173,10 +9242,10 @@
         <v>10</v>
       </c>
       <c r="Y87" t="s">
-        <v>416</v>
+        <v>558</v>
       </c>
       <c r="AA87" t="s">
-        <v>417</v>
+        <v>559</v>
       </c>
       <c r="AB87" t="s">
         <v>39</v>
@@ -9190,13 +9259,13 @@
     </row>
     <row r="88" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="C88" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="D88" t="s">
-        <v>424</v>
+        <v>560</v>
       </c>
       <c r="E88" t="s">
         <v>33</v>
@@ -9214,13 +9283,13 @@
         <v>54</v>
       </c>
       <c r="K88" t="s">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="L88" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="M88" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="N88" t="s">
         <v>33</v>
@@ -9232,16 +9301,16 @@
         <v>38</v>
       </c>
       <c r="Q88">
-        <v>22.99</v>
+        <v>59.99</v>
       </c>
       <c r="R88">
-        <v>3.83</v>
+        <v>10</v>
       </c>
       <c r="Y88" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="AA88" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="AB88" t="s">
         <v>39</v>
@@ -9255,13 +9324,13 @@
     </row>
     <row r="89" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>427</v>
+        <v>561</v>
       </c>
       <c r="C89" t="s">
-        <v>428</v>
+        <v>562</v>
       </c>
       <c r="D89" t="s">
-        <v>424</v>
+        <v>563</v>
       </c>
       <c r="E89" t="s">
         <v>33</v>
@@ -9279,13 +9348,13 @@
         <v>54</v>
       </c>
       <c r="K89" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L89" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M89" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N89" t="s">
         <v>33</v>
@@ -9297,19 +9366,19 @@
         <v>38</v>
       </c>
       <c r="Q89">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R89">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y89" t="s">
-        <v>96</v>
+        <v>564</v>
       </c>
       <c r="Z89" t="s">
-        <v>97</v>
+        <v>565</v>
       </c>
       <c r="AA89" t="s">
-        <v>429</v>
+        <v>566</v>
       </c>
       <c r="AB89" t="s">
         <v>39</v>
@@ -9323,13 +9392,13 @@
     </row>
     <row r="90" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>430</v>
+        <v>567</v>
       </c>
       <c r="C90" t="s">
-        <v>431</v>
+        <v>568</v>
       </c>
       <c r="D90" t="s">
-        <v>432</v>
+        <v>569</v>
       </c>
       <c r="E90" t="s">
         <v>33</v>
@@ -9347,13 +9416,13 @@
         <v>54</v>
       </c>
       <c r="K90" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="L90" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="M90" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="N90" t="s">
         <v>33</v>
@@ -9365,19 +9434,16 @@
         <v>38</v>
       </c>
       <c r="Q90">
-        <v>38.49</v>
+        <v>14.99</v>
       </c>
       <c r="R90">
-        <v>6.42</v>
+        <v>2.5</v>
       </c>
       <c r="Y90" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z90" t="s">
-        <v>433</v>
+        <v>69</v>
       </c>
       <c r="AA90" t="s">
-        <v>434</v>
+        <v>570</v>
       </c>
       <c r="AB90" t="s">
         <v>39</v>
@@ -9391,13 +9457,13 @@
     </row>
     <row r="91" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>435</v>
+        <v>413</v>
       </c>
       <c r="C91" t="s">
-        <v>436</v>
+        <v>414</v>
       </c>
       <c r="D91" t="s">
-        <v>437</v>
+        <v>415</v>
       </c>
       <c r="E91" t="s">
         <v>33</v>
@@ -9415,13 +9481,13 @@
         <v>54</v>
       </c>
       <c r="K91" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="L91" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="M91" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="N91" t="s">
         <v>33</v>
@@ -9433,16 +9499,16 @@
         <v>38</v>
       </c>
       <c r="Q91">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R91">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y91" t="s">
-        <v>438</v>
+        <v>416</v>
       </c>
       <c r="AA91" t="s">
-        <v>439</v>
+        <v>417</v>
       </c>
       <c r="AB91" t="s">
         <v>39</v>
@@ -9456,13 +9522,13 @@
     </row>
     <row r="92" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="C92" t="s">
-        <v>441</v>
+        <v>423</v>
       </c>
       <c r="D92" t="s">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="E92" t="s">
         <v>33</v>
@@ -9480,13 +9546,13 @@
         <v>54</v>
       </c>
       <c r="K92" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="L92" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="M92" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="N92" t="s">
         <v>33</v>
@@ -9498,16 +9564,16 @@
         <v>38</v>
       </c>
       <c r="Q92">
-        <v>37.99</v>
+        <v>22.99</v>
       </c>
       <c r="R92">
-        <v>6.33</v>
+        <v>3.83</v>
       </c>
       <c r="Y92" t="s">
-        <v>443</v>
+        <v>425</v>
       </c>
       <c r="AA92" t="s">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="AB92" t="s">
         <v>39</v>
@@ -9521,13 +9587,13 @@
     </row>
     <row r="93" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="C93" t="s">
-        <v>446</v>
+        <v>428</v>
       </c>
       <c r="D93" t="s">
-        <v>447</v>
+        <v>424</v>
       </c>
       <c r="E93" t="s">
         <v>33</v>
@@ -9545,13 +9611,13 @@
         <v>54</v>
       </c>
       <c r="K93" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L93" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M93" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N93" t="s">
         <v>33</v>
@@ -9563,16 +9629,19 @@
         <v>38</v>
       </c>
       <c r="Q93">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R93">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y93" t="s">
-        <v>448</v>
+        <v>96</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>97</v>
       </c>
       <c r="AA93" t="s">
-        <v>449</v>
+        <v>429</v>
       </c>
       <c r="AB93" t="s">
         <v>39</v>
@@ -9586,16 +9655,16 @@
     </row>
     <row r="94" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="C94" t="s">
-        <v>451</v>
+        <v>431</v>
       </c>
       <c r="D94" t="s">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="E94" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F94" t="s">
         <v>34</v>
@@ -9610,22 +9679,37 @@
         <v>54</v>
       </c>
       <c r="K94" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L94" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M94" t="s">
-        <v>42</v>
+        <v>45</v>
+      </c>
+      <c r="N94" t="s">
+        <v>33</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P94" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q94">
+        <v>38.49</v>
+      </c>
+      <c r="R94">
+        <v>6.42</v>
       </c>
       <c r="Y94" t="s">
-        <v>453</v>
+        <v>59</v>
+      </c>
+      <c r="Z94" t="s">
+        <v>433</v>
       </c>
       <c r="AA94" t="s">
-        <v>454</v>
+        <v>434</v>
       </c>
       <c r="AB94" t="s">
         <v>39</v>
@@ -9639,13 +9723,13 @@
     </row>
     <row r="95" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>403</v>
+        <v>435</v>
       </c>
       <c r="C95" t="s">
-        <v>404</v>
+        <v>436</v>
       </c>
       <c r="D95" t="s">
-        <v>455</v>
+        <v>437</v>
       </c>
       <c r="E95" t="s">
         <v>33</v>
@@ -9663,13 +9747,13 @@
         <v>54</v>
       </c>
       <c r="K95" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="L95" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="M95" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="N95" t="s">
         <v>33</v>
@@ -9681,22 +9765,16 @@
         <v>38</v>
       </c>
       <c r="Q95">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="R95">
-        <v>10</v>
-      </c>
-      <c r="S95">
-        <v>5.99</v>
-      </c>
-      <c r="T95">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="Y95" t="s">
-        <v>405</v>
+        <v>438</v>
       </c>
       <c r="AA95" t="s">
-        <v>406</v>
+        <v>439</v>
       </c>
       <c r="AB95" t="s">
         <v>39</v>
@@ -9710,13 +9788,13 @@
     </row>
     <row r="96" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>407</v>
+        <v>440</v>
       </c>
       <c r="C96" t="s">
-        <v>408</v>
+        <v>441</v>
       </c>
       <c r="D96" t="s">
-        <v>456</v>
+        <v>442</v>
       </c>
       <c r="E96" t="s">
         <v>33</v>
@@ -9734,13 +9812,13 @@
         <v>54</v>
       </c>
       <c r="K96" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="L96" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="M96" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="N96" t="s">
         <v>33</v>
@@ -9752,16 +9830,16 @@
         <v>38</v>
       </c>
       <c r="Q96">
-        <v>22.99</v>
+        <v>37.99</v>
       </c>
       <c r="R96">
-        <v>3.83</v>
+        <v>6.33</v>
       </c>
       <c r="Y96" t="s">
-        <v>409</v>
+        <v>443</v>
       </c>
       <c r="AA96" t="s">
-        <v>410</v>
+        <v>444</v>
       </c>
       <c r="AB96" t="s">
         <v>39</v>
@@ -9775,13 +9853,13 @@
     </row>
     <row r="97" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>399</v>
+        <v>445</v>
       </c>
       <c r="C97" t="s">
-        <v>400</v>
+        <v>446</v>
       </c>
       <c r="D97" t="s">
-        <v>411</v>
+        <v>447</v>
       </c>
       <c r="E97" t="s">
         <v>33</v>
@@ -9799,13 +9877,13 @@
         <v>54</v>
       </c>
       <c r="K97" t="s">
-        <v>340</v>
+        <v>40</v>
       </c>
       <c r="L97" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="M97" t="s">
-        <v>143</v>
+        <v>42</v>
       </c>
       <c r="N97" t="s">
         <v>33</v>
@@ -9817,16 +9895,16 @@
         <v>38</v>
       </c>
       <c r="Q97">
-        <v>44.99</v>
+        <v>59.99</v>
       </c>
       <c r="R97">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="Y97" t="s">
-        <v>401</v>
+        <v>448</v>
       </c>
       <c r="AA97" t="s">
-        <v>402</v>
+        <v>449</v>
       </c>
       <c r="AB97" t="s">
         <v>39</v>
@@ -9840,16 +9918,16 @@
     </row>
     <row r="98" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>394</v>
+        <v>450</v>
       </c>
       <c r="C98" t="s">
-        <v>395</v>
+        <v>451</v>
       </c>
       <c r="D98" t="s">
-        <v>412</v>
+        <v>452</v>
       </c>
       <c r="E98" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F98" t="s">
         <v>34</v>
@@ -9864,37 +9942,22 @@
         <v>54</v>
       </c>
       <c r="K98" t="s">
-        <v>340</v>
+        <v>40</v>
       </c>
       <c r="L98" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="M98" t="s">
-        <v>143</v>
-      </c>
-      <c r="N98" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O98">
-        <v>1</v>
-      </c>
-      <c r="P98" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q98">
-        <v>44.99</v>
-      </c>
-      <c r="R98">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Y98" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z98" t="s">
-        <v>397</v>
+        <v>453</v>
       </c>
       <c r="AA98" t="s">
-        <v>398</v>
+        <v>454</v>
       </c>
       <c r="AB98" t="s">
         <v>39</v>
@@ -9908,13 +9971,13 @@
     </row>
     <row r="99" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>338</v>
+        <v>403</v>
       </c>
       <c r="C99" t="s">
-        <v>339</v>
+        <v>404</v>
       </c>
       <c r="D99" t="s">
-        <v>662</v>
+        <v>455</v>
       </c>
       <c r="E99" t="s">
         <v>33</v>
@@ -9932,13 +9995,13 @@
         <v>54</v>
       </c>
       <c r="K99" t="s">
-        <v>340</v>
+        <v>40</v>
       </c>
       <c r="L99" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="M99" t="s">
-        <v>143</v>
+        <v>42</v>
       </c>
       <c r="N99" t="s">
         <v>33</v>
@@ -9950,16 +10013,22 @@
         <v>38</v>
       </c>
       <c r="Q99">
-        <v>44.99</v>
+        <v>59.99</v>
       </c>
       <c r="R99">
-        <v>7.5</v>
+        <v>10</v>
+      </c>
+      <c r="S99">
+        <v>5.99</v>
+      </c>
+      <c r="T99">
+        <v>1</v>
       </c>
       <c r="Y99" t="s">
-        <v>341</v>
+        <v>405</v>
       </c>
       <c r="AA99" t="s">
-        <v>342</v>
+        <v>406</v>
       </c>
       <c r="AB99" t="s">
         <v>39</v>
@@ -9973,13 +10042,13 @@
     </row>
     <row r="100" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>663</v>
+        <v>407</v>
       </c>
       <c r="C100" t="s">
-        <v>664</v>
+        <v>408</v>
       </c>
       <c r="D100" t="s">
-        <v>665</v>
+        <v>456</v>
       </c>
       <c r="E100" t="s">
         <v>33</v>
@@ -9997,13 +10066,13 @@
         <v>54</v>
       </c>
       <c r="K100" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="L100" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="M100" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="N100" t="s">
         <v>33</v>
@@ -10015,25 +10084,22 @@
         <v>38</v>
       </c>
       <c r="Q100">
-        <v>59.99</v>
+        <v>22.99</v>
       </c>
       <c r="R100">
-        <v>10</v>
+        <v>3.83</v>
       </c>
       <c r="Y100" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z100" t="s">
-        <v>666</v>
+        <v>409</v>
       </c>
       <c r="AA100" t="s">
-        <v>667</v>
+        <v>410</v>
       </c>
       <c r="AB100" t="s">
         <v>39</v>
       </c>
       <c r="AD100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG100" t="b">
         <v>0</v>
@@ -10041,13 +10107,13 @@
     </row>
     <row r="101" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>334</v>
+        <v>399</v>
       </c>
       <c r="C101" t="s">
-        <v>335</v>
+        <v>400</v>
       </c>
       <c r="D101" t="s">
-        <v>668</v>
+        <v>411</v>
       </c>
       <c r="E101" t="s">
         <v>33</v>
@@ -10065,13 +10131,13 @@
         <v>54</v>
       </c>
       <c r="K101" t="s">
-        <v>203</v>
+        <v>340</v>
       </c>
       <c r="L101" t="s">
-        <v>204</v>
+        <v>142</v>
       </c>
       <c r="M101" t="s">
-        <v>205</v>
+        <v>143</v>
       </c>
       <c r="N101" t="s">
         <v>33</v>
@@ -10083,16 +10149,16 @@
         <v>38</v>
       </c>
       <c r="Q101">
-        <v>69.989999999999995</v>
+        <v>44.99</v>
       </c>
       <c r="R101">
-        <v>11.67</v>
+        <v>7.5</v>
       </c>
       <c r="Y101" t="s">
-        <v>336</v>
+        <v>401</v>
       </c>
       <c r="AA101" t="s">
-        <v>337</v>
+        <v>402</v>
       </c>
       <c r="AB101" t="s">
         <v>39</v>
@@ -10106,13 +10172,13 @@
     </row>
     <row r="102" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="C102" t="s">
-        <v>327</v>
+        <v>395</v>
       </c>
       <c r="D102" t="s">
-        <v>669</v>
+        <v>412</v>
       </c>
       <c r="E102" t="s">
         <v>33</v>
@@ -10130,34 +10196,37 @@
         <v>54</v>
       </c>
       <c r="K102" t="s">
-        <v>48</v>
+        <v>340</v>
       </c>
       <c r="L102" t="s">
-        <v>49</v>
+        <v>142</v>
       </c>
       <c r="M102" t="s">
-        <v>50</v>
+        <v>143</v>
       </c>
       <c r="N102" t="s">
         <v>33</v>
       </c>
       <c r="O102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P102" t="s">
         <v>38</v>
       </c>
       <c r="Q102">
-        <v>75.98</v>
+        <v>44.99</v>
       </c>
       <c r="R102">
-        <v>12.66</v>
+        <v>7.5</v>
       </c>
       <c r="Y102" t="s">
-        <v>91</v>
+        <v>396</v>
+      </c>
+      <c r="Z102" t="s">
+        <v>397</v>
       </c>
       <c r="AA102" t="s">
-        <v>328</v>
+        <v>398</v>
       </c>
       <c r="AB102" t="s">
         <v>39</v>
@@ -10171,13 +10240,13 @@
     </row>
     <row r="103" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="C103" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="D103" t="s">
-        <v>345</v>
+        <v>662</v>
       </c>
       <c r="E103" t="s">
         <v>33</v>
@@ -10195,13 +10264,13 @@
         <v>54</v>
       </c>
       <c r="K103" t="s">
-        <v>40</v>
+        <v>340</v>
       </c>
       <c r="L103" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="M103" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="N103" t="s">
         <v>33</v>
@@ -10213,16 +10282,16 @@
         <v>38</v>
       </c>
       <c r="Q103">
-        <v>59.99</v>
+        <v>44.99</v>
       </c>
       <c r="R103">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="Y103" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="AA103" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="AB103" t="s">
         <v>39</v>
@@ -10236,13 +10305,13 @@
     </row>
     <row r="104" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>288</v>
+        <v>663</v>
       </c>
       <c r="C104" t="s">
-        <v>289</v>
+        <v>664</v>
       </c>
       <c r="D104" t="s">
-        <v>348</v>
+        <v>665</v>
       </c>
       <c r="E104" t="s">
         <v>33</v>
@@ -10257,43 +10326,46 @@
         <v>36</v>
       </c>
       <c r="J104" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K104" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L104" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M104" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N104" t="s">
         <v>33</v>
       </c>
       <c r="O104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P104" t="s">
         <v>38</v>
       </c>
       <c r="Q104">
-        <v>75.98</v>
+        <v>59.99</v>
       </c>
       <c r="R104">
-        <v>12.66</v>
+        <v>10</v>
       </c>
       <c r="Y104" t="s">
-        <v>290</v>
+        <v>62</v>
+      </c>
+      <c r="Z104" t="s">
+        <v>666</v>
       </c>
       <c r="AA104" t="s">
-        <v>291</v>
+        <v>667</v>
       </c>
       <c r="AB104" t="s">
         <v>39</v>
       </c>
       <c r="AD104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG104" t="b">
         <v>0</v>
@@ -10301,13 +10373,13 @@
     </row>
     <row r="105" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="C105" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="D105" t="s">
-        <v>351</v>
+        <v>668</v>
       </c>
       <c r="E105" t="s">
         <v>33</v>
@@ -10325,13 +10397,13 @@
         <v>54</v>
       </c>
       <c r="K105" t="s">
-        <v>48</v>
+        <v>203</v>
       </c>
       <c r="L105" t="s">
-        <v>49</v>
+        <v>204</v>
       </c>
       <c r="M105" t="s">
-        <v>50</v>
+        <v>205</v>
       </c>
       <c r="N105" t="s">
         <v>33</v>
@@ -10343,19 +10415,16 @@
         <v>38</v>
       </c>
       <c r="Q105">
-        <v>37.99</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="R105">
-        <v>6.33</v>
+        <v>11.67</v>
       </c>
       <c r="Y105" t="s">
-        <v>352</v>
-      </c>
-      <c r="Z105" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="AA105" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="AB105" t="s">
         <v>39</v>
@@ -10369,13 +10438,13 @@
     </row>
     <row r="106" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>355</v>
+        <v>326</v>
       </c>
       <c r="C106" t="s">
-        <v>356</v>
+        <v>327</v>
       </c>
       <c r="D106" t="s">
-        <v>357</v>
+        <v>669</v>
       </c>
       <c r="E106" t="s">
         <v>33</v>
@@ -10393,34 +10462,34 @@
         <v>54</v>
       </c>
       <c r="K106" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L106" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M106" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N106" t="s">
         <v>33</v>
       </c>
       <c r="O106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P106" t="s">
         <v>38</v>
       </c>
       <c r="Q106">
-        <v>11.99</v>
+        <v>75.98</v>
       </c>
       <c r="R106">
-        <v>2</v>
+        <v>12.66</v>
       </c>
       <c r="Y106" t="s">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="AA106" t="s">
-        <v>358</v>
+        <v>328</v>
       </c>
       <c r="AB106" t="s">
         <v>39</v>
@@ -10434,13 +10503,13 @@
     </row>
     <row r="107" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>359</v>
+        <v>343</v>
       </c>
       <c r="C107" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="D107" t="s">
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="E107" t="s">
         <v>33</v>
@@ -10458,37 +10527,34 @@
         <v>54</v>
       </c>
       <c r="K107" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L107" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M107" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N107" t="s">
         <v>33</v>
       </c>
       <c r="O107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P107" t="s">
         <v>38</v>
       </c>
       <c r="Q107">
-        <v>75.98</v>
+        <v>59.99</v>
       </c>
       <c r="R107">
-        <v>12.66</v>
+        <v>10</v>
       </c>
       <c r="Y107" t="s">
-        <v>101</v>
-      </c>
-      <c r="Z107" t="s">
-        <v>59</v>
+        <v>346</v>
       </c>
       <c r="AA107" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="AB107" t="s">
         <v>39</v>
@@ -10502,13 +10568,13 @@
     </row>
     <row r="108" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>363</v>
+        <v>288</v>
       </c>
       <c r="C108" t="s">
-        <v>364</v>
+        <v>289</v>
       </c>
       <c r="D108" t="s">
-        <v>365</v>
+        <v>348</v>
       </c>
       <c r="E108" t="s">
         <v>33</v>
@@ -10523,37 +10589,37 @@
         <v>36</v>
       </c>
       <c r="J108" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K108" t="s">
-        <v>260</v>
+        <v>48</v>
       </c>
       <c r="L108" t="s">
-        <v>261</v>
+        <v>49</v>
       </c>
       <c r="M108" t="s">
-        <v>262</v>
+        <v>50</v>
       </c>
       <c r="N108" t="s">
         <v>33</v>
       </c>
       <c r="O108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P108" t="s">
         <v>38</v>
       </c>
       <c r="Q108">
-        <v>24.49</v>
+        <v>75.98</v>
       </c>
       <c r="R108">
-        <v>4.08</v>
+        <v>12.66</v>
       </c>
       <c r="Y108" t="s">
-        <v>366</v>
+        <v>290</v>
       </c>
       <c r="AA108" t="s">
-        <v>367</v>
+        <v>291</v>
       </c>
       <c r="AB108" t="s">
         <v>39</v>
@@ -10567,13 +10633,13 @@
     </row>
     <row r="109" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>265</v>
+        <v>349</v>
       </c>
       <c r="C109" t="s">
-        <v>266</v>
+        <v>350</v>
       </c>
       <c r="D109" t="s">
-        <v>368</v>
+        <v>351</v>
       </c>
       <c r="E109" t="s">
         <v>33</v>
@@ -10615,10 +10681,13 @@
         <v>6.33</v>
       </c>
       <c r="Y109" t="s">
-        <v>267</v>
+        <v>352</v>
+      </c>
+      <c r="Z109" t="s">
+        <v>353</v>
       </c>
       <c r="AA109" t="s">
-        <v>268</v>
+        <v>354</v>
       </c>
       <c r="AB109" t="s">
         <v>39</v>
@@ -10632,13 +10701,13 @@
     </row>
     <row r="110" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="C110" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="D110" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="E110" t="s">
         <v>33</v>
@@ -10679,17 +10748,11 @@
       <c r="R110">
         <v>2</v>
       </c>
-      <c r="S110">
-        <v>5.99</v>
-      </c>
-      <c r="T110">
-        <v>1</v>
-      </c>
       <c r="Y110" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="AA110" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="AB110" t="s">
         <v>39</v>
@@ -10703,13 +10766,13 @@
     </row>
     <row r="111" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>373</v>
+        <v>359</v>
       </c>
       <c r="C111" t="s">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="D111" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="E111" t="s">
         <v>33</v>
@@ -10727,34 +10790,37 @@
         <v>54</v>
       </c>
       <c r="K111" t="s">
-        <v>260</v>
+        <v>48</v>
       </c>
       <c r="L111" t="s">
-        <v>261</v>
+        <v>49</v>
       </c>
       <c r="M111" t="s">
-        <v>262</v>
+        <v>50</v>
       </c>
       <c r="N111" t="s">
         <v>33</v>
       </c>
       <c r="O111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P111" t="s">
         <v>38</v>
       </c>
       <c r="Q111">
-        <v>24.49</v>
+        <v>75.98</v>
       </c>
       <c r="R111">
-        <v>4.08</v>
+        <v>12.66</v>
       </c>
       <c r="Y111" t="s">
-        <v>376</v>
+        <v>101</v>
+      </c>
+      <c r="Z111" t="s">
+        <v>59</v>
       </c>
       <c r="AA111" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="AB111" t="s">
         <v>39</v>
@@ -10768,13 +10834,13 @@
     </row>
     <row r="112" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="C112" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="D112" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="E112" t="s">
         <v>33</v>
@@ -10792,13 +10858,13 @@
         <v>54</v>
       </c>
       <c r="K112" t="s">
-        <v>40</v>
+        <v>260</v>
       </c>
       <c r="L112" t="s">
-        <v>41</v>
+        <v>261</v>
       </c>
       <c r="M112" t="s">
-        <v>42</v>
+        <v>262</v>
       </c>
       <c r="N112" t="s">
         <v>33</v>
@@ -10810,16 +10876,16 @@
         <v>38</v>
       </c>
       <c r="Q112">
-        <v>59.99</v>
+        <v>24.49</v>
       </c>
       <c r="R112">
-        <v>10</v>
+        <v>4.08</v>
       </c>
       <c r="Y112" t="s">
-        <v>57</v>
+        <v>366</v>
       </c>
       <c r="AA112" t="s">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="AB112" t="s">
         <v>39</v>
@@ -10833,13 +10899,13 @@
     </row>
     <row r="113" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>382</v>
+        <v>265</v>
       </c>
       <c r="C113" t="s">
-        <v>383</v>
+        <v>266</v>
       </c>
       <c r="D113" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
       <c r="E113" t="s">
         <v>33</v>
@@ -10857,13 +10923,13 @@
         <v>54</v>
       </c>
       <c r="K113" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L113" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M113" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N113" t="s">
         <v>33</v>
@@ -10875,16 +10941,16 @@
         <v>38</v>
       </c>
       <c r="Q113">
-        <v>11.99</v>
+        <v>37.99</v>
       </c>
       <c r="R113">
-        <v>2</v>
+        <v>6.33</v>
       </c>
       <c r="Y113" t="s">
-        <v>385</v>
+        <v>267</v>
       </c>
       <c r="AA113" t="s">
-        <v>386</v>
+        <v>268</v>
       </c>
       <c r="AB113" t="s">
         <v>39</v>
@@ -10898,16 +10964,16 @@
     </row>
     <row r="114" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="C114" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="D114" t="s">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="E114" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F114" t="s">
         <v>34</v>
@@ -10922,25 +10988,40 @@
         <v>54</v>
       </c>
       <c r="K114" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="L114" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="M114" t="s">
-        <v>45</v>
+        <v>74</v>
+      </c>
+      <c r="N114" t="s">
+        <v>33</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P114" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q114">
+        <v>11.99</v>
+      </c>
+      <c r="R114">
+        <v>2</v>
+      </c>
+      <c r="S114">
+        <v>5.99</v>
+      </c>
+      <c r="T114">
+        <v>1</v>
       </c>
       <c r="Y114" t="s">
-        <v>390</v>
-      </c>
-      <c r="Z114" t="s">
-        <v>391</v>
+        <v>84</v>
       </c>
       <c r="AA114" t="s">
-        <v>392</v>
+        <v>372</v>
       </c>
       <c r="AB114" t="s">
         <v>39</v>
@@ -10954,13 +11035,13 @@
     </row>
     <row r="115" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>323</v>
+        <v>373</v>
       </c>
       <c r="C115" t="s">
-        <v>324</v>
+        <v>374</v>
       </c>
       <c r="D115" t="s">
-        <v>393</v>
+        <v>375</v>
       </c>
       <c r="E115" t="s">
         <v>33</v>
@@ -10978,13 +11059,13 @@
         <v>54</v>
       </c>
       <c r="K115" t="s">
-        <v>95</v>
+        <v>260</v>
       </c>
       <c r="L115" t="s">
-        <v>85</v>
+        <v>261</v>
       </c>
       <c r="M115" t="s">
-        <v>86</v>
+        <v>262</v>
       </c>
       <c r="N115" t="s">
         <v>33</v>
@@ -10996,16 +11077,16 @@
         <v>38</v>
       </c>
       <c r="Q115">
-        <v>14.99</v>
+        <v>24.49</v>
       </c>
       <c r="R115">
-        <v>2.5</v>
+        <v>4.08</v>
       </c>
       <c r="Y115" t="s">
-        <v>58</v>
+        <v>376</v>
       </c>
       <c r="AA115" t="s">
-        <v>325</v>
+        <v>377</v>
       </c>
       <c r="AB115" t="s">
         <v>39</v>
@@ -11019,13 +11100,13 @@
     </row>
     <row r="116" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>318</v>
+        <v>378</v>
       </c>
       <c r="C116" t="s">
-        <v>319</v>
+        <v>379</v>
       </c>
       <c r="D116" t="s">
-        <v>320</v>
+        <v>380</v>
       </c>
       <c r="E116" t="s">
         <v>33</v>
@@ -11043,13 +11124,13 @@
         <v>54</v>
       </c>
       <c r="K116" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L116" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M116" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N116" t="s">
         <v>33</v>
@@ -11061,19 +11142,16 @@
         <v>38</v>
       </c>
       <c r="Q116">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R116">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y116" t="s">
-        <v>321</v>
-      </c>
-      <c r="Z116" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="AA116" t="s">
-        <v>322</v>
+        <v>381</v>
       </c>
       <c r="AB116" t="s">
         <v>39</v>
@@ -11087,13 +11165,13 @@
     </row>
     <row r="117" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>329</v>
+        <v>382</v>
       </c>
       <c r="C117" t="s">
-        <v>330</v>
+        <v>383</v>
       </c>
       <c r="D117" t="s">
-        <v>331</v>
+        <v>384</v>
       </c>
       <c r="E117" t="s">
         <v>33</v>
@@ -11111,13 +11189,13 @@
         <v>54</v>
       </c>
       <c r="K117" t="s">
-        <v>260</v>
+        <v>72</v>
       </c>
       <c r="L117" t="s">
-        <v>261</v>
+        <v>73</v>
       </c>
       <c r="M117" t="s">
-        <v>262</v>
+        <v>74</v>
       </c>
       <c r="N117" t="s">
         <v>33</v>
@@ -11129,16 +11207,16 @@
         <v>38</v>
       </c>
       <c r="Q117">
-        <v>24.49</v>
+        <v>11.99</v>
       </c>
       <c r="R117">
-        <v>4.08</v>
+        <v>2</v>
       </c>
       <c r="Y117" t="s">
-        <v>332</v>
+        <v>385</v>
       </c>
       <c r="AA117" t="s">
-        <v>333</v>
+        <v>386</v>
       </c>
       <c r="AB117" t="s">
         <v>39</v>
@@ -11152,16 +11230,16 @@
     </row>
     <row r="118" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>670</v>
+        <v>387</v>
       </c>
       <c r="C118" t="s">
-        <v>671</v>
+        <v>388</v>
       </c>
       <c r="D118" t="s">
-        <v>672</v>
+        <v>389</v>
       </c>
       <c r="E118" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F118" t="s">
         <v>34</v>
@@ -11176,34 +11254,25 @@
         <v>54</v>
       </c>
       <c r="K118" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L118" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M118" t="s">
-        <v>42</v>
-      </c>
-      <c r="N118" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O118">
-        <v>1</v>
-      </c>
-      <c r="P118" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q118">
-        <v>59.99</v>
-      </c>
-      <c r="R118">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y118" t="s">
-        <v>673</v>
+        <v>390</v>
+      </c>
+      <c r="Z118" t="s">
+        <v>391</v>
       </c>
       <c r="AA118" t="s">
-        <v>674</v>
+        <v>392</v>
       </c>
       <c r="AB118" t="s">
         <v>39</v>
@@ -11217,13 +11286,13 @@
     </row>
     <row r="119" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>675</v>
+        <v>323</v>
       </c>
       <c r="C119" t="s">
-        <v>676</v>
+        <v>324</v>
       </c>
       <c r="D119" t="s">
-        <v>677</v>
+        <v>393</v>
       </c>
       <c r="E119" t="s">
         <v>33</v>
@@ -11241,13 +11310,13 @@
         <v>54</v>
       </c>
       <c r="K119" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="L119" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="M119" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="N119" t="s">
         <v>33</v>
@@ -11259,16 +11328,16 @@
         <v>38</v>
       </c>
       <c r="Q119">
-        <v>37.99</v>
+        <v>14.99</v>
       </c>
       <c r="R119">
-        <v>6.33</v>
+        <v>2.5</v>
       </c>
       <c r="Y119" t="s">
-        <v>678</v>
+        <v>58</v>
       </c>
       <c r="AA119" t="s">
-        <v>679</v>
+        <v>325</v>
       </c>
       <c r="AB119" t="s">
         <v>39</v>
@@ -11282,13 +11351,13 @@
     </row>
     <row r="120" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>680</v>
+        <v>318</v>
       </c>
       <c r="C120" t="s">
-        <v>681</v>
+        <v>319</v>
       </c>
       <c r="D120" t="s">
-        <v>682</v>
+        <v>320</v>
       </c>
       <c r="E120" t="s">
         <v>33</v>
@@ -11306,13 +11375,13 @@
         <v>54</v>
       </c>
       <c r="K120" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L120" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M120" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N120" t="s">
         <v>33</v>
@@ -11324,19 +11393,19 @@
         <v>38</v>
       </c>
       <c r="Q120">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R120">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y120" t="s">
-        <v>683</v>
+        <v>321</v>
       </c>
       <c r="Z120" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="AA120" t="s">
-        <v>684</v>
+        <v>322</v>
       </c>
       <c r="AB120" t="s">
         <v>39</v>
@@ -11350,13 +11419,13 @@
     </row>
     <row r="121" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>685</v>
+        <v>329</v>
       </c>
       <c r="C121" t="s">
-        <v>686</v>
+        <v>330</v>
       </c>
       <c r="D121" t="s">
-        <v>687</v>
+        <v>331</v>
       </c>
       <c r="E121" t="s">
         <v>33</v>
@@ -11374,13 +11443,13 @@
         <v>54</v>
       </c>
       <c r="K121" t="s">
-        <v>48</v>
+        <v>260</v>
       </c>
       <c r="L121" t="s">
-        <v>49</v>
+        <v>261</v>
       </c>
       <c r="M121" t="s">
-        <v>50</v>
+        <v>262</v>
       </c>
       <c r="N121" t="s">
         <v>33</v>
@@ -11392,16 +11461,16 @@
         <v>38</v>
       </c>
       <c r="Q121">
-        <v>37.99</v>
+        <v>24.49</v>
       </c>
       <c r="R121">
-        <v>6.33</v>
+        <v>4.08</v>
       </c>
       <c r="Y121" t="s">
-        <v>52</v>
+        <v>332</v>
       </c>
       <c r="AA121" t="s">
-        <v>688</v>
+        <v>333</v>
       </c>
       <c r="AB121" t="s">
         <v>39</v>
@@ -11415,16 +11484,16 @@
     </row>
     <row r="122" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="C122" t="s">
-        <v>690</v>
+        <v>671</v>
       </c>
       <c r="D122" t="s">
-        <v>691</v>
+        <v>672</v>
       </c>
       <c r="E122" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F122" t="s">
         <v>34</v>
@@ -11436,28 +11505,37 @@
         <v>36</v>
       </c>
       <c r="J122" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K122" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L122" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M122" t="s">
-        <v>50</v>
+        <v>42</v>
+      </c>
+      <c r="N122" t="s">
+        <v>33</v>
       </c>
       <c r="O122">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P122" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q122">
+        <v>59.99</v>
+      </c>
+      <c r="R122">
+        <v>10</v>
       </c>
       <c r="Y122" t="s">
-        <v>692</v>
-      </c>
-      <c r="Z122" t="s">
-        <v>693</v>
+        <v>673</v>
       </c>
       <c r="AA122" t="s">
-        <v>694</v>
+        <v>674</v>
       </c>
       <c r="AB122" t="s">
         <v>39</v>
@@ -11471,16 +11549,16 @@
     </row>
     <row r="123" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
       <c r="C123" t="s">
-        <v>696</v>
+        <v>676</v>
       </c>
       <c r="D123" t="s">
-        <v>697</v>
+        <v>677</v>
       </c>
       <c r="E123" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F123" t="s">
         <v>34</v>
@@ -11492,7 +11570,7 @@
         <v>36</v>
       </c>
       <c r="J123" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K123" t="s">
         <v>48</v>
@@ -11503,17 +11581,26 @@
       <c r="M123" t="s">
         <v>50</v>
       </c>
+      <c r="N123" t="s">
+        <v>33</v>
+      </c>
       <c r="O123">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P123" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q123">
+        <v>37.99</v>
+      </c>
+      <c r="R123">
+        <v>6.33</v>
       </c>
       <c r="Y123" t="s">
-        <v>692</v>
-      </c>
-      <c r="Z123" t="s">
-        <v>693</v>
+        <v>678</v>
       </c>
       <c r="AA123" t="s">
-        <v>694</v>
+        <v>679</v>
       </c>
       <c r="AB123" t="s">
         <v>39</v>
@@ -11527,13 +11614,13 @@
     </row>
     <row r="124" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>300</v>
+        <v>680</v>
       </c>
       <c r="C124" t="s">
-        <v>301</v>
+        <v>681</v>
       </c>
       <c r="D124" t="s">
-        <v>698</v>
+        <v>682</v>
       </c>
       <c r="E124" t="s">
         <v>33</v>
@@ -11551,13 +11638,13 @@
         <v>54</v>
       </c>
       <c r="K124" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="L124" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="M124" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="N124" t="s">
         <v>33</v>
@@ -11569,16 +11656,19 @@
         <v>38</v>
       </c>
       <c r="Q124">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R124">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y124" t="s">
-        <v>58</v>
+        <v>683</v>
+      </c>
+      <c r="Z124" t="s">
+        <v>76</v>
       </c>
       <c r="AA124" t="s">
-        <v>302</v>
+        <v>684</v>
       </c>
       <c r="AB124" t="s">
         <v>39</v>
@@ -11592,16 +11682,16 @@
     </row>
     <row r="125" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="C125" t="s">
-        <v>700</v>
+        <v>686</v>
       </c>
       <c r="D125" t="s">
-        <v>701</v>
+        <v>687</v>
       </c>
       <c r="E125" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F125" t="s">
         <v>34</v>
@@ -11624,17 +11714,26 @@
       <c r="M125" t="s">
         <v>50</v>
       </c>
+      <c r="N125" t="s">
+        <v>33</v>
+      </c>
       <c r="O125">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P125" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q125">
+        <v>37.99</v>
+      </c>
+      <c r="R125">
+        <v>6.33</v>
       </c>
       <c r="Y125" t="s">
-        <v>692</v>
-      </c>
-      <c r="Z125" t="s">
-        <v>693</v>
+        <v>52</v>
       </c>
       <c r="AA125" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="AB125" t="s">
         <v>39</v>
@@ -11648,16 +11747,16 @@
     </row>
     <row r="126" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>303</v>
+        <v>689</v>
       </c>
       <c r="C126" t="s">
-        <v>304</v>
+        <v>690</v>
       </c>
       <c r="D126" t="s">
-        <v>702</v>
+        <v>691</v>
       </c>
       <c r="E126" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F126" t="s">
         <v>34</v>
@@ -11669,37 +11768,28 @@
         <v>36</v>
       </c>
       <c r="J126" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K126" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L126" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M126" t="s">
-        <v>42</v>
-      </c>
-      <c r="N126" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="O126">
-        <v>1</v>
-      </c>
-      <c r="P126" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q126">
-        <v>59.99</v>
-      </c>
-      <c r="R126">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y126" t="s">
-        <v>305</v>
+        <v>692</v>
+      </c>
+      <c r="Z126" t="s">
+        <v>693</v>
       </c>
       <c r="AA126" t="s">
-        <v>306</v>
+        <v>694</v>
       </c>
       <c r="AB126" t="s">
         <v>39</v>
@@ -11713,16 +11803,16 @@
     </row>
     <row r="127" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>292</v>
+        <v>695</v>
       </c>
       <c r="C127" t="s">
-        <v>293</v>
+        <v>696</v>
       </c>
       <c r="D127" t="s">
-        <v>294</v>
+        <v>697</v>
       </c>
       <c r="E127" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F127" t="s">
         <v>34</v>
@@ -11737,37 +11827,25 @@
         <v>37</v>
       </c>
       <c r="K127" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L127" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M127" t="s">
-        <v>42</v>
-      </c>
-      <c r="N127" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="O127">
-        <v>1</v>
-      </c>
-      <c r="P127" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q127">
-        <v>59.99</v>
-      </c>
-      <c r="R127">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y127" t="s">
-        <v>77</v>
+        <v>692</v>
       </c>
       <c r="Z127" t="s">
-        <v>92</v>
+        <v>693</v>
       </c>
       <c r="AA127" t="s">
-        <v>295</v>
+        <v>694</v>
       </c>
       <c r="AB127" t="s">
         <v>39</v>
@@ -11781,13 +11859,13 @@
     </row>
     <row r="128" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C128" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D128" t="s">
-        <v>298</v>
+        <v>698</v>
       </c>
       <c r="E128" t="s">
         <v>33</v>
@@ -11802,16 +11880,16 @@
         <v>36</v>
       </c>
       <c r="J128" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K128" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="L128" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="M128" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="N128" t="s">
         <v>33</v>
@@ -11823,19 +11901,16 @@
         <v>38</v>
       </c>
       <c r="Q128">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="R128">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="Y128" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z128" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="AA128" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AB128" t="s">
         <v>39</v>
@@ -11849,16 +11924,16 @@
     </row>
     <row r="129" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>307</v>
+        <v>699</v>
       </c>
       <c r="C129" t="s">
-        <v>308</v>
+        <v>700</v>
       </c>
       <c r="D129" t="s">
-        <v>309</v>
+        <v>701</v>
       </c>
       <c r="E129" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F129" t="s">
         <v>34</v>
@@ -11870,37 +11945,28 @@
         <v>36</v>
       </c>
       <c r="J129" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K129" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="L129" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="M129" t="s">
-        <v>89</v>
-      </c>
-      <c r="N129" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="O129">
-        <v>1</v>
-      </c>
-      <c r="P129" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q129">
-        <v>20.49</v>
-      </c>
-      <c r="R129">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="Y129" t="s">
-        <v>310</v>
+        <v>692</v>
+      </c>
+      <c r="Z129" t="s">
+        <v>693</v>
       </c>
       <c r="AA129" t="s">
-        <v>311</v>
+        <v>694</v>
       </c>
       <c r="AB129" t="s">
         <v>39</v>
@@ -11914,13 +11980,13 @@
     </row>
     <row r="130" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="C130" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="D130" t="s">
-        <v>314</v>
+        <v>702</v>
       </c>
       <c r="E130" t="s">
         <v>33</v>
@@ -11935,7 +12001,7 @@
         <v>36</v>
       </c>
       <c r="J130" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K130" t="s">
         <v>40</v>
@@ -11962,13 +12028,10 @@
         <v>10</v>
       </c>
       <c r="Y130" t="s">
-        <v>100</v>
-      </c>
-      <c r="Z130" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="AA130" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="AB130" t="s">
         <v>39</v>
@@ -11982,13 +12045,13 @@
     </row>
     <row r="131" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>253</v>
+        <v>292</v>
       </c>
       <c r="C131" t="s">
-        <v>254</v>
+        <v>293</v>
       </c>
       <c r="D131" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="E131" t="s">
         <v>33</v>
@@ -12003,7 +12066,7 @@
         <v>36</v>
       </c>
       <c r="J131" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K131" t="s">
         <v>40</v>
@@ -12030,13 +12093,13 @@
         <v>10</v>
       </c>
       <c r="Y131" t="s">
-        <v>255</v>
+        <v>77</v>
       </c>
       <c r="Z131" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="AA131" t="s">
-        <v>256</v>
+        <v>295</v>
       </c>
       <c r="AB131" t="s">
         <v>39</v>
@@ -12050,13 +12113,13 @@
     </row>
     <row r="132" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>257</v>
+        <v>296</v>
       </c>
       <c r="C132" t="s">
-        <v>258</v>
+        <v>297</v>
       </c>
       <c r="D132" t="s">
-        <v>259</v>
+        <v>298</v>
       </c>
       <c r="E132" t="s">
         <v>33</v>
@@ -12071,16 +12134,16 @@
         <v>36</v>
       </c>
       <c r="J132" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K132" t="s">
-        <v>260</v>
+        <v>40</v>
       </c>
       <c r="L132" t="s">
-        <v>261</v>
+        <v>41</v>
       </c>
       <c r="M132" t="s">
-        <v>262</v>
+        <v>42</v>
       </c>
       <c r="N132" t="s">
         <v>33</v>
@@ -12092,19 +12155,19 @@
         <v>38</v>
       </c>
       <c r="Q132">
-        <v>24.49</v>
+        <v>59.99</v>
       </c>
       <c r="R132">
-        <v>4.08</v>
+        <v>10</v>
       </c>
       <c r="Y132" t="s">
-        <v>263</v>
+        <v>62</v>
       </c>
       <c r="Z132" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="AA132" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="AB132" t="s">
         <v>39</v>
@@ -12118,13 +12181,13 @@
     </row>
     <row r="133" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>269</v>
+        <v>307</v>
       </c>
       <c r="C133" t="s">
-        <v>270</v>
+        <v>308</v>
       </c>
       <c r="D133" t="s">
-        <v>271</v>
+        <v>309</v>
       </c>
       <c r="E133" t="s">
         <v>33</v>
@@ -12139,16 +12202,16 @@
         <v>36</v>
       </c>
       <c r="J133" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K133" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="L133" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="M133" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="N133" t="s">
         <v>33</v>
@@ -12160,16 +12223,16 @@
         <v>38</v>
       </c>
       <c r="Q133">
-        <v>59.99</v>
+        <v>20.49</v>
       </c>
       <c r="R133">
-        <v>10</v>
+        <v>3.42</v>
       </c>
       <c r="Y133" t="s">
-        <v>272</v>
+        <v>310</v>
       </c>
       <c r="AA133" t="s">
-        <v>273</v>
+        <v>311</v>
       </c>
       <c r="AB133" t="s">
         <v>39</v>
@@ -12183,13 +12246,13 @@
     </row>
     <row r="134" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>149</v>
+        <v>312</v>
       </c>
       <c r="C134" t="s">
-        <v>150</v>
+        <v>313</v>
       </c>
       <c r="D134" t="s">
-        <v>274</v>
+        <v>314</v>
       </c>
       <c r="E134" t="s">
         <v>33</v>
@@ -12204,7 +12267,7 @@
         <v>36</v>
       </c>
       <c r="J134" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K134" t="s">
         <v>40</v>
@@ -12231,10 +12294,13 @@
         <v>10</v>
       </c>
       <c r="Y134" t="s">
-        <v>63</v>
+        <v>100</v>
+      </c>
+      <c r="Z134" t="s">
+        <v>315</v>
       </c>
       <c r="AA134" t="s">
-        <v>151</v>
+        <v>316</v>
       </c>
       <c r="AB134" t="s">
         <v>39</v>
@@ -12248,13 +12314,13 @@
     </row>
     <row r="135" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="C135" t="s">
-        <v>276</v>
+        <v>254</v>
       </c>
       <c r="D135" t="s">
-        <v>277</v>
+        <v>317</v>
       </c>
       <c r="E135" t="s">
         <v>33</v>
@@ -12284,25 +12350,25 @@
         <v>33</v>
       </c>
       <c r="O135">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P135" t="s">
         <v>38</v>
       </c>
       <c r="Q135">
-        <v>119.98</v>
+        <v>59.99</v>
       </c>
       <c r="R135">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Y135" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="Z135" t="s">
-        <v>279</v>
+        <v>102</v>
       </c>
       <c r="AA135" t="s">
-        <v>280</v>
+        <v>256</v>
       </c>
       <c r="AB135" t="s">
         <v>39</v>
@@ -12316,13 +12382,13 @@
     </row>
     <row r="136" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>281</v>
+        <v>257</v>
       </c>
       <c r="C136" t="s">
-        <v>282</v>
+        <v>258</v>
       </c>
       <c r="D136" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="E136" t="s">
         <v>33</v>
@@ -12337,16 +12403,16 @@
         <v>36</v>
       </c>
       <c r="J136" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K136" t="s">
-        <v>72</v>
+        <v>260</v>
       </c>
       <c r="L136" t="s">
-        <v>73</v>
+        <v>261</v>
       </c>
       <c r="M136" t="s">
-        <v>74</v>
+        <v>262</v>
       </c>
       <c r="N136" t="s">
         <v>33</v>
@@ -12358,16 +12424,19 @@
         <v>38</v>
       </c>
       <c r="Q136">
-        <v>11.99</v>
+        <v>24.49</v>
       </c>
       <c r="R136">
-        <v>2</v>
+        <v>4.08</v>
       </c>
       <c r="Y136" t="s">
-        <v>75</v>
+        <v>263</v>
+      </c>
+      <c r="Z136" t="s">
+        <v>64</v>
       </c>
       <c r="AA136" t="s">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="AB136" t="s">
         <v>39</v>
@@ -12381,16 +12450,16 @@
     </row>
     <row r="137" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>238</v>
+        <v>269</v>
       </c>
       <c r="C137" t="s">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="D137" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="E137" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F137" t="s">
         <v>34</v>
@@ -12413,14 +12482,26 @@
       <c r="M137" t="s">
         <v>42</v>
       </c>
+      <c r="N137" t="s">
+        <v>33</v>
+      </c>
       <c r="O137">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P137" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q137">
+        <v>59.99</v>
+      </c>
+      <c r="R137">
+        <v>10</v>
       </c>
       <c r="Y137" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="AA137" t="s">
-        <v>241</v>
+        <v>273</v>
       </c>
       <c r="AB137" t="s">
         <v>39</v>
@@ -12434,13 +12515,13 @@
     </row>
     <row r="138" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>224</v>
+        <v>149</v>
       </c>
       <c r="C138" t="s">
-        <v>225</v>
+        <v>150</v>
       </c>
       <c r="D138" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="E138" t="s">
         <v>33</v>
@@ -12482,10 +12563,10 @@
         <v>10</v>
       </c>
       <c r="Y138" t="s">
-        <v>226</v>
+        <v>63</v>
       </c>
       <c r="AA138" t="s">
-        <v>227</v>
+        <v>151</v>
       </c>
       <c r="AB138" t="s">
         <v>39</v>
@@ -12499,13 +12580,13 @@
     </row>
     <row r="139" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>213</v>
+        <v>275</v>
       </c>
       <c r="C139" t="s">
-        <v>214</v>
+        <v>276</v>
       </c>
       <c r="D139" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="E139" t="s">
         <v>33</v>
@@ -12535,25 +12616,25 @@
         <v>33</v>
       </c>
       <c r="O139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P139" t="s">
         <v>38</v>
       </c>
       <c r="Q139">
-        <v>59.99</v>
+        <v>119.98</v>
       </c>
       <c r="R139">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y139" t="s">
-        <v>215</v>
+        <v>278</v>
       </c>
       <c r="Z139" t="s">
-        <v>216</v>
+        <v>279</v>
       </c>
       <c r="AA139" t="s">
-        <v>217</v>
+        <v>280</v>
       </c>
       <c r="AB139" t="s">
         <v>39</v>
@@ -12567,13 +12648,13 @@
     </row>
     <row r="140" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>218</v>
+        <v>281</v>
       </c>
       <c r="C140" t="s">
-        <v>219</v>
+        <v>282</v>
       </c>
       <c r="D140" t="s">
-        <v>220</v>
+        <v>283</v>
       </c>
       <c r="E140" t="s">
         <v>33</v>
@@ -12588,16 +12669,16 @@
         <v>36</v>
       </c>
       <c r="J140" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K140" t="s">
-        <v>203</v>
+        <v>72</v>
       </c>
       <c r="L140" t="s">
-        <v>204</v>
+        <v>73</v>
       </c>
       <c r="M140" t="s">
-        <v>205</v>
+        <v>74</v>
       </c>
       <c r="N140" t="s">
         <v>33</v>
@@ -12609,19 +12690,16 @@
         <v>38</v>
       </c>
       <c r="Q140">
-        <v>69.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R140">
-        <v>11.67</v>
+        <v>2</v>
       </c>
       <c r="Y140" t="s">
-        <v>221</v>
-      </c>
-      <c r="Z140" t="s">
-        <v>222</v>
+        <v>75</v>
       </c>
       <c r="AA140" t="s">
-        <v>223</v>
+        <v>284</v>
       </c>
       <c r="AB140" t="s">
         <v>39</v>
@@ -12635,16 +12713,16 @@
     </row>
     <row r="141" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="C141" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="D141" t="s">
-        <v>230</v>
+        <v>285</v>
       </c>
       <c r="E141" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F141" t="s">
         <v>34</v>
@@ -12667,26 +12745,14 @@
       <c r="M141" t="s">
         <v>42</v>
       </c>
-      <c r="N141" t="s">
-        <v>33</v>
-      </c>
       <c r="O141">
-        <v>1</v>
-      </c>
-      <c r="P141" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q141">
-        <v>59.99</v>
-      </c>
-      <c r="R141">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y141" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="AA141" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="AB141" t="s">
         <v>39</v>
@@ -12700,13 +12766,13 @@
     </row>
     <row r="142" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="C142" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="D142" t="s">
-        <v>235</v>
+        <v>286</v>
       </c>
       <c r="E142" t="s">
         <v>33</v>
@@ -12724,13 +12790,13 @@
         <v>54</v>
       </c>
       <c r="K142" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="L142" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="M142" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="N142" t="s">
         <v>33</v>
@@ -12742,16 +12808,16 @@
         <v>38</v>
       </c>
       <c r="Q142">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R142">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y142" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="AA142" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="AB142" t="s">
         <v>39</v>
@@ -12765,16 +12831,16 @@
     </row>
     <row r="143" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>242</v>
+        <v>213</v>
       </c>
       <c r="C143" t="s">
-        <v>243</v>
+        <v>214</v>
       </c>
       <c r="D143" t="s">
-        <v>244</v>
+        <v>287</v>
       </c>
       <c r="E143" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F143" t="s">
         <v>34</v>
@@ -12797,14 +12863,29 @@
       <c r="M143" t="s">
         <v>42</v>
       </c>
+      <c r="N143" t="s">
+        <v>33</v>
+      </c>
       <c r="O143">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P143" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q143">
+        <v>59.99</v>
+      </c>
+      <c r="R143">
+        <v>10</v>
       </c>
       <c r="Y143" t="s">
-        <v>240</v>
+        <v>215</v>
+      </c>
+      <c r="Z143" t="s">
+        <v>216</v>
       </c>
       <c r="AA143" t="s">
-        <v>241</v>
+        <v>217</v>
       </c>
       <c r="AB143" t="s">
         <v>39</v>
@@ -12818,13 +12899,13 @@
     </row>
     <row r="144" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>245</v>
+        <v>218</v>
       </c>
       <c r="C144" t="s">
-        <v>246</v>
+        <v>219</v>
       </c>
       <c r="D144" t="s">
-        <v>247</v>
+        <v>220</v>
       </c>
       <c r="E144" t="s">
         <v>33</v>
@@ -12839,16 +12920,16 @@
         <v>36</v>
       </c>
       <c r="J144" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K144" t="s">
-        <v>40</v>
+        <v>203</v>
       </c>
       <c r="L144" t="s">
-        <v>41</v>
+        <v>204</v>
       </c>
       <c r="M144" t="s">
-        <v>42</v>
+        <v>205</v>
       </c>
       <c r="N144" t="s">
         <v>33</v>
@@ -12860,16 +12941,19 @@
         <v>38</v>
       </c>
       <c r="Q144">
-        <v>59.99</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="R144">
-        <v>10</v>
+        <v>11.67</v>
       </c>
       <c r="Y144" t="s">
-        <v>248</v>
+        <v>221</v>
+      </c>
+      <c r="Z144" t="s">
+        <v>222</v>
       </c>
       <c r="AA144" t="s">
-        <v>249</v>
+        <v>223</v>
       </c>
       <c r="AB144" t="s">
         <v>39</v>
@@ -12883,13 +12967,13 @@
     </row>
     <row r="145" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>188</v>
+        <v>228</v>
       </c>
       <c r="C145" t="s">
-        <v>189</v>
+        <v>229</v>
       </c>
       <c r="D145" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="E145" t="s">
         <v>33</v>
@@ -12904,16 +12988,16 @@
         <v>36</v>
       </c>
       <c r="J145" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K145" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L145" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M145" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N145" t="s">
         <v>33</v>
@@ -12925,16 +13009,16 @@
         <v>38</v>
       </c>
       <c r="Q145">
-        <v>37.99</v>
+        <v>59.99</v>
       </c>
       <c r="R145">
-        <v>6.33</v>
+        <v>10</v>
       </c>
       <c r="Y145" t="s">
-        <v>52</v>
+        <v>231</v>
       </c>
       <c r="AA145" t="s">
-        <v>190</v>
+        <v>232</v>
       </c>
       <c r="AB145" t="s">
         <v>39</v>
@@ -12948,13 +13032,13 @@
     </row>
     <row r="146" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>191</v>
+        <v>233</v>
       </c>
       <c r="C146" t="s">
-        <v>192</v>
+        <v>234</v>
       </c>
       <c r="D146" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="E146" t="s">
         <v>33</v>
@@ -12972,13 +13056,13 @@
         <v>54</v>
       </c>
       <c r="K146" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="L146" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="M146" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="N146" t="s">
         <v>33</v>
@@ -12990,16 +13074,16 @@
         <v>38</v>
       </c>
       <c r="Q146">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="R146">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="Y146" t="s">
-        <v>193</v>
+        <v>236</v>
       </c>
       <c r="AA146" t="s">
-        <v>194</v>
+        <v>237</v>
       </c>
       <c r="AB146" t="s">
         <v>39</v>
@@ -13013,16 +13097,16 @@
     </row>
     <row r="147" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>201</v>
+        <v>242</v>
       </c>
       <c r="C147" t="s">
-        <v>202</v>
+        <v>243</v>
       </c>
       <c r="D147" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="E147" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F147" t="s">
         <v>34</v>
@@ -13037,37 +13121,22 @@
         <v>54</v>
       </c>
       <c r="K147" t="s">
-        <v>203</v>
+        <v>40</v>
       </c>
       <c r="L147" t="s">
-        <v>204</v>
+        <v>41</v>
       </c>
       <c r="M147" t="s">
-        <v>205</v>
-      </c>
-      <c r="N147" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O147">
-        <v>1</v>
-      </c>
-      <c r="P147" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q147">
-        <v>69.989999999999995</v>
-      </c>
-      <c r="R147">
-        <v>11.67</v>
+        <v>0</v>
       </c>
       <c r="Y147" t="s">
-        <v>206</v>
-      </c>
-      <c r="Z147" t="s">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="AA147" t="s">
-        <v>207</v>
+        <v>241</v>
       </c>
       <c r="AB147" t="s">
         <v>39</v>
@@ -13081,13 +13150,13 @@
     </row>
     <row r="148" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>195</v>
+        <v>245</v>
       </c>
       <c r="C148" t="s">
-        <v>196</v>
+        <v>246</v>
       </c>
       <c r="D148" t="s">
-        <v>197</v>
+        <v>247</v>
       </c>
       <c r="E148" t="s">
         <v>33</v>
@@ -13129,13 +13198,10 @@
         <v>10</v>
       </c>
       <c r="Y148" t="s">
-        <v>198</v>
-      </c>
-      <c r="Z148" t="s">
-        <v>199</v>
+        <v>248</v>
       </c>
       <c r="AA148" t="s">
-        <v>200</v>
+        <v>249</v>
       </c>
       <c r="AB148" t="s">
         <v>39</v>
@@ -13149,13 +13215,13 @@
     </row>
     <row r="149" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="C149" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="D149" t="s">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="E149" t="s">
         <v>33</v>
@@ -13173,13 +13239,13 @@
         <v>37</v>
       </c>
       <c r="K149" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L149" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M149" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N149" t="s">
         <v>33</v>
@@ -13191,16 +13257,16 @@
         <v>38</v>
       </c>
       <c r="Q149">
-        <v>59.99</v>
+        <v>37.99</v>
       </c>
       <c r="R149">
-        <v>10</v>
+        <v>6.33</v>
       </c>
       <c r="Y149" t="s">
-        <v>211</v>
+        <v>52</v>
       </c>
       <c r="AA149" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="AB149" t="s">
         <v>39</v>
@@ -13214,13 +13280,13 @@
     </row>
     <row r="150" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>152</v>
+        <v>191</v>
       </c>
       <c r="C150" t="s">
-        <v>153</v>
+        <v>192</v>
       </c>
       <c r="D150" t="s">
-        <v>154</v>
+        <v>251</v>
       </c>
       <c r="E150" t="s">
         <v>33</v>
@@ -13238,13 +13304,13 @@
         <v>54</v>
       </c>
       <c r="K150" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="L150" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="M150" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="N150" t="s">
         <v>33</v>
@@ -13256,16 +13322,16 @@
         <v>38</v>
       </c>
       <c r="Q150">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R150">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y150" t="s">
-        <v>155</v>
+        <v>193</v>
       </c>
       <c r="AA150" t="s">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="AB150" t="s">
         <v>39</v>
@@ -13279,13 +13345,13 @@
     </row>
     <row r="151" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>157</v>
+        <v>201</v>
       </c>
       <c r="C151" t="s">
-        <v>158</v>
+        <v>202</v>
       </c>
       <c r="D151" t="s">
-        <v>159</v>
+        <v>252</v>
       </c>
       <c r="E151" t="s">
         <v>33</v>
@@ -13303,13 +13369,13 @@
         <v>54</v>
       </c>
       <c r="K151" t="s">
-        <v>72</v>
+        <v>203</v>
       </c>
       <c r="L151" t="s">
-        <v>73</v>
+        <v>204</v>
       </c>
       <c r="M151" t="s">
-        <v>74</v>
+        <v>205</v>
       </c>
       <c r="N151" t="s">
         <v>33</v>
@@ -13321,16 +13387,19 @@
         <v>38</v>
       </c>
       <c r="Q151">
-        <v>11.99</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="R151">
-        <v>2</v>
+        <v>11.67</v>
       </c>
       <c r="Y151" t="s">
-        <v>68</v>
+        <v>206</v>
+      </c>
+      <c r="Z151" t="s">
+        <v>60</v>
       </c>
       <c r="AA151" t="s">
-        <v>160</v>
+        <v>207</v>
       </c>
       <c r="AB151" t="s">
         <v>39</v>
@@ -13344,16 +13413,16 @@
     </row>
     <row r="152" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="C152" t="s">
-        <v>162</v>
+        <v>196</v>
       </c>
       <c r="D152" t="s">
-        <v>163</v>
+        <v>197</v>
       </c>
       <c r="E152" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F152" t="s">
         <v>34</v>
@@ -13365,7 +13434,7 @@
         <v>36</v>
       </c>
       <c r="J152" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K152" t="s">
         <v>40</v>
@@ -13376,14 +13445,29 @@
       <c r="M152" t="s">
         <v>42</v>
       </c>
+      <c r="N152" t="s">
+        <v>33</v>
+      </c>
       <c r="O152">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P152" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q152">
+        <v>59.99</v>
+      </c>
+      <c r="R152">
+        <v>10</v>
       </c>
       <c r="Y152" t="s">
-        <v>63</v>
+        <v>198</v>
+      </c>
+      <c r="Z152" t="s">
+        <v>199</v>
       </c>
       <c r="AA152" t="s">
-        <v>151</v>
+        <v>200</v>
       </c>
       <c r="AB152" t="s">
         <v>39</v>
@@ -13397,13 +13481,13 @@
     </row>
     <row r="153" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>164</v>
+        <v>208</v>
       </c>
       <c r="C153" t="s">
-        <v>165</v>
+        <v>209</v>
       </c>
       <c r="D153" t="s">
-        <v>166</v>
+        <v>210</v>
       </c>
       <c r="E153" t="s">
         <v>33</v>
@@ -13418,16 +13502,16 @@
         <v>36</v>
       </c>
       <c r="J153" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K153" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L153" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M153" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N153" t="s">
         <v>33</v>
@@ -13439,16 +13523,16 @@
         <v>38</v>
       </c>
       <c r="Q153">
-        <v>37.99</v>
+        <v>59.99</v>
       </c>
       <c r="R153">
-        <v>6.33</v>
+        <v>10</v>
       </c>
       <c r="Y153" t="s">
-        <v>100</v>
+        <v>211</v>
       </c>
       <c r="AA153" t="s">
-        <v>167</v>
+        <v>212</v>
       </c>
       <c r="AB153" t="s">
         <v>39</v>
@@ -13462,13 +13546,13 @@
     </row>
     <row r="154" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="C154" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="D154" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="E154" t="s">
         <v>33</v>
@@ -13486,13 +13570,13 @@
         <v>54</v>
       </c>
       <c r="K154" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="L154" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M154" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="N154" t="s">
         <v>33</v>
@@ -13504,16 +13588,16 @@
         <v>38</v>
       </c>
       <c r="Q154">
-        <v>11.99</v>
+        <v>14.99</v>
       </c>
       <c r="R154">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Y154" t="s">
-        <v>66</v>
+        <v>155</v>
       </c>
       <c r="AA154" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="AB154" t="s">
         <v>39</v>
@@ -13527,13 +13611,13 @@
     </row>
     <row r="155" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="C155" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="D155" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="E155" t="s">
         <v>33</v>
@@ -13551,13 +13635,13 @@
         <v>54</v>
       </c>
       <c r="K155" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L155" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M155" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="N155" t="s">
         <v>33</v>
@@ -13569,16 +13653,16 @@
         <v>38</v>
       </c>
       <c r="Q155">
-        <v>14.99</v>
+        <v>11.99</v>
       </c>
       <c r="R155">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Y155" t="s">
-        <v>175</v>
+        <v>68</v>
       </c>
       <c r="AA155" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="AB155" t="s">
         <v>39</v>
@@ -13592,16 +13676,16 @@
     </row>
     <row r="156" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="C156" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="D156" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="E156" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F156" t="s">
         <v>34</v>
@@ -13616,37 +13700,22 @@
         <v>54</v>
       </c>
       <c r="K156" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L156" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M156" t="s">
-        <v>50</v>
-      </c>
-      <c r="N156" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O156">
-        <v>1</v>
-      </c>
-      <c r="P156" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q156">
-        <v>37.99</v>
-      </c>
-      <c r="R156">
-        <v>6.33</v>
+        <v>0</v>
       </c>
       <c r="Y156" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z156" t="s">
-        <v>181</v>
+        <v>63</v>
       </c>
       <c r="AA156" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="AB156" t="s">
         <v>39</v>
@@ -13660,13 +13729,13 @@
     </row>
     <row r="157" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="C157" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="D157" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="E157" t="s">
         <v>33</v>
@@ -13696,25 +13765,22 @@
         <v>33</v>
       </c>
       <c r="O157">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P157" t="s">
         <v>38</v>
       </c>
       <c r="Q157">
-        <v>75.98</v>
+        <v>37.99</v>
       </c>
       <c r="R157">
-        <v>12.66</v>
+        <v>6.33</v>
       </c>
       <c r="Y157" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z157" t="s">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="AA157" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="AB157" t="s">
         <v>39</v>
@@ -13728,13 +13794,13 @@
     </row>
     <row r="158" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="C158" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="D158" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="E158" t="s">
         <v>33</v>
@@ -13776,10 +13842,10 @@
         <v>2</v>
       </c>
       <c r="Y158" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="AA158" t="s">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="AB158" t="s">
         <v>39</v>
@@ -13793,13 +13859,13 @@
     </row>
     <row r="159" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>117</v>
+        <v>172</v>
       </c>
       <c r="C159" t="s">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="D159" t="s">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="E159" t="s">
         <v>33</v>
@@ -13841,13 +13907,10 @@
         <v>2.5</v>
       </c>
       <c r="Y159" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z159" t="s">
-        <v>121</v>
+        <v>175</v>
       </c>
       <c r="AA159" t="s">
-        <v>122</v>
+        <v>176</v>
       </c>
       <c r="AB159" t="s">
         <v>39</v>
@@ -13861,13 +13924,13 @@
     </row>
     <row r="160" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>123</v>
+        <v>177</v>
       </c>
       <c r="C160" t="s">
-        <v>124</v>
+        <v>178</v>
       </c>
       <c r="D160" t="s">
-        <v>125</v>
+        <v>179</v>
       </c>
       <c r="E160" t="s">
         <v>33</v>
@@ -13885,13 +13948,13 @@
         <v>54</v>
       </c>
       <c r="K160" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L160" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M160" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N160" t="s">
         <v>33</v>
@@ -13903,19 +13966,19 @@
         <v>38</v>
       </c>
       <c r="Q160">
-        <v>59.99</v>
+        <v>37.99</v>
       </c>
       <c r="R160">
-        <v>10</v>
+        <v>6.33</v>
       </c>
       <c r="Y160" t="s">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="Z160" t="s">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="AA160" t="s">
-        <v>128</v>
+        <v>182</v>
       </c>
       <c r="AB160" t="s">
         <v>39</v>
@@ -13929,13 +13992,13 @@
     </row>
     <row r="161" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>129</v>
+        <v>183</v>
       </c>
       <c r="C161" t="s">
-        <v>130</v>
+        <v>184</v>
       </c>
       <c r="D161" t="s">
-        <v>131</v>
+        <v>179</v>
       </c>
       <c r="E161" t="s">
         <v>33</v>
@@ -13953,34 +14016,37 @@
         <v>54</v>
       </c>
       <c r="K161" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="L161" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M161" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="N161" t="s">
         <v>33</v>
       </c>
       <c r="O161">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P161" t="s">
         <v>38</v>
       </c>
       <c r="Q161">
-        <v>38.49</v>
+        <v>75.98</v>
       </c>
       <c r="R161">
-        <v>6.42</v>
+        <v>12.66</v>
       </c>
       <c r="Y161" t="s">
-        <v>78</v>
+        <v>70</v>
+      </c>
+      <c r="Z161" t="s">
+        <v>47</v>
       </c>
       <c r="AA161" t="s">
-        <v>132</v>
+        <v>185</v>
       </c>
       <c r="AB161" t="s">
         <v>39</v>
@@ -13994,16 +14060,16 @@
     </row>
     <row r="162" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="C162" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="D162" t="s">
-        <v>136</v>
+        <v>186</v>
       </c>
       <c r="E162" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F162" t="s">
         <v>34</v>
@@ -14018,22 +14084,34 @@
         <v>54</v>
       </c>
       <c r="K162" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L162" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M162" t="s">
-        <v>83</v>
+        <v>74</v>
+      </c>
+      <c r="N162" t="s">
+        <v>33</v>
       </c>
       <c r="O162">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P162" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q162">
+        <v>11.99</v>
+      </c>
+      <c r="R162">
+        <v>2</v>
       </c>
       <c r="Y162" t="s">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="AA162" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="AB162" t="s">
         <v>39</v>
@@ -14047,13 +14125,13 @@
     </row>
     <row r="163" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C163" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="D163" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="E163" t="s">
         <v>33</v>
@@ -14071,13 +14149,13 @@
         <v>54</v>
       </c>
       <c r="K163" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="L163" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="M163" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="N163" t="s">
         <v>33</v>
@@ -14089,19 +14167,19 @@
         <v>38</v>
       </c>
       <c r="Q163">
-        <v>37.99</v>
+        <v>14.99</v>
       </c>
       <c r="R163">
-        <v>6.33</v>
+        <v>2.5</v>
       </c>
       <c r="Y163" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="Z163" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AA163" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="AB163" t="s">
         <v>39</v>
@@ -14115,13 +14193,13 @@
     </row>
     <row r="164" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="C164" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D164" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E164" t="s">
         <v>33</v>
@@ -14136,7 +14214,7 @@
         <v>36</v>
       </c>
       <c r="J164" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K164" t="s">
         <v>40</v>
@@ -14163,13 +14241,13 @@
         <v>10</v>
       </c>
       <c r="Y164" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="Z164" t="s">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="AA164" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="AB164" t="s">
         <v>39</v>
@@ -14183,66 +14261,320 @@
     </row>
     <row r="165" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
+        <v>129</v>
+      </c>
+      <c r="C165" t="s">
+        <v>130</v>
+      </c>
+      <c r="D165" t="s">
+        <v>131</v>
+      </c>
+      <c r="E165" t="s">
+        <v>33</v>
+      </c>
+      <c r="F165" t="s">
+        <v>34</v>
+      </c>
+      <c r="G165" t="s">
+        <v>35</v>
+      </c>
+      <c r="H165" t="s">
+        <v>36</v>
+      </c>
+      <c r="J165" t="s">
+        <v>54</v>
+      </c>
+      <c r="K165" t="s">
+        <v>43</v>
+      </c>
+      <c r="L165" t="s">
+        <v>44</v>
+      </c>
+      <c r="M165" t="s">
+        <v>45</v>
+      </c>
+      <c r="N165" t="s">
+        <v>33</v>
+      </c>
+      <c r="O165">
+        <v>1</v>
+      </c>
+      <c r="P165" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q165">
+        <v>38.49</v>
+      </c>
+      <c r="R165">
+        <v>6.42</v>
+      </c>
+      <c r="Y165" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA165" t="s">
+        <v>132</v>
+      </c>
+      <c r="AB165" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG165" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>105</v>
+      </c>
+      <c r="C166" t="s">
+        <v>106</v>
+      </c>
+      <c r="D166" t="s">
+        <v>136</v>
+      </c>
+      <c r="E166" t="s">
+        <v>53</v>
+      </c>
+      <c r="F166" t="s">
+        <v>34</v>
+      </c>
+      <c r="G166" t="s">
+        <v>35</v>
+      </c>
+      <c r="H166" t="s">
+        <v>36</v>
+      </c>
+      <c r="J166" t="s">
+        <v>54</v>
+      </c>
+      <c r="K166" t="s">
+        <v>94</v>
+      </c>
+      <c r="L166" t="s">
+        <v>82</v>
+      </c>
+      <c r="M166" t="s">
+        <v>83</v>
+      </c>
+      <c r="O166">
+        <v>0</v>
+      </c>
+      <c r="Y166" t="s">
+        <v>103</v>
+      </c>
+      <c r="AA166" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB166" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG166" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>107</v>
+      </c>
+      <c r="C167" t="s">
+        <v>108</v>
+      </c>
+      <c r="D167" t="s">
+        <v>137</v>
+      </c>
+      <c r="E167" t="s">
+        <v>33</v>
+      </c>
+      <c r="F167" t="s">
+        <v>34</v>
+      </c>
+      <c r="G167" t="s">
+        <v>35</v>
+      </c>
+      <c r="H167" t="s">
+        <v>36</v>
+      </c>
+      <c r="J167" t="s">
+        <v>54</v>
+      </c>
+      <c r="K167" t="s">
+        <v>48</v>
+      </c>
+      <c r="L167" t="s">
+        <v>49</v>
+      </c>
+      <c r="M167" t="s">
+        <v>50</v>
+      </c>
+      <c r="N167" t="s">
+        <v>33</v>
+      </c>
+      <c r="O167">
+        <v>1</v>
+      </c>
+      <c r="P167" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q167">
+        <v>37.99</v>
+      </c>
+      <c r="R167">
+        <v>6.33</v>
+      </c>
+      <c r="Y167" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z167" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA167" t="s">
+        <v>111</v>
+      </c>
+      <c r="AB167" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG167" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>112</v>
+      </c>
+      <c r="C168" t="s">
+        <v>113</v>
+      </c>
+      <c r="D168" t="s">
+        <v>114</v>
+      </c>
+      <c r="E168" t="s">
+        <v>33</v>
+      </c>
+      <c r="F168" t="s">
+        <v>34</v>
+      </c>
+      <c r="G168" t="s">
+        <v>35</v>
+      </c>
+      <c r="H168" t="s">
+        <v>36</v>
+      </c>
+      <c r="J168" t="s">
+        <v>37</v>
+      </c>
+      <c r="K168" t="s">
+        <v>40</v>
+      </c>
+      <c r="L168" t="s">
+        <v>41</v>
+      </c>
+      <c r="M168" t="s">
+        <v>42</v>
+      </c>
+      <c r="N168" t="s">
+        <v>33</v>
+      </c>
+      <c r="O168">
+        <v>1</v>
+      </c>
+      <c r="P168" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q168">
+        <v>59.99</v>
+      </c>
+      <c r="R168">
+        <v>10</v>
+      </c>
+      <c r="Y168" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z168" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA168" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB168" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG168" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
         <v>703</v>
       </c>
-      <c r="C165" t="s">
+      <c r="C169" t="s">
         <v>704</v>
       </c>
-      <c r="D165" t="s">
+      <c r="D169" t="s">
         <v>705</v>
       </c>
-      <c r="E165" t="s">
-        <v>33</v>
-      </c>
-      <c r="F165" t="s">
-        <v>34</v>
-      </c>
-      <c r="G165" t="s">
-        <v>35</v>
-      </c>
-      <c r="H165" t="s">
-        <v>36</v>
-      </c>
-      <c r="J165" t="s">
-        <v>54</v>
-      </c>
-      <c r="K165" t="s">
+      <c r="E169" t="s">
+        <v>33</v>
+      </c>
+      <c r="F169" t="s">
+        <v>34</v>
+      </c>
+      <c r="G169" t="s">
+        <v>35</v>
+      </c>
+      <c r="H169" t="s">
+        <v>36</v>
+      </c>
+      <c r="J169" t="s">
+        <v>54</v>
+      </c>
+      <c r="K169" t="s">
         <v>72</v>
       </c>
-      <c r="L165" t="s">
+      <c r="L169" t="s">
         <v>73</v>
       </c>
-      <c r="M165" t="s">
+      <c r="M169" t="s">
         <v>74</v>
       </c>
-      <c r="N165" t="s">
-        <v>33</v>
-      </c>
-      <c r="O165">
-        <v>1</v>
-      </c>
-      <c r="P165" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q165">
+      <c r="N169" t="s">
+        <v>33</v>
+      </c>
+      <c r="O169">
+        <v>1</v>
+      </c>
+      <c r="P169" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q169">
         <v>11.99</v>
       </c>
-      <c r="R165">
+      <c r="R169">
         <v>2</v>
       </c>
-      <c r="Y165" t="s">
+      <c r="Y169" t="s">
         <v>706</v>
       </c>
-      <c r="AA165" t="s">
+      <c r="AA169" t="s">
         <v>707</v>
       </c>
-      <c r="AB165" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD165" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG165" t="b">
+      <c r="AB169" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG169" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Raw Sales Data/Amazon.xlsx
+++ b/Raw Sales Data/Amazon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2749" uniqueCount="891">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2842" uniqueCount="917">
   <si>
     <t>amazon-order-id</t>
   </si>
@@ -2692,6 +2692,84 @@
   </si>
   <si>
     <t>PA19 1HD</t>
+  </si>
+  <si>
+    <t>204-0139166-0117926</t>
+  </si>
+  <si>
+    <t>2026-03-11T18:40:23+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-11T19:10:33+00:00</t>
+  </si>
+  <si>
+    <t>MAYFIELD</t>
+  </si>
+  <si>
+    <t>TN20 6UR</t>
+  </si>
+  <si>
+    <t>204-2397636-9017927</t>
+  </si>
+  <si>
+    <t>2026-03-11T18:20:57+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-11T18:39:23+00:00</t>
+  </si>
+  <si>
+    <t>204-4459999-6679503</t>
+  </si>
+  <si>
+    <t>2026-03-11T18:17:14+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-11T18:41:07+00:00</t>
+  </si>
+  <si>
+    <t>203-7066115-8505931</t>
+  </si>
+  <si>
+    <t>2026-03-11T16:50:41+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-11T17:19:07+00:00</t>
+  </si>
+  <si>
+    <t>25cc Petrol Chainsaw, Lightweight Top Handle Tree Cutter, 2-Stroke Gas Chainsaw, Easy Start One-Hand Operation, 12 Inch Bar, Anti-Vibration Saw, Ideal Tool for Logging and Pruning, 4PCS Free Gloves</t>
+  </si>
+  <si>
+    <t>250601000004 + Gloves 251001000045 (4pc)</t>
+  </si>
+  <si>
+    <t>B0GQC9KZMM</t>
+  </si>
+  <si>
+    <t>206-1250481-9262761</t>
+  </si>
+  <si>
+    <t>2026-03-11T13:40:17+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-11T14:10:41+00:00</t>
+  </si>
+  <si>
+    <t>LISBURN</t>
+  </si>
+  <si>
+    <t>BT27 5LT</t>
+  </si>
+  <si>
+    <t>026-8051067-2263547</t>
+  </si>
+  <si>
+    <t>2026-03-11T09:33:53+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-11T11:10:04+00:00</t>
+  </si>
+  <si>
+    <t>PE11 3EP</t>
   </si>
 </sst>
 </file>
@@ -3498,7 +3576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG169"/>
+  <dimension ref="A1:AG175"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
@@ -3609,16 +3687,16 @@
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>869</v>
+        <v>891</v>
       </c>
       <c r="C2" t="s">
-        <v>870</v>
+        <v>892</v>
       </c>
       <c r="D2" t="s">
-        <v>871</v>
+        <v>893</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F2" t="s">
         <v>34</v>
@@ -3642,7 +3720,7 @@
         <v>42</v>
       </c>
       <c r="N2" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O2">
         <v>1</v>
@@ -3657,13 +3735,10 @@
         <v>11.33</v>
       </c>
       <c r="Y2" t="s">
-        <v>872</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>873</v>
+        <v>894</v>
       </c>
       <c r="AA2" t="s">
-        <v>874</v>
+        <v>895</v>
       </c>
       <c r="AB2" t="s">
         <v>39</v>
@@ -3677,16 +3752,16 @@
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>875</v>
+        <v>896</v>
       </c>
       <c r="C3" t="s">
-        <v>876</v>
+        <v>897</v>
       </c>
       <c r="D3" t="s">
-        <v>877</v>
+        <v>898</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F3" t="s">
         <v>34</v>
@@ -3709,26 +3784,14 @@
       <c r="M3" t="s">
         <v>42</v>
       </c>
-      <c r="N3" t="s">
-        <v>33</v>
-      </c>
       <c r="O3">
-        <v>1</v>
-      </c>
-      <c r="P3" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q3">
-        <v>67.989999999999995</v>
-      </c>
-      <c r="R3">
-        <v>11.33</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="s">
-        <v>878</v>
+        <v>894</v>
       </c>
       <c r="AA3" t="s">
-        <v>879</v>
+        <v>895</v>
       </c>
       <c r="AB3" t="s">
         <v>39</v>
@@ -3742,16 +3805,16 @@
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>880</v>
+        <v>899</v>
       </c>
       <c r="C4" t="s">
-        <v>881</v>
+        <v>900</v>
       </c>
       <c r="D4" t="s">
-        <v>882</v>
+        <v>901</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F4" t="s">
         <v>34</v>
@@ -3774,26 +3837,14 @@
       <c r="M4" t="s">
         <v>42</v>
       </c>
-      <c r="N4" t="s">
-        <v>33</v>
-      </c>
       <c r="O4">
-        <v>1</v>
-      </c>
-      <c r="P4" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q4">
-        <v>65.989999999999995</v>
-      </c>
-      <c r="R4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="s">
-        <v>883</v>
+        <v>894</v>
       </c>
       <c r="AA4" t="s">
-        <v>884</v>
+        <v>895</v>
       </c>
       <c r="AB4" t="s">
         <v>39</v>
@@ -3807,16 +3858,16 @@
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>885</v>
+        <v>902</v>
       </c>
       <c r="C5" t="s">
-        <v>886</v>
+        <v>903</v>
       </c>
       <c r="D5" t="s">
-        <v>887</v>
+        <v>904</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F5" t="s">
         <v>34</v>
@@ -3831,16 +3882,16 @@
         <v>54</v>
       </c>
       <c r="K5" t="s">
-        <v>40</v>
+        <v>905</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>906</v>
       </c>
       <c r="M5" t="s">
-        <v>42</v>
+        <v>907</v>
       </c>
       <c r="N5" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O5">
         <v>1</v>
@@ -3849,25 +3900,19 @@
         <v>38</v>
       </c>
       <c r="Q5">
-        <v>65.989999999999995</v>
-      </c>
-      <c r="R5">
-        <v>11</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="Y5" t="s">
-        <v>888</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>889</v>
+        <v>894</v>
       </c>
       <c r="AA5" t="s">
-        <v>890</v>
+        <v>895</v>
       </c>
       <c r="AB5" t="s">
         <v>39</v>
       </c>
       <c r="AD5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
@@ -3875,16 +3920,16 @@
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>864</v>
+        <v>908</v>
       </c>
       <c r="C6" t="s">
-        <v>865</v>
+        <v>909</v>
       </c>
       <c r="D6" t="s">
-        <v>866</v>
+        <v>910</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F6" t="s">
         <v>34</v>
@@ -3908,7 +3953,7 @@
         <v>42</v>
       </c>
       <c r="N6" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O6">
         <v>1</v>
@@ -3917,16 +3962,22 @@
         <v>38</v>
       </c>
       <c r="Q6">
-        <v>65.989999999999995</v>
+        <v>67.989999999999995</v>
       </c>
       <c r="R6">
-        <v>11</v>
+        <v>11.33</v>
+      </c>
+      <c r="S6">
+        <v>6.99</v>
+      </c>
+      <c r="T6">
+        <v>1.17</v>
       </c>
       <c r="Y6" t="s">
-        <v>867</v>
+        <v>911</v>
       </c>
       <c r="AA6" t="s">
-        <v>868</v>
+        <v>912</v>
       </c>
       <c r="AB6" t="s">
         <v>39</v>
@@ -3940,13 +3991,13 @@
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>846</v>
+        <v>913</v>
       </c>
       <c r="C7" t="s">
-        <v>847</v>
+        <v>914</v>
       </c>
       <c r="D7" t="s">
-        <v>848</v>
+        <v>915</v>
       </c>
       <c r="E7" t="s">
         <v>33</v>
@@ -3964,13 +4015,13 @@
         <v>54</v>
       </c>
       <c r="K7" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L7" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M7" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N7" t="s">
         <v>33</v>
@@ -3982,25 +4033,19 @@
         <v>38</v>
       </c>
       <c r="Q7">
-        <v>65.989999999999995</v>
+        <v>40.99</v>
       </c>
       <c r="R7">
-        <v>11</v>
-      </c>
-      <c r="S7">
-        <v>6.99</v>
-      </c>
-      <c r="T7">
-        <v>1.17</v>
+        <v>6.83</v>
       </c>
       <c r="Y7" t="s">
-        <v>849</v>
+        <v>420</v>
       </c>
       <c r="Z7" t="s">
-        <v>850</v>
+        <v>76</v>
       </c>
       <c r="AA7" t="s">
-        <v>851</v>
+        <v>916</v>
       </c>
       <c r="AB7" t="s">
         <v>39</v>
@@ -4014,16 +4059,16 @@
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>852</v>
+        <v>869</v>
       </c>
       <c r="C8" t="s">
-        <v>853</v>
+        <v>870</v>
       </c>
       <c r="D8" t="s">
-        <v>854</v>
+        <v>871</v>
       </c>
       <c r="E8" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F8" t="s">
         <v>34</v>
@@ -4046,14 +4091,29 @@
       <c r="M8" t="s">
         <v>42</v>
       </c>
+      <c r="N8" t="s">
+        <v>33</v>
+      </c>
       <c r="O8">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P8" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q8">
+        <v>67.989999999999995</v>
+      </c>
+      <c r="R8">
+        <v>11.33</v>
       </c>
       <c r="Y8" t="s">
-        <v>855</v>
+        <v>872</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>873</v>
       </c>
       <c r="AA8" t="s">
-        <v>856</v>
+        <v>874</v>
       </c>
       <c r="AB8" t="s">
         <v>39</v>
@@ -4067,13 +4127,13 @@
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>857</v>
+        <v>875</v>
       </c>
       <c r="C9" t="s">
-        <v>858</v>
+        <v>876</v>
       </c>
       <c r="D9" t="s">
-        <v>859</v>
+        <v>877</v>
       </c>
       <c r="E9" t="s">
         <v>33</v>
@@ -4109,16 +4169,16 @@
         <v>38</v>
       </c>
       <c r="Q9">
-        <v>65.989999999999995</v>
+        <v>67.989999999999995</v>
       </c>
       <c r="R9">
-        <v>11</v>
+        <v>11.33</v>
       </c>
       <c r="Y9" t="s">
-        <v>860</v>
+        <v>878</v>
       </c>
       <c r="AA9" t="s">
-        <v>861</v>
+        <v>879</v>
       </c>
       <c r="AB9" t="s">
         <v>39</v>
@@ -4132,13 +4192,13 @@
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>837</v>
+        <v>880</v>
       </c>
       <c r="C10" t="s">
-        <v>838</v>
+        <v>881</v>
       </c>
       <c r="D10" t="s">
-        <v>862</v>
+        <v>882</v>
       </c>
       <c r="E10" t="s">
         <v>33</v>
@@ -4156,13 +4216,13 @@
         <v>54</v>
       </c>
       <c r="K10" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L10" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M10" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N10" t="s">
         <v>33</v>
@@ -4174,16 +4234,16 @@
         <v>38</v>
       </c>
       <c r="Q10">
-        <v>40.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R10">
-        <v>6.83</v>
+        <v>11</v>
       </c>
       <c r="Y10" t="s">
-        <v>305</v>
+        <v>883</v>
       </c>
       <c r="AA10" t="s">
-        <v>840</v>
+        <v>884</v>
       </c>
       <c r="AB10" t="s">
         <v>39</v>
@@ -4197,13 +4257,13 @@
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>841</v>
+        <v>885</v>
       </c>
       <c r="C11" t="s">
-        <v>842</v>
+        <v>886</v>
       </c>
       <c r="D11" t="s">
-        <v>863</v>
+        <v>887</v>
       </c>
       <c r="E11" t="s">
         <v>33</v>
@@ -4244,17 +4304,14 @@
       <c r="R11">
         <v>11</v>
       </c>
-      <c r="S11">
-        <v>6.99</v>
-      </c>
-      <c r="T11">
-        <v>1.17</v>
-      </c>
       <c r="Y11" t="s">
-        <v>844</v>
+        <v>888</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>889</v>
       </c>
       <c r="AA11" t="s">
-        <v>845</v>
+        <v>890</v>
       </c>
       <c r="AB11" t="s">
         <v>39</v>
@@ -4268,16 +4325,16 @@
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>837</v>
+        <v>864</v>
       </c>
       <c r="C12" t="s">
-        <v>838</v>
+        <v>865</v>
       </c>
       <c r="D12" t="s">
-        <v>839</v>
+        <v>866</v>
       </c>
       <c r="E12" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F12" t="s">
         <v>34</v>
@@ -4292,16 +4349,16 @@
         <v>54</v>
       </c>
       <c r="K12" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L12" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M12" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N12" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O12">
         <v>1</v>
@@ -4310,16 +4367,16 @@
         <v>38</v>
       </c>
       <c r="Q12">
-        <v>40.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R12">
-        <v>6.83</v>
+        <v>11</v>
       </c>
       <c r="Y12" t="s">
-        <v>305</v>
+        <v>867</v>
       </c>
       <c r="AA12" t="s">
-        <v>840</v>
+        <v>868</v>
       </c>
       <c r="AB12" t="s">
         <v>39</v>
@@ -4333,16 +4390,16 @@
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="C13" t="s">
-        <v>842</v>
+        <v>847</v>
       </c>
       <c r="D13" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="E13" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F13" t="s">
         <v>34</v>
@@ -4366,7 +4423,7 @@
         <v>42</v>
       </c>
       <c r="N13" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O13">
         <v>1</v>
@@ -4387,10 +4444,13 @@
         <v>1.17</v>
       </c>
       <c r="Y13" t="s">
-        <v>844</v>
+        <v>849</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>850</v>
       </c>
       <c r="AA13" t="s">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="AB13" t="s">
         <v>39</v>
@@ -4404,16 +4464,16 @@
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>819</v>
+        <v>852</v>
       </c>
       <c r="C14" t="s">
-        <v>820</v>
+        <v>853</v>
       </c>
       <c r="D14" t="s">
-        <v>821</v>
+        <v>854</v>
       </c>
       <c r="E14" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="F14" t="s">
         <v>34</v>
@@ -4428,37 +4488,22 @@
         <v>54</v>
       </c>
       <c r="K14" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L14" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M14" t="s">
-        <v>50</v>
-      </c>
-      <c r="N14" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="O14">
-        <v>1</v>
-      </c>
-      <c r="P14" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q14">
-        <v>40.99</v>
-      </c>
-      <c r="R14">
-        <v>6.83</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="s">
-        <v>618</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>619</v>
+        <v>855</v>
       </c>
       <c r="AA14" t="s">
-        <v>620</v>
+        <v>856</v>
       </c>
       <c r="AB14" t="s">
         <v>39</v>
@@ -4472,16 +4517,16 @@
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>822</v>
+        <v>857</v>
       </c>
       <c r="C15" t="s">
-        <v>823</v>
+        <v>858</v>
       </c>
       <c r="D15" t="s">
-        <v>824</v>
+        <v>859</v>
       </c>
       <c r="E15" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F15" t="s">
         <v>34</v>
@@ -4496,16 +4541,16 @@
         <v>54</v>
       </c>
       <c r="K15" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L15" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M15" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N15" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O15">
         <v>1</v>
@@ -4514,16 +4559,16 @@
         <v>38</v>
       </c>
       <c r="Q15">
-        <v>14.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R15">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="Y15" t="s">
-        <v>825</v>
+        <v>860</v>
       </c>
       <c r="AA15" t="s">
-        <v>826</v>
+        <v>861</v>
       </c>
       <c r="AB15" t="s">
         <v>39</v>
@@ -4537,16 +4582,16 @@
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>827</v>
+        <v>837</v>
       </c>
       <c r="C16" t="s">
-        <v>828</v>
+        <v>838</v>
       </c>
       <c r="D16" t="s">
-        <v>829</v>
+        <v>862</v>
       </c>
       <c r="E16" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F16" t="s">
         <v>34</v>
@@ -4561,16 +4606,16 @@
         <v>54</v>
       </c>
       <c r="K16" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L16" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M16" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N16" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O16">
         <v>1</v>
@@ -4579,16 +4624,16 @@
         <v>38</v>
       </c>
       <c r="Q16">
-        <v>65.989999999999995</v>
-      </c>
-      <c r="S16">
-        <v>6.99</v>
+        <v>40.99</v>
+      </c>
+      <c r="R16">
+        <v>6.83</v>
       </c>
       <c r="Y16" t="s">
-        <v>830</v>
+        <v>305</v>
       </c>
       <c r="AA16" t="s">
-        <v>831</v>
+        <v>840</v>
       </c>
       <c r="AB16" t="s">
         <v>39</v>
@@ -4602,13 +4647,13 @@
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>832</v>
+        <v>841</v>
       </c>
       <c r="C17" t="s">
-        <v>833</v>
+        <v>842</v>
       </c>
       <c r="D17" t="s">
-        <v>834</v>
+        <v>863</v>
       </c>
       <c r="E17" t="s">
         <v>33</v>
@@ -4649,11 +4694,17 @@
       <c r="R17">
         <v>11</v>
       </c>
+      <c r="S17">
+        <v>6.99</v>
+      </c>
+      <c r="T17">
+        <v>1.17</v>
+      </c>
       <c r="Y17" t="s">
-        <v>835</v>
+        <v>844</v>
       </c>
       <c r="AA17" t="s">
-        <v>836</v>
+        <v>845</v>
       </c>
       <c r="AB17" t="s">
         <v>39</v>
@@ -4667,16 +4718,16 @@
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>780</v>
+        <v>837</v>
       </c>
       <c r="C18" t="s">
-        <v>781</v>
+        <v>838</v>
       </c>
       <c r="D18" t="s">
-        <v>782</v>
+        <v>839</v>
       </c>
       <c r="E18" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F18" t="s">
         <v>34</v>
@@ -4691,16 +4742,16 @@
         <v>54</v>
       </c>
       <c r="K18" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L18" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M18" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N18" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O18">
         <v>1</v>
@@ -4709,16 +4760,16 @@
         <v>38</v>
       </c>
       <c r="Q18">
-        <v>65.989999999999995</v>
+        <v>40.99</v>
       </c>
       <c r="R18">
-        <v>11</v>
+        <v>6.83</v>
       </c>
       <c r="Y18" t="s">
-        <v>783</v>
+        <v>305</v>
       </c>
       <c r="AA18" t="s">
-        <v>784</v>
+        <v>840</v>
       </c>
       <c r="AB18" t="s">
         <v>39</v>
@@ -4732,16 +4783,16 @@
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>785</v>
+        <v>841</v>
       </c>
       <c r="C19" t="s">
-        <v>786</v>
+        <v>842</v>
       </c>
       <c r="D19" t="s">
-        <v>787</v>
+        <v>843</v>
       </c>
       <c r="E19" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F19" t="s">
         <v>34</v>
@@ -4756,16 +4807,16 @@
         <v>54</v>
       </c>
       <c r="K19" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L19" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M19" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N19" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O19">
         <v>1</v>
@@ -4774,16 +4825,22 @@
         <v>38</v>
       </c>
       <c r="Q19">
-        <v>40.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R19">
-        <v>6.83</v>
+        <v>11</v>
+      </c>
+      <c r="S19">
+        <v>6.99</v>
+      </c>
+      <c r="T19">
+        <v>1.17</v>
       </c>
       <c r="Y19" t="s">
-        <v>788</v>
+        <v>844</v>
       </c>
       <c r="AA19" t="s">
-        <v>789</v>
+        <v>845</v>
       </c>
       <c r="AB19" t="s">
         <v>39</v>
@@ -4797,16 +4854,16 @@
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>790</v>
+        <v>819</v>
       </c>
       <c r="C20" t="s">
-        <v>791</v>
+        <v>820</v>
       </c>
       <c r="D20" t="s">
-        <v>792</v>
+        <v>821</v>
       </c>
       <c r="E20" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F20" t="s">
         <v>34</v>
@@ -4821,16 +4878,16 @@
         <v>54</v>
       </c>
       <c r="K20" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L20" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M20" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N20" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O20">
         <v>1</v>
@@ -4839,16 +4896,19 @@
         <v>38</v>
       </c>
       <c r="Q20">
-        <v>65.989999999999995</v>
+        <v>40.99</v>
       </c>
       <c r="R20">
-        <v>11</v>
+        <v>6.83</v>
       </c>
       <c r="Y20" t="s">
-        <v>793</v>
+        <v>618</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>619</v>
       </c>
       <c r="AA20" t="s">
-        <v>794</v>
+        <v>620</v>
       </c>
       <c r="AB20" t="s">
         <v>39</v>
@@ -4862,16 +4922,16 @@
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>795</v>
+        <v>822</v>
       </c>
       <c r="C21" t="s">
-        <v>796</v>
+        <v>823</v>
       </c>
       <c r="D21" t="s">
-        <v>797</v>
+        <v>824</v>
       </c>
       <c r="E21" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F21" t="s">
         <v>34</v>
@@ -4895,7 +4955,7 @@
         <v>74</v>
       </c>
       <c r="N21" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O21">
         <v>1</v>
@@ -4910,10 +4970,10 @@
         <v>2.5</v>
       </c>
       <c r="Y21" t="s">
-        <v>798</v>
+        <v>825</v>
       </c>
       <c r="AA21" t="s">
-        <v>799</v>
+        <v>826</v>
       </c>
       <c r="AB21" t="s">
         <v>39</v>
@@ -4927,16 +4987,16 @@
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>800</v>
+        <v>827</v>
       </c>
       <c r="C22" t="s">
-        <v>801</v>
+        <v>828</v>
       </c>
       <c r="D22" t="s">
-        <v>802</v>
+        <v>829</v>
       </c>
       <c r="E22" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F22" t="s">
         <v>34</v>
@@ -4951,16 +5011,16 @@
         <v>54</v>
       </c>
       <c r="K22" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L22" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M22" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N22" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O22">
         <v>1</v>
@@ -4969,16 +5029,16 @@
         <v>38</v>
       </c>
       <c r="Q22">
-        <v>14.99</v>
-      </c>
-      <c r="R22">
-        <v>2.5</v>
+        <v>65.989999999999995</v>
+      </c>
+      <c r="S22">
+        <v>6.99</v>
       </c>
       <c r="Y22" t="s">
-        <v>68</v>
+        <v>830</v>
       </c>
       <c r="AA22" t="s">
-        <v>803</v>
+        <v>831</v>
       </c>
       <c r="AB22" t="s">
         <v>39</v>
@@ -4992,13 +5052,13 @@
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>804</v>
+        <v>832</v>
       </c>
       <c r="C23" t="s">
-        <v>805</v>
+        <v>833</v>
       </c>
       <c r="D23" t="s">
-        <v>802</v>
+        <v>834</v>
       </c>
       <c r="E23" t="s">
         <v>33</v>
@@ -5016,13 +5076,13 @@
         <v>54</v>
       </c>
       <c r="K23" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L23" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M23" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N23" t="s">
         <v>33</v>
@@ -5034,16 +5094,16 @@
         <v>38</v>
       </c>
       <c r="Q23">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R23">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y23" t="s">
-        <v>806</v>
+        <v>835</v>
       </c>
       <c r="AA23" t="s">
-        <v>807</v>
+        <v>836</v>
       </c>
       <c r="AB23" t="s">
         <v>39</v>
@@ -5057,13 +5117,13 @@
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>808</v>
+        <v>780</v>
       </c>
       <c r="C24" t="s">
-        <v>809</v>
+        <v>781</v>
       </c>
       <c r="D24" t="s">
-        <v>810</v>
+        <v>782</v>
       </c>
       <c r="E24" t="s">
         <v>33</v>
@@ -5081,13 +5141,13 @@
         <v>54</v>
       </c>
       <c r="K24" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L24" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M24" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N24" t="s">
         <v>33</v>
@@ -5099,16 +5159,16 @@
         <v>38</v>
       </c>
       <c r="Q24">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R24">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y24" t="s">
-        <v>66</v>
+        <v>783</v>
       </c>
       <c r="AA24" t="s">
-        <v>811</v>
+        <v>784</v>
       </c>
       <c r="AB24" t="s">
         <v>39</v>
@@ -5122,13 +5182,13 @@
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>812</v>
+        <v>785</v>
       </c>
       <c r="C25" t="s">
-        <v>813</v>
+        <v>786</v>
       </c>
       <c r="D25" t="s">
-        <v>814</v>
+        <v>787</v>
       </c>
       <c r="E25" t="s">
         <v>33</v>
@@ -5146,13 +5206,13 @@
         <v>54</v>
       </c>
       <c r="K25" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="L25" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M25" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="N25" t="s">
         <v>33</v>
@@ -5170,10 +5230,10 @@
         <v>6.83</v>
       </c>
       <c r="Y25" t="s">
-        <v>815</v>
+        <v>788</v>
       </c>
       <c r="AA25" t="s">
-        <v>816</v>
+        <v>789</v>
       </c>
       <c r="AB25" t="s">
         <v>39</v>
@@ -5187,13 +5247,13 @@
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>745</v>
+        <v>790</v>
       </c>
       <c r="C26" t="s">
-        <v>746</v>
+        <v>791</v>
       </c>
       <c r="D26" t="s">
-        <v>817</v>
+        <v>792</v>
       </c>
       <c r="E26" t="s">
         <v>33</v>
@@ -5211,13 +5271,13 @@
         <v>54</v>
       </c>
       <c r="K26" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L26" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M26" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N26" t="s">
         <v>33</v>
@@ -5229,16 +5289,16 @@
         <v>38</v>
       </c>
       <c r="Q26">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R26">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y26" t="s">
-        <v>748</v>
+        <v>793</v>
       </c>
       <c r="AA26" t="s">
-        <v>749</v>
+        <v>794</v>
       </c>
       <c r="AB26" t="s">
         <v>39</v>
@@ -5252,13 +5312,13 @@
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>750</v>
+        <v>795</v>
       </c>
       <c r="C27" t="s">
-        <v>751</v>
+        <v>796</v>
       </c>
       <c r="D27" t="s">
-        <v>752</v>
+        <v>797</v>
       </c>
       <c r="E27" t="s">
         <v>33</v>
@@ -5276,13 +5336,13 @@
         <v>54</v>
       </c>
       <c r="K27" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L27" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M27" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N27" t="s">
         <v>33</v>
@@ -5294,16 +5354,16 @@
         <v>38</v>
       </c>
       <c r="Q27">
-        <v>65.989999999999995</v>
+        <v>14.99</v>
       </c>
       <c r="R27">
-        <v>11</v>
+        <v>2.5</v>
       </c>
       <c r="Y27" t="s">
-        <v>753</v>
+        <v>798</v>
       </c>
       <c r="AA27" t="s">
-        <v>754</v>
+        <v>799</v>
       </c>
       <c r="AB27" t="s">
         <v>39</v>
@@ -5317,13 +5377,13 @@
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>755</v>
+        <v>800</v>
       </c>
       <c r="C28" t="s">
-        <v>756</v>
+        <v>801</v>
       </c>
       <c r="D28" t="s">
-        <v>818</v>
+        <v>802</v>
       </c>
       <c r="E28" t="s">
         <v>33</v>
@@ -5341,13 +5401,13 @@
         <v>54</v>
       </c>
       <c r="K28" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L28" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M28" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N28" t="s">
         <v>33</v>
@@ -5359,25 +5419,16 @@
         <v>38</v>
       </c>
       <c r="Q28">
-        <v>65.989999999999995</v>
+        <v>14.99</v>
       </c>
       <c r="R28">
-        <v>11</v>
-      </c>
-      <c r="S28">
-        <v>6.99</v>
-      </c>
-      <c r="T28">
-        <v>1.17</v>
+        <v>2.5</v>
       </c>
       <c r="Y28" t="s">
-        <v>758</v>
-      </c>
-      <c r="Z28" t="s">
-        <v>759</v>
+        <v>68</v>
       </c>
       <c r="AA28" t="s">
-        <v>760</v>
+        <v>803</v>
       </c>
       <c r="AB28" t="s">
         <v>39</v>
@@ -5391,13 +5442,13 @@
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>761</v>
+        <v>804</v>
       </c>
       <c r="C29" t="s">
-        <v>762</v>
+        <v>805</v>
       </c>
       <c r="D29" t="s">
-        <v>763</v>
+        <v>802</v>
       </c>
       <c r="E29" t="s">
         <v>33</v>
@@ -5439,13 +5490,10 @@
         <v>2</v>
       </c>
       <c r="Y29" t="s">
-        <v>764</v>
-      </c>
-      <c r="Z29" t="s">
-        <v>279</v>
+        <v>806</v>
       </c>
       <c r="AA29" t="s">
-        <v>765</v>
+        <v>807</v>
       </c>
       <c r="AB29" t="s">
         <v>39</v>
@@ -5459,13 +5507,13 @@
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>766</v>
+        <v>808</v>
       </c>
       <c r="C30" t="s">
-        <v>767</v>
+        <v>809</v>
       </c>
       <c r="D30" t="s">
-        <v>768</v>
+        <v>810</v>
       </c>
       <c r="E30" t="s">
         <v>33</v>
@@ -5507,13 +5555,10 @@
         <v>2</v>
       </c>
       <c r="Y30" t="s">
-        <v>91</v>
-      </c>
-      <c r="Z30" t="s">
-        <v>121</v>
+        <v>66</v>
       </c>
       <c r="AA30" t="s">
-        <v>769</v>
+        <v>811</v>
       </c>
       <c r="AB30" t="s">
         <v>39</v>
@@ -5527,13 +5572,13 @@
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>770</v>
+        <v>812</v>
       </c>
       <c r="C31" t="s">
-        <v>771</v>
+        <v>813</v>
       </c>
       <c r="D31" t="s">
-        <v>772</v>
+        <v>814</v>
       </c>
       <c r="E31" t="s">
         <v>33</v>
@@ -5551,13 +5596,13 @@
         <v>54</v>
       </c>
       <c r="K31" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L31" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M31" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N31" t="s">
         <v>33</v>
@@ -5569,19 +5614,16 @@
         <v>38</v>
       </c>
       <c r="Q31">
-        <v>65.989999999999995</v>
+        <v>40.99</v>
       </c>
       <c r="R31">
-        <v>11</v>
+        <v>6.83</v>
       </c>
       <c r="Y31" t="s">
-        <v>773</v>
-      </c>
-      <c r="Z31" t="s">
-        <v>64</v>
+        <v>815</v>
       </c>
       <c r="AA31" t="s">
-        <v>774</v>
+        <v>816</v>
       </c>
       <c r="AB31" t="s">
         <v>39</v>
@@ -5595,13 +5637,13 @@
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>775</v>
+        <v>745</v>
       </c>
       <c r="C32" t="s">
-        <v>776</v>
+        <v>746</v>
       </c>
       <c r="D32" t="s">
-        <v>777</v>
+        <v>817</v>
       </c>
       <c r="E32" t="s">
         <v>33</v>
@@ -5619,13 +5661,13 @@
         <v>54</v>
       </c>
       <c r="K32" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L32" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M32" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N32" t="s">
         <v>33</v>
@@ -5637,16 +5679,16 @@
         <v>38</v>
       </c>
       <c r="Q32">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R32">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y32" t="s">
-        <v>778</v>
+        <v>748</v>
       </c>
       <c r="AA32" t="s">
-        <v>779</v>
+        <v>749</v>
       </c>
       <c r="AB32" t="s">
         <v>39</v>
@@ -5660,16 +5702,16 @@
     </row>
     <row r="33" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="C33" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="D33" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="E33" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F33" t="s">
         <v>34</v>
@@ -5684,16 +5726,16 @@
         <v>54</v>
       </c>
       <c r="K33" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L33" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M33" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N33" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O33">
         <v>1</v>
@@ -5702,16 +5744,16 @@
         <v>38</v>
       </c>
       <c r="Q33">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R33">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y33" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="AA33" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="AB33" t="s">
         <v>39</v>
@@ -5725,13 +5767,13 @@
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="C34" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="D34" t="s">
-        <v>752</v>
+        <v>818</v>
       </c>
       <c r="E34" t="s">
         <v>33</v>
@@ -5772,11 +5814,20 @@
       <c r="R34">
         <v>11</v>
       </c>
+      <c r="S34">
+        <v>6.99</v>
+      </c>
+      <c r="T34">
+        <v>1.17</v>
+      </c>
       <c r="Y34" t="s">
-        <v>753</v>
+        <v>758</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>759</v>
       </c>
       <c r="AA34" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
       <c r="AB34" t="s">
         <v>39</v>
@@ -5790,16 +5841,16 @@
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="C35" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="D35" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
       <c r="E35" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F35" t="s">
         <v>34</v>
@@ -5814,16 +5865,16 @@
         <v>54</v>
       </c>
       <c r="K35" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L35" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M35" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N35" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O35">
         <v>1</v>
@@ -5832,25 +5883,19 @@
         <v>38</v>
       </c>
       <c r="Q35">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R35">
-        <v>11</v>
-      </c>
-      <c r="S35">
-        <v>6.99</v>
-      </c>
-      <c r="T35">
-        <v>1.17</v>
+        <v>2</v>
       </c>
       <c r="Y35" t="s">
-        <v>758</v>
+        <v>764</v>
       </c>
       <c r="Z35" t="s">
-        <v>759</v>
+        <v>279</v>
       </c>
       <c r="AA35" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="AB35" t="s">
         <v>39</v>
@@ -5864,13 +5909,13 @@
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="C36" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="D36" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="E36" t="s">
         <v>33</v>
@@ -5912,13 +5957,13 @@
         <v>2</v>
       </c>
       <c r="Y36" t="s">
-        <v>764</v>
+        <v>91</v>
       </c>
       <c r="Z36" t="s">
-        <v>279</v>
+        <v>121</v>
       </c>
       <c r="AA36" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="AB36" t="s">
         <v>39</v>
@@ -5932,13 +5977,13 @@
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="C37" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="D37" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="E37" t="s">
         <v>33</v>
@@ -5956,13 +6001,13 @@
         <v>54</v>
       </c>
       <c r="K37" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L37" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M37" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N37" t="s">
         <v>33</v>
@@ -5974,19 +6019,19 @@
         <v>38</v>
       </c>
       <c r="Q37">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R37">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y37" t="s">
-        <v>91</v>
+        <v>773</v>
       </c>
       <c r="Z37" t="s">
-        <v>121</v>
+        <v>64</v>
       </c>
       <c r="AA37" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="AB37" t="s">
         <v>39</v>
@@ -6000,13 +6045,13 @@
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="C38" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="D38" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="E38" t="s">
         <v>33</v>
@@ -6048,13 +6093,10 @@
         <v>11</v>
       </c>
       <c r="Y38" t="s">
-        <v>773</v>
-      </c>
-      <c r="Z38" t="s">
-        <v>64</v>
+        <v>778</v>
       </c>
       <c r="AA38" t="s">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="AB38" t="s">
         <v>39</v>
@@ -6068,16 +6110,16 @@
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>775</v>
+        <v>745</v>
       </c>
       <c r="C39" t="s">
-        <v>776</v>
+        <v>746</v>
       </c>
       <c r="D39" t="s">
-        <v>777</v>
+        <v>747</v>
       </c>
       <c r="E39" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F39" t="s">
         <v>34</v>
@@ -6092,16 +6134,16 @@
         <v>54</v>
       </c>
       <c r="K39" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L39" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M39" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N39" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O39">
         <v>1</v>
@@ -6110,16 +6152,16 @@
         <v>38</v>
       </c>
       <c r="Q39">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R39">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y39" t="s">
-        <v>778</v>
+        <v>748</v>
       </c>
       <c r="AA39" t="s">
-        <v>779</v>
+        <v>749</v>
       </c>
       <c r="AB39" t="s">
         <v>39</v>
@@ -6133,16 +6175,16 @@
     </row>
     <row r="40" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>714</v>
+        <v>750</v>
       </c>
       <c r="C40" t="s">
-        <v>715</v>
+        <v>751</v>
       </c>
       <c r="D40" t="s">
-        <v>716</v>
+        <v>752</v>
       </c>
       <c r="E40" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F40" t="s">
         <v>34</v>
@@ -6157,16 +6199,16 @@
         <v>54</v>
       </c>
       <c r="K40" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L40" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M40" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N40" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O40">
         <v>1</v>
@@ -6175,19 +6217,16 @@
         <v>38</v>
       </c>
       <c r="Q40">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R40">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y40" t="s">
-        <v>717</v>
-      </c>
-      <c r="Z40" t="s">
-        <v>51</v>
+        <v>753</v>
       </c>
       <c r="AA40" t="s">
-        <v>718</v>
+        <v>754</v>
       </c>
       <c r="AB40" t="s">
         <v>39</v>
@@ -6201,16 +6240,16 @@
     </row>
     <row r="41" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>719</v>
+        <v>755</v>
       </c>
       <c r="C41" t="s">
-        <v>720</v>
+        <v>756</v>
       </c>
       <c r="D41" t="s">
-        <v>721</v>
+        <v>757</v>
       </c>
       <c r="E41" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F41" t="s">
         <v>34</v>
@@ -6225,16 +6264,16 @@
         <v>54</v>
       </c>
       <c r="K41" t="s">
-        <v>722</v>
+        <v>40</v>
       </c>
       <c r="L41" t="s">
-        <v>723</v>
+        <v>41</v>
       </c>
       <c r="M41" t="s">
-        <v>724</v>
+        <v>42</v>
       </c>
       <c r="N41" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O41">
         <v>1</v>
@@ -6243,19 +6282,25 @@
         <v>38</v>
       </c>
       <c r="Q41">
-        <v>12.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R41">
-        <v>2.17</v>
+        <v>11</v>
+      </c>
+      <c r="S41">
+        <v>6.99</v>
+      </c>
+      <c r="T41">
+        <v>1.17</v>
       </c>
       <c r="Y41" t="s">
-        <v>725</v>
+        <v>758</v>
       </c>
       <c r="Z41" t="s">
-        <v>726</v>
+        <v>759</v>
       </c>
       <c r="AA41" t="s">
-        <v>727</v>
+        <v>760</v>
       </c>
       <c r="AB41" t="s">
         <v>39</v>
@@ -6269,13 +6314,13 @@
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>728</v>
+        <v>761</v>
       </c>
       <c r="C42" t="s">
-        <v>729</v>
+        <v>762</v>
       </c>
       <c r="D42" t="s">
-        <v>730</v>
+        <v>763</v>
       </c>
       <c r="E42" t="s">
         <v>33</v>
@@ -6317,10 +6362,13 @@
         <v>2</v>
       </c>
       <c r="Y42" t="s">
-        <v>731</v>
+        <v>764</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>279</v>
       </c>
       <c r="AA42" t="s">
-        <v>732</v>
+        <v>765</v>
       </c>
       <c r="AB42" t="s">
         <v>39</v>
@@ -6334,13 +6382,13 @@
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>733</v>
+        <v>766</v>
       </c>
       <c r="C43" t="s">
-        <v>734</v>
+        <v>767</v>
       </c>
       <c r="D43" t="s">
-        <v>735</v>
+        <v>768</v>
       </c>
       <c r="E43" t="s">
         <v>33</v>
@@ -6358,13 +6406,13 @@
         <v>54</v>
       </c>
       <c r="K43" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="L43" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="M43" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="N43" t="s">
         <v>33</v>
@@ -6376,16 +6424,19 @@
         <v>38</v>
       </c>
       <c r="Q43">
-        <v>40.99</v>
+        <v>11.99</v>
       </c>
       <c r="R43">
-        <v>6.83</v>
+        <v>2</v>
       </c>
       <c r="Y43" t="s">
-        <v>736</v>
+        <v>91</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>121</v>
       </c>
       <c r="AA43" t="s">
-        <v>737</v>
+        <v>769</v>
       </c>
       <c r="AB43" t="s">
         <v>39</v>
@@ -6399,13 +6450,13 @@
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>738</v>
+        <v>770</v>
       </c>
       <c r="C44" t="s">
-        <v>739</v>
+        <v>771</v>
       </c>
       <c r="D44" t="s">
-        <v>740</v>
+        <v>772</v>
       </c>
       <c r="E44" t="s">
         <v>33</v>
@@ -6423,13 +6474,13 @@
         <v>54</v>
       </c>
       <c r="K44" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L44" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M44" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N44" t="s">
         <v>33</v>
@@ -6441,16 +6492,19 @@
         <v>38</v>
       </c>
       <c r="Q44">
-        <v>40.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R44">
-        <v>6.83</v>
+        <v>11</v>
       </c>
       <c r="Y44" t="s">
-        <v>741</v>
+        <v>773</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>64</v>
       </c>
       <c r="AA44" t="s">
-        <v>742</v>
+        <v>774</v>
       </c>
       <c r="AB44" t="s">
         <v>39</v>
@@ -6464,13 +6518,13 @@
     </row>
     <row r="45" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>708</v>
+        <v>775</v>
       </c>
       <c r="C45" t="s">
-        <v>709</v>
+        <v>776</v>
       </c>
       <c r="D45" t="s">
-        <v>743</v>
+        <v>777</v>
       </c>
       <c r="E45" t="s">
         <v>33</v>
@@ -6512,13 +6566,10 @@
         <v>11</v>
       </c>
       <c r="Y45" t="s">
-        <v>711</v>
-      </c>
-      <c r="Z45" t="s">
-        <v>712</v>
+        <v>778</v>
       </c>
       <c r="AA45" t="s">
-        <v>713</v>
+        <v>779</v>
       </c>
       <c r="AB45" t="s">
         <v>39</v>
@@ -6532,16 +6583,16 @@
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>643</v>
+        <v>714</v>
       </c>
       <c r="C46" t="s">
-        <v>644</v>
+        <v>715</v>
       </c>
       <c r="D46" t="s">
-        <v>744</v>
+        <v>716</v>
       </c>
       <c r="E46" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F46" t="s">
         <v>34</v>
@@ -6556,16 +6607,16 @@
         <v>54</v>
       </c>
       <c r="K46" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L46" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M46" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="N46" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O46">
         <v>1</v>
@@ -6574,16 +6625,19 @@
         <v>38</v>
       </c>
       <c r="Q46">
-        <v>14.99</v>
+        <v>11.99</v>
       </c>
       <c r="R46">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Y46" t="s">
-        <v>646</v>
+        <v>717</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>51</v>
       </c>
       <c r="AA46" t="s">
-        <v>647</v>
+        <v>718</v>
       </c>
       <c r="AB46" t="s">
         <v>39</v>
@@ -6597,16 +6651,16 @@
     </row>
     <row r="47" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>708</v>
+        <v>719</v>
       </c>
       <c r="C47" t="s">
-        <v>709</v>
+        <v>720</v>
       </c>
       <c r="D47" t="s">
-        <v>710</v>
+        <v>721</v>
       </c>
       <c r="E47" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F47" t="s">
         <v>34</v>
@@ -6621,16 +6675,16 @@
         <v>54</v>
       </c>
       <c r="K47" t="s">
-        <v>40</v>
+        <v>722</v>
       </c>
       <c r="L47" t="s">
-        <v>41</v>
+        <v>723</v>
       </c>
       <c r="M47" t="s">
-        <v>42</v>
+        <v>724</v>
       </c>
       <c r="N47" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O47">
         <v>1</v>
@@ -6639,19 +6693,19 @@
         <v>38</v>
       </c>
       <c r="Q47">
-        <v>65.989999999999995</v>
+        <v>12.99</v>
       </c>
       <c r="R47">
-        <v>11</v>
+        <v>2.17</v>
       </c>
       <c r="Y47" t="s">
-        <v>711</v>
+        <v>725</v>
       </c>
       <c r="Z47" t="s">
-        <v>712</v>
+        <v>726</v>
       </c>
       <c r="AA47" t="s">
-        <v>713</v>
+        <v>727</v>
       </c>
       <c r="AB47" t="s">
         <v>39</v>
@@ -6665,22 +6719,22 @@
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>138</v>
+        <v>728</v>
       </c>
       <c r="C48" t="s">
-        <v>139</v>
+        <v>729</v>
       </c>
       <c r="D48" t="s">
-        <v>187</v>
+        <v>730</v>
       </c>
       <c r="E48" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F48" t="s">
         <v>34</v>
       </c>
       <c r="G48" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="H48" t="s">
         <v>36</v>
@@ -6689,25 +6743,37 @@
         <v>54</v>
       </c>
       <c r="K48" t="s">
-        <v>141</v>
+        <v>72</v>
       </c>
       <c r="L48" t="s">
-        <v>142</v>
+        <v>73</v>
       </c>
       <c r="M48" t="s">
-        <v>143</v>
+        <v>74</v>
+      </c>
+      <c r="N48" t="s">
+        <v>33</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P48" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q48">
+        <v>11.99</v>
+      </c>
+      <c r="R48">
+        <v>2</v>
       </c>
       <c r="Y48" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA48">
-        <v>80100</v>
+        <v>731</v>
+      </c>
+      <c r="AA48" t="s">
+        <v>732</v>
       </c>
       <c r="AB48" t="s">
-        <v>145</v>
+        <v>39</v>
       </c>
       <c r="AD48" t="b">
         <v>0</v>
@@ -6718,22 +6784,22 @@
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>146</v>
+        <v>733</v>
       </c>
       <c r="C49" t="s">
-        <v>147</v>
+        <v>734</v>
       </c>
       <c r="D49" t="s">
-        <v>148</v>
+        <v>735</v>
       </c>
       <c r="E49" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F49" t="s">
         <v>34</v>
       </c>
       <c r="G49" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="H49" t="s">
         <v>36</v>
@@ -6742,25 +6808,37 @@
         <v>54</v>
       </c>
       <c r="K49" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="L49" t="s">
-        <v>142</v>
+        <v>44</v>
       </c>
       <c r="M49" t="s">
-        <v>143</v>
+        <v>45</v>
+      </c>
+      <c r="N49" t="s">
+        <v>33</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P49" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q49">
+        <v>40.99</v>
+      </c>
+      <c r="R49">
+        <v>6.83</v>
       </c>
       <c r="Y49" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA49">
-        <v>80100</v>
+        <v>736</v>
+      </c>
+      <c r="AA49" t="s">
+        <v>737</v>
       </c>
       <c r="AB49" t="s">
-        <v>145</v>
+        <v>39</v>
       </c>
       <c r="AD49" t="b">
         <v>0</v>
@@ -6771,22 +6849,22 @@
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>632</v>
+        <v>738</v>
       </c>
       <c r="C50" t="s">
-        <v>633</v>
+        <v>739</v>
       </c>
       <c r="D50" t="s">
-        <v>634</v>
+        <v>740</v>
       </c>
       <c r="E50" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F50" t="s">
         <v>34</v>
       </c>
       <c r="G50" t="s">
-        <v>635</v>
+        <v>35</v>
       </c>
       <c r="H50" t="s">
         <v>36</v>
@@ -6795,37 +6873,37 @@
         <v>54</v>
       </c>
       <c r="K50" t="s">
-        <v>636</v>
+        <v>48</v>
       </c>
       <c r="L50" t="s">
-        <v>637</v>
+        <v>49</v>
       </c>
       <c r="M50" t="s">
-        <v>638</v>
+        <v>50</v>
+      </c>
+      <c r="N50" t="s">
+        <v>33</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="Q50">
-        <v>22.9</v>
+        <v>40.99</v>
       </c>
       <c r="R50">
-        <v>4.8099999999999996</v>
+        <v>6.83</v>
       </c>
       <c r="Y50" t="s">
-        <v>639</v>
-      </c>
-      <c r="Z50" t="s">
-        <v>640</v>
+        <v>741</v>
       </c>
       <c r="AA50" t="s">
-        <v>641</v>
+        <v>742</v>
       </c>
       <c r="AB50" t="s">
-        <v>642</v>
+        <v>39</v>
       </c>
       <c r="AD50" t="b">
         <v>0</v>
@@ -6836,16 +6914,16 @@
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>643</v>
+        <v>708</v>
       </c>
       <c r="C51" t="s">
-        <v>644</v>
+        <v>709</v>
       </c>
       <c r="D51" t="s">
-        <v>645</v>
+        <v>743</v>
       </c>
       <c r="E51" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F51" t="s">
         <v>34</v>
@@ -6860,16 +6938,16 @@
         <v>54</v>
       </c>
       <c r="K51" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L51" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M51" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="N51" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O51">
         <v>1</v>
@@ -6878,16 +6956,19 @@
         <v>38</v>
       </c>
       <c r="Q51">
-        <v>14.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R51">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="Y51" t="s">
-        <v>646</v>
+        <v>711</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>712</v>
       </c>
       <c r="AA51" t="s">
-        <v>647</v>
+        <v>713</v>
       </c>
       <c r="AB51" t="s">
         <v>39</v>
@@ -6901,13 +6982,13 @@
     </row>
     <row r="52" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>609</v>
+        <v>643</v>
       </c>
       <c r="C52" t="s">
-        <v>610</v>
+        <v>644</v>
       </c>
       <c r="D52" t="s">
-        <v>611</v>
+        <v>744</v>
       </c>
       <c r="E52" t="s">
         <v>33</v>
@@ -6949,13 +7030,10 @@
         <v>2.5</v>
       </c>
       <c r="Y52" t="s">
-        <v>612</v>
-      </c>
-      <c r="Z52" t="s">
-        <v>613</v>
+        <v>646</v>
       </c>
       <c r="AA52" t="s">
-        <v>614</v>
+        <v>647</v>
       </c>
       <c r="AB52" t="s">
         <v>39</v>
@@ -6969,16 +7047,16 @@
     </row>
     <row r="53" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>493</v>
+        <v>708</v>
       </c>
       <c r="C53" t="s">
-        <v>494</v>
+        <v>709</v>
       </c>
       <c r="D53" t="s">
-        <v>648</v>
+        <v>710</v>
       </c>
       <c r="E53" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="F53" t="s">
         <v>34</v>
@@ -7001,14 +7079,29 @@
       <c r="M53" t="s">
         <v>42</v>
       </c>
+      <c r="N53" t="s">
+        <v>99</v>
+      </c>
       <c r="O53">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P53" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q53">
+        <v>65.989999999999995</v>
+      </c>
+      <c r="R53">
+        <v>11</v>
       </c>
       <c r="Y53" t="s">
-        <v>495</v>
+        <v>711</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>712</v>
       </c>
       <c r="AA53" t="s">
-        <v>496</v>
+        <v>713</v>
       </c>
       <c r="AB53" t="s">
         <v>39</v>
@@ -7022,22 +7115,22 @@
     </row>
     <row r="54" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>615</v>
+        <v>138</v>
       </c>
       <c r="C54" t="s">
-        <v>616</v>
+        <v>139</v>
       </c>
       <c r="D54" t="s">
-        <v>617</v>
+        <v>187</v>
       </c>
       <c r="E54" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="F54" t="s">
         <v>34</v>
       </c>
       <c r="G54" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="H54" t="s">
         <v>36</v>
@@ -7046,37 +7139,25 @@
         <v>54</v>
       </c>
       <c r="K54" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="L54" t="s">
-        <v>49</v>
+        <v>142</v>
       </c>
       <c r="M54" t="s">
-        <v>50</v>
-      </c>
-      <c r="N54" t="s">
-        <v>99</v>
+        <v>143</v>
       </c>
       <c r="O54">
-        <v>1</v>
-      </c>
-      <c r="P54" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q54">
-        <v>40.99</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="s">
-        <v>618</v>
-      </c>
-      <c r="Z54" t="s">
-        <v>619</v>
-      </c>
-      <c r="AA54" t="s">
-        <v>620</v>
+        <v>144</v>
+      </c>
+      <c r="AA54">
+        <v>80100</v>
       </c>
       <c r="AB54" t="s">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="AD54" t="b">
         <v>0</v>
@@ -7087,22 +7168,22 @@
     </row>
     <row r="55" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>621</v>
+        <v>146</v>
       </c>
       <c r="C55" t="s">
-        <v>622</v>
+        <v>147</v>
       </c>
       <c r="D55" t="s">
-        <v>623</v>
+        <v>148</v>
       </c>
       <c r="E55" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F55" t="s">
         <v>34</v>
       </c>
       <c r="G55" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="H55" t="s">
         <v>36</v>
@@ -7111,46 +7192,25 @@
         <v>54</v>
       </c>
       <c r="K55" t="s">
-        <v>40</v>
+        <v>141</v>
       </c>
       <c r="L55" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="M55" t="s">
-        <v>42</v>
-      </c>
-      <c r="N55" t="s">
-        <v>33</v>
+        <v>143</v>
       </c>
       <c r="O55">
-        <v>1</v>
-      </c>
-      <c r="P55" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q55">
-        <v>64.989999999999995</v>
-      </c>
-      <c r="R55">
-        <v>10.83</v>
-      </c>
-      <c r="S55">
-        <v>6.99</v>
-      </c>
-      <c r="T55">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="s">
-        <v>624</v>
-      </c>
-      <c r="Z55" t="s">
-        <v>625</v>
-      </c>
-      <c r="AA55" t="s">
-        <v>626</v>
+        <v>144</v>
+      </c>
+      <c r="AA55">
+        <v>80100</v>
       </c>
       <c r="AB55" t="s">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="AD55" t="b">
         <v>0</v>
@@ -7161,22 +7221,22 @@
     </row>
     <row r="56" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="C56" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="D56" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="E56" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F56" t="s">
         <v>34</v>
       </c>
       <c r="G56" t="s">
-        <v>35</v>
+        <v>635</v>
       </c>
       <c r="H56" t="s">
         <v>36</v>
@@ -7185,37 +7245,37 @@
         <v>54</v>
       </c>
       <c r="K56" t="s">
-        <v>72</v>
+        <v>636</v>
       </c>
       <c r="L56" t="s">
-        <v>73</v>
+        <v>637</v>
       </c>
       <c r="M56" t="s">
-        <v>74</v>
-      </c>
-      <c r="N56" t="s">
-        <v>33</v>
+        <v>638</v>
       </c>
       <c r="O56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P56" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="Q56">
-        <v>11.99</v>
+        <v>22.9</v>
       </c>
       <c r="R56">
-        <v>2</v>
+        <v>4.8099999999999996</v>
       </c>
       <c r="Y56" t="s">
-        <v>630</v>
+        <v>639</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>640</v>
       </c>
       <c r="AA56" t="s">
-        <v>631</v>
+        <v>641</v>
       </c>
       <c r="AB56" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="AD56" t="b">
         <v>0</v>
@@ -7226,16 +7286,16 @@
     </row>
     <row r="57" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="C57" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="D57" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="E57" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F57" t="s">
         <v>34</v>
@@ -7250,16 +7310,16 @@
         <v>54</v>
       </c>
       <c r="K57" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="L57" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="M57" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="N57" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O57">
         <v>1</v>
@@ -7268,19 +7328,16 @@
         <v>38</v>
       </c>
       <c r="Q57">
-        <v>39.99</v>
+        <v>14.99</v>
       </c>
       <c r="R57">
-        <v>6.67</v>
+        <v>2.5</v>
       </c>
       <c r="Y57" t="s">
-        <v>652</v>
-      </c>
-      <c r="Z57" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="AA57" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="AB57" t="s">
         <v>39</v>
@@ -7294,13 +7351,13 @@
     </row>
     <row r="58" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>655</v>
+        <v>609</v>
       </c>
       <c r="C58" t="s">
-        <v>656</v>
+        <v>610</v>
       </c>
       <c r="D58" t="s">
-        <v>657</v>
+        <v>611</v>
       </c>
       <c r="E58" t="s">
         <v>33</v>
@@ -7342,10 +7399,13 @@
         <v>2.5</v>
       </c>
       <c r="Y58" t="s">
-        <v>658</v>
+        <v>612</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>613</v>
       </c>
       <c r="AA58" t="s">
-        <v>659</v>
+        <v>614</v>
       </c>
       <c r="AB58" t="s">
         <v>39</v>
@@ -7359,16 +7419,16 @@
     </row>
     <row r="59" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>571</v>
+        <v>493</v>
       </c>
       <c r="C59" t="s">
-        <v>572</v>
+        <v>494</v>
       </c>
       <c r="D59" t="s">
-        <v>660</v>
+        <v>648</v>
       </c>
       <c r="E59" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F59" t="s">
         <v>34</v>
@@ -7391,26 +7451,14 @@
       <c r="M59" t="s">
         <v>42</v>
       </c>
-      <c r="N59" t="s">
-        <v>33</v>
-      </c>
       <c r="O59">
-        <v>1</v>
-      </c>
-      <c r="P59" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q59">
-        <v>64.989999999999995</v>
-      </c>
-      <c r="R59">
-        <v>10.83</v>
+        <v>0</v>
       </c>
       <c r="Y59" t="s">
-        <v>573</v>
+        <v>495</v>
       </c>
       <c r="AA59" t="s">
-        <v>574</v>
+        <v>496</v>
       </c>
       <c r="AB59" t="s">
         <v>39</v>
@@ -7424,16 +7472,16 @@
     </row>
     <row r="60" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>599</v>
+        <v>615</v>
       </c>
       <c r="C60" t="s">
-        <v>600</v>
+        <v>616</v>
       </c>
       <c r="D60" t="s">
-        <v>601</v>
+        <v>617</v>
       </c>
       <c r="E60" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F60" t="s">
         <v>34</v>
@@ -7448,16 +7496,16 @@
         <v>54</v>
       </c>
       <c r="K60" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="L60" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="M60" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="N60" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O60">
         <v>1</v>
@@ -7466,16 +7514,16 @@
         <v>38</v>
       </c>
       <c r="Q60">
-        <v>14.99</v>
-      </c>
-      <c r="R60">
-        <v>2.5</v>
+        <v>40.99</v>
       </c>
       <c r="Y60" t="s">
-        <v>61</v>
+        <v>618</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>619</v>
       </c>
       <c r="AA60" t="s">
-        <v>602</v>
+        <v>620</v>
       </c>
       <c r="AB60" t="s">
         <v>39</v>
@@ -7489,13 +7537,13 @@
     </row>
     <row r="61" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>589</v>
+        <v>621</v>
       </c>
       <c r="C61" t="s">
-        <v>590</v>
+        <v>622</v>
       </c>
       <c r="D61" t="s">
-        <v>591</v>
+        <v>623</v>
       </c>
       <c r="E61" t="s">
         <v>33</v>
@@ -7536,11 +7584,20 @@
       <c r="R61">
         <v>10.83</v>
       </c>
+      <c r="S61">
+        <v>6.99</v>
+      </c>
+      <c r="T61">
+        <v>1.17</v>
+      </c>
       <c r="Y61" t="s">
-        <v>592</v>
+        <v>624</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>625</v>
       </c>
       <c r="AA61" t="s">
-        <v>593</v>
+        <v>626</v>
       </c>
       <c r="AB61" t="s">
         <v>39</v>
@@ -7554,13 +7611,13 @@
     </row>
     <row r="62" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>594</v>
+        <v>627</v>
       </c>
       <c r="C62" t="s">
-        <v>595</v>
+        <v>628</v>
       </c>
       <c r="D62" t="s">
-        <v>596</v>
+        <v>629</v>
       </c>
       <c r="E62" t="s">
         <v>33</v>
@@ -7578,13 +7635,13 @@
         <v>54</v>
       </c>
       <c r="K62" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L62" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M62" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N62" t="s">
         <v>33</v>
@@ -7596,16 +7653,16 @@
         <v>38</v>
       </c>
       <c r="Q62">
-        <v>64.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R62">
-        <v>10.83</v>
+        <v>2</v>
       </c>
       <c r="Y62" t="s">
-        <v>597</v>
+        <v>630</v>
       </c>
       <c r="AA62" t="s">
-        <v>598</v>
+        <v>631</v>
       </c>
       <c r="AB62" t="s">
         <v>39</v>
@@ -7619,13 +7676,13 @@
     </row>
     <row r="63" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>603</v>
+        <v>649</v>
       </c>
       <c r="C63" t="s">
-        <v>604</v>
+        <v>650</v>
       </c>
       <c r="D63" t="s">
-        <v>605</v>
+        <v>651</v>
       </c>
       <c r="E63" t="s">
         <v>33</v>
@@ -7643,13 +7700,13 @@
         <v>54</v>
       </c>
       <c r="K63" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L63" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M63" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N63" t="s">
         <v>33</v>
@@ -7661,19 +7718,19 @@
         <v>38</v>
       </c>
       <c r="Q63">
-        <v>64.989999999999995</v>
+        <v>39.99</v>
       </c>
       <c r="R63">
-        <v>10.83</v>
+        <v>6.67</v>
       </c>
       <c r="Y63" t="s">
-        <v>606</v>
+        <v>652</v>
       </c>
       <c r="Z63" t="s">
-        <v>607</v>
+        <v>653</v>
       </c>
       <c r="AA63" t="s">
-        <v>608</v>
+        <v>654</v>
       </c>
       <c r="AB63" t="s">
         <v>39</v>
@@ -7687,13 +7744,13 @@
     </row>
     <row r="64" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>578</v>
+        <v>655</v>
       </c>
       <c r="C64" t="s">
-        <v>579</v>
+        <v>656</v>
       </c>
       <c r="D64" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="E64" t="s">
         <v>33</v>
@@ -7711,13 +7768,13 @@
         <v>54</v>
       </c>
       <c r="K64" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L64" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M64" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="N64" t="s">
         <v>33</v>
@@ -7729,19 +7786,16 @@
         <v>38</v>
       </c>
       <c r="Q64">
-        <v>64.989999999999995</v>
+        <v>14.99</v>
       </c>
       <c r="R64">
-        <v>10.83</v>
+        <v>2.5</v>
       </c>
       <c r="Y64" t="s">
-        <v>580</v>
-      </c>
-      <c r="Z64" t="s">
-        <v>581</v>
+        <v>658</v>
       </c>
       <c r="AA64" t="s">
-        <v>582</v>
+        <v>659</v>
       </c>
       <c r="AB64" t="s">
         <v>39</v>
@@ -7755,16 +7809,16 @@
     </row>
     <row r="65" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="C65" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="D65" t="s">
-        <v>577</v>
+        <v>660</v>
       </c>
       <c r="E65" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F65" t="s">
         <v>34</v>
@@ -7787,8 +7841,20 @@
       <c r="M65" t="s">
         <v>42</v>
       </c>
+      <c r="N65" t="s">
+        <v>33</v>
+      </c>
       <c r="O65">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P65" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q65">
+        <v>64.989999999999995</v>
+      </c>
+      <c r="R65">
+        <v>10.83</v>
       </c>
       <c r="Y65" t="s">
         <v>573</v>
@@ -7808,13 +7874,13 @@
     </row>
     <row r="66" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>518</v>
+        <v>599</v>
       </c>
       <c r="C66" t="s">
-        <v>519</v>
+        <v>600</v>
       </c>
       <c r="D66" t="s">
-        <v>583</v>
+        <v>601</v>
       </c>
       <c r="E66" t="s">
         <v>33</v>
@@ -7832,13 +7898,13 @@
         <v>54</v>
       </c>
       <c r="K66" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="L66" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="M66" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="N66" t="s">
         <v>33</v>
@@ -7850,22 +7916,16 @@
         <v>38</v>
       </c>
       <c r="Q66">
-        <v>37.99</v>
+        <v>14.99</v>
       </c>
       <c r="R66">
-        <v>6.33</v>
-      </c>
-      <c r="S66">
-        <v>6.99</v>
-      </c>
-      <c r="T66">
-        <v>1.17</v>
+        <v>2.5</v>
       </c>
       <c r="Y66" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="AA66" t="s">
-        <v>520</v>
+        <v>602</v>
       </c>
       <c r="AB66" t="s">
         <v>39</v>
@@ -7879,13 +7939,13 @@
     </row>
     <row r="67" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="C67" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="D67" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="E67" t="s">
         <v>33</v>
@@ -7927,10 +7987,10 @@
         <v>10.83</v>
       </c>
       <c r="Y67" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="AA67" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="AB67" t="s">
         <v>39</v>
@@ -7944,13 +8004,13 @@
     </row>
     <row r="68" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>457</v>
+        <v>594</v>
       </c>
       <c r="C68" t="s">
-        <v>458</v>
+        <v>595</v>
       </c>
       <c r="D68" t="s">
-        <v>459</v>
+        <v>596</v>
       </c>
       <c r="E68" t="s">
         <v>33</v>
@@ -7992,13 +8052,10 @@
         <v>10.83</v>
       </c>
       <c r="Y68" t="s">
-        <v>460</v>
-      </c>
-      <c r="Z68" t="s">
-        <v>279</v>
+        <v>597</v>
       </c>
       <c r="AA68" t="s">
-        <v>461</v>
+        <v>598</v>
       </c>
       <c r="AB68" t="s">
         <v>39</v>
@@ -8012,13 +8069,13 @@
     </row>
     <row r="69" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>462</v>
+        <v>603</v>
       </c>
       <c r="C69" t="s">
-        <v>463</v>
+        <v>604</v>
       </c>
       <c r="D69" t="s">
-        <v>459</v>
+        <v>605</v>
       </c>
       <c r="E69" t="s">
         <v>33</v>
@@ -8060,10 +8117,13 @@
         <v>10.83</v>
       </c>
       <c r="Y69" t="s">
-        <v>56</v>
+        <v>606</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>607</v>
       </c>
       <c r="AA69" t="s">
-        <v>464</v>
+        <v>608</v>
       </c>
       <c r="AB69" t="s">
         <v>39</v>
@@ -8077,13 +8137,13 @@
     </row>
     <row r="70" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>465</v>
+        <v>578</v>
       </c>
       <c r="C70" t="s">
-        <v>466</v>
+        <v>579</v>
       </c>
       <c r="D70" t="s">
-        <v>467</v>
+        <v>661</v>
       </c>
       <c r="E70" t="s">
         <v>33</v>
@@ -8101,34 +8161,37 @@
         <v>54</v>
       </c>
       <c r="K70" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L70" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M70" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N70" t="s">
         <v>33</v>
       </c>
       <c r="O70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P70" t="s">
         <v>38</v>
       </c>
       <c r="Q70">
-        <v>79.98</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R70">
-        <v>13.34</v>
+        <v>10.83</v>
       </c>
       <c r="Y70" t="s">
-        <v>468</v>
+        <v>580</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>581</v>
       </c>
       <c r="AA70" t="s">
-        <v>469</v>
+        <v>582</v>
       </c>
       <c r="AB70" t="s">
         <v>39</v>
@@ -8142,16 +8205,16 @@
     </row>
     <row r="71" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>470</v>
+        <v>575</v>
       </c>
       <c r="C71" t="s">
-        <v>471</v>
+        <v>576</v>
       </c>
       <c r="D71" t="s">
-        <v>472</v>
+        <v>577</v>
       </c>
       <c r="E71" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F71" t="s">
         <v>34</v>
@@ -8166,34 +8229,22 @@
         <v>54</v>
       </c>
       <c r="K71" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L71" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M71" t="s">
-        <v>50</v>
-      </c>
-      <c r="N71" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O71">
-        <v>1</v>
-      </c>
-      <c r="P71" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q71">
-        <v>37.99</v>
-      </c>
-      <c r="R71">
-        <v>6.33</v>
+        <v>0</v>
       </c>
       <c r="Y71" t="s">
-        <v>473</v>
+        <v>573</v>
       </c>
       <c r="AA71" t="s">
-        <v>474</v>
+        <v>574</v>
       </c>
       <c r="AB71" t="s">
         <v>39</v>
@@ -8207,16 +8258,16 @@
     </row>
     <row r="72" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>475</v>
+        <v>518</v>
       </c>
       <c r="C72" t="s">
-        <v>476</v>
+        <v>519</v>
       </c>
       <c r="D72" t="s">
-        <v>477</v>
+        <v>583</v>
       </c>
       <c r="E72" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F72" t="s">
         <v>34</v>
@@ -8231,25 +8282,40 @@
         <v>54</v>
       </c>
       <c r="K72" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L72" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M72" t="s">
-        <v>42</v>
+        <v>50</v>
+      </c>
+      <c r="N72" t="s">
+        <v>33</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P72" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q72">
+        <v>37.99</v>
+      </c>
+      <c r="R72">
+        <v>6.33</v>
+      </c>
+      <c r="S72">
+        <v>6.99</v>
+      </c>
+      <c r="T72">
+        <v>1.17</v>
       </c>
       <c r="Y72" t="s">
-        <v>478</v>
-      </c>
-      <c r="Z72" t="s">
-        <v>279</v>
+        <v>46</v>
       </c>
       <c r="AA72" t="s">
-        <v>479</v>
+        <v>520</v>
       </c>
       <c r="AB72" t="s">
         <v>39</v>
@@ -8263,13 +8329,13 @@
     </row>
     <row r="73" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>480</v>
+        <v>584</v>
       </c>
       <c r="C73" t="s">
-        <v>481</v>
+        <v>585</v>
       </c>
       <c r="D73" t="s">
-        <v>482</v>
+        <v>586</v>
       </c>
       <c r="E73" t="s">
         <v>33</v>
@@ -8287,13 +8353,13 @@
         <v>54</v>
       </c>
       <c r="K73" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L73" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M73" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N73" t="s">
         <v>33</v>
@@ -8305,16 +8371,16 @@
         <v>38</v>
       </c>
       <c r="Q73">
-        <v>11.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R73">
-        <v>2</v>
+        <v>10.83</v>
       </c>
       <c r="Y73" t="s">
-        <v>61</v>
+        <v>587</v>
       </c>
       <c r="AA73" t="s">
-        <v>483</v>
+        <v>588</v>
       </c>
       <c r="AB73" t="s">
         <v>39</v>
@@ -8328,13 +8394,13 @@
     </row>
     <row r="74" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>484</v>
+        <v>457</v>
       </c>
       <c r="C74" t="s">
-        <v>485</v>
+        <v>458</v>
       </c>
       <c r="D74" t="s">
-        <v>486</v>
+        <v>459</v>
       </c>
       <c r="E74" t="s">
         <v>33</v>
@@ -8376,10 +8442,13 @@
         <v>10.83</v>
       </c>
       <c r="Y74" t="s">
-        <v>67</v>
+        <v>460</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>279</v>
       </c>
       <c r="AA74" t="s">
-        <v>487</v>
+        <v>461</v>
       </c>
       <c r="AB74" t="s">
         <v>39</v>
@@ -8393,13 +8462,13 @@
     </row>
     <row r="75" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>488</v>
+        <v>462</v>
       </c>
       <c r="C75" t="s">
-        <v>489</v>
+        <v>463</v>
       </c>
       <c r="D75" t="s">
-        <v>490</v>
+        <v>459</v>
       </c>
       <c r="E75" t="s">
         <v>33</v>
@@ -8417,37 +8486,34 @@
         <v>54</v>
       </c>
       <c r="K75" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L75" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M75" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N75" t="s">
         <v>33</v>
       </c>
       <c r="O75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P75" t="s">
         <v>38</v>
       </c>
       <c r="Q75">
-        <v>79.98</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R75">
-        <v>13.34</v>
+        <v>10.83</v>
       </c>
       <c r="Y75" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z75" t="s">
-        <v>491</v>
+        <v>56</v>
       </c>
       <c r="AA75" t="s">
-        <v>492</v>
+        <v>464</v>
       </c>
       <c r="AB75" t="s">
         <v>39</v>
@@ -8461,13 +8527,13 @@
     </row>
     <row r="76" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>497</v>
+        <v>465</v>
       </c>
       <c r="C76" t="s">
-        <v>498</v>
+        <v>466</v>
       </c>
       <c r="D76" t="s">
-        <v>499</v>
+        <v>467</v>
       </c>
       <c r="E76" t="s">
         <v>33</v>
@@ -8485,37 +8551,34 @@
         <v>54</v>
       </c>
       <c r="K76" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L76" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M76" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N76" t="s">
         <v>33</v>
       </c>
       <c r="O76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P76" t="s">
         <v>38</v>
       </c>
       <c r="Q76">
-        <v>59.99</v>
+        <v>79.98</v>
       </c>
       <c r="R76">
-        <v>10</v>
+        <v>13.34</v>
       </c>
       <c r="Y76" t="s">
-        <v>500</v>
-      </c>
-      <c r="Z76" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="AA76" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="AB76" t="s">
         <v>39</v>
@@ -8529,13 +8592,13 @@
     </row>
     <row r="77" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="C77" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="D77" t="s">
-        <v>499</v>
+        <v>472</v>
       </c>
       <c r="E77" t="s">
         <v>33</v>
@@ -8553,13 +8616,13 @@
         <v>54</v>
       </c>
       <c r="K77" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L77" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M77" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N77" t="s">
         <v>33</v>
@@ -8571,19 +8634,16 @@
         <v>38</v>
       </c>
       <c r="Q77">
-        <v>59.99</v>
+        <v>37.99</v>
       </c>
       <c r="R77">
-        <v>10</v>
+        <v>6.33</v>
       </c>
       <c r="Y77" t="s">
-        <v>505</v>
-      </c>
-      <c r="Z77" t="s">
-        <v>93</v>
+        <v>473</v>
       </c>
       <c r="AA77" t="s">
-        <v>506</v>
+        <v>474</v>
       </c>
       <c r="AB77" t="s">
         <v>39</v>
@@ -8597,16 +8657,16 @@
     </row>
     <row r="78" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>507</v>
+        <v>475</v>
       </c>
       <c r="C78" t="s">
-        <v>508</v>
+        <v>476</v>
       </c>
       <c r="D78" t="s">
-        <v>509</v>
+        <v>477</v>
       </c>
       <c r="E78" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F78" t="s">
         <v>34</v>
@@ -8629,26 +8689,17 @@
       <c r="M78" t="s">
         <v>42</v>
       </c>
-      <c r="N78" t="s">
-        <v>33</v>
-      </c>
       <c r="O78">
-        <v>1</v>
-      </c>
-      <c r="P78" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q78">
-        <v>59.99</v>
-      </c>
-      <c r="R78">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y78" t="s">
-        <v>510</v>
+        <v>478</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>279</v>
       </c>
       <c r="AA78" t="s">
-        <v>511</v>
+        <v>479</v>
       </c>
       <c r="AB78" t="s">
         <v>39</v>
@@ -8662,13 +8713,13 @@
     </row>
     <row r="79" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>512</v>
+        <v>480</v>
       </c>
       <c r="C79" t="s">
-        <v>513</v>
+        <v>481</v>
       </c>
       <c r="D79" t="s">
-        <v>514</v>
+        <v>482</v>
       </c>
       <c r="E79" t="s">
         <v>33</v>
@@ -8686,13 +8737,13 @@
         <v>54</v>
       </c>
       <c r="K79" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L79" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M79" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N79" t="s">
         <v>33</v>
@@ -8704,19 +8755,16 @@
         <v>38</v>
       </c>
       <c r="Q79">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R79">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y79" t="s">
-        <v>515</v>
-      </c>
-      <c r="Z79" t="s">
-        <v>516</v>
+        <v>61</v>
       </c>
       <c r="AA79" t="s">
-        <v>517</v>
+        <v>483</v>
       </c>
       <c r="AB79" t="s">
         <v>39</v>
@@ -8730,13 +8778,13 @@
     </row>
     <row r="80" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>521</v>
+        <v>484</v>
       </c>
       <c r="C80" t="s">
-        <v>522</v>
+        <v>485</v>
       </c>
       <c r="D80" t="s">
-        <v>523</v>
+        <v>486</v>
       </c>
       <c r="E80" t="s">
         <v>33</v>
@@ -8754,13 +8802,13 @@
         <v>54</v>
       </c>
       <c r="K80" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L80" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M80" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="N80" t="s">
         <v>33</v>
@@ -8772,16 +8820,16 @@
         <v>38</v>
       </c>
       <c r="Q80">
-        <v>14.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R80">
-        <v>2.5</v>
+        <v>10.83</v>
       </c>
       <c r="Y80" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="AA80" t="s">
-        <v>524</v>
+        <v>487</v>
       </c>
       <c r="AB80" t="s">
         <v>39</v>
@@ -8795,13 +8843,13 @@
     </row>
     <row r="81" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>525</v>
+        <v>488</v>
       </c>
       <c r="C81" t="s">
-        <v>526</v>
+        <v>489</v>
       </c>
       <c r="D81" t="s">
-        <v>527</v>
+        <v>490</v>
       </c>
       <c r="E81" t="s">
         <v>33</v>
@@ -8819,34 +8867,37 @@
         <v>54</v>
       </c>
       <c r="K81" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L81" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M81" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N81" t="s">
         <v>33</v>
       </c>
       <c r="O81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P81" t="s">
         <v>38</v>
       </c>
       <c r="Q81">
-        <v>59.99</v>
+        <v>79.98</v>
       </c>
       <c r="R81">
-        <v>10</v>
+        <v>13.34</v>
       </c>
       <c r="Y81" t="s">
-        <v>90</v>
+        <v>63</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>491</v>
       </c>
       <c r="AA81" t="s">
-        <v>528</v>
+        <v>492</v>
       </c>
       <c r="AB81" t="s">
         <v>39</v>
@@ -8860,13 +8911,13 @@
     </row>
     <row r="82" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>529</v>
+        <v>497</v>
       </c>
       <c r="C82" t="s">
-        <v>530</v>
+        <v>498</v>
       </c>
       <c r="D82" t="s">
-        <v>527</v>
+        <v>499</v>
       </c>
       <c r="E82" t="s">
         <v>33</v>
@@ -8908,10 +8959,13 @@
         <v>10</v>
       </c>
       <c r="Y82" t="s">
-        <v>531</v>
+        <v>500</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>501</v>
       </c>
       <c r="AA82" t="s">
-        <v>532</v>
+        <v>502</v>
       </c>
       <c r="AB82" t="s">
         <v>39</v>
@@ -8925,13 +8979,13 @@
     </row>
     <row r="83" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>533</v>
+        <v>503</v>
       </c>
       <c r="C83" t="s">
-        <v>534</v>
+        <v>504</v>
       </c>
       <c r="D83" t="s">
-        <v>535</v>
+        <v>499</v>
       </c>
       <c r="E83" t="s">
         <v>33</v>
@@ -8949,13 +9003,13 @@
         <v>54</v>
       </c>
       <c r="K83" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L83" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M83" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N83" t="s">
         <v>33</v>
@@ -8967,19 +9021,19 @@
         <v>38</v>
       </c>
       <c r="Q83">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R83">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y83" t="s">
-        <v>536</v>
+        <v>505</v>
       </c>
       <c r="Z83" t="s">
-        <v>537</v>
+        <v>93</v>
       </c>
       <c r="AA83" t="s">
-        <v>538</v>
+        <v>506</v>
       </c>
       <c r="AB83" t="s">
         <v>39</v>
@@ -8993,13 +9047,13 @@
     </row>
     <row r="84" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>539</v>
+        <v>507</v>
       </c>
       <c r="C84" t="s">
-        <v>540</v>
+        <v>508</v>
       </c>
       <c r="D84" t="s">
-        <v>541</v>
+        <v>509</v>
       </c>
       <c r="E84" t="s">
         <v>33</v>
@@ -9041,13 +9095,10 @@
         <v>10</v>
       </c>
       <c r="Y84" t="s">
-        <v>71</v>
-      </c>
-      <c r="Z84" t="s">
-        <v>542</v>
+        <v>510</v>
       </c>
       <c r="AA84" t="s">
-        <v>543</v>
+        <v>511</v>
       </c>
       <c r="AB84" t="s">
         <v>39</v>
@@ -9061,13 +9112,13 @@
     </row>
     <row r="85" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>544</v>
+        <v>512</v>
       </c>
       <c r="C85" t="s">
-        <v>545</v>
+        <v>513</v>
       </c>
       <c r="D85" t="s">
-        <v>546</v>
+        <v>514</v>
       </c>
       <c r="E85" t="s">
         <v>33</v>
@@ -9085,37 +9136,37 @@
         <v>54</v>
       </c>
       <c r="K85" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L85" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M85" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N85" t="s">
         <v>33</v>
       </c>
       <c r="O85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P85" t="s">
         <v>38</v>
       </c>
       <c r="Q85">
-        <v>76.98</v>
+        <v>59.99</v>
       </c>
       <c r="R85">
-        <v>12.84</v>
+        <v>10</v>
       </c>
       <c r="Y85" t="s">
-        <v>547</v>
+        <v>515</v>
       </c>
       <c r="Z85" t="s">
-        <v>548</v>
+        <v>516</v>
       </c>
       <c r="AA85" t="s">
-        <v>549</v>
+        <v>517</v>
       </c>
       <c r="AB85" t="s">
         <v>39</v>
@@ -9129,13 +9180,13 @@
     </row>
     <row r="86" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>550</v>
+        <v>521</v>
       </c>
       <c r="C86" t="s">
-        <v>551</v>
+        <v>522</v>
       </c>
       <c r="D86" t="s">
-        <v>552</v>
+        <v>523</v>
       </c>
       <c r="E86" t="s">
         <v>33</v>
@@ -9153,13 +9204,13 @@
         <v>54</v>
       </c>
       <c r="K86" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L86" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M86" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="N86" t="s">
         <v>33</v>
@@ -9171,16 +9222,16 @@
         <v>38</v>
       </c>
       <c r="Q86">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="R86">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="Y86" t="s">
-        <v>553</v>
+        <v>58</v>
       </c>
       <c r="AA86" t="s">
-        <v>554</v>
+        <v>524</v>
       </c>
       <c r="AB86" t="s">
         <v>39</v>
@@ -9194,13 +9245,13 @@
     </row>
     <row r="87" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>555</v>
+        <v>525</v>
       </c>
       <c r="C87" t="s">
-        <v>556</v>
+        <v>526</v>
       </c>
       <c r="D87" t="s">
-        <v>557</v>
+        <v>527</v>
       </c>
       <c r="E87" t="s">
         <v>33</v>
@@ -9242,10 +9293,10 @@
         <v>10</v>
       </c>
       <c r="Y87" t="s">
-        <v>558</v>
+        <v>90</v>
       </c>
       <c r="AA87" t="s">
-        <v>559</v>
+        <v>528</v>
       </c>
       <c r="AB87" t="s">
         <v>39</v>
@@ -9259,13 +9310,13 @@
     </row>
     <row r="88" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>418</v>
+        <v>529</v>
       </c>
       <c r="C88" t="s">
-        <v>419</v>
+        <v>530</v>
       </c>
       <c r="D88" t="s">
-        <v>560</v>
+        <v>527</v>
       </c>
       <c r="E88" t="s">
         <v>33</v>
@@ -9307,10 +9358,10 @@
         <v>10</v>
       </c>
       <c r="Y88" t="s">
-        <v>420</v>
+        <v>531</v>
       </c>
       <c r="AA88" t="s">
-        <v>421</v>
+        <v>532</v>
       </c>
       <c r="AB88" t="s">
         <v>39</v>
@@ -9324,13 +9375,13 @@
     </row>
     <row r="89" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>561</v>
+        <v>533</v>
       </c>
       <c r="C89" t="s">
-        <v>562</v>
+        <v>534</v>
       </c>
       <c r="D89" t="s">
-        <v>563</v>
+        <v>535</v>
       </c>
       <c r="E89" t="s">
         <v>33</v>
@@ -9348,13 +9399,13 @@
         <v>54</v>
       </c>
       <c r="K89" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L89" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M89" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N89" t="s">
         <v>33</v>
@@ -9366,19 +9417,19 @@
         <v>38</v>
       </c>
       <c r="Q89">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R89">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y89" t="s">
-        <v>564</v>
+        <v>536</v>
       </c>
       <c r="Z89" t="s">
-        <v>565</v>
+        <v>537</v>
       </c>
       <c r="AA89" t="s">
-        <v>566</v>
+        <v>538</v>
       </c>
       <c r="AB89" t="s">
         <v>39</v>
@@ -9392,13 +9443,13 @@
     </row>
     <row r="90" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>567</v>
+        <v>539</v>
       </c>
       <c r="C90" t="s">
-        <v>568</v>
+        <v>540</v>
       </c>
       <c r="D90" t="s">
-        <v>569</v>
+        <v>541</v>
       </c>
       <c r="E90" t="s">
         <v>33</v>
@@ -9416,13 +9467,13 @@
         <v>54</v>
       </c>
       <c r="K90" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L90" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M90" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="N90" t="s">
         <v>33</v>
@@ -9434,16 +9485,19 @@
         <v>38</v>
       </c>
       <c r="Q90">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R90">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y90" t="s">
-        <v>69</v>
+        <v>71</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>542</v>
       </c>
       <c r="AA90" t="s">
-        <v>570</v>
+        <v>543</v>
       </c>
       <c r="AB90" t="s">
         <v>39</v>
@@ -9457,13 +9511,13 @@
     </row>
     <row r="91" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>413</v>
+        <v>544</v>
       </c>
       <c r="C91" t="s">
-        <v>414</v>
+        <v>545</v>
       </c>
       <c r="D91" t="s">
-        <v>415</v>
+        <v>546</v>
       </c>
       <c r="E91" t="s">
         <v>33</v>
@@ -9481,34 +9535,37 @@
         <v>54</v>
       </c>
       <c r="K91" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L91" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M91" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N91" t="s">
         <v>33</v>
       </c>
       <c r="O91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P91" t="s">
         <v>38</v>
       </c>
       <c r="Q91">
-        <v>59.99</v>
+        <v>76.98</v>
       </c>
       <c r="R91">
-        <v>10</v>
+        <v>12.84</v>
       </c>
       <c r="Y91" t="s">
-        <v>416</v>
+        <v>547</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>548</v>
       </c>
       <c r="AA91" t="s">
-        <v>417</v>
+        <v>549</v>
       </c>
       <c r="AB91" t="s">
         <v>39</v>
@@ -9522,13 +9579,13 @@
     </row>
     <row r="92" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>422</v>
+        <v>550</v>
       </c>
       <c r="C92" t="s">
-        <v>423</v>
+        <v>551</v>
       </c>
       <c r="D92" t="s">
-        <v>424</v>
+        <v>552</v>
       </c>
       <c r="E92" t="s">
         <v>33</v>
@@ -9546,13 +9603,13 @@
         <v>54</v>
       </c>
       <c r="K92" t="s">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="L92" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="M92" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="N92" t="s">
         <v>33</v>
@@ -9564,16 +9621,16 @@
         <v>38</v>
       </c>
       <c r="Q92">
-        <v>22.99</v>
+        <v>59.99</v>
       </c>
       <c r="R92">
-        <v>3.83</v>
+        <v>10</v>
       </c>
       <c r="Y92" t="s">
-        <v>425</v>
+        <v>553</v>
       </c>
       <c r="AA92" t="s">
-        <v>426</v>
+        <v>554</v>
       </c>
       <c r="AB92" t="s">
         <v>39</v>
@@ -9587,13 +9644,13 @@
     </row>
     <row r="93" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>427</v>
+        <v>555</v>
       </c>
       <c r="C93" t="s">
-        <v>428</v>
+        <v>556</v>
       </c>
       <c r="D93" t="s">
-        <v>424</v>
+        <v>557</v>
       </c>
       <c r="E93" t="s">
         <v>33</v>
@@ -9611,13 +9668,13 @@
         <v>54</v>
       </c>
       <c r="K93" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L93" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M93" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N93" t="s">
         <v>33</v>
@@ -9629,19 +9686,16 @@
         <v>38</v>
       </c>
       <c r="Q93">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R93">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y93" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z93" t="s">
-        <v>97</v>
+        <v>558</v>
       </c>
       <c r="AA93" t="s">
-        <v>429</v>
+        <v>559</v>
       </c>
       <c r="AB93" t="s">
         <v>39</v>
@@ -9655,13 +9709,13 @@
     </row>
     <row r="94" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="C94" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="D94" t="s">
-        <v>432</v>
+        <v>560</v>
       </c>
       <c r="E94" t="s">
         <v>33</v>
@@ -9679,13 +9733,13 @@
         <v>54</v>
       </c>
       <c r="K94" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L94" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M94" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N94" t="s">
         <v>33</v>
@@ -9697,19 +9751,16 @@
         <v>38</v>
       </c>
       <c r="Q94">
-        <v>38.49</v>
+        <v>59.99</v>
       </c>
       <c r="R94">
-        <v>6.42</v>
+        <v>10</v>
       </c>
       <c r="Y94" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z94" t="s">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="AA94" t="s">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="AB94" t="s">
         <v>39</v>
@@ -9723,13 +9774,13 @@
     </row>
     <row r="95" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>435</v>
+        <v>561</v>
       </c>
       <c r="C95" t="s">
-        <v>436</v>
+        <v>562</v>
       </c>
       <c r="D95" t="s">
-        <v>437</v>
+        <v>563</v>
       </c>
       <c r="E95" t="s">
         <v>33</v>
@@ -9747,13 +9798,13 @@
         <v>54</v>
       </c>
       <c r="K95" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="L95" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="M95" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="N95" t="s">
         <v>33</v>
@@ -9765,16 +9816,19 @@
         <v>38</v>
       </c>
       <c r="Q95">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R95">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y95" t="s">
-        <v>438</v>
+        <v>564</v>
+      </c>
+      <c r="Z95" t="s">
+        <v>565</v>
       </c>
       <c r="AA95" t="s">
-        <v>439</v>
+        <v>566</v>
       </c>
       <c r="AB95" t="s">
         <v>39</v>
@@ -9788,13 +9842,13 @@
     </row>
     <row r="96" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>440</v>
+        <v>567</v>
       </c>
       <c r="C96" t="s">
-        <v>441</v>
+        <v>568</v>
       </c>
       <c r="D96" t="s">
-        <v>442</v>
+        <v>569</v>
       </c>
       <c r="E96" t="s">
         <v>33</v>
@@ -9812,13 +9866,13 @@
         <v>54</v>
       </c>
       <c r="K96" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="L96" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="M96" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="N96" t="s">
         <v>33</v>
@@ -9830,16 +9884,16 @@
         <v>38</v>
       </c>
       <c r="Q96">
-        <v>37.99</v>
+        <v>14.99</v>
       </c>
       <c r="R96">
-        <v>6.33</v>
+        <v>2.5</v>
       </c>
       <c r="Y96" t="s">
-        <v>443</v>
+        <v>69</v>
       </c>
       <c r="AA96" t="s">
-        <v>444</v>
+        <v>570</v>
       </c>
       <c r="AB96" t="s">
         <v>39</v>
@@ -9853,13 +9907,13 @@
     </row>
     <row r="97" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>445</v>
+        <v>413</v>
       </c>
       <c r="C97" t="s">
-        <v>446</v>
+        <v>414</v>
       </c>
       <c r="D97" t="s">
-        <v>447</v>
+        <v>415</v>
       </c>
       <c r="E97" t="s">
         <v>33</v>
@@ -9901,10 +9955,10 @@
         <v>10</v>
       </c>
       <c r="Y97" t="s">
-        <v>448</v>
+        <v>416</v>
       </c>
       <c r="AA97" t="s">
-        <v>449</v>
+        <v>417</v>
       </c>
       <c r="AB97" t="s">
         <v>39</v>
@@ -9918,16 +9972,16 @@
     </row>
     <row r="98" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>450</v>
+        <v>422</v>
       </c>
       <c r="C98" t="s">
-        <v>451</v>
+        <v>423</v>
       </c>
       <c r="D98" t="s">
-        <v>452</v>
+        <v>424</v>
       </c>
       <c r="E98" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F98" t="s">
         <v>34</v>
@@ -9942,22 +9996,34 @@
         <v>54</v>
       </c>
       <c r="K98" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="L98" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="M98" t="s">
-        <v>42</v>
+        <v>81</v>
+      </c>
+      <c r="N98" t="s">
+        <v>33</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P98" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q98">
+        <v>22.99</v>
+      </c>
+      <c r="R98">
+        <v>3.83</v>
       </c>
       <c r="Y98" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="AA98" t="s">
-        <v>454</v>
+        <v>426</v>
       </c>
       <c r="AB98" t="s">
         <v>39</v>
@@ -9971,13 +10037,13 @@
     </row>
     <row r="99" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>403</v>
+        <v>427</v>
       </c>
       <c r="C99" t="s">
-        <v>404</v>
+        <v>428</v>
       </c>
       <c r="D99" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="E99" t="s">
         <v>33</v>
@@ -9995,13 +10061,13 @@
         <v>54</v>
       </c>
       <c r="K99" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L99" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M99" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N99" t="s">
         <v>33</v>
@@ -10013,22 +10079,19 @@
         <v>38</v>
       </c>
       <c r="Q99">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R99">
-        <v>10</v>
-      </c>
-      <c r="S99">
-        <v>5.99</v>
-      </c>
-      <c r="T99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y99" t="s">
-        <v>405</v>
+        <v>96</v>
+      </c>
+      <c r="Z99" t="s">
+        <v>97</v>
       </c>
       <c r="AA99" t="s">
-        <v>406</v>
+        <v>429</v>
       </c>
       <c r="AB99" t="s">
         <v>39</v>
@@ -10042,13 +10105,13 @@
     </row>
     <row r="100" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>407</v>
+        <v>430</v>
       </c>
       <c r="C100" t="s">
-        <v>408</v>
+        <v>431</v>
       </c>
       <c r="D100" t="s">
-        <v>456</v>
+        <v>432</v>
       </c>
       <c r="E100" t="s">
         <v>33</v>
@@ -10066,13 +10129,13 @@
         <v>54</v>
       </c>
       <c r="K100" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="L100" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="M100" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="N100" t="s">
         <v>33</v>
@@ -10084,16 +10147,19 @@
         <v>38</v>
       </c>
       <c r="Q100">
-        <v>22.99</v>
+        <v>38.49</v>
       </c>
       <c r="R100">
-        <v>3.83</v>
+        <v>6.42</v>
       </c>
       <c r="Y100" t="s">
-        <v>409</v>
+        <v>59</v>
+      </c>
+      <c r="Z100" t="s">
+        <v>433</v>
       </c>
       <c r="AA100" t="s">
-        <v>410</v>
+        <v>434</v>
       </c>
       <c r="AB100" t="s">
         <v>39</v>
@@ -10107,13 +10173,13 @@
     </row>
     <row r="101" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>399</v>
+        <v>435</v>
       </c>
       <c r="C101" t="s">
-        <v>400</v>
+        <v>436</v>
       </c>
       <c r="D101" t="s">
-        <v>411</v>
+        <v>437</v>
       </c>
       <c r="E101" t="s">
         <v>33</v>
@@ -10131,13 +10197,13 @@
         <v>54</v>
       </c>
       <c r="K101" t="s">
-        <v>340</v>
+        <v>95</v>
       </c>
       <c r="L101" t="s">
-        <v>142</v>
+        <v>85</v>
       </c>
       <c r="M101" t="s">
-        <v>143</v>
+        <v>86</v>
       </c>
       <c r="N101" t="s">
         <v>33</v>
@@ -10149,16 +10215,16 @@
         <v>38</v>
       </c>
       <c r="Q101">
-        <v>44.99</v>
+        <v>14.99</v>
       </c>
       <c r="R101">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="Y101" t="s">
-        <v>401</v>
+        <v>438</v>
       </c>
       <c r="AA101" t="s">
-        <v>402</v>
+        <v>439</v>
       </c>
       <c r="AB101" t="s">
         <v>39</v>
@@ -10172,13 +10238,13 @@
     </row>
     <row r="102" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>394</v>
+        <v>440</v>
       </c>
       <c r="C102" t="s">
-        <v>395</v>
+        <v>441</v>
       </c>
       <c r="D102" t="s">
-        <v>412</v>
+        <v>442</v>
       </c>
       <c r="E102" t="s">
         <v>33</v>
@@ -10196,13 +10262,13 @@
         <v>54</v>
       </c>
       <c r="K102" t="s">
-        <v>340</v>
+        <v>48</v>
       </c>
       <c r="L102" t="s">
-        <v>142</v>
+        <v>49</v>
       </c>
       <c r="M102" t="s">
-        <v>143</v>
+        <v>50</v>
       </c>
       <c r="N102" t="s">
         <v>33</v>
@@ -10214,19 +10280,16 @@
         <v>38</v>
       </c>
       <c r="Q102">
-        <v>44.99</v>
+        <v>37.99</v>
       </c>
       <c r="R102">
-        <v>7.5</v>
+        <v>6.33</v>
       </c>
       <c r="Y102" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z102" t="s">
-        <v>397</v>
+        <v>443</v>
       </c>
       <c r="AA102" t="s">
-        <v>398</v>
+        <v>444</v>
       </c>
       <c r="AB102" t="s">
         <v>39</v>
@@ -10240,13 +10303,13 @@
     </row>
     <row r="103" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>338</v>
+        <v>445</v>
       </c>
       <c r="C103" t="s">
-        <v>339</v>
+        <v>446</v>
       </c>
       <c r="D103" t="s">
-        <v>662</v>
+        <v>447</v>
       </c>
       <c r="E103" t="s">
         <v>33</v>
@@ -10264,13 +10327,13 @@
         <v>54</v>
       </c>
       <c r="K103" t="s">
-        <v>340</v>
+        <v>40</v>
       </c>
       <c r="L103" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="M103" t="s">
-        <v>143</v>
+        <v>42</v>
       </c>
       <c r="N103" t="s">
         <v>33</v>
@@ -10282,16 +10345,16 @@
         <v>38</v>
       </c>
       <c r="Q103">
-        <v>44.99</v>
+        <v>59.99</v>
       </c>
       <c r="R103">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="Y103" t="s">
-        <v>341</v>
+        <v>448</v>
       </c>
       <c r="AA103" t="s">
-        <v>342</v>
+        <v>449</v>
       </c>
       <c r="AB103" t="s">
         <v>39</v>
@@ -10305,16 +10368,16 @@
     </row>
     <row r="104" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>663</v>
+        <v>450</v>
       </c>
       <c r="C104" t="s">
-        <v>664</v>
+        <v>451</v>
       </c>
       <c r="D104" t="s">
-        <v>665</v>
+        <v>452</v>
       </c>
       <c r="E104" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F104" t="s">
         <v>34</v>
@@ -10337,35 +10400,20 @@
       <c r="M104" t="s">
         <v>42</v>
       </c>
-      <c r="N104" t="s">
-        <v>33</v>
-      </c>
       <c r="O104">
-        <v>1</v>
-      </c>
-      <c r="P104" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q104">
-        <v>59.99</v>
-      </c>
-      <c r="R104">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y104" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z104" t="s">
-        <v>666</v>
+        <v>453</v>
       </c>
       <c r="AA104" t="s">
-        <v>667</v>
+        <v>454</v>
       </c>
       <c r="AB104" t="s">
         <v>39</v>
       </c>
       <c r="AD104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG104" t="b">
         <v>0</v>
@@ -10373,13 +10421,13 @@
     </row>
     <row r="105" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>334</v>
+        <v>403</v>
       </c>
       <c r="C105" t="s">
-        <v>335</v>
+        <v>404</v>
       </c>
       <c r="D105" t="s">
-        <v>668</v>
+        <v>455</v>
       </c>
       <c r="E105" t="s">
         <v>33</v>
@@ -10397,13 +10445,13 @@
         <v>54</v>
       </c>
       <c r="K105" t="s">
-        <v>203</v>
+        <v>40</v>
       </c>
       <c r="L105" t="s">
-        <v>204</v>
+        <v>41</v>
       </c>
       <c r="M105" t="s">
-        <v>205</v>
+        <v>42</v>
       </c>
       <c r="N105" t="s">
         <v>33</v>
@@ -10415,16 +10463,22 @@
         <v>38</v>
       </c>
       <c r="Q105">
-        <v>69.989999999999995</v>
+        <v>59.99</v>
       </c>
       <c r="R105">
-        <v>11.67</v>
+        <v>10</v>
+      </c>
+      <c r="S105">
+        <v>5.99</v>
+      </c>
+      <c r="T105">
+        <v>1</v>
       </c>
       <c r="Y105" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="AA105" t="s">
-        <v>337</v>
+        <v>406</v>
       </c>
       <c r="AB105" t="s">
         <v>39</v>
@@ -10438,13 +10492,13 @@
     </row>
     <row r="106" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>326</v>
+        <v>407</v>
       </c>
       <c r="C106" t="s">
-        <v>327</v>
+        <v>408</v>
       </c>
       <c r="D106" t="s">
-        <v>669</v>
+        <v>456</v>
       </c>
       <c r="E106" t="s">
         <v>33</v>
@@ -10462,34 +10516,34 @@
         <v>54</v>
       </c>
       <c r="K106" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="L106" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="M106" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="N106" t="s">
         <v>33</v>
       </c>
       <c r="O106">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P106" t="s">
         <v>38</v>
       </c>
       <c r="Q106">
-        <v>75.98</v>
+        <v>22.99</v>
       </c>
       <c r="R106">
-        <v>12.66</v>
+        <v>3.83</v>
       </c>
       <c r="Y106" t="s">
-        <v>91</v>
+        <v>409</v>
       </c>
       <c r="AA106" t="s">
-        <v>328</v>
+        <v>410</v>
       </c>
       <c r="AB106" t="s">
         <v>39</v>
@@ -10503,13 +10557,13 @@
     </row>
     <row r="107" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>343</v>
+        <v>399</v>
       </c>
       <c r="C107" t="s">
-        <v>344</v>
+        <v>400</v>
       </c>
       <c r="D107" t="s">
-        <v>345</v>
+        <v>411</v>
       </c>
       <c r="E107" t="s">
         <v>33</v>
@@ -10527,13 +10581,13 @@
         <v>54</v>
       </c>
       <c r="K107" t="s">
-        <v>40</v>
+        <v>340</v>
       </c>
       <c r="L107" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="M107" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="N107" t="s">
         <v>33</v>
@@ -10545,16 +10599,16 @@
         <v>38</v>
       </c>
       <c r="Q107">
-        <v>59.99</v>
+        <v>44.99</v>
       </c>
       <c r="R107">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="Y107" t="s">
-        <v>346</v>
+        <v>401</v>
       </c>
       <c r="AA107" t="s">
-        <v>347</v>
+        <v>402</v>
       </c>
       <c r="AB107" t="s">
         <v>39</v>
@@ -10568,13 +10622,13 @@
     </row>
     <row r="108" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>288</v>
+        <v>394</v>
       </c>
       <c r="C108" t="s">
-        <v>289</v>
+        <v>395</v>
       </c>
       <c r="D108" t="s">
-        <v>348</v>
+        <v>412</v>
       </c>
       <c r="E108" t="s">
         <v>33</v>
@@ -10589,37 +10643,40 @@
         <v>36</v>
       </c>
       <c r="J108" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K108" t="s">
-        <v>48</v>
+        <v>340</v>
       </c>
       <c r="L108" t="s">
-        <v>49</v>
+        <v>142</v>
       </c>
       <c r="M108" t="s">
-        <v>50</v>
+        <v>143</v>
       </c>
       <c r="N108" t="s">
         <v>33</v>
       </c>
       <c r="O108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P108" t="s">
         <v>38</v>
       </c>
       <c r="Q108">
-        <v>75.98</v>
+        <v>44.99</v>
       </c>
       <c r="R108">
-        <v>12.66</v>
+        <v>7.5</v>
       </c>
       <c r="Y108" t="s">
-        <v>290</v>
+        <v>396</v>
+      </c>
+      <c r="Z108" t="s">
+        <v>397</v>
       </c>
       <c r="AA108" t="s">
-        <v>291</v>
+        <v>398</v>
       </c>
       <c r="AB108" t="s">
         <v>39</v>
@@ -10633,13 +10690,13 @@
     </row>
     <row r="109" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="C109" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="D109" t="s">
-        <v>351</v>
+        <v>662</v>
       </c>
       <c r="E109" t="s">
         <v>33</v>
@@ -10657,13 +10714,13 @@
         <v>54</v>
       </c>
       <c r="K109" t="s">
-        <v>48</v>
+        <v>340</v>
       </c>
       <c r="L109" t="s">
-        <v>49</v>
+        <v>142</v>
       </c>
       <c r="M109" t="s">
-        <v>50</v>
+        <v>143</v>
       </c>
       <c r="N109" t="s">
         <v>33</v>
@@ -10675,19 +10732,16 @@
         <v>38</v>
       </c>
       <c r="Q109">
-        <v>37.99</v>
+        <v>44.99</v>
       </c>
       <c r="R109">
-        <v>6.33</v>
+        <v>7.5</v>
       </c>
       <c r="Y109" t="s">
-        <v>352</v>
-      </c>
-      <c r="Z109" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="AA109" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="AB109" t="s">
         <v>39</v>
@@ -10701,13 +10755,13 @@
     </row>
     <row r="110" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>355</v>
+        <v>663</v>
       </c>
       <c r="C110" t="s">
-        <v>356</v>
+        <v>664</v>
       </c>
       <c r="D110" t="s">
-        <v>357</v>
+        <v>665</v>
       </c>
       <c r="E110" t="s">
         <v>33</v>
@@ -10725,13 +10779,13 @@
         <v>54</v>
       </c>
       <c r="K110" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L110" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M110" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N110" t="s">
         <v>33</v>
@@ -10743,22 +10797,25 @@
         <v>38</v>
       </c>
       <c r="Q110">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R110">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y110" t="s">
-        <v>58</v>
+        <v>62</v>
+      </c>
+      <c r="Z110" t="s">
+        <v>666</v>
       </c>
       <c r="AA110" t="s">
-        <v>358</v>
+        <v>667</v>
       </c>
       <c r="AB110" t="s">
         <v>39</v>
       </c>
       <c r="AD110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG110" t="b">
         <v>0</v>
@@ -10766,13 +10823,13 @@
     </row>
     <row r="111" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>359</v>
+        <v>334</v>
       </c>
       <c r="C111" t="s">
-        <v>360</v>
+        <v>335</v>
       </c>
       <c r="D111" t="s">
-        <v>361</v>
+        <v>668</v>
       </c>
       <c r="E111" t="s">
         <v>33</v>
@@ -10790,37 +10847,34 @@
         <v>54</v>
       </c>
       <c r="K111" t="s">
-        <v>48</v>
+        <v>203</v>
       </c>
       <c r="L111" t="s">
-        <v>49</v>
+        <v>204</v>
       </c>
       <c r="M111" t="s">
-        <v>50</v>
+        <v>205</v>
       </c>
       <c r="N111" t="s">
         <v>33</v>
       </c>
       <c r="O111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P111" t="s">
         <v>38</v>
       </c>
       <c r="Q111">
-        <v>75.98</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="R111">
-        <v>12.66</v>
+        <v>11.67</v>
       </c>
       <c r="Y111" t="s">
-        <v>101</v>
-      </c>
-      <c r="Z111" t="s">
-        <v>59</v>
+        <v>336</v>
       </c>
       <c r="AA111" t="s">
-        <v>362</v>
+        <v>337</v>
       </c>
       <c r="AB111" t="s">
         <v>39</v>
@@ -10834,13 +10888,13 @@
     </row>
     <row r="112" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>363</v>
+        <v>326</v>
       </c>
       <c r="C112" t="s">
-        <v>364</v>
+        <v>327</v>
       </c>
       <c r="D112" t="s">
-        <v>365</v>
+        <v>669</v>
       </c>
       <c r="E112" t="s">
         <v>33</v>
@@ -10858,34 +10912,34 @@
         <v>54</v>
       </c>
       <c r="K112" t="s">
-        <v>260</v>
+        <v>48</v>
       </c>
       <c r="L112" t="s">
-        <v>261</v>
+        <v>49</v>
       </c>
       <c r="M112" t="s">
-        <v>262</v>
+        <v>50</v>
       </c>
       <c r="N112" t="s">
         <v>33</v>
       </c>
       <c r="O112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P112" t="s">
         <v>38</v>
       </c>
       <c r="Q112">
-        <v>24.49</v>
+        <v>75.98</v>
       </c>
       <c r="R112">
-        <v>4.08</v>
+        <v>12.66</v>
       </c>
       <c r="Y112" t="s">
-        <v>366</v>
+        <v>91</v>
       </c>
       <c r="AA112" t="s">
-        <v>367</v>
+        <v>328</v>
       </c>
       <c r="AB112" t="s">
         <v>39</v>
@@ -10899,13 +10953,13 @@
     </row>
     <row r="113" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>265</v>
+        <v>343</v>
       </c>
       <c r="C113" t="s">
-        <v>266</v>
+        <v>344</v>
       </c>
       <c r="D113" t="s">
-        <v>368</v>
+        <v>345</v>
       </c>
       <c r="E113" t="s">
         <v>33</v>
@@ -10923,13 +10977,13 @@
         <v>54</v>
       </c>
       <c r="K113" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L113" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M113" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N113" t="s">
         <v>33</v>
@@ -10941,16 +10995,16 @@
         <v>38</v>
       </c>
       <c r="Q113">
-        <v>37.99</v>
+        <v>59.99</v>
       </c>
       <c r="R113">
-        <v>6.33</v>
+        <v>10</v>
       </c>
       <c r="Y113" t="s">
-        <v>267</v>
+        <v>346</v>
       </c>
       <c r="AA113" t="s">
-        <v>268</v>
+        <v>347</v>
       </c>
       <c r="AB113" t="s">
         <v>39</v>
@@ -10964,13 +11018,13 @@
     </row>
     <row r="114" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>369</v>
+        <v>288</v>
       </c>
       <c r="C114" t="s">
-        <v>370</v>
+        <v>289</v>
       </c>
       <c r="D114" t="s">
-        <v>371</v>
+        <v>348</v>
       </c>
       <c r="E114" t="s">
         <v>33</v>
@@ -10985,43 +11039,37 @@
         <v>36</v>
       </c>
       <c r="J114" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K114" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L114" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M114" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N114" t="s">
         <v>33</v>
       </c>
       <c r="O114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P114" t="s">
         <v>38</v>
       </c>
       <c r="Q114">
-        <v>11.99</v>
+        <v>75.98</v>
       </c>
       <c r="R114">
-        <v>2</v>
-      </c>
-      <c r="S114">
-        <v>5.99</v>
-      </c>
-      <c r="T114">
-        <v>1</v>
+        <v>12.66</v>
       </c>
       <c r="Y114" t="s">
-        <v>84</v>
+        <v>290</v>
       </c>
       <c r="AA114" t="s">
-        <v>372</v>
+        <v>291</v>
       </c>
       <c r="AB114" t="s">
         <v>39</v>
@@ -11035,13 +11083,13 @@
     </row>
     <row r="115" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
       <c r="C115" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
       <c r="D115" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
       <c r="E115" t="s">
         <v>33</v>
@@ -11059,13 +11107,13 @@
         <v>54</v>
       </c>
       <c r="K115" t="s">
-        <v>260</v>
+        <v>48</v>
       </c>
       <c r="L115" t="s">
-        <v>261</v>
+        <v>49</v>
       </c>
       <c r="M115" t="s">
-        <v>262</v>
+        <v>50</v>
       </c>
       <c r="N115" t="s">
         <v>33</v>
@@ -11077,16 +11125,19 @@
         <v>38</v>
       </c>
       <c r="Q115">
-        <v>24.49</v>
+        <v>37.99</v>
       </c>
       <c r="R115">
-        <v>4.08</v>
+        <v>6.33</v>
       </c>
       <c r="Y115" t="s">
-        <v>376</v>
+        <v>352</v>
+      </c>
+      <c r="Z115" t="s">
+        <v>353</v>
       </c>
       <c r="AA115" t="s">
-        <v>377</v>
+        <v>354</v>
       </c>
       <c r="AB115" t="s">
         <v>39</v>
@@ -11100,13 +11151,13 @@
     </row>
     <row r="116" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>378</v>
+        <v>355</v>
       </c>
       <c r="C116" t="s">
-        <v>379</v>
+        <v>356</v>
       </c>
       <c r="D116" t="s">
-        <v>380</v>
+        <v>357</v>
       </c>
       <c r="E116" t="s">
         <v>33</v>
@@ -11124,13 +11175,13 @@
         <v>54</v>
       </c>
       <c r="K116" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L116" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M116" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N116" t="s">
         <v>33</v>
@@ -11142,16 +11193,16 @@
         <v>38</v>
       </c>
       <c r="Q116">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R116">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y116" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AA116" t="s">
-        <v>381</v>
+        <v>358</v>
       </c>
       <c r="AB116" t="s">
         <v>39</v>
@@ -11165,13 +11216,13 @@
     </row>
     <row r="117" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>382</v>
+        <v>359</v>
       </c>
       <c r="C117" t="s">
-        <v>383</v>
+        <v>360</v>
       </c>
       <c r="D117" t="s">
-        <v>384</v>
+        <v>361</v>
       </c>
       <c r="E117" t="s">
         <v>33</v>
@@ -11189,34 +11240,37 @@
         <v>54</v>
       </c>
       <c r="K117" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L117" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M117" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N117" t="s">
         <v>33</v>
       </c>
       <c r="O117">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P117" t="s">
         <v>38</v>
       </c>
       <c r="Q117">
-        <v>11.99</v>
+        <v>75.98</v>
       </c>
       <c r="R117">
-        <v>2</v>
+        <v>12.66</v>
       </c>
       <c r="Y117" t="s">
-        <v>385</v>
+        <v>101</v>
+      </c>
+      <c r="Z117" t="s">
+        <v>59</v>
       </c>
       <c r="AA117" t="s">
-        <v>386</v>
+        <v>362</v>
       </c>
       <c r="AB117" t="s">
         <v>39</v>
@@ -11230,16 +11284,16 @@
     </row>
     <row r="118" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>387</v>
+        <v>363</v>
       </c>
       <c r="C118" t="s">
-        <v>388</v>
+        <v>364</v>
       </c>
       <c r="D118" t="s">
-        <v>389</v>
+        <v>365</v>
       </c>
       <c r="E118" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F118" t="s">
         <v>34</v>
@@ -11254,25 +11308,34 @@
         <v>54</v>
       </c>
       <c r="K118" t="s">
-        <v>43</v>
+        <v>260</v>
       </c>
       <c r="L118" t="s">
-        <v>44</v>
+        <v>261</v>
       </c>
       <c r="M118" t="s">
-        <v>45</v>
+        <v>262</v>
+      </c>
+      <c r="N118" t="s">
+        <v>33</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P118" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q118">
+        <v>24.49</v>
+      </c>
+      <c r="R118">
+        <v>4.08</v>
       </c>
       <c r="Y118" t="s">
-        <v>390</v>
-      </c>
-      <c r="Z118" t="s">
-        <v>391</v>
+        <v>366</v>
       </c>
       <c r="AA118" t="s">
-        <v>392</v>
+        <v>367</v>
       </c>
       <c r="AB118" t="s">
         <v>39</v>
@@ -11286,13 +11349,13 @@
     </row>
     <row r="119" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>323</v>
+        <v>265</v>
       </c>
       <c r="C119" t="s">
-        <v>324</v>
+        <v>266</v>
       </c>
       <c r="D119" t="s">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="E119" t="s">
         <v>33</v>
@@ -11310,13 +11373,13 @@
         <v>54</v>
       </c>
       <c r="K119" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="L119" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="M119" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="N119" t="s">
         <v>33</v>
@@ -11328,16 +11391,16 @@
         <v>38</v>
       </c>
       <c r="Q119">
-        <v>14.99</v>
+        <v>37.99</v>
       </c>
       <c r="R119">
-        <v>2.5</v>
+        <v>6.33</v>
       </c>
       <c r="Y119" t="s">
-        <v>58</v>
+        <v>267</v>
       </c>
       <c r="AA119" t="s">
-        <v>325</v>
+        <v>268</v>
       </c>
       <c r="AB119" t="s">
         <v>39</v>
@@ -11351,13 +11414,13 @@
     </row>
     <row r="120" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>318</v>
+        <v>369</v>
       </c>
       <c r="C120" t="s">
-        <v>319</v>
+        <v>370</v>
       </c>
       <c r="D120" t="s">
-        <v>320</v>
+        <v>371</v>
       </c>
       <c r="E120" t="s">
         <v>33</v>
@@ -11398,14 +11461,17 @@
       <c r="R120">
         <v>2</v>
       </c>
+      <c r="S120">
+        <v>5.99</v>
+      </c>
+      <c r="T120">
+        <v>1</v>
+      </c>
       <c r="Y120" t="s">
-        <v>321</v>
-      </c>
-      <c r="Z120" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="AA120" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="AB120" t="s">
         <v>39</v>
@@ -11419,13 +11485,13 @@
     </row>
     <row r="121" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>329</v>
+        <v>373</v>
       </c>
       <c r="C121" t="s">
-        <v>330</v>
+        <v>374</v>
       </c>
       <c r="D121" t="s">
-        <v>331</v>
+        <v>375</v>
       </c>
       <c r="E121" t="s">
         <v>33</v>
@@ -11467,10 +11533,10 @@
         <v>4.08</v>
       </c>
       <c r="Y121" t="s">
-        <v>332</v>
+        <v>376</v>
       </c>
       <c r="AA121" t="s">
-        <v>333</v>
+        <v>377</v>
       </c>
       <c r="AB121" t="s">
         <v>39</v>
@@ -11484,13 +11550,13 @@
     </row>
     <row r="122" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>670</v>
+        <v>378</v>
       </c>
       <c r="C122" t="s">
-        <v>671</v>
+        <v>379</v>
       </c>
       <c r="D122" t="s">
-        <v>672</v>
+        <v>380</v>
       </c>
       <c r="E122" t="s">
         <v>33</v>
@@ -11532,10 +11598,10 @@
         <v>10</v>
       </c>
       <c r="Y122" t="s">
-        <v>673</v>
+        <v>57</v>
       </c>
       <c r="AA122" t="s">
-        <v>674</v>
+        <v>381</v>
       </c>
       <c r="AB122" t="s">
         <v>39</v>
@@ -11549,13 +11615,13 @@
     </row>
     <row r="123" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>675</v>
+        <v>382</v>
       </c>
       <c r="C123" t="s">
-        <v>676</v>
+        <v>383</v>
       </c>
       <c r="D123" t="s">
-        <v>677</v>
+        <v>384</v>
       </c>
       <c r="E123" t="s">
         <v>33</v>
@@ -11573,13 +11639,13 @@
         <v>54</v>
       </c>
       <c r="K123" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L123" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M123" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="N123" t="s">
         <v>33</v>
@@ -11591,16 +11657,16 @@
         <v>38</v>
       </c>
       <c r="Q123">
-        <v>37.99</v>
+        <v>11.99</v>
       </c>
       <c r="R123">
-        <v>6.33</v>
+        <v>2</v>
       </c>
       <c r="Y123" t="s">
-        <v>678</v>
+        <v>385</v>
       </c>
       <c r="AA123" t="s">
-        <v>679</v>
+        <v>386</v>
       </c>
       <c r="AB123" t="s">
         <v>39</v>
@@ -11614,16 +11680,16 @@
     </row>
     <row r="124" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>680</v>
+        <v>387</v>
       </c>
       <c r="C124" t="s">
-        <v>681</v>
+        <v>388</v>
       </c>
       <c r="D124" t="s">
-        <v>682</v>
+        <v>389</v>
       </c>
       <c r="E124" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F124" t="s">
         <v>34</v>
@@ -11638,37 +11704,25 @@
         <v>54</v>
       </c>
       <c r="K124" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L124" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M124" t="s">
-        <v>42</v>
-      </c>
-      <c r="N124" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O124">
-        <v>1</v>
-      </c>
-      <c r="P124" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q124">
-        <v>59.99</v>
-      </c>
-      <c r="R124">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y124" t="s">
-        <v>683</v>
+        <v>390</v>
       </c>
       <c r="Z124" t="s">
-        <v>76</v>
+        <v>391</v>
       </c>
       <c r="AA124" t="s">
-        <v>684</v>
+        <v>392</v>
       </c>
       <c r="AB124" t="s">
         <v>39</v>
@@ -11682,13 +11736,13 @@
     </row>
     <row r="125" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>685</v>
+        <v>323</v>
       </c>
       <c r="C125" t="s">
-        <v>686</v>
+        <v>324</v>
       </c>
       <c r="D125" t="s">
-        <v>687</v>
+        <v>393</v>
       </c>
       <c r="E125" t="s">
         <v>33</v>
@@ -11706,13 +11760,13 @@
         <v>54</v>
       </c>
       <c r="K125" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="L125" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="M125" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="N125" t="s">
         <v>33</v>
@@ -11724,16 +11778,16 @@
         <v>38</v>
       </c>
       <c r="Q125">
-        <v>37.99</v>
+        <v>14.99</v>
       </c>
       <c r="R125">
-        <v>6.33</v>
+        <v>2.5</v>
       </c>
       <c r="Y125" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="AA125" t="s">
-        <v>688</v>
+        <v>325</v>
       </c>
       <c r="AB125" t="s">
         <v>39</v>
@@ -11747,16 +11801,16 @@
     </row>
     <row r="126" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>689</v>
+        <v>318</v>
       </c>
       <c r="C126" t="s">
-        <v>690</v>
+        <v>319</v>
       </c>
       <c r="D126" t="s">
-        <v>691</v>
+        <v>320</v>
       </c>
       <c r="E126" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F126" t="s">
         <v>34</v>
@@ -11768,28 +11822,40 @@
         <v>36</v>
       </c>
       <c r="J126" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K126" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L126" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M126" t="s">
-        <v>50</v>
+        <v>74</v>
+      </c>
+      <c r="N126" t="s">
+        <v>33</v>
       </c>
       <c r="O126">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P126" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q126">
+        <v>11.99</v>
+      </c>
+      <c r="R126">
+        <v>2</v>
       </c>
       <c r="Y126" t="s">
-        <v>692</v>
+        <v>321</v>
       </c>
       <c r="Z126" t="s">
-        <v>693</v>
+        <v>65</v>
       </c>
       <c r="AA126" t="s">
-        <v>694</v>
+        <v>322</v>
       </c>
       <c r="AB126" t="s">
         <v>39</v>
@@ -11803,16 +11869,16 @@
     </row>
     <row r="127" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>695</v>
+        <v>329</v>
       </c>
       <c r="C127" t="s">
-        <v>696</v>
+        <v>330</v>
       </c>
       <c r="D127" t="s">
-        <v>697</v>
+        <v>331</v>
       </c>
       <c r="E127" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F127" t="s">
         <v>34</v>
@@ -11824,28 +11890,37 @@
         <v>36</v>
       </c>
       <c r="J127" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K127" t="s">
-        <v>48</v>
+        <v>260</v>
       </c>
       <c r="L127" t="s">
-        <v>49</v>
+        <v>261</v>
       </c>
       <c r="M127" t="s">
-        <v>50</v>
+        <v>262</v>
+      </c>
+      <c r="N127" t="s">
+        <v>33</v>
       </c>
       <c r="O127">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P127" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q127">
+        <v>24.49</v>
+      </c>
+      <c r="R127">
+        <v>4.08</v>
       </c>
       <c r="Y127" t="s">
-        <v>692</v>
-      </c>
-      <c r="Z127" t="s">
-        <v>693</v>
+        <v>332</v>
       </c>
       <c r="AA127" t="s">
-        <v>694</v>
+        <v>333</v>
       </c>
       <c r="AB127" t="s">
         <v>39</v>
@@ -11859,13 +11934,13 @@
     </row>
     <row r="128" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>300</v>
+        <v>670</v>
       </c>
       <c r="C128" t="s">
-        <v>301</v>
+        <v>671</v>
       </c>
       <c r="D128" t="s">
-        <v>698</v>
+        <v>672</v>
       </c>
       <c r="E128" t="s">
         <v>33</v>
@@ -11883,13 +11958,13 @@
         <v>54</v>
       </c>
       <c r="K128" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="L128" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="M128" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="N128" t="s">
         <v>33</v>
@@ -11901,16 +11976,16 @@
         <v>38</v>
       </c>
       <c r="Q128">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R128">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y128" t="s">
-        <v>58</v>
+        <v>673</v>
       </c>
       <c r="AA128" t="s">
-        <v>302</v>
+        <v>674</v>
       </c>
       <c r="AB128" t="s">
         <v>39</v>
@@ -11924,16 +11999,16 @@
     </row>
     <row r="129" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>699</v>
+        <v>675</v>
       </c>
       <c r="C129" t="s">
-        <v>700</v>
+        <v>676</v>
       </c>
       <c r="D129" t="s">
-        <v>701</v>
+        <v>677</v>
       </c>
       <c r="E129" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F129" t="s">
         <v>34</v>
@@ -11956,17 +12031,26 @@
       <c r="M129" t="s">
         <v>50</v>
       </c>
+      <c r="N129" t="s">
+        <v>33</v>
+      </c>
       <c r="O129">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P129" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q129">
+        <v>37.99</v>
+      </c>
+      <c r="R129">
+        <v>6.33</v>
       </c>
       <c r="Y129" t="s">
-        <v>692</v>
-      </c>
-      <c r="Z129" t="s">
-        <v>693</v>
+        <v>678</v>
       </c>
       <c r="AA129" t="s">
-        <v>694</v>
+        <v>679</v>
       </c>
       <c r="AB129" t="s">
         <v>39</v>
@@ -11980,13 +12064,13 @@
     </row>
     <row r="130" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>303</v>
+        <v>680</v>
       </c>
       <c r="C130" t="s">
-        <v>304</v>
+        <v>681</v>
       </c>
       <c r="D130" t="s">
-        <v>702</v>
+        <v>682</v>
       </c>
       <c r="E130" t="s">
         <v>33</v>
@@ -12028,10 +12112,13 @@
         <v>10</v>
       </c>
       <c r="Y130" t="s">
-        <v>305</v>
+        <v>683</v>
+      </c>
+      <c r="Z130" t="s">
+        <v>76</v>
       </c>
       <c r="AA130" t="s">
-        <v>306</v>
+        <v>684</v>
       </c>
       <c r="AB130" t="s">
         <v>39</v>
@@ -12045,13 +12132,13 @@
     </row>
     <row r="131" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>292</v>
+        <v>685</v>
       </c>
       <c r="C131" t="s">
-        <v>293</v>
+        <v>686</v>
       </c>
       <c r="D131" t="s">
-        <v>294</v>
+        <v>687</v>
       </c>
       <c r="E131" t="s">
         <v>33</v>
@@ -12066,16 +12153,16 @@
         <v>36</v>
       </c>
       <c r="J131" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K131" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L131" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M131" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N131" t="s">
         <v>33</v>
@@ -12087,19 +12174,16 @@
         <v>38</v>
       </c>
       <c r="Q131">
-        <v>59.99</v>
+        <v>37.99</v>
       </c>
       <c r="R131">
-        <v>10</v>
+        <v>6.33</v>
       </c>
       <c r="Y131" t="s">
-        <v>77</v>
-      </c>
-      <c r="Z131" t="s">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="AA131" t="s">
-        <v>295</v>
+        <v>688</v>
       </c>
       <c r="AB131" t="s">
         <v>39</v>
@@ -12113,16 +12197,16 @@
     </row>
     <row r="132" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>296</v>
+        <v>689</v>
       </c>
       <c r="C132" t="s">
-        <v>297</v>
+        <v>690</v>
       </c>
       <c r="D132" t="s">
-        <v>298</v>
+        <v>691</v>
       </c>
       <c r="E132" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F132" t="s">
         <v>34</v>
@@ -12137,37 +12221,25 @@
         <v>37</v>
       </c>
       <c r="K132" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L132" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M132" t="s">
-        <v>42</v>
-      </c>
-      <c r="N132" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="O132">
-        <v>1</v>
-      </c>
-      <c r="P132" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q132">
-        <v>59.99</v>
-      </c>
-      <c r="R132">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y132" t="s">
-        <v>62</v>
+        <v>692</v>
       </c>
       <c r="Z132" t="s">
-        <v>51</v>
+        <v>693</v>
       </c>
       <c r="AA132" t="s">
-        <v>299</v>
+        <v>694</v>
       </c>
       <c r="AB132" t="s">
         <v>39</v>
@@ -12181,16 +12253,16 @@
     </row>
     <row r="133" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>307</v>
+        <v>695</v>
       </c>
       <c r="C133" t="s">
-        <v>308</v>
+        <v>696</v>
       </c>
       <c r="D133" t="s">
-        <v>309</v>
+        <v>697</v>
       </c>
       <c r="E133" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F133" t="s">
         <v>34</v>
@@ -12205,34 +12277,25 @@
         <v>37</v>
       </c>
       <c r="K133" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="L133" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="M133" t="s">
-        <v>89</v>
-      </c>
-      <c r="N133" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="O133">
-        <v>1</v>
-      </c>
-      <c r="P133" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q133">
-        <v>20.49</v>
-      </c>
-      <c r="R133">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="Y133" t="s">
-        <v>310</v>
+        <v>692</v>
+      </c>
+      <c r="Z133" t="s">
+        <v>693</v>
       </c>
       <c r="AA133" t="s">
-        <v>311</v>
+        <v>694</v>
       </c>
       <c r="AB133" t="s">
         <v>39</v>
@@ -12246,13 +12309,13 @@
     </row>
     <row r="134" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="C134" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="D134" t="s">
-        <v>314</v>
+        <v>698</v>
       </c>
       <c r="E134" t="s">
         <v>33</v>
@@ -12267,16 +12330,16 @@
         <v>36</v>
       </c>
       <c r="J134" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K134" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="L134" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="M134" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="N134" t="s">
         <v>33</v>
@@ -12288,19 +12351,16 @@
         <v>38</v>
       </c>
       <c r="Q134">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="R134">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="Y134" t="s">
-        <v>100</v>
-      </c>
-      <c r="Z134" t="s">
-        <v>315</v>
+        <v>58</v>
       </c>
       <c r="AA134" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="AB134" t="s">
         <v>39</v>
@@ -12314,16 +12374,16 @@
     </row>
     <row r="135" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>253</v>
+        <v>699</v>
       </c>
       <c r="C135" t="s">
-        <v>254</v>
+        <v>700</v>
       </c>
       <c r="D135" t="s">
-        <v>317</v>
+        <v>701</v>
       </c>
       <c r="E135" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F135" t="s">
         <v>34</v>
@@ -12338,37 +12398,25 @@
         <v>54</v>
       </c>
       <c r="K135" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L135" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M135" t="s">
-        <v>42</v>
-      </c>
-      <c r="N135" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="O135">
-        <v>1</v>
-      </c>
-      <c r="P135" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q135">
-        <v>59.99</v>
-      </c>
-      <c r="R135">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y135" t="s">
-        <v>255</v>
+        <v>692</v>
       </c>
       <c r="Z135" t="s">
-        <v>102</v>
+        <v>693</v>
       </c>
       <c r="AA135" t="s">
-        <v>256</v>
+        <v>694</v>
       </c>
       <c r="AB135" t="s">
         <v>39</v>
@@ -12382,13 +12430,13 @@
     </row>
     <row r="136" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>257</v>
+        <v>303</v>
       </c>
       <c r="C136" t="s">
-        <v>258</v>
+        <v>304</v>
       </c>
       <c r="D136" t="s">
-        <v>259</v>
+        <v>702</v>
       </c>
       <c r="E136" t="s">
         <v>33</v>
@@ -12406,13 +12454,13 @@
         <v>54</v>
       </c>
       <c r="K136" t="s">
-        <v>260</v>
+        <v>40</v>
       </c>
       <c r="L136" t="s">
-        <v>261</v>
+        <v>41</v>
       </c>
       <c r="M136" t="s">
-        <v>262</v>
+        <v>42</v>
       </c>
       <c r="N136" t="s">
         <v>33</v>
@@ -12424,19 +12472,16 @@
         <v>38</v>
       </c>
       <c r="Q136">
-        <v>24.49</v>
+        <v>59.99</v>
       </c>
       <c r="R136">
-        <v>4.08</v>
+        <v>10</v>
       </c>
       <c r="Y136" t="s">
-        <v>263</v>
-      </c>
-      <c r="Z136" t="s">
-        <v>64</v>
+        <v>305</v>
       </c>
       <c r="AA136" t="s">
-        <v>264</v>
+        <v>306</v>
       </c>
       <c r="AB136" t="s">
         <v>39</v>
@@ -12450,13 +12495,13 @@
     </row>
     <row r="137" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="C137" t="s">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="D137" t="s">
-        <v>271</v>
+        <v>294</v>
       </c>
       <c r="E137" t="s">
         <v>33</v>
@@ -12471,7 +12516,7 @@
         <v>36</v>
       </c>
       <c r="J137" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K137" t="s">
         <v>40</v>
@@ -12498,10 +12543,13 @@
         <v>10</v>
       </c>
       <c r="Y137" t="s">
-        <v>272</v>
+        <v>77</v>
+      </c>
+      <c r="Z137" t="s">
+        <v>92</v>
       </c>
       <c r="AA137" t="s">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="AB137" t="s">
         <v>39</v>
@@ -12515,13 +12563,13 @@
     </row>
     <row r="138" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>149</v>
+        <v>296</v>
       </c>
       <c r="C138" t="s">
-        <v>150</v>
+        <v>297</v>
       </c>
       <c r="D138" t="s">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="E138" t="s">
         <v>33</v>
@@ -12536,7 +12584,7 @@
         <v>36</v>
       </c>
       <c r="J138" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K138" t="s">
         <v>40</v>
@@ -12563,10 +12611,13 @@
         <v>10</v>
       </c>
       <c r="Y138" t="s">
-        <v>63</v>
+        <v>62</v>
+      </c>
+      <c r="Z138" t="s">
+        <v>51</v>
       </c>
       <c r="AA138" t="s">
-        <v>151</v>
+        <v>299</v>
       </c>
       <c r="AB138" t="s">
         <v>39</v>
@@ -12580,13 +12631,13 @@
     </row>
     <row r="139" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>275</v>
+        <v>307</v>
       </c>
       <c r="C139" t="s">
-        <v>276</v>
+        <v>308</v>
       </c>
       <c r="D139" t="s">
-        <v>277</v>
+        <v>309</v>
       </c>
       <c r="E139" t="s">
         <v>33</v>
@@ -12601,40 +12652,37 @@
         <v>36</v>
       </c>
       <c r="J139" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K139" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="L139" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="M139" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="N139" t="s">
         <v>33</v>
       </c>
       <c r="O139">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P139" t="s">
         <v>38</v>
       </c>
       <c r="Q139">
-        <v>119.98</v>
+        <v>20.49</v>
       </c>
       <c r="R139">
-        <v>20</v>
+        <v>3.42</v>
       </c>
       <c r="Y139" t="s">
-        <v>278</v>
-      </c>
-      <c r="Z139" t="s">
-        <v>279</v>
+        <v>310</v>
       </c>
       <c r="AA139" t="s">
-        <v>280</v>
+        <v>311</v>
       </c>
       <c r="AB139" t="s">
         <v>39</v>
@@ -12648,13 +12696,13 @@
     </row>
     <row r="140" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>281</v>
+        <v>312</v>
       </c>
       <c r="C140" t="s">
-        <v>282</v>
+        <v>313</v>
       </c>
       <c r="D140" t="s">
-        <v>283</v>
+        <v>314</v>
       </c>
       <c r="E140" t="s">
         <v>33</v>
@@ -12672,13 +12720,13 @@
         <v>37</v>
       </c>
       <c r="K140" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L140" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M140" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N140" t="s">
         <v>33</v>
@@ -12690,16 +12738,19 @@
         <v>38</v>
       </c>
       <c r="Q140">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R140">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y140" t="s">
-        <v>75</v>
+        <v>100</v>
+      </c>
+      <c r="Z140" t="s">
+        <v>315</v>
       </c>
       <c r="AA140" t="s">
-        <v>284</v>
+        <v>316</v>
       </c>
       <c r="AB140" t="s">
         <v>39</v>
@@ -12713,16 +12764,16 @@
     </row>
     <row r="141" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="C141" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="D141" t="s">
-        <v>285</v>
+        <v>317</v>
       </c>
       <c r="E141" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F141" t="s">
         <v>34</v>
@@ -12745,14 +12796,29 @@
       <c r="M141" t="s">
         <v>42</v>
       </c>
+      <c r="N141" t="s">
+        <v>33</v>
+      </c>
       <c r="O141">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P141" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q141">
+        <v>59.99</v>
+      </c>
+      <c r="R141">
+        <v>10</v>
       </c>
       <c r="Y141" t="s">
-        <v>240</v>
+        <v>255</v>
+      </c>
+      <c r="Z141" t="s">
+        <v>102</v>
       </c>
       <c r="AA141" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="AB141" t="s">
         <v>39</v>
@@ -12766,13 +12832,13 @@
     </row>
     <row r="142" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>224</v>
+        <v>257</v>
       </c>
       <c r="C142" t="s">
-        <v>225</v>
+        <v>258</v>
       </c>
       <c r="D142" t="s">
-        <v>286</v>
+        <v>259</v>
       </c>
       <c r="E142" t="s">
         <v>33</v>
@@ -12790,13 +12856,13 @@
         <v>54</v>
       </c>
       <c r="K142" t="s">
-        <v>40</v>
+        <v>260</v>
       </c>
       <c r="L142" t="s">
-        <v>41</v>
+        <v>261</v>
       </c>
       <c r="M142" t="s">
-        <v>42</v>
+        <v>262</v>
       </c>
       <c r="N142" t="s">
         <v>33</v>
@@ -12808,16 +12874,19 @@
         <v>38</v>
       </c>
       <c r="Q142">
-        <v>59.99</v>
+        <v>24.49</v>
       </c>
       <c r="R142">
-        <v>10</v>
+        <v>4.08</v>
       </c>
       <c r="Y142" t="s">
-        <v>226</v>
+        <v>263</v>
+      </c>
+      <c r="Z142" t="s">
+        <v>64</v>
       </c>
       <c r="AA142" t="s">
-        <v>227</v>
+        <v>264</v>
       </c>
       <c r="AB142" t="s">
         <v>39</v>
@@ -12831,13 +12900,13 @@
     </row>
     <row r="143" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>213</v>
+        <v>269</v>
       </c>
       <c r="C143" t="s">
-        <v>214</v>
+        <v>270</v>
       </c>
       <c r="D143" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="E143" t="s">
         <v>33</v>
@@ -12879,13 +12948,10 @@
         <v>10</v>
       </c>
       <c r="Y143" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z143" t="s">
-        <v>216</v>
+        <v>272</v>
       </c>
       <c r="AA143" t="s">
-        <v>217</v>
+        <v>273</v>
       </c>
       <c r="AB143" t="s">
         <v>39</v>
@@ -12899,13 +12965,13 @@
     </row>
     <row r="144" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>218</v>
+        <v>149</v>
       </c>
       <c r="C144" t="s">
-        <v>219</v>
+        <v>150</v>
       </c>
       <c r="D144" t="s">
-        <v>220</v>
+        <v>274</v>
       </c>
       <c r="E144" t="s">
         <v>33</v>
@@ -12923,13 +12989,13 @@
         <v>54</v>
       </c>
       <c r="K144" t="s">
-        <v>203</v>
+        <v>40</v>
       </c>
       <c r="L144" t="s">
-        <v>204</v>
+        <v>41</v>
       </c>
       <c r="M144" t="s">
-        <v>205</v>
+        <v>42</v>
       </c>
       <c r="N144" t="s">
         <v>33</v>
@@ -12941,19 +13007,16 @@
         <v>38</v>
       </c>
       <c r="Q144">
-        <v>69.989999999999995</v>
+        <v>59.99</v>
       </c>
       <c r="R144">
-        <v>11.67</v>
+        <v>10</v>
       </c>
       <c r="Y144" t="s">
-        <v>221</v>
-      </c>
-      <c r="Z144" t="s">
-        <v>222</v>
+        <v>63</v>
       </c>
       <c r="AA144" t="s">
-        <v>223</v>
+        <v>151</v>
       </c>
       <c r="AB144" t="s">
         <v>39</v>
@@ -12967,13 +13030,13 @@
     </row>
     <row r="145" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>228</v>
+        <v>275</v>
       </c>
       <c r="C145" t="s">
-        <v>229</v>
+        <v>276</v>
       </c>
       <c r="D145" t="s">
-        <v>230</v>
+        <v>277</v>
       </c>
       <c r="E145" t="s">
         <v>33</v>
@@ -13003,22 +13066,25 @@
         <v>33</v>
       </c>
       <c r="O145">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P145" t="s">
         <v>38</v>
       </c>
       <c r="Q145">
-        <v>59.99</v>
+        <v>119.98</v>
       </c>
       <c r="R145">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y145" t="s">
-        <v>231</v>
+        <v>278</v>
+      </c>
+      <c r="Z145" t="s">
+        <v>279</v>
       </c>
       <c r="AA145" t="s">
-        <v>232</v>
+        <v>280</v>
       </c>
       <c r="AB145" t="s">
         <v>39</v>
@@ -13032,13 +13098,13 @@
     </row>
     <row r="146" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>233</v>
+        <v>281</v>
       </c>
       <c r="C146" t="s">
-        <v>234</v>
+        <v>282</v>
       </c>
       <c r="D146" t="s">
-        <v>235</v>
+        <v>283</v>
       </c>
       <c r="E146" t="s">
         <v>33</v>
@@ -13053,16 +13119,16 @@
         <v>36</v>
       </c>
       <c r="J146" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K146" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="L146" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="M146" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="N146" t="s">
         <v>33</v>
@@ -13074,16 +13140,16 @@
         <v>38</v>
       </c>
       <c r="Q146">
-        <v>14.99</v>
+        <v>11.99</v>
       </c>
       <c r="R146">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Y146" t="s">
-        <v>236</v>
+        <v>75</v>
       </c>
       <c r="AA146" t="s">
-        <v>237</v>
+        <v>284</v>
       </c>
       <c r="AB146" t="s">
         <v>39</v>
@@ -13097,13 +13163,13 @@
     </row>
     <row r="147" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C147" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D147" t="s">
-        <v>244</v>
+        <v>285</v>
       </c>
       <c r="E147" t="s">
         <v>53</v>
@@ -13150,13 +13216,13 @@
     </row>
     <row r="148" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="C148" t="s">
-        <v>246</v>
+        <v>225</v>
       </c>
       <c r="D148" t="s">
-        <v>247</v>
+        <v>286</v>
       </c>
       <c r="E148" t="s">
         <v>33</v>
@@ -13171,7 +13237,7 @@
         <v>36</v>
       </c>
       <c r="J148" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K148" t="s">
         <v>40</v>
@@ -13198,10 +13264,10 @@
         <v>10</v>
       </c>
       <c r="Y148" t="s">
-        <v>248</v>
+        <v>226</v>
       </c>
       <c r="AA148" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="AB148" t="s">
         <v>39</v>
@@ -13215,13 +13281,13 @@
     </row>
     <row r="149" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="C149" t="s">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="D149" t="s">
-        <v>250</v>
+        <v>287</v>
       </c>
       <c r="E149" t="s">
         <v>33</v>
@@ -13236,16 +13302,16 @@
         <v>36</v>
       </c>
       <c r="J149" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K149" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L149" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M149" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N149" t="s">
         <v>33</v>
@@ -13257,16 +13323,19 @@
         <v>38</v>
       </c>
       <c r="Q149">
-        <v>37.99</v>
+        <v>59.99</v>
       </c>
       <c r="R149">
-        <v>6.33</v>
+        <v>10</v>
       </c>
       <c r="Y149" t="s">
-        <v>52</v>
+        <v>215</v>
+      </c>
+      <c r="Z149" t="s">
+        <v>216</v>
       </c>
       <c r="AA149" t="s">
-        <v>190</v>
+        <v>217</v>
       </c>
       <c r="AB149" t="s">
         <v>39</v>
@@ -13280,13 +13349,13 @@
     </row>
     <row r="150" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>191</v>
+        <v>218</v>
       </c>
       <c r="C150" t="s">
-        <v>192</v>
+        <v>219</v>
       </c>
       <c r="D150" t="s">
-        <v>251</v>
+        <v>220</v>
       </c>
       <c r="E150" t="s">
         <v>33</v>
@@ -13304,13 +13373,13 @@
         <v>54</v>
       </c>
       <c r="K150" t="s">
-        <v>40</v>
+        <v>203</v>
       </c>
       <c r="L150" t="s">
-        <v>41</v>
+        <v>204</v>
       </c>
       <c r="M150" t="s">
-        <v>42</v>
+        <v>205</v>
       </c>
       <c r="N150" t="s">
         <v>33</v>
@@ -13322,16 +13391,19 @@
         <v>38</v>
       </c>
       <c r="Q150">
-        <v>59.99</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="R150">
-        <v>10</v>
+        <v>11.67</v>
       </c>
       <c r="Y150" t="s">
-        <v>193</v>
+        <v>221</v>
+      </c>
+      <c r="Z150" t="s">
+        <v>222</v>
       </c>
       <c r="AA150" t="s">
-        <v>194</v>
+        <v>223</v>
       </c>
       <c r="AB150" t="s">
         <v>39</v>
@@ -13345,13 +13417,13 @@
     </row>
     <row r="151" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>201</v>
+        <v>228</v>
       </c>
       <c r="C151" t="s">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="D151" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="E151" t="s">
         <v>33</v>
@@ -13369,13 +13441,13 @@
         <v>54</v>
       </c>
       <c r="K151" t="s">
-        <v>203</v>
+        <v>40</v>
       </c>
       <c r="L151" t="s">
-        <v>204</v>
+        <v>41</v>
       </c>
       <c r="M151" t="s">
-        <v>205</v>
+        <v>42</v>
       </c>
       <c r="N151" t="s">
         <v>33</v>
@@ -13387,19 +13459,16 @@
         <v>38</v>
       </c>
       <c r="Q151">
-        <v>69.989999999999995</v>
+        <v>59.99</v>
       </c>
       <c r="R151">
-        <v>11.67</v>
+        <v>10</v>
       </c>
       <c r="Y151" t="s">
-        <v>206</v>
-      </c>
-      <c r="Z151" t="s">
-        <v>60</v>
+        <v>231</v>
       </c>
       <c r="AA151" t="s">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="AB151" t="s">
         <v>39</v>
@@ -13413,13 +13482,13 @@
     </row>
     <row r="152" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>195</v>
+        <v>233</v>
       </c>
       <c r="C152" t="s">
-        <v>196</v>
+        <v>234</v>
       </c>
       <c r="D152" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="E152" t="s">
         <v>33</v>
@@ -13434,16 +13503,16 @@
         <v>36</v>
       </c>
       <c r="J152" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K152" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="L152" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="M152" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="N152" t="s">
         <v>33</v>
@@ -13455,19 +13524,16 @@
         <v>38</v>
       </c>
       <c r="Q152">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="R152">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="Y152" t="s">
-        <v>198</v>
-      </c>
-      <c r="Z152" t="s">
-        <v>199</v>
+        <v>236</v>
       </c>
       <c r="AA152" t="s">
-        <v>200</v>
+        <v>237</v>
       </c>
       <c r="AB152" t="s">
         <v>39</v>
@@ -13481,16 +13547,16 @@
     </row>
     <row r="153" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>208</v>
+        <v>242</v>
       </c>
       <c r="C153" t="s">
-        <v>209</v>
+        <v>243</v>
       </c>
       <c r="D153" t="s">
-        <v>210</v>
+        <v>244</v>
       </c>
       <c r="E153" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F153" t="s">
         <v>34</v>
@@ -13502,7 +13568,7 @@
         <v>36</v>
       </c>
       <c r="J153" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K153" t="s">
         <v>40</v>
@@ -13513,26 +13579,14 @@
       <c r="M153" t="s">
         <v>42</v>
       </c>
-      <c r="N153" t="s">
-        <v>33</v>
-      </c>
       <c r="O153">
-        <v>1</v>
-      </c>
-      <c r="P153" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q153">
-        <v>59.99</v>
-      </c>
-      <c r="R153">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y153" t="s">
-        <v>211</v>
+        <v>240</v>
       </c>
       <c r="AA153" t="s">
-        <v>212</v>
+        <v>241</v>
       </c>
       <c r="AB153" t="s">
         <v>39</v>
@@ -13546,13 +13600,13 @@
     </row>
     <row r="154" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>152</v>
+        <v>245</v>
       </c>
       <c r="C154" t="s">
-        <v>153</v>
+        <v>246</v>
       </c>
       <c r="D154" t="s">
-        <v>154</v>
+        <v>247</v>
       </c>
       <c r="E154" t="s">
         <v>33</v>
@@ -13567,16 +13621,16 @@
         <v>36</v>
       </c>
       <c r="J154" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K154" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="L154" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="M154" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="N154" t="s">
         <v>33</v>
@@ -13588,16 +13642,16 @@
         <v>38</v>
       </c>
       <c r="Q154">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R154">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y154" t="s">
-        <v>155</v>
+        <v>248</v>
       </c>
       <c r="AA154" t="s">
-        <v>156</v>
+        <v>249</v>
       </c>
       <c r="AB154" t="s">
         <v>39</v>
@@ -13611,13 +13665,13 @@
     </row>
     <row r="155" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="C155" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="D155" t="s">
-        <v>159</v>
+        <v>250</v>
       </c>
       <c r="E155" t="s">
         <v>33</v>
@@ -13632,16 +13686,16 @@
         <v>36</v>
       </c>
       <c r="J155" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K155" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L155" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M155" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N155" t="s">
         <v>33</v>
@@ -13653,16 +13707,16 @@
         <v>38</v>
       </c>
       <c r="Q155">
-        <v>11.99</v>
+        <v>37.99</v>
       </c>
       <c r="R155">
-        <v>2</v>
+        <v>6.33</v>
       </c>
       <c r="Y155" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="AA155" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AB155" t="s">
         <v>39</v>
@@ -13676,16 +13730,16 @@
     </row>
     <row r="156" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>161</v>
+        <v>191</v>
       </c>
       <c r="C156" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="D156" t="s">
-        <v>163</v>
+        <v>251</v>
       </c>
       <c r="E156" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F156" t="s">
         <v>34</v>
@@ -13708,14 +13762,26 @@
       <c r="M156" t="s">
         <v>42</v>
       </c>
+      <c r="N156" t="s">
+        <v>33</v>
+      </c>
       <c r="O156">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P156" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q156">
+        <v>59.99</v>
+      </c>
+      <c r="R156">
+        <v>10</v>
       </c>
       <c r="Y156" t="s">
-        <v>63</v>
+        <v>193</v>
       </c>
       <c r="AA156" t="s">
-        <v>151</v>
+        <v>194</v>
       </c>
       <c r="AB156" t="s">
         <v>39</v>
@@ -13729,13 +13795,13 @@
     </row>
     <row r="157" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>164</v>
+        <v>201</v>
       </c>
       <c r="C157" t="s">
-        <v>165</v>
+        <v>202</v>
       </c>
       <c r="D157" t="s">
-        <v>166</v>
+        <v>252</v>
       </c>
       <c r="E157" t="s">
         <v>33</v>
@@ -13753,13 +13819,13 @@
         <v>54</v>
       </c>
       <c r="K157" t="s">
-        <v>48</v>
+        <v>203</v>
       </c>
       <c r="L157" t="s">
-        <v>49</v>
+        <v>204</v>
       </c>
       <c r="M157" t="s">
-        <v>50</v>
+        <v>205</v>
       </c>
       <c r="N157" t="s">
         <v>33</v>
@@ -13771,16 +13837,19 @@
         <v>38</v>
       </c>
       <c r="Q157">
-        <v>37.99</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="R157">
-        <v>6.33</v>
+        <v>11.67</v>
       </c>
       <c r="Y157" t="s">
-        <v>100</v>
+        <v>206</v>
+      </c>
+      <c r="Z157" t="s">
+        <v>60</v>
       </c>
       <c r="AA157" t="s">
-        <v>167</v>
+        <v>207</v>
       </c>
       <c r="AB157" t="s">
         <v>39</v>
@@ -13794,13 +13863,13 @@
     </row>
     <row r="158" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="C158" t="s">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="D158" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="E158" t="s">
         <v>33</v>
@@ -13815,16 +13884,16 @@
         <v>36</v>
       </c>
       <c r="J158" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K158" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L158" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M158" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N158" t="s">
         <v>33</v>
@@ -13836,16 +13905,19 @@
         <v>38</v>
       </c>
       <c r="Q158">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R158">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y158" t="s">
-        <v>66</v>
+        <v>198</v>
+      </c>
+      <c r="Z158" t="s">
+        <v>199</v>
       </c>
       <c r="AA158" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="AB158" t="s">
         <v>39</v>
@@ -13859,13 +13931,13 @@
     </row>
     <row r="159" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>172</v>
+        <v>208</v>
       </c>
       <c r="C159" t="s">
-        <v>173</v>
+        <v>209</v>
       </c>
       <c r="D159" t="s">
-        <v>174</v>
+        <v>210</v>
       </c>
       <c r="E159" t="s">
         <v>33</v>
@@ -13880,16 +13952,16 @@
         <v>36</v>
       </c>
       <c r="J159" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K159" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L159" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M159" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="N159" t="s">
         <v>33</v>
@@ -13901,16 +13973,16 @@
         <v>38</v>
       </c>
       <c r="Q159">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R159">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y159" t="s">
-        <v>175</v>
+        <v>211</v>
       </c>
       <c r="AA159" t="s">
-        <v>176</v>
+        <v>212</v>
       </c>
       <c r="AB159" t="s">
         <v>39</v>
@@ -13924,13 +13996,13 @@
     </row>
     <row r="160" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="C160" t="s">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="D160" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="E160" t="s">
         <v>33</v>
@@ -13948,13 +14020,13 @@
         <v>54</v>
       </c>
       <c r="K160" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="L160" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="M160" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="N160" t="s">
         <v>33</v>
@@ -13966,19 +14038,16 @@
         <v>38</v>
       </c>
       <c r="Q160">
-        <v>37.99</v>
+        <v>14.99</v>
       </c>
       <c r="R160">
-        <v>6.33</v>
+        <v>2.5</v>
       </c>
       <c r="Y160" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z160" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="AA160" t="s">
-        <v>182</v>
+        <v>156</v>
       </c>
       <c r="AB160" t="s">
         <v>39</v>
@@ -13992,13 +14061,13 @@
     </row>
     <row r="161" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="C161" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="D161" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="E161" t="s">
         <v>33</v>
@@ -14016,37 +14085,34 @@
         <v>54</v>
       </c>
       <c r="K161" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L161" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M161" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="N161" t="s">
         <v>33</v>
       </c>
       <c r="O161">
+        <v>1</v>
+      </c>
+      <c r="P161" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q161">
+        <v>11.99</v>
+      </c>
+      <c r="R161">
         <v>2</v>
       </c>
-      <c r="P161" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q161">
-        <v>75.98</v>
-      </c>
-      <c r="R161">
-        <v>12.66</v>
-      </c>
       <c r="Y161" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z161" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="AA161" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="AB161" t="s">
         <v>39</v>
@@ -14060,16 +14126,16 @@
     </row>
     <row r="162" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>133</v>
+        <v>161</v>
       </c>
       <c r="C162" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="D162" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="E162" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F162" t="s">
         <v>34</v>
@@ -14084,34 +14150,22 @@
         <v>54</v>
       </c>
       <c r="K162" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L162" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M162" t="s">
-        <v>74</v>
-      </c>
-      <c r="N162" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O162">
-        <v>1</v>
-      </c>
-      <c r="P162" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q162">
-        <v>11.99</v>
-      </c>
-      <c r="R162">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y162" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="AA162" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="AB162" t="s">
         <v>39</v>
@@ -14125,13 +14179,13 @@
     </row>
     <row r="163" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>117</v>
+        <v>164</v>
       </c>
       <c r="C163" t="s">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="D163" t="s">
-        <v>119</v>
+        <v>166</v>
       </c>
       <c r="E163" t="s">
         <v>33</v>
@@ -14149,13 +14203,13 @@
         <v>54</v>
       </c>
       <c r="K163" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="L163" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="M163" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="N163" t="s">
         <v>33</v>
@@ -14167,19 +14221,16 @@
         <v>38</v>
       </c>
       <c r="Q163">
-        <v>14.99</v>
+        <v>37.99</v>
       </c>
       <c r="R163">
-        <v>2.5</v>
+        <v>6.33</v>
       </c>
       <c r="Y163" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z163" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="AA163" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="AB163" t="s">
         <v>39</v>
@@ -14193,13 +14244,13 @@
     </row>
     <row r="164" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>123</v>
+        <v>168</v>
       </c>
       <c r="C164" t="s">
-        <v>124</v>
+        <v>169</v>
       </c>
       <c r="D164" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="E164" t="s">
         <v>33</v>
@@ -14217,13 +14268,13 @@
         <v>54</v>
       </c>
       <c r="K164" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L164" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M164" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N164" t="s">
         <v>33</v>
@@ -14235,19 +14286,16 @@
         <v>38</v>
       </c>
       <c r="Q164">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R164">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y164" t="s">
-        <v>126</v>
-      </c>
-      <c r="Z164" t="s">
-        <v>127</v>
+        <v>66</v>
       </c>
       <c r="AA164" t="s">
-        <v>128</v>
+        <v>171</v>
       </c>
       <c r="AB164" t="s">
         <v>39</v>
@@ -14261,13 +14309,13 @@
     </row>
     <row r="165" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>129</v>
+        <v>172</v>
       </c>
       <c r="C165" t="s">
-        <v>130</v>
+        <v>173</v>
       </c>
       <c r="D165" t="s">
-        <v>131</v>
+        <v>174</v>
       </c>
       <c r="E165" t="s">
         <v>33</v>
@@ -14285,13 +14333,13 @@
         <v>54</v>
       </c>
       <c r="K165" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="L165" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="M165" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="N165" t="s">
         <v>33</v>
@@ -14303,16 +14351,16 @@
         <v>38</v>
       </c>
       <c r="Q165">
-        <v>38.49</v>
+        <v>14.99</v>
       </c>
       <c r="R165">
-        <v>6.42</v>
+        <v>2.5</v>
       </c>
       <c r="Y165" t="s">
-        <v>78</v>
+        <v>175</v>
       </c>
       <c r="AA165" t="s">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="AB165" t="s">
         <v>39</v>
@@ -14326,16 +14374,16 @@
     </row>
     <row r="166" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>105</v>
+        <v>177</v>
       </c>
       <c r="C166" t="s">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="D166" t="s">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="E166" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F166" t="s">
         <v>34</v>
@@ -14350,22 +14398,37 @@
         <v>54</v>
       </c>
       <c r="K166" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="L166" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="M166" t="s">
-        <v>83</v>
+        <v>50</v>
+      </c>
+      <c r="N166" t="s">
+        <v>33</v>
       </c>
       <c r="O166">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P166" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q166">
+        <v>37.99</v>
+      </c>
+      <c r="R166">
+        <v>6.33</v>
       </c>
       <c r="Y166" t="s">
-        <v>103</v>
+        <v>180</v>
+      </c>
+      <c r="Z166" t="s">
+        <v>181</v>
       </c>
       <c r="AA166" t="s">
-        <v>104</v>
+        <v>182</v>
       </c>
       <c r="AB166" t="s">
         <v>39</v>
@@ -14379,13 +14442,13 @@
     </row>
     <row r="167" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>107</v>
+        <v>183</v>
       </c>
       <c r="C167" t="s">
-        <v>108</v>
+        <v>184</v>
       </c>
       <c r="D167" t="s">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="E167" t="s">
         <v>33</v>
@@ -14415,25 +14478,25 @@
         <v>33</v>
       </c>
       <c r="O167">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P167" t="s">
         <v>38</v>
       </c>
       <c r="Q167">
-        <v>37.99</v>
+        <v>75.98</v>
       </c>
       <c r="R167">
-        <v>6.33</v>
+        <v>12.66</v>
       </c>
       <c r="Y167" t="s">
-        <v>109</v>
+        <v>70</v>
       </c>
       <c r="Z167" t="s">
-        <v>110</v>
+        <v>47</v>
       </c>
       <c r="AA167" t="s">
-        <v>111</v>
+        <v>185</v>
       </c>
       <c r="AB167" t="s">
         <v>39</v>
@@ -14447,13 +14510,13 @@
     </row>
     <row r="168" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="C168" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="D168" t="s">
-        <v>114</v>
+        <v>186</v>
       </c>
       <c r="E168" t="s">
         <v>33</v>
@@ -14468,16 +14531,16 @@
         <v>36</v>
       </c>
       <c r="J168" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K168" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L168" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M168" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N168" t="s">
         <v>33</v>
@@ -14489,19 +14552,16 @@
         <v>38</v>
       </c>
       <c r="Q168">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R168">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y168" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z168" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="AA168" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="AB168" t="s">
         <v>39</v>
@@ -14515,66 +14575,456 @@
     </row>
     <row r="169" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
+        <v>117</v>
+      </c>
+      <c r="C169" t="s">
+        <v>118</v>
+      </c>
+      <c r="D169" t="s">
+        <v>119</v>
+      </c>
+      <c r="E169" t="s">
+        <v>33</v>
+      </c>
+      <c r="F169" t="s">
+        <v>34</v>
+      </c>
+      <c r="G169" t="s">
+        <v>35</v>
+      </c>
+      <c r="H169" t="s">
+        <v>36</v>
+      </c>
+      <c r="J169" t="s">
+        <v>54</v>
+      </c>
+      <c r="K169" t="s">
+        <v>94</v>
+      </c>
+      <c r="L169" t="s">
+        <v>82</v>
+      </c>
+      <c r="M169" t="s">
+        <v>83</v>
+      </c>
+      <c r="N169" t="s">
+        <v>33</v>
+      </c>
+      <c r="O169">
+        <v>1</v>
+      </c>
+      <c r="P169" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q169">
+        <v>14.99</v>
+      </c>
+      <c r="R169">
+        <v>2.5</v>
+      </c>
+      <c r="Y169" t="s">
+        <v>120</v>
+      </c>
+      <c r="Z169" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA169" t="s">
+        <v>122</v>
+      </c>
+      <c r="AB169" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG169" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>123</v>
+      </c>
+      <c r="C170" t="s">
+        <v>124</v>
+      </c>
+      <c r="D170" t="s">
+        <v>125</v>
+      </c>
+      <c r="E170" t="s">
+        <v>33</v>
+      </c>
+      <c r="F170" t="s">
+        <v>34</v>
+      </c>
+      <c r="G170" t="s">
+        <v>35</v>
+      </c>
+      <c r="H170" t="s">
+        <v>36</v>
+      </c>
+      <c r="J170" t="s">
+        <v>54</v>
+      </c>
+      <c r="K170" t="s">
+        <v>40</v>
+      </c>
+      <c r="L170" t="s">
+        <v>41</v>
+      </c>
+      <c r="M170" t="s">
+        <v>42</v>
+      </c>
+      <c r="N170" t="s">
+        <v>33</v>
+      </c>
+      <c r="O170">
+        <v>1</v>
+      </c>
+      <c r="P170" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q170">
+        <v>59.99</v>
+      </c>
+      <c r="R170">
+        <v>10</v>
+      </c>
+      <c r="Y170" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z170" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA170" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB170" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG170" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>129</v>
+      </c>
+      <c r="C171" t="s">
+        <v>130</v>
+      </c>
+      <c r="D171" t="s">
+        <v>131</v>
+      </c>
+      <c r="E171" t="s">
+        <v>33</v>
+      </c>
+      <c r="F171" t="s">
+        <v>34</v>
+      </c>
+      <c r="G171" t="s">
+        <v>35</v>
+      </c>
+      <c r="H171" t="s">
+        <v>36</v>
+      </c>
+      <c r="J171" t="s">
+        <v>54</v>
+      </c>
+      <c r="K171" t="s">
+        <v>43</v>
+      </c>
+      <c r="L171" t="s">
+        <v>44</v>
+      </c>
+      <c r="M171" t="s">
+        <v>45</v>
+      </c>
+      <c r="N171" t="s">
+        <v>33</v>
+      </c>
+      <c r="O171">
+        <v>1</v>
+      </c>
+      <c r="P171" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q171">
+        <v>38.49</v>
+      </c>
+      <c r="R171">
+        <v>6.42</v>
+      </c>
+      <c r="Y171" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA171" t="s">
+        <v>132</v>
+      </c>
+      <c r="AB171" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG171" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>105</v>
+      </c>
+      <c r="C172" t="s">
+        <v>106</v>
+      </c>
+      <c r="D172" t="s">
+        <v>136</v>
+      </c>
+      <c r="E172" t="s">
+        <v>53</v>
+      </c>
+      <c r="F172" t="s">
+        <v>34</v>
+      </c>
+      <c r="G172" t="s">
+        <v>35</v>
+      </c>
+      <c r="H172" t="s">
+        <v>36</v>
+      </c>
+      <c r="J172" t="s">
+        <v>54</v>
+      </c>
+      <c r="K172" t="s">
+        <v>94</v>
+      </c>
+      <c r="L172" t="s">
+        <v>82</v>
+      </c>
+      <c r="M172" t="s">
+        <v>83</v>
+      </c>
+      <c r="O172">
+        <v>0</v>
+      </c>
+      <c r="Y172" t="s">
+        <v>103</v>
+      </c>
+      <c r="AA172" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB172" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG172" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>107</v>
+      </c>
+      <c r="C173" t="s">
+        <v>108</v>
+      </c>
+      <c r="D173" t="s">
+        <v>137</v>
+      </c>
+      <c r="E173" t="s">
+        <v>33</v>
+      </c>
+      <c r="F173" t="s">
+        <v>34</v>
+      </c>
+      <c r="G173" t="s">
+        <v>35</v>
+      </c>
+      <c r="H173" t="s">
+        <v>36</v>
+      </c>
+      <c r="J173" t="s">
+        <v>54</v>
+      </c>
+      <c r="K173" t="s">
+        <v>48</v>
+      </c>
+      <c r="L173" t="s">
+        <v>49</v>
+      </c>
+      <c r="M173" t="s">
+        <v>50</v>
+      </c>
+      <c r="N173" t="s">
+        <v>33</v>
+      </c>
+      <c r="O173">
+        <v>1</v>
+      </c>
+      <c r="P173" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q173">
+        <v>37.99</v>
+      </c>
+      <c r="R173">
+        <v>6.33</v>
+      </c>
+      <c r="Y173" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z173" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA173" t="s">
+        <v>111</v>
+      </c>
+      <c r="AB173" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG173" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>112</v>
+      </c>
+      <c r="C174" t="s">
+        <v>113</v>
+      </c>
+      <c r="D174" t="s">
+        <v>114</v>
+      </c>
+      <c r="E174" t="s">
+        <v>33</v>
+      </c>
+      <c r="F174" t="s">
+        <v>34</v>
+      </c>
+      <c r="G174" t="s">
+        <v>35</v>
+      </c>
+      <c r="H174" t="s">
+        <v>36</v>
+      </c>
+      <c r="J174" t="s">
+        <v>37</v>
+      </c>
+      <c r="K174" t="s">
+        <v>40</v>
+      </c>
+      <c r="L174" t="s">
+        <v>41</v>
+      </c>
+      <c r="M174" t="s">
+        <v>42</v>
+      </c>
+      <c r="N174" t="s">
+        <v>33</v>
+      </c>
+      <c r="O174">
+        <v>1</v>
+      </c>
+      <c r="P174" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q174">
+        <v>59.99</v>
+      </c>
+      <c r="R174">
+        <v>10</v>
+      </c>
+      <c r="Y174" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z174" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA174" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB174" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG174" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
         <v>703</v>
       </c>
-      <c r="C169" t="s">
+      <c r="C175" t="s">
         <v>704</v>
       </c>
-      <c r="D169" t="s">
+      <c r="D175" t="s">
         <v>705</v>
       </c>
-      <c r="E169" t="s">
-        <v>33</v>
-      </c>
-      <c r="F169" t="s">
-        <v>34</v>
-      </c>
-      <c r="G169" t="s">
-        <v>35</v>
-      </c>
-      <c r="H169" t="s">
-        <v>36</v>
-      </c>
-      <c r="J169" t="s">
-        <v>54</v>
-      </c>
-      <c r="K169" t="s">
+      <c r="E175" t="s">
+        <v>33</v>
+      </c>
+      <c r="F175" t="s">
+        <v>34</v>
+      </c>
+      <c r="G175" t="s">
+        <v>35</v>
+      </c>
+      <c r="H175" t="s">
+        <v>36</v>
+      </c>
+      <c r="J175" t="s">
+        <v>54</v>
+      </c>
+      <c r="K175" t="s">
         <v>72</v>
       </c>
-      <c r="L169" t="s">
+      <c r="L175" t="s">
         <v>73</v>
       </c>
-      <c r="M169" t="s">
+      <c r="M175" t="s">
         <v>74</v>
       </c>
-      <c r="N169" t="s">
-        <v>33</v>
-      </c>
-      <c r="O169">
-        <v>1</v>
-      </c>
-      <c r="P169" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q169">
+      <c r="N175" t="s">
+        <v>33</v>
+      </c>
+      <c r="O175">
+        <v>1</v>
+      </c>
+      <c r="P175" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q175">
         <v>11.99</v>
       </c>
-      <c r="R169">
+      <c r="R175">
         <v>2</v>
       </c>
-      <c r="Y169" t="s">
+      <c r="Y175" t="s">
         <v>706</v>
       </c>
-      <c r="AA169" t="s">
+      <c r="AA175" t="s">
         <v>707</v>
       </c>
-      <c r="AB169" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD169" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG169" t="b">
+      <c r="AB175" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG175" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Raw Sales Data/Amazon.xlsx
+++ b/Raw Sales Data/Amazon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2842" uniqueCount="917">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2891" uniqueCount="932">
   <si>
     <t>amazon-order-id</t>
   </si>
@@ -2770,6 +2770,51 @@
   </si>
   <si>
     <t>PE11 3EP</t>
+  </si>
+  <si>
+    <t>203-9761887-0677949</t>
+  </si>
+  <si>
+    <t>2026-03-12T20:56:35+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-12T21:26:46+00:00</t>
+  </si>
+  <si>
+    <t>NEATH</t>
+  </si>
+  <si>
+    <t>SA11 5RP</t>
+  </si>
+  <si>
+    <t>204-7566724-3728328</t>
+  </si>
+  <si>
+    <t>2026-03-12T12:39:18+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-12T17:22:04+00:00</t>
+  </si>
+  <si>
+    <t>Truro</t>
+  </si>
+  <si>
+    <t>TR2 5TE</t>
+  </si>
+  <si>
+    <t>202-1381924-8562718</t>
+  </si>
+  <si>
+    <t>2026-03-12T12:11:12+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-12T12:40:24+00:00</t>
+  </si>
+  <si>
+    <t>DOWNPATRICK</t>
+  </si>
+  <si>
+    <t>BT30 8HX</t>
   </si>
 </sst>
 </file>
@@ -3576,7 +3621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG175"/>
+  <dimension ref="A1:AG178"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
@@ -3687,13 +3732,13 @@
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>891</v>
+        <v>917</v>
       </c>
       <c r="C2" t="s">
-        <v>892</v>
+        <v>918</v>
       </c>
       <c r="D2" t="s">
-        <v>893</v>
+        <v>919</v>
       </c>
       <c r="E2" t="s">
         <v>98</v>
@@ -3735,10 +3780,10 @@
         <v>11.33</v>
       </c>
       <c r="Y2" t="s">
-        <v>894</v>
+        <v>920</v>
       </c>
       <c r="AA2" t="s">
-        <v>895</v>
+        <v>921</v>
       </c>
       <c r="AB2" t="s">
         <v>39</v>
@@ -3752,16 +3797,16 @@
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>896</v>
+        <v>922</v>
       </c>
       <c r="C3" t="s">
-        <v>897</v>
+        <v>923</v>
       </c>
       <c r="D3" t="s">
-        <v>898</v>
+        <v>924</v>
       </c>
       <c r="E3" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F3" t="s">
         <v>34</v>
@@ -3784,14 +3829,29 @@
       <c r="M3" t="s">
         <v>42</v>
       </c>
+      <c r="N3" t="s">
+        <v>33</v>
+      </c>
       <c r="O3">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P3" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q3">
+        <v>67.989999999999995</v>
+      </c>
+      <c r="R3">
+        <v>11.33</v>
       </c>
       <c r="Y3" t="s">
-        <v>894</v>
+        <v>925</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>619</v>
       </c>
       <c r="AA3" t="s">
-        <v>895</v>
+        <v>926</v>
       </c>
       <c r="AB3" t="s">
         <v>39</v>
@@ -3805,16 +3865,16 @@
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>899</v>
+        <v>927</v>
       </c>
       <c r="C4" t="s">
-        <v>900</v>
+        <v>928</v>
       </c>
       <c r="D4" t="s">
-        <v>901</v>
+        <v>929</v>
       </c>
       <c r="E4" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="F4" t="s">
         <v>34</v>
@@ -3837,14 +3897,32 @@
       <c r="M4" t="s">
         <v>42</v>
       </c>
+      <c r="N4" t="s">
+        <v>99</v>
+      </c>
       <c r="O4">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P4" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q4">
+        <v>67.989999999999995</v>
+      </c>
+      <c r="R4">
+        <v>11.33</v>
+      </c>
+      <c r="S4">
+        <v>6.99</v>
+      </c>
+      <c r="T4">
+        <v>1.17</v>
       </c>
       <c r="Y4" t="s">
-        <v>894</v>
+        <v>930</v>
       </c>
       <c r="AA4" t="s">
-        <v>895</v>
+        <v>931</v>
       </c>
       <c r="AB4" t="s">
         <v>39</v>
@@ -3858,13 +3936,13 @@
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>902</v>
+        <v>891</v>
       </c>
       <c r="C5" t="s">
-        <v>903</v>
+        <v>892</v>
       </c>
       <c r="D5" t="s">
-        <v>904</v>
+        <v>893</v>
       </c>
       <c r="E5" t="s">
         <v>98</v>
@@ -3882,13 +3960,13 @@
         <v>54</v>
       </c>
       <c r="K5" t="s">
-        <v>905</v>
+        <v>40</v>
       </c>
       <c r="L5" t="s">
-        <v>906</v>
+        <v>41</v>
       </c>
       <c r="M5" t="s">
-        <v>907</v>
+        <v>42</v>
       </c>
       <c r="N5" t="s">
         <v>99</v>
@@ -3900,7 +3978,10 @@
         <v>38</v>
       </c>
       <c r="Q5">
-        <v>69.989999999999995</v>
+        <v>67.989999999999995</v>
+      </c>
+      <c r="R5">
+        <v>11.33</v>
       </c>
       <c r="Y5" t="s">
         <v>894</v>
@@ -3912,7 +3993,7 @@
         <v>39</v>
       </c>
       <c r="AD5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
@@ -3920,16 +4001,16 @@
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>908</v>
+        <v>896</v>
       </c>
       <c r="C6" t="s">
-        <v>909</v>
+        <v>897</v>
       </c>
       <c r="D6" t="s">
-        <v>910</v>
+        <v>898</v>
       </c>
       <c r="E6" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="F6" t="s">
         <v>34</v>
@@ -3952,32 +4033,14 @@
       <c r="M6" t="s">
         <v>42</v>
       </c>
-      <c r="N6" t="s">
-        <v>99</v>
-      </c>
       <c r="O6">
-        <v>1</v>
-      </c>
-      <c r="P6" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q6">
-        <v>67.989999999999995</v>
-      </c>
-      <c r="R6">
-        <v>11.33</v>
-      </c>
-      <c r="S6">
-        <v>6.99</v>
-      </c>
-      <c r="T6">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>911</v>
+        <v>894</v>
       </c>
       <c r="AA6" t="s">
-        <v>912</v>
+        <v>895</v>
       </c>
       <c r="AB6" t="s">
         <v>39</v>
@@ -3991,16 +4054,16 @@
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>913</v>
+        <v>899</v>
       </c>
       <c r="C7" t="s">
-        <v>914</v>
+        <v>900</v>
       </c>
       <c r="D7" t="s">
-        <v>915</v>
+        <v>901</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F7" t="s">
         <v>34</v>
@@ -4015,37 +4078,22 @@
         <v>54</v>
       </c>
       <c r="K7" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L7" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M7" t="s">
-        <v>50</v>
-      </c>
-      <c r="N7" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O7">
-        <v>1</v>
-      </c>
-      <c r="P7" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q7">
-        <v>40.99</v>
-      </c>
-      <c r="R7">
-        <v>6.83</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>420</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>76</v>
+        <v>894</v>
       </c>
       <c r="AA7" t="s">
-        <v>916</v>
+        <v>895</v>
       </c>
       <c r="AB7" t="s">
         <v>39</v>
@@ -4059,16 +4107,16 @@
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>869</v>
+        <v>902</v>
       </c>
       <c r="C8" t="s">
-        <v>870</v>
+        <v>903</v>
       </c>
       <c r="D8" t="s">
-        <v>871</v>
+        <v>904</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F8" t="s">
         <v>34</v>
@@ -4083,16 +4131,16 @@
         <v>54</v>
       </c>
       <c r="K8" t="s">
-        <v>40</v>
+        <v>905</v>
       </c>
       <c r="L8" t="s">
-        <v>41</v>
+        <v>906</v>
       </c>
       <c r="M8" t="s">
-        <v>42</v>
+        <v>907</v>
       </c>
       <c r="N8" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O8">
         <v>1</v>
@@ -4101,25 +4149,19 @@
         <v>38</v>
       </c>
       <c r="Q8">
-        <v>67.989999999999995</v>
-      </c>
-      <c r="R8">
-        <v>11.33</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="Y8" t="s">
-        <v>872</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>873</v>
+        <v>894</v>
       </c>
       <c r="AA8" t="s">
-        <v>874</v>
+        <v>895</v>
       </c>
       <c r="AB8" t="s">
         <v>39</v>
       </c>
       <c r="AD8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG8" t="b">
         <v>0</v>
@@ -4127,16 +4169,16 @@
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>875</v>
+        <v>908</v>
       </c>
       <c r="C9" t="s">
-        <v>876</v>
+        <v>909</v>
       </c>
       <c r="D9" t="s">
-        <v>877</v>
+        <v>910</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F9" t="s">
         <v>34</v>
@@ -4160,7 +4202,7 @@
         <v>42</v>
       </c>
       <c r="N9" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O9">
         <v>1</v>
@@ -4174,11 +4216,17 @@
       <c r="R9">
         <v>11.33</v>
       </c>
+      <c r="S9">
+        <v>6.99</v>
+      </c>
+      <c r="T9">
+        <v>1.17</v>
+      </c>
       <c r="Y9" t="s">
-        <v>878</v>
+        <v>911</v>
       </c>
       <c r="AA9" t="s">
-        <v>879</v>
+        <v>912</v>
       </c>
       <c r="AB9" t="s">
         <v>39</v>
@@ -4192,13 +4240,13 @@
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>880</v>
+        <v>913</v>
       </c>
       <c r="C10" t="s">
-        <v>881</v>
+        <v>914</v>
       </c>
       <c r="D10" t="s">
-        <v>882</v>
+        <v>915</v>
       </c>
       <c r="E10" t="s">
         <v>33</v>
@@ -4216,13 +4264,13 @@
         <v>54</v>
       </c>
       <c r="K10" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L10" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M10" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N10" t="s">
         <v>33</v>
@@ -4234,16 +4282,19 @@
         <v>38</v>
       </c>
       <c r="Q10">
-        <v>65.989999999999995</v>
+        <v>40.99</v>
       </c>
       <c r="R10">
-        <v>11</v>
+        <v>6.83</v>
       </c>
       <c r="Y10" t="s">
-        <v>883</v>
+        <v>420</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>76</v>
       </c>
       <c r="AA10" t="s">
-        <v>884</v>
+        <v>916</v>
       </c>
       <c r="AB10" t="s">
         <v>39</v>
@@ -4257,13 +4308,13 @@
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>885</v>
+        <v>869</v>
       </c>
       <c r="C11" t="s">
-        <v>886</v>
+        <v>870</v>
       </c>
       <c r="D11" t="s">
-        <v>887</v>
+        <v>871</v>
       </c>
       <c r="E11" t="s">
         <v>33</v>
@@ -4299,19 +4350,19 @@
         <v>38</v>
       </c>
       <c r="Q11">
-        <v>65.989999999999995</v>
+        <v>67.989999999999995</v>
       </c>
       <c r="R11">
-        <v>11</v>
+        <v>11.33</v>
       </c>
       <c r="Y11" t="s">
-        <v>888</v>
+        <v>872</v>
       </c>
       <c r="Z11" t="s">
-        <v>889</v>
+        <v>873</v>
       </c>
       <c r="AA11" t="s">
-        <v>890</v>
+        <v>874</v>
       </c>
       <c r="AB11" t="s">
         <v>39</v>
@@ -4325,13 +4376,13 @@
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>864</v>
+        <v>875</v>
       </c>
       <c r="C12" t="s">
-        <v>865</v>
+        <v>876</v>
       </c>
       <c r="D12" t="s">
-        <v>866</v>
+        <v>877</v>
       </c>
       <c r="E12" t="s">
         <v>33</v>
@@ -4367,16 +4418,16 @@
         <v>38</v>
       </c>
       <c r="Q12">
-        <v>65.989999999999995</v>
+        <v>67.989999999999995</v>
       </c>
       <c r="R12">
-        <v>11</v>
+        <v>11.33</v>
       </c>
       <c r="Y12" t="s">
-        <v>867</v>
+        <v>878</v>
       </c>
       <c r="AA12" t="s">
-        <v>868</v>
+        <v>879</v>
       </c>
       <c r="AB12" t="s">
         <v>39</v>
@@ -4390,13 +4441,13 @@
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>846</v>
+        <v>880</v>
       </c>
       <c r="C13" t="s">
-        <v>847</v>
+        <v>881</v>
       </c>
       <c r="D13" t="s">
-        <v>848</v>
+        <v>882</v>
       </c>
       <c r="E13" t="s">
         <v>33</v>
@@ -4437,20 +4488,11 @@
       <c r="R13">
         <v>11</v>
       </c>
-      <c r="S13">
-        <v>6.99</v>
-      </c>
-      <c r="T13">
-        <v>1.17</v>
-      </c>
       <c r="Y13" t="s">
-        <v>849</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>850</v>
+        <v>883</v>
       </c>
       <c r="AA13" t="s">
-        <v>851</v>
+        <v>884</v>
       </c>
       <c r="AB13" t="s">
         <v>39</v>
@@ -4464,16 +4506,16 @@
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>852</v>
+        <v>885</v>
       </c>
       <c r="C14" t="s">
-        <v>853</v>
+        <v>886</v>
       </c>
       <c r="D14" t="s">
-        <v>854</v>
+        <v>887</v>
       </c>
       <c r="E14" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F14" t="s">
         <v>34</v>
@@ -4496,14 +4538,29 @@
       <c r="M14" t="s">
         <v>42</v>
       </c>
+      <c r="N14" t="s">
+        <v>33</v>
+      </c>
       <c r="O14">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P14" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q14">
+        <v>65.989999999999995</v>
+      </c>
+      <c r="R14">
+        <v>11</v>
       </c>
       <c r="Y14" t="s">
-        <v>855</v>
+        <v>888</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>889</v>
       </c>
       <c r="AA14" t="s">
-        <v>856</v>
+        <v>890</v>
       </c>
       <c r="AB14" t="s">
         <v>39</v>
@@ -4517,13 +4574,13 @@
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>857</v>
+        <v>864</v>
       </c>
       <c r="C15" t="s">
-        <v>858</v>
+        <v>865</v>
       </c>
       <c r="D15" t="s">
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="E15" t="s">
         <v>33</v>
@@ -4565,10 +4622,10 @@
         <v>11</v>
       </c>
       <c r="Y15" t="s">
-        <v>860</v>
+        <v>867</v>
       </c>
       <c r="AA15" t="s">
-        <v>861</v>
+        <v>868</v>
       </c>
       <c r="AB15" t="s">
         <v>39</v>
@@ -4582,13 +4639,13 @@
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>837</v>
+        <v>846</v>
       </c>
       <c r="C16" t="s">
-        <v>838</v>
+        <v>847</v>
       </c>
       <c r="D16" t="s">
-        <v>862</v>
+        <v>848</v>
       </c>
       <c r="E16" t="s">
         <v>33</v>
@@ -4606,13 +4663,13 @@
         <v>54</v>
       </c>
       <c r="K16" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L16" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M16" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N16" t="s">
         <v>33</v>
@@ -4624,16 +4681,25 @@
         <v>38</v>
       </c>
       <c r="Q16">
-        <v>40.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R16">
-        <v>6.83</v>
+        <v>11</v>
+      </c>
+      <c r="S16">
+        <v>6.99</v>
+      </c>
+      <c r="T16">
+        <v>1.17</v>
       </c>
       <c r="Y16" t="s">
-        <v>305</v>
+        <v>849</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>850</v>
       </c>
       <c r="AA16" t="s">
-        <v>840</v>
+        <v>851</v>
       </c>
       <c r="AB16" t="s">
         <v>39</v>
@@ -4647,16 +4713,16 @@
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>841</v>
+        <v>852</v>
       </c>
       <c r="C17" t="s">
-        <v>842</v>
+        <v>853</v>
       </c>
       <c r="D17" t="s">
-        <v>863</v>
+        <v>854</v>
       </c>
       <c r="E17" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F17" t="s">
         <v>34</v>
@@ -4679,32 +4745,14 @@
       <c r="M17" t="s">
         <v>42</v>
       </c>
-      <c r="N17" t="s">
-        <v>33</v>
-      </c>
       <c r="O17">
-        <v>1</v>
-      </c>
-      <c r="P17" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q17">
-        <v>65.989999999999995</v>
-      </c>
-      <c r="R17">
-        <v>11</v>
-      </c>
-      <c r="S17">
-        <v>6.99</v>
-      </c>
-      <c r="T17">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="s">
-        <v>844</v>
+        <v>855</v>
       </c>
       <c r="AA17" t="s">
-        <v>845</v>
+        <v>856</v>
       </c>
       <c r="AB17" t="s">
         <v>39</v>
@@ -4718,16 +4766,16 @@
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>837</v>
+        <v>857</v>
       </c>
       <c r="C18" t="s">
-        <v>838</v>
+        <v>858</v>
       </c>
       <c r="D18" t="s">
-        <v>839</v>
+        <v>859</v>
       </c>
       <c r="E18" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F18" t="s">
         <v>34</v>
@@ -4742,16 +4790,16 @@
         <v>54</v>
       </c>
       <c r="K18" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L18" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M18" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N18" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O18">
         <v>1</v>
@@ -4760,16 +4808,16 @@
         <v>38</v>
       </c>
       <c r="Q18">
-        <v>40.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R18">
-        <v>6.83</v>
+        <v>11</v>
       </c>
       <c r="Y18" t="s">
-        <v>305</v>
+        <v>860</v>
       </c>
       <c r="AA18" t="s">
-        <v>840</v>
+        <v>861</v>
       </c>
       <c r="AB18" t="s">
         <v>39</v>
@@ -4783,16 +4831,16 @@
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="C19" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="D19" t="s">
-        <v>843</v>
+        <v>862</v>
       </c>
       <c r="E19" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F19" t="s">
         <v>34</v>
@@ -4807,16 +4855,16 @@
         <v>54</v>
       </c>
       <c r="K19" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L19" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M19" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N19" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O19">
         <v>1</v>
@@ -4825,22 +4873,16 @@
         <v>38</v>
       </c>
       <c r="Q19">
-        <v>65.989999999999995</v>
+        <v>40.99</v>
       </c>
       <c r="R19">
-        <v>11</v>
-      </c>
-      <c r="S19">
-        <v>6.99</v>
-      </c>
-      <c r="T19">
-        <v>1.17</v>
+        <v>6.83</v>
       </c>
       <c r="Y19" t="s">
-        <v>844</v>
+        <v>305</v>
       </c>
       <c r="AA19" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="AB19" t="s">
         <v>39</v>
@@ -4854,16 +4896,16 @@
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>819</v>
+        <v>841</v>
       </c>
       <c r="C20" t="s">
-        <v>820</v>
+        <v>842</v>
       </c>
       <c r="D20" t="s">
-        <v>821</v>
+        <v>863</v>
       </c>
       <c r="E20" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F20" t="s">
         <v>34</v>
@@ -4878,16 +4920,16 @@
         <v>54</v>
       </c>
       <c r="K20" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L20" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M20" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N20" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O20">
         <v>1</v>
@@ -4896,19 +4938,22 @@
         <v>38</v>
       </c>
       <c r="Q20">
-        <v>40.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R20">
-        <v>6.83</v>
+        <v>11</v>
+      </c>
+      <c r="S20">
+        <v>6.99</v>
+      </c>
+      <c r="T20">
+        <v>1.17</v>
       </c>
       <c r="Y20" t="s">
-        <v>618</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>619</v>
+        <v>844</v>
       </c>
       <c r="AA20" t="s">
-        <v>620</v>
+        <v>845</v>
       </c>
       <c r="AB20" t="s">
         <v>39</v>
@@ -4922,13 +4967,13 @@
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>822</v>
+        <v>837</v>
       </c>
       <c r="C21" t="s">
-        <v>823</v>
+        <v>838</v>
       </c>
       <c r="D21" t="s">
-        <v>824</v>
+        <v>839</v>
       </c>
       <c r="E21" t="s">
         <v>98</v>
@@ -4946,13 +4991,13 @@
         <v>54</v>
       </c>
       <c r="K21" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L21" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M21" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N21" t="s">
         <v>99</v>
@@ -4964,16 +5009,16 @@
         <v>38</v>
       </c>
       <c r="Q21">
-        <v>14.99</v>
+        <v>40.99</v>
       </c>
       <c r="R21">
-        <v>2.5</v>
+        <v>6.83</v>
       </c>
       <c r="Y21" t="s">
-        <v>825</v>
+        <v>305</v>
       </c>
       <c r="AA21" t="s">
-        <v>826</v>
+        <v>840</v>
       </c>
       <c r="AB21" t="s">
         <v>39</v>
@@ -4987,13 +5032,13 @@
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>827</v>
+        <v>841</v>
       </c>
       <c r="C22" t="s">
-        <v>828</v>
+        <v>842</v>
       </c>
       <c r="D22" t="s">
-        <v>829</v>
+        <v>843</v>
       </c>
       <c r="E22" t="s">
         <v>98</v>
@@ -5031,14 +5076,20 @@
       <c r="Q22">
         <v>65.989999999999995</v>
       </c>
+      <c r="R22">
+        <v>11</v>
+      </c>
       <c r="S22">
         <v>6.99</v>
       </c>
+      <c r="T22">
+        <v>1.17</v>
+      </c>
       <c r="Y22" t="s">
-        <v>830</v>
+        <v>844</v>
       </c>
       <c r="AA22" t="s">
-        <v>831</v>
+        <v>845</v>
       </c>
       <c r="AB22" t="s">
         <v>39</v>
@@ -5052,16 +5103,16 @@
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>832</v>
+        <v>819</v>
       </c>
       <c r="C23" t="s">
-        <v>833</v>
+        <v>820</v>
       </c>
       <c r="D23" t="s">
-        <v>834</v>
+        <v>821</v>
       </c>
       <c r="E23" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F23" t="s">
         <v>34</v>
@@ -5076,16 +5127,16 @@
         <v>54</v>
       </c>
       <c r="K23" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L23" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M23" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N23" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O23">
         <v>1</v>
@@ -5094,16 +5145,19 @@
         <v>38</v>
       </c>
       <c r="Q23">
-        <v>65.989999999999995</v>
+        <v>40.99</v>
       </c>
       <c r="R23">
-        <v>11</v>
+        <v>6.83</v>
       </c>
       <c r="Y23" t="s">
-        <v>835</v>
+        <v>618</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>619</v>
       </c>
       <c r="AA23" t="s">
-        <v>836</v>
+        <v>620</v>
       </c>
       <c r="AB23" t="s">
         <v>39</v>
@@ -5117,16 +5171,16 @@
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>780</v>
+        <v>822</v>
       </c>
       <c r="C24" t="s">
-        <v>781</v>
+        <v>823</v>
       </c>
       <c r="D24" t="s">
-        <v>782</v>
+        <v>824</v>
       </c>
       <c r="E24" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F24" t="s">
         <v>34</v>
@@ -5141,16 +5195,16 @@
         <v>54</v>
       </c>
       <c r="K24" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L24" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M24" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N24" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O24">
         <v>1</v>
@@ -5159,16 +5213,16 @@
         <v>38</v>
       </c>
       <c r="Q24">
-        <v>65.989999999999995</v>
+        <v>14.99</v>
       </c>
       <c r="R24">
-        <v>11</v>
+        <v>2.5</v>
       </c>
       <c r="Y24" t="s">
-        <v>783</v>
+        <v>825</v>
       </c>
       <c r="AA24" t="s">
-        <v>784</v>
+        <v>826</v>
       </c>
       <c r="AB24" t="s">
         <v>39</v>
@@ -5182,16 +5236,16 @@
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>785</v>
+        <v>827</v>
       </c>
       <c r="C25" t="s">
-        <v>786</v>
+        <v>828</v>
       </c>
       <c r="D25" t="s">
-        <v>787</v>
+        <v>829</v>
       </c>
       <c r="E25" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F25" t="s">
         <v>34</v>
@@ -5206,16 +5260,16 @@
         <v>54</v>
       </c>
       <c r="K25" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L25" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M25" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N25" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O25">
         <v>1</v>
@@ -5224,16 +5278,16 @@
         <v>38</v>
       </c>
       <c r="Q25">
-        <v>40.99</v>
-      </c>
-      <c r="R25">
-        <v>6.83</v>
+        <v>65.989999999999995</v>
+      </c>
+      <c r="S25">
+        <v>6.99</v>
       </c>
       <c r="Y25" t="s">
-        <v>788</v>
+        <v>830</v>
       </c>
       <c r="AA25" t="s">
-        <v>789</v>
+        <v>831</v>
       </c>
       <c r="AB25" t="s">
         <v>39</v>
@@ -5247,13 +5301,13 @@
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>790</v>
+        <v>832</v>
       </c>
       <c r="C26" t="s">
-        <v>791</v>
+        <v>833</v>
       </c>
       <c r="D26" t="s">
-        <v>792</v>
+        <v>834</v>
       </c>
       <c r="E26" t="s">
         <v>33</v>
@@ -5295,10 +5349,10 @@
         <v>11</v>
       </c>
       <c r="Y26" t="s">
-        <v>793</v>
+        <v>835</v>
       </c>
       <c r="AA26" t="s">
-        <v>794</v>
+        <v>836</v>
       </c>
       <c r="AB26" t="s">
         <v>39</v>
@@ -5312,13 +5366,13 @@
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>795</v>
+        <v>780</v>
       </c>
       <c r="C27" t="s">
-        <v>796</v>
+        <v>781</v>
       </c>
       <c r="D27" t="s">
-        <v>797</v>
+        <v>782</v>
       </c>
       <c r="E27" t="s">
         <v>33</v>
@@ -5336,13 +5390,13 @@
         <v>54</v>
       </c>
       <c r="K27" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L27" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M27" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N27" t="s">
         <v>33</v>
@@ -5354,16 +5408,16 @@
         <v>38</v>
       </c>
       <c r="Q27">
-        <v>14.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R27">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="Y27" t="s">
-        <v>798</v>
+        <v>783</v>
       </c>
       <c r="AA27" t="s">
-        <v>799</v>
+        <v>784</v>
       </c>
       <c r="AB27" t="s">
         <v>39</v>
@@ -5377,13 +5431,13 @@
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>800</v>
+        <v>785</v>
       </c>
       <c r="C28" t="s">
-        <v>801</v>
+        <v>786</v>
       </c>
       <c r="D28" t="s">
-        <v>802</v>
+        <v>787</v>
       </c>
       <c r="E28" t="s">
         <v>33</v>
@@ -5401,13 +5455,13 @@
         <v>54</v>
       </c>
       <c r="K28" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L28" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M28" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N28" t="s">
         <v>33</v>
@@ -5419,16 +5473,16 @@
         <v>38</v>
       </c>
       <c r="Q28">
-        <v>14.99</v>
+        <v>40.99</v>
       </c>
       <c r="R28">
-        <v>2.5</v>
+        <v>6.83</v>
       </c>
       <c r="Y28" t="s">
-        <v>68</v>
+        <v>788</v>
       </c>
       <c r="AA28" t="s">
-        <v>803</v>
+        <v>789</v>
       </c>
       <c r="AB28" t="s">
         <v>39</v>
@@ -5442,13 +5496,13 @@
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>804</v>
+        <v>790</v>
       </c>
       <c r="C29" t="s">
-        <v>805</v>
+        <v>791</v>
       </c>
       <c r="D29" t="s">
-        <v>802</v>
+        <v>792</v>
       </c>
       <c r="E29" t="s">
         <v>33</v>
@@ -5466,13 +5520,13 @@
         <v>54</v>
       </c>
       <c r="K29" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L29" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M29" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N29" t="s">
         <v>33</v>
@@ -5484,16 +5538,16 @@
         <v>38</v>
       </c>
       <c r="Q29">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R29">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y29" t="s">
-        <v>806</v>
+        <v>793</v>
       </c>
       <c r="AA29" t="s">
-        <v>807</v>
+        <v>794</v>
       </c>
       <c r="AB29" t="s">
         <v>39</v>
@@ -5507,13 +5561,13 @@
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>808</v>
+        <v>795</v>
       </c>
       <c r="C30" t="s">
-        <v>809</v>
+        <v>796</v>
       </c>
       <c r="D30" t="s">
-        <v>810</v>
+        <v>797</v>
       </c>
       <c r="E30" t="s">
         <v>33</v>
@@ -5549,16 +5603,16 @@
         <v>38</v>
       </c>
       <c r="Q30">
-        <v>11.99</v>
+        <v>14.99</v>
       </c>
       <c r="R30">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Y30" t="s">
-        <v>66</v>
+        <v>798</v>
       </c>
       <c r="AA30" t="s">
-        <v>811</v>
+        <v>799</v>
       </c>
       <c r="AB30" t="s">
         <v>39</v>
@@ -5572,13 +5626,13 @@
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>812</v>
+        <v>800</v>
       </c>
       <c r="C31" t="s">
-        <v>813</v>
+        <v>801</v>
       </c>
       <c r="D31" t="s">
-        <v>814</v>
+        <v>802</v>
       </c>
       <c r="E31" t="s">
         <v>33</v>
@@ -5596,13 +5650,13 @@
         <v>54</v>
       </c>
       <c r="K31" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="L31" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="M31" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="N31" t="s">
         <v>33</v>
@@ -5614,16 +5668,16 @@
         <v>38</v>
       </c>
       <c r="Q31">
-        <v>40.99</v>
+        <v>14.99</v>
       </c>
       <c r="R31">
-        <v>6.83</v>
+        <v>2.5</v>
       </c>
       <c r="Y31" t="s">
-        <v>815</v>
+        <v>68</v>
       </c>
       <c r="AA31" t="s">
-        <v>816</v>
+        <v>803</v>
       </c>
       <c r="AB31" t="s">
         <v>39</v>
@@ -5637,13 +5691,13 @@
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>745</v>
+        <v>804</v>
       </c>
       <c r="C32" t="s">
-        <v>746</v>
+        <v>805</v>
       </c>
       <c r="D32" t="s">
-        <v>817</v>
+        <v>802</v>
       </c>
       <c r="E32" t="s">
         <v>33</v>
@@ -5685,10 +5739,10 @@
         <v>2</v>
       </c>
       <c r="Y32" t="s">
-        <v>748</v>
+        <v>806</v>
       </c>
       <c r="AA32" t="s">
-        <v>749</v>
+        <v>807</v>
       </c>
       <c r="AB32" t="s">
         <v>39</v>
@@ -5702,13 +5756,13 @@
     </row>
     <row r="33" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>750</v>
+        <v>808</v>
       </c>
       <c r="C33" t="s">
-        <v>751</v>
+        <v>809</v>
       </c>
       <c r="D33" t="s">
-        <v>752</v>
+        <v>810</v>
       </c>
       <c r="E33" t="s">
         <v>33</v>
@@ -5726,13 +5780,13 @@
         <v>54</v>
       </c>
       <c r="K33" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L33" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N33" t="s">
         <v>33</v>
@@ -5744,16 +5798,16 @@
         <v>38</v>
       </c>
       <c r="Q33">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R33">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y33" t="s">
-        <v>753</v>
+        <v>66</v>
       </c>
       <c r="AA33" t="s">
-        <v>754</v>
+        <v>811</v>
       </c>
       <c r="AB33" t="s">
         <v>39</v>
@@ -5767,13 +5821,13 @@
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>755</v>
+        <v>812</v>
       </c>
       <c r="C34" t="s">
-        <v>756</v>
+        <v>813</v>
       </c>
       <c r="D34" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="E34" t="s">
         <v>33</v>
@@ -5791,13 +5845,13 @@
         <v>54</v>
       </c>
       <c r="K34" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L34" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M34" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N34" t="s">
         <v>33</v>
@@ -5809,25 +5863,16 @@
         <v>38</v>
       </c>
       <c r="Q34">
-        <v>65.989999999999995</v>
+        <v>40.99</v>
       </c>
       <c r="R34">
-        <v>11</v>
-      </c>
-      <c r="S34">
-        <v>6.99</v>
-      </c>
-      <c r="T34">
-        <v>1.17</v>
+        <v>6.83</v>
       </c>
       <c r="Y34" t="s">
-        <v>758</v>
-      </c>
-      <c r="Z34" t="s">
-        <v>759</v>
+        <v>815</v>
       </c>
       <c r="AA34" t="s">
-        <v>760</v>
+        <v>816</v>
       </c>
       <c r="AB34" t="s">
         <v>39</v>
@@ -5841,13 +5886,13 @@
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>761</v>
+        <v>745</v>
       </c>
       <c r="C35" t="s">
-        <v>762</v>
+        <v>746</v>
       </c>
       <c r="D35" t="s">
-        <v>763</v>
+        <v>817</v>
       </c>
       <c r="E35" t="s">
         <v>33</v>
@@ -5889,13 +5934,10 @@
         <v>2</v>
       </c>
       <c r="Y35" t="s">
-        <v>764</v>
-      </c>
-      <c r="Z35" t="s">
-        <v>279</v>
+        <v>748</v>
       </c>
       <c r="AA35" t="s">
-        <v>765</v>
+        <v>749</v>
       </c>
       <c r="AB35" t="s">
         <v>39</v>
@@ -5909,13 +5951,13 @@
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>766</v>
+        <v>750</v>
       </c>
       <c r="C36" t="s">
-        <v>767</v>
+        <v>751</v>
       </c>
       <c r="D36" t="s">
-        <v>768</v>
+        <v>752</v>
       </c>
       <c r="E36" t="s">
         <v>33</v>
@@ -5933,13 +5975,13 @@
         <v>54</v>
       </c>
       <c r="K36" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L36" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M36" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N36" t="s">
         <v>33</v>
@@ -5951,19 +5993,16 @@
         <v>38</v>
       </c>
       <c r="Q36">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R36">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y36" t="s">
-        <v>91</v>
-      </c>
-      <c r="Z36" t="s">
-        <v>121</v>
+        <v>753</v>
       </c>
       <c r="AA36" t="s">
-        <v>769</v>
+        <v>754</v>
       </c>
       <c r="AB36" t="s">
         <v>39</v>
@@ -5977,13 +6016,13 @@
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>770</v>
+        <v>755</v>
       </c>
       <c r="C37" t="s">
-        <v>771</v>
+        <v>756</v>
       </c>
       <c r="D37" t="s">
-        <v>772</v>
+        <v>818</v>
       </c>
       <c r="E37" t="s">
         <v>33</v>
@@ -6024,14 +6063,20 @@
       <c r="R37">
         <v>11</v>
       </c>
+      <c r="S37">
+        <v>6.99</v>
+      </c>
+      <c r="T37">
+        <v>1.17</v>
+      </c>
       <c r="Y37" t="s">
-        <v>773</v>
+        <v>758</v>
       </c>
       <c r="Z37" t="s">
-        <v>64</v>
+        <v>759</v>
       </c>
       <c r="AA37" t="s">
-        <v>774</v>
+        <v>760</v>
       </c>
       <c r="AB37" t="s">
         <v>39</v>
@@ -6045,13 +6090,13 @@
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>775</v>
+        <v>761</v>
       </c>
       <c r="C38" t="s">
-        <v>776</v>
+        <v>762</v>
       </c>
       <c r="D38" t="s">
-        <v>777</v>
+        <v>763</v>
       </c>
       <c r="E38" t="s">
         <v>33</v>
@@ -6069,13 +6114,13 @@
         <v>54</v>
       </c>
       <c r="K38" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L38" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M38" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N38" t="s">
         <v>33</v>
@@ -6087,16 +6132,19 @@
         <v>38</v>
       </c>
       <c r="Q38">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R38">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y38" t="s">
-        <v>778</v>
+        <v>764</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>279</v>
       </c>
       <c r="AA38" t="s">
-        <v>779</v>
+        <v>765</v>
       </c>
       <c r="AB38" t="s">
         <v>39</v>
@@ -6110,16 +6158,16 @@
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>745</v>
+        <v>766</v>
       </c>
       <c r="C39" t="s">
-        <v>746</v>
+        <v>767</v>
       </c>
       <c r="D39" t="s">
-        <v>747</v>
+        <v>768</v>
       </c>
       <c r="E39" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F39" t="s">
         <v>34</v>
@@ -6143,7 +6191,7 @@
         <v>74</v>
       </c>
       <c r="N39" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O39">
         <v>1</v>
@@ -6158,10 +6206,13 @@
         <v>2</v>
       </c>
       <c r="Y39" t="s">
-        <v>748</v>
+        <v>91</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>121</v>
       </c>
       <c r="AA39" t="s">
-        <v>749</v>
+        <v>769</v>
       </c>
       <c r="AB39" t="s">
         <v>39</v>
@@ -6175,13 +6226,13 @@
     </row>
     <row r="40" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>750</v>
+        <v>770</v>
       </c>
       <c r="C40" t="s">
-        <v>751</v>
+        <v>771</v>
       </c>
       <c r="D40" t="s">
-        <v>752</v>
+        <v>772</v>
       </c>
       <c r="E40" t="s">
         <v>33</v>
@@ -6223,10 +6274,13 @@
         <v>11</v>
       </c>
       <c r="Y40" t="s">
-        <v>753</v>
+        <v>773</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>64</v>
       </c>
       <c r="AA40" t="s">
-        <v>754</v>
+        <v>774</v>
       </c>
       <c r="AB40" t="s">
         <v>39</v>
@@ -6240,16 +6294,16 @@
     </row>
     <row r="41" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>755</v>
+        <v>775</v>
       </c>
       <c r="C41" t="s">
-        <v>756</v>
+        <v>776</v>
       </c>
       <c r="D41" t="s">
-        <v>757</v>
+        <v>777</v>
       </c>
       <c r="E41" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F41" t="s">
         <v>34</v>
@@ -6273,7 +6327,7 @@
         <v>42</v>
       </c>
       <c r="N41" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O41">
         <v>1</v>
@@ -6287,20 +6341,11 @@
       <c r="R41">
         <v>11</v>
       </c>
-      <c r="S41">
-        <v>6.99</v>
-      </c>
-      <c r="T41">
-        <v>1.17</v>
-      </c>
       <c r="Y41" t="s">
-        <v>758</v>
-      </c>
-      <c r="Z41" t="s">
-        <v>759</v>
+        <v>778</v>
       </c>
       <c r="AA41" t="s">
-        <v>760</v>
+        <v>779</v>
       </c>
       <c r="AB41" t="s">
         <v>39</v>
@@ -6314,16 +6359,16 @@
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>761</v>
+        <v>745</v>
       </c>
       <c r="C42" t="s">
-        <v>762</v>
+        <v>746</v>
       </c>
       <c r="D42" t="s">
-        <v>763</v>
+        <v>747</v>
       </c>
       <c r="E42" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F42" t="s">
         <v>34</v>
@@ -6347,7 +6392,7 @@
         <v>74</v>
       </c>
       <c r="N42" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O42">
         <v>1</v>
@@ -6362,13 +6407,10 @@
         <v>2</v>
       </c>
       <c r="Y42" t="s">
-        <v>764</v>
-      </c>
-      <c r="Z42" t="s">
-        <v>279</v>
+        <v>748</v>
       </c>
       <c r="AA42" t="s">
-        <v>765</v>
+        <v>749</v>
       </c>
       <c r="AB42" t="s">
         <v>39</v>
@@ -6382,13 +6424,13 @@
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>766</v>
+        <v>750</v>
       </c>
       <c r="C43" t="s">
-        <v>767</v>
+        <v>751</v>
       </c>
       <c r="D43" t="s">
-        <v>768</v>
+        <v>752</v>
       </c>
       <c r="E43" t="s">
         <v>33</v>
@@ -6406,13 +6448,13 @@
         <v>54</v>
       </c>
       <c r="K43" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L43" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M43" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N43" t="s">
         <v>33</v>
@@ -6424,19 +6466,16 @@
         <v>38</v>
       </c>
       <c r="Q43">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R43">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y43" t="s">
-        <v>91</v>
-      </c>
-      <c r="Z43" t="s">
-        <v>121</v>
+        <v>753</v>
       </c>
       <c r="AA43" t="s">
-        <v>769</v>
+        <v>754</v>
       </c>
       <c r="AB43" t="s">
         <v>39</v>
@@ -6450,16 +6489,16 @@
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>770</v>
+        <v>755</v>
       </c>
       <c r="C44" t="s">
-        <v>771</v>
+        <v>756</v>
       </c>
       <c r="D44" t="s">
-        <v>772</v>
+        <v>757</v>
       </c>
       <c r="E44" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F44" t="s">
         <v>34</v>
@@ -6483,7 +6522,7 @@
         <v>42</v>
       </c>
       <c r="N44" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O44">
         <v>1</v>
@@ -6497,14 +6536,20 @@
       <c r="R44">
         <v>11</v>
       </c>
+      <c r="S44">
+        <v>6.99</v>
+      </c>
+      <c r="T44">
+        <v>1.17</v>
+      </c>
       <c r="Y44" t="s">
-        <v>773</v>
+        <v>758</v>
       </c>
       <c r="Z44" t="s">
-        <v>64</v>
+        <v>759</v>
       </c>
       <c r="AA44" t="s">
-        <v>774</v>
+        <v>760</v>
       </c>
       <c r="AB44" t="s">
         <v>39</v>
@@ -6518,13 +6563,13 @@
     </row>
     <row r="45" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>775</v>
+        <v>761</v>
       </c>
       <c r="C45" t="s">
-        <v>776</v>
+        <v>762</v>
       </c>
       <c r="D45" t="s">
-        <v>777</v>
+        <v>763</v>
       </c>
       <c r="E45" t="s">
         <v>33</v>
@@ -6542,13 +6587,13 @@
         <v>54</v>
       </c>
       <c r="K45" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L45" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M45" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N45" t="s">
         <v>33</v>
@@ -6560,16 +6605,19 @@
         <v>38</v>
       </c>
       <c r="Q45">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R45">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y45" t="s">
-        <v>778</v>
+        <v>764</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>279</v>
       </c>
       <c r="AA45" t="s">
-        <v>779</v>
+        <v>765</v>
       </c>
       <c r="AB45" t="s">
         <v>39</v>
@@ -6583,16 +6631,16 @@
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>714</v>
+        <v>766</v>
       </c>
       <c r="C46" t="s">
-        <v>715</v>
+        <v>767</v>
       </c>
       <c r="D46" t="s">
-        <v>716</v>
+        <v>768</v>
       </c>
       <c r="E46" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F46" t="s">
         <v>34</v>
@@ -6616,7 +6664,7 @@
         <v>74</v>
       </c>
       <c r="N46" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O46">
         <v>1</v>
@@ -6631,13 +6679,13 @@
         <v>2</v>
       </c>
       <c r="Y46" t="s">
-        <v>717</v>
+        <v>91</v>
       </c>
       <c r="Z46" t="s">
-        <v>51</v>
+        <v>121</v>
       </c>
       <c r="AA46" t="s">
-        <v>718</v>
+        <v>769</v>
       </c>
       <c r="AB46" t="s">
         <v>39</v>
@@ -6651,13 +6699,13 @@
     </row>
     <row r="47" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>719</v>
+        <v>770</v>
       </c>
       <c r="C47" t="s">
-        <v>720</v>
+        <v>771</v>
       </c>
       <c r="D47" t="s">
-        <v>721</v>
+        <v>772</v>
       </c>
       <c r="E47" t="s">
         <v>33</v>
@@ -6675,13 +6723,13 @@
         <v>54</v>
       </c>
       <c r="K47" t="s">
-        <v>722</v>
+        <v>40</v>
       </c>
       <c r="L47" t="s">
-        <v>723</v>
+        <v>41</v>
       </c>
       <c r="M47" t="s">
-        <v>724</v>
+        <v>42</v>
       </c>
       <c r="N47" t="s">
         <v>33</v>
@@ -6693,19 +6741,19 @@
         <v>38</v>
       </c>
       <c r="Q47">
-        <v>12.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R47">
-        <v>2.17</v>
+        <v>11</v>
       </c>
       <c r="Y47" t="s">
-        <v>725</v>
+        <v>773</v>
       </c>
       <c r="Z47" t="s">
-        <v>726</v>
+        <v>64</v>
       </c>
       <c r="AA47" t="s">
-        <v>727</v>
+        <v>774</v>
       </c>
       <c r="AB47" t="s">
         <v>39</v>
@@ -6719,13 +6767,13 @@
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>728</v>
+        <v>775</v>
       </c>
       <c r="C48" t="s">
-        <v>729</v>
+        <v>776</v>
       </c>
       <c r="D48" t="s">
-        <v>730</v>
+        <v>777</v>
       </c>
       <c r="E48" t="s">
         <v>33</v>
@@ -6743,13 +6791,13 @@
         <v>54</v>
       </c>
       <c r="K48" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L48" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M48" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N48" t="s">
         <v>33</v>
@@ -6761,16 +6809,16 @@
         <v>38</v>
       </c>
       <c r="Q48">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R48">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y48" t="s">
-        <v>731</v>
+        <v>778</v>
       </c>
       <c r="AA48" t="s">
-        <v>732</v>
+        <v>779</v>
       </c>
       <c r="AB48" t="s">
         <v>39</v>
@@ -6784,16 +6832,16 @@
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>733</v>
+        <v>714</v>
       </c>
       <c r="C49" t="s">
-        <v>734</v>
+        <v>715</v>
       </c>
       <c r="D49" t="s">
-        <v>735</v>
+        <v>716</v>
       </c>
       <c r="E49" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F49" t="s">
         <v>34</v>
@@ -6808,16 +6856,16 @@
         <v>54</v>
       </c>
       <c r="K49" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="L49" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="M49" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="N49" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O49">
         <v>1</v>
@@ -6826,16 +6874,19 @@
         <v>38</v>
       </c>
       <c r="Q49">
-        <v>40.99</v>
+        <v>11.99</v>
       </c>
       <c r="R49">
-        <v>6.83</v>
+        <v>2</v>
       </c>
       <c r="Y49" t="s">
-        <v>736</v>
+        <v>717</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>51</v>
       </c>
       <c r="AA49" t="s">
-        <v>737</v>
+        <v>718</v>
       </c>
       <c r="AB49" t="s">
         <v>39</v>
@@ -6849,13 +6900,13 @@
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>738</v>
+        <v>719</v>
       </c>
       <c r="C50" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="D50" t="s">
-        <v>740</v>
+        <v>721</v>
       </c>
       <c r="E50" t="s">
         <v>33</v>
@@ -6873,13 +6924,13 @@
         <v>54</v>
       </c>
       <c r="K50" t="s">
-        <v>48</v>
+        <v>722</v>
       </c>
       <c r="L50" t="s">
-        <v>49</v>
+        <v>723</v>
       </c>
       <c r="M50" t="s">
-        <v>50</v>
+        <v>724</v>
       </c>
       <c r="N50" t="s">
         <v>33</v>
@@ -6891,16 +6942,19 @@
         <v>38</v>
       </c>
       <c r="Q50">
-        <v>40.99</v>
+        <v>12.99</v>
       </c>
       <c r="R50">
-        <v>6.83</v>
+        <v>2.17</v>
       </c>
       <c r="Y50" t="s">
-        <v>741</v>
+        <v>725</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>726</v>
       </c>
       <c r="AA50" t="s">
-        <v>742</v>
+        <v>727</v>
       </c>
       <c r="AB50" t="s">
         <v>39</v>
@@ -6914,13 +6968,13 @@
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>708</v>
+        <v>728</v>
       </c>
       <c r="C51" t="s">
-        <v>709</v>
+        <v>729</v>
       </c>
       <c r="D51" t="s">
-        <v>743</v>
+        <v>730</v>
       </c>
       <c r="E51" t="s">
         <v>33</v>
@@ -6938,13 +6992,13 @@
         <v>54</v>
       </c>
       <c r="K51" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L51" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M51" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N51" t="s">
         <v>33</v>
@@ -6956,19 +7010,16 @@
         <v>38</v>
       </c>
       <c r="Q51">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R51">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y51" t="s">
-        <v>711</v>
-      </c>
-      <c r="Z51" t="s">
-        <v>712</v>
+        <v>731</v>
       </c>
       <c r="AA51" t="s">
-        <v>713</v>
+        <v>732</v>
       </c>
       <c r="AB51" t="s">
         <v>39</v>
@@ -6982,13 +7033,13 @@
     </row>
     <row r="52" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>643</v>
+        <v>733</v>
       </c>
       <c r="C52" t="s">
-        <v>644</v>
+        <v>734</v>
       </c>
       <c r="D52" t="s">
-        <v>744</v>
+        <v>735</v>
       </c>
       <c r="E52" t="s">
         <v>33</v>
@@ -7006,13 +7057,13 @@
         <v>54</v>
       </c>
       <c r="K52" t="s">
-        <v>94</v>
+        <v>43</v>
       </c>
       <c r="L52" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="M52" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="N52" t="s">
         <v>33</v>
@@ -7024,16 +7075,16 @@
         <v>38</v>
       </c>
       <c r="Q52">
-        <v>14.99</v>
+        <v>40.99</v>
       </c>
       <c r="R52">
-        <v>2.5</v>
+        <v>6.83</v>
       </c>
       <c r="Y52" t="s">
-        <v>646</v>
+        <v>736</v>
       </c>
       <c r="AA52" t="s">
-        <v>647</v>
+        <v>737</v>
       </c>
       <c r="AB52" t="s">
         <v>39</v>
@@ -7047,16 +7098,16 @@
     </row>
     <row r="53" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>708</v>
+        <v>738</v>
       </c>
       <c r="C53" t="s">
-        <v>709</v>
+        <v>739</v>
       </c>
       <c r="D53" t="s">
-        <v>710</v>
+        <v>740</v>
       </c>
       <c r="E53" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F53" t="s">
         <v>34</v>
@@ -7071,16 +7122,16 @@
         <v>54</v>
       </c>
       <c r="K53" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L53" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M53" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N53" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O53">
         <v>1</v>
@@ -7089,19 +7140,16 @@
         <v>38</v>
       </c>
       <c r="Q53">
-        <v>65.989999999999995</v>
+        <v>40.99</v>
       </c>
       <c r="R53">
-        <v>11</v>
+        <v>6.83</v>
       </c>
       <c r="Y53" t="s">
-        <v>711</v>
-      </c>
-      <c r="Z53" t="s">
-        <v>712</v>
+        <v>741</v>
       </c>
       <c r="AA53" t="s">
-        <v>713</v>
+        <v>742</v>
       </c>
       <c r="AB53" t="s">
         <v>39</v>
@@ -7115,22 +7163,22 @@
     </row>
     <row r="54" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>138</v>
+        <v>708</v>
       </c>
       <c r="C54" t="s">
-        <v>139</v>
+        <v>709</v>
       </c>
       <c r="D54" t="s">
-        <v>187</v>
+        <v>743</v>
       </c>
       <c r="E54" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F54" t="s">
         <v>34</v>
       </c>
       <c r="G54" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="H54" t="s">
         <v>36</v>
@@ -7139,25 +7187,40 @@
         <v>54</v>
       </c>
       <c r="K54" t="s">
-        <v>141</v>
+        <v>40</v>
       </c>
       <c r="L54" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="M54" t="s">
-        <v>143</v>
+        <v>42</v>
+      </c>
+      <c r="N54" t="s">
+        <v>33</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P54" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q54">
+        <v>65.989999999999995</v>
+      </c>
+      <c r="R54">
+        <v>11</v>
       </c>
       <c r="Y54" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA54">
-        <v>80100</v>
+        <v>711</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>712</v>
+      </c>
+      <c r="AA54" t="s">
+        <v>713</v>
       </c>
       <c r="AB54" t="s">
-        <v>145</v>
+        <v>39</v>
       </c>
       <c r="AD54" t="b">
         <v>0</v>
@@ -7168,22 +7231,22 @@
     </row>
     <row r="55" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>146</v>
+        <v>643</v>
       </c>
       <c r="C55" t="s">
-        <v>147</v>
+        <v>644</v>
       </c>
       <c r="D55" t="s">
-        <v>148</v>
+        <v>744</v>
       </c>
       <c r="E55" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F55" t="s">
         <v>34</v>
       </c>
       <c r="G55" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="H55" t="s">
         <v>36</v>
@@ -7192,25 +7255,37 @@
         <v>54</v>
       </c>
       <c r="K55" t="s">
-        <v>141</v>
+        <v>94</v>
       </c>
       <c r="L55" t="s">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="M55" t="s">
-        <v>143</v>
+        <v>83</v>
+      </c>
+      <c r="N55" t="s">
+        <v>33</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P55" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q55">
+        <v>14.99</v>
+      </c>
+      <c r="R55">
+        <v>2.5</v>
       </c>
       <c r="Y55" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA55">
-        <v>80100</v>
+        <v>646</v>
+      </c>
+      <c r="AA55" t="s">
+        <v>647</v>
       </c>
       <c r="AB55" t="s">
-        <v>145</v>
+        <v>39</v>
       </c>
       <c r="AD55" t="b">
         <v>0</v>
@@ -7221,22 +7296,22 @@
     </row>
     <row r="56" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>632</v>
+        <v>708</v>
       </c>
       <c r="C56" t="s">
-        <v>633</v>
+        <v>709</v>
       </c>
       <c r="D56" t="s">
-        <v>634</v>
+        <v>710</v>
       </c>
       <c r="E56" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="F56" t="s">
         <v>34</v>
       </c>
       <c r="G56" t="s">
-        <v>635</v>
+        <v>35</v>
       </c>
       <c r="H56" t="s">
         <v>36</v>
@@ -7245,37 +7320,40 @@
         <v>54</v>
       </c>
       <c r="K56" t="s">
-        <v>636</v>
+        <v>40</v>
       </c>
       <c r="L56" t="s">
-        <v>637</v>
+        <v>41</v>
       </c>
       <c r="M56" t="s">
-        <v>638</v>
+        <v>42</v>
+      </c>
+      <c r="N56" t="s">
+        <v>99</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="Q56">
-        <v>22.9</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R56">
-        <v>4.8099999999999996</v>
+        <v>11</v>
       </c>
       <c r="Y56" t="s">
-        <v>639</v>
+        <v>711</v>
       </c>
       <c r="Z56" t="s">
-        <v>640</v>
+        <v>712</v>
       </c>
       <c r="AA56" t="s">
-        <v>641</v>
+        <v>713</v>
       </c>
       <c r="AB56" t="s">
-        <v>642</v>
+        <v>39</v>
       </c>
       <c r="AD56" t="b">
         <v>0</v>
@@ -7286,22 +7364,22 @@
     </row>
     <row r="57" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>643</v>
+        <v>138</v>
       </c>
       <c r="C57" t="s">
-        <v>644</v>
+        <v>139</v>
       </c>
       <c r="D57" t="s">
-        <v>645</v>
+        <v>187</v>
       </c>
       <c r="E57" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="F57" t="s">
         <v>34</v>
       </c>
       <c r="G57" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="H57" t="s">
         <v>36</v>
@@ -7310,37 +7388,25 @@
         <v>54</v>
       </c>
       <c r="K57" t="s">
-        <v>94</v>
+        <v>141</v>
       </c>
       <c r="L57" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="M57" t="s">
-        <v>83</v>
-      </c>
-      <c r="N57" t="s">
-        <v>99</v>
+        <v>143</v>
       </c>
       <c r="O57">
-        <v>1</v>
-      </c>
-      <c r="P57" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q57">
-        <v>14.99</v>
-      </c>
-      <c r="R57">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y57" t="s">
-        <v>646</v>
-      </c>
-      <c r="AA57" t="s">
-        <v>647</v>
+        <v>144</v>
+      </c>
+      <c r="AA57">
+        <v>80100</v>
       </c>
       <c r="AB57" t="s">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="AD57" t="b">
         <v>0</v>
@@ -7351,22 +7417,22 @@
     </row>
     <row r="58" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>609</v>
+        <v>146</v>
       </c>
       <c r="C58" t="s">
-        <v>610</v>
+        <v>147</v>
       </c>
       <c r="D58" t="s">
-        <v>611</v>
+        <v>148</v>
       </c>
       <c r="E58" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F58" t="s">
         <v>34</v>
       </c>
       <c r="G58" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="H58" t="s">
         <v>36</v>
@@ -7375,40 +7441,25 @@
         <v>54</v>
       </c>
       <c r="K58" t="s">
-        <v>94</v>
+        <v>141</v>
       </c>
       <c r="L58" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="M58" t="s">
-        <v>83</v>
-      </c>
-      <c r="N58" t="s">
-        <v>33</v>
+        <v>143</v>
       </c>
       <c r="O58">
-        <v>1</v>
-      </c>
-      <c r="P58" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q58">
-        <v>14.99</v>
-      </c>
-      <c r="R58">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y58" t="s">
-        <v>612</v>
-      </c>
-      <c r="Z58" t="s">
-        <v>613</v>
-      </c>
-      <c r="AA58" t="s">
-        <v>614</v>
+        <v>144</v>
+      </c>
+      <c r="AA58">
+        <v>80100</v>
       </c>
       <c r="AB58" t="s">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="AD58" t="b">
         <v>0</v>
@@ -7419,13 +7470,13 @@
     </row>
     <row r="59" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>493</v>
+        <v>632</v>
       </c>
       <c r="C59" t="s">
-        <v>494</v>
+        <v>633</v>
       </c>
       <c r="D59" t="s">
-        <v>648</v>
+        <v>634</v>
       </c>
       <c r="E59" t="s">
         <v>53</v>
@@ -7434,7 +7485,7 @@
         <v>34</v>
       </c>
       <c r="G59" t="s">
-        <v>35</v>
+        <v>635</v>
       </c>
       <c r="H59" t="s">
         <v>36</v>
@@ -7443,25 +7494,37 @@
         <v>54</v>
       </c>
       <c r="K59" t="s">
-        <v>40</v>
+        <v>636</v>
       </c>
       <c r="L59" t="s">
-        <v>41</v>
+        <v>637</v>
       </c>
       <c r="M59" t="s">
-        <v>42</v>
+        <v>638</v>
       </c>
       <c r="O59">
         <v>0</v>
       </c>
+      <c r="P59" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q59">
+        <v>22.9</v>
+      </c>
+      <c r="R59">
+        <v>4.8099999999999996</v>
+      </c>
       <c r="Y59" t="s">
-        <v>495</v>
+        <v>639</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>640</v>
       </c>
       <c r="AA59" t="s">
-        <v>496</v>
+        <v>641</v>
       </c>
       <c r="AB59" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="AD59" t="b">
         <v>0</v>
@@ -7472,13 +7535,13 @@
     </row>
     <row r="60" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
       <c r="C60" t="s">
-        <v>616</v>
+        <v>644</v>
       </c>
       <c r="D60" t="s">
-        <v>617</v>
+        <v>645</v>
       </c>
       <c r="E60" t="s">
         <v>98</v>
@@ -7496,13 +7559,13 @@
         <v>54</v>
       </c>
       <c r="K60" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="L60" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="M60" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="N60" t="s">
         <v>99</v>
@@ -7514,16 +7577,16 @@
         <v>38</v>
       </c>
       <c r="Q60">
-        <v>40.99</v>
+        <v>14.99</v>
+      </c>
+      <c r="R60">
+        <v>2.5</v>
       </c>
       <c r="Y60" t="s">
-        <v>618</v>
-      </c>
-      <c r="Z60" t="s">
-        <v>619</v>
+        <v>646</v>
       </c>
       <c r="AA60" t="s">
-        <v>620</v>
+        <v>647</v>
       </c>
       <c r="AB60" t="s">
         <v>39</v>
@@ -7537,13 +7600,13 @@
     </row>
     <row r="61" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="C61" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="D61" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="E61" t="s">
         <v>33</v>
@@ -7561,13 +7624,13 @@
         <v>54</v>
       </c>
       <c r="K61" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L61" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M61" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="N61" t="s">
         <v>33</v>
@@ -7579,25 +7642,19 @@
         <v>38</v>
       </c>
       <c r="Q61">
-        <v>64.989999999999995</v>
+        <v>14.99</v>
       </c>
       <c r="R61">
-        <v>10.83</v>
-      </c>
-      <c r="S61">
-        <v>6.99</v>
-      </c>
-      <c r="T61">
-        <v>1.17</v>
+        <v>2.5</v>
       </c>
       <c r="Y61" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="Z61" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="AA61" t="s">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="AB61" t="s">
         <v>39</v>
@@ -7611,16 +7668,16 @@
     </row>
     <row r="62" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>627</v>
+        <v>493</v>
       </c>
       <c r="C62" t="s">
-        <v>628</v>
+        <v>494</v>
       </c>
       <c r="D62" t="s">
-        <v>629</v>
+        <v>648</v>
       </c>
       <c r="E62" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F62" t="s">
         <v>34</v>
@@ -7635,34 +7692,22 @@
         <v>54</v>
       </c>
       <c r="K62" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L62" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M62" t="s">
-        <v>74</v>
-      </c>
-      <c r="N62" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O62">
-        <v>1</v>
-      </c>
-      <c r="P62" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q62">
-        <v>11.99</v>
-      </c>
-      <c r="R62">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="s">
-        <v>630</v>
+        <v>495</v>
       </c>
       <c r="AA62" t="s">
-        <v>631</v>
+        <v>496</v>
       </c>
       <c r="AB62" t="s">
         <v>39</v>
@@ -7676,16 +7721,16 @@
     </row>
     <row r="63" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>649</v>
+        <v>615</v>
       </c>
       <c r="C63" t="s">
-        <v>650</v>
+        <v>616</v>
       </c>
       <c r="D63" t="s">
-        <v>651</v>
+        <v>617</v>
       </c>
       <c r="E63" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F63" t="s">
         <v>34</v>
@@ -7709,7 +7754,7 @@
         <v>50</v>
       </c>
       <c r="N63" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O63">
         <v>1</v>
@@ -7718,19 +7763,16 @@
         <v>38</v>
       </c>
       <c r="Q63">
-        <v>39.99</v>
-      </c>
-      <c r="R63">
-        <v>6.67</v>
+        <v>40.99</v>
       </c>
       <c r="Y63" t="s">
-        <v>652</v>
+        <v>618</v>
       </c>
       <c r="Z63" t="s">
-        <v>653</v>
+        <v>619</v>
       </c>
       <c r="AA63" t="s">
-        <v>654</v>
+        <v>620</v>
       </c>
       <c r="AB63" t="s">
         <v>39</v>
@@ -7744,13 +7786,13 @@
     </row>
     <row r="64" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>655</v>
+        <v>621</v>
       </c>
       <c r="C64" t="s">
-        <v>656</v>
+        <v>622</v>
       </c>
       <c r="D64" t="s">
-        <v>657</v>
+        <v>623</v>
       </c>
       <c r="E64" t="s">
         <v>33</v>
@@ -7768,13 +7810,13 @@
         <v>54</v>
       </c>
       <c r="K64" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L64" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M64" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="N64" t="s">
         <v>33</v>
@@ -7786,16 +7828,25 @@
         <v>38</v>
       </c>
       <c r="Q64">
-        <v>14.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R64">
-        <v>2.5</v>
+        <v>10.83</v>
+      </c>
+      <c r="S64">
+        <v>6.99</v>
+      </c>
+      <c r="T64">
+        <v>1.17</v>
       </c>
       <c r="Y64" t="s">
-        <v>658</v>
+        <v>624</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>625</v>
       </c>
       <c r="AA64" t="s">
-        <v>659</v>
+        <v>626</v>
       </c>
       <c r="AB64" t="s">
         <v>39</v>
@@ -7809,13 +7860,13 @@
     </row>
     <row r="65" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>571</v>
+        <v>627</v>
       </c>
       <c r="C65" t="s">
-        <v>572</v>
+        <v>628</v>
       </c>
       <c r="D65" t="s">
-        <v>660</v>
+        <v>629</v>
       </c>
       <c r="E65" t="s">
         <v>33</v>
@@ -7833,13 +7884,13 @@
         <v>54</v>
       </c>
       <c r="K65" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L65" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M65" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N65" t="s">
         <v>33</v>
@@ -7851,16 +7902,16 @@
         <v>38</v>
       </c>
       <c r="Q65">
-        <v>64.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R65">
-        <v>10.83</v>
+        <v>2</v>
       </c>
       <c r="Y65" t="s">
-        <v>573</v>
+        <v>630</v>
       </c>
       <c r="AA65" t="s">
-        <v>574</v>
+        <v>631</v>
       </c>
       <c r="AB65" t="s">
         <v>39</v>
@@ -7874,13 +7925,13 @@
     </row>
     <row r="66" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>599</v>
+        <v>649</v>
       </c>
       <c r="C66" t="s">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="D66" t="s">
-        <v>601</v>
+        <v>651</v>
       </c>
       <c r="E66" t="s">
         <v>33</v>
@@ -7898,13 +7949,13 @@
         <v>54</v>
       </c>
       <c r="K66" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="L66" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="M66" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="N66" t="s">
         <v>33</v>
@@ -7916,16 +7967,19 @@
         <v>38</v>
       </c>
       <c r="Q66">
-        <v>14.99</v>
+        <v>39.99</v>
       </c>
       <c r="R66">
-        <v>2.5</v>
+        <v>6.67</v>
       </c>
       <c r="Y66" t="s">
-        <v>61</v>
+        <v>652</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>653</v>
       </c>
       <c r="AA66" t="s">
-        <v>602</v>
+        <v>654</v>
       </c>
       <c r="AB66" t="s">
         <v>39</v>
@@ -7939,13 +7993,13 @@
     </row>
     <row r="67" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>589</v>
+        <v>655</v>
       </c>
       <c r="C67" t="s">
-        <v>590</v>
+        <v>656</v>
       </c>
       <c r="D67" t="s">
-        <v>591</v>
+        <v>657</v>
       </c>
       <c r="E67" t="s">
         <v>33</v>
@@ -7963,13 +8017,13 @@
         <v>54</v>
       </c>
       <c r="K67" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L67" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M67" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="N67" t="s">
         <v>33</v>
@@ -7981,16 +8035,16 @@
         <v>38</v>
       </c>
       <c r="Q67">
-        <v>64.989999999999995</v>
+        <v>14.99</v>
       </c>
       <c r="R67">
-        <v>10.83</v>
+        <v>2.5</v>
       </c>
       <c r="Y67" t="s">
-        <v>592</v>
+        <v>658</v>
       </c>
       <c r="AA67" t="s">
-        <v>593</v>
+        <v>659</v>
       </c>
       <c r="AB67" t="s">
         <v>39</v>
@@ -8004,13 +8058,13 @@
     </row>
     <row r="68" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>594</v>
+        <v>571</v>
       </c>
       <c r="C68" t="s">
-        <v>595</v>
+        <v>572</v>
       </c>
       <c r="D68" t="s">
-        <v>596</v>
+        <v>660</v>
       </c>
       <c r="E68" t="s">
         <v>33</v>
@@ -8052,10 +8106,10 @@
         <v>10.83</v>
       </c>
       <c r="Y68" t="s">
-        <v>597</v>
+        <v>573</v>
       </c>
       <c r="AA68" t="s">
-        <v>598</v>
+        <v>574</v>
       </c>
       <c r="AB68" t="s">
         <v>39</v>
@@ -8069,13 +8123,13 @@
     </row>
     <row r="69" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="C69" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="D69" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="E69" t="s">
         <v>33</v>
@@ -8093,13 +8147,13 @@
         <v>54</v>
       </c>
       <c r="K69" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L69" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M69" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="N69" t="s">
         <v>33</v>
@@ -8111,19 +8165,16 @@
         <v>38</v>
       </c>
       <c r="Q69">
-        <v>64.989999999999995</v>
+        <v>14.99</v>
       </c>
       <c r="R69">
-        <v>10.83</v>
+        <v>2.5</v>
       </c>
       <c r="Y69" t="s">
-        <v>606</v>
-      </c>
-      <c r="Z69" t="s">
-        <v>607</v>
+        <v>61</v>
       </c>
       <c r="AA69" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="AB69" t="s">
         <v>39</v>
@@ -8137,13 +8188,13 @@
     </row>
     <row r="70" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>578</v>
+        <v>589</v>
       </c>
       <c r="C70" t="s">
-        <v>579</v>
+        <v>590</v>
       </c>
       <c r="D70" t="s">
-        <v>661</v>
+        <v>591</v>
       </c>
       <c r="E70" t="s">
         <v>33</v>
@@ -8185,13 +8236,10 @@
         <v>10.83</v>
       </c>
       <c r="Y70" t="s">
-        <v>580</v>
-      </c>
-      <c r="Z70" t="s">
-        <v>581</v>
+        <v>592</v>
       </c>
       <c r="AA70" t="s">
-        <v>582</v>
+        <v>593</v>
       </c>
       <c r="AB70" t="s">
         <v>39</v>
@@ -8205,16 +8253,16 @@
     </row>
     <row r="71" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>575</v>
+        <v>594</v>
       </c>
       <c r="C71" t="s">
-        <v>576</v>
+        <v>595</v>
       </c>
       <c r="D71" t="s">
-        <v>577</v>
+        <v>596</v>
       </c>
       <c r="E71" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F71" t="s">
         <v>34</v>
@@ -8237,14 +8285,26 @@
       <c r="M71" t="s">
         <v>42</v>
       </c>
+      <c r="N71" t="s">
+        <v>33</v>
+      </c>
       <c r="O71">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P71" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q71">
+        <v>64.989999999999995</v>
+      </c>
+      <c r="R71">
+        <v>10.83</v>
       </c>
       <c r="Y71" t="s">
-        <v>573</v>
+        <v>597</v>
       </c>
       <c r="AA71" t="s">
-        <v>574</v>
+        <v>598</v>
       </c>
       <c r="AB71" t="s">
         <v>39</v>
@@ -8258,13 +8318,13 @@
     </row>
     <row r="72" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>518</v>
+        <v>603</v>
       </c>
       <c r="C72" t="s">
-        <v>519</v>
+        <v>604</v>
       </c>
       <c r="D72" t="s">
-        <v>583</v>
+        <v>605</v>
       </c>
       <c r="E72" t="s">
         <v>33</v>
@@ -8282,13 +8342,13 @@
         <v>54</v>
       </c>
       <c r="K72" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L72" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M72" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N72" t="s">
         <v>33</v>
@@ -8300,22 +8360,19 @@
         <v>38</v>
       </c>
       <c r="Q72">
-        <v>37.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R72">
-        <v>6.33</v>
-      </c>
-      <c r="S72">
-        <v>6.99</v>
-      </c>
-      <c r="T72">
-        <v>1.17</v>
+        <v>10.83</v>
       </c>
       <c r="Y72" t="s">
-        <v>46</v>
+        <v>606</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>607</v>
       </c>
       <c r="AA72" t="s">
-        <v>520</v>
+        <v>608</v>
       </c>
       <c r="AB72" t="s">
         <v>39</v>
@@ -8329,13 +8386,13 @@
     </row>
     <row r="73" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="C73" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="D73" t="s">
-        <v>586</v>
+        <v>661</v>
       </c>
       <c r="E73" t="s">
         <v>33</v>
@@ -8377,10 +8434,13 @@
         <v>10.83</v>
       </c>
       <c r="Y73" t="s">
-        <v>587</v>
+        <v>580</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>581</v>
       </c>
       <c r="AA73" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="AB73" t="s">
         <v>39</v>
@@ -8394,16 +8454,16 @@
     </row>
     <row r="74" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>457</v>
+        <v>575</v>
       </c>
       <c r="C74" t="s">
-        <v>458</v>
+        <v>576</v>
       </c>
       <c r="D74" t="s">
-        <v>459</v>
+        <v>577</v>
       </c>
       <c r="E74" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F74" t="s">
         <v>34</v>
@@ -8426,29 +8486,14 @@
       <c r="M74" t="s">
         <v>42</v>
       </c>
-      <c r="N74" t="s">
-        <v>33</v>
-      </c>
       <c r="O74">
-        <v>1</v>
-      </c>
-      <c r="P74" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q74">
-        <v>64.989999999999995</v>
-      </c>
-      <c r="R74">
-        <v>10.83</v>
+        <v>0</v>
       </c>
       <c r="Y74" t="s">
-        <v>460</v>
-      </c>
-      <c r="Z74" t="s">
-        <v>279</v>
+        <v>573</v>
       </c>
       <c r="AA74" t="s">
-        <v>461</v>
+        <v>574</v>
       </c>
       <c r="AB74" t="s">
         <v>39</v>
@@ -8462,13 +8507,13 @@
     </row>
     <row r="75" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>462</v>
+        <v>518</v>
       </c>
       <c r="C75" t="s">
-        <v>463</v>
+        <v>519</v>
       </c>
       <c r="D75" t="s">
-        <v>459</v>
+        <v>583</v>
       </c>
       <c r="E75" t="s">
         <v>33</v>
@@ -8486,13 +8531,13 @@
         <v>54</v>
       </c>
       <c r="K75" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L75" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M75" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N75" t="s">
         <v>33</v>
@@ -8504,16 +8549,22 @@
         <v>38</v>
       </c>
       <c r="Q75">
-        <v>64.989999999999995</v>
+        <v>37.99</v>
       </c>
       <c r="R75">
-        <v>10.83</v>
+        <v>6.33</v>
+      </c>
+      <c r="S75">
+        <v>6.99</v>
+      </c>
+      <c r="T75">
+        <v>1.17</v>
       </c>
       <c r="Y75" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="AA75" t="s">
-        <v>464</v>
+        <v>520</v>
       </c>
       <c r="AB75" t="s">
         <v>39</v>
@@ -8527,13 +8578,13 @@
     </row>
     <row r="76" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>465</v>
+        <v>584</v>
       </c>
       <c r="C76" t="s">
-        <v>466</v>
+        <v>585</v>
       </c>
       <c r="D76" t="s">
-        <v>467</v>
+        <v>586</v>
       </c>
       <c r="E76" t="s">
         <v>33</v>
@@ -8551,34 +8602,34 @@
         <v>54</v>
       </c>
       <c r="K76" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L76" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M76" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N76" t="s">
         <v>33</v>
       </c>
       <c r="O76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P76" t="s">
         <v>38</v>
       </c>
       <c r="Q76">
-        <v>79.98</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R76">
-        <v>13.34</v>
+        <v>10.83</v>
       </c>
       <c r="Y76" t="s">
-        <v>468</v>
+        <v>587</v>
       </c>
       <c r="AA76" t="s">
-        <v>469</v>
+        <v>588</v>
       </c>
       <c r="AB76" t="s">
         <v>39</v>
@@ -8592,13 +8643,13 @@
     </row>
     <row r="77" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
       <c r="C77" t="s">
-        <v>471</v>
+        <v>458</v>
       </c>
       <c r="D77" t="s">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="E77" t="s">
         <v>33</v>
@@ -8616,13 +8667,13 @@
         <v>54</v>
       </c>
       <c r="K77" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L77" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M77" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N77" t="s">
         <v>33</v>
@@ -8634,16 +8685,19 @@
         <v>38</v>
       </c>
       <c r="Q77">
-        <v>37.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R77">
-        <v>6.33</v>
+        <v>10.83</v>
       </c>
       <c r="Y77" t="s">
-        <v>473</v>
+        <v>460</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>279</v>
       </c>
       <c r="AA77" t="s">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="AB77" t="s">
         <v>39</v>
@@ -8657,16 +8711,16 @@
     </row>
     <row r="78" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="C78" t="s">
-        <v>476</v>
+        <v>463</v>
       </c>
       <c r="D78" t="s">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="E78" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F78" t="s">
         <v>34</v>
@@ -8689,17 +8743,26 @@
       <c r="M78" t="s">
         <v>42</v>
       </c>
+      <c r="N78" t="s">
+        <v>33</v>
+      </c>
       <c r="O78">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P78" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q78">
+        <v>64.989999999999995</v>
+      </c>
+      <c r="R78">
+        <v>10.83</v>
       </c>
       <c r="Y78" t="s">
-        <v>478</v>
-      </c>
-      <c r="Z78" t="s">
-        <v>279</v>
+        <v>56</v>
       </c>
       <c r="AA78" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="AB78" t="s">
         <v>39</v>
@@ -8713,13 +8776,13 @@
     </row>
     <row r="79" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>480</v>
+        <v>465</v>
       </c>
       <c r="C79" t="s">
-        <v>481</v>
+        <v>466</v>
       </c>
       <c r="D79" t="s">
-        <v>482</v>
+        <v>467</v>
       </c>
       <c r="E79" t="s">
         <v>33</v>
@@ -8737,34 +8800,34 @@
         <v>54</v>
       </c>
       <c r="K79" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L79" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M79" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N79" t="s">
         <v>33</v>
       </c>
       <c r="O79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P79" t="s">
         <v>38</v>
       </c>
       <c r="Q79">
-        <v>11.99</v>
+        <v>79.98</v>
       </c>
       <c r="R79">
-        <v>2</v>
+        <v>13.34</v>
       </c>
       <c r="Y79" t="s">
-        <v>61</v>
+        <v>468</v>
       </c>
       <c r="AA79" t="s">
-        <v>483</v>
+        <v>469</v>
       </c>
       <c r="AB79" t="s">
         <v>39</v>
@@ -8778,13 +8841,13 @@
     </row>
     <row r="80" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>484</v>
+        <v>470</v>
       </c>
       <c r="C80" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="D80" t="s">
-        <v>486</v>
+        <v>472</v>
       </c>
       <c r="E80" t="s">
         <v>33</v>
@@ -8802,13 +8865,13 @@
         <v>54</v>
       </c>
       <c r="K80" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L80" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M80" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N80" t="s">
         <v>33</v>
@@ -8820,16 +8883,16 @@
         <v>38</v>
       </c>
       <c r="Q80">
-        <v>64.989999999999995</v>
+        <v>37.99</v>
       </c>
       <c r="R80">
-        <v>10.83</v>
+        <v>6.33</v>
       </c>
       <c r="Y80" t="s">
-        <v>67</v>
+        <v>473</v>
       </c>
       <c r="AA80" t="s">
-        <v>487</v>
+        <v>474</v>
       </c>
       <c r="AB80" t="s">
         <v>39</v>
@@ -8843,16 +8906,16 @@
     </row>
     <row r="81" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="C81" t="s">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="D81" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="E81" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F81" t="s">
         <v>34</v>
@@ -8867,37 +8930,25 @@
         <v>54</v>
       </c>
       <c r="K81" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L81" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M81" t="s">
-        <v>50</v>
-      </c>
-      <c r="N81" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O81">
-        <v>2</v>
-      </c>
-      <c r="P81" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q81">
-        <v>79.98</v>
-      </c>
-      <c r="R81">
-        <v>13.34</v>
+        <v>0</v>
       </c>
       <c r="Y81" t="s">
-        <v>63</v>
+        <v>478</v>
       </c>
       <c r="Z81" t="s">
-        <v>491</v>
+        <v>279</v>
       </c>
       <c r="AA81" t="s">
-        <v>492</v>
+        <v>479</v>
       </c>
       <c r="AB81" t="s">
         <v>39</v>
@@ -8911,13 +8962,13 @@
     </row>
     <row r="82" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>497</v>
+        <v>480</v>
       </c>
       <c r="C82" t="s">
-        <v>498</v>
+        <v>481</v>
       </c>
       <c r="D82" t="s">
-        <v>499</v>
+        <v>482</v>
       </c>
       <c r="E82" t="s">
         <v>33</v>
@@ -8935,13 +8986,13 @@
         <v>54</v>
       </c>
       <c r="K82" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L82" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M82" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N82" t="s">
         <v>33</v>
@@ -8953,19 +9004,16 @@
         <v>38</v>
       </c>
       <c r="Q82">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R82">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y82" t="s">
-        <v>500</v>
-      </c>
-      <c r="Z82" t="s">
-        <v>501</v>
+        <v>61</v>
       </c>
       <c r="AA82" t="s">
-        <v>502</v>
+        <v>483</v>
       </c>
       <c r="AB82" t="s">
         <v>39</v>
@@ -8979,13 +9027,13 @@
     </row>
     <row r="83" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>503</v>
+        <v>484</v>
       </c>
       <c r="C83" t="s">
-        <v>504</v>
+        <v>485</v>
       </c>
       <c r="D83" t="s">
-        <v>499</v>
+        <v>486</v>
       </c>
       <c r="E83" t="s">
         <v>33</v>
@@ -9021,19 +9069,16 @@
         <v>38</v>
       </c>
       <c r="Q83">
-        <v>59.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R83">
-        <v>10</v>
+        <v>10.83</v>
       </c>
       <c r="Y83" t="s">
-        <v>505</v>
-      </c>
-      <c r="Z83" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="AA83" t="s">
-        <v>506</v>
+        <v>487</v>
       </c>
       <c r="AB83" t="s">
         <v>39</v>
@@ -9047,13 +9092,13 @@
     </row>
     <row r="84" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>507</v>
+        <v>488</v>
       </c>
       <c r="C84" t="s">
-        <v>508</v>
+        <v>489</v>
       </c>
       <c r="D84" t="s">
-        <v>509</v>
+        <v>490</v>
       </c>
       <c r="E84" t="s">
         <v>33</v>
@@ -9071,34 +9116,37 @@
         <v>54</v>
       </c>
       <c r="K84" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L84" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M84" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N84" t="s">
         <v>33</v>
       </c>
       <c r="O84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P84" t="s">
         <v>38</v>
       </c>
       <c r="Q84">
-        <v>59.99</v>
+        <v>79.98</v>
       </c>
       <c r="R84">
-        <v>10</v>
+        <v>13.34</v>
       </c>
       <c r="Y84" t="s">
-        <v>510</v>
+        <v>63</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>491</v>
       </c>
       <c r="AA84" t="s">
-        <v>511</v>
+        <v>492</v>
       </c>
       <c r="AB84" t="s">
         <v>39</v>
@@ -9112,13 +9160,13 @@
     </row>
     <row r="85" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>512</v>
+        <v>497</v>
       </c>
       <c r="C85" t="s">
-        <v>513</v>
+        <v>498</v>
       </c>
       <c r="D85" t="s">
-        <v>514</v>
+        <v>499</v>
       </c>
       <c r="E85" t="s">
         <v>33</v>
@@ -9160,13 +9208,13 @@
         <v>10</v>
       </c>
       <c r="Y85" t="s">
-        <v>515</v>
+        <v>500</v>
       </c>
       <c r="Z85" t="s">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="AA85" t="s">
-        <v>517</v>
+        <v>502</v>
       </c>
       <c r="AB85" t="s">
         <v>39</v>
@@ -9180,13 +9228,13 @@
     </row>
     <row r="86" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>521</v>
+        <v>503</v>
       </c>
       <c r="C86" t="s">
-        <v>522</v>
+        <v>504</v>
       </c>
       <c r="D86" t="s">
-        <v>523</v>
+        <v>499</v>
       </c>
       <c r="E86" t="s">
         <v>33</v>
@@ -9204,13 +9252,13 @@
         <v>54</v>
       </c>
       <c r="K86" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L86" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M86" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="N86" t="s">
         <v>33</v>
@@ -9222,16 +9270,19 @@
         <v>38</v>
       </c>
       <c r="Q86">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R86">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y86" t="s">
-        <v>58</v>
+        <v>505</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>93</v>
       </c>
       <c r="AA86" t="s">
-        <v>524</v>
+        <v>506</v>
       </c>
       <c r="AB86" t="s">
         <v>39</v>
@@ -9245,13 +9296,13 @@
     </row>
     <row r="87" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>525</v>
+        <v>507</v>
       </c>
       <c r="C87" t="s">
-        <v>526</v>
+        <v>508</v>
       </c>
       <c r="D87" t="s">
-        <v>527</v>
+        <v>509</v>
       </c>
       <c r="E87" t="s">
         <v>33</v>
@@ -9293,10 +9344,10 @@
         <v>10</v>
       </c>
       <c r="Y87" t="s">
-        <v>90</v>
+        <v>510</v>
       </c>
       <c r="AA87" t="s">
-        <v>528</v>
+        <v>511</v>
       </c>
       <c r="AB87" t="s">
         <v>39</v>
@@ -9310,13 +9361,13 @@
     </row>
     <row r="88" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>529</v>
+        <v>512</v>
       </c>
       <c r="C88" t="s">
-        <v>530</v>
+        <v>513</v>
       </c>
       <c r="D88" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
       <c r="E88" t="s">
         <v>33</v>
@@ -9358,10 +9409,13 @@
         <v>10</v>
       </c>
       <c r="Y88" t="s">
-        <v>531</v>
+        <v>515</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>516</v>
       </c>
       <c r="AA88" t="s">
-        <v>532</v>
+        <v>517</v>
       </c>
       <c r="AB88" t="s">
         <v>39</v>
@@ -9375,13 +9429,13 @@
     </row>
     <row r="89" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
       <c r="C89" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="D89" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="E89" t="s">
         <v>33</v>
@@ -9399,13 +9453,13 @@
         <v>54</v>
       </c>
       <c r="K89" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="L89" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="M89" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="N89" t="s">
         <v>33</v>
@@ -9417,19 +9471,16 @@
         <v>38</v>
       </c>
       <c r="Q89">
-        <v>11.99</v>
+        <v>14.99</v>
       </c>
       <c r="R89">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Y89" t="s">
-        <v>536</v>
-      </c>
-      <c r="Z89" t="s">
-        <v>537</v>
+        <v>58</v>
       </c>
       <c r="AA89" t="s">
-        <v>538</v>
+        <v>524</v>
       </c>
       <c r="AB89" t="s">
         <v>39</v>
@@ -9443,13 +9494,13 @@
     </row>
     <row r="90" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>539</v>
+        <v>525</v>
       </c>
       <c r="C90" t="s">
-        <v>540</v>
+        <v>526</v>
       </c>
       <c r="D90" t="s">
-        <v>541</v>
+        <v>527</v>
       </c>
       <c r="E90" t="s">
         <v>33</v>
@@ -9491,13 +9542,10 @@
         <v>10</v>
       </c>
       <c r="Y90" t="s">
-        <v>71</v>
-      </c>
-      <c r="Z90" t="s">
-        <v>542</v>
+        <v>90</v>
       </c>
       <c r="AA90" t="s">
-        <v>543</v>
+        <v>528</v>
       </c>
       <c r="AB90" t="s">
         <v>39</v>
@@ -9511,13 +9559,13 @@
     </row>
     <row r="91" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>544</v>
+        <v>529</v>
       </c>
       <c r="C91" t="s">
-        <v>545</v>
+        <v>530</v>
       </c>
       <c r="D91" t="s">
-        <v>546</v>
+        <v>527</v>
       </c>
       <c r="E91" t="s">
         <v>33</v>
@@ -9535,37 +9583,34 @@
         <v>54</v>
       </c>
       <c r="K91" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L91" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M91" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N91" t="s">
         <v>33</v>
       </c>
       <c r="O91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P91" t="s">
         <v>38</v>
       </c>
       <c r="Q91">
-        <v>76.98</v>
+        <v>59.99</v>
       </c>
       <c r="R91">
-        <v>12.84</v>
+        <v>10</v>
       </c>
       <c r="Y91" t="s">
-        <v>547</v>
-      </c>
-      <c r="Z91" t="s">
-        <v>548</v>
+        <v>531</v>
       </c>
       <c r="AA91" t="s">
-        <v>549</v>
+        <v>532</v>
       </c>
       <c r="AB91" t="s">
         <v>39</v>
@@ -9579,13 +9624,13 @@
     </row>
     <row r="92" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>550</v>
+        <v>533</v>
       </c>
       <c r="C92" t="s">
-        <v>551</v>
+        <v>534</v>
       </c>
       <c r="D92" t="s">
-        <v>552</v>
+        <v>535</v>
       </c>
       <c r="E92" t="s">
         <v>33</v>
@@ -9603,13 +9648,13 @@
         <v>54</v>
       </c>
       <c r="K92" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L92" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M92" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N92" t="s">
         <v>33</v>
@@ -9621,16 +9666,19 @@
         <v>38</v>
       </c>
       <c r="Q92">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R92">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y92" t="s">
-        <v>553</v>
+        <v>536</v>
+      </c>
+      <c r="Z92" t="s">
+        <v>537</v>
       </c>
       <c r="AA92" t="s">
-        <v>554</v>
+        <v>538</v>
       </c>
       <c r="AB92" t="s">
         <v>39</v>
@@ -9644,13 +9692,13 @@
     </row>
     <row r="93" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>555</v>
+        <v>539</v>
       </c>
       <c r="C93" t="s">
-        <v>556</v>
+        <v>540</v>
       </c>
       <c r="D93" t="s">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="E93" t="s">
         <v>33</v>
@@ -9692,10 +9740,13 @@
         <v>10</v>
       </c>
       <c r="Y93" t="s">
-        <v>558</v>
+        <v>71</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>542</v>
       </c>
       <c r="AA93" t="s">
-        <v>559</v>
+        <v>543</v>
       </c>
       <c r="AB93" t="s">
         <v>39</v>
@@ -9709,13 +9760,13 @@
     </row>
     <row r="94" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>418</v>
+        <v>544</v>
       </c>
       <c r="C94" t="s">
-        <v>419</v>
+        <v>545</v>
       </c>
       <c r="D94" t="s">
-        <v>560</v>
+        <v>546</v>
       </c>
       <c r="E94" t="s">
         <v>33</v>
@@ -9733,34 +9784,37 @@
         <v>54</v>
       </c>
       <c r="K94" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L94" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M94" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N94" t="s">
         <v>33</v>
       </c>
       <c r="O94">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P94" t="s">
         <v>38</v>
       </c>
       <c r="Q94">
-        <v>59.99</v>
+        <v>76.98</v>
       </c>
       <c r="R94">
-        <v>10</v>
+        <v>12.84</v>
       </c>
       <c r="Y94" t="s">
-        <v>420</v>
+        <v>547</v>
+      </c>
+      <c r="Z94" t="s">
+        <v>548</v>
       </c>
       <c r="AA94" t="s">
-        <v>421</v>
+        <v>549</v>
       </c>
       <c r="AB94" t="s">
         <v>39</v>
@@ -9774,13 +9828,13 @@
     </row>
     <row r="95" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="C95" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
       <c r="D95" t="s">
-        <v>563</v>
+        <v>552</v>
       </c>
       <c r="E95" t="s">
         <v>33</v>
@@ -9822,13 +9876,10 @@
         <v>10</v>
       </c>
       <c r="Y95" t="s">
-        <v>564</v>
-      </c>
-      <c r="Z95" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="AA95" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="AB95" t="s">
         <v>39</v>
@@ -9842,13 +9893,13 @@
     </row>
     <row r="96" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="C96" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
       <c r="D96" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="E96" t="s">
         <v>33</v>
@@ -9866,13 +9917,13 @@
         <v>54</v>
       </c>
       <c r="K96" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L96" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M96" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="N96" t="s">
         <v>33</v>
@@ -9884,16 +9935,16 @@
         <v>38</v>
       </c>
       <c r="Q96">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R96">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y96" t="s">
-        <v>69</v>
+        <v>558</v>
       </c>
       <c r="AA96" t="s">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="AB96" t="s">
         <v>39</v>
@@ -9907,13 +9958,13 @@
     </row>
     <row r="97" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C97" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="D97" t="s">
-        <v>415</v>
+        <v>560</v>
       </c>
       <c r="E97" t="s">
         <v>33</v>
@@ -9955,10 +10006,10 @@
         <v>10</v>
       </c>
       <c r="Y97" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="AA97" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="AB97" t="s">
         <v>39</v>
@@ -9972,13 +10023,13 @@
     </row>
     <row r="98" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>422</v>
+        <v>561</v>
       </c>
       <c r="C98" t="s">
-        <v>423</v>
+        <v>562</v>
       </c>
       <c r="D98" t="s">
-        <v>424</v>
+        <v>563</v>
       </c>
       <c r="E98" t="s">
         <v>33</v>
@@ -9996,13 +10047,13 @@
         <v>54</v>
       </c>
       <c r="K98" t="s">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="L98" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="M98" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="N98" t="s">
         <v>33</v>
@@ -10014,16 +10065,19 @@
         <v>38</v>
       </c>
       <c r="Q98">
-        <v>22.99</v>
+        <v>59.99</v>
       </c>
       <c r="R98">
-        <v>3.83</v>
+        <v>10</v>
       </c>
       <c r="Y98" t="s">
-        <v>425</v>
+        <v>564</v>
+      </c>
+      <c r="Z98" t="s">
+        <v>565</v>
       </c>
       <c r="AA98" t="s">
-        <v>426</v>
+        <v>566</v>
       </c>
       <c r="AB98" t="s">
         <v>39</v>
@@ -10037,13 +10091,13 @@
     </row>
     <row r="99" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>427</v>
+        <v>567</v>
       </c>
       <c r="C99" t="s">
-        <v>428</v>
+        <v>568</v>
       </c>
       <c r="D99" t="s">
-        <v>424</v>
+        <v>569</v>
       </c>
       <c r="E99" t="s">
         <v>33</v>
@@ -10061,13 +10115,13 @@
         <v>54</v>
       </c>
       <c r="K99" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="L99" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="M99" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="N99" t="s">
         <v>33</v>
@@ -10079,19 +10133,16 @@
         <v>38</v>
       </c>
       <c r="Q99">
-        <v>11.99</v>
+        <v>14.99</v>
       </c>
       <c r="R99">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Y99" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z99" t="s">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="AA99" t="s">
-        <v>429</v>
+        <v>570</v>
       </c>
       <c r="AB99" t="s">
         <v>39</v>
@@ -10105,13 +10156,13 @@
     </row>
     <row r="100" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>430</v>
+        <v>413</v>
       </c>
       <c r="C100" t="s">
-        <v>431</v>
+        <v>414</v>
       </c>
       <c r="D100" t="s">
-        <v>432</v>
+        <v>415</v>
       </c>
       <c r="E100" t="s">
         <v>33</v>
@@ -10129,13 +10180,13 @@
         <v>54</v>
       </c>
       <c r="K100" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L100" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M100" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N100" t="s">
         <v>33</v>
@@ -10147,19 +10198,16 @@
         <v>38</v>
       </c>
       <c r="Q100">
-        <v>38.49</v>
+        <v>59.99</v>
       </c>
       <c r="R100">
-        <v>6.42</v>
+        <v>10</v>
       </c>
       <c r="Y100" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z100" t="s">
-        <v>433</v>
+        <v>416</v>
       </c>
       <c r="AA100" t="s">
-        <v>434</v>
+        <v>417</v>
       </c>
       <c r="AB100" t="s">
         <v>39</v>
@@ -10173,13 +10221,13 @@
     </row>
     <row r="101" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="C101" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="D101" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="E101" t="s">
         <v>33</v>
@@ -10197,13 +10245,13 @@
         <v>54</v>
       </c>
       <c r="K101" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="L101" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="M101" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="N101" t="s">
         <v>33</v>
@@ -10215,16 +10263,16 @@
         <v>38</v>
       </c>
       <c r="Q101">
-        <v>14.99</v>
+        <v>22.99</v>
       </c>
       <c r="R101">
-        <v>2.5</v>
+        <v>3.83</v>
       </c>
       <c r="Y101" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="AA101" t="s">
-        <v>439</v>
+        <v>426</v>
       </c>
       <c r="AB101" t="s">
         <v>39</v>
@@ -10238,13 +10286,13 @@
     </row>
     <row r="102" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="C102" t="s">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="D102" t="s">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="E102" t="s">
         <v>33</v>
@@ -10262,13 +10310,13 @@
         <v>54</v>
       </c>
       <c r="K102" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L102" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M102" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="N102" t="s">
         <v>33</v>
@@ -10280,16 +10328,19 @@
         <v>38</v>
       </c>
       <c r="Q102">
-        <v>37.99</v>
+        <v>11.99</v>
       </c>
       <c r="R102">
-        <v>6.33</v>
+        <v>2</v>
       </c>
       <c r="Y102" t="s">
-        <v>443</v>
+        <v>96</v>
+      </c>
+      <c r="Z102" t="s">
+        <v>97</v>
       </c>
       <c r="AA102" t="s">
-        <v>444</v>
+        <v>429</v>
       </c>
       <c r="AB102" t="s">
         <v>39</v>
@@ -10303,13 +10354,13 @@
     </row>
     <row r="103" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="C103" t="s">
-        <v>446</v>
+        <v>431</v>
       </c>
       <c r="D103" t="s">
-        <v>447</v>
+        <v>432</v>
       </c>
       <c r="E103" t="s">
         <v>33</v>
@@ -10327,13 +10378,13 @@
         <v>54</v>
       </c>
       <c r="K103" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L103" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M103" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N103" t="s">
         <v>33</v>
@@ -10345,16 +10396,19 @@
         <v>38</v>
       </c>
       <c r="Q103">
-        <v>59.99</v>
+        <v>38.49</v>
       </c>
       <c r="R103">
-        <v>10</v>
+        <v>6.42</v>
       </c>
       <c r="Y103" t="s">
-        <v>448</v>
+        <v>59</v>
+      </c>
+      <c r="Z103" t="s">
+        <v>433</v>
       </c>
       <c r="AA103" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="AB103" t="s">
         <v>39</v>
@@ -10368,16 +10422,16 @@
     </row>
     <row r="104" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="C104" t="s">
-        <v>451</v>
+        <v>436</v>
       </c>
       <c r="D104" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="E104" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F104" t="s">
         <v>34</v>
@@ -10392,22 +10446,34 @@
         <v>54</v>
       </c>
       <c r="K104" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="L104" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="M104" t="s">
-        <v>42</v>
+        <v>86</v>
+      </c>
+      <c r="N104" t="s">
+        <v>33</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P104" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q104">
+        <v>14.99</v>
+      </c>
+      <c r="R104">
+        <v>2.5</v>
       </c>
       <c r="Y104" t="s">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="AA104" t="s">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="AB104" t="s">
         <v>39</v>
@@ -10421,13 +10487,13 @@
     </row>
     <row r="105" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>403</v>
+        <v>440</v>
       </c>
       <c r="C105" t="s">
-        <v>404</v>
+        <v>441</v>
       </c>
       <c r="D105" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="E105" t="s">
         <v>33</v>
@@ -10445,13 +10511,13 @@
         <v>54</v>
       </c>
       <c r="K105" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L105" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M105" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N105" t="s">
         <v>33</v>
@@ -10463,22 +10529,16 @@
         <v>38</v>
       </c>
       <c r="Q105">
-        <v>59.99</v>
+        <v>37.99</v>
       </c>
       <c r="R105">
-        <v>10</v>
-      </c>
-      <c r="S105">
-        <v>5.99</v>
-      </c>
-      <c r="T105">
-        <v>1</v>
+        <v>6.33</v>
       </c>
       <c r="Y105" t="s">
-        <v>405</v>
+        <v>443</v>
       </c>
       <c r="AA105" t="s">
-        <v>406</v>
+        <v>444</v>
       </c>
       <c r="AB105" t="s">
         <v>39</v>
@@ -10492,13 +10552,13 @@
     </row>
     <row r="106" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>407</v>
+        <v>445</v>
       </c>
       <c r="C106" t="s">
-        <v>408</v>
+        <v>446</v>
       </c>
       <c r="D106" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="E106" t="s">
         <v>33</v>
@@ -10516,13 +10576,13 @@
         <v>54</v>
       </c>
       <c r="K106" t="s">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="L106" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="M106" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="N106" t="s">
         <v>33</v>
@@ -10534,16 +10594,16 @@
         <v>38</v>
       </c>
       <c r="Q106">
-        <v>22.99</v>
+        <v>59.99</v>
       </c>
       <c r="R106">
-        <v>3.83</v>
+        <v>10</v>
       </c>
       <c r="Y106" t="s">
-        <v>409</v>
+        <v>448</v>
       </c>
       <c r="AA106" t="s">
-        <v>410</v>
+        <v>449</v>
       </c>
       <c r="AB106" t="s">
         <v>39</v>
@@ -10557,16 +10617,16 @@
     </row>
     <row r="107" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>399</v>
+        <v>450</v>
       </c>
       <c r="C107" t="s">
-        <v>400</v>
+        <v>451</v>
       </c>
       <c r="D107" t="s">
-        <v>411</v>
+        <v>452</v>
       </c>
       <c r="E107" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F107" t="s">
         <v>34</v>
@@ -10581,34 +10641,22 @@
         <v>54</v>
       </c>
       <c r="K107" t="s">
-        <v>340</v>
+        <v>40</v>
       </c>
       <c r="L107" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="M107" t="s">
-        <v>143</v>
-      </c>
-      <c r="N107" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O107">
-        <v>1</v>
-      </c>
-      <c r="P107" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q107">
-        <v>44.99</v>
-      </c>
-      <c r="R107">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Y107" t="s">
-        <v>401</v>
+        <v>453</v>
       </c>
       <c r="AA107" t="s">
-        <v>402</v>
+        <v>454</v>
       </c>
       <c r="AB107" t="s">
         <v>39</v>
@@ -10622,13 +10670,13 @@
     </row>
     <row r="108" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="C108" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="D108" t="s">
-        <v>412</v>
+        <v>455</v>
       </c>
       <c r="E108" t="s">
         <v>33</v>
@@ -10646,13 +10694,13 @@
         <v>54</v>
       </c>
       <c r="K108" t="s">
-        <v>340</v>
+        <v>40</v>
       </c>
       <c r="L108" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="M108" t="s">
-        <v>143</v>
+        <v>42</v>
       </c>
       <c r="N108" t="s">
         <v>33</v>
@@ -10664,19 +10712,22 @@
         <v>38</v>
       </c>
       <c r="Q108">
-        <v>44.99</v>
+        <v>59.99</v>
       </c>
       <c r="R108">
-        <v>7.5</v>
+        <v>10</v>
+      </c>
+      <c r="S108">
+        <v>5.99</v>
+      </c>
+      <c r="T108">
+        <v>1</v>
       </c>
       <c r="Y108" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z108" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="AA108" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="AB108" t="s">
         <v>39</v>
@@ -10690,13 +10741,13 @@
     </row>
     <row r="109" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>338</v>
+        <v>407</v>
       </c>
       <c r="C109" t="s">
-        <v>339</v>
+        <v>408</v>
       </c>
       <c r="D109" t="s">
-        <v>662</v>
+        <v>456</v>
       </c>
       <c r="E109" t="s">
         <v>33</v>
@@ -10714,13 +10765,13 @@
         <v>54</v>
       </c>
       <c r="K109" t="s">
-        <v>340</v>
+        <v>79</v>
       </c>
       <c r="L109" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="M109" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
       <c r="N109" t="s">
         <v>33</v>
@@ -10732,16 +10783,16 @@
         <v>38</v>
       </c>
       <c r="Q109">
-        <v>44.99</v>
+        <v>22.99</v>
       </c>
       <c r="R109">
-        <v>7.5</v>
+        <v>3.83</v>
       </c>
       <c r="Y109" t="s">
-        <v>341</v>
+        <v>409</v>
       </c>
       <c r="AA109" t="s">
-        <v>342</v>
+        <v>410</v>
       </c>
       <c r="AB109" t="s">
         <v>39</v>
@@ -10755,13 +10806,13 @@
     </row>
     <row r="110" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>663</v>
+        <v>399</v>
       </c>
       <c r="C110" t="s">
-        <v>664</v>
+        <v>400</v>
       </c>
       <c r="D110" t="s">
-        <v>665</v>
+        <v>411</v>
       </c>
       <c r="E110" t="s">
         <v>33</v>
@@ -10779,13 +10830,13 @@
         <v>54</v>
       </c>
       <c r="K110" t="s">
-        <v>40</v>
+        <v>340</v>
       </c>
       <c r="L110" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="M110" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="N110" t="s">
         <v>33</v>
@@ -10797,25 +10848,22 @@
         <v>38</v>
       </c>
       <c r="Q110">
-        <v>59.99</v>
+        <v>44.99</v>
       </c>
       <c r="R110">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="Y110" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z110" t="s">
-        <v>666</v>
+        <v>401</v>
       </c>
       <c r="AA110" t="s">
-        <v>667</v>
+        <v>402</v>
       </c>
       <c r="AB110" t="s">
         <v>39</v>
       </c>
       <c r="AD110" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG110" t="b">
         <v>0</v>
@@ -10823,13 +10871,13 @@
     </row>
     <row r="111" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>334</v>
+        <v>394</v>
       </c>
       <c r="C111" t="s">
-        <v>335</v>
+        <v>395</v>
       </c>
       <c r="D111" t="s">
-        <v>668</v>
+        <v>412</v>
       </c>
       <c r="E111" t="s">
         <v>33</v>
@@ -10847,13 +10895,13 @@
         <v>54</v>
       </c>
       <c r="K111" t="s">
-        <v>203</v>
+        <v>340</v>
       </c>
       <c r="L111" t="s">
-        <v>204</v>
+        <v>142</v>
       </c>
       <c r="M111" t="s">
-        <v>205</v>
+        <v>143</v>
       </c>
       <c r="N111" t="s">
         <v>33</v>
@@ -10865,16 +10913,19 @@
         <v>38</v>
       </c>
       <c r="Q111">
-        <v>69.989999999999995</v>
+        <v>44.99</v>
       </c>
       <c r="R111">
-        <v>11.67</v>
+        <v>7.5</v>
       </c>
       <c r="Y111" t="s">
-        <v>336</v>
+        <v>396</v>
+      </c>
+      <c r="Z111" t="s">
+        <v>397</v>
       </c>
       <c r="AA111" t="s">
-        <v>337</v>
+        <v>398</v>
       </c>
       <c r="AB111" t="s">
         <v>39</v>
@@ -10888,13 +10939,13 @@
     </row>
     <row r="112" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="C112" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="D112" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="E112" t="s">
         <v>33</v>
@@ -10912,34 +10963,34 @@
         <v>54</v>
       </c>
       <c r="K112" t="s">
-        <v>48</v>
+        <v>340</v>
       </c>
       <c r="L112" t="s">
-        <v>49</v>
+        <v>142</v>
       </c>
       <c r="M112" t="s">
-        <v>50</v>
+        <v>143</v>
       </c>
       <c r="N112" t="s">
         <v>33</v>
       </c>
       <c r="O112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P112" t="s">
         <v>38</v>
       </c>
       <c r="Q112">
-        <v>75.98</v>
+        <v>44.99</v>
       </c>
       <c r="R112">
-        <v>12.66</v>
+        <v>7.5</v>
       </c>
       <c r="Y112" t="s">
-        <v>91</v>
+        <v>341</v>
       </c>
       <c r="AA112" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="AB112" t="s">
         <v>39</v>
@@ -10953,13 +11004,13 @@
     </row>
     <row r="113" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>343</v>
+        <v>663</v>
       </c>
       <c r="C113" t="s">
-        <v>344</v>
+        <v>664</v>
       </c>
       <c r="D113" t="s">
-        <v>345</v>
+        <v>665</v>
       </c>
       <c r="E113" t="s">
         <v>33</v>
@@ -11001,16 +11052,19 @@
         <v>10</v>
       </c>
       <c r="Y113" t="s">
-        <v>346</v>
+        <v>62</v>
+      </c>
+      <c r="Z113" t="s">
+        <v>666</v>
       </c>
       <c r="AA113" t="s">
-        <v>347</v>
+        <v>667</v>
       </c>
       <c r="AB113" t="s">
         <v>39</v>
       </c>
       <c r="AD113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG113" t="b">
         <v>0</v>
@@ -11018,13 +11072,13 @@
     </row>
     <row r="114" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>288</v>
+        <v>334</v>
       </c>
       <c r="C114" t="s">
-        <v>289</v>
+        <v>335</v>
       </c>
       <c r="D114" t="s">
-        <v>348</v>
+        <v>668</v>
       </c>
       <c r="E114" t="s">
         <v>33</v>
@@ -11039,37 +11093,37 @@
         <v>36</v>
       </c>
       <c r="J114" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K114" t="s">
-        <v>48</v>
+        <v>203</v>
       </c>
       <c r="L114" t="s">
-        <v>49</v>
+        <v>204</v>
       </c>
       <c r="M114" t="s">
-        <v>50</v>
+        <v>205</v>
       </c>
       <c r="N114" t="s">
         <v>33</v>
       </c>
       <c r="O114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P114" t="s">
         <v>38</v>
       </c>
       <c r="Q114">
-        <v>75.98</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="R114">
-        <v>12.66</v>
+        <v>11.67</v>
       </c>
       <c r="Y114" t="s">
-        <v>290</v>
+        <v>336</v>
       </c>
       <c r="AA114" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="AB114" t="s">
         <v>39</v>
@@ -11083,13 +11137,13 @@
     </row>
     <row r="115" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="C115" t="s">
-        <v>350</v>
+        <v>327</v>
       </c>
       <c r="D115" t="s">
-        <v>351</v>
+        <v>669</v>
       </c>
       <c r="E115" t="s">
         <v>33</v>
@@ -11119,25 +11173,22 @@
         <v>33</v>
       </c>
       <c r="O115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P115" t="s">
         <v>38</v>
       </c>
       <c r="Q115">
-        <v>37.99</v>
+        <v>75.98</v>
       </c>
       <c r="R115">
-        <v>6.33</v>
+        <v>12.66</v>
       </c>
       <c r="Y115" t="s">
-        <v>352</v>
-      </c>
-      <c r="Z115" t="s">
-        <v>353</v>
+        <v>91</v>
       </c>
       <c r="AA115" t="s">
-        <v>354</v>
+        <v>328</v>
       </c>
       <c r="AB115" t="s">
         <v>39</v>
@@ -11151,13 +11202,13 @@
     </row>
     <row r="116" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="C116" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="D116" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="E116" t="s">
         <v>33</v>
@@ -11175,13 +11226,13 @@
         <v>54</v>
       </c>
       <c r="K116" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L116" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M116" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N116" t="s">
         <v>33</v>
@@ -11193,16 +11244,16 @@
         <v>38</v>
       </c>
       <c r="Q116">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R116">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y116" t="s">
-        <v>58</v>
+        <v>346</v>
       </c>
       <c r="AA116" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="AB116" t="s">
         <v>39</v>
@@ -11216,13 +11267,13 @@
     </row>
     <row r="117" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>359</v>
+        <v>288</v>
       </c>
       <c r="C117" t="s">
-        <v>360</v>
+        <v>289</v>
       </c>
       <c r="D117" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="E117" t="s">
         <v>33</v>
@@ -11237,7 +11288,7 @@
         <v>36</v>
       </c>
       <c r="J117" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K117" t="s">
         <v>48</v>
@@ -11264,13 +11315,10 @@
         <v>12.66</v>
       </c>
       <c r="Y117" t="s">
-        <v>101</v>
-      </c>
-      <c r="Z117" t="s">
-        <v>59</v>
+        <v>290</v>
       </c>
       <c r="AA117" t="s">
-        <v>362</v>
+        <v>291</v>
       </c>
       <c r="AB117" t="s">
         <v>39</v>
@@ -11284,13 +11332,13 @@
     </row>
     <row r="118" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="C118" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="D118" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="E118" t="s">
         <v>33</v>
@@ -11308,13 +11356,13 @@
         <v>54</v>
       </c>
       <c r="K118" t="s">
-        <v>260</v>
+        <v>48</v>
       </c>
       <c r="L118" t="s">
-        <v>261</v>
+        <v>49</v>
       </c>
       <c r="M118" t="s">
-        <v>262</v>
+        <v>50</v>
       </c>
       <c r="N118" t="s">
         <v>33</v>
@@ -11326,16 +11374,19 @@
         <v>38</v>
       </c>
       <c r="Q118">
-        <v>24.49</v>
+        <v>37.99</v>
       </c>
       <c r="R118">
-        <v>4.08</v>
+        <v>6.33</v>
       </c>
       <c r="Y118" t="s">
-        <v>366</v>
+        <v>352</v>
+      </c>
+      <c r="Z118" t="s">
+        <v>353</v>
       </c>
       <c r="AA118" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="AB118" t="s">
         <v>39</v>
@@ -11349,13 +11400,13 @@
     </row>
     <row r="119" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>265</v>
+        <v>355</v>
       </c>
       <c r="C119" t="s">
-        <v>266</v>
+        <v>356</v>
       </c>
       <c r="D119" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="E119" t="s">
         <v>33</v>
@@ -11373,13 +11424,13 @@
         <v>54</v>
       </c>
       <c r="K119" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L119" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M119" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="N119" t="s">
         <v>33</v>
@@ -11391,16 +11442,16 @@
         <v>38</v>
       </c>
       <c r="Q119">
-        <v>37.99</v>
+        <v>11.99</v>
       </c>
       <c r="R119">
-        <v>6.33</v>
+        <v>2</v>
       </c>
       <c r="Y119" t="s">
-        <v>267</v>
+        <v>58</v>
       </c>
       <c r="AA119" t="s">
-        <v>268</v>
+        <v>358</v>
       </c>
       <c r="AB119" t="s">
         <v>39</v>
@@ -11414,13 +11465,13 @@
     </row>
     <row r="120" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="C120" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="D120" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="E120" t="s">
         <v>33</v>
@@ -11438,40 +11489,37 @@
         <v>54</v>
       </c>
       <c r="K120" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L120" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M120" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N120" t="s">
         <v>33</v>
       </c>
       <c r="O120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P120" t="s">
         <v>38</v>
       </c>
       <c r="Q120">
-        <v>11.99</v>
+        <v>75.98</v>
       </c>
       <c r="R120">
-        <v>2</v>
-      </c>
-      <c r="S120">
-        <v>5.99</v>
-      </c>
-      <c r="T120">
-        <v>1</v>
+        <v>12.66</v>
       </c>
       <c r="Y120" t="s">
-        <v>84</v>
+        <v>101</v>
+      </c>
+      <c r="Z120" t="s">
+        <v>59</v>
       </c>
       <c r="AA120" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="AB120" t="s">
         <v>39</v>
@@ -11485,13 +11533,13 @@
     </row>
     <row r="121" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="C121" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="D121" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="E121" t="s">
         <v>33</v>
@@ -11533,10 +11581,10 @@
         <v>4.08</v>
       </c>
       <c r="Y121" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="AA121" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="AB121" t="s">
         <v>39</v>
@@ -11550,13 +11598,13 @@
     </row>
     <row r="122" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>378</v>
+        <v>265</v>
       </c>
       <c r="C122" t="s">
-        <v>379</v>
+        <v>266</v>
       </c>
       <c r="D122" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="E122" t="s">
         <v>33</v>
@@ -11574,13 +11622,13 @@
         <v>54</v>
       </c>
       <c r="K122" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L122" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M122" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N122" t="s">
         <v>33</v>
@@ -11592,16 +11640,16 @@
         <v>38</v>
       </c>
       <c r="Q122">
-        <v>59.99</v>
+        <v>37.99</v>
       </c>
       <c r="R122">
-        <v>10</v>
+        <v>6.33</v>
       </c>
       <c r="Y122" t="s">
-        <v>57</v>
+        <v>267</v>
       </c>
       <c r="AA122" t="s">
-        <v>381</v>
+        <v>268</v>
       </c>
       <c r="AB122" t="s">
         <v>39</v>
@@ -11615,13 +11663,13 @@
     </row>
     <row r="123" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="C123" t="s">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="D123" t="s">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="E123" t="s">
         <v>33</v>
@@ -11662,11 +11710,17 @@
       <c r="R123">
         <v>2</v>
       </c>
+      <c r="S123">
+        <v>5.99</v>
+      </c>
+      <c r="T123">
+        <v>1</v>
+      </c>
       <c r="Y123" t="s">
-        <v>385</v>
+        <v>84</v>
       </c>
       <c r="AA123" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="AB123" t="s">
         <v>39</v>
@@ -11680,16 +11734,16 @@
     </row>
     <row r="124" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="C124" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="D124" t="s">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="E124" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F124" t="s">
         <v>34</v>
@@ -11704,25 +11758,34 @@
         <v>54</v>
       </c>
       <c r="K124" t="s">
-        <v>43</v>
+        <v>260</v>
       </c>
       <c r="L124" t="s">
-        <v>44</v>
+        <v>261</v>
       </c>
       <c r="M124" t="s">
-        <v>45</v>
+        <v>262</v>
+      </c>
+      <c r="N124" t="s">
+        <v>33</v>
       </c>
       <c r="O124">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P124" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q124">
+        <v>24.49</v>
+      </c>
+      <c r="R124">
+        <v>4.08</v>
       </c>
       <c r="Y124" t="s">
-        <v>390</v>
-      </c>
-      <c r="Z124" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="AA124" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="AB124" t="s">
         <v>39</v>
@@ -11736,13 +11799,13 @@
     </row>
     <row r="125" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>323</v>
+        <v>378</v>
       </c>
       <c r="C125" t="s">
-        <v>324</v>
+        <v>379</v>
       </c>
       <c r="D125" t="s">
-        <v>393</v>
+        <v>380</v>
       </c>
       <c r="E125" t="s">
         <v>33</v>
@@ -11760,13 +11823,13 @@
         <v>54</v>
       </c>
       <c r="K125" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="L125" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="M125" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="N125" t="s">
         <v>33</v>
@@ -11778,16 +11841,16 @@
         <v>38</v>
       </c>
       <c r="Q125">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R125">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y125" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AA125" t="s">
-        <v>325</v>
+        <v>381</v>
       </c>
       <c r="AB125" t="s">
         <v>39</v>
@@ -11801,13 +11864,13 @@
     </row>
     <row r="126" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>318</v>
+        <v>382</v>
       </c>
       <c r="C126" t="s">
-        <v>319</v>
+        <v>383</v>
       </c>
       <c r="D126" t="s">
-        <v>320</v>
+        <v>384</v>
       </c>
       <c r="E126" t="s">
         <v>33</v>
@@ -11849,13 +11912,10 @@
         <v>2</v>
       </c>
       <c r="Y126" t="s">
-        <v>321</v>
-      </c>
-      <c r="Z126" t="s">
-        <v>65</v>
+        <v>385</v>
       </c>
       <c r="AA126" t="s">
-        <v>322</v>
+        <v>386</v>
       </c>
       <c r="AB126" t="s">
         <v>39</v>
@@ -11869,16 +11929,16 @@
     </row>
     <row r="127" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>329</v>
+        <v>387</v>
       </c>
       <c r="C127" t="s">
-        <v>330</v>
+        <v>388</v>
       </c>
       <c r="D127" t="s">
-        <v>331</v>
+        <v>389</v>
       </c>
       <c r="E127" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F127" t="s">
         <v>34</v>
@@ -11893,34 +11953,25 @@
         <v>54</v>
       </c>
       <c r="K127" t="s">
-        <v>260</v>
+        <v>43</v>
       </c>
       <c r="L127" t="s">
-        <v>261</v>
+        <v>44</v>
       </c>
       <c r="M127" t="s">
-        <v>262</v>
-      </c>
-      <c r="N127" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O127">
-        <v>1</v>
-      </c>
-      <c r="P127" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q127">
-        <v>24.49</v>
-      </c>
-      <c r="R127">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="Y127" t="s">
-        <v>332</v>
+        <v>390</v>
+      </c>
+      <c r="Z127" t="s">
+        <v>391</v>
       </c>
       <c r="AA127" t="s">
-        <v>333</v>
+        <v>392</v>
       </c>
       <c r="AB127" t="s">
         <v>39</v>
@@ -11934,13 +11985,13 @@
     </row>
     <row r="128" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>670</v>
+        <v>323</v>
       </c>
       <c r="C128" t="s">
-        <v>671</v>
+        <v>324</v>
       </c>
       <c r="D128" t="s">
-        <v>672</v>
+        <v>393</v>
       </c>
       <c r="E128" t="s">
         <v>33</v>
@@ -11958,13 +12009,13 @@
         <v>54</v>
       </c>
       <c r="K128" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="L128" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="M128" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="N128" t="s">
         <v>33</v>
@@ -11976,16 +12027,16 @@
         <v>38</v>
       </c>
       <c r="Q128">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="R128">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="Y128" t="s">
-        <v>673</v>
+        <v>58</v>
       </c>
       <c r="AA128" t="s">
-        <v>674</v>
+        <v>325</v>
       </c>
       <c r="AB128" t="s">
         <v>39</v>
@@ -11999,13 +12050,13 @@
     </row>
     <row r="129" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>675</v>
+        <v>318</v>
       </c>
       <c r="C129" t="s">
-        <v>676</v>
+        <v>319</v>
       </c>
       <c r="D129" t="s">
-        <v>677</v>
+        <v>320</v>
       </c>
       <c r="E129" t="s">
         <v>33</v>
@@ -12023,13 +12074,13 @@
         <v>54</v>
       </c>
       <c r="K129" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L129" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M129" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="N129" t="s">
         <v>33</v>
@@ -12041,16 +12092,19 @@
         <v>38</v>
       </c>
       <c r="Q129">
-        <v>37.99</v>
+        <v>11.99</v>
       </c>
       <c r="R129">
-        <v>6.33</v>
+        <v>2</v>
       </c>
       <c r="Y129" t="s">
-        <v>678</v>
+        <v>321</v>
+      </c>
+      <c r="Z129" t="s">
+        <v>65</v>
       </c>
       <c r="AA129" t="s">
-        <v>679</v>
+        <v>322</v>
       </c>
       <c r="AB129" t="s">
         <v>39</v>
@@ -12064,13 +12118,13 @@
     </row>
     <row r="130" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>680</v>
+        <v>329</v>
       </c>
       <c r="C130" t="s">
-        <v>681</v>
+        <v>330</v>
       </c>
       <c r="D130" t="s">
-        <v>682</v>
+        <v>331</v>
       </c>
       <c r="E130" t="s">
         <v>33</v>
@@ -12088,13 +12142,13 @@
         <v>54</v>
       </c>
       <c r="K130" t="s">
-        <v>40</v>
+        <v>260</v>
       </c>
       <c r="L130" t="s">
-        <v>41</v>
+        <v>261</v>
       </c>
       <c r="M130" t="s">
-        <v>42</v>
+        <v>262</v>
       </c>
       <c r="N130" t="s">
         <v>33</v>
@@ -12106,19 +12160,16 @@
         <v>38</v>
       </c>
       <c r="Q130">
-        <v>59.99</v>
+        <v>24.49</v>
       </c>
       <c r="R130">
-        <v>10</v>
+        <v>4.08</v>
       </c>
       <c r="Y130" t="s">
-        <v>683</v>
-      </c>
-      <c r="Z130" t="s">
-        <v>76</v>
+        <v>332</v>
       </c>
       <c r="AA130" t="s">
-        <v>684</v>
+        <v>333</v>
       </c>
       <c r="AB130" t="s">
         <v>39</v>
@@ -12132,13 +12183,13 @@
     </row>
     <row r="131" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>685</v>
+        <v>670</v>
       </c>
       <c r="C131" t="s">
-        <v>686</v>
+        <v>671</v>
       </c>
       <c r="D131" t="s">
-        <v>687</v>
+        <v>672</v>
       </c>
       <c r="E131" t="s">
         <v>33</v>
@@ -12156,13 +12207,13 @@
         <v>54</v>
       </c>
       <c r="K131" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L131" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M131" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N131" t="s">
         <v>33</v>
@@ -12174,16 +12225,16 @@
         <v>38</v>
       </c>
       <c r="Q131">
-        <v>37.99</v>
+        <v>59.99</v>
       </c>
       <c r="R131">
-        <v>6.33</v>
+        <v>10</v>
       </c>
       <c r="Y131" t="s">
-        <v>52</v>
+        <v>673</v>
       </c>
       <c r="AA131" t="s">
-        <v>688</v>
+        <v>674</v>
       </c>
       <c r="AB131" t="s">
         <v>39</v>
@@ -12197,16 +12248,16 @@
     </row>
     <row r="132" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>689</v>
+        <v>675</v>
       </c>
       <c r="C132" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D132" t="s">
-        <v>691</v>
+        <v>677</v>
       </c>
       <c r="E132" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F132" t="s">
         <v>34</v>
@@ -12218,7 +12269,7 @@
         <v>36</v>
       </c>
       <c r="J132" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K132" t="s">
         <v>48</v>
@@ -12229,17 +12280,26 @@
       <c r="M132" t="s">
         <v>50</v>
       </c>
+      <c r="N132" t="s">
+        <v>33</v>
+      </c>
       <c r="O132">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P132" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q132">
+        <v>37.99</v>
+      </c>
+      <c r="R132">
+        <v>6.33</v>
       </c>
       <c r="Y132" t="s">
-        <v>692</v>
-      </c>
-      <c r="Z132" t="s">
-        <v>693</v>
+        <v>678</v>
       </c>
       <c r="AA132" t="s">
-        <v>694</v>
+        <v>679</v>
       </c>
       <c r="AB132" t="s">
         <v>39</v>
@@ -12253,16 +12313,16 @@
     </row>
     <row r="133" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>695</v>
+        <v>680</v>
       </c>
       <c r="C133" t="s">
-        <v>696</v>
+        <v>681</v>
       </c>
       <c r="D133" t="s">
-        <v>697</v>
+        <v>682</v>
       </c>
       <c r="E133" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F133" t="s">
         <v>34</v>
@@ -12274,28 +12334,40 @@
         <v>36</v>
       </c>
       <c r="J133" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K133" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L133" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M133" t="s">
-        <v>50</v>
+        <v>42</v>
+      </c>
+      <c r="N133" t="s">
+        <v>33</v>
       </c>
       <c r="O133">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P133" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q133">
+        <v>59.99</v>
+      </c>
+      <c r="R133">
+        <v>10</v>
       </c>
       <c r="Y133" t="s">
-        <v>692</v>
+        <v>683</v>
       </c>
       <c r="Z133" t="s">
-        <v>693</v>
+        <v>76</v>
       </c>
       <c r="AA133" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="AB133" t="s">
         <v>39</v>
@@ -12309,13 +12381,13 @@
     </row>
     <row r="134" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>300</v>
+        <v>685</v>
       </c>
       <c r="C134" t="s">
-        <v>301</v>
+        <v>686</v>
       </c>
       <c r="D134" t="s">
-        <v>698</v>
+        <v>687</v>
       </c>
       <c r="E134" t="s">
         <v>33</v>
@@ -12333,13 +12405,13 @@
         <v>54</v>
       </c>
       <c r="K134" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="L134" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="M134" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="N134" t="s">
         <v>33</v>
@@ -12351,16 +12423,16 @@
         <v>38</v>
       </c>
       <c r="Q134">
-        <v>14.99</v>
+        <v>37.99</v>
       </c>
       <c r="R134">
-        <v>2.5</v>
+        <v>6.33</v>
       </c>
       <c r="Y134" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="AA134" t="s">
-        <v>302</v>
+        <v>688</v>
       </c>
       <c r="AB134" t="s">
         <v>39</v>
@@ -12374,13 +12446,13 @@
     </row>
     <row r="135" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>699</v>
+        <v>689</v>
       </c>
       <c r="C135" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="D135" t="s">
-        <v>701</v>
+        <v>691</v>
       </c>
       <c r="E135" t="s">
         <v>53</v>
@@ -12395,7 +12467,7 @@
         <v>36</v>
       </c>
       <c r="J135" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K135" t="s">
         <v>48</v>
@@ -12430,16 +12502,16 @@
     </row>
     <row r="136" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>303</v>
+        <v>695</v>
       </c>
       <c r="C136" t="s">
-        <v>304</v>
+        <v>696</v>
       </c>
       <c r="D136" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="E136" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F136" t="s">
         <v>34</v>
@@ -12451,37 +12523,28 @@
         <v>36</v>
       </c>
       <c r="J136" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K136" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L136" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M136" t="s">
-        <v>42</v>
-      </c>
-      <c r="N136" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="O136">
-        <v>1</v>
-      </c>
-      <c r="P136" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q136">
-        <v>59.99</v>
-      </c>
-      <c r="R136">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y136" t="s">
-        <v>305</v>
+        <v>692</v>
+      </c>
+      <c r="Z136" t="s">
+        <v>693</v>
       </c>
       <c r="AA136" t="s">
-        <v>306</v>
+        <v>694</v>
       </c>
       <c r="AB136" t="s">
         <v>39</v>
@@ -12495,13 +12558,13 @@
     </row>
     <row r="137" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="C137" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="D137" t="s">
-        <v>294</v>
+        <v>698</v>
       </c>
       <c r="E137" t="s">
         <v>33</v>
@@ -12516,16 +12579,16 @@
         <v>36</v>
       </c>
       <c r="J137" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K137" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="L137" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="M137" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="N137" t="s">
         <v>33</v>
@@ -12537,19 +12600,16 @@
         <v>38</v>
       </c>
       <c r="Q137">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="R137">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="Y137" t="s">
-        <v>77</v>
-      </c>
-      <c r="Z137" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="AA137" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="AB137" t="s">
         <v>39</v>
@@ -12563,16 +12623,16 @@
     </row>
     <row r="138" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>296</v>
+        <v>699</v>
       </c>
       <c r="C138" t="s">
-        <v>297</v>
+        <v>700</v>
       </c>
       <c r="D138" t="s">
-        <v>298</v>
+        <v>701</v>
       </c>
       <c r="E138" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F138" t="s">
         <v>34</v>
@@ -12584,40 +12644,28 @@
         <v>36</v>
       </c>
       <c r="J138" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K138" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L138" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M138" t="s">
-        <v>42</v>
-      </c>
-      <c r="N138" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="O138">
-        <v>1</v>
-      </c>
-      <c r="P138" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q138">
-        <v>59.99</v>
-      </c>
-      <c r="R138">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y138" t="s">
-        <v>62</v>
+        <v>692</v>
       </c>
       <c r="Z138" t="s">
-        <v>51</v>
+        <v>693</v>
       </c>
       <c r="AA138" t="s">
-        <v>299</v>
+        <v>694</v>
       </c>
       <c r="AB138" t="s">
         <v>39</v>
@@ -12631,13 +12679,13 @@
     </row>
     <row r="139" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C139" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D139" t="s">
-        <v>309</v>
+        <v>702</v>
       </c>
       <c r="E139" t="s">
         <v>33</v>
@@ -12652,16 +12700,16 @@
         <v>36</v>
       </c>
       <c r="J139" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K139" t="s">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="L139" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="M139" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="N139" t="s">
         <v>33</v>
@@ -12673,16 +12721,16 @@
         <v>38</v>
       </c>
       <c r="Q139">
-        <v>20.49</v>
+        <v>59.99</v>
       </c>
       <c r="R139">
-        <v>3.42</v>
+        <v>10</v>
       </c>
       <c r="Y139" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="AA139" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="AB139" t="s">
         <v>39</v>
@@ -12696,13 +12744,13 @@
     </row>
     <row r="140" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>312</v>
+        <v>292</v>
       </c>
       <c r="C140" t="s">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="D140" t="s">
-        <v>314</v>
+        <v>294</v>
       </c>
       <c r="E140" t="s">
         <v>33</v>
@@ -12744,13 +12792,13 @@
         <v>10</v>
       </c>
       <c r="Y140" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="Z140" t="s">
-        <v>315</v>
+        <v>92</v>
       </c>
       <c r="AA140" t="s">
-        <v>316</v>
+        <v>295</v>
       </c>
       <c r="AB140" t="s">
         <v>39</v>
@@ -12764,13 +12812,13 @@
     </row>
     <row r="141" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>253</v>
+        <v>296</v>
       </c>
       <c r="C141" t="s">
-        <v>254</v>
+        <v>297</v>
       </c>
       <c r="D141" t="s">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="E141" t="s">
         <v>33</v>
@@ -12785,7 +12833,7 @@
         <v>36</v>
       </c>
       <c r="J141" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K141" t="s">
         <v>40</v>
@@ -12812,13 +12860,13 @@
         <v>10</v>
       </c>
       <c r="Y141" t="s">
-        <v>255</v>
+        <v>62</v>
       </c>
       <c r="Z141" t="s">
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="AA141" t="s">
-        <v>256</v>
+        <v>299</v>
       </c>
       <c r="AB141" t="s">
         <v>39</v>
@@ -12832,13 +12880,13 @@
     </row>
     <row r="142" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>257</v>
+        <v>307</v>
       </c>
       <c r="C142" t="s">
-        <v>258</v>
+        <v>308</v>
       </c>
       <c r="D142" t="s">
-        <v>259</v>
+        <v>309</v>
       </c>
       <c r="E142" t="s">
         <v>33</v>
@@ -12853,16 +12901,16 @@
         <v>36</v>
       </c>
       <c r="J142" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K142" t="s">
-        <v>260</v>
+        <v>87</v>
       </c>
       <c r="L142" t="s">
-        <v>261</v>
+        <v>88</v>
       </c>
       <c r="M142" t="s">
-        <v>262</v>
+        <v>89</v>
       </c>
       <c r="N142" t="s">
         <v>33</v>
@@ -12874,19 +12922,16 @@
         <v>38</v>
       </c>
       <c r="Q142">
-        <v>24.49</v>
+        <v>20.49</v>
       </c>
       <c r="R142">
-        <v>4.08</v>
+        <v>3.42</v>
       </c>
       <c r="Y142" t="s">
-        <v>263</v>
-      </c>
-      <c r="Z142" t="s">
-        <v>64</v>
+        <v>310</v>
       </c>
       <c r="AA142" t="s">
-        <v>264</v>
+        <v>311</v>
       </c>
       <c r="AB142" t="s">
         <v>39</v>
@@ -12900,13 +12945,13 @@
     </row>
     <row r="143" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>269</v>
+        <v>312</v>
       </c>
       <c r="C143" t="s">
-        <v>270</v>
+        <v>313</v>
       </c>
       <c r="D143" t="s">
-        <v>271</v>
+        <v>314</v>
       </c>
       <c r="E143" t="s">
         <v>33</v>
@@ -12921,7 +12966,7 @@
         <v>36</v>
       </c>
       <c r="J143" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K143" t="s">
         <v>40</v>
@@ -12948,10 +12993,13 @@
         <v>10</v>
       </c>
       <c r="Y143" t="s">
-        <v>272</v>
+        <v>100</v>
+      </c>
+      <c r="Z143" t="s">
+        <v>315</v>
       </c>
       <c r="AA143" t="s">
-        <v>273</v>
+        <v>316</v>
       </c>
       <c r="AB143" t="s">
         <v>39</v>
@@ -12965,13 +13013,13 @@
     </row>
     <row r="144" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>149</v>
+        <v>253</v>
       </c>
       <c r="C144" t="s">
-        <v>150</v>
+        <v>254</v>
       </c>
       <c r="D144" t="s">
-        <v>274</v>
+        <v>317</v>
       </c>
       <c r="E144" t="s">
         <v>33</v>
@@ -13013,10 +13061,13 @@
         <v>10</v>
       </c>
       <c r="Y144" t="s">
-        <v>63</v>
+        <v>255</v>
+      </c>
+      <c r="Z144" t="s">
+        <v>102</v>
       </c>
       <c r="AA144" t="s">
-        <v>151</v>
+        <v>256</v>
       </c>
       <c r="AB144" t="s">
         <v>39</v>
@@ -13030,13 +13081,13 @@
     </row>
     <row r="145" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="C145" t="s">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="D145" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="E145" t="s">
         <v>33</v>
@@ -13054,37 +13105,37 @@
         <v>54</v>
       </c>
       <c r="K145" t="s">
-        <v>40</v>
+        <v>260</v>
       </c>
       <c r="L145" t="s">
-        <v>41</v>
+        <v>261</v>
       </c>
       <c r="M145" t="s">
-        <v>42</v>
+        <v>262</v>
       </c>
       <c r="N145" t="s">
         <v>33</v>
       </c>
       <c r="O145">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P145" t="s">
         <v>38</v>
       </c>
       <c r="Q145">
-        <v>119.98</v>
+        <v>24.49</v>
       </c>
       <c r="R145">
-        <v>20</v>
+        <v>4.08</v>
       </c>
       <c r="Y145" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="Z145" t="s">
-        <v>279</v>
+        <v>64</v>
       </c>
       <c r="AA145" t="s">
-        <v>280</v>
+        <v>264</v>
       </c>
       <c r="AB145" t="s">
         <v>39</v>
@@ -13098,13 +13149,13 @@
     </row>
     <row r="146" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C146" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="D146" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="E146" t="s">
         <v>33</v>
@@ -13119,16 +13170,16 @@
         <v>36</v>
       </c>
       <c r="J146" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K146" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L146" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M146" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N146" t="s">
         <v>33</v>
@@ -13140,16 +13191,16 @@
         <v>38</v>
       </c>
       <c r="Q146">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R146">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y146" t="s">
-        <v>75</v>
+        <v>272</v>
       </c>
       <c r="AA146" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="AB146" t="s">
         <v>39</v>
@@ -13163,16 +13214,16 @@
     </row>
     <row r="147" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>238</v>
+        <v>149</v>
       </c>
       <c r="C147" t="s">
-        <v>239</v>
+        <v>150</v>
       </c>
       <c r="D147" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="E147" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F147" t="s">
         <v>34</v>
@@ -13195,14 +13246,26 @@
       <c r="M147" t="s">
         <v>42</v>
       </c>
+      <c r="N147" t="s">
+        <v>33</v>
+      </c>
       <c r="O147">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P147" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q147">
+        <v>59.99</v>
+      </c>
+      <c r="R147">
+        <v>10</v>
       </c>
       <c r="Y147" t="s">
-        <v>240</v>
+        <v>63</v>
       </c>
       <c r="AA147" t="s">
-        <v>241</v>
+        <v>151</v>
       </c>
       <c r="AB147" t="s">
         <v>39</v>
@@ -13216,13 +13279,13 @@
     </row>
     <row r="148" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>224</v>
+        <v>275</v>
       </c>
       <c r="C148" t="s">
-        <v>225</v>
+        <v>276</v>
       </c>
       <c r="D148" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="E148" t="s">
         <v>33</v>
@@ -13252,22 +13315,25 @@
         <v>33</v>
       </c>
       <c r="O148">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P148" t="s">
         <v>38</v>
       </c>
       <c r="Q148">
-        <v>59.99</v>
+        <v>119.98</v>
       </c>
       <c r="R148">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y148" t="s">
-        <v>226</v>
+        <v>278</v>
+      </c>
+      <c r="Z148" t="s">
+        <v>279</v>
       </c>
       <c r="AA148" t="s">
-        <v>227</v>
+        <v>280</v>
       </c>
       <c r="AB148" t="s">
         <v>39</v>
@@ -13281,13 +13347,13 @@
     </row>
     <row r="149" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>213</v>
+        <v>281</v>
       </c>
       <c r="C149" t="s">
-        <v>214</v>
+        <v>282</v>
       </c>
       <c r="D149" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="E149" t="s">
         <v>33</v>
@@ -13302,16 +13368,16 @@
         <v>36</v>
       </c>
       <c r="J149" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K149" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L149" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M149" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N149" t="s">
         <v>33</v>
@@ -13323,19 +13389,16 @@
         <v>38</v>
       </c>
       <c r="Q149">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R149">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y149" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z149" t="s">
-        <v>216</v>
+        <v>75</v>
       </c>
       <c r="AA149" t="s">
-        <v>217</v>
+        <v>284</v>
       </c>
       <c r="AB149" t="s">
         <v>39</v>
@@ -13349,16 +13412,16 @@
     </row>
     <row r="150" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="C150" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="D150" t="s">
-        <v>220</v>
+        <v>285</v>
       </c>
       <c r="E150" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F150" t="s">
         <v>34</v>
@@ -13373,37 +13436,22 @@
         <v>54</v>
       </c>
       <c r="K150" t="s">
-        <v>203</v>
+        <v>40</v>
       </c>
       <c r="L150" t="s">
-        <v>204</v>
+        <v>41</v>
       </c>
       <c r="M150" t="s">
-        <v>205</v>
-      </c>
-      <c r="N150" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O150">
-        <v>1</v>
-      </c>
-      <c r="P150" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q150">
-        <v>69.989999999999995</v>
-      </c>
-      <c r="R150">
-        <v>11.67</v>
+        <v>0</v>
       </c>
       <c r="Y150" t="s">
-        <v>221</v>
-      </c>
-      <c r="Z150" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="AA150" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="AB150" t="s">
         <v>39</v>
@@ -13417,13 +13465,13 @@
     </row>
     <row r="151" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C151" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D151" t="s">
-        <v>230</v>
+        <v>286</v>
       </c>
       <c r="E151" t="s">
         <v>33</v>
@@ -13465,10 +13513,10 @@
         <v>10</v>
       </c>
       <c r="Y151" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="AA151" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="AB151" t="s">
         <v>39</v>
@@ -13482,13 +13530,13 @@
     </row>
     <row r="152" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="C152" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="D152" t="s">
-        <v>235</v>
+        <v>287</v>
       </c>
       <c r="E152" t="s">
         <v>33</v>
@@ -13506,13 +13554,13 @@
         <v>54</v>
       </c>
       <c r="K152" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="L152" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="M152" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="N152" t="s">
         <v>33</v>
@@ -13524,16 +13572,19 @@
         <v>38</v>
       </c>
       <c r="Q152">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R152">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y152" t="s">
-        <v>236</v>
+        <v>215</v>
+      </c>
+      <c r="Z152" t="s">
+        <v>216</v>
       </c>
       <c r="AA152" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="AB152" t="s">
         <v>39</v>
@@ -13547,16 +13598,16 @@
     </row>
     <row r="153" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="C153" t="s">
-        <v>243</v>
+        <v>219</v>
       </c>
       <c r="D153" t="s">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="E153" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F153" t="s">
         <v>34</v>
@@ -13571,22 +13622,37 @@
         <v>54</v>
       </c>
       <c r="K153" t="s">
-        <v>40</v>
+        <v>203</v>
       </c>
       <c r="L153" t="s">
-        <v>41</v>
+        <v>204</v>
       </c>
       <c r="M153" t="s">
-        <v>42</v>
+        <v>205</v>
+      </c>
+      <c r="N153" t="s">
+        <v>33</v>
       </c>
       <c r="O153">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P153" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q153">
+        <v>69.989999999999995</v>
+      </c>
+      <c r="R153">
+        <v>11.67</v>
       </c>
       <c r="Y153" t="s">
-        <v>240</v>
+        <v>221</v>
+      </c>
+      <c r="Z153" t="s">
+        <v>222</v>
       </c>
       <c r="AA153" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="AB153" t="s">
         <v>39</v>
@@ -13600,13 +13666,13 @@
     </row>
     <row r="154" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="C154" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="D154" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="E154" t="s">
         <v>33</v>
@@ -13621,7 +13687,7 @@
         <v>36</v>
       </c>
       <c r="J154" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K154" t="s">
         <v>40</v>
@@ -13648,10 +13714,10 @@
         <v>10</v>
       </c>
       <c r="Y154" t="s">
-        <v>248</v>
+        <v>231</v>
       </c>
       <c r="AA154" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="AB154" t="s">
         <v>39</v>
@@ -13665,13 +13731,13 @@
     </row>
     <row r="155" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>188</v>
+        <v>233</v>
       </c>
       <c r="C155" t="s">
-        <v>189</v>
+        <v>234</v>
       </c>
       <c r="D155" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="E155" t="s">
         <v>33</v>
@@ -13686,16 +13752,16 @@
         <v>36</v>
       </c>
       <c r="J155" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K155" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="L155" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="M155" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="N155" t="s">
         <v>33</v>
@@ -13707,16 +13773,16 @@
         <v>38</v>
       </c>
       <c r="Q155">
-        <v>37.99</v>
+        <v>14.99</v>
       </c>
       <c r="R155">
-        <v>6.33</v>
+        <v>2.5</v>
       </c>
       <c r="Y155" t="s">
-        <v>52</v>
+        <v>236</v>
       </c>
       <c r="AA155" t="s">
-        <v>190</v>
+        <v>237</v>
       </c>
       <c r="AB155" t="s">
         <v>39</v>
@@ -13730,16 +13796,16 @@
     </row>
     <row r="156" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>191</v>
+        <v>242</v>
       </c>
       <c r="C156" t="s">
-        <v>192</v>
+        <v>243</v>
       </c>
       <c r="D156" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="E156" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F156" t="s">
         <v>34</v>
@@ -13762,26 +13828,14 @@
       <c r="M156" t="s">
         <v>42</v>
       </c>
-      <c r="N156" t="s">
-        <v>33</v>
-      </c>
       <c r="O156">
-        <v>1</v>
-      </c>
-      <c r="P156" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q156">
-        <v>59.99</v>
-      </c>
-      <c r="R156">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y156" t="s">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="AA156" t="s">
-        <v>194</v>
+        <v>241</v>
       </c>
       <c r="AB156" t="s">
         <v>39</v>
@@ -13795,13 +13849,13 @@
     </row>
     <row r="157" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>201</v>
+        <v>245</v>
       </c>
       <c r="C157" t="s">
-        <v>202</v>
+        <v>246</v>
       </c>
       <c r="D157" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E157" t="s">
         <v>33</v>
@@ -13816,16 +13870,16 @@
         <v>36</v>
       </c>
       <c r="J157" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K157" t="s">
-        <v>203</v>
+        <v>40</v>
       </c>
       <c r="L157" t="s">
-        <v>204</v>
+        <v>41</v>
       </c>
       <c r="M157" t="s">
-        <v>205</v>
+        <v>42</v>
       </c>
       <c r="N157" t="s">
         <v>33</v>
@@ -13837,19 +13891,16 @@
         <v>38</v>
       </c>
       <c r="Q157">
-        <v>69.989999999999995</v>
+        <v>59.99</v>
       </c>
       <c r="R157">
-        <v>11.67</v>
+        <v>10</v>
       </c>
       <c r="Y157" t="s">
-        <v>206</v>
-      </c>
-      <c r="Z157" t="s">
-        <v>60</v>
+        <v>248</v>
       </c>
       <c r="AA157" t="s">
-        <v>207</v>
+        <v>249</v>
       </c>
       <c r="AB157" t="s">
         <v>39</v>
@@ -13863,13 +13914,13 @@
     </row>
     <row r="158" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C158" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="D158" t="s">
-        <v>197</v>
+        <v>250</v>
       </c>
       <c r="E158" t="s">
         <v>33</v>
@@ -13887,13 +13938,13 @@
         <v>37</v>
       </c>
       <c r="K158" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L158" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M158" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N158" t="s">
         <v>33</v>
@@ -13905,19 +13956,16 @@
         <v>38</v>
       </c>
       <c r="Q158">
-        <v>59.99</v>
+        <v>37.99</v>
       </c>
       <c r="R158">
-        <v>10</v>
+        <v>6.33</v>
       </c>
       <c r="Y158" t="s">
-        <v>198</v>
-      </c>
-      <c r="Z158" t="s">
-        <v>199</v>
+        <v>52</v>
       </c>
       <c r="AA158" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AB158" t="s">
         <v>39</v>
@@ -13931,13 +13979,13 @@
     </row>
     <row r="159" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="C159" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="D159" t="s">
-        <v>210</v>
+        <v>251</v>
       </c>
       <c r="E159" t="s">
         <v>33</v>
@@ -13952,7 +14000,7 @@
         <v>36</v>
       </c>
       <c r="J159" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K159" t="s">
         <v>40</v>
@@ -13979,10 +14027,10 @@
         <v>10</v>
       </c>
       <c r="Y159" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="AA159" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="AB159" t="s">
         <v>39</v>
@@ -13996,13 +14044,13 @@
     </row>
     <row r="160" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>152</v>
+        <v>201</v>
       </c>
       <c r="C160" t="s">
-        <v>153</v>
+        <v>202</v>
       </c>
       <c r="D160" t="s">
-        <v>154</v>
+        <v>252</v>
       </c>
       <c r="E160" t="s">
         <v>33</v>
@@ -14020,13 +14068,13 @@
         <v>54</v>
       </c>
       <c r="K160" t="s">
-        <v>95</v>
+        <v>203</v>
       </c>
       <c r="L160" t="s">
-        <v>85</v>
+        <v>204</v>
       </c>
       <c r="M160" t="s">
-        <v>86</v>
+        <v>205</v>
       </c>
       <c r="N160" t="s">
         <v>33</v>
@@ -14038,16 +14086,19 @@
         <v>38</v>
       </c>
       <c r="Q160">
-        <v>14.99</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="R160">
-        <v>2.5</v>
+        <v>11.67</v>
       </c>
       <c r="Y160" t="s">
-        <v>155</v>
+        <v>206</v>
+      </c>
+      <c r="Z160" t="s">
+        <v>60</v>
       </c>
       <c r="AA160" t="s">
-        <v>156</v>
+        <v>207</v>
       </c>
       <c r="AB160" t="s">
         <v>39</v>
@@ -14061,13 +14112,13 @@
     </row>
     <row r="161" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>157</v>
+        <v>195</v>
       </c>
       <c r="C161" t="s">
-        <v>158</v>
+        <v>196</v>
       </c>
       <c r="D161" t="s">
-        <v>159</v>
+        <v>197</v>
       </c>
       <c r="E161" t="s">
         <v>33</v>
@@ -14082,16 +14133,16 @@
         <v>36</v>
       </c>
       <c r="J161" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K161" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L161" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M161" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N161" t="s">
         <v>33</v>
@@ -14103,16 +14154,19 @@
         <v>38</v>
       </c>
       <c r="Q161">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R161">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y161" t="s">
-        <v>68</v>
+        <v>198</v>
+      </c>
+      <c r="Z161" t="s">
+        <v>199</v>
       </c>
       <c r="AA161" t="s">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="AB161" t="s">
         <v>39</v>
@@ -14126,16 +14180,16 @@
     </row>
     <row r="162" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>161</v>
+        <v>208</v>
       </c>
       <c r="C162" t="s">
-        <v>162</v>
+        <v>209</v>
       </c>
       <c r="D162" t="s">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="E162" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F162" t="s">
         <v>34</v>
@@ -14147,7 +14201,7 @@
         <v>36</v>
       </c>
       <c r="J162" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K162" t="s">
         <v>40</v>
@@ -14158,14 +14212,26 @@
       <c r="M162" t="s">
         <v>42</v>
       </c>
+      <c r="N162" t="s">
+        <v>33</v>
+      </c>
       <c r="O162">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P162" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q162">
+        <v>59.99</v>
+      </c>
+      <c r="R162">
+        <v>10</v>
       </c>
       <c r="Y162" t="s">
-        <v>63</v>
+        <v>211</v>
       </c>
       <c r="AA162" t="s">
-        <v>151</v>
+        <v>212</v>
       </c>
       <c r="AB162" t="s">
         <v>39</v>
@@ -14179,13 +14245,13 @@
     </row>
     <row r="163" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C163" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="D163" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="E163" t="s">
         <v>33</v>
@@ -14203,13 +14269,13 @@
         <v>54</v>
       </c>
       <c r="K163" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="L163" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="M163" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="N163" t="s">
         <v>33</v>
@@ -14221,16 +14287,16 @@
         <v>38</v>
       </c>
       <c r="Q163">
-        <v>37.99</v>
+        <v>14.99</v>
       </c>
       <c r="R163">
-        <v>6.33</v>
+        <v>2.5</v>
       </c>
       <c r="Y163" t="s">
-        <v>100</v>
+        <v>155</v>
       </c>
       <c r="AA163" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="AB163" t="s">
         <v>39</v>
@@ -14244,13 +14310,13 @@
     </row>
     <row r="164" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="C164" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="D164" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="E164" t="s">
         <v>33</v>
@@ -14292,10 +14358,10 @@
         <v>2</v>
       </c>
       <c r="Y164" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AA164" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="AB164" t="s">
         <v>39</v>
@@ -14309,16 +14375,16 @@
     </row>
     <row r="165" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="C165" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="D165" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="E165" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F165" t="s">
         <v>34</v>
@@ -14333,34 +14399,22 @@
         <v>54</v>
       </c>
       <c r="K165" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L165" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M165" t="s">
-        <v>83</v>
-      </c>
-      <c r="N165" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O165">
-        <v>1</v>
-      </c>
-      <c r="P165" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q165">
-        <v>14.99</v>
-      </c>
-      <c r="R165">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y165" t="s">
-        <v>175</v>
+        <v>63</v>
       </c>
       <c r="AA165" t="s">
-        <v>176</v>
+        <v>151</v>
       </c>
       <c r="AB165" t="s">
         <v>39</v>
@@ -14374,13 +14428,13 @@
     </row>
     <row r="166" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="C166" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="D166" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="E166" t="s">
         <v>33</v>
@@ -14422,13 +14476,10 @@
         <v>6.33</v>
       </c>
       <c r="Y166" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z166" t="s">
-        <v>181</v>
+        <v>100</v>
       </c>
       <c r="AA166" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="AB166" t="s">
         <v>39</v>
@@ -14442,13 +14493,13 @@
     </row>
     <row r="167" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="C167" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="D167" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="E167" t="s">
         <v>33</v>
@@ -14466,37 +14517,34 @@
         <v>54</v>
       </c>
       <c r="K167" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L167" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M167" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="N167" t="s">
         <v>33</v>
       </c>
       <c r="O167">
+        <v>1</v>
+      </c>
+      <c r="P167" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q167">
+        <v>11.99</v>
+      </c>
+      <c r="R167">
         <v>2</v>
       </c>
-      <c r="P167" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q167">
-        <v>75.98</v>
-      </c>
-      <c r="R167">
-        <v>12.66</v>
-      </c>
       <c r="Y167" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z167" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="AA167" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="AB167" t="s">
         <v>39</v>
@@ -14510,13 +14558,13 @@
     </row>
     <row r="168" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>133</v>
+        <v>172</v>
       </c>
       <c r="C168" t="s">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="D168" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="E168" t="s">
         <v>33</v>
@@ -14534,13 +14582,13 @@
         <v>54</v>
       </c>
       <c r="K168" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="L168" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="M168" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="N168" t="s">
         <v>33</v>
@@ -14552,16 +14600,16 @@
         <v>38</v>
       </c>
       <c r="Q168">
-        <v>11.99</v>
+        <v>14.99</v>
       </c>
       <c r="R168">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Y168" t="s">
-        <v>69</v>
+        <v>175</v>
       </c>
       <c r="AA168" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="AB168" t="s">
         <v>39</v>
@@ -14575,13 +14623,13 @@
     </row>
     <row r="169" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>117</v>
+        <v>177</v>
       </c>
       <c r="C169" t="s">
-        <v>118</v>
+        <v>178</v>
       </c>
       <c r="D169" t="s">
-        <v>119</v>
+        <v>179</v>
       </c>
       <c r="E169" t="s">
         <v>33</v>
@@ -14599,13 +14647,13 @@
         <v>54</v>
       </c>
       <c r="K169" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="L169" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="M169" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="N169" t="s">
         <v>33</v>
@@ -14617,19 +14665,19 @@
         <v>38</v>
       </c>
       <c r="Q169">
-        <v>14.99</v>
+        <v>37.99</v>
       </c>
       <c r="R169">
-        <v>2.5</v>
+        <v>6.33</v>
       </c>
       <c r="Y169" t="s">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="Z169" t="s">
-        <v>121</v>
+        <v>181</v>
       </c>
       <c r="AA169" t="s">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="AB169" t="s">
         <v>39</v>
@@ -14643,13 +14691,13 @@
     </row>
     <row r="170" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>123</v>
+        <v>183</v>
       </c>
       <c r="C170" t="s">
-        <v>124</v>
+        <v>184</v>
       </c>
       <c r="D170" t="s">
-        <v>125</v>
+        <v>179</v>
       </c>
       <c r="E170" t="s">
         <v>33</v>
@@ -14667,37 +14715,37 @@
         <v>54</v>
       </c>
       <c r="K170" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L170" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M170" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N170" t="s">
         <v>33</v>
       </c>
       <c r="O170">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P170" t="s">
         <v>38</v>
       </c>
       <c r="Q170">
-        <v>59.99</v>
+        <v>75.98</v>
       </c>
       <c r="R170">
-        <v>10</v>
+        <v>12.66</v>
       </c>
       <c r="Y170" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="Z170" t="s">
-        <v>127</v>
+        <v>47</v>
       </c>
       <c r="AA170" t="s">
-        <v>128</v>
+        <v>185</v>
       </c>
       <c r="AB170" t="s">
         <v>39</v>
@@ -14711,13 +14759,13 @@
     </row>
     <row r="171" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C171" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D171" t="s">
-        <v>131</v>
+        <v>186</v>
       </c>
       <c r="E171" t="s">
         <v>33</v>
@@ -14735,13 +14783,13 @@
         <v>54</v>
       </c>
       <c r="K171" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="L171" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="M171" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="N171" t="s">
         <v>33</v>
@@ -14753,16 +14801,16 @@
         <v>38</v>
       </c>
       <c r="Q171">
-        <v>38.49</v>
+        <v>11.99</v>
       </c>
       <c r="R171">
-        <v>6.42</v>
+        <v>2</v>
       </c>
       <c r="Y171" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="AA171" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="AB171" t="s">
         <v>39</v>
@@ -14776,16 +14824,16 @@
     </row>
     <row r="172" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="C172" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="D172" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="E172" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F172" t="s">
         <v>34</v>
@@ -14808,14 +14856,29 @@
       <c r="M172" t="s">
         <v>83</v>
       </c>
+      <c r="N172" t="s">
+        <v>33</v>
+      </c>
       <c r="O172">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P172" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q172">
+        <v>14.99</v>
+      </c>
+      <c r="R172">
+        <v>2.5</v>
       </c>
       <c r="Y172" t="s">
-        <v>103</v>
+        <v>120</v>
+      </c>
+      <c r="Z172" t="s">
+        <v>121</v>
       </c>
       <c r="AA172" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="AB172" t="s">
         <v>39</v>
@@ -14829,13 +14892,13 @@
     </row>
     <row r="173" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="C173" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="D173" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="E173" t="s">
         <v>33</v>
@@ -14853,13 +14916,13 @@
         <v>54</v>
       </c>
       <c r="K173" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L173" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M173" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N173" t="s">
         <v>33</v>
@@ -14871,19 +14934,19 @@
         <v>38</v>
       </c>
       <c r="Q173">
-        <v>37.99</v>
+        <v>59.99</v>
       </c>
       <c r="R173">
-        <v>6.33</v>
+        <v>10</v>
       </c>
       <c r="Y173" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="Z173" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="AA173" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="AB173" t="s">
         <v>39</v>
@@ -14897,13 +14960,13 @@
     </row>
     <row r="174" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="C174" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="D174" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="E174" t="s">
         <v>33</v>
@@ -14918,16 +14981,16 @@
         <v>36</v>
       </c>
       <c r="J174" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K174" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L174" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M174" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N174" t="s">
         <v>33</v>
@@ -14939,19 +15002,16 @@
         <v>38</v>
       </c>
       <c r="Q174">
-        <v>59.99</v>
+        <v>38.49</v>
       </c>
       <c r="R174">
-        <v>10</v>
+        <v>6.42</v>
       </c>
       <c r="Y174" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z174" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AA174" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="AB174" t="s">
         <v>39</v>
@@ -14965,66 +15025,255 @@
     </row>
     <row r="175" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
+        <v>105</v>
+      </c>
+      <c r="C175" t="s">
+        <v>106</v>
+      </c>
+      <c r="D175" t="s">
+        <v>136</v>
+      </c>
+      <c r="E175" t="s">
+        <v>53</v>
+      </c>
+      <c r="F175" t="s">
+        <v>34</v>
+      </c>
+      <c r="G175" t="s">
+        <v>35</v>
+      </c>
+      <c r="H175" t="s">
+        <v>36</v>
+      </c>
+      <c r="J175" t="s">
+        <v>54</v>
+      </c>
+      <c r="K175" t="s">
+        <v>94</v>
+      </c>
+      <c r="L175" t="s">
+        <v>82</v>
+      </c>
+      <c r="M175" t="s">
+        <v>83</v>
+      </c>
+      <c r="O175">
+        <v>0</v>
+      </c>
+      <c r="Y175" t="s">
+        <v>103</v>
+      </c>
+      <c r="AA175" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB175" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG175" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>107</v>
+      </c>
+      <c r="C176" t="s">
+        <v>108</v>
+      </c>
+      <c r="D176" t="s">
+        <v>137</v>
+      </c>
+      <c r="E176" t="s">
+        <v>33</v>
+      </c>
+      <c r="F176" t="s">
+        <v>34</v>
+      </c>
+      <c r="G176" t="s">
+        <v>35</v>
+      </c>
+      <c r="H176" t="s">
+        <v>36</v>
+      </c>
+      <c r="J176" t="s">
+        <v>54</v>
+      </c>
+      <c r="K176" t="s">
+        <v>48</v>
+      </c>
+      <c r="L176" t="s">
+        <v>49</v>
+      </c>
+      <c r="M176" t="s">
+        <v>50</v>
+      </c>
+      <c r="N176" t="s">
+        <v>33</v>
+      </c>
+      <c r="O176">
+        <v>1</v>
+      </c>
+      <c r="P176" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q176">
+        <v>37.99</v>
+      </c>
+      <c r="R176">
+        <v>6.33</v>
+      </c>
+      <c r="Y176" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z176" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA176" t="s">
+        <v>111</v>
+      </c>
+      <c r="AB176" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG176" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>112</v>
+      </c>
+      <c r="C177" t="s">
+        <v>113</v>
+      </c>
+      <c r="D177" t="s">
+        <v>114</v>
+      </c>
+      <c r="E177" t="s">
+        <v>33</v>
+      </c>
+      <c r="F177" t="s">
+        <v>34</v>
+      </c>
+      <c r="G177" t="s">
+        <v>35</v>
+      </c>
+      <c r="H177" t="s">
+        <v>36</v>
+      </c>
+      <c r="J177" t="s">
+        <v>37</v>
+      </c>
+      <c r="K177" t="s">
+        <v>40</v>
+      </c>
+      <c r="L177" t="s">
+        <v>41</v>
+      </c>
+      <c r="M177" t="s">
+        <v>42</v>
+      </c>
+      <c r="N177" t="s">
+        <v>33</v>
+      </c>
+      <c r="O177">
+        <v>1</v>
+      </c>
+      <c r="P177" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q177">
+        <v>59.99</v>
+      </c>
+      <c r="R177">
+        <v>10</v>
+      </c>
+      <c r="Y177" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z177" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA177" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB177" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG177" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
         <v>703</v>
       </c>
-      <c r="C175" t="s">
+      <c r="C178" t="s">
         <v>704</v>
       </c>
-      <c r="D175" t="s">
+      <c r="D178" t="s">
         <v>705</v>
       </c>
-      <c r="E175" t="s">
-        <v>33</v>
-      </c>
-      <c r="F175" t="s">
-        <v>34</v>
-      </c>
-      <c r="G175" t="s">
-        <v>35</v>
-      </c>
-      <c r="H175" t="s">
-        <v>36</v>
-      </c>
-      <c r="J175" t="s">
-        <v>54</v>
-      </c>
-      <c r="K175" t="s">
+      <c r="E178" t="s">
+        <v>33</v>
+      </c>
+      <c r="F178" t="s">
+        <v>34</v>
+      </c>
+      <c r="G178" t="s">
+        <v>35</v>
+      </c>
+      <c r="H178" t="s">
+        <v>36</v>
+      </c>
+      <c r="J178" t="s">
+        <v>54</v>
+      </c>
+      <c r="K178" t="s">
         <v>72</v>
       </c>
-      <c r="L175" t="s">
+      <c r="L178" t="s">
         <v>73</v>
       </c>
-      <c r="M175" t="s">
+      <c r="M178" t="s">
         <v>74</v>
       </c>
-      <c r="N175" t="s">
-        <v>33</v>
-      </c>
-      <c r="O175">
-        <v>1</v>
-      </c>
-      <c r="P175" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q175">
+      <c r="N178" t="s">
+        <v>33</v>
+      </c>
+      <c r="O178">
+        <v>1</v>
+      </c>
+      <c r="P178" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q178">
         <v>11.99</v>
       </c>
-      <c r="R175">
+      <c r="R178">
         <v>2</v>
       </c>
-      <c r="Y175" t="s">
+      <c r="Y178" t="s">
         <v>706</v>
       </c>
-      <c r="AA175" t="s">
+      <c r="AA178" t="s">
         <v>707</v>
       </c>
-      <c r="AB175" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD175" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG175" t="b">
+      <c r="AB178" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG178" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Raw Sales Data/Amazon.xlsx
+++ b/Raw Sales Data/Amazon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2891" uniqueCount="932">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2924" uniqueCount="942">
   <si>
     <t>amazon-order-id</t>
   </si>
@@ -2815,6 +2815,36 @@
   </si>
   <si>
     <t>BT30 8HX</t>
+  </si>
+  <si>
+    <t>206-4034777-9648321</t>
+  </si>
+  <si>
+    <t>2026-03-13T20:58:04+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-13T21:28:31+00:00</t>
+  </si>
+  <si>
+    <t>Uk</t>
+  </si>
+  <si>
+    <t>SE20 8LP</t>
+  </si>
+  <si>
+    <t>026-0211574-7537958</t>
+  </si>
+  <si>
+    <t>2026-03-13T13:12:02+00:00</t>
+  </si>
+  <si>
+    <t>2026-03-14T00:50:26+00:00</t>
+  </si>
+  <si>
+    <t>HUDDERSFIELD</t>
+  </si>
+  <si>
+    <t>HD8 9PL</t>
   </si>
 </sst>
 </file>
@@ -3621,7 +3651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG178"/>
+  <dimension ref="A1:AG180"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
@@ -3732,13 +3762,13 @@
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>917</v>
+        <v>932</v>
       </c>
       <c r="C2" t="s">
-        <v>918</v>
+        <v>933</v>
       </c>
       <c r="D2" t="s">
-        <v>919</v>
+        <v>934</v>
       </c>
       <c r="E2" t="s">
         <v>98</v>
@@ -3780,10 +3810,13 @@
         <v>11.33</v>
       </c>
       <c r="Y2" t="s">
-        <v>920</v>
+        <v>58</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>935</v>
       </c>
       <c r="AA2" t="s">
-        <v>921</v>
+        <v>936</v>
       </c>
       <c r="AB2" t="s">
         <v>39</v>
@@ -3797,16 +3830,16 @@
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>922</v>
+        <v>937</v>
       </c>
       <c r="C3" t="s">
-        <v>923</v>
+        <v>938</v>
       </c>
       <c r="D3" t="s">
-        <v>924</v>
+        <v>939</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F3" t="s">
         <v>34</v>
@@ -3830,7 +3863,7 @@
         <v>42</v>
       </c>
       <c r="N3" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O3">
         <v>1</v>
@@ -3845,13 +3878,10 @@
         <v>11.33</v>
       </c>
       <c r="Y3" t="s">
-        <v>925</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>619</v>
+        <v>940</v>
       </c>
       <c r="AA3" t="s">
-        <v>926</v>
+        <v>941</v>
       </c>
       <c r="AB3" t="s">
         <v>39</v>
@@ -3865,13 +3895,13 @@
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>927</v>
+        <v>917</v>
       </c>
       <c r="C4" t="s">
-        <v>928</v>
+        <v>918</v>
       </c>
       <c r="D4" t="s">
-        <v>929</v>
+        <v>919</v>
       </c>
       <c r="E4" t="s">
         <v>98</v>
@@ -3912,17 +3942,11 @@
       <c r="R4">
         <v>11.33</v>
       </c>
-      <c r="S4">
-        <v>6.99</v>
-      </c>
-      <c r="T4">
-        <v>1.17</v>
-      </c>
       <c r="Y4" t="s">
-        <v>930</v>
+        <v>920</v>
       </c>
       <c r="AA4" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="AB4" t="s">
         <v>39</v>
@@ -3936,16 +3960,16 @@
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>891</v>
+        <v>922</v>
       </c>
       <c r="C5" t="s">
-        <v>892</v>
+        <v>923</v>
       </c>
       <c r="D5" t="s">
-        <v>893</v>
+        <v>924</v>
       </c>
       <c r="E5" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F5" t="s">
         <v>34</v>
@@ -3969,7 +3993,7 @@
         <v>42</v>
       </c>
       <c r="N5" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O5">
         <v>1</v>
@@ -3984,10 +4008,13 @@
         <v>11.33</v>
       </c>
       <c r="Y5" t="s">
-        <v>894</v>
+        <v>925</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>619</v>
       </c>
       <c r="AA5" t="s">
-        <v>895</v>
+        <v>926</v>
       </c>
       <c r="AB5" t="s">
         <v>39</v>
@@ -4001,16 +4028,16 @@
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>896</v>
+        <v>927</v>
       </c>
       <c r="C6" t="s">
-        <v>897</v>
+        <v>928</v>
       </c>
       <c r="D6" t="s">
-        <v>898</v>
+        <v>929</v>
       </c>
       <c r="E6" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="F6" t="s">
         <v>34</v>
@@ -4033,14 +4060,32 @@
       <c r="M6" t="s">
         <v>42</v>
       </c>
+      <c r="N6" t="s">
+        <v>99</v>
+      </c>
       <c r="O6">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q6">
+        <v>67.989999999999995</v>
+      </c>
+      <c r="R6">
+        <v>11.33</v>
+      </c>
+      <c r="S6">
+        <v>6.99</v>
+      </c>
+      <c r="T6">
+        <v>1.17</v>
       </c>
       <c r="Y6" t="s">
-        <v>894</v>
+        <v>930</v>
       </c>
       <c r="AA6" t="s">
-        <v>895</v>
+        <v>931</v>
       </c>
       <c r="AB6" t="s">
         <v>39</v>
@@ -4054,16 +4099,16 @@
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>899</v>
+        <v>891</v>
       </c>
       <c r="C7" t="s">
-        <v>900</v>
+        <v>892</v>
       </c>
       <c r="D7" t="s">
-        <v>901</v>
+        <v>893</v>
       </c>
       <c r="E7" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="F7" t="s">
         <v>34</v>
@@ -4086,8 +4131,20 @@
       <c r="M7" t="s">
         <v>42</v>
       </c>
+      <c r="N7" t="s">
+        <v>99</v>
+      </c>
       <c r="O7">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P7" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q7">
+        <v>67.989999999999995</v>
+      </c>
+      <c r="R7">
+        <v>11.33</v>
       </c>
       <c r="Y7" t="s">
         <v>894</v>
@@ -4107,16 +4164,16 @@
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>902</v>
+        <v>896</v>
       </c>
       <c r="C8" t="s">
-        <v>903</v>
+        <v>897</v>
       </c>
       <c r="D8" t="s">
-        <v>904</v>
+        <v>898</v>
       </c>
       <c r="E8" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="F8" t="s">
         <v>34</v>
@@ -4131,25 +4188,16 @@
         <v>54</v>
       </c>
       <c r="K8" t="s">
-        <v>905</v>
+        <v>40</v>
       </c>
       <c r="L8" t="s">
-        <v>906</v>
+        <v>41</v>
       </c>
       <c r="M8" t="s">
-        <v>907</v>
-      </c>
-      <c r="N8" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="O8">
-        <v>1</v>
-      </c>
-      <c r="P8" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q8">
-        <v>69.989999999999995</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="s">
         <v>894</v>
@@ -4161,7 +4209,7 @@
         <v>39</v>
       </c>
       <c r="AD8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="b">
         <v>0</v>
@@ -4169,16 +4217,16 @@
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>908</v>
+        <v>899</v>
       </c>
       <c r="C9" t="s">
-        <v>909</v>
+        <v>900</v>
       </c>
       <c r="D9" t="s">
-        <v>910</v>
+        <v>901</v>
       </c>
       <c r="E9" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="F9" t="s">
         <v>34</v>
@@ -4201,32 +4249,14 @@
       <c r="M9" t="s">
         <v>42</v>
       </c>
-      <c r="N9" t="s">
-        <v>99</v>
-      </c>
       <c r="O9">
-        <v>1</v>
-      </c>
-      <c r="P9" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q9">
-        <v>67.989999999999995</v>
-      </c>
-      <c r="R9">
-        <v>11.33</v>
-      </c>
-      <c r="S9">
-        <v>6.99</v>
-      </c>
-      <c r="T9">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="s">
-        <v>911</v>
+        <v>894</v>
       </c>
       <c r="AA9" t="s">
-        <v>912</v>
+        <v>895</v>
       </c>
       <c r="AB9" t="s">
         <v>39</v>
@@ -4240,16 +4270,16 @@
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="C10" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="D10" t="s">
-        <v>915</v>
+        <v>904</v>
       </c>
       <c r="E10" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F10" t="s">
         <v>34</v>
@@ -4264,16 +4294,16 @@
         <v>54</v>
       </c>
       <c r="K10" t="s">
-        <v>48</v>
+        <v>905</v>
       </c>
       <c r="L10" t="s">
-        <v>49</v>
+        <v>906</v>
       </c>
       <c r="M10" t="s">
-        <v>50</v>
+        <v>907</v>
       </c>
       <c r="N10" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O10">
         <v>1</v>
@@ -4282,25 +4312,19 @@
         <v>38</v>
       </c>
       <c r="Q10">
-        <v>40.99</v>
-      </c>
-      <c r="R10">
-        <v>6.83</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="Y10" t="s">
-        <v>420</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>76</v>
+        <v>894</v>
       </c>
       <c r="AA10" t="s">
-        <v>916</v>
+        <v>895</v>
       </c>
       <c r="AB10" t="s">
         <v>39</v>
       </c>
       <c r="AD10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10" t="b">
         <v>0</v>
@@ -4308,16 +4332,16 @@
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>869</v>
+        <v>908</v>
       </c>
       <c r="C11" t="s">
-        <v>870</v>
+        <v>909</v>
       </c>
       <c r="D11" t="s">
-        <v>871</v>
+        <v>910</v>
       </c>
       <c r="E11" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F11" t="s">
         <v>34</v>
@@ -4341,7 +4365,7 @@
         <v>42</v>
       </c>
       <c r="N11" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O11">
         <v>1</v>
@@ -4355,14 +4379,17 @@
       <c r="R11">
         <v>11.33</v>
       </c>
+      <c r="S11">
+        <v>6.99</v>
+      </c>
+      <c r="T11">
+        <v>1.17</v>
+      </c>
       <c r="Y11" t="s">
-        <v>872</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>873</v>
+        <v>911</v>
       </c>
       <c r="AA11" t="s">
-        <v>874</v>
+        <v>912</v>
       </c>
       <c r="AB11" t="s">
         <v>39</v>
@@ -4376,13 +4403,13 @@
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>875</v>
+        <v>913</v>
       </c>
       <c r="C12" t="s">
-        <v>876</v>
+        <v>914</v>
       </c>
       <c r="D12" t="s">
-        <v>877</v>
+        <v>915</v>
       </c>
       <c r="E12" t="s">
         <v>33</v>
@@ -4400,13 +4427,13 @@
         <v>54</v>
       </c>
       <c r="K12" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L12" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M12" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N12" t="s">
         <v>33</v>
@@ -4418,16 +4445,19 @@
         <v>38</v>
       </c>
       <c r="Q12">
-        <v>67.989999999999995</v>
+        <v>40.99</v>
       </c>
       <c r="R12">
-        <v>11.33</v>
+        <v>6.83</v>
       </c>
       <c r="Y12" t="s">
-        <v>878</v>
+        <v>420</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>76</v>
       </c>
       <c r="AA12" t="s">
-        <v>879</v>
+        <v>916</v>
       </c>
       <c r="AB12" t="s">
         <v>39</v>
@@ -4441,13 +4471,13 @@
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>880</v>
+        <v>869</v>
       </c>
       <c r="C13" t="s">
-        <v>881</v>
+        <v>870</v>
       </c>
       <c r="D13" t="s">
-        <v>882</v>
+        <v>871</v>
       </c>
       <c r="E13" t="s">
         <v>33</v>
@@ -4483,16 +4513,19 @@
         <v>38</v>
       </c>
       <c r="Q13">
-        <v>65.989999999999995</v>
+        <v>67.989999999999995</v>
       </c>
       <c r="R13">
-        <v>11</v>
+        <v>11.33</v>
       </c>
       <c r="Y13" t="s">
-        <v>883</v>
+        <v>872</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>873</v>
       </c>
       <c r="AA13" t="s">
-        <v>884</v>
+        <v>874</v>
       </c>
       <c r="AB13" t="s">
         <v>39</v>
@@ -4506,13 +4539,13 @@
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>885</v>
+        <v>875</v>
       </c>
       <c r="C14" t="s">
-        <v>886</v>
+        <v>876</v>
       </c>
       <c r="D14" t="s">
-        <v>887</v>
+        <v>877</v>
       </c>
       <c r="E14" t="s">
         <v>33</v>
@@ -4548,19 +4581,16 @@
         <v>38</v>
       </c>
       <c r="Q14">
-        <v>65.989999999999995</v>
+        <v>67.989999999999995</v>
       </c>
       <c r="R14">
-        <v>11</v>
+        <v>11.33</v>
       </c>
       <c r="Y14" t="s">
-        <v>888</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>889</v>
+        <v>878</v>
       </c>
       <c r="AA14" t="s">
-        <v>890</v>
+        <v>879</v>
       </c>
       <c r="AB14" t="s">
         <v>39</v>
@@ -4574,13 +4604,13 @@
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>864</v>
+        <v>880</v>
       </c>
       <c r="C15" t="s">
-        <v>865</v>
+        <v>881</v>
       </c>
       <c r="D15" t="s">
-        <v>866</v>
+        <v>882</v>
       </c>
       <c r="E15" t="s">
         <v>33</v>
@@ -4622,10 +4652,10 @@
         <v>11</v>
       </c>
       <c r="Y15" t="s">
-        <v>867</v>
+        <v>883</v>
       </c>
       <c r="AA15" t="s">
-        <v>868</v>
+        <v>884</v>
       </c>
       <c r="AB15" t="s">
         <v>39</v>
@@ -4639,13 +4669,13 @@
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>846</v>
+        <v>885</v>
       </c>
       <c r="C16" t="s">
-        <v>847</v>
+        <v>886</v>
       </c>
       <c r="D16" t="s">
-        <v>848</v>
+        <v>887</v>
       </c>
       <c r="E16" t="s">
         <v>33</v>
@@ -4686,20 +4716,14 @@
       <c r="R16">
         <v>11</v>
       </c>
-      <c r="S16">
-        <v>6.99</v>
-      </c>
-      <c r="T16">
-        <v>1.17</v>
-      </c>
       <c r="Y16" t="s">
-        <v>849</v>
+        <v>888</v>
       </c>
       <c r="Z16" t="s">
-        <v>850</v>
+        <v>889</v>
       </c>
       <c r="AA16" t="s">
-        <v>851</v>
+        <v>890</v>
       </c>
       <c r="AB16" t="s">
         <v>39</v>
@@ -4713,16 +4737,16 @@
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>852</v>
+        <v>864</v>
       </c>
       <c r="C17" t="s">
-        <v>853</v>
+        <v>865</v>
       </c>
       <c r="D17" t="s">
-        <v>854</v>
+        <v>866</v>
       </c>
       <c r="E17" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F17" t="s">
         <v>34</v>
@@ -4745,14 +4769,26 @@
       <c r="M17" t="s">
         <v>42</v>
       </c>
+      <c r="N17" t="s">
+        <v>33</v>
+      </c>
       <c r="O17">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P17" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q17">
+        <v>65.989999999999995</v>
+      </c>
+      <c r="R17">
+        <v>11</v>
       </c>
       <c r="Y17" t="s">
-        <v>855</v>
+        <v>867</v>
       </c>
       <c r="AA17" t="s">
-        <v>856</v>
+        <v>868</v>
       </c>
       <c r="AB17" t="s">
         <v>39</v>
@@ -4766,13 +4802,13 @@
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>857</v>
+        <v>846</v>
       </c>
       <c r="C18" t="s">
-        <v>858</v>
+        <v>847</v>
       </c>
       <c r="D18" t="s">
-        <v>859</v>
+        <v>848</v>
       </c>
       <c r="E18" t="s">
         <v>33</v>
@@ -4813,11 +4849,20 @@
       <c r="R18">
         <v>11</v>
       </c>
+      <c r="S18">
+        <v>6.99</v>
+      </c>
+      <c r="T18">
+        <v>1.17</v>
+      </c>
       <c r="Y18" t="s">
-        <v>860</v>
+        <v>849</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>850</v>
       </c>
       <c r="AA18" t="s">
-        <v>861</v>
+        <v>851</v>
       </c>
       <c r="AB18" t="s">
         <v>39</v>
@@ -4831,16 +4876,16 @@
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>837</v>
+        <v>852</v>
       </c>
       <c r="C19" t="s">
-        <v>838</v>
+        <v>853</v>
       </c>
       <c r="D19" t="s">
-        <v>862</v>
+        <v>854</v>
       </c>
       <c r="E19" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F19" t="s">
         <v>34</v>
@@ -4855,34 +4900,22 @@
         <v>54</v>
       </c>
       <c r="K19" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L19" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M19" t="s">
-        <v>50</v>
-      </c>
-      <c r="N19" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O19">
-        <v>1</v>
-      </c>
-      <c r="P19" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q19">
-        <v>40.99</v>
-      </c>
-      <c r="R19">
-        <v>6.83</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="s">
-        <v>305</v>
+        <v>855</v>
       </c>
       <c r="AA19" t="s">
-        <v>840</v>
+        <v>856</v>
       </c>
       <c r="AB19" t="s">
         <v>39</v>
@@ -4896,13 +4929,13 @@
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>841</v>
+        <v>857</v>
       </c>
       <c r="C20" t="s">
-        <v>842</v>
+        <v>858</v>
       </c>
       <c r="D20" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="E20" t="s">
         <v>33</v>
@@ -4943,17 +4976,11 @@
       <c r="R20">
         <v>11</v>
       </c>
-      <c r="S20">
-        <v>6.99</v>
-      </c>
-      <c r="T20">
-        <v>1.17</v>
-      </c>
       <c r="Y20" t="s">
-        <v>844</v>
+        <v>860</v>
       </c>
       <c r="AA20" t="s">
-        <v>845</v>
+        <v>861</v>
       </c>
       <c r="AB20" t="s">
         <v>39</v>
@@ -4973,10 +5000,10 @@
         <v>838</v>
       </c>
       <c r="D21" t="s">
-        <v>839</v>
+        <v>862</v>
       </c>
       <c r="E21" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F21" t="s">
         <v>34</v>
@@ -5000,7 +5027,7 @@
         <v>50</v>
       </c>
       <c r="N21" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O21">
         <v>1</v>
@@ -5038,10 +5065,10 @@
         <v>842</v>
       </c>
       <c r="D22" t="s">
-        <v>843</v>
+        <v>863</v>
       </c>
       <c r="E22" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F22" t="s">
         <v>34</v>
@@ -5065,7 +5092,7 @@
         <v>42</v>
       </c>
       <c r="N22" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O22">
         <v>1</v>
@@ -5103,13 +5130,13 @@
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>819</v>
+        <v>837</v>
       </c>
       <c r="C23" t="s">
-        <v>820</v>
+        <v>838</v>
       </c>
       <c r="D23" t="s">
-        <v>821</v>
+        <v>839</v>
       </c>
       <c r="E23" t="s">
         <v>98</v>
@@ -5151,13 +5178,10 @@
         <v>6.83</v>
       </c>
       <c r="Y23" t="s">
-        <v>618</v>
-      </c>
-      <c r="Z23" t="s">
-        <v>619</v>
+        <v>305</v>
       </c>
       <c r="AA23" t="s">
-        <v>620</v>
+        <v>840</v>
       </c>
       <c r="AB23" t="s">
         <v>39</v>
@@ -5171,13 +5195,13 @@
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>822</v>
+        <v>841</v>
       </c>
       <c r="C24" t="s">
-        <v>823</v>
+        <v>842</v>
       </c>
       <c r="D24" t="s">
-        <v>824</v>
+        <v>843</v>
       </c>
       <c r="E24" t="s">
         <v>98</v>
@@ -5195,13 +5219,13 @@
         <v>54</v>
       </c>
       <c r="K24" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L24" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M24" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N24" t="s">
         <v>99</v>
@@ -5213,16 +5237,22 @@
         <v>38</v>
       </c>
       <c r="Q24">
-        <v>14.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R24">
-        <v>2.5</v>
+        <v>11</v>
+      </c>
+      <c r="S24">
+        <v>6.99</v>
+      </c>
+      <c r="T24">
+        <v>1.17</v>
       </c>
       <c r="Y24" t="s">
-        <v>825</v>
+        <v>844</v>
       </c>
       <c r="AA24" t="s">
-        <v>826</v>
+        <v>845</v>
       </c>
       <c r="AB24" t="s">
         <v>39</v>
@@ -5236,13 +5266,13 @@
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>827</v>
+        <v>819</v>
       </c>
       <c r="C25" t="s">
-        <v>828</v>
+        <v>820</v>
       </c>
       <c r="D25" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
       <c r="E25" t="s">
         <v>98</v>
@@ -5260,13 +5290,13 @@
         <v>54</v>
       </c>
       <c r="K25" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L25" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M25" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N25" t="s">
         <v>99</v>
@@ -5278,16 +5308,19 @@
         <v>38</v>
       </c>
       <c r="Q25">
-        <v>65.989999999999995</v>
-      </c>
-      <c r="S25">
-        <v>6.99</v>
+        <v>40.99</v>
+      </c>
+      <c r="R25">
+        <v>6.83</v>
       </c>
       <c r="Y25" t="s">
-        <v>830</v>
+        <v>618</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>619</v>
       </c>
       <c r="AA25" t="s">
-        <v>831</v>
+        <v>620</v>
       </c>
       <c r="AB25" t="s">
         <v>39</v>
@@ -5301,16 +5334,16 @@
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>832</v>
+        <v>822</v>
       </c>
       <c r="C26" t="s">
-        <v>833</v>
+        <v>823</v>
       </c>
       <c r="D26" t="s">
-        <v>834</v>
+        <v>824</v>
       </c>
       <c r="E26" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F26" t="s">
         <v>34</v>
@@ -5325,16 +5358,16 @@
         <v>54</v>
       </c>
       <c r="K26" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L26" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M26" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N26" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O26">
         <v>1</v>
@@ -5343,16 +5376,16 @@
         <v>38</v>
       </c>
       <c r="Q26">
-        <v>65.989999999999995</v>
+        <v>14.99</v>
       </c>
       <c r="R26">
-        <v>11</v>
+        <v>2.5</v>
       </c>
       <c r="Y26" t="s">
-        <v>835</v>
+        <v>825</v>
       </c>
       <c r="AA26" t="s">
-        <v>836</v>
+        <v>826</v>
       </c>
       <c r="AB26" t="s">
         <v>39</v>
@@ -5366,16 +5399,16 @@
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>780</v>
+        <v>827</v>
       </c>
       <c r="C27" t="s">
-        <v>781</v>
+        <v>828</v>
       </c>
       <c r="D27" t="s">
-        <v>782</v>
+        <v>829</v>
       </c>
       <c r="E27" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F27" t="s">
         <v>34</v>
@@ -5399,7 +5432,7 @@
         <v>42</v>
       </c>
       <c r="N27" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O27">
         <v>1</v>
@@ -5410,14 +5443,14 @@
       <c r="Q27">
         <v>65.989999999999995</v>
       </c>
-      <c r="R27">
-        <v>11</v>
+      <c r="S27">
+        <v>6.99</v>
       </c>
       <c r="Y27" t="s">
-        <v>783</v>
+        <v>830</v>
       </c>
       <c r="AA27" t="s">
-        <v>784</v>
+        <v>831</v>
       </c>
       <c r="AB27" t="s">
         <v>39</v>
@@ -5431,13 +5464,13 @@
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>785</v>
+        <v>832</v>
       </c>
       <c r="C28" t="s">
-        <v>786</v>
+        <v>833</v>
       </c>
       <c r="D28" t="s">
-        <v>787</v>
+        <v>834</v>
       </c>
       <c r="E28" t="s">
         <v>33</v>
@@ -5455,13 +5488,13 @@
         <v>54</v>
       </c>
       <c r="K28" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L28" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M28" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N28" t="s">
         <v>33</v>
@@ -5473,16 +5506,16 @@
         <v>38</v>
       </c>
       <c r="Q28">
-        <v>40.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R28">
-        <v>6.83</v>
+        <v>11</v>
       </c>
       <c r="Y28" t="s">
-        <v>788</v>
+        <v>835</v>
       </c>
       <c r="AA28" t="s">
-        <v>789</v>
+        <v>836</v>
       </c>
       <c r="AB28" t="s">
         <v>39</v>
@@ -5496,13 +5529,13 @@
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>790</v>
+        <v>780</v>
       </c>
       <c r="C29" t="s">
-        <v>791</v>
+        <v>781</v>
       </c>
       <c r="D29" t="s">
-        <v>792</v>
+        <v>782</v>
       </c>
       <c r="E29" t="s">
         <v>33</v>
@@ -5544,10 +5577,10 @@
         <v>11</v>
       </c>
       <c r="Y29" t="s">
-        <v>793</v>
+        <v>783</v>
       </c>
       <c r="AA29" t="s">
-        <v>794</v>
+        <v>784</v>
       </c>
       <c r="AB29" t="s">
         <v>39</v>
@@ -5561,13 +5594,13 @@
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>795</v>
+        <v>785</v>
       </c>
       <c r="C30" t="s">
-        <v>796</v>
+        <v>786</v>
       </c>
       <c r="D30" t="s">
-        <v>797</v>
+        <v>787</v>
       </c>
       <c r="E30" t="s">
         <v>33</v>
@@ -5585,13 +5618,13 @@
         <v>54</v>
       </c>
       <c r="K30" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L30" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M30" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N30" t="s">
         <v>33</v>
@@ -5603,16 +5636,16 @@
         <v>38</v>
       </c>
       <c r="Q30">
-        <v>14.99</v>
+        <v>40.99</v>
       </c>
       <c r="R30">
-        <v>2.5</v>
+        <v>6.83</v>
       </c>
       <c r="Y30" t="s">
-        <v>798</v>
+        <v>788</v>
       </c>
       <c r="AA30" t="s">
-        <v>799</v>
+        <v>789</v>
       </c>
       <c r="AB30" t="s">
         <v>39</v>
@@ -5626,13 +5659,13 @@
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>800</v>
+        <v>790</v>
       </c>
       <c r="C31" t="s">
-        <v>801</v>
+        <v>791</v>
       </c>
       <c r="D31" t="s">
-        <v>802</v>
+        <v>792</v>
       </c>
       <c r="E31" t="s">
         <v>33</v>
@@ -5650,13 +5683,13 @@
         <v>54</v>
       </c>
       <c r="K31" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L31" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M31" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N31" t="s">
         <v>33</v>
@@ -5668,16 +5701,16 @@
         <v>38</v>
       </c>
       <c r="Q31">
-        <v>14.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R31">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="Y31" t="s">
-        <v>68</v>
+        <v>793</v>
       </c>
       <c r="AA31" t="s">
-        <v>803</v>
+        <v>794</v>
       </c>
       <c r="AB31" t="s">
         <v>39</v>
@@ -5691,13 +5724,13 @@
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>804</v>
+        <v>795</v>
       </c>
       <c r="C32" t="s">
-        <v>805</v>
+        <v>796</v>
       </c>
       <c r="D32" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="E32" t="s">
         <v>33</v>
@@ -5733,16 +5766,16 @@
         <v>38</v>
       </c>
       <c r="Q32">
-        <v>11.99</v>
+        <v>14.99</v>
       </c>
       <c r="R32">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Y32" t="s">
-        <v>806</v>
+        <v>798</v>
       </c>
       <c r="AA32" t="s">
-        <v>807</v>
+        <v>799</v>
       </c>
       <c r="AB32" t="s">
         <v>39</v>
@@ -5756,13 +5789,13 @@
     </row>
     <row r="33" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>808</v>
+        <v>800</v>
       </c>
       <c r="C33" t="s">
-        <v>809</v>
+        <v>801</v>
       </c>
       <c r="D33" t="s">
-        <v>810</v>
+        <v>802</v>
       </c>
       <c r="E33" t="s">
         <v>33</v>
@@ -5798,16 +5831,16 @@
         <v>38</v>
       </c>
       <c r="Q33">
-        <v>11.99</v>
+        <v>14.99</v>
       </c>
       <c r="R33">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Y33" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AA33" t="s">
-        <v>811</v>
+        <v>803</v>
       </c>
       <c r="AB33" t="s">
         <v>39</v>
@@ -5821,13 +5854,13 @@
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>812</v>
+        <v>804</v>
       </c>
       <c r="C34" t="s">
-        <v>813</v>
+        <v>805</v>
       </c>
       <c r="D34" t="s">
-        <v>814</v>
+        <v>802</v>
       </c>
       <c r="E34" t="s">
         <v>33</v>
@@ -5845,13 +5878,13 @@
         <v>54</v>
       </c>
       <c r="K34" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="L34" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="M34" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="N34" t="s">
         <v>33</v>
@@ -5863,16 +5896,16 @@
         <v>38</v>
       </c>
       <c r="Q34">
-        <v>40.99</v>
+        <v>11.99</v>
       </c>
       <c r="R34">
-        <v>6.83</v>
+        <v>2</v>
       </c>
       <c r="Y34" t="s">
-        <v>815</v>
+        <v>806</v>
       </c>
       <c r="AA34" t="s">
-        <v>816</v>
+        <v>807</v>
       </c>
       <c r="AB34" t="s">
         <v>39</v>
@@ -5886,13 +5919,13 @@
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>745</v>
+        <v>808</v>
       </c>
       <c r="C35" t="s">
-        <v>746</v>
+        <v>809</v>
       </c>
       <c r="D35" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="E35" t="s">
         <v>33</v>
@@ -5934,10 +5967,10 @@
         <v>2</v>
       </c>
       <c r="Y35" t="s">
-        <v>748</v>
+        <v>66</v>
       </c>
       <c r="AA35" t="s">
-        <v>749</v>
+        <v>811</v>
       </c>
       <c r="AB35" t="s">
         <v>39</v>
@@ -5951,13 +5984,13 @@
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>750</v>
+        <v>812</v>
       </c>
       <c r="C36" t="s">
-        <v>751</v>
+        <v>813</v>
       </c>
       <c r="D36" t="s">
-        <v>752</v>
+        <v>814</v>
       </c>
       <c r="E36" t="s">
         <v>33</v>
@@ -5975,13 +6008,13 @@
         <v>54</v>
       </c>
       <c r="K36" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L36" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M36" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N36" t="s">
         <v>33</v>
@@ -5993,16 +6026,16 @@
         <v>38</v>
       </c>
       <c r="Q36">
-        <v>65.989999999999995</v>
+        <v>40.99</v>
       </c>
       <c r="R36">
-        <v>11</v>
+        <v>6.83</v>
       </c>
       <c r="Y36" t="s">
-        <v>753</v>
+        <v>815</v>
       </c>
       <c r="AA36" t="s">
-        <v>754</v>
+        <v>816</v>
       </c>
       <c r="AB36" t="s">
         <v>39</v>
@@ -6016,13 +6049,13 @@
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>755</v>
+        <v>745</v>
       </c>
       <c r="C37" t="s">
-        <v>756</v>
+        <v>746</v>
       </c>
       <c r="D37" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="E37" t="s">
         <v>33</v>
@@ -6040,13 +6073,13 @@
         <v>54</v>
       </c>
       <c r="K37" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L37" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M37" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N37" t="s">
         <v>33</v>
@@ -6058,25 +6091,16 @@
         <v>38</v>
       </c>
       <c r="Q37">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R37">
-        <v>11</v>
-      </c>
-      <c r="S37">
-        <v>6.99</v>
-      </c>
-      <c r="T37">
-        <v>1.17</v>
+        <v>2</v>
       </c>
       <c r="Y37" t="s">
-        <v>758</v>
-      </c>
-      <c r="Z37" t="s">
-        <v>759</v>
+        <v>748</v>
       </c>
       <c r="AA37" t="s">
-        <v>760</v>
+        <v>749</v>
       </c>
       <c r="AB37" t="s">
         <v>39</v>
@@ -6090,13 +6114,13 @@
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>761</v>
+        <v>750</v>
       </c>
       <c r="C38" t="s">
-        <v>762</v>
+        <v>751</v>
       </c>
       <c r="D38" t="s">
-        <v>763</v>
+        <v>752</v>
       </c>
       <c r="E38" t="s">
         <v>33</v>
@@ -6114,13 +6138,13 @@
         <v>54</v>
       </c>
       <c r="K38" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L38" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M38" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N38" t="s">
         <v>33</v>
@@ -6132,19 +6156,16 @@
         <v>38</v>
       </c>
       <c r="Q38">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R38">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y38" t="s">
-        <v>764</v>
-      </c>
-      <c r="Z38" t="s">
-        <v>279</v>
+        <v>753</v>
       </c>
       <c r="AA38" t="s">
-        <v>765</v>
+        <v>754</v>
       </c>
       <c r="AB38" t="s">
         <v>39</v>
@@ -6158,13 +6179,13 @@
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>766</v>
+        <v>755</v>
       </c>
       <c r="C39" t="s">
-        <v>767</v>
+        <v>756</v>
       </c>
       <c r="D39" t="s">
-        <v>768</v>
+        <v>818</v>
       </c>
       <c r="E39" t="s">
         <v>33</v>
@@ -6182,13 +6203,13 @@
         <v>54</v>
       </c>
       <c r="K39" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L39" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M39" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N39" t="s">
         <v>33</v>
@@ -6200,19 +6221,25 @@
         <v>38</v>
       </c>
       <c r="Q39">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R39">
-        <v>2</v>
+        <v>11</v>
+      </c>
+      <c r="S39">
+        <v>6.99</v>
+      </c>
+      <c r="T39">
+        <v>1.17</v>
       </c>
       <c r="Y39" t="s">
-        <v>91</v>
+        <v>758</v>
       </c>
       <c r="Z39" t="s">
-        <v>121</v>
+        <v>759</v>
       </c>
       <c r="AA39" t="s">
-        <v>769</v>
+        <v>760</v>
       </c>
       <c r="AB39" t="s">
         <v>39</v>
@@ -6226,13 +6253,13 @@
     </row>
     <row r="40" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>770</v>
+        <v>761</v>
       </c>
       <c r="C40" t="s">
-        <v>771</v>
+        <v>762</v>
       </c>
       <c r="D40" t="s">
-        <v>772</v>
+        <v>763</v>
       </c>
       <c r="E40" t="s">
         <v>33</v>
@@ -6250,13 +6277,13 @@
         <v>54</v>
       </c>
       <c r="K40" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L40" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M40" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N40" t="s">
         <v>33</v>
@@ -6268,19 +6295,19 @@
         <v>38</v>
       </c>
       <c r="Q40">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R40">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y40" t="s">
-        <v>773</v>
+        <v>764</v>
       </c>
       <c r="Z40" t="s">
-        <v>64</v>
+        <v>279</v>
       </c>
       <c r="AA40" t="s">
-        <v>774</v>
+        <v>765</v>
       </c>
       <c r="AB40" t="s">
         <v>39</v>
@@ -6294,13 +6321,13 @@
     </row>
     <row r="41" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>775</v>
+        <v>766</v>
       </c>
       <c r="C41" t="s">
-        <v>776</v>
+        <v>767</v>
       </c>
       <c r="D41" t="s">
-        <v>777</v>
+        <v>768</v>
       </c>
       <c r="E41" t="s">
         <v>33</v>
@@ -6318,13 +6345,13 @@
         <v>54</v>
       </c>
       <c r="K41" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L41" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M41" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N41" t="s">
         <v>33</v>
@@ -6336,16 +6363,19 @@
         <v>38</v>
       </c>
       <c r="Q41">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R41">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y41" t="s">
-        <v>778</v>
+        <v>91</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>121</v>
       </c>
       <c r="AA41" t="s">
-        <v>779</v>
+        <v>769</v>
       </c>
       <c r="AB41" t="s">
         <v>39</v>
@@ -6359,16 +6389,16 @@
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>745</v>
+        <v>770</v>
       </c>
       <c r="C42" t="s">
-        <v>746</v>
+        <v>771</v>
       </c>
       <c r="D42" t="s">
-        <v>747</v>
+        <v>772</v>
       </c>
       <c r="E42" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F42" t="s">
         <v>34</v>
@@ -6383,16 +6413,16 @@
         <v>54</v>
       </c>
       <c r="K42" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L42" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M42" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N42" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O42">
         <v>1</v>
@@ -6401,16 +6431,19 @@
         <v>38</v>
       </c>
       <c r="Q42">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R42">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y42" t="s">
-        <v>748</v>
+        <v>773</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>64</v>
       </c>
       <c r="AA42" t="s">
-        <v>749</v>
+        <v>774</v>
       </c>
       <c r="AB42" t="s">
         <v>39</v>
@@ -6424,13 +6457,13 @@
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>750</v>
+        <v>775</v>
       </c>
       <c r="C43" t="s">
-        <v>751</v>
+        <v>776</v>
       </c>
       <c r="D43" t="s">
-        <v>752</v>
+        <v>777</v>
       </c>
       <c r="E43" t="s">
         <v>33</v>
@@ -6472,10 +6505,10 @@
         <v>11</v>
       </c>
       <c r="Y43" t="s">
-        <v>753</v>
+        <v>778</v>
       </c>
       <c r="AA43" t="s">
-        <v>754</v>
+        <v>779</v>
       </c>
       <c r="AB43" t="s">
         <v>39</v>
@@ -6489,13 +6522,13 @@
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>755</v>
+        <v>745</v>
       </c>
       <c r="C44" t="s">
-        <v>756</v>
+        <v>746</v>
       </c>
       <c r="D44" t="s">
-        <v>757</v>
+        <v>747</v>
       </c>
       <c r="E44" t="s">
         <v>98</v>
@@ -6513,13 +6546,13 @@
         <v>54</v>
       </c>
       <c r="K44" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L44" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M44" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N44" t="s">
         <v>99</v>
@@ -6531,25 +6564,16 @@
         <v>38</v>
       </c>
       <c r="Q44">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R44">
-        <v>11</v>
-      </c>
-      <c r="S44">
-        <v>6.99</v>
-      </c>
-      <c r="T44">
-        <v>1.17</v>
+        <v>2</v>
       </c>
       <c r="Y44" t="s">
-        <v>758</v>
-      </c>
-      <c r="Z44" t="s">
-        <v>759</v>
+        <v>748</v>
       </c>
       <c r="AA44" t="s">
-        <v>760</v>
+        <v>749</v>
       </c>
       <c r="AB44" t="s">
         <v>39</v>
@@ -6563,13 +6587,13 @@
     </row>
     <row r="45" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>761</v>
+        <v>750</v>
       </c>
       <c r="C45" t="s">
-        <v>762</v>
+        <v>751</v>
       </c>
       <c r="D45" t="s">
-        <v>763</v>
+        <v>752</v>
       </c>
       <c r="E45" t="s">
         <v>33</v>
@@ -6587,13 +6611,13 @@
         <v>54</v>
       </c>
       <c r="K45" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L45" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M45" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N45" t="s">
         <v>33</v>
@@ -6605,19 +6629,16 @@
         <v>38</v>
       </c>
       <c r="Q45">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R45">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y45" t="s">
-        <v>764</v>
-      </c>
-      <c r="Z45" t="s">
-        <v>279</v>
+        <v>753</v>
       </c>
       <c r="AA45" t="s">
-        <v>765</v>
+        <v>754</v>
       </c>
       <c r="AB45" t="s">
         <v>39</v>
@@ -6631,16 +6652,16 @@
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>766</v>
+        <v>755</v>
       </c>
       <c r="C46" t="s">
-        <v>767</v>
+        <v>756</v>
       </c>
       <c r="D46" t="s">
-        <v>768</v>
+        <v>757</v>
       </c>
       <c r="E46" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F46" t="s">
         <v>34</v>
@@ -6655,16 +6676,16 @@
         <v>54</v>
       </c>
       <c r="K46" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L46" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M46" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N46" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O46">
         <v>1</v>
@@ -6673,19 +6694,25 @@
         <v>38</v>
       </c>
       <c r="Q46">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R46">
-        <v>2</v>
+        <v>11</v>
+      </c>
+      <c r="S46">
+        <v>6.99</v>
+      </c>
+      <c r="T46">
+        <v>1.17</v>
       </c>
       <c r="Y46" t="s">
-        <v>91</v>
+        <v>758</v>
       </c>
       <c r="Z46" t="s">
-        <v>121</v>
+        <v>759</v>
       </c>
       <c r="AA46" t="s">
-        <v>769</v>
+        <v>760</v>
       </c>
       <c r="AB46" t="s">
         <v>39</v>
@@ -6699,13 +6726,13 @@
     </row>
     <row r="47" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>770</v>
+        <v>761</v>
       </c>
       <c r="C47" t="s">
-        <v>771</v>
+        <v>762</v>
       </c>
       <c r="D47" t="s">
-        <v>772</v>
+        <v>763</v>
       </c>
       <c r="E47" t="s">
         <v>33</v>
@@ -6723,13 +6750,13 @@
         <v>54</v>
       </c>
       <c r="K47" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L47" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M47" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N47" t="s">
         <v>33</v>
@@ -6741,19 +6768,19 @@
         <v>38</v>
       </c>
       <c r="Q47">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R47">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y47" t="s">
-        <v>773</v>
+        <v>764</v>
       </c>
       <c r="Z47" t="s">
-        <v>64</v>
+        <v>279</v>
       </c>
       <c r="AA47" t="s">
-        <v>774</v>
+        <v>765</v>
       </c>
       <c r="AB47" t="s">
         <v>39</v>
@@ -6767,13 +6794,13 @@
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>775</v>
+        <v>766</v>
       </c>
       <c r="C48" t="s">
-        <v>776</v>
+        <v>767</v>
       </c>
       <c r="D48" t="s">
-        <v>777</v>
+        <v>768</v>
       </c>
       <c r="E48" t="s">
         <v>33</v>
@@ -6791,13 +6818,13 @@
         <v>54</v>
       </c>
       <c r="K48" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L48" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M48" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N48" t="s">
         <v>33</v>
@@ -6809,16 +6836,19 @@
         <v>38</v>
       </c>
       <c r="Q48">
-        <v>65.989999999999995</v>
+        <v>11.99</v>
       </c>
       <c r="R48">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y48" t="s">
-        <v>778</v>
+        <v>91</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>121</v>
       </c>
       <c r="AA48" t="s">
-        <v>779</v>
+        <v>769</v>
       </c>
       <c r="AB48" t="s">
         <v>39</v>
@@ -6832,16 +6862,16 @@
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>714</v>
+        <v>770</v>
       </c>
       <c r="C49" t="s">
-        <v>715</v>
+        <v>771</v>
       </c>
       <c r="D49" t="s">
-        <v>716</v>
+        <v>772</v>
       </c>
       <c r="E49" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F49" t="s">
         <v>34</v>
@@ -6856,16 +6886,16 @@
         <v>54</v>
       </c>
       <c r="K49" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L49" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M49" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N49" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O49">
         <v>1</v>
@@ -6874,19 +6904,19 @@
         <v>38</v>
       </c>
       <c r="Q49">
-        <v>11.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R49">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y49" t="s">
-        <v>717</v>
+        <v>773</v>
       </c>
       <c r="Z49" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="AA49" t="s">
-        <v>718</v>
+        <v>774</v>
       </c>
       <c r="AB49" t="s">
         <v>39</v>
@@ -6900,13 +6930,13 @@
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>719</v>
+        <v>775</v>
       </c>
       <c r="C50" t="s">
-        <v>720</v>
+        <v>776</v>
       </c>
       <c r="D50" t="s">
-        <v>721</v>
+        <v>777</v>
       </c>
       <c r="E50" t="s">
         <v>33</v>
@@ -6924,13 +6954,13 @@
         <v>54</v>
       </c>
       <c r="K50" t="s">
-        <v>722</v>
+        <v>40</v>
       </c>
       <c r="L50" t="s">
-        <v>723</v>
+        <v>41</v>
       </c>
       <c r="M50" t="s">
-        <v>724</v>
+        <v>42</v>
       </c>
       <c r="N50" t="s">
         <v>33</v>
@@ -6942,19 +6972,16 @@
         <v>38</v>
       </c>
       <c r="Q50">
-        <v>12.99</v>
+        <v>65.989999999999995</v>
       </c>
       <c r="R50">
-        <v>2.17</v>
+        <v>11</v>
       </c>
       <c r="Y50" t="s">
-        <v>725</v>
-      </c>
-      <c r="Z50" t="s">
-        <v>726</v>
+        <v>778</v>
       </c>
       <c r="AA50" t="s">
-        <v>727</v>
+        <v>779</v>
       </c>
       <c r="AB50" t="s">
         <v>39</v>
@@ -6968,16 +6995,16 @@
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="C51" t="s">
-        <v>729</v>
+        <v>715</v>
       </c>
       <c r="D51" t="s">
-        <v>730</v>
+        <v>716</v>
       </c>
       <c r="E51" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F51" t="s">
         <v>34</v>
@@ -7001,7 +7028,7 @@
         <v>74</v>
       </c>
       <c r="N51" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O51">
         <v>1</v>
@@ -7016,10 +7043,13 @@
         <v>2</v>
       </c>
       <c r="Y51" t="s">
-        <v>731</v>
+        <v>717</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>51</v>
       </c>
       <c r="AA51" t="s">
-        <v>732</v>
+        <v>718</v>
       </c>
       <c r="AB51" t="s">
         <v>39</v>
@@ -7033,13 +7063,13 @@
     </row>
     <row r="52" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>733</v>
+        <v>719</v>
       </c>
       <c r="C52" t="s">
-        <v>734</v>
+        <v>720</v>
       </c>
       <c r="D52" t="s">
-        <v>735</v>
+        <v>721</v>
       </c>
       <c r="E52" t="s">
         <v>33</v>
@@ -7057,13 +7087,13 @@
         <v>54</v>
       </c>
       <c r="K52" t="s">
-        <v>43</v>
+        <v>722</v>
       </c>
       <c r="L52" t="s">
-        <v>44</v>
+        <v>723</v>
       </c>
       <c r="M52" t="s">
-        <v>45</v>
+        <v>724</v>
       </c>
       <c r="N52" t="s">
         <v>33</v>
@@ -7075,16 +7105,19 @@
         <v>38</v>
       </c>
       <c r="Q52">
-        <v>40.99</v>
+        <v>12.99</v>
       </c>
       <c r="R52">
-        <v>6.83</v>
+        <v>2.17</v>
       </c>
       <c r="Y52" t="s">
-        <v>736</v>
+        <v>725</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>726</v>
       </c>
       <c r="AA52" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
       <c r="AB52" t="s">
         <v>39</v>
@@ -7098,13 +7131,13 @@
     </row>
     <row r="53" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>738</v>
+        <v>728</v>
       </c>
       <c r="C53" t="s">
-        <v>739</v>
+        <v>729</v>
       </c>
       <c r="D53" t="s">
-        <v>740</v>
+        <v>730</v>
       </c>
       <c r="E53" t="s">
         <v>33</v>
@@ -7122,13 +7155,13 @@
         <v>54</v>
       </c>
       <c r="K53" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L53" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M53" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="N53" t="s">
         <v>33</v>
@@ -7140,16 +7173,16 @@
         <v>38</v>
       </c>
       <c r="Q53">
-        <v>40.99</v>
+        <v>11.99</v>
       </c>
       <c r="R53">
-        <v>6.83</v>
+        <v>2</v>
       </c>
       <c r="Y53" t="s">
-        <v>741</v>
+        <v>731</v>
       </c>
       <c r="AA53" t="s">
-        <v>742</v>
+        <v>732</v>
       </c>
       <c r="AB53" t="s">
         <v>39</v>
@@ -7163,13 +7196,13 @@
     </row>
     <row r="54" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>708</v>
+        <v>733</v>
       </c>
       <c r="C54" t="s">
-        <v>709</v>
+        <v>734</v>
       </c>
       <c r="D54" t="s">
-        <v>743</v>
+        <v>735</v>
       </c>
       <c r="E54" t="s">
         <v>33</v>
@@ -7187,13 +7220,13 @@
         <v>54</v>
       </c>
       <c r="K54" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L54" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M54" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N54" t="s">
         <v>33</v>
@@ -7205,19 +7238,16 @@
         <v>38</v>
       </c>
       <c r="Q54">
-        <v>65.989999999999995</v>
+        <v>40.99</v>
       </c>
       <c r="R54">
-        <v>11</v>
+        <v>6.83</v>
       </c>
       <c r="Y54" t="s">
-        <v>711</v>
-      </c>
-      <c r="Z54" t="s">
-        <v>712</v>
+        <v>736</v>
       </c>
       <c r="AA54" t="s">
-        <v>713</v>
+        <v>737</v>
       </c>
       <c r="AB54" t="s">
         <v>39</v>
@@ -7231,13 +7261,13 @@
     </row>
     <row r="55" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>643</v>
+        <v>738</v>
       </c>
       <c r="C55" t="s">
-        <v>644</v>
+        <v>739</v>
       </c>
       <c r="D55" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="E55" t="s">
         <v>33</v>
@@ -7255,13 +7285,13 @@
         <v>54</v>
       </c>
       <c r="K55" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="L55" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="M55" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="N55" t="s">
         <v>33</v>
@@ -7273,16 +7303,16 @@
         <v>38</v>
       </c>
       <c r="Q55">
-        <v>14.99</v>
+        <v>40.99</v>
       </c>
       <c r="R55">
-        <v>2.5</v>
+        <v>6.83</v>
       </c>
       <c r="Y55" t="s">
-        <v>646</v>
+        <v>741</v>
       </c>
       <c r="AA55" t="s">
-        <v>647</v>
+        <v>742</v>
       </c>
       <c r="AB55" t="s">
         <v>39</v>
@@ -7302,10 +7332,10 @@
         <v>709</v>
       </c>
       <c r="D56" t="s">
-        <v>710</v>
+        <v>743</v>
       </c>
       <c r="E56" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F56" t="s">
         <v>34</v>
@@ -7329,7 +7359,7 @@
         <v>42</v>
       </c>
       <c r="N56" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O56">
         <v>1</v>
@@ -7364,22 +7394,22 @@
     </row>
     <row r="57" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>138</v>
+        <v>643</v>
       </c>
       <c r="C57" t="s">
-        <v>139</v>
+        <v>644</v>
       </c>
       <c r="D57" t="s">
-        <v>187</v>
+        <v>744</v>
       </c>
       <c r="E57" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F57" t="s">
         <v>34</v>
       </c>
       <c r="G57" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="H57" t="s">
         <v>36</v>
@@ -7388,25 +7418,37 @@
         <v>54</v>
       </c>
       <c r="K57" t="s">
-        <v>141</v>
+        <v>94</v>
       </c>
       <c r="L57" t="s">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="M57" t="s">
-        <v>143</v>
+        <v>83</v>
+      </c>
+      <c r="N57" t="s">
+        <v>33</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P57" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q57">
+        <v>14.99</v>
+      </c>
+      <c r="R57">
+        <v>2.5</v>
       </c>
       <c r="Y57" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA57">
-        <v>80100</v>
+        <v>646</v>
+      </c>
+      <c r="AA57" t="s">
+        <v>647</v>
       </c>
       <c r="AB57" t="s">
-        <v>145</v>
+        <v>39</v>
       </c>
       <c r="AD57" t="b">
         <v>0</v>
@@ -7417,22 +7459,22 @@
     </row>
     <row r="58" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>146</v>
+        <v>708</v>
       </c>
       <c r="C58" t="s">
-        <v>147</v>
+        <v>709</v>
       </c>
       <c r="D58" t="s">
-        <v>148</v>
+        <v>710</v>
       </c>
       <c r="E58" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="F58" t="s">
         <v>34</v>
       </c>
       <c r="G58" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="H58" t="s">
         <v>36</v>
@@ -7441,25 +7483,40 @@
         <v>54</v>
       </c>
       <c r="K58" t="s">
-        <v>141</v>
+        <v>40</v>
       </c>
       <c r="L58" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="M58" t="s">
-        <v>143</v>
+        <v>42</v>
+      </c>
+      <c r="N58" t="s">
+        <v>99</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P58" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q58">
+        <v>65.989999999999995</v>
+      </c>
+      <c r="R58">
+        <v>11</v>
       </c>
       <c r="Y58" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA58">
-        <v>80100</v>
+        <v>711</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>712</v>
+      </c>
+      <c r="AA58" t="s">
+        <v>713</v>
       </c>
       <c r="AB58" t="s">
-        <v>145</v>
+        <v>39</v>
       </c>
       <c r="AD58" t="b">
         <v>0</v>
@@ -7470,13 +7527,13 @@
     </row>
     <row r="59" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>632</v>
+        <v>138</v>
       </c>
       <c r="C59" t="s">
-        <v>633</v>
+        <v>139</v>
       </c>
       <c r="D59" t="s">
-        <v>634</v>
+        <v>187</v>
       </c>
       <c r="E59" t="s">
         <v>53</v>
@@ -7485,7 +7542,7 @@
         <v>34</v>
       </c>
       <c r="G59" t="s">
-        <v>635</v>
+        <v>140</v>
       </c>
       <c r="H59" t="s">
         <v>36</v>
@@ -7494,37 +7551,25 @@
         <v>54</v>
       </c>
       <c r="K59" t="s">
-        <v>636</v>
+        <v>141</v>
       </c>
       <c r="L59" t="s">
-        <v>637</v>
+        <v>142</v>
       </c>
       <c r="M59" t="s">
-        <v>638</v>
+        <v>143</v>
       </c>
       <c r="O59">
         <v>0</v>
       </c>
-      <c r="P59" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q59">
-        <v>22.9</v>
-      </c>
-      <c r="R59">
-        <v>4.8099999999999996</v>
-      </c>
       <c r="Y59" t="s">
-        <v>639</v>
-      </c>
-      <c r="Z59" t="s">
-        <v>640</v>
-      </c>
-      <c r="AA59" t="s">
-        <v>641</v>
+        <v>144</v>
+      </c>
+      <c r="AA59">
+        <v>80100</v>
       </c>
       <c r="AB59" t="s">
-        <v>642</v>
+        <v>145</v>
       </c>
       <c r="AD59" t="b">
         <v>0</v>
@@ -7535,22 +7580,22 @@
     </row>
     <row r="60" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>643</v>
+        <v>146</v>
       </c>
       <c r="C60" t="s">
-        <v>644</v>
+        <v>147</v>
       </c>
       <c r="D60" t="s">
-        <v>645</v>
+        <v>148</v>
       </c>
       <c r="E60" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="F60" t="s">
         <v>34</v>
       </c>
       <c r="G60" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="H60" t="s">
         <v>36</v>
@@ -7559,37 +7604,25 @@
         <v>54</v>
       </c>
       <c r="K60" t="s">
-        <v>94</v>
+        <v>141</v>
       </c>
       <c r="L60" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="M60" t="s">
-        <v>83</v>
-      </c>
-      <c r="N60" t="s">
-        <v>99</v>
+        <v>143</v>
       </c>
       <c r="O60">
-        <v>1</v>
-      </c>
-      <c r="P60" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q60">
-        <v>14.99</v>
-      </c>
-      <c r="R60">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y60" t="s">
-        <v>646</v>
-      </c>
-      <c r="AA60" t="s">
-        <v>647</v>
+        <v>144</v>
+      </c>
+      <c r="AA60">
+        <v>80100</v>
       </c>
       <c r="AB60" t="s">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="AD60" t="b">
         <v>0</v>
@@ -7600,22 +7633,22 @@
     </row>
     <row r="61" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>609</v>
+        <v>632</v>
       </c>
       <c r="C61" t="s">
-        <v>610</v>
+        <v>633</v>
       </c>
       <c r="D61" t="s">
-        <v>611</v>
+        <v>634</v>
       </c>
       <c r="E61" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F61" t="s">
         <v>34</v>
       </c>
       <c r="G61" t="s">
-        <v>35</v>
+        <v>635</v>
       </c>
       <c r="H61" t="s">
         <v>36</v>
@@ -7624,40 +7657,37 @@
         <v>54</v>
       </c>
       <c r="K61" t="s">
-        <v>94</v>
+        <v>636</v>
       </c>
       <c r="L61" t="s">
-        <v>82</v>
+        <v>637</v>
       </c>
       <c r="M61" t="s">
-        <v>83</v>
-      </c>
-      <c r="N61" t="s">
-        <v>33</v>
+        <v>638</v>
       </c>
       <c r="O61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P61" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="Q61">
-        <v>14.99</v>
+        <v>22.9</v>
       </c>
       <c r="R61">
-        <v>2.5</v>
+        <v>4.8099999999999996</v>
       </c>
       <c r="Y61" t="s">
-        <v>612</v>
+        <v>639</v>
       </c>
       <c r="Z61" t="s">
-        <v>613</v>
+        <v>640</v>
       </c>
       <c r="AA61" t="s">
-        <v>614</v>
+        <v>641</v>
       </c>
       <c r="AB61" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="AD61" t="b">
         <v>0</v>
@@ -7668,16 +7698,16 @@
     </row>
     <row r="62" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>493</v>
+        <v>643</v>
       </c>
       <c r="C62" t="s">
-        <v>494</v>
+        <v>644</v>
       </c>
       <c r="D62" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="E62" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="F62" t="s">
         <v>34</v>
@@ -7692,22 +7722,34 @@
         <v>54</v>
       </c>
       <c r="K62" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L62" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M62" t="s">
-        <v>42</v>
+        <v>83</v>
+      </c>
+      <c r="N62" t="s">
+        <v>99</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P62" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q62">
+        <v>14.99</v>
+      </c>
+      <c r="R62">
+        <v>2.5</v>
       </c>
       <c r="Y62" t="s">
-        <v>495</v>
+        <v>646</v>
       </c>
       <c r="AA62" t="s">
-        <v>496</v>
+        <v>647</v>
       </c>
       <c r="AB62" t="s">
         <v>39</v>
@@ -7721,16 +7763,16 @@
     </row>
     <row r="63" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="C63" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="D63" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="E63" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F63" t="s">
         <v>34</v>
@@ -7745,16 +7787,16 @@
         <v>54</v>
       </c>
       <c r="K63" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="L63" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="M63" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="N63" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O63">
         <v>1</v>
@@ -7763,16 +7805,19 @@
         <v>38</v>
       </c>
       <c r="Q63">
-        <v>40.99</v>
+        <v>14.99</v>
+      </c>
+      <c r="R63">
+        <v>2.5</v>
       </c>
       <c r="Y63" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="Z63" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="AA63" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="AB63" t="s">
         <v>39</v>
@@ -7786,16 +7831,16 @@
     </row>
     <row r="64" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>621</v>
+        <v>493</v>
       </c>
       <c r="C64" t="s">
-        <v>622</v>
+        <v>494</v>
       </c>
       <c r="D64" t="s">
-        <v>623</v>
+        <v>648</v>
       </c>
       <c r="E64" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F64" t="s">
         <v>34</v>
@@ -7818,35 +7863,14 @@
       <c r="M64" t="s">
         <v>42</v>
       </c>
-      <c r="N64" t="s">
-        <v>33</v>
-      </c>
       <c r="O64">
-        <v>1</v>
-      </c>
-      <c r="P64" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q64">
-        <v>64.989999999999995</v>
-      </c>
-      <c r="R64">
-        <v>10.83</v>
-      </c>
-      <c r="S64">
-        <v>6.99</v>
-      </c>
-      <c r="T64">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Y64" t="s">
-        <v>624</v>
-      </c>
-      <c r="Z64" t="s">
-        <v>625</v>
+        <v>495</v>
       </c>
       <c r="AA64" t="s">
-        <v>626</v>
+        <v>496</v>
       </c>
       <c r="AB64" t="s">
         <v>39</v>
@@ -7860,16 +7884,16 @@
     </row>
     <row r="65" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="C65" t="s">
-        <v>628</v>
+        <v>616</v>
       </c>
       <c r="D65" t="s">
-        <v>629</v>
+        <v>617</v>
       </c>
       <c r="E65" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F65" t="s">
         <v>34</v>
@@ -7884,16 +7908,16 @@
         <v>54</v>
       </c>
       <c r="K65" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L65" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M65" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N65" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="O65">
         <v>1</v>
@@ -7902,16 +7926,16 @@
         <v>38</v>
       </c>
       <c r="Q65">
-        <v>11.99</v>
-      </c>
-      <c r="R65">
-        <v>2</v>
+        <v>40.99</v>
       </c>
       <c r="Y65" t="s">
-        <v>630</v>
+        <v>618</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>619</v>
       </c>
       <c r="AA65" t="s">
-        <v>631</v>
+        <v>620</v>
       </c>
       <c r="AB65" t="s">
         <v>39</v>
@@ -7925,13 +7949,13 @@
     </row>
     <row r="66" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>649</v>
+        <v>621</v>
       </c>
       <c r="C66" t="s">
-        <v>650</v>
+        <v>622</v>
       </c>
       <c r="D66" t="s">
-        <v>651</v>
+        <v>623</v>
       </c>
       <c r="E66" t="s">
         <v>33</v>
@@ -7949,13 +7973,13 @@
         <v>54</v>
       </c>
       <c r="K66" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L66" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M66" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N66" t="s">
         <v>33</v>
@@ -7967,19 +7991,25 @@
         <v>38</v>
       </c>
       <c r="Q66">
-        <v>39.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R66">
-        <v>6.67</v>
+        <v>10.83</v>
+      </c>
+      <c r="S66">
+        <v>6.99</v>
+      </c>
+      <c r="T66">
+        <v>1.17</v>
       </c>
       <c r="Y66" t="s">
-        <v>652</v>
+        <v>624</v>
       </c>
       <c r="Z66" t="s">
-        <v>653</v>
+        <v>625</v>
       </c>
       <c r="AA66" t="s">
-        <v>654</v>
+        <v>626</v>
       </c>
       <c r="AB66" t="s">
         <v>39</v>
@@ -7993,13 +8023,13 @@
     </row>
     <row r="67" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>655</v>
+        <v>627</v>
       </c>
       <c r="C67" t="s">
-        <v>656</v>
+        <v>628</v>
       </c>
       <c r="D67" t="s">
-        <v>657</v>
+        <v>629</v>
       </c>
       <c r="E67" t="s">
         <v>33</v>
@@ -8017,13 +8047,13 @@
         <v>54</v>
       </c>
       <c r="K67" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L67" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M67" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="N67" t="s">
         <v>33</v>
@@ -8035,16 +8065,16 @@
         <v>38</v>
       </c>
       <c r="Q67">
-        <v>14.99</v>
+        <v>11.99</v>
       </c>
       <c r="R67">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Y67" t="s">
-        <v>658</v>
+        <v>630</v>
       </c>
       <c r="AA67" t="s">
-        <v>659</v>
+        <v>631</v>
       </c>
       <c r="AB67" t="s">
         <v>39</v>
@@ -8058,13 +8088,13 @@
     </row>
     <row r="68" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>571</v>
+        <v>649</v>
       </c>
       <c r="C68" t="s">
-        <v>572</v>
+        <v>650</v>
       </c>
       <c r="D68" t="s">
-        <v>660</v>
+        <v>651</v>
       </c>
       <c r="E68" t="s">
         <v>33</v>
@@ -8082,13 +8112,13 @@
         <v>54</v>
       </c>
       <c r="K68" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L68" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M68" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N68" t="s">
         <v>33</v>
@@ -8100,16 +8130,19 @@
         <v>38</v>
       </c>
       <c r="Q68">
-        <v>64.989999999999995</v>
+        <v>39.99</v>
       </c>
       <c r="R68">
-        <v>10.83</v>
+        <v>6.67</v>
       </c>
       <c r="Y68" t="s">
-        <v>573</v>
+        <v>652</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>653</v>
       </c>
       <c r="AA68" t="s">
-        <v>574</v>
+        <v>654</v>
       </c>
       <c r="AB68" t="s">
         <v>39</v>
@@ -8123,13 +8156,13 @@
     </row>
     <row r="69" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>599</v>
+        <v>655</v>
       </c>
       <c r="C69" t="s">
-        <v>600</v>
+        <v>656</v>
       </c>
       <c r="D69" t="s">
-        <v>601</v>
+        <v>657</v>
       </c>
       <c r="E69" t="s">
         <v>33</v>
@@ -8171,10 +8204,10 @@
         <v>2.5</v>
       </c>
       <c r="Y69" t="s">
-        <v>61</v>
+        <v>658</v>
       </c>
       <c r="AA69" t="s">
-        <v>602</v>
+        <v>659</v>
       </c>
       <c r="AB69" t="s">
         <v>39</v>
@@ -8188,13 +8221,13 @@
     </row>
     <row r="70" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>589</v>
+        <v>571</v>
       </c>
       <c r="C70" t="s">
-        <v>590</v>
+        <v>572</v>
       </c>
       <c r="D70" t="s">
-        <v>591</v>
+        <v>660</v>
       </c>
       <c r="E70" t="s">
         <v>33</v>
@@ -8236,10 +8269,10 @@
         <v>10.83</v>
       </c>
       <c r="Y70" t="s">
-        <v>592</v>
+        <v>573</v>
       </c>
       <c r="AA70" t="s">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="AB70" t="s">
         <v>39</v>
@@ -8253,13 +8286,13 @@
     </row>
     <row r="71" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="C71" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="D71" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="E71" t="s">
         <v>33</v>
@@ -8277,13 +8310,13 @@
         <v>54</v>
       </c>
       <c r="K71" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L71" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M71" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="N71" t="s">
         <v>33</v>
@@ -8295,16 +8328,16 @@
         <v>38</v>
       </c>
       <c r="Q71">
-        <v>64.989999999999995</v>
+        <v>14.99</v>
       </c>
       <c r="R71">
-        <v>10.83</v>
+        <v>2.5</v>
       </c>
       <c r="Y71" t="s">
-        <v>597</v>
+        <v>61</v>
       </c>
       <c r="AA71" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="AB71" t="s">
         <v>39</v>
@@ -8318,13 +8351,13 @@
     </row>
     <row r="72" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>603</v>
+        <v>589</v>
       </c>
       <c r="C72" t="s">
-        <v>604</v>
+        <v>590</v>
       </c>
       <c r="D72" t="s">
-        <v>605</v>
+        <v>591</v>
       </c>
       <c r="E72" t="s">
         <v>33</v>
@@ -8366,13 +8399,10 @@
         <v>10.83</v>
       </c>
       <c r="Y72" t="s">
-        <v>606</v>
-      </c>
-      <c r="Z72" t="s">
-        <v>607</v>
+        <v>592</v>
       </c>
       <c r="AA72" t="s">
-        <v>608</v>
+        <v>593</v>
       </c>
       <c r="AB72" t="s">
         <v>39</v>
@@ -8386,13 +8416,13 @@
     </row>
     <row r="73" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>578</v>
+        <v>594</v>
       </c>
       <c r="C73" t="s">
-        <v>579</v>
+        <v>595</v>
       </c>
       <c r="D73" t="s">
-        <v>661</v>
+        <v>596</v>
       </c>
       <c r="E73" t="s">
         <v>33</v>
@@ -8434,13 +8464,10 @@
         <v>10.83</v>
       </c>
       <c r="Y73" t="s">
-        <v>580</v>
-      </c>
-      <c r="Z73" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="AA73" t="s">
-        <v>582</v>
+        <v>598</v>
       </c>
       <c r="AB73" t="s">
         <v>39</v>
@@ -8454,16 +8481,16 @@
     </row>
     <row r="74" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>575</v>
+        <v>603</v>
       </c>
       <c r="C74" t="s">
-        <v>576</v>
+        <v>604</v>
       </c>
       <c r="D74" t="s">
-        <v>577</v>
+        <v>605</v>
       </c>
       <c r="E74" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F74" t="s">
         <v>34</v>
@@ -8486,14 +8513,29 @@
       <c r="M74" t="s">
         <v>42</v>
       </c>
+      <c r="N74" t="s">
+        <v>33</v>
+      </c>
       <c r="O74">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P74" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q74">
+        <v>64.989999999999995</v>
+      </c>
+      <c r="R74">
+        <v>10.83</v>
       </c>
       <c r="Y74" t="s">
-        <v>573</v>
+        <v>606</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>607</v>
       </c>
       <c r="AA74" t="s">
-        <v>574</v>
+        <v>608</v>
       </c>
       <c r="AB74" t="s">
         <v>39</v>
@@ -8507,13 +8549,13 @@
     </row>
     <row r="75" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>518</v>
+        <v>578</v>
       </c>
       <c r="C75" t="s">
-        <v>519</v>
+        <v>579</v>
       </c>
       <c r="D75" t="s">
-        <v>583</v>
+        <v>661</v>
       </c>
       <c r="E75" t="s">
         <v>33</v>
@@ -8531,13 +8573,13 @@
         <v>54</v>
       </c>
       <c r="K75" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L75" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M75" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N75" t="s">
         <v>33</v>
@@ -8549,22 +8591,19 @@
         <v>38</v>
       </c>
       <c r="Q75">
-        <v>37.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R75">
-        <v>6.33</v>
-      </c>
-      <c r="S75">
-        <v>6.99</v>
-      </c>
-      <c r="T75">
-        <v>1.17</v>
+        <v>10.83</v>
       </c>
       <c r="Y75" t="s">
-        <v>46</v>
+        <v>580</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>581</v>
       </c>
       <c r="AA75" t="s">
-        <v>520</v>
+        <v>582</v>
       </c>
       <c r="AB75" t="s">
         <v>39</v>
@@ -8578,16 +8617,16 @@
     </row>
     <row r="76" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="C76" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="D76" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="E76" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F76" t="s">
         <v>34</v>
@@ -8610,26 +8649,14 @@
       <c r="M76" t="s">
         <v>42</v>
       </c>
-      <c r="N76" t="s">
-        <v>33</v>
-      </c>
       <c r="O76">
-        <v>1</v>
-      </c>
-      <c r="P76" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q76">
-        <v>64.989999999999995</v>
-      </c>
-      <c r="R76">
-        <v>10.83</v>
+        <v>0</v>
       </c>
       <c r="Y76" t="s">
-        <v>587</v>
+        <v>573</v>
       </c>
       <c r="AA76" t="s">
-        <v>588</v>
+        <v>574</v>
       </c>
       <c r="AB76" t="s">
         <v>39</v>
@@ -8643,13 +8670,13 @@
     </row>
     <row r="77" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>457</v>
+        <v>518</v>
       </c>
       <c r="C77" t="s">
-        <v>458</v>
+        <v>519</v>
       </c>
       <c r="D77" t="s">
-        <v>459</v>
+        <v>583</v>
       </c>
       <c r="E77" t="s">
         <v>33</v>
@@ -8667,13 +8694,13 @@
         <v>54</v>
       </c>
       <c r="K77" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L77" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M77" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N77" t="s">
         <v>33</v>
@@ -8685,19 +8712,22 @@
         <v>38</v>
       </c>
       <c r="Q77">
-        <v>64.989999999999995</v>
+        <v>37.99</v>
       </c>
       <c r="R77">
-        <v>10.83</v>
+        <v>6.33</v>
+      </c>
+      <c r="S77">
+        <v>6.99</v>
+      </c>
+      <c r="T77">
+        <v>1.17</v>
       </c>
       <c r="Y77" t="s">
-        <v>460</v>
-      </c>
-      <c r="Z77" t="s">
-        <v>279</v>
+        <v>46</v>
       </c>
       <c r="AA77" t="s">
-        <v>461</v>
+        <v>520</v>
       </c>
       <c r="AB77" t="s">
         <v>39</v>
@@ -8711,13 +8741,13 @@
     </row>
     <row r="78" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>462</v>
+        <v>584</v>
       </c>
       <c r="C78" t="s">
-        <v>463</v>
+        <v>585</v>
       </c>
       <c r="D78" t="s">
-        <v>459</v>
+        <v>586</v>
       </c>
       <c r="E78" t="s">
         <v>33</v>
@@ -8759,10 +8789,10 @@
         <v>10.83</v>
       </c>
       <c r="Y78" t="s">
-        <v>56</v>
+        <v>587</v>
       </c>
       <c r="AA78" t="s">
-        <v>464</v>
+        <v>588</v>
       </c>
       <c r="AB78" t="s">
         <v>39</v>
@@ -8776,13 +8806,13 @@
     </row>
     <row r="79" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="C79" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D79" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="E79" t="s">
         <v>33</v>
@@ -8800,34 +8830,37 @@
         <v>54</v>
       </c>
       <c r="K79" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L79" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M79" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N79" t="s">
         <v>33</v>
       </c>
       <c r="O79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P79" t="s">
         <v>38</v>
       </c>
       <c r="Q79">
-        <v>79.98</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R79">
-        <v>13.34</v>
+        <v>10.83</v>
       </c>
       <c r="Y79" t="s">
-        <v>468</v>
+        <v>460</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>279</v>
       </c>
       <c r="AA79" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="AB79" t="s">
         <v>39</v>
@@ -8841,13 +8874,13 @@
     </row>
     <row r="80" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="C80" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="D80" t="s">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="E80" t="s">
         <v>33</v>
@@ -8865,13 +8898,13 @@
         <v>54</v>
       </c>
       <c r="K80" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L80" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M80" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N80" t="s">
         <v>33</v>
@@ -8883,16 +8916,16 @@
         <v>38</v>
       </c>
       <c r="Q80">
-        <v>37.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R80">
-        <v>6.33</v>
+        <v>10.83</v>
       </c>
       <c r="Y80" t="s">
-        <v>473</v>
+        <v>56</v>
       </c>
       <c r="AA80" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="AB80" t="s">
         <v>39</v>
@@ -8906,16 +8939,16 @@
     </row>
     <row r="81" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="C81" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="D81" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="E81" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F81" t="s">
         <v>34</v>
@@ -8930,25 +8963,34 @@
         <v>54</v>
       </c>
       <c r="K81" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L81" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M81" t="s">
-        <v>42</v>
+        <v>50</v>
+      </c>
+      <c r="N81" t="s">
+        <v>33</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="P81" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q81">
+        <v>79.98</v>
+      </c>
+      <c r="R81">
+        <v>13.34</v>
       </c>
       <c r="Y81" t="s">
-        <v>478</v>
-      </c>
-      <c r="Z81" t="s">
-        <v>279</v>
+        <v>468</v>
       </c>
       <c r="AA81" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="AB81" t="s">
         <v>39</v>
@@ -8962,13 +9004,13 @@
     </row>
     <row r="82" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="C82" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="D82" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="E82" t="s">
         <v>33</v>
@@ -8986,13 +9028,13 @@
         <v>54</v>
       </c>
       <c r="K82" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L82" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M82" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N82" t="s">
         <v>33</v>
@@ -9004,16 +9046,16 @@
         <v>38</v>
       </c>
       <c r="Q82">
-        <v>11.99</v>
+        <v>37.99</v>
       </c>
       <c r="R82">
-        <v>2</v>
+        <v>6.33</v>
       </c>
       <c r="Y82" t="s">
-        <v>61</v>
+        <v>473</v>
       </c>
       <c r="AA82" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="AB82" t="s">
         <v>39</v>
@@ -9027,16 +9069,16 @@
     </row>
     <row r="83" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="C83" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="D83" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="E83" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F83" t="s">
         <v>34</v>
@@ -9059,26 +9101,17 @@
       <c r="M83" t="s">
         <v>42</v>
       </c>
-      <c r="N83" t="s">
-        <v>33</v>
-      </c>
       <c r="O83">
-        <v>1</v>
-      </c>
-      <c r="P83" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q83">
-        <v>64.989999999999995</v>
-      </c>
-      <c r="R83">
-        <v>10.83</v>
+        <v>0</v>
       </c>
       <c r="Y83" t="s">
-        <v>67</v>
+        <v>478</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>279</v>
       </c>
       <c r="AA83" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="AB83" t="s">
         <v>39</v>
@@ -9092,13 +9125,13 @@
     </row>
     <row r="84" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="C84" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="D84" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="E84" t="s">
         <v>33</v>
@@ -9116,37 +9149,34 @@
         <v>54</v>
       </c>
       <c r="K84" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L84" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M84" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="N84" t="s">
         <v>33</v>
       </c>
       <c r="O84">
+        <v>1</v>
+      </c>
+      <c r="P84" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q84">
+        <v>11.99</v>
+      </c>
+      <c r="R84">
         <v>2</v>
       </c>
-      <c r="P84" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q84">
-        <v>79.98</v>
-      </c>
-      <c r="R84">
-        <v>13.34</v>
-      </c>
       <c r="Y84" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z84" t="s">
-        <v>491</v>
+        <v>61</v>
       </c>
       <c r="AA84" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="AB84" t="s">
         <v>39</v>
@@ -9160,13 +9190,13 @@
     </row>
     <row r="85" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="C85" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="D85" t="s">
-        <v>499</v>
+        <v>486</v>
       </c>
       <c r="E85" t="s">
         <v>33</v>
@@ -9202,19 +9232,16 @@
         <v>38</v>
       </c>
       <c r="Q85">
-        <v>59.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="R85">
-        <v>10</v>
+        <v>10.83</v>
       </c>
       <c r="Y85" t="s">
-        <v>500</v>
-      </c>
-      <c r="Z85" t="s">
-        <v>501</v>
+        <v>67</v>
       </c>
       <c r="AA85" t="s">
-        <v>502</v>
+        <v>487</v>
       </c>
       <c r="AB85" t="s">
         <v>39</v>
@@ -9228,13 +9255,13 @@
     </row>
     <row r="86" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>503</v>
+        <v>488</v>
       </c>
       <c r="C86" t="s">
-        <v>504</v>
+        <v>489</v>
       </c>
       <c r="D86" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="E86" t="s">
         <v>33</v>
@@ -9252,37 +9279,37 @@
         <v>54</v>
       </c>
       <c r="K86" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L86" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M86" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N86" t="s">
         <v>33</v>
       </c>
       <c r="O86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P86" t="s">
         <v>38</v>
       </c>
       <c r="Q86">
-        <v>59.99</v>
+        <v>79.98</v>
       </c>
       <c r="R86">
-        <v>10</v>
+        <v>13.34</v>
       </c>
       <c r="Y86" t="s">
-        <v>505</v>
+        <v>63</v>
       </c>
       <c r="Z86" t="s">
-        <v>93</v>
+        <v>491</v>
       </c>
       <c r="AA86" t="s">
-        <v>506</v>
+        <v>492</v>
       </c>
       <c r="AB86" t="s">
         <v>39</v>
@@ -9296,13 +9323,13 @@
     </row>
     <row r="87" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="C87" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="D87" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="E87" t="s">
         <v>33</v>
@@ -9344,10 +9371,13 @@
         <v>10</v>
       </c>
       <c r="Y87" t="s">
-        <v>510</v>
+        <v>500</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>501</v>
       </c>
       <c r="AA87" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="AB87" t="s">
         <v>39</v>
@@ -9361,13 +9391,13 @@
     </row>
     <row r="88" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="C88" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="D88" t="s">
-        <v>514</v>
+        <v>499</v>
       </c>
       <c r="E88" t="s">
         <v>33</v>
@@ -9409,13 +9439,13 @@
         <v>10</v>
       </c>
       <c r="Y88" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="Z88" t="s">
-        <v>516</v>
+        <v>93</v>
       </c>
       <c r="AA88" t="s">
-        <v>517</v>
+        <v>506</v>
       </c>
       <c r="AB88" t="s">
         <v>39</v>
@@ -9429,13 +9459,13 @@
     </row>
     <row r="89" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>521</v>
+        <v>507</v>
       </c>
       <c r="C89" t="s">
-        <v>522</v>
+        <v>508</v>
       </c>
       <c r="D89" t="s">
-        <v>523</v>
+        <v>509</v>
       </c>
       <c r="E89" t="s">
         <v>33</v>
@@ -9453,13 +9483,13 @@
         <v>54</v>
       </c>
       <c r="K89" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L89" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M89" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="N89" t="s">
         <v>33</v>
@@ -9471,16 +9501,16 @@
         <v>38</v>
       </c>
       <c r="Q89">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R89">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y89" t="s">
-        <v>58</v>
+        <v>510</v>
       </c>
       <c r="AA89" t="s">
-        <v>524</v>
+        <v>511</v>
       </c>
       <c r="AB89" t="s">
         <v>39</v>
@@ -9494,13 +9524,13 @@
     </row>
     <row r="90" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="C90" t="s">
-        <v>526</v>
+        <v>513</v>
       </c>
       <c r="D90" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
       <c r="E90" t="s">
         <v>33</v>
@@ -9542,10 +9572,13 @@
         <v>10</v>
       </c>
       <c r="Y90" t="s">
-        <v>90</v>
+        <v>515</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>516</v>
       </c>
       <c r="AA90" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="AB90" t="s">
         <v>39</v>
@@ -9559,13 +9592,13 @@
     </row>
     <row r="91" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="C91" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="D91" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="E91" t="s">
         <v>33</v>
@@ -9583,13 +9616,13 @@
         <v>54</v>
       </c>
       <c r="K91" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L91" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M91" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="N91" t="s">
         <v>33</v>
@@ -9601,16 +9634,16 @@
         <v>38</v>
       </c>
       <c r="Q91">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="R91">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="Y91" t="s">
-        <v>531</v>
+        <v>58</v>
       </c>
       <c r="AA91" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="AB91" t="s">
         <v>39</v>
@@ -9624,13 +9657,13 @@
     </row>
     <row r="92" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="C92" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="D92" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="E92" t="s">
         <v>33</v>
@@ -9648,13 +9681,13 @@
         <v>54</v>
       </c>
       <c r="K92" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L92" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M92" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N92" t="s">
         <v>33</v>
@@ -9666,19 +9699,16 @@
         <v>38</v>
       </c>
       <c r="Q92">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R92">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y92" t="s">
-        <v>536</v>
-      </c>
-      <c r="Z92" t="s">
-        <v>537</v>
+        <v>90</v>
       </c>
       <c r="AA92" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="AB92" t="s">
         <v>39</v>
@@ -9692,13 +9722,13 @@
     </row>
     <row r="93" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="C93" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="D93" t="s">
-        <v>541</v>
+        <v>527</v>
       </c>
       <c r="E93" t="s">
         <v>33</v>
@@ -9740,13 +9770,10 @@
         <v>10</v>
       </c>
       <c r="Y93" t="s">
-        <v>71</v>
-      </c>
-      <c r="Z93" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="AA93" t="s">
-        <v>543</v>
+        <v>532</v>
       </c>
       <c r="AB93" t="s">
         <v>39</v>
@@ -9760,13 +9787,13 @@
     </row>
     <row r="94" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
       <c r="C94" t="s">
-        <v>545</v>
+        <v>534</v>
       </c>
       <c r="D94" t="s">
-        <v>546</v>
+        <v>535</v>
       </c>
       <c r="E94" t="s">
         <v>33</v>
@@ -9784,37 +9811,37 @@
         <v>54</v>
       </c>
       <c r="K94" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="L94" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="M94" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="N94" t="s">
         <v>33</v>
       </c>
       <c r="O94">
+        <v>1</v>
+      </c>
+      <c r="P94" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q94">
+        <v>11.99</v>
+      </c>
+      <c r="R94">
         <v>2</v>
       </c>
-      <c r="P94" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q94">
-        <v>76.98</v>
-      </c>
-      <c r="R94">
-        <v>12.84</v>
-      </c>
       <c r="Y94" t="s">
-        <v>547</v>
+        <v>536</v>
       </c>
       <c r="Z94" t="s">
-        <v>548</v>
+        <v>537</v>
       </c>
       <c r="AA94" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="AB94" t="s">
         <v>39</v>
@@ -9828,13 +9855,13 @@
     </row>
     <row r="95" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>550</v>
+        <v>539</v>
       </c>
       <c r="C95" t="s">
-        <v>551</v>
+        <v>540</v>
       </c>
       <c r="D95" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="E95" t="s">
         <v>33</v>
@@ -9876,10 +9903,13 @@
         <v>10</v>
       </c>
       <c r="Y95" t="s">
-        <v>553</v>
+        <v>71</v>
+      </c>
+      <c r="Z95" t="s">
+        <v>542</v>
       </c>
       <c r="AA95" t="s">
-        <v>554</v>
+        <v>543</v>
       </c>
       <c r="AB95" t="s">
         <v>39</v>
@@ -9893,13 +9923,13 @@
     </row>
     <row r="96" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>555</v>
+        <v>544</v>
       </c>
       <c r="C96" t="s">
-        <v>556</v>
+        <v>545</v>
       </c>
       <c r="D96" t="s">
-        <v>557</v>
+        <v>546</v>
       </c>
       <c r="E96" t="s">
         <v>33</v>
@@ -9917,34 +9947,37 @@
         <v>54</v>
       </c>
       <c r="K96" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L96" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M96" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N96" t="s">
         <v>33</v>
       </c>
       <c r="O96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P96" t="s">
         <v>38</v>
       </c>
       <c r="Q96">
-        <v>59.99</v>
+        <v>76.98</v>
       </c>
       <c r="R96">
-        <v>10</v>
+        <v>12.84</v>
       </c>
       <c r="Y96" t="s">
-        <v>558</v>
+        <v>547</v>
+      </c>
+      <c r="Z96" t="s">
+        <v>548</v>
       </c>
       <c r="AA96" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
       <c r="AB96" t="s">
         <v>39</v>
@@ -9958,13 +9991,13 @@
     </row>
     <row r="97" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>418</v>
+        <v>550</v>
       </c>
       <c r="C97" t="s">
-        <v>419</v>
+        <v>551</v>
       </c>
       <c r="D97" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="E97" t="s">
         <v>33</v>
@@ -10006,10 +10039,10 @@
         <v>10</v>
       </c>
       <c r="Y97" t="s">
-        <v>420</v>
+        <v>553</v>
       </c>
       <c r="AA97" t="s">
-        <v>421</v>
+        <v>554</v>
       </c>
       <c r="AB97" t="s">
         <v>39</v>
@@ -10023,13 +10056,13 @@
     </row>
     <row r="98" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="C98" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="D98" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="E98" t="s">
         <v>33</v>
@@ -10071,13 +10104,10 @@
         <v>10</v>
       </c>
       <c r="Y98" t="s">
-        <v>564</v>
-      </c>
-      <c r="Z98" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="AA98" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="AB98" t="s">
         <v>39</v>
@@ -10091,13 +10121,13 @@
     </row>
     <row r="99" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>567</v>
+        <v>418</v>
       </c>
       <c r="C99" t="s">
-        <v>568</v>
+        <v>419</v>
       </c>
       <c r="D99" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="E99" t="s">
         <v>33</v>
@@ -10115,13 +10145,13 @@
         <v>54</v>
       </c>
       <c r="K99" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L99" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M99" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="N99" t="s">
         <v>33</v>
@@ -10133,16 +10163,16 @@
         <v>38</v>
       </c>
       <c r="Q99">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R99">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y99" t="s">
-        <v>69</v>
+        <v>420</v>
       </c>
       <c r="AA99" t="s">
-        <v>570</v>
+        <v>421</v>
       </c>
       <c r="AB99" t="s">
         <v>39</v>
@@ -10156,13 +10186,13 @@
     </row>
     <row r="100" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>413</v>
+        <v>561</v>
       </c>
       <c r="C100" t="s">
-        <v>414</v>
+        <v>562</v>
       </c>
       <c r="D100" t="s">
-        <v>415</v>
+        <v>563</v>
       </c>
       <c r="E100" t="s">
         <v>33</v>
@@ -10204,10 +10234,13 @@
         <v>10</v>
       </c>
       <c r="Y100" t="s">
-        <v>416</v>
+        <v>564</v>
+      </c>
+      <c r="Z100" t="s">
+        <v>565</v>
       </c>
       <c r="AA100" t="s">
-        <v>417</v>
+        <v>566</v>
       </c>
       <c r="AB100" t="s">
         <v>39</v>
@@ -10221,13 +10254,13 @@
     </row>
     <row r="101" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>422</v>
+        <v>567</v>
       </c>
       <c r="C101" t="s">
-        <v>423</v>
+        <v>568</v>
       </c>
       <c r="D101" t="s">
-        <v>424</v>
+        <v>569</v>
       </c>
       <c r="E101" t="s">
         <v>33</v>
@@ -10245,13 +10278,13 @@
         <v>54</v>
       </c>
       <c r="K101" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="L101" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M101" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="N101" t="s">
         <v>33</v>
@@ -10263,16 +10296,16 @@
         <v>38</v>
       </c>
       <c r="Q101">
-        <v>22.99</v>
+        <v>14.99</v>
       </c>
       <c r="R101">
-        <v>3.83</v>
+        <v>2.5</v>
       </c>
       <c r="Y101" t="s">
-        <v>425</v>
+        <v>69</v>
       </c>
       <c r="AA101" t="s">
-        <v>426</v>
+        <v>570</v>
       </c>
       <c r="AB101" t="s">
         <v>39</v>
@@ -10286,13 +10319,13 @@
     </row>
     <row r="102" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="C102" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="D102" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="E102" t="s">
         <v>33</v>
@@ -10310,13 +10343,13 @@
         <v>54</v>
       </c>
       <c r="K102" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L102" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M102" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N102" t="s">
         <v>33</v>
@@ -10328,19 +10361,16 @@
         <v>38</v>
       </c>
       <c r="Q102">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R102">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y102" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z102" t="s">
-        <v>97</v>
+        <v>416</v>
       </c>
       <c r="AA102" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="AB102" t="s">
         <v>39</v>
@@ -10354,13 +10384,13 @@
     </row>
     <row r="103" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="C103" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="D103" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="E103" t="s">
         <v>33</v>
@@ -10378,13 +10408,13 @@
         <v>54</v>
       </c>
       <c r="K103" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="L103" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="M103" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="N103" t="s">
         <v>33</v>
@@ -10396,19 +10426,16 @@
         <v>38</v>
       </c>
       <c r="Q103">
-        <v>38.49</v>
+        <v>22.99</v>
       </c>
       <c r="R103">
-        <v>6.42</v>
+        <v>3.83</v>
       </c>
       <c r="Y103" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z103" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="AA103" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="AB103" t="s">
         <v>39</v>
@@ -10422,13 +10449,13 @@
     </row>
     <row r="104" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="C104" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="D104" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="E104" t="s">
         <v>33</v>
@@ -10446,13 +10473,13 @@
         <v>54</v>
       </c>
       <c r="K104" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="L104" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="M104" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="N104" t="s">
         <v>33</v>
@@ -10464,16 +10491,19 @@
         <v>38</v>
       </c>
       <c r="Q104">
-        <v>14.99</v>
+        <v>11.99</v>
       </c>
       <c r="R104">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Y104" t="s">
-        <v>438</v>
+        <v>96</v>
+      </c>
+      <c r="Z104" t="s">
+        <v>97</v>
       </c>
       <c r="AA104" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="AB104" t="s">
         <v>39</v>
@@ -10487,13 +10517,13 @@
     </row>
     <row r="105" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="C105" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="D105" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="E105" t="s">
         <v>33</v>
@@ -10511,13 +10541,13 @@
         <v>54</v>
       </c>
       <c r="K105" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="L105" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="M105" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="N105" t="s">
         <v>33</v>
@@ -10529,16 +10559,19 @@
         <v>38</v>
       </c>
       <c r="Q105">
-        <v>37.99</v>
+        <v>38.49</v>
       </c>
       <c r="R105">
-        <v>6.33</v>
+        <v>6.42</v>
       </c>
       <c r="Y105" t="s">
-        <v>443</v>
+        <v>59</v>
+      </c>
+      <c r="Z105" t="s">
+        <v>433</v>
       </c>
       <c r="AA105" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="AB105" t="s">
         <v>39</v>
@@ -10552,13 +10585,13 @@
     </row>
     <row r="106" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="C106" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="D106" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="E106" t="s">
         <v>33</v>
@@ -10576,13 +10609,13 @@
         <v>54</v>
       </c>
       <c r="K106" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="L106" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="M106" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="N106" t="s">
         <v>33</v>
@@ -10594,16 +10627,16 @@
         <v>38</v>
       </c>
       <c r="Q106">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="R106">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="Y106" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="AA106" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="AB106" t="s">
         <v>39</v>
@@ -10617,16 +10650,16 @@
     </row>
     <row r="107" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="C107" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="D107" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="E107" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F107" t="s">
         <v>34</v>
@@ -10641,22 +10674,34 @@
         <v>54</v>
       </c>
       <c r="K107" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L107" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M107" t="s">
-        <v>42</v>
+        <v>50</v>
+      </c>
+      <c r="N107" t="s">
+        <v>33</v>
       </c>
       <c r="O107">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P107" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q107">
+        <v>37.99</v>
+      </c>
+      <c r="R107">
+        <v>6.33</v>
       </c>
       <c r="Y107" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="AA107" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="AB107" t="s">
         <v>39</v>
@@ -10670,13 +10715,13 @@
     </row>
     <row r="108" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>403</v>
+        <v>445</v>
       </c>
       <c r="C108" t="s">
-        <v>404</v>
+        <v>446</v>
       </c>
       <c r="D108" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="E108" t="s">
         <v>33</v>
@@ -10717,17 +10762,11 @@
       <c r="R108">
         <v>10</v>
       </c>
-      <c r="S108">
-        <v>5.99</v>
-      </c>
-      <c r="T108">
-        <v>1</v>
-      </c>
       <c r="Y108" t="s">
-        <v>405</v>
+        <v>448</v>
       </c>
       <c r="AA108" t="s">
-        <v>406</v>
+        <v>449</v>
       </c>
       <c r="AB108" t="s">
         <v>39</v>
@@ -10741,16 +10780,16 @@
     </row>
     <row r="109" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>407</v>
+        <v>450</v>
       </c>
       <c r="C109" t="s">
-        <v>408</v>
+        <v>451</v>
       </c>
       <c r="D109" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="E109" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F109" t="s">
         <v>34</v>
@@ -10765,34 +10804,22 @@
         <v>54</v>
       </c>
       <c r="K109" t="s">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="L109" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="M109" t="s">
-        <v>81</v>
-      </c>
-      <c r="N109" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O109">
-        <v>1</v>
-      </c>
-      <c r="P109" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q109">
-        <v>22.99</v>
-      </c>
-      <c r="R109">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="Y109" t="s">
-        <v>409</v>
+        <v>453</v>
       </c>
       <c r="AA109" t="s">
-        <v>410</v>
+        <v>454</v>
       </c>
       <c r="AB109" t="s">
         <v>39</v>
@@ -10806,13 +10833,13 @@
     </row>
     <row r="110" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C110" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="D110" t="s">
-        <v>411</v>
+        <v>455</v>
       </c>
       <c r="E110" t="s">
         <v>33</v>
@@ -10830,13 +10857,13 @@
         <v>54</v>
       </c>
       <c r="K110" t="s">
-        <v>340</v>
+        <v>40</v>
       </c>
       <c r="L110" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="M110" t="s">
-        <v>143</v>
+        <v>42</v>
       </c>
       <c r="N110" t="s">
         <v>33</v>
@@ -10848,16 +10875,22 @@
         <v>38</v>
       </c>
       <c r="Q110">
-        <v>44.99</v>
+        <v>59.99</v>
       </c>
       <c r="R110">
-        <v>7.5</v>
+        <v>10</v>
+      </c>
+      <c r="S110">
+        <v>5.99</v>
+      </c>
+      <c r="T110">
+        <v>1</v>
       </c>
       <c r="Y110" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="AA110" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="AB110" t="s">
         <v>39</v>
@@ -10871,13 +10904,13 @@
     </row>
     <row r="111" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="C111" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="D111" t="s">
-        <v>412</v>
+        <v>456</v>
       </c>
       <c r="E111" t="s">
         <v>33</v>
@@ -10895,13 +10928,13 @@
         <v>54</v>
       </c>
       <c r="K111" t="s">
-        <v>340</v>
+        <v>79</v>
       </c>
       <c r="L111" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="M111" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
       <c r="N111" t="s">
         <v>33</v>
@@ -10913,19 +10946,16 @@
         <v>38</v>
       </c>
       <c r="Q111">
-        <v>44.99</v>
+        <v>22.99</v>
       </c>
       <c r="R111">
-        <v>7.5</v>
+        <v>3.83</v>
       </c>
       <c r="Y111" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z111" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="AA111" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="AB111" t="s">
         <v>39</v>
@@ -10939,13 +10969,13 @@
     </row>
     <row r="112" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>338</v>
+        <v>399</v>
       </c>
       <c r="C112" t="s">
-        <v>339</v>
+        <v>400</v>
       </c>
       <c r="D112" t="s">
-        <v>662</v>
+        <v>411</v>
       </c>
       <c r="E112" t="s">
         <v>33</v>
@@ -10987,10 +11017,10 @@
         <v>7.5</v>
       </c>
       <c r="Y112" t="s">
-        <v>341</v>
+        <v>401</v>
       </c>
       <c r="AA112" t="s">
-        <v>342</v>
+        <v>402</v>
       </c>
       <c r="AB112" t="s">
         <v>39</v>
@@ -11004,13 +11034,13 @@
     </row>
     <row r="113" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>663</v>
+        <v>394</v>
       </c>
       <c r="C113" t="s">
-        <v>664</v>
+        <v>395</v>
       </c>
       <c r="D113" t="s">
-        <v>665</v>
+        <v>412</v>
       </c>
       <c r="E113" t="s">
         <v>33</v>
@@ -11028,13 +11058,13 @@
         <v>54</v>
       </c>
       <c r="K113" t="s">
-        <v>40</v>
+        <v>340</v>
       </c>
       <c r="L113" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="M113" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="N113" t="s">
         <v>33</v>
@@ -11046,25 +11076,25 @@
         <v>38</v>
       </c>
       <c r="Q113">
-        <v>59.99</v>
+        <v>44.99</v>
       </c>
       <c r="R113">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="Y113" t="s">
-        <v>62</v>
+        <v>396</v>
       </c>
       <c r="Z113" t="s">
-        <v>666</v>
+        <v>397</v>
       </c>
       <c r="AA113" t="s">
-        <v>667</v>
+        <v>398</v>
       </c>
       <c r="AB113" t="s">
         <v>39</v>
       </c>
       <c r="AD113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG113" t="b">
         <v>0</v>
@@ -11072,13 +11102,13 @@
     </row>
     <row r="114" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C114" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D114" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="E114" t="s">
         <v>33</v>
@@ -11096,13 +11126,13 @@
         <v>54</v>
       </c>
       <c r="K114" t="s">
-        <v>203</v>
+        <v>340</v>
       </c>
       <c r="L114" t="s">
-        <v>204</v>
+        <v>142</v>
       </c>
       <c r="M114" t="s">
-        <v>205</v>
+        <v>143</v>
       </c>
       <c r="N114" t="s">
         <v>33</v>
@@ -11114,16 +11144,16 @@
         <v>38</v>
       </c>
       <c r="Q114">
-        <v>69.989999999999995</v>
+        <v>44.99</v>
       </c>
       <c r="R114">
-        <v>11.67</v>
+        <v>7.5</v>
       </c>
       <c r="Y114" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="AA114" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="AB114" t="s">
         <v>39</v>
@@ -11137,13 +11167,13 @@
     </row>
     <row r="115" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>326</v>
+        <v>663</v>
       </c>
       <c r="C115" t="s">
-        <v>327</v>
+        <v>664</v>
       </c>
       <c r="D115" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="E115" t="s">
         <v>33</v>
@@ -11161,40 +11191,43 @@
         <v>54</v>
       </c>
       <c r="K115" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L115" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M115" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N115" t="s">
         <v>33</v>
       </c>
       <c r="O115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P115" t="s">
         <v>38</v>
       </c>
       <c r="Q115">
-        <v>75.98</v>
+        <v>59.99</v>
       </c>
       <c r="R115">
-        <v>12.66</v>
+        <v>10</v>
       </c>
       <c r="Y115" t="s">
-        <v>91</v>
+        <v>62</v>
+      </c>
+      <c r="Z115" t="s">
+        <v>666</v>
       </c>
       <c r="AA115" t="s">
-        <v>328</v>
+        <v>667</v>
       </c>
       <c r="AB115" t="s">
         <v>39</v>
       </c>
       <c r="AD115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG115" t="b">
         <v>0</v>
@@ -11202,13 +11235,13 @@
     </row>
     <row r="116" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="C116" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D116" t="s">
-        <v>345</v>
+        <v>668</v>
       </c>
       <c r="E116" t="s">
         <v>33</v>
@@ -11226,13 +11259,13 @@
         <v>54</v>
       </c>
       <c r="K116" t="s">
-        <v>40</v>
+        <v>203</v>
       </c>
       <c r="L116" t="s">
-        <v>41</v>
+        <v>204</v>
       </c>
       <c r="M116" t="s">
-        <v>42</v>
+        <v>205</v>
       </c>
       <c r="N116" t="s">
         <v>33</v>
@@ -11244,16 +11277,16 @@
         <v>38</v>
       </c>
       <c r="Q116">
-        <v>59.99</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="R116">
-        <v>10</v>
+        <v>11.67</v>
       </c>
       <c r="Y116" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="AA116" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="AB116" t="s">
         <v>39</v>
@@ -11267,13 +11300,13 @@
     </row>
     <row r="117" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="C117" t="s">
-        <v>289</v>
+        <v>327</v>
       </c>
       <c r="D117" t="s">
-        <v>348</v>
+        <v>669</v>
       </c>
       <c r="E117" t="s">
         <v>33</v>
@@ -11288,7 +11321,7 @@
         <v>36</v>
       </c>
       <c r="J117" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K117" t="s">
         <v>48</v>
@@ -11315,10 +11348,10 @@
         <v>12.66</v>
       </c>
       <c r="Y117" t="s">
-        <v>290</v>
+        <v>91</v>
       </c>
       <c r="AA117" t="s">
-        <v>291</v>
+        <v>328</v>
       </c>
       <c r="AB117" t="s">
         <v>39</v>
@@ -11332,13 +11365,13 @@
     </row>
     <row r="118" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="C118" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="D118" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="E118" t="s">
         <v>33</v>
@@ -11356,13 +11389,13 @@
         <v>54</v>
       </c>
       <c r="K118" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L118" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M118" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N118" t="s">
         <v>33</v>
@@ -11374,19 +11407,16 @@
         <v>38</v>
       </c>
       <c r="Q118">
-        <v>37.99</v>
+        <v>59.99</v>
       </c>
       <c r="R118">
-        <v>6.33</v>
+        <v>10</v>
       </c>
       <c r="Y118" t="s">
-        <v>352</v>
-      </c>
-      <c r="Z118" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="AA118" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="AB118" t="s">
         <v>39</v>
@@ -11400,13 +11430,13 @@
     </row>
     <row r="119" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>355</v>
+        <v>288</v>
       </c>
       <c r="C119" t="s">
-        <v>356</v>
+        <v>289</v>
       </c>
       <c r="D119" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="E119" t="s">
         <v>33</v>
@@ -11421,37 +11451,37 @@
         <v>36</v>
       </c>
       <c r="J119" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K119" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L119" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M119" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N119" t="s">
         <v>33</v>
       </c>
       <c r="O119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P119" t="s">
         <v>38</v>
       </c>
       <c r="Q119">
-        <v>11.99</v>
+        <v>75.98</v>
       </c>
       <c r="R119">
-        <v>2</v>
+        <v>12.66</v>
       </c>
       <c r="Y119" t="s">
-        <v>58</v>
+        <v>290</v>
       </c>
       <c r="AA119" t="s">
-        <v>358</v>
+        <v>291</v>
       </c>
       <c r="AB119" t="s">
         <v>39</v>
@@ -11465,13 +11495,13 @@
     </row>
     <row r="120" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="C120" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="D120" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="E120" t="s">
         <v>33</v>
@@ -11501,25 +11531,25 @@
         <v>33</v>
       </c>
       <c r="O120">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P120" t="s">
         <v>38</v>
       </c>
       <c r="Q120">
-        <v>75.98</v>
+        <v>37.99</v>
       </c>
       <c r="R120">
-        <v>12.66</v>
+        <v>6.33</v>
       </c>
       <c r="Y120" t="s">
-        <v>101</v>
+        <v>352</v>
       </c>
       <c r="Z120" t="s">
-        <v>59</v>
+        <v>353</v>
       </c>
       <c r="AA120" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="AB120" t="s">
         <v>39</v>
@@ -11533,13 +11563,13 @@
     </row>
     <row r="121" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="C121" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="D121" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="E121" t="s">
         <v>33</v>
@@ -11557,13 +11587,13 @@
         <v>54</v>
       </c>
       <c r="K121" t="s">
-        <v>260</v>
+        <v>72</v>
       </c>
       <c r="L121" t="s">
-        <v>261</v>
+        <v>73</v>
       </c>
       <c r="M121" t="s">
-        <v>262</v>
+        <v>74</v>
       </c>
       <c r="N121" t="s">
         <v>33</v>
@@ -11575,16 +11605,16 @@
         <v>38</v>
       </c>
       <c r="Q121">
-        <v>24.49</v>
+        <v>11.99</v>
       </c>
       <c r="R121">
-        <v>4.08</v>
+        <v>2</v>
       </c>
       <c r="Y121" t="s">
-        <v>366</v>
+        <v>58</v>
       </c>
       <c r="AA121" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="AB121" t="s">
         <v>39</v>
@@ -11598,13 +11628,13 @@
     </row>
     <row r="122" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>265</v>
+        <v>359</v>
       </c>
       <c r="C122" t="s">
-        <v>266</v>
+        <v>360</v>
       </c>
       <c r="D122" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="E122" t="s">
         <v>33</v>
@@ -11634,22 +11664,25 @@
         <v>33</v>
       </c>
       <c r="O122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P122" t="s">
         <v>38</v>
       </c>
       <c r="Q122">
-        <v>37.99</v>
+        <v>75.98</v>
       </c>
       <c r="R122">
-        <v>6.33</v>
+        <v>12.66</v>
       </c>
       <c r="Y122" t="s">
-        <v>267</v>
+        <v>101</v>
+      </c>
+      <c r="Z122" t="s">
+        <v>59</v>
       </c>
       <c r="AA122" t="s">
-        <v>268</v>
+        <v>362</v>
       </c>
       <c r="AB122" t="s">
         <v>39</v>
@@ -11663,13 +11696,13 @@
     </row>
     <row r="123" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="C123" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="D123" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="E123" t="s">
         <v>33</v>
@@ -11687,13 +11720,13 @@
         <v>54</v>
       </c>
       <c r="K123" t="s">
-        <v>72</v>
+        <v>260</v>
       </c>
       <c r="L123" t="s">
-        <v>73</v>
+        <v>261</v>
       </c>
       <c r="M123" t="s">
-        <v>74</v>
+        <v>262</v>
       </c>
       <c r="N123" t="s">
         <v>33</v>
@@ -11705,22 +11738,16 @@
         <v>38</v>
       </c>
       <c r="Q123">
-        <v>11.99</v>
+        <v>24.49</v>
       </c>
       <c r="R123">
-        <v>2</v>
-      </c>
-      <c r="S123">
-        <v>5.99</v>
-      </c>
-      <c r="T123">
-        <v>1</v>
+        <v>4.08</v>
       </c>
       <c r="Y123" t="s">
-        <v>84</v>
+        <v>366</v>
       </c>
       <c r="AA123" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="AB123" t="s">
         <v>39</v>
@@ -11734,13 +11761,13 @@
     </row>
     <row r="124" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>373</v>
+        <v>265</v>
       </c>
       <c r="C124" t="s">
-        <v>374</v>
+        <v>266</v>
       </c>
       <c r="D124" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="E124" t="s">
         <v>33</v>
@@ -11758,13 +11785,13 @@
         <v>54</v>
       </c>
       <c r="K124" t="s">
-        <v>260</v>
+        <v>48</v>
       </c>
       <c r="L124" t="s">
-        <v>261</v>
+        <v>49</v>
       </c>
       <c r="M124" t="s">
-        <v>262</v>
+        <v>50</v>
       </c>
       <c r="N124" t="s">
         <v>33</v>
@@ -11776,16 +11803,16 @@
         <v>38</v>
       </c>
       <c r="Q124">
-        <v>24.49</v>
+        <v>37.99</v>
       </c>
       <c r="R124">
-        <v>4.08</v>
+        <v>6.33</v>
       </c>
       <c r="Y124" t="s">
-        <v>376</v>
+        <v>267</v>
       </c>
       <c r="AA124" t="s">
-        <v>377</v>
+        <v>268</v>
       </c>
       <c r="AB124" t="s">
         <v>39</v>
@@ -11799,13 +11826,13 @@
     </row>
     <row r="125" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="C125" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="D125" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="E125" t="s">
         <v>33</v>
@@ -11823,13 +11850,13 @@
         <v>54</v>
       </c>
       <c r="K125" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L125" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M125" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N125" t="s">
         <v>33</v>
@@ -11841,16 +11868,22 @@
         <v>38</v>
       </c>
       <c r="Q125">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R125">
-        <v>10</v>
+        <v>2</v>
+      </c>
+      <c r="S125">
+        <v>5.99</v>
+      </c>
+      <c r="T125">
+        <v>1</v>
       </c>
       <c r="Y125" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="AA125" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="AB125" t="s">
         <v>39</v>
@@ -11864,13 +11897,13 @@
     </row>
     <row r="126" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="C126" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="D126" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="E126" t="s">
         <v>33</v>
@@ -11888,13 +11921,13 @@
         <v>54</v>
       </c>
       <c r="K126" t="s">
-        <v>72</v>
+        <v>260</v>
       </c>
       <c r="L126" t="s">
-        <v>73</v>
+        <v>261</v>
       </c>
       <c r="M126" t="s">
-        <v>74</v>
+        <v>262</v>
       </c>
       <c r="N126" t="s">
         <v>33</v>
@@ -11906,16 +11939,16 @@
         <v>38</v>
       </c>
       <c r="Q126">
-        <v>11.99</v>
+        <v>24.49</v>
       </c>
       <c r="R126">
-        <v>2</v>
+        <v>4.08</v>
       </c>
       <c r="Y126" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="AA126" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="AB126" t="s">
         <v>39</v>
@@ -11929,16 +11962,16 @@
     </row>
     <row r="127" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="C127" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="E127" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F127" t="s">
         <v>34</v>
@@ -11953,25 +11986,34 @@
         <v>54</v>
       </c>
       <c r="K127" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L127" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M127" t="s">
-        <v>45</v>
+        <v>42</v>
+      </c>
+      <c r="N127" t="s">
+        <v>33</v>
       </c>
       <c r="O127">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P127" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q127">
+        <v>59.99</v>
+      </c>
+      <c r="R127">
+        <v>10</v>
       </c>
       <c r="Y127" t="s">
-        <v>390</v>
-      </c>
-      <c r="Z127" t="s">
-        <v>391</v>
+        <v>57</v>
       </c>
       <c r="AA127" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="AB127" t="s">
         <v>39</v>
@@ -11985,13 +12027,13 @@
     </row>
     <row r="128" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>323</v>
+        <v>382</v>
       </c>
       <c r="C128" t="s">
-        <v>324</v>
+        <v>383</v>
       </c>
       <c r="D128" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="E128" t="s">
         <v>33</v>
@@ -12009,13 +12051,13 @@
         <v>54</v>
       </c>
       <c r="K128" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="L128" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="M128" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="N128" t="s">
         <v>33</v>
@@ -12027,16 +12069,16 @@
         <v>38</v>
       </c>
       <c r="Q128">
-        <v>14.99</v>
+        <v>11.99</v>
       </c>
       <c r="R128">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Y128" t="s">
-        <v>58</v>
+        <v>385</v>
       </c>
       <c r="AA128" t="s">
-        <v>325</v>
+        <v>386</v>
       </c>
       <c r="AB128" t="s">
         <v>39</v>
@@ -12050,16 +12092,16 @@
     </row>
     <row r="129" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>318</v>
+        <v>387</v>
       </c>
       <c r="C129" t="s">
-        <v>319</v>
+        <v>388</v>
       </c>
       <c r="D129" t="s">
-        <v>320</v>
+        <v>389</v>
       </c>
       <c r="E129" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F129" t="s">
         <v>34</v>
@@ -12074,37 +12116,25 @@
         <v>54</v>
       </c>
       <c r="K129" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="L129" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="M129" t="s">
-        <v>74</v>
-      </c>
-      <c r="N129" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O129">
-        <v>1</v>
-      </c>
-      <c r="P129" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q129">
-        <v>11.99</v>
-      </c>
-      <c r="R129">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y129" t="s">
-        <v>321</v>
+        <v>390</v>
       </c>
       <c r="Z129" t="s">
-        <v>65</v>
+        <v>391</v>
       </c>
       <c r="AA129" t="s">
-        <v>322</v>
+        <v>392</v>
       </c>
       <c r="AB129" t="s">
         <v>39</v>
@@ -12118,13 +12148,13 @@
     </row>
     <row r="130" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C130" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="D130" t="s">
-        <v>331</v>
+        <v>393</v>
       </c>
       <c r="E130" t="s">
         <v>33</v>
@@ -12142,13 +12172,13 @@
         <v>54</v>
       </c>
       <c r="K130" t="s">
-        <v>260</v>
+        <v>95</v>
       </c>
       <c r="L130" t="s">
-        <v>261</v>
+        <v>85</v>
       </c>
       <c r="M130" t="s">
-        <v>262</v>
+        <v>86</v>
       </c>
       <c r="N130" t="s">
         <v>33</v>
@@ -12160,16 +12190,16 @@
         <v>38</v>
       </c>
       <c r="Q130">
-        <v>24.49</v>
+        <v>14.99</v>
       </c>
       <c r="R130">
-        <v>4.08</v>
+        <v>2.5</v>
       </c>
       <c r="Y130" t="s">
-        <v>332</v>
+        <v>58</v>
       </c>
       <c r="AA130" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="AB130" t="s">
         <v>39</v>
@@ -12183,13 +12213,13 @@
     </row>
     <row r="131" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>670</v>
+        <v>318</v>
       </c>
       <c r="C131" t="s">
-        <v>671</v>
+        <v>319</v>
       </c>
       <c r="D131" t="s">
-        <v>672</v>
+        <v>320</v>
       </c>
       <c r="E131" t="s">
         <v>33</v>
@@ -12207,13 +12237,13 @@
         <v>54</v>
       </c>
       <c r="K131" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L131" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M131" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N131" t="s">
         <v>33</v>
@@ -12225,16 +12255,19 @@
         <v>38</v>
       </c>
       <c r="Q131">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R131">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y131" t="s">
-        <v>673</v>
+        <v>321</v>
+      </c>
+      <c r="Z131" t="s">
+        <v>65</v>
       </c>
       <c r="AA131" t="s">
-        <v>674</v>
+        <v>322</v>
       </c>
       <c r="AB131" t="s">
         <v>39</v>
@@ -12248,13 +12281,13 @@
     </row>
     <row r="132" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>675</v>
+        <v>329</v>
       </c>
       <c r="C132" t="s">
-        <v>676</v>
+        <v>330</v>
       </c>
       <c r="D132" t="s">
-        <v>677</v>
+        <v>331</v>
       </c>
       <c r="E132" t="s">
         <v>33</v>
@@ -12272,13 +12305,13 @@
         <v>54</v>
       </c>
       <c r="K132" t="s">
-        <v>48</v>
+        <v>260</v>
       </c>
       <c r="L132" t="s">
-        <v>49</v>
+        <v>261</v>
       </c>
       <c r="M132" t="s">
-        <v>50</v>
+        <v>262</v>
       </c>
       <c r="N132" t="s">
         <v>33</v>
@@ -12290,16 +12323,16 @@
         <v>38</v>
       </c>
       <c r="Q132">
-        <v>37.99</v>
+        <v>24.49</v>
       </c>
       <c r="R132">
-        <v>6.33</v>
+        <v>4.08</v>
       </c>
       <c r="Y132" t="s">
-        <v>678</v>
+        <v>332</v>
       </c>
       <c r="AA132" t="s">
-        <v>679</v>
+        <v>333</v>
       </c>
       <c r="AB132" t="s">
         <v>39</v>
@@ -12313,13 +12346,13 @@
     </row>
     <row r="133" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="C133" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="D133" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="E133" t="s">
         <v>33</v>
@@ -12361,13 +12394,10 @@
         <v>10</v>
       </c>
       <c r="Y133" t="s">
-        <v>683</v>
-      </c>
-      <c r="Z133" t="s">
-        <v>76</v>
+        <v>673</v>
       </c>
       <c r="AA133" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="AB133" t="s">
         <v>39</v>
@@ -12381,13 +12411,13 @@
     </row>
     <row r="134" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="C134" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D134" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
       <c r="E134" t="s">
         <v>33</v>
@@ -12429,10 +12459,10 @@
         <v>6.33</v>
       </c>
       <c r="Y134" t="s">
-        <v>52</v>
+        <v>678</v>
       </c>
       <c r="AA134" t="s">
-        <v>688</v>
+        <v>679</v>
       </c>
       <c r="AB134" t="s">
         <v>39</v>
@@ -12446,16 +12476,16 @@
     </row>
     <row r="135" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
       <c r="C135" t="s">
-        <v>690</v>
+        <v>681</v>
       </c>
       <c r="D135" t="s">
-        <v>691</v>
+        <v>682</v>
       </c>
       <c r="E135" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F135" t="s">
         <v>34</v>
@@ -12467,28 +12497,40 @@
         <v>36</v>
       </c>
       <c r="J135" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K135" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L135" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M135" t="s">
-        <v>50</v>
+        <v>42</v>
+      </c>
+      <c r="N135" t="s">
+        <v>33</v>
       </c>
       <c r="O135">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P135" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q135">
+        <v>59.99</v>
+      </c>
+      <c r="R135">
+        <v>10</v>
       </c>
       <c r="Y135" t="s">
-        <v>692</v>
+        <v>683</v>
       </c>
       <c r="Z135" t="s">
-        <v>693</v>
+        <v>76</v>
       </c>
       <c r="AA135" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="AB135" t="s">
         <v>39</v>
@@ -12502,16 +12544,16 @@
     </row>
     <row r="136" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="C136" t="s">
-        <v>696</v>
+        <v>686</v>
       </c>
       <c r="D136" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="E136" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F136" t="s">
         <v>34</v>
@@ -12523,7 +12565,7 @@
         <v>36</v>
       </c>
       <c r="J136" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K136" t="s">
         <v>48</v>
@@ -12534,17 +12576,26 @@
       <c r="M136" t="s">
         <v>50</v>
       </c>
+      <c r="N136" t="s">
+        <v>33</v>
+      </c>
       <c r="O136">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P136" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q136">
+        <v>37.99</v>
+      </c>
+      <c r="R136">
+        <v>6.33</v>
       </c>
       <c r="Y136" t="s">
-        <v>692</v>
-      </c>
-      <c r="Z136" t="s">
-        <v>693</v>
+        <v>52</v>
       </c>
       <c r="AA136" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="AB136" t="s">
         <v>39</v>
@@ -12558,16 +12609,16 @@
     </row>
     <row r="137" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>300</v>
+        <v>689</v>
       </c>
       <c r="C137" t="s">
-        <v>301</v>
+        <v>690</v>
       </c>
       <c r="D137" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="E137" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F137" t="s">
         <v>34</v>
@@ -12579,37 +12630,28 @@
         <v>36</v>
       </c>
       <c r="J137" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K137" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="L137" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="M137" t="s">
-        <v>86</v>
-      </c>
-      <c r="N137" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="O137">
-        <v>1</v>
-      </c>
-      <c r="P137" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q137">
-        <v>14.99</v>
-      </c>
-      <c r="R137">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y137" t="s">
-        <v>58</v>
+        <v>692</v>
+      </c>
+      <c r="Z137" t="s">
+        <v>693</v>
       </c>
       <c r="AA137" t="s">
-        <v>302</v>
+        <v>694</v>
       </c>
       <c r="AB137" t="s">
         <v>39</v>
@@ -12623,13 +12665,13 @@
     </row>
     <row r="138" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="C138" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="D138" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="E138" t="s">
         <v>53</v>
@@ -12644,7 +12686,7 @@
         <v>36</v>
       </c>
       <c r="J138" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K138" t="s">
         <v>48</v>
@@ -12679,13 +12721,13 @@
     </row>
     <row r="139" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C139" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D139" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="E139" t="s">
         <v>33</v>
@@ -12703,13 +12745,13 @@
         <v>54</v>
       </c>
       <c r="K139" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="L139" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="M139" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="N139" t="s">
         <v>33</v>
@@ -12721,16 +12763,16 @@
         <v>38</v>
       </c>
       <c r="Q139">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="R139">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="Y139" t="s">
-        <v>305</v>
+        <v>58</v>
       </c>
       <c r="AA139" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="AB139" t="s">
         <v>39</v>
@@ -12744,16 +12786,16 @@
     </row>
     <row r="140" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>292</v>
+        <v>699</v>
       </c>
       <c r="C140" t="s">
-        <v>293</v>
+        <v>700</v>
       </c>
       <c r="D140" t="s">
-        <v>294</v>
+        <v>701</v>
       </c>
       <c r="E140" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F140" t="s">
         <v>34</v>
@@ -12765,40 +12807,28 @@
         <v>36</v>
       </c>
       <c r="J140" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K140" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L140" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M140" t="s">
-        <v>42</v>
-      </c>
-      <c r="N140" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="O140">
-        <v>1</v>
-      </c>
-      <c r="P140" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q140">
-        <v>59.99</v>
-      </c>
-      <c r="R140">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y140" t="s">
-        <v>77</v>
+        <v>692</v>
       </c>
       <c r="Z140" t="s">
-        <v>92</v>
+        <v>693</v>
       </c>
       <c r="AA140" t="s">
-        <v>295</v>
+        <v>694</v>
       </c>
       <c r="AB140" t="s">
         <v>39</v>
@@ -12812,13 +12842,13 @@
     </row>
     <row r="141" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C141" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="D141" t="s">
-        <v>298</v>
+        <v>702</v>
       </c>
       <c r="E141" t="s">
         <v>33</v>
@@ -12833,7 +12863,7 @@
         <v>36</v>
       </c>
       <c r="J141" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K141" t="s">
         <v>40</v>
@@ -12860,13 +12890,10 @@
         <v>10</v>
       </c>
       <c r="Y141" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z141" t="s">
-        <v>51</v>
+        <v>305</v>
       </c>
       <c r="AA141" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="AB141" t="s">
         <v>39</v>
@@ -12880,13 +12907,13 @@
     </row>
     <row r="142" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="C142" t="s">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="D142" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="E142" t="s">
         <v>33</v>
@@ -12904,13 +12931,13 @@
         <v>37</v>
       </c>
       <c r="K142" t="s">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="L142" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="M142" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="N142" t="s">
         <v>33</v>
@@ -12922,16 +12949,19 @@
         <v>38</v>
       </c>
       <c r="Q142">
-        <v>20.49</v>
+        <v>59.99</v>
       </c>
       <c r="R142">
-        <v>3.42</v>
+        <v>10</v>
       </c>
       <c r="Y142" t="s">
-        <v>310</v>
+        <v>77</v>
+      </c>
+      <c r="Z142" t="s">
+        <v>92</v>
       </c>
       <c r="AA142" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="AB142" t="s">
         <v>39</v>
@@ -12945,13 +12975,13 @@
     </row>
     <row r="143" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>312</v>
+        <v>296</v>
       </c>
       <c r="C143" t="s">
-        <v>313</v>
+        <v>297</v>
       </c>
       <c r="D143" t="s">
-        <v>314</v>
+        <v>298</v>
       </c>
       <c r="E143" t="s">
         <v>33</v>
@@ -12993,13 +13023,13 @@
         <v>10</v>
       </c>
       <c r="Y143" t="s">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="Z143" t="s">
-        <v>315</v>
+        <v>51</v>
       </c>
       <c r="AA143" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
       <c r="AB143" t="s">
         <v>39</v>
@@ -13013,13 +13043,13 @@
     </row>
     <row r="144" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>253</v>
+        <v>307</v>
       </c>
       <c r="C144" t="s">
-        <v>254</v>
+        <v>308</v>
       </c>
       <c r="D144" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="E144" t="s">
         <v>33</v>
@@ -13034,16 +13064,16 @@
         <v>36</v>
       </c>
       <c r="J144" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K144" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="L144" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="M144" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="N144" t="s">
         <v>33</v>
@@ -13055,19 +13085,16 @@
         <v>38</v>
       </c>
       <c r="Q144">
-        <v>59.99</v>
+        <v>20.49</v>
       </c>
       <c r="R144">
-        <v>10</v>
+        <v>3.42</v>
       </c>
       <c r="Y144" t="s">
-        <v>255</v>
-      </c>
-      <c r="Z144" t="s">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="AA144" t="s">
-        <v>256</v>
+        <v>311</v>
       </c>
       <c r="AB144" t="s">
         <v>39</v>
@@ -13081,13 +13108,13 @@
     </row>
     <row r="145" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>257</v>
+        <v>312</v>
       </c>
       <c r="C145" t="s">
-        <v>258</v>
+        <v>313</v>
       </c>
       <c r="D145" t="s">
-        <v>259</v>
+        <v>314</v>
       </c>
       <c r="E145" t="s">
         <v>33</v>
@@ -13102,16 +13129,16 @@
         <v>36</v>
       </c>
       <c r="J145" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K145" t="s">
-        <v>260</v>
+        <v>40</v>
       </c>
       <c r="L145" t="s">
-        <v>261</v>
+        <v>41</v>
       </c>
       <c r="M145" t="s">
-        <v>262</v>
+        <v>42</v>
       </c>
       <c r="N145" t="s">
         <v>33</v>
@@ -13123,19 +13150,19 @@
         <v>38</v>
       </c>
       <c r="Q145">
-        <v>24.49</v>
+        <v>59.99</v>
       </c>
       <c r="R145">
-        <v>4.08</v>
+        <v>10</v>
       </c>
       <c r="Y145" t="s">
-        <v>263</v>
+        <v>100</v>
       </c>
       <c r="Z145" t="s">
-        <v>64</v>
+        <v>315</v>
       </c>
       <c r="AA145" t="s">
-        <v>264</v>
+        <v>316</v>
       </c>
       <c r="AB145" t="s">
         <v>39</v>
@@ -13149,13 +13176,13 @@
     </row>
     <row r="146" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>269</v>
+        <v>253</v>
       </c>
       <c r="C146" t="s">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="D146" t="s">
-        <v>271</v>
+        <v>317</v>
       </c>
       <c r="E146" t="s">
         <v>33</v>
@@ -13197,10 +13224,13 @@
         <v>10</v>
       </c>
       <c r="Y146" t="s">
-        <v>272</v>
+        <v>255</v>
+      </c>
+      <c r="Z146" t="s">
+        <v>102</v>
       </c>
       <c r="AA146" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="AB146" t="s">
         <v>39</v>
@@ -13214,13 +13244,13 @@
     </row>
     <row r="147" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>149</v>
+        <v>257</v>
       </c>
       <c r="C147" t="s">
-        <v>150</v>
+        <v>258</v>
       </c>
       <c r="D147" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="E147" t="s">
         <v>33</v>
@@ -13238,13 +13268,13 @@
         <v>54</v>
       </c>
       <c r="K147" t="s">
-        <v>40</v>
+        <v>260</v>
       </c>
       <c r="L147" t="s">
-        <v>41</v>
+        <v>261</v>
       </c>
       <c r="M147" t="s">
-        <v>42</v>
+        <v>262</v>
       </c>
       <c r="N147" t="s">
         <v>33</v>
@@ -13256,16 +13286,19 @@
         <v>38</v>
       </c>
       <c r="Q147">
-        <v>59.99</v>
+        <v>24.49</v>
       </c>
       <c r="R147">
-        <v>10</v>
+        <v>4.08</v>
       </c>
       <c r="Y147" t="s">
-        <v>63</v>
+        <v>263</v>
+      </c>
+      <c r="Z147" t="s">
+        <v>64</v>
       </c>
       <c r="AA147" t="s">
-        <v>151</v>
+        <v>264</v>
       </c>
       <c r="AB147" t="s">
         <v>39</v>
@@ -13279,13 +13312,13 @@
     </row>
     <row r="148" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="C148" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="D148" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="E148" t="s">
         <v>33</v>
@@ -13315,25 +13348,22 @@
         <v>33</v>
       </c>
       <c r="O148">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P148" t="s">
         <v>38</v>
       </c>
       <c r="Q148">
-        <v>119.98</v>
+        <v>59.99</v>
       </c>
       <c r="R148">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Y148" t="s">
-        <v>278</v>
-      </c>
-      <c r="Z148" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="AA148" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="AB148" t="s">
         <v>39</v>
@@ -13347,13 +13377,13 @@
     </row>
     <row r="149" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>281</v>
+        <v>149</v>
       </c>
       <c r="C149" t="s">
-        <v>282</v>
+        <v>150</v>
       </c>
       <c r="D149" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="E149" t="s">
         <v>33</v>
@@ -13368,16 +13398,16 @@
         <v>36</v>
       </c>
       <c r="J149" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K149" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L149" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M149" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N149" t="s">
         <v>33</v>
@@ -13389,16 +13419,16 @@
         <v>38</v>
       </c>
       <c r="Q149">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R149">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y149" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="AA149" t="s">
-        <v>284</v>
+        <v>151</v>
       </c>
       <c r="AB149" t="s">
         <v>39</v>
@@ -13412,16 +13442,16 @@
     </row>
     <row r="150" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>238</v>
+        <v>275</v>
       </c>
       <c r="C150" t="s">
-        <v>239</v>
+        <v>276</v>
       </c>
       <c r="D150" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="E150" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F150" t="s">
         <v>34</v>
@@ -13444,14 +13474,29 @@
       <c r="M150" t="s">
         <v>42</v>
       </c>
+      <c r="N150" t="s">
+        <v>33</v>
+      </c>
       <c r="O150">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="P150" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q150">
+        <v>119.98</v>
+      </c>
+      <c r="R150">
+        <v>20</v>
       </c>
       <c r="Y150" t="s">
-        <v>240</v>
+        <v>278</v>
+      </c>
+      <c r="Z150" t="s">
+        <v>279</v>
       </c>
       <c r="AA150" t="s">
-        <v>241</v>
+        <v>280</v>
       </c>
       <c r="AB150" t="s">
         <v>39</v>
@@ -13465,13 +13510,13 @@
     </row>
     <row r="151" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>224</v>
+        <v>281</v>
       </c>
       <c r="C151" t="s">
-        <v>225</v>
+        <v>282</v>
       </c>
       <c r="D151" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="E151" t="s">
         <v>33</v>
@@ -13486,16 +13531,16 @@
         <v>36</v>
       </c>
       <c r="J151" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K151" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L151" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M151" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N151" t="s">
         <v>33</v>
@@ -13507,16 +13552,16 @@
         <v>38</v>
       </c>
       <c r="Q151">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R151">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y151" t="s">
-        <v>226</v>
+        <v>75</v>
       </c>
       <c r="AA151" t="s">
-        <v>227</v>
+        <v>284</v>
       </c>
       <c r="AB151" t="s">
         <v>39</v>
@@ -13530,16 +13575,16 @@
     </row>
     <row r="152" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>213</v>
+        <v>238</v>
       </c>
       <c r="C152" t="s">
-        <v>214</v>
+        <v>239</v>
       </c>
       <c r="D152" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E152" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F152" t="s">
         <v>34</v>
@@ -13562,29 +13607,14 @@
       <c r="M152" t="s">
         <v>42</v>
       </c>
-      <c r="N152" t="s">
-        <v>33</v>
-      </c>
       <c r="O152">
-        <v>1</v>
-      </c>
-      <c r="P152" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q152">
-        <v>59.99</v>
-      </c>
-      <c r="R152">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y152" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z152" t="s">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="AA152" t="s">
-        <v>217</v>
+        <v>241</v>
       </c>
       <c r="AB152" t="s">
         <v>39</v>
@@ -13598,13 +13628,13 @@
     </row>
     <row r="153" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C153" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="D153" t="s">
-        <v>220</v>
+        <v>286</v>
       </c>
       <c r="E153" t="s">
         <v>33</v>
@@ -13622,13 +13652,13 @@
         <v>54</v>
       </c>
       <c r="K153" t="s">
-        <v>203</v>
+        <v>40</v>
       </c>
       <c r="L153" t="s">
-        <v>204</v>
+        <v>41</v>
       </c>
       <c r="M153" t="s">
-        <v>205</v>
+        <v>42</v>
       </c>
       <c r="N153" t="s">
         <v>33</v>
@@ -13640,19 +13670,16 @@
         <v>38</v>
       </c>
       <c r="Q153">
-        <v>69.989999999999995</v>
+        <v>59.99</v>
       </c>
       <c r="R153">
-        <v>11.67</v>
+        <v>10</v>
       </c>
       <c r="Y153" t="s">
-        <v>221</v>
-      </c>
-      <c r="Z153" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AA153" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="AB153" t="s">
         <v>39</v>
@@ -13666,13 +13693,13 @@
     </row>
     <row r="154" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="C154" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="D154" t="s">
-        <v>230</v>
+        <v>287</v>
       </c>
       <c r="E154" t="s">
         <v>33</v>
@@ -13714,10 +13741,13 @@
         <v>10</v>
       </c>
       <c r="Y154" t="s">
-        <v>231</v>
+        <v>215</v>
+      </c>
+      <c r="Z154" t="s">
+        <v>216</v>
       </c>
       <c r="AA154" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="AB154" t="s">
         <v>39</v>
@@ -13731,13 +13761,13 @@
     </row>
     <row r="155" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="C155" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="D155" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="E155" t="s">
         <v>33</v>
@@ -13755,13 +13785,13 @@
         <v>54</v>
       </c>
       <c r="K155" t="s">
-        <v>95</v>
+        <v>203</v>
       </c>
       <c r="L155" t="s">
-        <v>85</v>
+        <v>204</v>
       </c>
       <c r="M155" t="s">
-        <v>86</v>
+        <v>205</v>
       </c>
       <c r="N155" t="s">
         <v>33</v>
@@ -13773,16 +13803,19 @@
         <v>38</v>
       </c>
       <c r="Q155">
-        <v>14.99</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="R155">
-        <v>2.5</v>
+        <v>11.67</v>
       </c>
       <c r="Y155" t="s">
-        <v>236</v>
+        <v>221</v>
+      </c>
+      <c r="Z155" t="s">
+        <v>222</v>
       </c>
       <c r="AA155" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="AB155" t="s">
         <v>39</v>
@@ -13796,16 +13829,16 @@
     </row>
     <row r="156" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="C156" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="D156" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="E156" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F156" t="s">
         <v>34</v>
@@ -13828,14 +13861,26 @@
       <c r="M156" t="s">
         <v>42</v>
       </c>
+      <c r="N156" t="s">
+        <v>33</v>
+      </c>
       <c r="O156">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P156" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q156">
+        <v>59.99</v>
+      </c>
+      <c r="R156">
+        <v>10</v>
       </c>
       <c r="Y156" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="AA156" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="AB156" t="s">
         <v>39</v>
@@ -13849,13 +13894,13 @@
     </row>
     <row r="157" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="C157" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D157" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="E157" t="s">
         <v>33</v>
@@ -13870,16 +13915,16 @@
         <v>36</v>
       </c>
       <c r="J157" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K157" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="L157" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="M157" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="N157" t="s">
         <v>33</v>
@@ -13891,16 +13936,16 @@
         <v>38</v>
       </c>
       <c r="Q157">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="R157">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="Y157" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="AA157" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="AB157" t="s">
         <v>39</v>
@@ -13914,16 +13959,16 @@
     </row>
     <row r="158" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>188</v>
+        <v>242</v>
       </c>
       <c r="C158" t="s">
-        <v>189</v>
+        <v>243</v>
       </c>
       <c r="D158" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="E158" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F158" t="s">
         <v>34</v>
@@ -13935,37 +13980,25 @@
         <v>36</v>
       </c>
       <c r="J158" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K158" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L158" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M158" t="s">
-        <v>50</v>
-      </c>
-      <c r="N158" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O158">
-        <v>1</v>
-      </c>
-      <c r="P158" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q158">
-        <v>37.99</v>
-      </c>
-      <c r="R158">
-        <v>6.33</v>
+        <v>0</v>
       </c>
       <c r="Y158" t="s">
-        <v>52</v>
+        <v>240</v>
       </c>
       <c r="AA158" t="s">
-        <v>190</v>
+        <v>241</v>
       </c>
       <c r="AB158" t="s">
         <v>39</v>
@@ -13979,13 +14012,13 @@
     </row>
     <row r="159" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>191</v>
+        <v>245</v>
       </c>
       <c r="C159" t="s">
-        <v>192</v>
+        <v>246</v>
       </c>
       <c r="D159" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="E159" t="s">
         <v>33</v>
@@ -14000,7 +14033,7 @@
         <v>36</v>
       </c>
       <c r="J159" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K159" t="s">
         <v>40</v>
@@ -14027,10 +14060,10 @@
         <v>10</v>
       </c>
       <c r="Y159" t="s">
-        <v>193</v>
+        <v>248</v>
       </c>
       <c r="AA159" t="s">
-        <v>194</v>
+        <v>249</v>
       </c>
       <c r="AB159" t="s">
         <v>39</v>
@@ -14044,13 +14077,13 @@
     </row>
     <row r="160" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="C160" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="D160" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E160" t="s">
         <v>33</v>
@@ -14065,16 +14098,16 @@
         <v>36</v>
       </c>
       <c r="J160" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K160" t="s">
-        <v>203</v>
+        <v>48</v>
       </c>
       <c r="L160" t="s">
-        <v>204</v>
+        <v>49</v>
       </c>
       <c r="M160" t="s">
-        <v>205</v>
+        <v>50</v>
       </c>
       <c r="N160" t="s">
         <v>33</v>
@@ -14086,19 +14119,16 @@
         <v>38</v>
       </c>
       <c r="Q160">
-        <v>69.989999999999995</v>
+        <v>37.99</v>
       </c>
       <c r="R160">
-        <v>11.67</v>
+        <v>6.33</v>
       </c>
       <c r="Y160" t="s">
-        <v>206</v>
-      </c>
-      <c r="Z160" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="AA160" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="AB160" t="s">
         <v>39</v>
@@ -14112,13 +14142,13 @@
     </row>
     <row r="161" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C161" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D161" t="s">
-        <v>197</v>
+        <v>251</v>
       </c>
       <c r="E161" t="s">
         <v>33</v>
@@ -14133,7 +14163,7 @@
         <v>36</v>
       </c>
       <c r="J161" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K161" t="s">
         <v>40</v>
@@ -14160,13 +14190,10 @@
         <v>10</v>
       </c>
       <c r="Y161" t="s">
-        <v>198</v>
-      </c>
-      <c r="Z161" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="AA161" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="AB161" t="s">
         <v>39</v>
@@ -14180,13 +14207,13 @@
     </row>
     <row r="162" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="C162" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="D162" t="s">
-        <v>210</v>
+        <v>252</v>
       </c>
       <c r="E162" t="s">
         <v>33</v>
@@ -14201,16 +14228,16 @@
         <v>36</v>
       </c>
       <c r="J162" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K162" t="s">
-        <v>40</v>
+        <v>203</v>
       </c>
       <c r="L162" t="s">
-        <v>41</v>
+        <v>204</v>
       </c>
       <c r="M162" t="s">
-        <v>42</v>
+        <v>205</v>
       </c>
       <c r="N162" t="s">
         <v>33</v>
@@ -14222,16 +14249,19 @@
         <v>38</v>
       </c>
       <c r="Q162">
-        <v>59.99</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="R162">
-        <v>10</v>
+        <v>11.67</v>
       </c>
       <c r="Y162" t="s">
-        <v>211</v>
+        <v>206</v>
+      </c>
+      <c r="Z162" t="s">
+        <v>60</v>
       </c>
       <c r="AA162" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="AB162" t="s">
         <v>39</v>
@@ -14245,13 +14275,13 @@
     </row>
     <row r="163" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>152</v>
+        <v>195</v>
       </c>
       <c r="C163" t="s">
-        <v>153</v>
+        <v>196</v>
       </c>
       <c r="D163" t="s">
-        <v>154</v>
+        <v>197</v>
       </c>
       <c r="E163" t="s">
         <v>33</v>
@@ -14266,16 +14296,16 @@
         <v>36</v>
       </c>
       <c r="J163" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K163" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="L163" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="M163" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="N163" t="s">
         <v>33</v>
@@ -14287,16 +14317,19 @@
         <v>38</v>
       </c>
       <c r="Q163">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="R163">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="Y163" t="s">
-        <v>155</v>
+        <v>198</v>
+      </c>
+      <c r="Z163" t="s">
+        <v>199</v>
       </c>
       <c r="AA163" t="s">
-        <v>156</v>
+        <v>200</v>
       </c>
       <c r="AB163" t="s">
         <v>39</v>
@@ -14310,13 +14343,13 @@
     </row>
     <row r="164" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>157</v>
+        <v>208</v>
       </c>
       <c r="C164" t="s">
-        <v>158</v>
+        <v>209</v>
       </c>
       <c r="D164" t="s">
-        <v>159</v>
+        <v>210</v>
       </c>
       <c r="E164" t="s">
         <v>33</v>
@@ -14331,16 +14364,16 @@
         <v>36</v>
       </c>
       <c r="J164" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K164" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L164" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M164" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="N164" t="s">
         <v>33</v>
@@ -14352,16 +14385,16 @@
         <v>38</v>
       </c>
       <c r="Q164">
-        <v>11.99</v>
+        <v>59.99</v>
       </c>
       <c r="R164">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y164" t="s">
-        <v>68</v>
+        <v>211</v>
       </c>
       <c r="AA164" t="s">
-        <v>160</v>
+        <v>212</v>
       </c>
       <c r="AB164" t="s">
         <v>39</v>
@@ -14375,16 +14408,16 @@
     </row>
     <row r="165" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="C165" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D165" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="E165" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F165" t="s">
         <v>34</v>
@@ -14399,22 +14432,34 @@
         <v>54</v>
       </c>
       <c r="K165" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="L165" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="M165" t="s">
-        <v>42</v>
+        <v>86</v>
+      </c>
+      <c r="N165" t="s">
+        <v>33</v>
       </c>
       <c r="O165">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P165" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q165">
+        <v>14.99</v>
+      </c>
+      <c r="R165">
+        <v>2.5</v>
       </c>
       <c r="Y165" t="s">
-        <v>63</v>
+        <v>155</v>
       </c>
       <c r="AA165" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="AB165" t="s">
         <v>39</v>
@@ -14428,13 +14473,13 @@
     </row>
     <row r="166" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C166" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D166" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E166" t="s">
         <v>33</v>
@@ -14452,13 +14497,13 @@
         <v>54</v>
       </c>
       <c r="K166" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L166" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M166" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="N166" t="s">
         <v>33</v>
@@ -14470,16 +14515,16 @@
         <v>38</v>
       </c>
       <c r="Q166">
-        <v>37.99</v>
+        <v>11.99</v>
       </c>
       <c r="R166">
-        <v>6.33</v>
+        <v>2</v>
       </c>
       <c r="Y166" t="s">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="AA166" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="AB166" t="s">
         <v>39</v>
@@ -14493,16 +14538,16 @@
     </row>
     <row r="167" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C167" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="D167" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="E167" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F167" t="s">
         <v>34</v>
@@ -14517,34 +14562,22 @@
         <v>54</v>
       </c>
       <c r="K167" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L167" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M167" t="s">
-        <v>74</v>
-      </c>
-      <c r="N167" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O167">
-        <v>1</v>
-      </c>
-      <c r="P167" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q167">
-        <v>11.99</v>
-      </c>
-      <c r="R167">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y167" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="AA167" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="AB167" t="s">
         <v>39</v>
@@ -14558,13 +14591,13 @@
     </row>
     <row r="168" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C168" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="D168" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="E168" t="s">
         <v>33</v>
@@ -14582,13 +14615,13 @@
         <v>54</v>
       </c>
       <c r="K168" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="L168" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="M168" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="N168" t="s">
         <v>33</v>
@@ -14600,16 +14633,16 @@
         <v>38</v>
       </c>
       <c r="Q168">
-        <v>14.99</v>
+        <v>37.99</v>
       </c>
       <c r="R168">
-        <v>2.5</v>
+        <v>6.33</v>
       </c>
       <c r="Y168" t="s">
-        <v>175</v>
+        <v>100</v>
       </c>
       <c r="AA168" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="AB168" t="s">
         <v>39</v>
@@ -14623,13 +14656,13 @@
     </row>
     <row r="169" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="C169" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="D169" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="E169" t="s">
         <v>33</v>
@@ -14647,13 +14680,13 @@
         <v>54</v>
       </c>
       <c r="K169" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L169" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M169" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="N169" t="s">
         <v>33</v>
@@ -14665,19 +14698,16 @@
         <v>38</v>
       </c>
       <c r="Q169">
-        <v>37.99</v>
+        <v>11.99</v>
       </c>
       <c r="R169">
-        <v>6.33</v>
+        <v>2</v>
       </c>
       <c r="Y169" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z169" t="s">
-        <v>181</v>
+        <v>66</v>
       </c>
       <c r="AA169" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="AB169" t="s">
         <v>39</v>
@@ -14691,13 +14721,13 @@
     </row>
     <row r="170" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="C170" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="D170" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="E170" t="s">
         <v>33</v>
@@ -14715,37 +14745,34 @@
         <v>54</v>
       </c>
       <c r="K170" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="L170" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="M170" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="N170" t="s">
         <v>33</v>
       </c>
       <c r="O170">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P170" t="s">
         <v>38</v>
       </c>
       <c r="Q170">
-        <v>75.98</v>
+        <v>14.99</v>
       </c>
       <c r="R170">
-        <v>12.66</v>
+        <v>2.5</v>
       </c>
       <c r="Y170" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z170" t="s">
-        <v>47</v>
+        <v>175</v>
       </c>
       <c r="AA170" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="AB170" t="s">
         <v>39</v>
@@ -14759,13 +14786,13 @@
     </row>
     <row r="171" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>133</v>
+        <v>177</v>
       </c>
       <c r="C171" t="s">
-        <v>134</v>
+        <v>178</v>
       </c>
       <c r="D171" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="E171" t="s">
         <v>33</v>
@@ -14783,13 +14810,13 @@
         <v>54</v>
       </c>
       <c r="K171" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L171" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M171" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N171" t="s">
         <v>33</v>
@@ -14801,16 +14828,19 @@
         <v>38</v>
       </c>
       <c r="Q171">
-        <v>11.99</v>
+        <v>37.99</v>
       </c>
       <c r="R171">
-        <v>2</v>
+        <v>6.33</v>
       </c>
       <c r="Y171" t="s">
-        <v>69</v>
+        <v>180</v>
+      </c>
+      <c r="Z171" t="s">
+        <v>181</v>
       </c>
       <c r="AA171" t="s">
-        <v>135</v>
+        <v>182</v>
       </c>
       <c r="AB171" t="s">
         <v>39</v>
@@ -14824,13 +14854,13 @@
     </row>
     <row r="172" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>117</v>
+        <v>183</v>
       </c>
       <c r="C172" t="s">
-        <v>118</v>
+        <v>184</v>
       </c>
       <c r="D172" t="s">
-        <v>119</v>
+        <v>179</v>
       </c>
       <c r="E172" t="s">
         <v>33</v>
@@ -14848,37 +14878,37 @@
         <v>54</v>
       </c>
       <c r="K172" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="L172" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="M172" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="N172" t="s">
         <v>33</v>
       </c>
       <c r="O172">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P172" t="s">
         <v>38</v>
       </c>
       <c r="Q172">
-        <v>14.99</v>
+        <v>75.98</v>
       </c>
       <c r="R172">
-        <v>2.5</v>
+        <v>12.66</v>
       </c>
       <c r="Y172" t="s">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="Z172" t="s">
-        <v>121</v>
+        <v>47</v>
       </c>
       <c r="AA172" t="s">
-        <v>122</v>
+        <v>185</v>
       </c>
       <c r="AB172" t="s">
         <v>39</v>
@@ -14892,13 +14922,13 @@
     </row>
     <row r="173" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="C173" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="D173" t="s">
-        <v>125</v>
+        <v>186</v>
       </c>
       <c r="E173" t="s">
         <v>33</v>
@@ -14916,13 +14946,13 @@
         <v>54</v>
       </c>
       <c r="K173" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L173" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M173" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N173" t="s">
         <v>33</v>
@@ -14934,19 +14964,16 @@
         <v>38</v>
       </c>
       <c r="Q173">
-        <v>59.99</v>
+        <v>11.99</v>
       </c>
       <c r="R173">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y173" t="s">
-        <v>126</v>
-      </c>
-      <c r="Z173" t="s">
-        <v>127</v>
+        <v>69</v>
       </c>
       <c r="AA173" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="AB173" t="s">
         <v>39</v>
@@ -14960,13 +14987,13 @@
     </row>
     <row r="174" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="C174" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="D174" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="E174" t="s">
         <v>33</v>
@@ -14984,13 +15011,13 @@
         <v>54</v>
       </c>
       <c r="K174" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="L174" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="M174" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="N174" t="s">
         <v>33</v>
@@ -15002,16 +15029,19 @@
         <v>38</v>
       </c>
       <c r="Q174">
-        <v>38.49</v>
+        <v>14.99</v>
       </c>
       <c r="R174">
-        <v>6.42</v>
+        <v>2.5</v>
       </c>
       <c r="Y174" t="s">
-        <v>78</v>
+        <v>120</v>
+      </c>
+      <c r="Z174" t="s">
+        <v>121</v>
       </c>
       <c r="AA174" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="AB174" t="s">
         <v>39</v>
@@ -15025,16 +15055,16 @@
     </row>
     <row r="175" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="C175" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="D175" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E175" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F175" t="s">
         <v>34</v>
@@ -15049,22 +15079,37 @@
         <v>54</v>
       </c>
       <c r="K175" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="L175" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="M175" t="s">
-        <v>83</v>
+        <v>42</v>
+      </c>
+      <c r="N175" t="s">
+        <v>33</v>
       </c>
       <c r="O175">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P175" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q175">
+        <v>59.99</v>
+      </c>
+      <c r="R175">
+        <v>10</v>
       </c>
       <c r="Y175" t="s">
-        <v>103</v>
+        <v>126</v>
+      </c>
+      <c r="Z175" t="s">
+        <v>127</v>
       </c>
       <c r="AA175" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="AB175" t="s">
         <v>39</v>
@@ -15078,13 +15123,13 @@
     </row>
     <row r="176" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="C176" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="D176" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="E176" t="s">
         <v>33</v>
@@ -15102,13 +15147,13 @@
         <v>54</v>
       </c>
       <c r="K176" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="L176" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="M176" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="N176" t="s">
         <v>33</v>
@@ -15120,19 +15165,16 @@
         <v>38</v>
       </c>
       <c r="Q176">
-        <v>37.99</v>
+        <v>38.49</v>
       </c>
       <c r="R176">
-        <v>6.33</v>
+        <v>6.42</v>
       </c>
       <c r="Y176" t="s">
-        <v>109</v>
-      </c>
-      <c r="Z176" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="AA176" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="AB176" t="s">
         <v>39</v>
@@ -15146,16 +15188,16 @@
     </row>
     <row r="177" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C177" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D177" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="E177" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F177" t="s">
         <v>34</v>
@@ -15167,40 +15209,25 @@
         <v>36</v>
       </c>
       <c r="J177" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K177" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L177" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="M177" t="s">
-        <v>42</v>
-      </c>
-      <c r="N177" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="O177">
-        <v>1</v>
-      </c>
-      <c r="P177" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q177">
-        <v>59.99</v>
-      </c>
-      <c r="R177">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y177" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z177" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="AA177" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="AB177" t="s">
         <v>39</v>
@@ -15214,66 +15241,202 @@
     </row>
     <row r="178" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
+        <v>107</v>
+      </c>
+      <c r="C178" t="s">
+        <v>108</v>
+      </c>
+      <c r="D178" t="s">
+        <v>137</v>
+      </c>
+      <c r="E178" t="s">
+        <v>33</v>
+      </c>
+      <c r="F178" t="s">
+        <v>34</v>
+      </c>
+      <c r="G178" t="s">
+        <v>35</v>
+      </c>
+      <c r="H178" t="s">
+        <v>36</v>
+      </c>
+      <c r="J178" t="s">
+        <v>54</v>
+      </c>
+      <c r="K178" t="s">
+        <v>48</v>
+      </c>
+      <c r="L178" t="s">
+        <v>49</v>
+      </c>
+      <c r="M178" t="s">
+        <v>50</v>
+      </c>
+      <c r="N178" t="s">
+        <v>33</v>
+      </c>
+      <c r="O178">
+        <v>1</v>
+      </c>
+      <c r="P178" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q178">
+        <v>37.99</v>
+      </c>
+      <c r="R178">
+        <v>6.33</v>
+      </c>
+      <c r="Y178" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z178" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA178" t="s">
+        <v>111</v>
+      </c>
+      <c r="AB178" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG178" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>112</v>
+      </c>
+      <c r="C179" t="s">
+        <v>113</v>
+      </c>
+      <c r="D179" t="s">
+        <v>114</v>
+      </c>
+      <c r="E179" t="s">
+        <v>33</v>
+      </c>
+      <c r="F179" t="s">
+        <v>34</v>
+      </c>
+      <c r="G179" t="s">
+        <v>35</v>
+      </c>
+      <c r="H179" t="s">
+        <v>36</v>
+      </c>
+      <c r="J179" t="s">
+        <v>37</v>
+      </c>
+      <c r="K179" t="s">
+        <v>40</v>
+      </c>
+      <c r="L179" t="s">
+        <v>41</v>
+      </c>
+      <c r="M179" t="s">
+        <v>42</v>
+      </c>
+      <c r="N179" t="s">
+        <v>33</v>
+      </c>
+      <c r="O179">
+        <v>1</v>
+      </c>
+      <c r="P179" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q179">
+        <v>59.99</v>
+      </c>
+      <c r="R179">
+        <v>10</v>
+      </c>
+      <c r="Y179" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z179" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA179" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB179" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG179" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
         <v>703</v>
       </c>
-      <c r="C178" t="s">
+      <c r="C180" t="s">
         <v>704</v>
       </c>
-      <c r="D178" t="s">
+      <c r="D180" t="s">
         <v>705</v>
       </c>
-      <c r="E178" t="s">
-        <v>33</v>
-      </c>
-      <c r="F178" t="s">
-        <v>34</v>
-      </c>
-      <c r="G178" t="s">
-        <v>35</v>
-      </c>
-      <c r="H178" t="s">
-        <v>36</v>
-      </c>
-      <c r="J178" t="s">
-        <v>54</v>
-      </c>
-      <c r="K178" t="s">
+      <c r="E180" t="s">
+        <v>33</v>
+      </c>
+      <c r="F180" t="s">
+        <v>34</v>
+      </c>
+      <c r="G180" t="s">
+        <v>35</v>
+      </c>
+      <c r="H180" t="s">
+        <v>36</v>
+      </c>
+      <c r="J180" t="s">
+        <v>54</v>
+      </c>
+      <c r="K180" t="s">
         <v>72</v>
       </c>
-      <c r="L178" t="s">
+      <c r="L180" t="s">
         <v>73</v>
       </c>
-      <c r="M178" t="s">
+      <c r="M180" t="s">
         <v>74</v>
       </c>
-      <c r="N178" t="s">
-        <v>33</v>
-      </c>
-      <c r="O178">
-        <v>1</v>
-      </c>
-      <c r="P178" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q178">
+      <c r="N180" t="s">
+        <v>33</v>
+      </c>
+      <c r="O180">
+        <v>1</v>
+      </c>
+      <c r="P180" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q180">
         <v>11.99</v>
       </c>
-      <c r="R178">
+      <c r="R180">
         <v>2</v>
       </c>
-      <c r="Y178" t="s">
+      <c r="Y180" t="s">
         <v>706</v>
       </c>
-      <c r="AA178" t="s">
+      <c r="AA180" t="s">
         <v>707</v>
       </c>
-      <c r="AB178" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD178" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG178" t="b">
+      <c r="AB180" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG180" t="b">
         <v>0</v>
       </c>
     </row>
